--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -1,24 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{572298CD-B983-4E6D-8079-5D89B6C1EDE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="212">
   <si>
-    <t>Prénom artiste</t>
-  </si>
-  <si>
     <t>Patronyme artiste</t>
   </si>
   <si>
@@ -650,13 +653,16 @@
   </si>
   <si>
     <t>Bois polychrome doré</t>
+  </si>
+  <si>
+    <t>mmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmm</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -701,18 +707,26 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -750,7 +764,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -784,6 +798,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -818,9 +833,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -993,908 +1009,911 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="41.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:22">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E2" t="s">
+        <v>118</v>
+      </c>
+      <c r="I2" t="s">
+        <v>142</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R2" t="s">
+        <v>199</v>
+      </c>
+      <c r="V2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>47</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C3" t="s">
         <v>74</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D3" t="s">
         <v>103</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
         <v>119</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I3" t="s">
         <v>143</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="R2" t="s">
+      <c r="R3" t="s">
         <v>200</v>
       </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" t="s">
+      <c r="V3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>48</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>75</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E4" t="s">
+        <v>120</v>
+      </c>
+      <c r="I4" t="s">
+        <v>144</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="R4" t="s">
+        <v>200</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
         <v>104</v>
       </c>
-      <c r="E3" t="s">
-        <v>120</v>
-      </c>
-      <c r="I3" t="s">
-        <v>144</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="R3" t="s">
+      <c r="E5" t="s">
+        <v>121</v>
+      </c>
+      <c r="I5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="R5" t="s">
+        <v>200</v>
+      </c>
+      <c r="V5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" t="s">
+        <v>104</v>
+      </c>
+      <c r="E6" t="s">
+        <v>122</v>
+      </c>
+      <c r="I6" t="s">
+        <v>146</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="R6" t="s">
+        <v>200</v>
+      </c>
+      <c r="V6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" t="s">
+        <v>123</v>
+      </c>
+      <c r="I7" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="R7" t="s">
+        <v>200</v>
+      </c>
+      <c r="V7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" t="s">
+        <v>79</v>
+      </c>
+      <c r="D8" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" t="s">
+        <v>124</v>
+      </c>
+      <c r="I8" t="s">
+        <v>148</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R8" t="s">
         <v>201</v>
       </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="V8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" t="s">
+        <v>107</v>
+      </c>
+      <c r="E9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" t="s">
+        <v>149</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="R9" t="s">
+        <v>199</v>
+      </c>
+      <c r="V9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" t="s">
         <v>121</v>
       </c>
-      <c r="I4" t="s">
-        <v>145</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="R4" t="s">
-        <v>201</v>
-      </c>
-      <c r="V4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="I10" t="s">
+        <v>150</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="R10" t="s">
+        <v>199</v>
+      </c>
+      <c r="V10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" t="s">
+        <v>151</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R11" t="s">
+        <v>202</v>
+      </c>
+      <c r="V11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" t="s">
+        <v>109</v>
+      </c>
+      <c r="E12" t="s">
+        <v>127</v>
+      </c>
+      <c r="I12" t="s">
+        <v>152</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="R12" t="s">
+        <v>200</v>
+      </c>
+      <c r="V12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E13" t="s">
+        <v>128</v>
+      </c>
+      <c r="I13" t="s">
+        <v>153</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="R13" t="s">
+        <v>203</v>
+      </c>
+      <c r="V13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" t="s">
+        <v>129</v>
+      </c>
+      <c r="I14" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="R14" t="s">
+        <v>200</v>
+      </c>
+      <c r="V14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="I15" t="s">
+        <v>155</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="R15" t="s">
+        <v>204</v>
+      </c>
+      <c r="V15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" t="s">
+        <v>87</v>
+      </c>
+      <c r="D16" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" t="s">
+        <v>131</v>
+      </c>
+      <c r="I16" t="s">
+        <v>156</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="R16" t="s">
+        <v>200</v>
+      </c>
+      <c r="V16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="I17" t="s">
+        <v>157</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="R17" t="s">
+        <v>205</v>
+      </c>
+      <c r="V17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B18" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" t="s">
+        <v>89</v>
+      </c>
+      <c r="D18" t="s">
+        <v>104</v>
+      </c>
+      <c r="E18" t="s">
+        <v>121</v>
+      </c>
+      <c r="I18" t="s">
+        <v>158</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="R18" t="s">
+        <v>199</v>
+      </c>
+      <c r="V18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>36</v>
+      </c>
+      <c r="B19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C19" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" t="s">
+        <v>121</v>
+      </c>
+      <c r="I19" t="s">
+        <v>150</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R19" t="s">
+        <v>199</v>
+      </c>
+      <c r="V19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" t="s">
+        <v>112</v>
+      </c>
+      <c r="E20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I20" t="s">
+        <v>159</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R20" t="s">
+        <v>200</v>
+      </c>
+      <c r="V20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" t="s">
+        <v>134</v>
+      </c>
+      <c r="I21" t="s">
+        <v>160</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="R21" t="s">
+        <v>206</v>
+      </c>
+      <c r="V21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" t="s">
+        <v>65</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" t="s">
+        <v>161</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="R22" t="s">
+        <v>207</v>
+      </c>
+      <c r="V22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" t="s">
+        <v>66</v>
+      </c>
+      <c r="C23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" t="s">
+        <v>114</v>
+      </c>
+      <c r="E23" t="s">
+        <v>135</v>
+      </c>
+      <c r="I23" t="s">
+        <v>162</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="R23" t="s">
+        <v>208</v>
+      </c>
+      <c r="V23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D24" t="s">
+        <v>112</v>
+      </c>
+      <c r="E24" t="s">
+        <v>136</v>
+      </c>
+      <c r="I24" t="s">
+        <v>163</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="R24" t="s">
+        <v>200</v>
+      </c>
+      <c r="V24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" t="s">
+        <v>96</v>
+      </c>
+      <c r="D25" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" t="s">
+        <v>137</v>
+      </c>
+      <c r="I25" t="s">
+        <v>164</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="R25" t="s">
+        <v>200</v>
+      </c>
+      <c r="V25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" t="s">
+        <v>138</v>
+      </c>
+      <c r="I26" t="s">
+        <v>165</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="R26" t="s">
+        <v>202</v>
+      </c>
+      <c r="V26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E27" t="s">
+        <v>139</v>
+      </c>
+      <c r="I27" t="s">
+        <v>166</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="R27" t="s">
+        <v>200</v>
+      </c>
+      <c r="V27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>99</v>
+      </c>
+      <c r="D28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
         <v>122</v>
       </c>
-      <c r="I5" t="s">
-        <v>146</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="R5" t="s">
-        <v>201</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22">
-      <c r="A6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
-      </c>
-      <c r="E6" t="s">
-        <v>123</v>
-      </c>
-      <c r="I6" t="s">
-        <v>147</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="R6" t="s">
-        <v>201</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" t="s">
-        <v>124</v>
-      </c>
-      <c r="I7" t="s">
-        <v>148</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="R7" t="s">
-        <v>201</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E8" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" t="s">
-        <v>149</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="R8" t="s">
-        <v>202</v>
-      </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>108</v>
-      </c>
-      <c r="E9" t="s">
-        <v>126</v>
-      </c>
-      <c r="I9" t="s">
-        <v>150</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="R9" t="s">
+      <c r="I28" t="s">
+        <v>167</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="R28" t="s">
         <v>200</v>
       </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E10" t="s">
-        <v>122</v>
-      </c>
-      <c r="I10" t="s">
-        <v>151</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="R10" t="s">
-        <v>200</v>
-      </c>
-      <c r="V10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>109</v>
-      </c>
-      <c r="E11" t="s">
-        <v>127</v>
-      </c>
-      <c r="I11" t="s">
-        <v>152</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="R11" t="s">
-        <v>203</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
-      <c r="A12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" t="s">
-        <v>128</v>
-      </c>
-      <c r="I12" t="s">
-        <v>153</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="R12" t="s">
-        <v>201</v>
-      </c>
-      <c r="V12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
-      <c r="A13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>129</v>
-      </c>
-      <c r="I13" t="s">
-        <v>154</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="R13" t="s">
-        <v>204</v>
-      </c>
-      <c r="V13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
-      <c r="A14" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D14" t="s">
-        <v>105</v>
-      </c>
-      <c r="E14" t="s">
-        <v>130</v>
-      </c>
-      <c r="I14" t="s">
-        <v>155</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="R14" t="s">
-        <v>201</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
-      <c r="A15" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" t="s">
-        <v>131</v>
-      </c>
-      <c r="I15" t="s">
-        <v>156</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="R15" t="s">
-        <v>205</v>
-      </c>
-      <c r="V15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
-      <c r="A16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>88</v>
-      </c>
-      <c r="D16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E16" t="s">
-        <v>132</v>
-      </c>
-      <c r="I16" t="s">
-        <v>157</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="R16" t="s">
-        <v>201</v>
-      </c>
-      <c r="V16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
-      <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D17" t="s">
-        <v>112</v>
-      </c>
-      <c r="E17" t="s">
-        <v>133</v>
-      </c>
-      <c r="I17" t="s">
-        <v>158</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="R17" t="s">
-        <v>206</v>
-      </c>
-      <c r="V17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>90</v>
-      </c>
-      <c r="D18" t="s">
-        <v>105</v>
-      </c>
-      <c r="E18" t="s">
-        <v>122</v>
-      </c>
-      <c r="I18" t="s">
-        <v>159</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="R18" t="s">
-        <v>200</v>
-      </c>
-      <c r="V18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22">
-      <c r="A19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C19" t="s">
-        <v>91</v>
-      </c>
-      <c r="D19" t="s">
-        <v>105</v>
-      </c>
-      <c r="E19" t="s">
-        <v>122</v>
-      </c>
-      <c r="I19" t="s">
-        <v>151</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="R19" t="s">
-        <v>200</v>
-      </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22">
-      <c r="A20" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" t="s">
-        <v>92</v>
-      </c>
-      <c r="D20" t="s">
-        <v>113</v>
-      </c>
-      <c r="E20" t="s">
-        <v>134</v>
-      </c>
-      <c r="I20" t="s">
-        <v>160</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="R20" t="s">
-        <v>201</v>
-      </c>
-      <c r="V20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22">
-      <c r="A21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" t="s">
-        <v>65</v>
-      </c>
-      <c r="C21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" t="s">
-        <v>114</v>
-      </c>
-      <c r="E21" t="s">
-        <v>135</v>
-      </c>
-      <c r="I21" t="s">
-        <v>161</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="R21" t="s">
-        <v>207</v>
-      </c>
-      <c r="V21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22">
-      <c r="A22" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" t="s">
-        <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E22" t="s">
-        <v>130</v>
-      </c>
-      <c r="I22" t="s">
-        <v>162</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="R22" t="s">
-        <v>208</v>
-      </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" t="s">
-        <v>136</v>
-      </c>
-      <c r="I23" t="s">
-        <v>163</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="V28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" t="s">
+        <v>100</v>
+      </c>
+      <c r="D29" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" t="s">
+        <v>140</v>
+      </c>
+      <c r="I29" t="s">
+        <v>168</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="R29" t="s">
         <v>209</v>
       </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22">
-      <c r="A24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" t="s">
-        <v>68</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" t="s">
-        <v>113</v>
-      </c>
-      <c r="E24" t="s">
-        <v>137</v>
-      </c>
-      <c r="I24" t="s">
-        <v>164</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="R24" t="s">
-        <v>201</v>
-      </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="A25" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" t="s">
-        <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" t="s">
-        <v>165</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="R25" t="s">
-        <v>201</v>
-      </c>
-      <c r="V25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="A26" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" t="s">
-        <v>98</v>
-      </c>
-      <c r="D26" t="s">
-        <v>116</v>
-      </c>
-      <c r="E26" t="s">
-        <v>139</v>
-      </c>
-      <c r="I26" t="s">
-        <v>166</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="R26" t="s">
-        <v>203</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
-      <c r="A27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B27" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" t="s">
-        <v>99</v>
-      </c>
-      <c r="D27" t="s">
-        <v>105</v>
-      </c>
-      <c r="E27" t="s">
-        <v>140</v>
-      </c>
-      <c r="I27" t="s">
-        <v>167</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="R27" t="s">
-        <v>201</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22">
-      <c r="A28" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" t="s">
-        <v>71</v>
-      </c>
-      <c r="C28" t="s">
-        <v>100</v>
-      </c>
-      <c r="D28" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" t="s">
-        <v>123</v>
-      </c>
-      <c r="I28" t="s">
-        <v>168</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="R28" t="s">
-        <v>201</v>
-      </c>
-      <c r="V28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22">
-      <c r="A29" t="s">
+      <c r="V29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>45</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>72</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>101</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>117</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>141</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I30" t="s">
         <v>169</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="K30" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="R29" t="s">
+      <c r="R30" t="s">
         <v>210</v>
-      </c>
-      <c r="V29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22">
-      <c r="A30" t="s">
-        <v>46</v>
-      </c>
-      <c r="B30" t="s">
-        <v>73</v>
-      </c>
-      <c r="C30" t="s">
-        <v>102</v>
-      </c>
-      <c r="D30" t="s">
-        <v>118</v>
-      </c>
-      <c r="E30" t="s">
-        <v>142</v>
-      </c>
-      <c r="I30" t="s">
-        <v>170</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="R30" t="s">
-        <v>211</v>
       </c>
       <c r="V30">
         <v>1</v>
@@ -1902,35 +1921,35 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1"/>
-    <hyperlink ref="K3" r:id="rId2"/>
-    <hyperlink ref="K4" r:id="rId3"/>
-    <hyperlink ref="K5" r:id="rId4"/>
-    <hyperlink ref="K6" r:id="rId5"/>
-    <hyperlink ref="K7" r:id="rId6"/>
-    <hyperlink ref="K8" r:id="rId7"/>
-    <hyperlink ref="K9" r:id="rId8"/>
-    <hyperlink ref="K10" r:id="rId9"/>
-    <hyperlink ref="K11" r:id="rId10"/>
-    <hyperlink ref="K12" r:id="rId11"/>
-    <hyperlink ref="K13" r:id="rId12"/>
-    <hyperlink ref="K14" r:id="rId13"/>
-    <hyperlink ref="K15" r:id="rId14"/>
-    <hyperlink ref="K16" r:id="rId15"/>
-    <hyperlink ref="K17" r:id="rId16"/>
-    <hyperlink ref="K18" r:id="rId17"/>
-    <hyperlink ref="K19" r:id="rId18"/>
-    <hyperlink ref="K20" r:id="rId19"/>
-    <hyperlink ref="K21" r:id="rId20"/>
-    <hyperlink ref="K22" r:id="rId21"/>
-    <hyperlink ref="K23" r:id="rId22"/>
-    <hyperlink ref="K24" r:id="rId23"/>
-    <hyperlink ref="K25" r:id="rId24"/>
-    <hyperlink ref="K26" r:id="rId25"/>
-    <hyperlink ref="K27" r:id="rId26"/>
-    <hyperlink ref="K28" r:id="rId27"/>
-    <hyperlink ref="K29" r:id="rId28"/>
-    <hyperlink ref="K30" r:id="rId29"/>
+    <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="K5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="K6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="K7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="K8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="K11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="K12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="K13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="K14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="K15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
+    <hyperlink ref="K20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
+    <hyperlink ref="K23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C180D6-1EF9-435D-92E7-C50936B86557}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AEA014-F0ED-4A0E-B532-6DD6CA92EEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="390" windowWidth="28800" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="212">
-  <si>
-    <t>mmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmmm</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="211">
   <si>
     <t>Patronyme artiste</t>
   </si>
@@ -702,9 +699,10 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -1022,920 +1020,915 @@
   <dimension ref="A1:V30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="41.7109375" customWidth="1"/>
-    <col min="16" max="16" width="1" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="41.7109375" style="1" customWidth="1"/>
+    <col min="3" max="15" width="9.140625" style="1"/>
+    <col min="16" max="16" width="1" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1" hidden="1" customWidth="1"/>
+    <col min="18" max="22" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+    </row>
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="B2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="I2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I2" t="s">
+      <c r="K2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="R2" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="R2" t="s">
+      <c r="V2" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="V2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E3" t="s">
+      <c r="I3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="I3" t="s">
+      <c r="K3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="R3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="R3" t="s">
+      <c r="V3" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="V3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="B4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I4" t="s">
+      <c r="K4" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="R4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="R4" t="s">
-        <v>37</v>
-      </c>
-      <c r="V4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="B5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I5" t="s">
+      <c r="K5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="R5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="R5" t="s">
-        <v>37</v>
-      </c>
-      <c r="V5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D6" t="s">
+      <c r="I6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V6" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="V8" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V9" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="R6" t="s">
-        <v>37</v>
-      </c>
-      <c r="V6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" t="s">
-        <v>62</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="R7" t="s">
-        <v>37</v>
-      </c>
-      <c r="V7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E8" t="s">
-        <v>68</v>
-      </c>
-      <c r="I8" t="s">
-        <v>69</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" t="s">
+      <c r="I10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V10" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="V11" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V12" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="V13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V14" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="V15" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="V17" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V18" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="V19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="V21" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="V22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="V23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V24" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V25" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="V26" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="V8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>76</v>
-      </c>
-      <c r="I9" t="s">
-        <v>77</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R9" t="s">
-        <v>29</v>
-      </c>
-      <c r="V9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" t="s">
-        <v>48</v>
-      </c>
-      <c r="I10" t="s">
-        <v>81</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="R10" t="s">
-        <v>29</v>
-      </c>
-      <c r="V10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" t="s">
-        <v>84</v>
-      </c>
-      <c r="C11" t="s">
-        <v>85</v>
-      </c>
-      <c r="D11" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" t="s">
-        <v>87</v>
-      </c>
-      <c r="I11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="R11" t="s">
-        <v>90</v>
-      </c>
-      <c r="V11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E12" t="s">
-        <v>95</v>
-      </c>
-      <c r="I12" t="s">
-        <v>96</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="R12" t="s">
-        <v>37</v>
-      </c>
-      <c r="V12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>30</v>
-      </c>
-      <c r="B13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>100</v>
-      </c>
-      <c r="I13" t="s">
-        <v>101</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="R13" t="s">
-        <v>103</v>
-      </c>
-      <c r="V13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>104</v>
-      </c>
-      <c r="B14" t="s">
-        <v>98</v>
-      </c>
-      <c r="C14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D14" t="s">
-        <v>47</v>
-      </c>
-      <c r="E14" t="s">
-        <v>106</v>
-      </c>
-      <c r="I14" t="s">
-        <v>107</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="R14" t="s">
-        <v>37</v>
-      </c>
-      <c r="V14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>109</v>
-      </c>
-      <c r="B15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E15" t="s">
-        <v>112</v>
-      </c>
-      <c r="I15" t="s">
-        <v>113</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="R15" t="s">
-        <v>115</v>
-      </c>
-      <c r="V15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>116</v>
-      </c>
-      <c r="B16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C16" t="s">
-        <v>118</v>
-      </c>
-      <c r="D16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" t="s">
-        <v>120</v>
-      </c>
-      <c r="I16" t="s">
-        <v>121</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="R16" t="s">
-        <v>37</v>
-      </c>
-      <c r="V16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>123</v>
-      </c>
-      <c r="B17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C17" t="s">
-        <v>125</v>
-      </c>
-      <c r="D17" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" t="s">
-        <v>127</v>
-      </c>
-      <c r="I17" t="s">
-        <v>128</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="R17" t="s">
-        <v>130</v>
-      </c>
-      <c r="V17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>131</v>
-      </c>
-      <c r="B18" t="s">
-        <v>132</v>
-      </c>
-      <c r="C18" t="s">
-        <v>133</v>
-      </c>
-      <c r="D18" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" t="s">
-        <v>134</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="R18" t="s">
-        <v>29</v>
-      </c>
-      <c r="V18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>136</v>
-      </c>
-      <c r="B19" t="s">
-        <v>137</v>
-      </c>
-      <c r="C19" t="s">
-        <v>138</v>
-      </c>
-      <c r="D19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" t="s">
-        <v>81</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="R19" t="s">
-        <v>29</v>
-      </c>
-      <c r="V19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>140</v>
-      </c>
-      <c r="B20" t="s">
-        <v>141</v>
-      </c>
-      <c r="C20" t="s">
-        <v>142</v>
-      </c>
-      <c r="D20" t="s">
-        <v>143</v>
-      </c>
-      <c r="E20" t="s">
-        <v>144</v>
-      </c>
-      <c r="I20" t="s">
-        <v>145</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="R20" t="s">
-        <v>37</v>
-      </c>
-      <c r="V20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>147</v>
-      </c>
-      <c r="B21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C21" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" t="s">
-        <v>150</v>
-      </c>
-      <c r="E21" t="s">
-        <v>151</v>
-      </c>
-      <c r="I21" t="s">
-        <v>152</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="R21" t="s">
-        <v>154</v>
-      </c>
-      <c r="V21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B22" t="s">
-        <v>156</v>
-      </c>
-      <c r="C22" t="s">
-        <v>157</v>
-      </c>
-      <c r="D22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E22" t="s">
-        <v>106</v>
-      </c>
-      <c r="I22" t="s">
-        <v>158</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="R22" t="s">
-        <v>160</v>
-      </c>
-      <c r="V22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>161</v>
-      </c>
-      <c r="B23" t="s">
-        <v>162</v>
-      </c>
-      <c r="C23" t="s">
-        <v>163</v>
-      </c>
-      <c r="D23" t="s">
-        <v>164</v>
-      </c>
-      <c r="E23" t="s">
-        <v>165</v>
-      </c>
-      <c r="I23" t="s">
-        <v>166</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="R23" t="s">
-        <v>168</v>
-      </c>
-      <c r="V23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>123</v>
-      </c>
-      <c r="B24" t="s">
-        <v>169</v>
-      </c>
-      <c r="C24" t="s">
-        <v>170</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>171</v>
-      </c>
-      <c r="I24" t="s">
-        <v>172</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="R24" t="s">
-        <v>37</v>
-      </c>
-      <c r="V24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>174</v>
-      </c>
-      <c r="B25" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" t="s">
-        <v>176</v>
-      </c>
-      <c r="D25" t="s">
-        <v>25</v>
-      </c>
-      <c r="E25" t="s">
-        <v>177</v>
-      </c>
-      <c r="I25" t="s">
-        <v>178</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="R25" t="s">
-        <v>37</v>
-      </c>
-      <c r="V25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>180</v>
-      </c>
-      <c r="B26" t="s">
-        <v>181</v>
-      </c>
-      <c r="C26" t="s">
-        <v>182</v>
-      </c>
-      <c r="D26" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" t="s">
-        <v>185</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="B27" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="R26" t="s">
-        <v>90</v>
-      </c>
-      <c r="V26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>72</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C27" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="D27" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="I27" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="I27" t="s">
+      <c r="K27" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="R27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V27" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="R27" t="s">
-        <v>37</v>
-      </c>
-      <c r="V27">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B28" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B28" t="s">
-        <v>187</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="D28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="D28" t="s">
-        <v>47</v>
-      </c>
-      <c r="E28" t="s">
-        <v>54</v>
-      </c>
-      <c r="I28" t="s">
+      <c r="K28" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="R28" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V28" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="R28" t="s">
-        <v>37</v>
-      </c>
-      <c r="V28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="B29" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="E29" t="s">
+      <c r="I29" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="I29" t="s">
+      <c r="K29" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="R29" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="R29" t="s">
+      <c r="V29" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="V29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="B30" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E30" t="s">
+      <c r="I30" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="I30" t="s">
+      <c r="K30" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="R30" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="R30" t="s">
-        <v>211</v>
-      </c>
-      <c r="V30">
+      <c r="V30" s="1">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:V30">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>IFERROR(--$V2,0)=1</formula>
-    </cfRule>
-  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AEA014-F0ED-4A0E-B532-6DD6CA92EEB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D57B177-C665-494C-B3C9-8002255AE012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="306">
   <si>
     <t>Patronyme artiste</t>
   </si>
@@ -493,12 +493,6 @@
     <t>1425-1452</t>
   </si>
   <si>
-    <t>"La Porte du Paradis"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/9e/Firenze_Battistero_Porta_Ghiberti_detta_del_Paradiso.jpg/1280px-Firenze_Battistero_Porta_Ghiberti_detta_del_Paradiso.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Bronze doré</t>
   </si>
   <si>
@@ -653,6 +647,297 @@
   </si>
   <si>
     <t>Bois polychrome doré</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David </t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Ronde-bosse</t>
+  </si>
+  <si>
+    <t>158 cm</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1408-1409</t>
+  </si>
+  <si>
+    <t>David in marmo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>191 cm</t>
+  </si>
+  <si>
+    <t>1415-1417</t>
+  </si>
+  <si>
+    <t>Saint Georges</t>
+  </si>
+  <si>
+    <t>San Giorgio</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>209 cm</t>
+  </si>
+  <si>
+    <t>1411-1413</t>
+  </si>
+  <si>
+    <t>Église d'Orsanmichele</t>
+  </si>
+  <si>
+    <t>Saint Marc</t>
+  </si>
+  <si>
+    <t>San Marco</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>236 cm</t>
+  </si>
+  <si>
+    <t>1423-1425</t>
+  </si>
+  <si>
+    <t>Baptistère San Giovanni</t>
+  </si>
+  <si>
+    <t>Le Festin d'Hérode</t>
+  </si>
+  <si>
+    <t>Banchetto di Erode</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Fontaine baptismale du baptistère de Sienne</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Fonte_battesimale_di_Siena.jpg/960px-Fonte_battesimale_di_Siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bas-relief</t>
+  </si>
+  <si>
+    <t>60 cm</t>
+  </si>
+  <si>
+    <t>1435 environ</t>
+  </si>
+  <si>
+    <t>Annonciation Cavalcanti</t>
+  </si>
+  <si>
+    <t>Annunciazione Cavalcanti</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg/960px-Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Pierre sereine dorée, putti en terre cuite</t>
+  </si>
+  <si>
+    <t>1445-1453</t>
+  </si>
+  <si>
+    <t>Padoue</t>
+  </si>
+  <si>
+    <t>Piazza del Santo</t>
+  </si>
+  <si>
+    <t>Monument équestre à Gattamelata</t>
+  </si>
+  <si>
+    <t>Monumento equestre al Gattamelata</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>340 cm</t>
+  </si>
+  <si>
+    <t>390 cm</t>
+  </si>
+  <si>
+    <t>1453-1455</t>
+  </si>
+  <si>
+    <t>Madeleine pénitente</t>
+  </si>
+  <si>
+    <t>Maddalena penitente</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Donatello%2C_maria_maddalena_02.JPG/960px-Donatello%2C_maria_maddalena_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bois de peuplier polychrome</t>
+  </si>
+  <si>
+    <t>188 cm</t>
+  </si>
+  <si>
+    <t>La Porte du Paradis</t>
+  </si>
+  <si>
+    <t>Porta del Paradiso</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>520 cm</t>
+  </si>
+  <si>
+    <t>310 cm</t>
+  </si>
+  <si>
+    <t>1403-1424</t>
+  </si>
+  <si>
+    <t>Porte Nord du Baptistère</t>
+  </si>
+  <si>
+    <t>Porta nord du battistero</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>460 cm</t>
+  </si>
+  <si>
+    <t>270 cm</t>
+  </si>
+  <si>
+    <t>1412-1416</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Saint Jean-Baptiste</t>
+  </si>
+  <si>
+    <t>San Giovanni Battista</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Albizzo di Piero en 1414</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>255 cm</t>
+  </si>
+  <si>
+    <t>1419-1423</t>
+  </si>
+  <si>
+    <t>Saint Matthieu</t>
+  </si>
+  <si>
+    <t>San Matteo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Copie installée en 2005 sur la façade de l'Eglise Orsanmichele dans le tabernacle  sculpté par Lorenzo Ghiberti en 1414</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1425-1429</t>
+  </si>
+  <si>
+    <t>Saint Étienne</t>
+  </si>
+  <si>
+    <t>Sant'Stefano</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Andrea Pisano en 1340</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5c/St_Stephen_Ghiberti_Orsanmichele.jpg/960px-St_Stephen_Ghiberti_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>242 cm</t>
+  </si>
+  <si>
+    <t>1417-1427</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Baptême du Christ </t>
+  </si>
+  <si>
+    <t>Battesimo di Cristo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>L'Arrestation de Saint Jean-Baptiste</t>
+  </si>
+  <si>
+    <t>Cattura di San Giovanni Battista</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1432-1442</t>
+  </si>
+  <si>
+    <t>Cathédrale Santa Maria del Fiore</t>
+  </si>
+  <si>
+    <t>Chapelle de Saint Zenobe</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Châsse de Saint Zenobe</t>
+  </si>
+  <si>
+    <t>Arca di san Zanobi</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -701,23 +986,16 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFC6E0B4"/>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1017,914 +1295,1548 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:V44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="1"/>
-    <col min="2" max="2" width="41.7109375" style="1" customWidth="1"/>
-    <col min="3" max="15" width="9.140625" style="1"/>
-    <col min="16" max="16" width="1" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.140625" style="1" hidden="1" customWidth="1"/>
-    <col min="18" max="22" width="9.140625" style="1"/>
+    <col min="1" max="1" width="17.140625" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="16" max="16" width="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="22" max="22" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B1" s="1" t="s">
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" t="s">
         <v>28</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>34</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="1">
+      <c r="V3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="A4" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>39</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" t="s">
         <v>41</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="R4" t="s">
         <v>36</v>
       </c>
-      <c r="V4" s="1">
+      <c r="V4" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="K5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="R5" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="1">
+      <c r="V5" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="A6" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="R6" t="s">
         <v>36</v>
       </c>
-      <c r="V6" s="1">
+      <c r="V6" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" t="s">
         <v>59</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" t="s">
         <v>61</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="R7" s="1" t="s">
+      <c r="R7" t="s">
         <v>36</v>
       </c>
-      <c r="V7" s="1">
+      <c r="V7" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="A8" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>64</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" t="s">
         <v>67</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" t="s">
         <v>68</v>
       </c>
-      <c r="K8" s="2" t="s">
+      <c r="K8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="R8" s="1" t="s">
+      <c r="R8" t="s">
         <v>70</v>
       </c>
-      <c r="V8" s="1">
+      <c r="V8" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="A9" t="s">
         <v>71</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>72</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" t="s">
         <v>75</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" t="s">
         <v>76</v>
       </c>
-      <c r="K9" s="2" t="s">
+      <c r="K9" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="1" t="s">
+      <c r="R9" t="s">
         <v>28</v>
       </c>
-      <c r="V9" s="1">
+      <c r="V9" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" t="s">
         <v>29</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>78</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" t="s">
         <v>47</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" t="s">
         <v>80</v>
       </c>
-      <c r="K10" s="2" t="s">
+      <c r="K10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="R10" s="1" t="s">
+      <c r="R10" t="s">
         <v>28</v>
       </c>
-      <c r="V10" s="1">
+      <c r="V10" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" t="s">
         <v>86</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" t="s">
         <v>87</v>
       </c>
-      <c r="K11" s="2" t="s">
+      <c r="K11" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="R11" s="1" t="s">
+      <c r="R11" t="s">
         <v>89</v>
       </c>
-      <c r="V11" s="1">
+      <c r="V11" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>91</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" t="s">
         <v>93</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" t="s">
         <v>94</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" t="s">
         <v>95</v>
       </c>
-      <c r="K12" s="2" t="s">
+      <c r="K12" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="R12" s="1" t="s">
+      <c r="R12" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="1">
+      <c r="V12" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>97</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" t="s">
         <v>99</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" t="s">
         <v>100</v>
       </c>
-      <c r="K13" s="2" t="s">
+      <c r="K13" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="R13" s="1" t="s">
+      <c r="R13" t="s">
         <v>102</v>
       </c>
-      <c r="V13" s="1">
+      <c r="V13" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>97</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" t="s">
         <v>46</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" t="s">
         <v>105</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" t="s">
         <v>106</v>
       </c>
-      <c r="K14" s="2" t="s">
+      <c r="K14" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="R14" s="1" t="s">
+      <c r="R14" t="s">
         <v>36</v>
       </c>
-      <c r="V14" s="1">
+      <c r="V14" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" t="s">
         <v>108</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>109</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" t="s">
         <v>110</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" t="s">
         <v>111</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" t="s">
         <v>112</v>
       </c>
-      <c r="K15" s="2" t="s">
+      <c r="K15" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="R15" s="1" t="s">
+      <c r="R15" t="s">
         <v>114</v>
       </c>
-      <c r="V15" s="1">
+      <c r="V15" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" t="s">
         <v>115</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>116</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" t="s">
         <v>117</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" t="s">
         <v>118</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" t="s">
         <v>119</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" t="s">
         <v>120</v>
       </c>
-      <c r="K16" s="2" t="s">
+      <c r="K16" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="R16" s="1" t="s">
+      <c r="R16" t="s">
         <v>36</v>
       </c>
-      <c r="V16" s="1">
+      <c r="V16" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="A17" t="s">
         <v>122</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>123</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" t="s">
         <v>126</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" t="s">
         <v>127</v>
       </c>
-      <c r="K17" s="2" t="s">
+      <c r="K17" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="R17" t="s">
         <v>129</v>
       </c>
-      <c r="V17" s="1">
+      <c r="V17" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="A18" t="s">
         <v>130</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>131</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" t="s">
         <v>132</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" t="s">
         <v>47</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" t="s">
         <v>133</v>
       </c>
-      <c r="K18" s="2" t="s">
+      <c r="K18" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="R18" s="1" t="s">
+      <c r="R18" t="s">
         <v>28</v>
       </c>
-      <c r="V18" s="1">
+      <c r="V18" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="A19" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>136</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" t="s">
         <v>137</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" t="s">
         <v>47</v>
       </c>
-      <c r="I19" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="K19" s="2" t="s">
+      <c r="I19" t="s">
+        <v>209</v>
+      </c>
+      <c r="J19" t="s">
+        <v>210</v>
+      </c>
+      <c r="K19" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="R19" s="1" t="s">
+      <c r="Q19" t="s">
+        <v>211</v>
+      </c>
+      <c r="R19" t="s">
         <v>28</v>
       </c>
-      <c r="V19" s="1">
+      <c r="S19" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="T19" s="2">
+        <v>51</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B20" t="s">
+        <v>136</v>
+      </c>
+      <c r="C20" t="s">
+        <v>214</v>
+      </c>
+      <c r="D20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E20" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" t="s">
+        <v>209</v>
+      </c>
+      <c r="J20" t="s">
+        <v>215</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>211</v>
+      </c>
+      <c r="R20" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T20" s="2">
+        <v>57</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" t="s">
+        <v>218</v>
+      </c>
+      <c r="D21" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
+      <c r="I21" t="s">
+        <v>219</v>
+      </c>
+      <c r="J21" t="s">
+        <v>220</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>211</v>
+      </c>
+      <c r="R21" t="s">
+        <v>36</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="T21" s="2"/>
+      <c r="V21" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" t="s">
+        <v>223</v>
+      </c>
+      <c r="D22" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" t="s">
+        <v>224</v>
+      </c>
+      <c r="I22" t="s">
+        <v>225</v>
+      </c>
+      <c r="J22" t="s">
+        <v>226</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>211</v>
+      </c>
+      <c r="R22" t="s">
+        <v>36</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="T22" s="2"/>
+      <c r="V22" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>229</v>
+      </c>
+      <c r="D23" t="s">
+        <v>93</v>
+      </c>
+      <c r="E23" t="s">
+        <v>230</v>
+      </c>
+      <c r="I23" t="s">
+        <v>231</v>
+      </c>
+      <c r="J23" t="s">
+        <v>232</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s">
+        <v>234</v>
+      </c>
+      <c r="M23" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>236</v>
+      </c>
+      <c r="R23" t="s">
+        <v>157</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>135</v>
+      </c>
+      <c r="B24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C24" t="s">
+        <v>238</v>
+      </c>
+      <c r="D24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" t="s">
+        <v>239</v>
+      </c>
+      <c r="J24" t="s">
+        <v>240</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="R24" t="s">
+        <v>242</v>
+      </c>
+      <c r="S24" s="2">
+        <v>420</v>
+      </c>
+      <c r="T24" s="2">
+        <v>274</v>
+      </c>
+      <c r="U24">
+        <v>30</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" t="s">
+        <v>243</v>
+      </c>
+      <c r="D25" t="s">
+        <v>244</v>
+      </c>
+      <c r="E25" t="s">
+        <v>245</v>
+      </c>
+      <c r="I25" t="s">
+        <v>246</v>
+      </c>
+      <c r="J25" t="s">
+        <v>247</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="R25" t="s">
+        <v>28</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" t="s">
+        <v>251</v>
+      </c>
+      <c r="D26" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" t="s">
+        <v>105</v>
+      </c>
+      <c r="I26" t="s">
+        <v>252</v>
+      </c>
+      <c r="J26" t="s">
+        <v>253</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="R26" t="s">
+        <v>255</v>
+      </c>
+      <c r="S26" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="T26" s="2"/>
+      <c r="V26" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>139</v>
+      </c>
+      <c r="B27" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" t="s">
+        <v>142</v>
+      </c>
+      <c r="E27" t="s">
+        <v>143</v>
+      </c>
+      <c r="I27" t="s">
+        <v>144</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="R27" t="s">
+        <v>36</v>
+      </c>
+      <c r="V27" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="1" t="s">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C28" t="s">
+        <v>148</v>
+      </c>
+      <c r="D28" t="s">
+        <v>149</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="I28" t="s">
+        <v>151</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="R28" t="s">
+        <v>153</v>
+      </c>
+      <c r="V28" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>154</v>
+      </c>
+      <c r="B29" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" t="s">
+        <v>46</v>
+      </c>
+      <c r="E29" t="s">
+        <v>105</v>
+      </c>
+      <c r="I29" t="s">
+        <v>257</v>
+      </c>
+      <c r="J29" t="s">
+        <v>258</v>
+      </c>
+      <c r="K29" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="O29" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>236</v>
+      </c>
+      <c r="R29" t="s">
+        <v>157</v>
+      </c>
+      <c r="S29" t="s">
+        <v>262</v>
+      </c>
+      <c r="T29" t="s">
+        <v>263</v>
+      </c>
+      <c r="U29">
+        <v>11</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>154</v>
+      </c>
+      <c r="B30" t="s">
+        <v>155</v>
+      </c>
+      <c r="C30" t="s">
+        <v>264</v>
+      </c>
+      <c r="D30" t="s">
+        <v>46</v>
+      </c>
+      <c r="E30" t="s">
+        <v>105</v>
+      </c>
+      <c r="I30" t="s">
+        <v>265</v>
+      </c>
+      <c r="J30" t="s">
+        <v>266</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>236</v>
+      </c>
+      <c r="R30" t="s">
+        <v>28</v>
+      </c>
+      <c r="S30" t="s">
+        <v>268</v>
+      </c>
+      <c r="T30" t="s">
+        <v>269</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>154</v>
+      </c>
+      <c r="B31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C31" t="s">
+        <v>270</v>
+      </c>
+      <c r="D31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E31" t="s">
+        <v>224</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I31" t="s">
+        <v>272</v>
+      </c>
+      <c r="J31" t="s">
+        <v>273</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L31" t="s">
+        <v>275</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>211</v>
+      </c>
+      <c r="R31" t="s">
+        <v>28</v>
+      </c>
+      <c r="S31" t="s">
+        <v>277</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>154</v>
+      </c>
+      <c r="B32" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" t="s">
+        <v>278</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>224</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I32" t="s">
+        <v>279</v>
+      </c>
+      <c r="J32" t="s">
+        <v>280</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="L32" t="s">
+        <v>282</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>211</v>
+      </c>
+      <c r="R32" t="s">
+        <v>28</v>
+      </c>
+      <c r="S32" t="s">
+        <v>269</v>
+      </c>
+      <c r="V32" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>154</v>
+      </c>
+      <c r="B33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" t="s">
+        <v>284</v>
+      </c>
+      <c r="D33" t="s">
+        <v>46</v>
+      </c>
+      <c r="E33" t="s">
+        <v>224</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I33" t="s">
+        <v>285</v>
+      </c>
+      <c r="J33" t="s">
+        <v>286</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="L33" t="s">
+        <v>288</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>211</v>
+      </c>
+      <c r="R33" t="s">
+        <v>28</v>
+      </c>
+      <c r="S33" t="s">
+        <v>290</v>
+      </c>
+      <c r="V33" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>154</v>
+      </c>
+      <c r="B34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C34" t="s">
+        <v>291</v>
+      </c>
+      <c r="D34" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" t="s">
+        <v>230</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="I34" t="s">
+        <v>293</v>
+      </c>
+      <c r="J34" t="s">
+        <v>294</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>236</v>
+      </c>
+      <c r="R34" t="s">
+        <v>157</v>
+      </c>
+      <c r="S34" t="s">
+        <v>237</v>
+      </c>
+      <c r="T34" t="s">
+        <v>237</v>
+      </c>
+      <c r="V34" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>154</v>
+      </c>
+      <c r="B35" t="s">
+        <v>155</v>
+      </c>
+      <c r="C35" t="s">
+        <v>291</v>
+      </c>
+      <c r="D35" t="s">
+        <v>93</v>
+      </c>
+      <c r="E35" t="s">
+        <v>230</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="I35" t="s">
+        <v>296</v>
+      </c>
+      <c r="J35" t="s">
+        <v>297</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>236</v>
+      </c>
+      <c r="R35" t="s">
+        <v>157</v>
+      </c>
+      <c r="S35" t="s">
+        <v>237</v>
+      </c>
+      <c r="T35" t="s">
+        <v>237</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>154</v>
+      </c>
+      <c r="B36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C36" t="s">
+        <v>299</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>300</v>
+      </c>
+      <c r="G36" t="s">
+        <v>301</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="I36" t="s">
+        <v>303</v>
+      </c>
+      <c r="J36" t="s">
+        <v>304</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>236</v>
+      </c>
+      <c r="R36" t="s">
+        <v>28</v>
+      </c>
+      <c r="S36">
+        <v>85</v>
+      </c>
+      <c r="T36">
+        <v>193</v>
+      </c>
+      <c r="V36" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" t="s">
+        <v>162</v>
+      </c>
+      <c r="I37" t="s">
+        <v>163</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="R37" t="s">
+        <v>165</v>
+      </c>
+      <c r="V37" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" t="s">
+        <v>166</v>
+      </c>
+      <c r="C38" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38" t="s">
         <v>142</v>
       </c>
-      <c r="E20" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="R20" s="1" t="s">
+      <c r="E38" t="s">
+        <v>168</v>
+      </c>
+      <c r="I38" t="s">
+        <v>169</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="R38" t="s">
         <v>36</v>
       </c>
-      <c r="V20" s="1">
+      <c r="V38" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="V21" s="1">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>171</v>
+      </c>
+      <c r="B39" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" t="s">
+        <v>173</v>
+      </c>
+      <c r="D39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" t="s">
+        <v>174</v>
+      </c>
+      <c r="I39" t="s">
+        <v>175</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="R39" t="s">
+        <v>36</v>
+      </c>
+      <c r="V39" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="D22" s="1" t="s">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>177</v>
+      </c>
+      <c r="B40" t="s">
+        <v>178</v>
+      </c>
+      <c r="C40" t="s">
+        <v>179</v>
+      </c>
+      <c r="D40" t="s">
+        <v>180</v>
+      </c>
+      <c r="E40" t="s">
+        <v>181</v>
+      </c>
+      <c r="I40" t="s">
+        <v>182</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="R40" t="s">
+        <v>89</v>
+      </c>
+      <c r="V40" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>71</v>
+      </c>
+      <c r="B41" t="s">
+        <v>184</v>
+      </c>
+      <c r="C41" t="s">
+        <v>185</v>
+      </c>
+      <c r="D41" t="s">
         <v>46</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="V22" s="1">
+      <c r="E41" t="s">
+        <v>186</v>
+      </c>
+      <c r="I41" t="s">
+        <v>187</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="R41" t="s">
+        <v>36</v>
+      </c>
+      <c r="V41" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="V23" s="1">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" t="s">
+        <v>184</v>
+      </c>
+      <c r="C42" t="s">
+        <v>190</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" t="s">
+        <v>53</v>
+      </c>
+      <c r="I42" t="s">
+        <v>191</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="R42" t="s">
+        <v>36</v>
+      </c>
+      <c r="V42" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V24" s="1">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>193</v>
+      </c>
+      <c r="B43" t="s">
+        <v>194</v>
+      </c>
+      <c r="C43" t="s">
+        <v>195</v>
+      </c>
+      <c r="D43" t="s">
+        <v>196</v>
+      </c>
+      <c r="E43" t="s">
+        <v>197</v>
+      </c>
+      <c r="I43" t="s">
+        <v>198</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="R43" t="s">
+        <v>200</v>
+      </c>
+      <c r="V43" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="V26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K28" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="V28" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="K29" s="2" t="s">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
         <v>201</v>
       </c>
-      <c r="R29" s="1" t="s">
+      <c r="B44" t="s">
         <v>202</v>
       </c>
-      <c r="V29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
+      <c r="C44" t="s">
         <v>203</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="D44" t="s">
         <v>204</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="E44" t="s">
         <v>205</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="I44" t="s">
         <v>206</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="K44" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="R44" t="s">
         <v>208</v>
       </c>
-      <c r="K30" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="V30" s="1">
+      <c r="V44" s="2">
         <v>1</v>
       </c>
     </row>
@@ -1947,18 +2859,44 @@
     <hyperlink ref="K16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
     <hyperlink ref="K17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
     <hyperlink ref="K18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K19" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000011000000}"/>
-    <hyperlink ref="K20" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K21" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K22" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="K23" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K24" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K25" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K26" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K27" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K28" r:id="rId27" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K29" r:id="rId28" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K30" r:id="rId29" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K41" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K42" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K43" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
+    <hyperlink ref="K44" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K40" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K39" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K37" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K19" r:id="rId28" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
+    <hyperlink ref="K20" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
+    <hyperlink ref="K21" r:id="rId30" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
+    <hyperlink ref="K22" r:id="rId31" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
+    <hyperlink ref="K23" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
+    <hyperlink ref="M23" r:id="rId33" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
+    <hyperlink ref="K24" r:id="rId34" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
+    <hyperlink ref="K25" r:id="rId35" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
+    <hyperlink ref="K26" r:id="rId36" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
+    <hyperlink ref="K29" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
+    <hyperlink ref="M29" r:id="rId38" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
+    <hyperlink ref="O29" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
+    <hyperlink ref="K30" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
+    <hyperlink ref="M30" r:id="rId41" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
+    <hyperlink ref="K31" r:id="rId42" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
+    <hyperlink ref="M31" r:id="rId43" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
+    <hyperlink ref="K32" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
+    <hyperlink ref="F31" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
+    <hyperlink ref="F32:F33" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
+    <hyperlink ref="M32" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
+    <hyperlink ref="M33" r:id="rId48" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
+    <hyperlink ref="K33" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
+    <hyperlink ref="K34" r:id="rId50" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
+    <hyperlink ref="F34" r:id="rId51" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
+    <hyperlink ref="F35" r:id="rId52" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
+    <hyperlink ref="K35" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
+    <hyperlink ref="K36" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
+    <hyperlink ref="H36" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D57B177-C665-494C-B3C9-8002255AE012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05740131-6CC6-4247-945F-E71C80A2BE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="502">
   <si>
     <t>Patronyme artiste</t>
   </si>
@@ -205,9 +218,6 @@
     <t>Bode-Museum</t>
   </si>
   <si>
-    <t>"Buste de Marietta Strozzi"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG/1280px-Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -262,12 +272,6 @@
     <t>1473-1475</t>
   </si>
   <si>
-    <t>"David (bronze)"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Niccolò</t>
   </si>
   <si>
@@ -307,9 +311,6 @@
     <t>Piazza del Campo</t>
   </si>
   <si>
-    <t>"La Fonte Gaia"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -340,9 +341,6 @@
     <t>Museo dell'Opera del Duomo</t>
   </si>
   <si>
-    <t>"La Cantoria"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -601,30 +599,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Claus</t>
-  </si>
-  <si>
-    <t>SLUTER</t>
-  </si>
-  <si>
-    <t>1395-1403</t>
-  </si>
-  <si>
-    <t>Dijon</t>
-  </si>
-  <si>
-    <t>Chartreuse de Champmol</t>
-  </si>
-  <si>
-    <t>"Le Puits de Moïse (détail : le prophète Isaïe)"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/f4/Dijon_%28C%C3%B4te-d%27Or%29_-_Puits_de_Mo%C3%AFse_-_Isa%C3%AFe.jpg/1280px-Dijon_%28C%C3%B4te-d%27Or%29_-_Puits_de_Mo%C3%AFse_-_Isa%C3%AFe.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Pierre calcaire polychrome</t>
-  </si>
-  <si>
     <t>Veit</t>
   </si>
   <si>
@@ -938,6 +912,633 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg</t>
+  </si>
+  <si>
+    <t>126 cm</t>
+  </si>
+  <si>
+    <t>1467-1483</t>
+  </si>
+  <si>
+    <t>L'Incrédulité de saint Thomas</t>
+  </si>
+  <si>
+    <t>Incredulità di san Tommaso</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Copie installée en 1992 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Donatello et Michelozzo en 1423</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg/960px-Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Groupe Ronde-bosse</t>
+  </si>
+  <si>
+    <t>230 cm</t>
+  </si>
+  <si>
+    <t>1480-1488</t>
+  </si>
+  <si>
+    <t>Campo Santi Giovanni e Paolo</t>
+  </si>
+  <si>
+    <t>Monument équestre à Bartolomeo Colleoni</t>
+  </si>
+  <si>
+    <t>Monumento a Bartolomeo Colleoni</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue équestre</t>
+  </si>
+  <si>
+    <t>395 cm</t>
+  </si>
+  <si>
+    <t>vers 1470</t>
+  </si>
+  <si>
+    <t>Palazzo Vecchio</t>
+  </si>
+  <si>
+    <t>Enfant au dauphin</t>
+  </si>
+  <si>
+    <t>Putto con delfino</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Putto_col_delfino_di_verrocchio_02.JPG/960px-Putto_col_delfino_di_verrocchio_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Copie en bronze installée en 1959 dans le cortile de Palazzo Vacchio conçu par Michelozzo en 1453. La fontaine a été conçue par Vasari en 1555.</t>
+  </si>
+  <si>
+    <t>Statue de fontaine</t>
+  </si>
+  <si>
+    <t>67 cm</t>
+  </si>
+  <si>
+    <t>1475</t>
+  </si>
+  <si>
+    <t>Dame au bouquet</t>
+  </si>
+  <si>
+    <t>Dama col mazzolino</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Buste</t>
+  </si>
+  <si>
+    <t>1469-1472</t>
+  </si>
+  <si>
+    <t>Basilique San Lorenzo</t>
+  </si>
+  <si>
+    <t>Vieille Sacristie</t>
+  </si>
+  <si>
+    <t>Tombeau de Pierre et Jean de Médicis</t>
+  </si>
+  <si>
+    <t>Tomba di Piero e Giovanni de' Medici</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monument funéraire</t>
+  </si>
+  <si>
+    <t>Marbre, bronze et porphyre</t>
+  </si>
+  <si>
+    <t>vers 1475</t>
+  </si>
+  <si>
+    <t>Buste de Giuliano de' Medici</t>
+  </si>
+  <si>
+    <t>Busto di Giuliano de' Medici</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Verrocchio%2C_giuliano_de%27_medici%2C_1475-78.JPG/1280px-Verrocchio%2C_giuliano_de%27_medici%2C_1475-78.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Terre cuite peinte</t>
+  </si>
+  <si>
+    <t>61 cm</t>
+  </si>
+  <si>
+    <t>1478-1480</t>
+  </si>
+  <si>
+    <t>Décollation de saint Jean-Baptiste</t>
+  </si>
+  <si>
+    <t>Decollazione del Battista</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Beheading_of_Saint_John.jpg/1280px-Beheading_of_Saint_John.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Autel d'argent de San Giovanni</t>
+  </si>
+  <si>
+    <t>Argent</t>
+  </si>
+  <si>
+    <t>31 cm</t>
+  </si>
+  <si>
+    <t>42 cm</t>
+  </si>
+  <si>
+    <t>La Cantoria</t>
+  </si>
+  <si>
+    <t>Cantoria</t>
+  </si>
+  <si>
+    <t>328 cm</t>
+  </si>
+  <si>
+    <t>560 cm</t>
+  </si>
+  <si>
+    <t>1442-1444</t>
+  </si>
+  <si>
+    <t>La Résurrection</t>
+  </si>
+  <si>
+    <t>Resurrezione di Cristo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Terre cuite émaillée</t>
+  </si>
+  <si>
+    <t>1446-1475</t>
+  </si>
+  <si>
+    <t>Porte en bronze de la Sacristie</t>
+  </si>
+  <si>
+    <t>Porta della Sacrestia delle Messe</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1454-1455</t>
+  </si>
+  <si>
+    <t>Basilique San Miniato al Monte</t>
+  </si>
+  <si>
+    <t>Tombeau du cardinal du Portugal</t>
+  </si>
+  <si>
+    <t>Monumento funebre del cardinale del Portogallo</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/A_Rossellino_Tumba_del_Cardenal_de_Portugal_San_Miniato_Florencia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Marbre et terre cuite</t>
+  </si>
+  <si>
+    <t>Les Quatre Vertus Cardinales</t>
+  </si>
+  <si>
+    <t>Le quattro virtù cardinali</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>Impruneta</t>
+  </si>
+  <si>
+    <t>Collegiata di Santa Maria Impruneta</t>
+  </si>
+  <si>
+    <t>Tabernacle de la Sainte Croix</t>
+  </si>
+  <si>
+    <t>Tabernacolo della Santa Croce</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Spedale degli Innocenti</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Spedale_innocenti%2C_veduta_01.JPG/1280px-Spedale_innocenti%2C_veduta_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bc/Spedale-degli-innocenti-tondi-eingang-rechts.jpg/1280px-Spedale-degli-innocenti-tondi-eingang-rechts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Médaillons des Enfants Trouvés</t>
+  </si>
+  <si>
+    <t>Putti degli Innocenti</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1450 environ</t>
+  </si>
+  <si>
+    <t>Vierge à l'Enfant  avec trois chérubins</t>
+  </si>
+  <si>
+    <t>Madonna col Bambino (Madonna Genois)</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1492</t>
+  </si>
+  <si>
+    <t>Cathédrale du Wawel</t>
+  </si>
+  <si>
+    <t>Tombeau du roi Casimir IV Jagellon</t>
+  </si>
+  <si>
+    <t>Nagrobek Kazimierza IV Jagiellończyka</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Marbre rouge de Salzbourg</t>
+  </si>
+  <si>
+    <t>v. 1495</t>
+  </si>
+  <si>
+    <t>Église des Dominicains</t>
+  </si>
+  <si>
+    <t>Épitaphe de Callimaque (Filippo Buonaccorsi)</t>
+  </si>
+  <si>
+    <t>Tablica epitafijna Kallimacha</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/.Epitafium_Kallimacha02.JPG/960px-.Epitafium_Kallimacha02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1491</t>
+  </si>
+  <si>
+    <t>Crucifix de Slacker</t>
+  </si>
+  <si>
+    <t>Krucyfiks kamienny Wita Stwosza</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Krucyfiks_Wita_Stwosza_03.jpg/1280px-Krucyfiks_Wita_Stwosza_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Pierre calcaire</t>
+  </si>
+  <si>
+    <t>v. 1495-1500</t>
+  </si>
+  <si>
+    <t>Musée National Germanique</t>
+  </si>
+  <si>
+    <t>Vierge à l'Enfant (Vierge de Nuremberg)</t>
+  </si>
+  <si>
+    <t>Nürnberger Madonna</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bois de tilleul</t>
+  </si>
+  <si>
+    <t>Tombeau de l'évêque Piotr de Bnina</t>
+  </si>
+  <si>
+    <t>Nagrobek biskupa Piotra z Bnina</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Tilman</t>
+  </si>
+  <si>
+    <t>RIEMENSCHNEIDER</t>
+  </si>
+  <si>
+    <t>1490-1492</t>
+  </si>
+  <si>
+    <t>Wurtzbourg</t>
+  </si>
+  <si>
+    <t>Mainfränkisches Museum</t>
+  </si>
+  <si>
+    <t>Adam et Ève</t>
+  </si>
+  <si>
+    <t>Adam und Eva</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg/1280px-Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG/1280px-Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Pierre de grès</t>
+  </si>
+  <si>
+    <t>189 cm (Adam), 181 cm (Ève)</t>
+  </si>
+  <si>
+    <t>1490-1494</t>
+  </si>
+  <si>
+    <t>Münnerstadt</t>
+  </si>
+  <si>
+    <t>Église Sainte-Marie-Madeleine</t>
+  </si>
+  <si>
+    <t>Retable de Sainte Marie-Madeleine</t>
+  </si>
+  <si>
+    <t>Magdalenenaltar</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Environ 250 cm</t>
+  </si>
+  <si>
+    <t>1496</t>
+  </si>
+  <si>
+    <t>Heidelberg</t>
+  </si>
+  <si>
+    <t>Kurpfälzisches Museum</t>
+  </si>
+  <si>
+    <t>Retable des Douze Apôtres de Windsheim</t>
+  </si>
+  <si>
+    <t>Windsheimer Zwölfbotenaltar</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Bad_Windsheim-007.jpg/1280px-Bad_Windsheim-007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Bois de tilleul polychrome</t>
+  </si>
+  <si>
+    <t>Environ 160 cm</t>
+  </si>
+  <si>
+    <t>1499</t>
+  </si>
+  <si>
+    <t>Bamberg</t>
+  </si>
+  <si>
+    <t>Cathédrale Saint-Pierre et Saint-Georges</t>
+  </si>
+  <si>
+    <t>Tombeau de l'empereur Henri II et de l'impératrice Cunégonde (commencé)</t>
+  </si>
+  <si>
+    <t>Kaisergrab im Bamberger Dom</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/BambergDom-GrabHeinrichKunigunde.JPG/1280px-BambergDom-GrabHeinrichKunigunde.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Monumental</t>
+  </si>
+  <si>
+    <t>Cleveland</t>
+  </si>
+  <si>
+    <t>Cleveland Museum of Art</t>
+  </si>
+  <si>
+    <t>Saint Jérôme et le Lion</t>
+  </si>
+  <si>
+    <t>Heiliger Hieronymus mit dem Löwen</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Alabâtre</t>
+  </si>
+  <si>
+    <t>38 cm</t>
+  </si>
+  <si>
+    <t>Santa Maria della Scala (originaux)</t>
+  </si>
+  <si>
+    <t>La Fonte Gaia</t>
+  </si>
+  <si>
+    <t>Fonte Gaia</t>
+  </si>
+  <si>
+    <t>Fontaine / Reliefs monumentaux</t>
+  </si>
+  <si>
+    <t>1406</t>
+  </si>
+  <si>
+    <t>Lucques</t>
+  </si>
+  <si>
+    <t>Cathédrale Saint-Martin</t>
+  </si>
+  <si>
+    <t>Tombeau d'Ilaria del Carretto</t>
+  </si>
+  <si>
+    <t>Monumento funebre a Ilaria del Carretto</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Gisant / Tombeau</t>
+  </si>
+  <si>
+    <t>1425-1438</t>
+  </si>
+  <si>
+    <t>Basilique San Petronio</t>
+  </si>
+  <si>
+    <t>Portail central</t>
+  </si>
+  <si>
+    <t>Portail de San Petronio (Porta Magna)</t>
+  </si>
+  <si>
+    <t>Porta Magna</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Portail sculpté / Reliefs</t>
+  </si>
+  <si>
+    <t>Pierre d'Istrie</t>
+  </si>
+  <si>
+    <t>1425</t>
+  </si>
+  <si>
+    <t>La Création d'Adam</t>
+  </si>
+  <si>
+    <t>Creazione di Adamo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Relief</t>
+  </si>
+  <si>
+    <t>99 cm environ</t>
+  </si>
+  <si>
+    <t>92 cm environ</t>
+  </si>
+  <si>
+    <t>Basilique San Frediano</t>
+  </si>
+  <si>
+    <t>Chapelle Trenta</t>
+  </si>
+  <si>
+    <t>Retable Trenta</t>
+  </si>
+  <si>
+    <t>Polittico Trenta</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Retable / Autel sculpté</t>
+  </si>
+  <si>
+    <t>Dalles funéraires de Lorenzo Trenta et sa femme</t>
+  </si>
+  <si>
+    <t>Tombe de Lorenzo Trenta e sua moglie</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Dalles funéraires</t>
+  </si>
+  <si>
+    <t>Buste de Marietta Strozzi</t>
+  </si>
+  <si>
+    <t>Ritratto di Marietta Strozzi</t>
+  </si>
+  <si>
+    <t>52.5 cm</t>
+  </si>
+  <si>
+    <t>1450-1455</t>
+  </si>
+  <si>
+    <t>Tombeau de Carlo Marsuppini</t>
+  </si>
+  <si>
+    <t>Monumento funebre a Carlo Marsuppini</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG/960px-Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>environ 600 cm</t>
+  </si>
+  <si>
+    <t>1461</t>
+  </si>
+  <si>
+    <t>Tabernacle du Sacrement</t>
+  </si>
+  <si>
+    <t>Tabernacolo del Sacramento</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1455-1460 environ</t>
+  </si>
+  <si>
+    <t>Saint Jean-Baptiste enfant (Buste)</t>
+  </si>
+  <si>
+    <t>San Giovannino (Busto)</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>50 cm</t>
   </si>
 </sst>
 </file>
@@ -984,10 +1585,13 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1295,15 +1899,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V44"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
     <col min="2" max="2" width="43.140625" customWidth="1"/>
     <col min="3" max="3" width="15.42578125" customWidth="1"/>
+    <col min="9" max="9" width="36.28515625" customWidth="1"/>
     <col min="16" max="16" width="1" customWidth="1"/>
     <col min="17" max="17" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="2"/>
+    <col min="22" max="22" width="9.140625" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1367,7 +1972,7 @@
       <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="V1" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1397,7 +2002,7 @@
         <v>28</v>
       </c>
       <c r="V2" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
@@ -1426,7 +2031,7 @@
         <v>36</v>
       </c>
       <c r="V3" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
@@ -1452,7 +2057,7 @@
         <v>36</v>
       </c>
       <c r="V4" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
@@ -1481,7 +2086,7 @@
         <v>36</v>
       </c>
       <c r="V5" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
@@ -1510,7 +2115,7 @@
         <v>36</v>
       </c>
       <c r="V6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
@@ -1530,85 +2135,100 @@
         <v>60</v>
       </c>
       <c r="I7" t="s">
+        <v>485</v>
+      </c>
+      <c r="J7" t="s">
+        <v>486</v>
+      </c>
+      <c r="K7" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="R7" t="s">
         <v>36</v>
       </c>
+      <c r="S7" t="s">
+        <v>487</v>
+      </c>
       <c r="V7" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>488</v>
       </c>
       <c r="D8" t="s">
-        <v>66</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="I8" t="s">
-        <v>68</v>
+        <v>489</v>
+      </c>
+      <c r="J8" t="s">
+        <v>490</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>69</v>
+        <v>491</v>
       </c>
       <c r="R8" t="s">
-        <v>70</v>
+        <v>36</v>
+      </c>
+      <c r="S8" t="s">
+        <v>492</v>
       </c>
       <c r="V8" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>493</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>324</v>
       </c>
       <c r="I9" t="s">
-        <v>76</v>
+        <v>494</v>
+      </c>
+      <c r="J9" t="s">
+        <v>495</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>496</v>
       </c>
       <c r="R9" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="V9" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>497</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -1617,73 +2237,79 @@
         <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>80</v>
+        <v>498</v>
+      </c>
+      <c r="J10" t="s">
+        <v>499</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>81</v>
+        <v>500</v>
       </c>
       <c r="R10" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="S10" t="s">
+        <v>501</v>
       </c>
       <c r="V10" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="B11" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E11" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="I11" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
       <c r="R11" t="s">
-        <v>89</v>
-      </c>
-      <c r="V11" s="2">
+        <v>69</v>
+      </c>
+      <c r="V11" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="B12" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="I12" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="R12" t="s">
-        <v>36</v>
-      </c>
-      <c r="V12" s="2">
+        <v>28</v>
+      </c>
+      <c r="V12" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1692,181 +2318,253 @@
         <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
         <v>46</v>
       </c>
       <c r="E13" t="s">
-        <v>99</v>
+        <v>47</v>
       </c>
       <c r="I13" t="s">
-        <v>100</v>
+        <v>196</v>
+      </c>
+      <c r="J13" t="s">
+        <v>197</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>101</v>
+        <v>293</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>198</v>
       </c>
       <c r="R13" t="s">
-        <v>102</v>
-      </c>
-      <c r="V13" s="2">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="S13" t="s">
+        <v>294</v>
+      </c>
+      <c r="V13" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>104</v>
+        <v>295</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>105</v>
+        <v>211</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="I14" t="s">
-        <v>106</v>
+        <v>296</v>
+      </c>
+      <c r="J14" t="s">
+        <v>297</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>107</v>
+        <v>298</v>
+      </c>
+      <c r="L14" t="s">
+        <v>299</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>301</v>
       </c>
       <c r="R14" t="s">
-        <v>36</v>
-      </c>
-      <c r="V14" s="2">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="S14" t="s">
+        <v>302</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>108</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>303</v>
+      </c>
+      <c r="D15" t="s">
+        <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>111</v>
+        <v>304</v>
       </c>
       <c r="I15" t="s">
-        <v>112</v>
+        <v>305</v>
+      </c>
+      <c r="J15" t="s">
+        <v>306</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>113</v>
+        <v>307</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>308</v>
       </c>
       <c r="R15" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="2">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="S15" t="s">
+        <v>309</v>
+      </c>
+      <c r="T15">
+        <v>380</v>
+      </c>
+      <c r="V15" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>310</v>
       </c>
       <c r="D16" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>311</v>
       </c>
       <c r="I16" t="s">
-        <v>120</v>
+        <v>312</v>
+      </c>
+      <c r="J16" t="s">
+        <v>313</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>121</v>
+        <v>314</v>
+      </c>
+      <c r="L16" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>316</v>
       </c>
       <c r="R16" t="s">
-        <v>36</v>
-      </c>
-      <c r="V16" s="2">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="S16" t="s">
+        <v>317</v>
+      </c>
+      <c r="V16" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="B17" t="s">
-        <v>123</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>318</v>
       </c>
       <c r="D17" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="I17" t="s">
-        <v>127</v>
+        <v>319</v>
+      </c>
+      <c r="J17" t="s">
+        <v>320</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>128</v>
+        <v>321</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>322</v>
       </c>
       <c r="R17" t="s">
-        <v>129</v>
-      </c>
-      <c r="V17" s="2">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="S17" t="s">
+        <v>224</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>130</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>323</v>
       </c>
       <c r="D18" t="s">
         <v>46</v>
       </c>
       <c r="E18" t="s">
-        <v>47</v>
+        <v>324</v>
+      </c>
+      <c r="G18" t="s">
+        <v>325</v>
       </c>
       <c r="I18" t="s">
-        <v>133</v>
+        <v>326</v>
+      </c>
+      <c r="J18" t="s">
+        <v>327</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>134</v>
+        <v>328</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>329</v>
       </c>
       <c r="R18" t="s">
-        <v>28</v>
-      </c>
-      <c r="V18" s="2">
-        <v>1</v>
+        <v>330</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>137</v>
+        <v>331</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
@@ -1875,969 +2573,2048 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>209</v>
+        <v>332</v>
       </c>
       <c r="J19" t="s">
-        <v>210</v>
+        <v>333</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>138</v>
+        <v>334</v>
       </c>
       <c r="Q19" t="s">
-        <v>211</v>
+        <v>322</v>
       </c>
       <c r="R19" t="s">
-        <v>28</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="T19" s="2">
-        <v>51</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>213</v>
+        <v>335</v>
+      </c>
+      <c r="S19" t="s">
+        <v>336</v>
+      </c>
+      <c r="V19" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>135</v>
+        <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>214</v>
+        <v>337</v>
       </c>
       <c r="D20" t="s">
         <v>46</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="I20" t="s">
-        <v>209</v>
+        <v>338</v>
       </c>
       <c r="J20" t="s">
-        <v>215</v>
+        <v>339</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>216</v>
+        <v>340</v>
+      </c>
+      <c r="L20" t="s">
+        <v>341</v>
       </c>
       <c r="Q20" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="R20" t="s">
-        <v>36</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="T20" s="2">
-        <v>57</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>213</v>
+        <v>342</v>
+      </c>
+      <c r="S20" t="s">
+        <v>343</v>
+      </c>
+      <c r="T20" t="s">
+        <v>344</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>81</v>
       </c>
       <c r="D21" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="I21" t="s">
-        <v>219</v>
-      </c>
-      <c r="J21" t="s">
-        <v>220</v>
+        <v>84</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>211</v>
+        <v>85</v>
       </c>
       <c r="R21" t="s">
-        <v>36</v>
-      </c>
-      <c r="S21" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="T21" s="2"/>
-      <c r="V21" s="2" t="s">
-        <v>213</v>
+        <v>86</v>
+      </c>
+      <c r="V21" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B22" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="C22" t="s">
-        <v>223</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>224</v>
+        <v>91</v>
+      </c>
+      <c r="G22" t="s">
+        <v>449</v>
       </c>
       <c r="I22" t="s">
-        <v>225</v>
+        <v>450</v>
       </c>
       <c r="J22" t="s">
-        <v>226</v>
+        <v>451</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>227</v>
+        <v>92</v>
       </c>
       <c r="Q22" t="s">
-        <v>211</v>
+        <v>452</v>
       </c>
       <c r="R22" t="s">
         <v>36</v>
       </c>
-      <c r="S22" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="T22" s="2"/>
-      <c r="V22" s="2" t="s">
-        <v>213</v>
+      <c r="V22" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="C23" t="s">
-        <v>229</v>
+        <v>453</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
+        <v>454</v>
       </c>
       <c r="E23" t="s">
-        <v>230</v>
+        <v>455</v>
       </c>
       <c r="I23" t="s">
-        <v>231</v>
+        <v>456</v>
       </c>
       <c r="J23" t="s">
-        <v>232</v>
+        <v>457</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="L23" t="s">
-        <v>234</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>235</v>
+        <v>458</v>
       </c>
       <c r="Q23" t="s">
-        <v>236</v>
+        <v>459</v>
       </c>
       <c r="R23" t="s">
-        <v>157</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>213</v>
+        <v>36</v>
+      </c>
+      <c r="V23" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B24" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>238</v>
+        <v>460</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>461</v>
+      </c>
+      <c r="G24" t="s">
+        <v>462</v>
       </c>
       <c r="I24" t="s">
-        <v>239</v>
+        <v>463</v>
       </c>
       <c r="J24" t="s">
-        <v>240</v>
+        <v>464</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>241</v>
+        <v>465</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>466</v>
       </c>
       <c r="R24" t="s">
-        <v>242</v>
-      </c>
-      <c r="S24" s="2">
-        <v>420</v>
-      </c>
-      <c r="T24" s="2">
-        <v>274</v>
-      </c>
-      <c r="U24">
-        <v>30</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>213</v>
+        <v>467</v>
+      </c>
+      <c r="V24" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B25" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="C25" t="s">
-        <v>243</v>
+        <v>468</v>
       </c>
       <c r="D25" t="s">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="E25" t="s">
-        <v>245</v>
+        <v>461</v>
+      </c>
+      <c r="G25" t="s">
+        <v>464</v>
       </c>
       <c r="I25" t="s">
-        <v>246</v>
+        <v>469</v>
       </c>
       <c r="J25" t="s">
-        <v>247</v>
+        <v>470</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>248</v>
+        <v>471</v>
+      </c>
+      <c r="L25" t="s">
+        <v>464</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>472</v>
       </c>
       <c r="R25" t="s">
-        <v>28</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="T25" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>213</v>
+        <v>467</v>
+      </c>
+      <c r="S25" t="s">
+        <v>473</v>
+      </c>
+      <c r="T25" t="s">
+        <v>474</v>
+      </c>
+      <c r="V25" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="B26" t="s">
-        <v>136</v>
+        <v>88</v>
       </c>
       <c r="C26" t="s">
-        <v>251</v>
+        <v>210</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>454</v>
       </c>
       <c r="E26" t="s">
-        <v>105</v>
+        <v>475</v>
+      </c>
+      <c r="G26" t="s">
+        <v>476</v>
       </c>
       <c r="I26" t="s">
-        <v>252</v>
+        <v>477</v>
       </c>
       <c r="J26" t="s">
-        <v>253</v>
+        <v>478</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>254</v>
+        <v>479</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>480</v>
       </c>
       <c r="R26" t="s">
-        <v>255</v>
-      </c>
-      <c r="S26" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="T26" s="2"/>
-      <c r="V26" s="2" t="s">
-        <v>213</v>
+        <v>36</v>
+      </c>
+      <c r="V26" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="B27" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="C27" t="s">
-        <v>141</v>
+        <v>210</v>
       </c>
       <c r="D27" t="s">
-        <v>142</v>
+        <v>454</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>475</v>
+      </c>
+      <c r="G27" t="s">
+        <v>476</v>
       </c>
       <c r="I27" t="s">
-        <v>144</v>
+        <v>481</v>
+      </c>
+      <c r="J27" t="s">
+        <v>482</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>145</v>
+        <v>483</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>484</v>
       </c>
       <c r="R27" t="s">
         <v>36</v>
       </c>
       <c r="V27" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>29</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="D28" t="s">
-        <v>149</v>
+        <v>46</v>
       </c>
       <c r="E28" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="I28" t="s">
-        <v>151</v>
+        <v>96</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>152</v>
+        <v>97</v>
       </c>
       <c r="R28" t="s">
-        <v>153</v>
-      </c>
-      <c r="V28" s="2">
+        <v>98</v>
+      </c>
+      <c r="V28" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>154</v>
+        <v>29</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C29" t="s">
-        <v>156</v>
+        <v>379</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="I29" t="s">
-        <v>257</v>
+        <v>380</v>
       </c>
       <c r="J29" t="s">
-        <v>258</v>
+        <v>381</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>236</v>
+        <v>382</v>
       </c>
       <c r="R29" t="s">
-        <v>157</v>
-      </c>
-      <c r="S29" t="s">
-        <v>262</v>
-      </c>
-      <c r="T29" t="s">
-        <v>263</v>
+        <v>353</v>
+      </c>
+      <c r="S29">
+        <v>118</v>
+      </c>
+      <c r="T29">
+        <v>73</v>
       </c>
       <c r="U29">
-        <v>11</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>213</v>
+        <v>16</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="B30" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C30" t="s">
-        <v>264</v>
+        <v>100</v>
       </c>
       <c r="D30" t="s">
         <v>46</v>
       </c>
       <c r="E30" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="I30" t="s">
-        <v>265</v>
+        <v>345</v>
       </c>
       <c r="J30" t="s">
-        <v>266</v>
+        <v>346</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>236</v>
+        <v>102</v>
       </c>
       <c r="R30" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S30" t="s">
-        <v>268</v>
+        <v>347</v>
       </c>
       <c r="T30" t="s">
-        <v>269</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>213</v>
+        <v>348</v>
+      </c>
+      <c r="V30" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="B31" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C31" t="s">
-        <v>270</v>
+        <v>349</v>
       </c>
       <c r="D31" t="s">
         <v>46</v>
       </c>
       <c r="E31" t="s">
-        <v>224</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="I31" t="s">
-        <v>272</v>
+        <v>350</v>
       </c>
       <c r="J31" t="s">
-        <v>273</v>
+        <v>351</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="L31" t="s">
-        <v>275</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>211</v>
+        <v>352</v>
       </c>
       <c r="R31" t="s">
-        <v>28</v>
-      </c>
-      <c r="S31" t="s">
-        <v>277</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>213</v>
+        <v>353</v>
+      </c>
+      <c r="V31" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="B32" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C32" t="s">
-        <v>278</v>
+        <v>354</v>
       </c>
       <c r="D32" t="s">
         <v>46</v>
       </c>
       <c r="E32" t="s">
-        <v>224</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="I32" t="s">
-        <v>279</v>
+        <v>355</v>
       </c>
       <c r="J32" t="s">
-        <v>280</v>
+        <v>356</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="L32" t="s">
-        <v>282</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>211</v>
+        <v>357</v>
       </c>
       <c r="R32" t="s">
         <v>28</v>
       </c>
-      <c r="S32" t="s">
-        <v>269</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>213</v>
+      <c r="V32" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="B33" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C33" t="s">
-        <v>284</v>
+        <v>358</v>
       </c>
       <c r="D33" t="s">
         <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>224</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>271</v>
+        <v>359</v>
       </c>
       <c r="I33" t="s">
-        <v>285</v>
+        <v>360</v>
       </c>
       <c r="J33" t="s">
-        <v>286</v>
+        <v>361</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="L33" t="s">
-        <v>288</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>211</v>
+        <v>362</v>
       </c>
       <c r="R33" t="s">
-        <v>28</v>
-      </c>
-      <c r="S33" t="s">
-        <v>290</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>213</v>
+        <v>363</v>
+      </c>
+      <c r="V33" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>291</v>
+        <v>180</v>
       </c>
       <c r="D34" t="s">
-        <v>93</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>230</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>292</v>
+        <v>359</v>
       </c>
       <c r="I34" t="s">
-        <v>293</v>
+        <v>364</v>
       </c>
       <c r="J34" t="s">
-        <v>294</v>
+        <v>365</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>236</v>
+        <v>366</v>
       </c>
       <c r="R34" t="s">
-        <v>157</v>
-      </c>
-      <c r="S34" t="s">
-        <v>237</v>
-      </c>
-      <c r="T34" t="s">
-        <v>237</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>213</v>
+        <v>353</v>
+      </c>
+      <c r="V34" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C35" t="s">
-        <v>291</v>
+        <v>185</v>
       </c>
       <c r="D35" t="s">
-        <v>93</v>
+        <v>367</v>
       </c>
       <c r="E35" t="s">
-        <v>230</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>292</v>
+        <v>368</v>
       </c>
       <c r="I35" t="s">
-        <v>296</v>
+        <v>369</v>
       </c>
       <c r="J35" t="s">
-        <v>297</v>
+        <v>370</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>236</v>
+        <v>371</v>
+      </c>
+      <c r="L35" s="1" t="s">
+        <v>372</v>
       </c>
       <c r="R35" t="s">
-        <v>157</v>
-      </c>
-      <c r="S35" t="s">
-        <v>237</v>
-      </c>
-      <c r="T35" t="s">
-        <v>237</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>213</v>
+        <v>353</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
-        <v>299</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>300</v>
-      </c>
-      <c r="G36" t="s">
-        <v>301</v>
+        <v>373</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>374</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>302</v>
+        <v>375</v>
       </c>
       <c r="I36" t="s">
-        <v>303</v>
+        <v>376</v>
       </c>
       <c r="J36" t="s">
-        <v>304</v>
+        <v>377</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>236</v>
+        <v>378</v>
       </c>
       <c r="R36" t="s">
-        <v>28</v>
-      </c>
-      <c r="S36">
-        <v>85</v>
-      </c>
-      <c r="T36">
-        <v>193</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>213</v>
+        <v>353</v>
+      </c>
+      <c r="V36" s="3" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
-        <v>159</v>
+        <v>104</v>
       </c>
       <c r="C37" t="s">
-        <v>160</v>
-      </c>
-      <c r="D37" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="I37" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="R37" t="s">
-        <v>165</v>
-      </c>
-      <c r="V37" s="2">
-        <v>1</v>
+        <v>109</v>
+      </c>
+      <c r="V37" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B38" t="s">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
-        <v>167</v>
+        <v>112</v>
       </c>
       <c r="D38" t="s">
-        <v>142</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="I38" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="R38" t="s">
         <v>36</v>
       </c>
-      <c r="V38" s="2">
-        <v>1</v>
+      <c r="V38" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>171</v>
+        <v>117</v>
       </c>
       <c r="B39" t="s">
-        <v>172</v>
+        <v>118</v>
       </c>
       <c r="C39" t="s">
-        <v>173</v>
+        <v>119</v>
       </c>
       <c r="D39" t="s">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="E39" t="s">
-        <v>174</v>
+        <v>121</v>
       </c>
       <c r="I39" t="s">
-        <v>175</v>
+        <v>122</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>176</v>
+        <v>123</v>
       </c>
       <c r="R39" t="s">
-        <v>36</v>
-      </c>
-      <c r="V39" s="2">
-        <v>1</v>
+        <v>124</v>
+      </c>
+      <c r="V39" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="B40" t="s">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="C40" t="s">
-        <v>179</v>
+        <v>127</v>
       </c>
       <c r="D40" t="s">
-        <v>180</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>181</v>
+        <v>47</v>
       </c>
       <c r="I40" t="s">
-        <v>182</v>
+        <v>128</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>183</v>
+        <v>129</v>
       </c>
       <c r="R40" t="s">
-        <v>89</v>
-      </c>
-      <c r="V40" s="2">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="V40" s="3">
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>130</v>
       </c>
       <c r="B41" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="C41" t="s">
-        <v>185</v>
+        <v>132</v>
       </c>
       <c r="D41" t="s">
         <v>46</v>
       </c>
       <c r="E41" t="s">
-        <v>186</v>
+        <v>47</v>
       </c>
       <c r="I41" t="s">
-        <v>187</v>
+        <v>196</v>
+      </c>
+      <c r="J41" t="s">
+        <v>197</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>188</v>
+        <v>133</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>198</v>
       </c>
       <c r="R41" t="s">
-        <v>36</v>
-      </c>
-      <c r="V41" s="2">
+        <v>28</v>
+      </c>
+      <c r="S41" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="T41" s="2">
+        <v>51</v>
+      </c>
+      <c r="V41" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="B42" t="s">
-        <v>184</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="D42" t="s">
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I42" t="s">
-        <v>191</v>
+        <v>196</v>
+      </c>
+      <c r="J42" t="s">
+        <v>202</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>198</v>
       </c>
       <c r="R42" t="s">
         <v>36</v>
       </c>
-      <c r="V42" s="2">
+      <c r="S42" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="T42" s="2">
+        <v>57</v>
+      </c>
+      <c r="V42" s="3">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>193</v>
+        <v>130</v>
       </c>
       <c r="B43" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="C43" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="D43" t="s">
-        <v>196</v>
+        <v>46</v>
       </c>
       <c r="E43" t="s">
-        <v>197</v>
+        <v>47</v>
       </c>
       <c r="I43" t="s">
+        <v>206</v>
+      </c>
+      <c r="J43" t="s">
+        <v>207</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="Q43" t="s">
         <v>198</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="R43" t="s">
+        <v>36</v>
+      </c>
+      <c r="S43" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="T43" s="2"/>
+      <c r="V43" s="3" t="s">
         <v>200</v>
-      </c>
-      <c r="V43" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="B44" t="s">
-        <v>202</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D44" t="s">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="E44" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="I44" t="s">
-        <v>206</v>
+        <v>212</v>
+      </c>
+      <c r="J44" t="s">
+        <v>213</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>207</v>
+        <v>214</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>198</v>
       </c>
       <c r="R44" t="s">
-        <v>208</v>
-      </c>
-      <c r="V44" s="2">
+        <v>36</v>
+      </c>
+      <c r="S44" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="T44" s="2"/>
+      <c r="V44" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>130</v>
+      </c>
+      <c r="B45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C45" t="s">
+        <v>216</v>
+      </c>
+      <c r="D45" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" t="s">
+        <v>217</v>
+      </c>
+      <c r="I45" t="s">
+        <v>218</v>
+      </c>
+      <c r="J45" t="s">
+        <v>219</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="L45" t="s">
+        <v>221</v>
+      </c>
+      <c r="M45" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>223</v>
+      </c>
+      <c r="R45" t="s">
+        <v>152</v>
+      </c>
+      <c r="S45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="T45" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C46" t="s">
+        <v>225</v>
+      </c>
+      <c r="D46" t="s">
+        <v>46</v>
+      </c>
+      <c r="E46" t="s">
+        <v>53</v>
+      </c>
+      <c r="I46" t="s">
+        <v>226</v>
+      </c>
+      <c r="J46" t="s">
+        <v>227</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="R46" t="s">
+        <v>229</v>
+      </c>
+      <c r="S46" s="2">
+        <v>420</v>
+      </c>
+      <c r="T46" s="2">
+        <v>274</v>
+      </c>
+      <c r="U46">
+        <v>30</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>130</v>
+      </c>
+      <c r="B47" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" t="s">
+        <v>230</v>
+      </c>
+      <c r="D47" t="s">
+        <v>231</v>
+      </c>
+      <c r="E47" t="s">
+        <v>232</v>
+      </c>
+      <c r="I47" t="s">
+        <v>233</v>
+      </c>
+      <c r="J47" t="s">
+        <v>234</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="R47" t="s">
+        <v>28</v>
+      </c>
+      <c r="S47" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="T47" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" t="s">
+        <v>238</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" t="s">
+        <v>101</v>
+      </c>
+      <c r="I48" t="s">
+        <v>239</v>
+      </c>
+      <c r="J48" t="s">
+        <v>240</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="R48" t="s">
+        <v>242</v>
+      </c>
+      <c r="S48" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="T48" s="2"/>
+      <c r="V48" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>134</v>
+      </c>
+      <c r="B49" t="s">
+        <v>135</v>
+      </c>
+      <c r="C49" t="s">
+        <v>136</v>
+      </c>
+      <c r="D49" t="s">
+        <v>137</v>
+      </c>
+      <c r="E49" t="s">
+        <v>138</v>
+      </c>
+      <c r="I49" t="s">
+        <v>139</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="R49" t="s">
+        <v>36</v>
+      </c>
+      <c r="V49" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" t="s">
+        <v>143</v>
+      </c>
+      <c r="D50" t="s">
+        <v>144</v>
+      </c>
+      <c r="E50" t="s">
+        <v>145</v>
+      </c>
+      <c r="I50" t="s">
+        <v>146</v>
+      </c>
+      <c r="K50" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="R50" t="s">
+        <v>148</v>
+      </c>
+      <c r="V50" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>149</v>
+      </c>
+      <c r="B51" t="s">
+        <v>150</v>
+      </c>
+      <c r="C51" t="s">
+        <v>151</v>
+      </c>
+      <c r="D51" t="s">
+        <v>46</v>
+      </c>
+      <c r="E51" t="s">
+        <v>101</v>
+      </c>
+      <c r="I51" t="s">
+        <v>244</v>
+      </c>
+      <c r="J51" t="s">
+        <v>245</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>223</v>
+      </c>
+      <c r="R51" t="s">
+        <v>152</v>
+      </c>
+      <c r="S51" t="s">
+        <v>249</v>
+      </c>
+      <c r="T51" t="s">
+        <v>250</v>
+      </c>
+      <c r="U51">
+        <v>11</v>
+      </c>
+      <c r="V51" s="3">
         <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>149</v>
+      </c>
+      <c r="B52" t="s">
+        <v>150</v>
+      </c>
+      <c r="C52" t="s">
+        <v>251</v>
+      </c>
+      <c r="D52" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" t="s">
+        <v>101</v>
+      </c>
+      <c r="I52" t="s">
+        <v>252</v>
+      </c>
+      <c r="J52" t="s">
+        <v>253</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="M52" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>223</v>
+      </c>
+      <c r="R52" t="s">
+        <v>28</v>
+      </c>
+      <c r="S52" t="s">
+        <v>255</v>
+      </c>
+      <c r="T52" t="s">
+        <v>256</v>
+      </c>
+      <c r="V52" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" t="s">
+        <v>257</v>
+      </c>
+      <c r="D53" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" t="s">
+        <v>211</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I53" t="s">
+        <v>259</v>
+      </c>
+      <c r="J53" t="s">
+        <v>260</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="L53" t="s">
+        <v>262</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>198</v>
+      </c>
+      <c r="R53" t="s">
+        <v>28</v>
+      </c>
+      <c r="S53" t="s">
+        <v>264</v>
+      </c>
+      <c r="V53" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>149</v>
+      </c>
+      <c r="B54" t="s">
+        <v>150</v>
+      </c>
+      <c r="C54" t="s">
+        <v>265</v>
+      </c>
+      <c r="D54" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" t="s">
+        <v>211</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I54" t="s">
+        <v>266</v>
+      </c>
+      <c r="J54" t="s">
+        <v>267</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="L54" t="s">
+        <v>269</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>198</v>
+      </c>
+      <c r="R54" t="s">
+        <v>28</v>
+      </c>
+      <c r="S54" t="s">
+        <v>256</v>
+      </c>
+      <c r="V54" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" t="s">
+        <v>271</v>
+      </c>
+      <c r="D55" t="s">
+        <v>46</v>
+      </c>
+      <c r="E55" t="s">
+        <v>211</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="I55" t="s">
+        <v>272</v>
+      </c>
+      <c r="J55" t="s">
+        <v>273</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="L55" t="s">
+        <v>275</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>198</v>
+      </c>
+      <c r="R55" t="s">
+        <v>28</v>
+      </c>
+      <c r="S55" t="s">
+        <v>277</v>
+      </c>
+      <c r="V55" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" t="s">
+        <v>150</v>
+      </c>
+      <c r="C56" t="s">
+        <v>278</v>
+      </c>
+      <c r="D56" t="s">
+        <v>90</v>
+      </c>
+      <c r="E56" t="s">
+        <v>217</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I56" t="s">
+        <v>280</v>
+      </c>
+      <c r="J56" t="s">
+        <v>281</v>
+      </c>
+      <c r="K56" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>223</v>
+      </c>
+      <c r="R56" t="s">
+        <v>152</v>
+      </c>
+      <c r="S56" t="s">
+        <v>224</v>
+      </c>
+      <c r="T56" t="s">
+        <v>224</v>
+      </c>
+      <c r="V56" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57" t="s">
+        <v>278</v>
+      </c>
+      <c r="D57" t="s">
+        <v>90</v>
+      </c>
+      <c r="E57" t="s">
+        <v>217</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I57" t="s">
+        <v>283</v>
+      </c>
+      <c r="J57" t="s">
+        <v>284</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>223</v>
+      </c>
+      <c r="R57" t="s">
+        <v>152</v>
+      </c>
+      <c r="S57" t="s">
+        <v>224</v>
+      </c>
+      <c r="T57" t="s">
+        <v>224</v>
+      </c>
+      <c r="V57" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>149</v>
+      </c>
+      <c r="B58" t="s">
+        <v>150</v>
+      </c>
+      <c r="C58" t="s">
+        <v>286</v>
+      </c>
+      <c r="D58" t="s">
+        <v>46</v>
+      </c>
+      <c r="E58" t="s">
+        <v>287</v>
+      </c>
+      <c r="G58" t="s">
+        <v>288</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I58" t="s">
+        <v>290</v>
+      </c>
+      <c r="J58" t="s">
+        <v>291</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>292</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>223</v>
+      </c>
+      <c r="R58" t="s">
+        <v>28</v>
+      </c>
+      <c r="S58">
+        <v>85</v>
+      </c>
+      <c r="T58">
+        <v>193</v>
+      </c>
+      <c r="V58" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59" t="s">
+        <v>155</v>
+      </c>
+      <c r="D59" t="s">
+        <v>156</v>
+      </c>
+      <c r="E59" t="s">
+        <v>157</v>
+      </c>
+      <c r="I59" t="s">
+        <v>158</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="R59" t="s">
+        <v>160</v>
+      </c>
+      <c r="V59" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>117</v>
+      </c>
+      <c r="B60" t="s">
+        <v>161</v>
+      </c>
+      <c r="C60" t="s">
+        <v>162</v>
+      </c>
+      <c r="D60" t="s">
+        <v>137</v>
+      </c>
+      <c r="E60" t="s">
+        <v>163</v>
+      </c>
+      <c r="I60" t="s">
+        <v>164</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="R60" t="s">
+        <v>36</v>
+      </c>
+      <c r="V60" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>166</v>
+      </c>
+      <c r="B61" t="s">
+        <v>167</v>
+      </c>
+      <c r="C61" t="s">
+        <v>168</v>
+      </c>
+      <c r="D61" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" t="s">
+        <v>169</v>
+      </c>
+      <c r="I61" t="s">
+        <v>170</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="R61" t="s">
+        <v>36</v>
+      </c>
+      <c r="V61" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>172</v>
+      </c>
+      <c r="B62" t="s">
+        <v>173</v>
+      </c>
+      <c r="C62" t="s">
+        <v>174</v>
+      </c>
+      <c r="D62" t="s">
+        <v>175</v>
+      </c>
+      <c r="E62" t="s">
+        <v>176</v>
+      </c>
+      <c r="I62" t="s">
+        <v>177</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="R62" t="s">
+        <v>86</v>
+      </c>
+      <c r="V62" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>409</v>
+      </c>
+      <c r="B63" t="s">
+        <v>410</v>
+      </c>
+      <c r="C63" t="s">
+        <v>411</v>
+      </c>
+      <c r="D63" t="s">
+        <v>412</v>
+      </c>
+      <c r="E63" t="s">
+        <v>413</v>
+      </c>
+      <c r="I63" t="s">
+        <v>414</v>
+      </c>
+      <c r="J63" t="s">
+        <v>415</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="R63" t="s">
+        <v>418</v>
+      </c>
+      <c r="S63" t="s">
+        <v>419</v>
+      </c>
+      <c r="V63" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>409</v>
+      </c>
+      <c r="B64" t="s">
+        <v>410</v>
+      </c>
+      <c r="C64" t="s">
+        <v>420</v>
+      </c>
+      <c r="D64" t="s">
+        <v>421</v>
+      </c>
+      <c r="E64" t="s">
+        <v>422</v>
+      </c>
+      <c r="I64" t="s">
+        <v>423</v>
+      </c>
+      <c r="J64" t="s">
+        <v>424</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="R64" t="s">
+        <v>405</v>
+      </c>
+      <c r="S64" t="s">
+        <v>426</v>
+      </c>
+      <c r="V64" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>409</v>
+      </c>
+      <c r="B65" t="s">
+        <v>410</v>
+      </c>
+      <c r="C65" t="s">
+        <v>427</v>
+      </c>
+      <c r="D65" t="s">
+        <v>428</v>
+      </c>
+      <c r="E65" t="s">
+        <v>429</v>
+      </c>
+      <c r="I65" t="s">
+        <v>430</v>
+      </c>
+      <c r="J65" t="s">
+        <v>431</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="R65" t="s">
+        <v>433</v>
+      </c>
+      <c r="S65" t="s">
+        <v>434</v>
+      </c>
+      <c r="V65" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>409</v>
+      </c>
+      <c r="B66" t="s">
+        <v>410</v>
+      </c>
+      <c r="C66" t="s">
+        <v>435</v>
+      </c>
+      <c r="D66" t="s">
+        <v>436</v>
+      </c>
+      <c r="E66" t="s">
+        <v>437</v>
+      </c>
+      <c r="I66" t="s">
+        <v>438</v>
+      </c>
+      <c r="J66" t="s">
+        <v>439</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="R66" t="s">
+        <v>36</v>
+      </c>
+      <c r="S66" t="s">
+        <v>441</v>
+      </c>
+      <c r="V66" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>409</v>
+      </c>
+      <c r="B67" t="s">
+        <v>410</v>
+      </c>
+      <c r="C67" t="s">
+        <v>383</v>
+      </c>
+      <c r="D67" t="s">
+        <v>442</v>
+      </c>
+      <c r="E67" t="s">
+        <v>443</v>
+      </c>
+      <c r="I67" t="s">
+        <v>444</v>
+      </c>
+      <c r="J67" t="s">
+        <v>445</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>446</v>
+      </c>
+      <c r="R67" t="s">
+        <v>447</v>
+      </c>
+      <c r="S67" t="s">
+        <v>448</v>
+      </c>
+      <c r="V67" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" t="s">
+        <v>179</v>
+      </c>
+      <c r="C68" t="s">
+        <v>180</v>
+      </c>
+      <c r="D68" t="s">
+        <v>46</v>
+      </c>
+      <c r="E68" t="s">
+        <v>181</v>
+      </c>
+      <c r="I68" t="s">
+        <v>182</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="R68" t="s">
+        <v>36</v>
+      </c>
+      <c r="V68" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>184</v>
+      </c>
+      <c r="B69" t="s">
+        <v>179</v>
+      </c>
+      <c r="C69" t="s">
+        <v>185</v>
+      </c>
+      <c r="D69" t="s">
+        <v>46</v>
+      </c>
+      <c r="E69" t="s">
+        <v>53</v>
+      </c>
+      <c r="I69" t="s">
+        <v>186</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="R69" t="s">
+        <v>36</v>
+      </c>
+      <c r="V69" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>188</v>
+      </c>
+      <c r="B70" t="s">
+        <v>189</v>
+      </c>
+      <c r="C70" t="s">
+        <v>190</v>
+      </c>
+      <c r="D70" t="s">
+        <v>191</v>
+      </c>
+      <c r="E70" t="s">
+        <v>192</v>
+      </c>
+      <c r="I70" t="s">
+        <v>193</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="R70" t="s">
+        <v>195</v>
+      </c>
+      <c r="V70" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>188</v>
+      </c>
+      <c r="B71" t="s">
+        <v>189</v>
+      </c>
+      <c r="C71" t="s">
+        <v>383</v>
+      </c>
+      <c r="D71" t="s">
+        <v>191</v>
+      </c>
+      <c r="E71" t="s">
+        <v>384</v>
+      </c>
+      <c r="I71" t="s">
+        <v>385</v>
+      </c>
+      <c r="J71" t="s">
+        <v>386</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="R71" t="s">
+        <v>388</v>
+      </c>
+      <c r="V71" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>188</v>
+      </c>
+      <c r="B72" t="s">
+        <v>189</v>
+      </c>
+      <c r="C72" t="s">
+        <v>389</v>
+      </c>
+      <c r="D72" t="s">
+        <v>191</v>
+      </c>
+      <c r="E72" t="s">
+        <v>390</v>
+      </c>
+      <c r="I72" t="s">
+        <v>391</v>
+      </c>
+      <c r="J72" t="s">
+        <v>392</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="R72" t="s">
+        <v>28</v>
+      </c>
+      <c r="V72" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>188</v>
+      </c>
+      <c r="B73" t="s">
+        <v>189</v>
+      </c>
+      <c r="C73" t="s">
+        <v>394</v>
+      </c>
+      <c r="D73" t="s">
+        <v>191</v>
+      </c>
+      <c r="E73" t="s">
+        <v>192</v>
+      </c>
+      <c r="I73" t="s">
+        <v>395</v>
+      </c>
+      <c r="J73" t="s">
+        <v>396</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="L73" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="R73" t="s">
+        <v>399</v>
+      </c>
+      <c r="V73" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>188</v>
+      </c>
+      <c r="B74" t="s">
+        <v>189</v>
+      </c>
+      <c r="C74" t="s">
+        <v>400</v>
+      </c>
+      <c r="D74" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74" t="s">
+        <v>401</v>
+      </c>
+      <c r="I74" t="s">
+        <v>402</v>
+      </c>
+      <c r="J74" t="s">
+        <v>403</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="R74" t="s">
+        <v>405</v>
+      </c>
+      <c r="V74" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>188</v>
+      </c>
+      <c r="B75" t="s">
+        <v>189</v>
+      </c>
+      <c r="C75" t="s">
+        <v>383</v>
+      </c>
+      <c r="D75" t="s">
+        <v>191</v>
+      </c>
+      <c r="E75" t="s">
+        <v>384</v>
+      </c>
+      <c r="I75" t="s">
+        <v>406</v>
+      </c>
+      <c r="J75" t="s">
+        <v>407</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="R75" t="s">
+        <v>36</v>
+      </c>
+      <c r="V75" s="3">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -2847,56 +4624,94 @@
     <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
     <hyperlink ref="K5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
     <hyperlink ref="K6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="K7" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="K8" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="K9" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="K10" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="K11" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K12" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="K13" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="K14" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="K15" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K16" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="K17" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K18" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K41" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K42" r:id="rId19" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K43" r:id="rId20" xr:uid="{00000000-0004-0000-0000-00001B000000}"/>
-    <hyperlink ref="K44" r:id="rId21" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K40" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K39" r:id="rId23" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K38" r:id="rId24" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K37" r:id="rId25" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K28" r:id="rId26" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K27" r:id="rId27" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K19" r:id="rId28" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
-    <hyperlink ref="K20" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
-    <hyperlink ref="K21" r:id="rId30" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
-    <hyperlink ref="K22" r:id="rId31" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
-    <hyperlink ref="K23" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
-    <hyperlink ref="M23" r:id="rId33" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
-    <hyperlink ref="K24" r:id="rId34" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
-    <hyperlink ref="K25" r:id="rId35" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
-    <hyperlink ref="K26" r:id="rId36" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
-    <hyperlink ref="K29" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
-    <hyperlink ref="M29" r:id="rId38" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
-    <hyperlink ref="O29" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
-    <hyperlink ref="K30" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
-    <hyperlink ref="M30" r:id="rId41" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
-    <hyperlink ref="K31" r:id="rId42" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
-    <hyperlink ref="M31" r:id="rId43" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
-    <hyperlink ref="K32" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
-    <hyperlink ref="F31" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
-    <hyperlink ref="F32:F33" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
-    <hyperlink ref="M32" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
-    <hyperlink ref="M33" r:id="rId48" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
-    <hyperlink ref="K33" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
-    <hyperlink ref="K34" r:id="rId50" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
-    <hyperlink ref="F34" r:id="rId51" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
-    <hyperlink ref="F35" r:id="rId52" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
-    <hyperlink ref="K35" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
-    <hyperlink ref="K36" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
-    <hyperlink ref="H36" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
+    <hyperlink ref="K11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K21" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="K28" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="K37" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K38" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K39" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K40" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K68" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K69" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
+    <hyperlink ref="K70" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K62" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
+    <hyperlink ref="K61" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K60" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
+    <hyperlink ref="K59" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K50" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K49" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K41" r:id="rId23" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
+    <hyperlink ref="K42" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
+    <hyperlink ref="K43" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
+    <hyperlink ref="K44" r:id="rId26" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
+    <hyperlink ref="K45" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
+    <hyperlink ref="M45" r:id="rId28" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
+    <hyperlink ref="K46" r:id="rId29" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
+    <hyperlink ref="K47" r:id="rId30" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
+    <hyperlink ref="K48" r:id="rId31" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
+    <hyperlink ref="K51" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
+    <hyperlink ref="M51" r:id="rId33" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
+    <hyperlink ref="O51" r:id="rId34" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
+    <hyperlink ref="K52" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
+    <hyperlink ref="M52" r:id="rId36" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
+    <hyperlink ref="K53" r:id="rId37" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
+    <hyperlink ref="M53" r:id="rId38" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
+    <hyperlink ref="K54" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
+    <hyperlink ref="F53" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
+    <hyperlink ref="F54:F55" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
+    <hyperlink ref="M54" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
+    <hyperlink ref="M55" r:id="rId43" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
+    <hyperlink ref="K55" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
+    <hyperlink ref="K56" r:id="rId45" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
+    <hyperlink ref="F56" r:id="rId46" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
+    <hyperlink ref="F57" r:id="rId47" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
+    <hyperlink ref="K57" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
+    <hyperlink ref="K58" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
+    <hyperlink ref="H58" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
+    <hyperlink ref="K13" r:id="rId51" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
+    <hyperlink ref="K14" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
+    <hyperlink ref="M14" r:id="rId53" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
+    <hyperlink ref="F14" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
+    <hyperlink ref="K15" r:id="rId55" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
+    <hyperlink ref="K16" r:id="rId56" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
+    <hyperlink ref="K17" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
+    <hyperlink ref="K18" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
+    <hyperlink ref="K19" r:id="rId59" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
+    <hyperlink ref="K20" r:id="rId60" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
+    <hyperlink ref="K30" r:id="rId61" xr:uid="{C61A9D98-CECD-4B5E-B96E-4289BBC0D262}"/>
+    <hyperlink ref="K31" r:id="rId62" xr:uid="{EB7CB685-E0C1-4945-9E14-9CA8A1A342EC}"/>
+    <hyperlink ref="K32" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F065AADE-42A0-4C3C-B801-4BE9B5FA9BEB}"/>
+    <hyperlink ref="K33" r:id="rId64" xr:uid="{819ABFBD-4499-4FE6-9CDB-0A9FE7A07280}"/>
+    <hyperlink ref="K34" r:id="rId65" xr:uid="{48E832D6-CC6D-436E-BC8A-74B5489EE9B1}"/>
+    <hyperlink ref="K35" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8CE24E7-04FD-4348-88B3-8498A10C097C}"/>
+    <hyperlink ref="K36" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5381B954-6617-4930-A5BC-415052E36793}"/>
+    <hyperlink ref="L35" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCF513E3-779E-478B-83FF-5E58604AFA16}"/>
+    <hyperlink ref="H36" r:id="rId69" xr:uid="{B822FBF8-7DC0-48FD-BCB2-A7B3FC9F1F52}"/>
+    <hyperlink ref="F36" r:id="rId70" xr:uid="{3D8C3557-F6D2-4A3A-BE13-D18D5DD3FB6A}"/>
+    <hyperlink ref="K29" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
+    <hyperlink ref="K71" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
+    <hyperlink ref="L73" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
+    <hyperlink ref="K73" r:id="rId74" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
+    <hyperlink ref="K72" r:id="rId75" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
+    <hyperlink ref="K75" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
+    <hyperlink ref="K74" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
+    <hyperlink ref="M63" r:id="rId78" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
+    <hyperlink ref="K63" r:id="rId79" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
+    <hyperlink ref="K64" r:id="rId80" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
+    <hyperlink ref="K67" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
+    <hyperlink ref="K66" r:id="rId82" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
+    <hyperlink ref="K65" r:id="rId83" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
+    <hyperlink ref="K22" r:id="rId84" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
+    <hyperlink ref="K23" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
+    <hyperlink ref="K24" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
+    <hyperlink ref="K25" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
+    <hyperlink ref="K26" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
+    <hyperlink ref="K27" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
+    <hyperlink ref="K7" r:id="rId90" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
+    <hyperlink ref="K8" r:id="rId91" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
+    <hyperlink ref="K9" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
+    <hyperlink ref="K10" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05740131-6CC6-4247-945F-E71C80A2BE82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BB33D7-557D-41A8-83A7-EC4F0C087499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="626">
   <si>
     <t>Patronyme artiste</t>
   </si>
@@ -179,9 +179,6 @@
     <t>Museo Nazionale del Bargello</t>
   </si>
   <si>
-    <t>"Buste de Piero de Médicis"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>Basilique Santa Croce</t>
   </si>
   <si>
-    <t>"Chaire de Santa Croce"</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG/960px-Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -527,9 +521,6 @@
     <t>Palazzo Abatellis</t>
   </si>
   <si>
-    <t>"Buste d'Éléonore d'Aragon"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg/1280px-Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -566,9 +557,6 @@
     <t>Église San Giovanni Battista</t>
   </si>
   <si>
-    <t>"Compianto sul Cristo morto (groupe en terre cuite polychrome)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG/1280px-Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -593,9 +581,6 @@
     <t>1445-1450</t>
   </si>
   <si>
-    <t>"Tombeau de Leonardo Bruni"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -1539,13 +1524,400 @@
   </si>
   <si>
     <t>50 cm</t>
+  </si>
+  <si>
+    <t>Nef</t>
+  </si>
+  <si>
+    <t>Tombeau de Leonardo Bruni</t>
+  </si>
+  <si>
+    <t>Tomba di Leonardo Bruni</t>
+  </si>
+  <si>
+    <t>Marbre scuplté et polychromie</t>
+  </si>
+  <si>
+    <t>610 cm</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>1443-1444</t>
+  </si>
+  <si>
+    <t>Arezzo</t>
+  </si>
+  <si>
+    <t>Palazzo della Fraternita dei Laici</t>
+  </si>
+  <si>
+    <t>Façade</t>
+  </si>
+  <si>
+    <t>Vierge de miséricorde et bas-reliefs de la façade</t>
+  </si>
+  <si>
+    <t>Madonna della Misericordia</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue et relief de façade</t>
+  </si>
+  <si>
+    <t>Marbre et pierre</t>
+  </si>
+  <si>
+    <t>1447</t>
+  </si>
+  <si>
+    <t>Palazzo Publico / Badia Fiorentina</t>
+  </si>
+  <si>
+    <t>Portail</t>
+  </si>
+  <si>
+    <t>Portail de la Badia Fiorentina</t>
+  </si>
+  <si>
+    <t>Portale de la Badia Fiorentina</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Badia_fiorentina%2C_portale%2C_01.JPG/960px-Badia_fiorentina%2C_portale%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Portail architectural</t>
+  </si>
+  <si>
+    <t>Marbre sculpté</t>
+  </si>
+  <si>
+    <t>1451-1452</t>
+  </si>
+  <si>
+    <t>Pistoia</t>
+  </si>
+  <si>
+    <t>Cathédrale Saint-Zénon</t>
+  </si>
+  <si>
+    <t>Chapelle du Sacrement</t>
+  </si>
+  <si>
+    <t>Tombeau du juriste Filippo Lazzari</t>
+  </si>
+  <si>
+    <t>Tomba di Filippo Lazzari</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Tombeau du cardinal de Portugal (Jacques de Lusitanie)</t>
+  </si>
+  <si>
+    <t>Tomba del Cardinale del Portogallo</t>
+  </si>
+  <si>
+    <t>Londres</t>
+  </si>
+  <si>
+    <t>Victoria and Albety Museum</t>
+  </si>
+  <si>
+    <t>Buste de Giovanni Chellini</t>
+  </si>
+  <si>
+    <t>Busto di Giovanni di San Miniato</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Buste de Matteo Palmieri</t>
+  </si>
+  <si>
+    <t>Busto di Matteo Palmieri</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>v. 1470</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Metropolitan Museum of Art</t>
+  </si>
+  <si>
+    <t>Vierge à l'Enfant</t>
+  </si>
+  <si>
+    <t>Madonna col Bambino</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Madonna_and_Child_with_Angels_MET_DP236934.jpg/960px-Madonna_and_Child_with_Angels_MET_DP236934.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Haut-relief</t>
+  </si>
+  <si>
+    <t>Buste de Piero de Médicis</t>
+  </si>
+  <si>
+    <t>Busto di Piero de' Medici</t>
+  </si>
+  <si>
+    <t>Buste portrait</t>
+  </si>
+  <si>
+    <t>51 cm</t>
+  </si>
+  <si>
+    <t>1454</t>
+  </si>
+  <si>
+    <t>Buste de Giovanni de Médicis</t>
+  </si>
+  <si>
+    <t>Busto di Giovanni de' Medici</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>52 cm</t>
+  </si>
+  <si>
+    <t>1456</t>
+  </si>
+  <si>
+    <t>Buste de Rinaldo della Luna</t>
+  </si>
+  <si>
+    <t>Busto di Rinaldo della Luna</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ef/A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg/1280px-A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>49 cm</t>
+  </si>
+  <si>
+    <t>1464</t>
+  </si>
+  <si>
+    <t>Chapelle Giugni</t>
+  </si>
+  <si>
+    <t>Tombeau de Bernardo Giugni</t>
+  </si>
+  <si>
+    <t>Tomba di Bernardo Giugni</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Mino_da_fiesole%2C_tomba_di_bernardo_giugni%2C_02.JPG/1280px-Mino_da_fiesole%2C_tomba_di_bernardo_giugni%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Chaire de Santa Croce</t>
+  </si>
+  <si>
+    <t>Pulpito di Santa Croce</t>
+  </si>
+  <si>
+    <t>1474</t>
+  </si>
+  <si>
+    <t>Buste de Pietro Mellini</t>
+  </si>
+  <si>
+    <t>Busto di Pietro Mellini</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Benedetto_da_maiano%2C_busto_di_pietro_mellini.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Statue</t>
+  </si>
+  <si>
+    <t>135 cm</t>
+  </si>
+  <si>
+    <t>1470-1475</t>
+  </si>
+  <si>
+    <t>Faenza</t>
+  </si>
+  <si>
+    <t>Cathédrale de Faenza</t>
+  </si>
+  <si>
+    <t>Tombe de Saint Savin</t>
+  </si>
+  <si>
+    <t>Arca di san Savino</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Galleria Regionale della Sicilia</t>
+  </si>
+  <si>
+    <t>Buste d'Éléonore d'Aragon</t>
+  </si>
+  <si>
+    <t>Busto di Eleonora d'Aragona</t>
+  </si>
+  <si>
+    <t>Buste de portrait</t>
+  </si>
+  <si>
+    <t>around 43 cm</t>
+  </si>
+  <si>
+    <t>1471-1474</t>
+  </si>
+  <si>
+    <t>Naples</t>
+  </si>
+  <si>
+    <t>Castel Nuovo</t>
+  </si>
+  <si>
+    <t>Arc de triomphe d'Alphonse d'Aragon</t>
+  </si>
+  <si>
+    <t>Le Triomphe d'Alphonse d'Aragon (Reliefs)</t>
+  </si>
+  <si>
+    <t>Il Trionfo di Alfonso d'Aragona</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Triumphbogen_Castel_Nuovo_Neapel.jpg/500px-Triumphbogen_Castel_Nuovo_Neapel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Relief monumental architectural</t>
+  </si>
+  <si>
+    <t>around 150 cm</t>
+  </si>
+  <si>
+    <t>v. 1475</t>
+  </si>
+  <si>
+    <t>Département des Sculptures</t>
+  </si>
+  <si>
+    <t>Buste de Marie de Sicile</t>
+  </si>
+  <si>
+    <t>Busto di Maria di Sicilia</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>around 44 cm</t>
+  </si>
+  <si>
+    <t>v. 1474-1475</t>
+  </si>
+  <si>
+    <t>Vienne</t>
+  </si>
+  <si>
+    <t>Kunsthistorisches Museum</t>
+  </si>
+  <si>
+    <t>Kunstkammer</t>
+  </si>
+  <si>
+    <t>Buste de Laure de Noves</t>
+  </si>
+  <si>
+    <t>Busto di Laura de Noves</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Marbre polychrome</t>
+  </si>
+  <si>
+    <t>around 40 cm</t>
+  </si>
+  <si>
+    <t>Compianto sul Cristo morto (groupe en terre cuite polychrome)</t>
+  </si>
+  <si>
+    <t>Compianto sul Cristo morto</t>
+  </si>
+  <si>
+    <t>Groupe sculptural</t>
+  </si>
+  <si>
+    <t>1480-1485</t>
+  </si>
+  <si>
+    <t>Ferrare</t>
+  </si>
+  <si>
+    <t>Église Gesù</t>
+  </si>
+  <si>
+    <t>Déploration sur le Christ mort</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1485</t>
+  </si>
+  <si>
+    <t>Cathédrale de Modène</t>
+  </si>
+  <si>
+    <t>Crypta</t>
+  </si>
+  <si>
+    <t>L'Adoration des bergers (Crèche)</t>
+  </si>
+  <si>
+    <t>Presepio (Adorazione dei pastori)</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/20/Mazzoni_Adoration_Modena.jpg/1280px-Mazzoni_Adoration_Modena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1492-1494</t>
+  </si>
+  <si>
+    <t>Église Sant'Anna dei Lombardi</t>
+  </si>
+  <si>
+    <t>Cappella Compianto</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg/1280px-GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1559,6 +1931,12 @@
       <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1585,13 +1963,10 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1899,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -1908,7 +2283,7 @@
     <col min="9" max="9" width="36.28515625" customWidth="1"/>
     <col min="16" max="16" width="1" customWidth="1"/>
     <col min="17" max="17" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="22" max="22" width="9.140625" style="3"/>
+    <col min="22" max="22" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
@@ -1972,7 +2347,7 @@
       <c r="U1" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2077,158 +2452,182 @@
         <v>47</v>
       </c>
       <c r="I5" t="s">
+        <v>545</v>
+      </c>
+      <c r="J5" t="s">
+        <v>546</v>
+      </c>
+      <c r="K5" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="1" t="s">
-        <v>49</v>
+      <c r="Q5" t="s">
+        <v>547</v>
       </c>
       <c r="R5" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="2">
-        <v>3</v>
+      <c r="S5" t="s">
+        <v>548</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>549</v>
       </c>
       <c r="D6" t="s">
         <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>54</v>
+        <v>550</v>
+      </c>
+      <c r="J6" t="s">
+        <v>551</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>55</v>
+        <v>552</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>547</v>
       </c>
       <c r="R6" t="s">
         <v>36</v>
       </c>
-      <c r="V6" s="2">
-        <v>3</v>
+      <c r="S6" t="s">
+        <v>553</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>554</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="I7" t="s">
-        <v>485</v>
+        <v>555</v>
       </c>
       <c r="J7" t="s">
-        <v>486</v>
+        <v>556</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>61</v>
+        <v>557</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>547</v>
       </c>
       <c r="R7" t="s">
         <v>36</v>
       </c>
       <c r="S7" t="s">
-        <v>487</v>
-      </c>
-      <c r="V7" s="2">
-        <v>3</v>
+        <v>558</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>488</v>
+        <v>559</v>
       </c>
       <c r="D8" t="s">
         <v>46</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="G8" t="s">
+        <v>560</v>
       </c>
       <c r="I8" t="s">
-        <v>489</v>
+        <v>561</v>
       </c>
       <c r="J8" t="s">
-        <v>490</v>
+        <v>562</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>491</v>
+        <v>563</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>324</v>
       </c>
       <c r="R8" t="s">
         <v>36</v>
       </c>
-      <c r="S8" t="s">
-        <v>492</v>
-      </c>
-      <c r="V8" s="2">
-        <v>3</v>
+      <c r="V8" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>493</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>46</v>
       </c>
       <c r="E9" t="s">
-        <v>324</v>
+        <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>494</v>
+        <v>564</v>
       </c>
       <c r="J9" t="s">
-        <v>495</v>
+        <v>565</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>496</v>
+        <v>53</v>
       </c>
       <c r="R9" t="s">
         <v>36</v>
       </c>
-      <c r="V9" s="2">
-        <v>3</v>
+      <c r="V9" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>497</v>
+        <v>566</v>
       </c>
       <c r="D10" t="s">
         <v>46</v>
@@ -2237,323 +2636,293 @@
         <v>47</v>
       </c>
       <c r="I10" t="s">
-        <v>498</v>
+        <v>567</v>
       </c>
       <c r="J10" t="s">
-        <v>499</v>
+        <v>568</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>500</v>
+        <v>569</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>317</v>
       </c>
       <c r="R10" t="s">
         <v>36</v>
       </c>
       <c r="S10" t="s">
-        <v>501</v>
-      </c>
-      <c r="V10" s="2">
-        <v>3</v>
+        <v>548</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>313</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>306</v>
       </c>
       <c r="I11" t="s">
-        <v>67</v>
+        <v>254</v>
+      </c>
+      <c r="J11" t="s">
+        <v>255</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>68</v>
+        <v>570</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>571</v>
       </c>
       <c r="R11" t="s">
-        <v>69</v>
-      </c>
-      <c r="V11" s="3">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="S11" t="s">
+        <v>572</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>573</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>574</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>575</v>
       </c>
       <c r="I12" t="s">
-        <v>75</v>
+        <v>576</v>
+      </c>
+      <c r="J12" t="s">
+        <v>577</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>76</v>
+        <v>578</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>324</v>
       </c>
       <c r="R12" t="s">
-        <v>28</v>
-      </c>
-      <c r="V12" s="3">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="I13" t="s">
-        <v>196</v>
+        <v>480</v>
       </c>
       <c r="J13" t="s">
-        <v>197</v>
+        <v>481</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>198</v>
+        <v>59</v>
       </c>
       <c r="R13" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S13" t="s">
-        <v>294</v>
-      </c>
-      <c r="V13" s="3" t="s">
-        <v>200</v>
+        <v>482</v>
+      </c>
+      <c r="V13" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>295</v>
+        <v>483</v>
       </c>
       <c r="D14" t="s">
         <v>46</v>
       </c>
       <c r="E14" t="s">
-        <v>211</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>258</v>
+        <v>52</v>
       </c>
       <c r="I14" t="s">
-        <v>296</v>
+        <v>484</v>
       </c>
       <c r="J14" t="s">
-        <v>297</v>
+        <v>485</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>298</v>
-      </c>
-      <c r="L14" t="s">
-        <v>299</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>301</v>
+        <v>486</v>
       </c>
       <c r="R14" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S14" t="s">
-        <v>302</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>200</v>
+        <v>487</v>
+      </c>
+      <c r="V14" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>303</v>
+        <v>488</v>
       </c>
       <c r="D15" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E15" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="I15" t="s">
-        <v>305</v>
+        <v>489</v>
       </c>
       <c r="J15" t="s">
-        <v>306</v>
+        <v>490</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>308</v>
+        <v>491</v>
       </c>
       <c r="R15" t="s">
-        <v>28</v>
-      </c>
-      <c r="S15" t="s">
-        <v>309</v>
-      </c>
-      <c r="T15">
-        <v>380</v>
-      </c>
-      <c r="V15" s="3" t="s">
-        <v>200</v>
+        <v>36</v>
+      </c>
+      <c r="V15" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
-        <v>310</v>
+        <v>492</v>
       </c>
       <c r="D16" t="s">
         <v>46</v>
       </c>
       <c r="E16" t="s">
-        <v>311</v>
+        <v>47</v>
       </c>
       <c r="I16" t="s">
-        <v>312</v>
+        <v>493</v>
       </c>
       <c r="J16" t="s">
-        <v>313</v>
+        <v>494</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="L16" t="s">
-        <v>315</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>316</v>
+        <v>495</v>
       </c>
       <c r="R16" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="S16" t="s">
-        <v>317</v>
-      </c>
-      <c r="V16" s="3" t="s">
-        <v>200</v>
+        <v>496</v>
+      </c>
+      <c r="V16" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="B17" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
-        <v>318</v>
+        <v>62</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="I17" t="s">
-        <v>319</v>
-      </c>
-      <c r="J17" t="s">
-        <v>320</v>
+        <v>65</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>322</v>
+        <v>66</v>
       </c>
       <c r="R17" t="s">
-        <v>36</v>
-      </c>
-      <c r="S17" t="s">
-        <v>224</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>200</v>
+        <v>67</v>
+      </c>
+      <c r="V17" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="C18" t="s">
-        <v>323</v>
+        <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>46</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
-        <v>324</v>
-      </c>
-      <c r="G18" t="s">
-        <v>325</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>326</v>
-      </c>
-      <c r="J18" t="s">
-        <v>327</v>
+        <v>73</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>329</v>
+        <v>74</v>
       </c>
       <c r="R18" t="s">
-        <v>330</v>
-      </c>
-      <c r="V18" s="3" t="s">
-        <v>200</v>
+        <v>28</v>
+      </c>
+      <c r="V18" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
@@ -2561,10 +2930,10 @@
         <v>29</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C19" t="s">
-        <v>331</v>
+        <v>76</v>
       </c>
       <c r="D19" t="s">
         <v>46</v>
@@ -2573,25 +2942,25 @@
         <v>47</v>
       </c>
       <c r="I19" t="s">
-        <v>332</v>
+        <v>191</v>
       </c>
       <c r="J19" t="s">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>334</v>
+        <v>288</v>
       </c>
       <c r="Q19" t="s">
-        <v>322</v>
+        <v>193</v>
       </c>
       <c r="R19" t="s">
-        <v>335</v>
+        <v>28</v>
       </c>
       <c r="S19" t="s">
-        <v>336</v>
-      </c>
-      <c r="V19" s="3" t="s">
-        <v>200</v>
+        <v>289</v>
+      </c>
+      <c r="V19" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
@@ -2599,2119 +2968,2910 @@
         <v>29</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C20" t="s">
-        <v>337</v>
+        <v>290</v>
       </c>
       <c r="D20" t="s">
         <v>46</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>206</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="I20" t="s">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="J20" t="s">
-        <v>339</v>
+        <v>292</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>340</v>
+        <v>293</v>
       </c>
       <c r="L20" t="s">
-        <v>341</v>
+        <v>294</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="Q20" t="s">
-        <v>223</v>
+        <v>296</v>
       </c>
       <c r="R20" t="s">
-        <v>342</v>
+        <v>28</v>
       </c>
       <c r="S20" t="s">
-        <v>343</v>
-      </c>
-      <c r="T20" t="s">
-        <v>344</v>
-      </c>
-      <c r="V20" s="3" t="s">
-        <v>200</v>
+        <v>297</v>
+      </c>
+      <c r="V20" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B21" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>81</v>
+        <v>298</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="I21" t="s">
-        <v>84</v>
+        <v>300</v>
+      </c>
+      <c r="J21" t="s">
+        <v>301</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>85</v>
+        <v>302</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>303</v>
       </c>
       <c r="R21" t="s">
-        <v>86</v>
-      </c>
-      <c r="V21" s="3">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="S21" t="s">
+        <v>304</v>
+      </c>
+      <c r="T21">
+        <v>380</v>
+      </c>
+      <c r="V21" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>305</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>46</v>
       </c>
       <c r="E22" t="s">
-        <v>91</v>
-      </c>
-      <c r="G22" t="s">
-        <v>449</v>
+        <v>306</v>
       </c>
       <c r="I22" t="s">
-        <v>450</v>
+        <v>307</v>
       </c>
       <c r="J22" t="s">
-        <v>451</v>
+        <v>308</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>92</v>
+        <v>309</v>
+      </c>
+      <c r="L22" t="s">
+        <v>310</v>
       </c>
       <c r="Q22" t="s">
-        <v>452</v>
+        <v>311</v>
       </c>
       <c r="R22" t="s">
-        <v>36</v>
-      </c>
-      <c r="V22" s="2">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="S22" t="s">
+        <v>312</v>
+      </c>
+      <c r="V22" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C23" t="s">
-        <v>453</v>
+        <v>313</v>
       </c>
       <c r="D23" t="s">
-        <v>454</v>
+        <v>46</v>
       </c>
       <c r="E23" t="s">
-        <v>455</v>
+        <v>47</v>
       </c>
       <c r="I23" t="s">
-        <v>456</v>
+        <v>314</v>
       </c>
       <c r="J23" t="s">
-        <v>457</v>
+        <v>315</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>458</v>
+        <v>316</v>
       </c>
       <c r="Q23" t="s">
-        <v>459</v>
+        <v>317</v>
       </c>
       <c r="R23" t="s">
         <v>36</v>
       </c>
-      <c r="V23" s="2">
-        <v>2</v>
+      <c r="S23" t="s">
+        <v>219</v>
+      </c>
+      <c r="V23" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C24" t="s">
-        <v>460</v>
+        <v>318</v>
       </c>
       <c r="D24" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="E24" t="s">
-        <v>461</v>
+        <v>319</v>
       </c>
       <c r="G24" t="s">
-        <v>462</v>
+        <v>320</v>
       </c>
       <c r="I24" t="s">
-        <v>463</v>
+        <v>321</v>
       </c>
       <c r="J24" t="s">
-        <v>464</v>
+        <v>322</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>465</v>
+        <v>323</v>
       </c>
       <c r="Q24" t="s">
-        <v>466</v>
+        <v>324</v>
       </c>
       <c r="R24" t="s">
-        <v>467</v>
-      </c>
-      <c r="V24" s="2">
-        <v>2</v>
+        <v>325</v>
+      </c>
+      <c r="V24" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B25" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C25" t="s">
-        <v>468</v>
+        <v>326</v>
       </c>
       <c r="D25" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="E25" t="s">
-        <v>461</v>
-      </c>
-      <c r="G25" t="s">
-        <v>464</v>
+        <v>47</v>
       </c>
       <c r="I25" t="s">
-        <v>469</v>
+        <v>327</v>
       </c>
       <c r="J25" t="s">
-        <v>470</v>
+        <v>328</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="L25" t="s">
-        <v>464</v>
+        <v>329</v>
       </c>
       <c r="Q25" t="s">
-        <v>472</v>
+        <v>317</v>
       </c>
       <c r="R25" t="s">
-        <v>467</v>
+        <v>330</v>
       </c>
       <c r="S25" t="s">
-        <v>473</v>
-      </c>
-      <c r="T25" t="s">
-        <v>474</v>
-      </c>
-      <c r="V25" s="2">
-        <v>2</v>
+        <v>331</v>
+      </c>
+      <c r="V25" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>87</v>
+        <v>29</v>
       </c>
       <c r="B26" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="C26" t="s">
-        <v>210</v>
+        <v>332</v>
       </c>
       <c r="D26" t="s">
-        <v>454</v>
+        <v>46</v>
       </c>
       <c r="E26" t="s">
-        <v>475</v>
-      </c>
-      <c r="G26" t="s">
-        <v>476</v>
+        <v>99</v>
       </c>
       <c r="I26" t="s">
-        <v>477</v>
+        <v>333</v>
       </c>
       <c r="J26" t="s">
-        <v>478</v>
+        <v>334</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>479</v>
+        <v>335</v>
+      </c>
+      <c r="L26" t="s">
+        <v>336</v>
       </c>
       <c r="Q26" t="s">
-        <v>480</v>
+        <v>218</v>
       </c>
       <c r="R26" t="s">
-        <v>36</v>
-      </c>
-      <c r="V26" s="2">
-        <v>2</v>
+        <v>337</v>
+      </c>
+      <c r="S26" t="s">
+        <v>338</v>
+      </c>
+      <c r="T26" t="s">
+        <v>339</v>
+      </c>
+      <c r="V26" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>210</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>454</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>475</v>
-      </c>
-      <c r="G27" t="s">
-        <v>476</v>
+        <v>81</v>
       </c>
       <c r="I27" t="s">
-        <v>481</v>
-      </c>
-      <c r="J27" t="s">
-        <v>482</v>
+        <v>82</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>484</v>
+        <v>83</v>
       </c>
       <c r="R27" t="s">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="V27" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="D28" t="s">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="E28" t="s">
-        <v>95</v>
+        <v>89</v>
+      </c>
+      <c r="G28" t="s">
+        <v>444</v>
       </c>
       <c r="I28" t="s">
-        <v>96</v>
+        <v>445</v>
+      </c>
+      <c r="J28" t="s">
+        <v>446</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>97</v>
+        <v>90</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>447</v>
       </c>
       <c r="R28" t="s">
-        <v>98</v>
-      </c>
-      <c r="V28" s="3">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="V28" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
-        <v>379</v>
+        <v>448</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>449</v>
       </c>
       <c r="E29" t="s">
-        <v>121</v>
+        <v>450</v>
       </c>
       <c r="I29" t="s">
-        <v>380</v>
+        <v>451</v>
       </c>
       <c r="J29" t="s">
-        <v>381</v>
+        <v>452</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>382</v>
+        <v>453</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>454</v>
       </c>
       <c r="R29" t="s">
-        <v>353</v>
-      </c>
-      <c r="S29">
-        <v>118</v>
-      </c>
-      <c r="T29">
-        <v>73</v>
-      </c>
-      <c r="U29">
-        <v>16</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>200</v>
+        <v>36</v>
+      </c>
+      <c r="V29" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
-        <v>100</v>
+        <v>455</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>456</v>
+      </c>
+      <c r="G30" t="s">
+        <v>457</v>
       </c>
       <c r="I30" t="s">
-        <v>345</v>
+        <v>458</v>
       </c>
       <c r="J30" t="s">
-        <v>346</v>
+        <v>459</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>102</v>
+        <v>460</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>461</v>
       </c>
       <c r="R30" t="s">
-        <v>36</v>
-      </c>
-      <c r="S30" t="s">
-        <v>347</v>
-      </c>
-      <c r="T30" t="s">
-        <v>348</v>
-      </c>
-      <c r="V30" s="3">
-        <v>1</v>
+        <v>462</v>
+      </c>
+      <c r="V30" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>349</v>
+        <v>463</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="E31" t="s">
-        <v>287</v>
+        <v>456</v>
+      </c>
+      <c r="G31" t="s">
+        <v>459</v>
       </c>
       <c r="I31" t="s">
-        <v>350</v>
+        <v>464</v>
       </c>
       <c r="J31" t="s">
-        <v>351</v>
+        <v>465</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>352</v>
+        <v>466</v>
+      </c>
+      <c r="L31" t="s">
+        <v>459</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>467</v>
       </c>
       <c r="R31" t="s">
-        <v>353</v>
-      </c>
-      <c r="V31" s="3">
-        <v>1</v>
+        <v>462</v>
+      </c>
+      <c r="S31" t="s">
+        <v>468</v>
+      </c>
+      <c r="T31" t="s">
+        <v>469</v>
+      </c>
+      <c r="V31" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>354</v>
+        <v>205</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>449</v>
       </c>
       <c r="E32" t="s">
-        <v>287</v>
+        <v>470</v>
+      </c>
+      <c r="G32" t="s">
+        <v>471</v>
       </c>
       <c r="I32" t="s">
-        <v>355</v>
+        <v>472</v>
       </c>
       <c r="J32" t="s">
-        <v>356</v>
+        <v>473</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>357</v>
+        <v>474</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>475</v>
       </c>
       <c r="R32" t="s">
-        <v>28</v>
-      </c>
-      <c r="V32" s="3">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="V32" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>358</v>
+        <v>205</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>449</v>
       </c>
       <c r="E33" t="s">
-        <v>359</v>
+        <v>470</v>
+      </c>
+      <c r="G33" t="s">
+        <v>471</v>
       </c>
       <c r="I33" t="s">
-        <v>360</v>
+        <v>476</v>
       </c>
       <c r="J33" t="s">
-        <v>361</v>
+        <v>477</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>362</v>
+        <v>478</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>479</v>
       </c>
       <c r="R33" t="s">
-        <v>363</v>
-      </c>
-      <c r="V33" s="3">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="V33" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C34" t="s">
-        <v>180</v>
+        <v>92</v>
       </c>
       <c r="D34" t="s">
         <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>359</v>
+        <v>93</v>
       </c>
       <c r="I34" t="s">
-        <v>364</v>
-      </c>
-      <c r="J34" t="s">
-        <v>365</v>
+        <v>94</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>366</v>
+        <v>95</v>
       </c>
       <c r="R34" t="s">
-        <v>353</v>
-      </c>
-      <c r="V34" s="3">
+        <v>96</v>
+      </c>
+      <c r="V34" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>29</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C35" t="s">
-        <v>185</v>
+        <v>374</v>
       </c>
       <c r="D35" t="s">
-        <v>367</v>
+        <v>118</v>
       </c>
       <c r="E35" t="s">
-        <v>368</v>
+        <v>119</v>
       </c>
       <c r="I35" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="J35" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>371</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="R35" t="s">
-        <v>353</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>200</v>
+        <v>348</v>
+      </c>
+      <c r="S35">
+        <v>118</v>
+      </c>
+      <c r="T35">
+        <v>73</v>
+      </c>
+      <c r="U35">
+        <v>16</v>
+      </c>
+      <c r="V35" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>373</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>375</v>
+        <v>99</v>
       </c>
       <c r="I36" t="s">
-        <v>376</v>
+        <v>340</v>
       </c>
       <c r="J36" t="s">
-        <v>377</v>
+        <v>341</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>378</v>
+        <v>100</v>
       </c>
       <c r="R36" t="s">
-        <v>353</v>
-      </c>
-      <c r="V36" s="3" t="s">
-        <v>200</v>
+        <v>36</v>
+      </c>
+      <c r="S36" t="s">
+        <v>342</v>
+      </c>
+      <c r="T36" t="s">
+        <v>343</v>
+      </c>
+      <c r="V36" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B37" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="C37" t="s">
-        <v>105</v>
+        <v>344</v>
+      </c>
+      <c r="D37" t="s">
+        <v>46</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>282</v>
       </c>
       <c r="I37" t="s">
-        <v>107</v>
+        <v>345</v>
+      </c>
+      <c r="J37" t="s">
+        <v>346</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>108</v>
+        <v>347</v>
       </c>
       <c r="R37" t="s">
-        <v>109</v>
-      </c>
-      <c r="V37" s="3">
-        <v>3</v>
+        <v>348</v>
+      </c>
+      <c r="V37" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C38" t="s">
-        <v>112</v>
+        <v>349</v>
       </c>
       <c r="D38" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>282</v>
       </c>
       <c r="I38" t="s">
-        <v>115</v>
+        <v>350</v>
+      </c>
+      <c r="J38" t="s">
+        <v>351</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>116</v>
+        <v>352</v>
       </c>
       <c r="R38" t="s">
-        <v>36</v>
-      </c>
-      <c r="V38" s="3">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="V38" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>353</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="E39" t="s">
-        <v>121</v>
+        <v>354</v>
       </c>
       <c r="I39" t="s">
-        <v>122</v>
+        <v>355</v>
+      </c>
+      <c r="J39" t="s">
+        <v>356</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>123</v>
+        <v>357</v>
       </c>
       <c r="R39" t="s">
-        <v>124</v>
-      </c>
-      <c r="V39" s="3">
-        <v>3</v>
+        <v>358</v>
+      </c>
+      <c r="V39" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
+        <v>176</v>
       </c>
       <c r="D40" t="s">
         <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>47</v>
+        <v>354</v>
       </c>
       <c r="I40" t="s">
-        <v>128</v>
+        <v>359</v>
+      </c>
+      <c r="J40" t="s">
+        <v>360</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>129</v>
+        <v>361</v>
       </c>
       <c r="R40" t="s">
-        <v>28</v>
-      </c>
-      <c r="V40" s="3">
-        <v>3</v>
+        <v>348</v>
+      </c>
+      <c r="V40" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C41" t="s">
-        <v>132</v>
+        <v>181</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>362</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>363</v>
       </c>
       <c r="I41" t="s">
-        <v>196</v>
+        <v>364</v>
       </c>
       <c r="J41" t="s">
-        <v>197</v>
+        <v>365</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>198</v>
+        <v>366</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>367</v>
       </c>
       <c r="R41" t="s">
-        <v>28</v>
-      </c>
-      <c r="S41" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="T41" s="2">
-        <v>51</v>
-      </c>
-      <c r="V41" s="3">
-        <v>1</v>
+        <v>348</v>
+      </c>
+      <c r="V41" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>201</v>
+        <v>79</v>
       </c>
       <c r="D42" t="s">
         <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>368</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>370</v>
       </c>
       <c r="I42" t="s">
-        <v>196</v>
+        <v>371</v>
       </c>
       <c r="J42" t="s">
-        <v>202</v>
+        <v>372</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>198</v>
+        <v>373</v>
       </c>
       <c r="R42" t="s">
-        <v>36</v>
-      </c>
-      <c r="S42" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="T42" s="2">
-        <v>57</v>
-      </c>
-      <c r="V42" s="3">
-        <v>1</v>
+        <v>348</v>
+      </c>
+      <c r="V42" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="B43" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
-      </c>
-      <c r="D43" t="s">
-        <v>46</v>
+        <v>103</v>
       </c>
       <c r="E43" t="s">
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="I43" t="s">
-        <v>206</v>
-      </c>
-      <c r="J43" t="s">
-        <v>207</v>
+        <v>105</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>198</v>
+        <v>106</v>
       </c>
       <c r="R43" t="s">
-        <v>36</v>
-      </c>
-      <c r="S43" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="T43" s="2"/>
-      <c r="V43" s="3" t="s">
-        <v>200</v>
+        <v>107</v>
+      </c>
+      <c r="V43" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C44" t="s">
-        <v>210</v>
+        <v>110</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="E44" t="s">
-        <v>211</v>
+        <v>112</v>
       </c>
       <c r="I44" t="s">
-        <v>212</v>
-      </c>
-      <c r="J44" t="s">
-        <v>213</v>
+        <v>113</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>198</v>
+        <v>114</v>
       </c>
       <c r="R44" t="s">
         <v>36</v>
       </c>
-      <c r="S44" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="T44" s="2"/>
-      <c r="V44" s="3" t="s">
-        <v>200</v>
+      <c r="V44" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>130</v>
+        <v>115</v>
       </c>
       <c r="B45" t="s">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C45" t="s">
-        <v>216</v>
+        <v>117</v>
       </c>
       <c r="D45" t="s">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="E45" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="I45" t="s">
-        <v>218</v>
-      </c>
-      <c r="J45" t="s">
-        <v>219</v>
+        <v>120</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="L45" t="s">
-        <v>221</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>223</v>
+        <v>121</v>
       </c>
       <c r="R45" t="s">
-        <v>152</v>
-      </c>
-      <c r="S45" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="T45" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="V45" s="3" t="s">
-        <v>200</v>
+        <v>122</v>
+      </c>
+      <c r="V45" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="B46" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="C46" t="s">
-        <v>225</v>
+        <v>125</v>
       </c>
       <c r="D46" t="s">
         <v>46</v>
       </c>
       <c r="E46" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="I46" t="s">
-        <v>226</v>
-      </c>
-      <c r="J46" t="s">
-        <v>227</v>
+        <v>126</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>228</v>
+        <v>127</v>
       </c>
       <c r="R46" t="s">
-        <v>229</v>
-      </c>
-      <c r="S46" s="2">
-        <v>420</v>
-      </c>
-      <c r="T46" s="2">
-        <v>274</v>
-      </c>
-      <c r="U46">
-        <v>30</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>200</v>
+        <v>28</v>
+      </c>
+      <c r="V46" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B47" t="s">
+        <v>129</v>
+      </c>
+      <c r="C47" t="s">
         <v>130</v>
       </c>
-      <c r="B47" t="s">
+      <c r="D47" t="s">
+        <v>46</v>
+      </c>
+      <c r="E47" t="s">
+        <v>47</v>
+      </c>
+      <c r="I47" t="s">
+        <v>191</v>
+      </c>
+      <c r="J47" t="s">
+        <v>192</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="C47" t="s">
-        <v>230</v>
-      </c>
-      <c r="D47" t="s">
-        <v>231</v>
-      </c>
-      <c r="E47" t="s">
-        <v>232</v>
-      </c>
-      <c r="I47" t="s">
-        <v>233</v>
-      </c>
-      <c r="J47" t="s">
-        <v>234</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>235</v>
+      <c r="Q47" t="s">
+        <v>193</v>
       </c>
       <c r="R47" t="s">
         <v>28</v>
       </c>
       <c r="S47" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="T47" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="V47" s="3" t="s">
-        <v>200</v>
+        <v>194</v>
+      </c>
+      <c r="T47" s="2">
+        <v>51</v>
+      </c>
+      <c r="V47" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C48" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="D48" t="s">
         <v>46</v>
       </c>
       <c r="E48" t="s">
-        <v>101</v>
+        <v>47</v>
       </c>
       <c r="I48" t="s">
-        <v>239</v>
+        <v>191</v>
       </c>
       <c r="J48" t="s">
-        <v>240</v>
+        <v>197</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>241</v>
+        <v>198</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>193</v>
       </c>
       <c r="R48" t="s">
-        <v>242</v>
+        <v>36</v>
       </c>
       <c r="S48" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="T48" s="2"/>
-      <c r="V48" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
+      </c>
+      <c r="T48" s="2">
+        <v>57</v>
+      </c>
+      <c r="V48" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B49" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C49" t="s">
-        <v>136</v>
+        <v>200</v>
       </c>
       <c r="D49" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="E49" t="s">
-        <v>138</v>
+        <v>47</v>
       </c>
       <c r="I49" t="s">
-        <v>139</v>
+        <v>201</v>
+      </c>
+      <c r="J49" t="s">
+        <v>202</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>140</v>
+        <v>203</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>193</v>
       </c>
       <c r="R49" t="s">
         <v>36</v>
       </c>
-      <c r="V49" s="3">
-        <v>3</v>
+      <c r="S49" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="T49" s="2"/>
+      <c r="V49" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="B50" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C50" t="s">
-        <v>143</v>
+        <v>205</v>
       </c>
       <c r="D50" t="s">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="E50" t="s">
-        <v>145</v>
+        <v>206</v>
       </c>
       <c r="I50" t="s">
-        <v>146</v>
+        <v>207</v>
+      </c>
+      <c r="J50" t="s">
+        <v>208</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>147</v>
+        <v>209</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>193</v>
       </c>
       <c r="R50" t="s">
-        <v>148</v>
-      </c>
-      <c r="V50" s="3">
-        <v>3</v>
+        <v>36</v>
+      </c>
+      <c r="S50" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="T50" s="2"/>
+      <c r="V50" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
+        <v>129</v>
+      </c>
+      <c r="C51" t="s">
+        <v>211</v>
+      </c>
+      <c r="D51" t="s">
+        <v>88</v>
+      </c>
+      <c r="E51" t="s">
+        <v>212</v>
+      </c>
+      <c r="I51" t="s">
+        <v>213</v>
+      </c>
+      <c r="J51" t="s">
+        <v>214</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="L51" t="s">
+        <v>216</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>218</v>
+      </c>
+      <c r="R51" t="s">
         <v>150</v>
       </c>
-      <c r="C51" t="s">
-        <v>151</v>
-      </c>
-      <c r="D51" t="s">
-        <v>46</v>
-      </c>
-      <c r="E51" t="s">
-        <v>101</v>
-      </c>
-      <c r="I51" t="s">
-        <v>244</v>
-      </c>
-      <c r="J51" t="s">
-        <v>245</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>223</v>
-      </c>
-      <c r="R51" t="s">
-        <v>152</v>
-      </c>
-      <c r="S51" t="s">
-        <v>249</v>
-      </c>
-      <c r="T51" t="s">
-        <v>250</v>
-      </c>
-      <c r="U51">
-        <v>11</v>
-      </c>
-      <c r="V51" s="3">
-        <v>1</v>
+      <c r="S51" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="T51" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V51" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="C52" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="D52" t="s">
         <v>46</v>
       </c>
       <c r="E52" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="I52" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="J52" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q52" t="s">
         <v>223</v>
       </c>
       <c r="R52" t="s">
-        <v>28</v>
-      </c>
-      <c r="S52" t="s">
-        <v>255</v>
-      </c>
-      <c r="T52" t="s">
-        <v>256</v>
-      </c>
-      <c r="V52" s="3">
-        <v>1</v>
+        <v>224</v>
+      </c>
+      <c r="S52" s="2">
+        <v>420</v>
+      </c>
+      <c r="T52" s="2">
+        <v>274</v>
+      </c>
+      <c r="U52">
+        <v>30</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="C53" t="s">
-        <v>257</v>
+        <v>225</v>
       </c>
       <c r="D53" t="s">
-        <v>46</v>
+        <v>226</v>
       </c>
       <c r="E53" t="s">
-        <v>211</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="I53" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="J53" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="L53" t="s">
-        <v>262</v>
-      </c>
-      <c r="M53" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="Q53" t="s">
-        <v>198</v>
+        <v>230</v>
       </c>
       <c r="R53" t="s">
         <v>28</v>
       </c>
-      <c r="S53" t="s">
-        <v>264</v>
-      </c>
-      <c r="V53" s="3">
-        <v>1</v>
+      <c r="S53" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="T53" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="V53" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>149</v>
+        <v>128</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>129</v>
       </c>
       <c r="C54" t="s">
-        <v>265</v>
+        <v>233</v>
       </c>
       <c r="D54" t="s">
         <v>46</v>
       </c>
       <c r="E54" t="s">
-        <v>211</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>258</v>
+        <v>99</v>
       </c>
       <c r="I54" t="s">
-        <v>266</v>
+        <v>234</v>
       </c>
       <c r="J54" t="s">
-        <v>267</v>
+        <v>235</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="L54" t="s">
-        <v>269</v>
-      </c>
-      <c r="M54" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>198</v>
+        <v>236</v>
       </c>
       <c r="R54" t="s">
-        <v>28</v>
-      </c>
-      <c r="S54" t="s">
-        <v>256</v>
-      </c>
-      <c r="V54" s="3">
-        <v>1</v>
+        <v>237</v>
+      </c>
+      <c r="S54" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="T54" s="2"/>
+      <c r="V54" s="2" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="C55" t="s">
-        <v>271</v>
+        <v>134</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>135</v>
       </c>
       <c r="E55" t="s">
-        <v>211</v>
-      </c>
-      <c r="F55" s="1" t="s">
-        <v>258</v>
+        <v>136</v>
       </c>
       <c r="I55" t="s">
-        <v>272</v>
-      </c>
-      <c r="J55" t="s">
-        <v>273</v>
+        <v>137</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="L55" t="s">
-        <v>275</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q55" t="s">
-        <v>198</v>
+        <v>138</v>
       </c>
       <c r="R55" t="s">
-        <v>28</v>
-      </c>
-      <c r="S55" t="s">
-        <v>277</v>
-      </c>
-      <c r="V55" s="3">
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="V55" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C56" t="s">
-        <v>278</v>
+        <v>141</v>
       </c>
       <c r="D56" t="s">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
-        <v>217</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="I56" t="s">
-        <v>280</v>
-      </c>
-      <c r="J56" t="s">
-        <v>281</v>
+        <v>144</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="Q56" t="s">
-        <v>223</v>
+        <v>145</v>
       </c>
       <c r="R56" t="s">
-        <v>152</v>
-      </c>
-      <c r="S56" t="s">
-        <v>224</v>
-      </c>
-      <c r="T56" t="s">
-        <v>224</v>
-      </c>
-      <c r="V56" s="3">
-        <v>1</v>
+        <v>146</v>
+      </c>
+      <c r="V56" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>147</v>
+      </c>
+      <c r="B57" t="s">
+        <v>148</v>
+      </c>
+      <c r="C57" t="s">
         <v>149</v>
       </c>
-      <c r="B57" t="s">
+      <c r="D57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" t="s">
+        <v>99</v>
+      </c>
+      <c r="I57" t="s">
+        <v>239</v>
+      </c>
+      <c r="J57" t="s">
+        <v>240</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>218</v>
+      </c>
+      <c r="R57" t="s">
         <v>150</v>
       </c>
-      <c r="C57" t="s">
-        <v>278</v>
-      </c>
-      <c r="D57" t="s">
-        <v>90</v>
-      </c>
-      <c r="E57" t="s">
-        <v>217</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="I57" t="s">
-        <v>283</v>
-      </c>
-      <c r="J57" t="s">
-        <v>284</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>223</v>
-      </c>
-      <c r="R57" t="s">
-        <v>152</v>
-      </c>
       <c r="S57" t="s">
-        <v>224</v>
+        <v>244</v>
       </c>
       <c r="T57" t="s">
-        <v>224</v>
-      </c>
-      <c r="V57" s="3">
+        <v>245</v>
+      </c>
+      <c r="U57">
+        <v>11</v>
+      </c>
+      <c r="V57" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B58" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C58" t="s">
-        <v>286</v>
+        <v>246</v>
       </c>
       <c r="D58" t="s">
         <v>46</v>
       </c>
       <c r="E58" t="s">
-        <v>287</v>
-      </c>
-      <c r="G58" t="s">
-        <v>288</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>289</v>
+        <v>99</v>
       </c>
       <c r="I58" t="s">
-        <v>290</v>
+        <v>247</v>
       </c>
       <c r="J58" t="s">
-        <v>291</v>
+        <v>248</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>292</v>
+        <v>249</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="Q58" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="R58" t="s">
         <v>28</v>
       </c>
-      <c r="S58">
-        <v>85</v>
-      </c>
-      <c r="T58">
-        <v>193</v>
-      </c>
-      <c r="V58" s="3">
+      <c r="S58" t="s">
+        <v>250</v>
+      </c>
+      <c r="T58" t="s">
+        <v>251</v>
+      </c>
+      <c r="V58" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B59" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="C59" t="s">
-        <v>155</v>
+        <v>252</v>
       </c>
       <c r="D59" t="s">
-        <v>156</v>
+        <v>46</v>
       </c>
       <c r="E59" t="s">
-        <v>157</v>
+        <v>206</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="I59" t="s">
-        <v>158</v>
+        <v>254</v>
+      </c>
+      <c r="J59" t="s">
+        <v>255</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>159</v>
+        <v>256</v>
+      </c>
+      <c r="L59" t="s">
+        <v>257</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>193</v>
       </c>
       <c r="R59" t="s">
-        <v>160</v>
-      </c>
-      <c r="V59" s="3">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="S59" t="s">
+        <v>259</v>
+      </c>
+      <c r="V59" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="C60" t="s">
-        <v>162</v>
+        <v>260</v>
       </c>
       <c r="D60" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="E60" t="s">
-        <v>163</v>
+        <v>206</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="I60" t="s">
-        <v>164</v>
+        <v>261</v>
+      </c>
+      <c r="J60" t="s">
+        <v>262</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>165</v>
+        <v>263</v>
+      </c>
+      <c r="L60" t="s">
+        <v>264</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>193</v>
       </c>
       <c r="R60" t="s">
-        <v>36</v>
-      </c>
-      <c r="V60" s="3">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="S60" t="s">
+        <v>251</v>
+      </c>
+      <c r="V60" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="B61" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C61" t="s">
-        <v>168</v>
+        <v>266</v>
       </c>
       <c r="D61" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E61" t="s">
-        <v>169</v>
+        <v>206</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="I61" t="s">
-        <v>170</v>
+        <v>267</v>
+      </c>
+      <c r="J61" t="s">
+        <v>268</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>171</v>
+        <v>269</v>
+      </c>
+      <c r="L61" t="s">
+        <v>270</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>193</v>
       </c>
       <c r="R61" t="s">
-        <v>36</v>
-      </c>
-      <c r="V61" s="3">
-        <v>3</v>
+        <v>28</v>
+      </c>
+      <c r="S61" t="s">
+        <v>272</v>
+      </c>
+      <c r="V61" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="B62" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="C62" t="s">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="D62" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="E62" t="s">
-        <v>176</v>
+        <v>212</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="I62" t="s">
-        <v>177</v>
+        <v>275</v>
+      </c>
+      <c r="J62" t="s">
+        <v>276</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>178</v>
+        <v>277</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>218</v>
       </c>
       <c r="R62" t="s">
-        <v>86</v>
-      </c>
-      <c r="V62" s="3">
-        <v>3</v>
+        <v>150</v>
+      </c>
+      <c r="S62" t="s">
+        <v>219</v>
+      </c>
+      <c r="T62" t="s">
+        <v>219</v>
+      </c>
+      <c r="V62" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>409</v>
+        <v>147</v>
       </c>
       <c r="B63" t="s">
-        <v>410</v>
+        <v>148</v>
       </c>
       <c r="C63" t="s">
-        <v>411</v>
+        <v>273</v>
       </c>
       <c r="D63" t="s">
-        <v>412</v>
+        <v>88</v>
       </c>
       <c r="E63" t="s">
-        <v>413</v>
+        <v>212</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="I63" t="s">
-        <v>414</v>
+        <v>278</v>
       </c>
       <c r="J63" t="s">
-        <v>415</v>
+        <v>279</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>417</v>
+        <v>280</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>218</v>
       </c>
       <c r="R63" t="s">
-        <v>418</v>
+        <v>150</v>
       </c>
       <c r="S63" t="s">
-        <v>419</v>
-      </c>
-      <c r="V63" s="3">
-        <v>2</v>
+        <v>219</v>
+      </c>
+      <c r="T63" t="s">
+        <v>219</v>
+      </c>
+      <c r="V63" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>409</v>
+        <v>147</v>
       </c>
       <c r="B64" t="s">
-        <v>410</v>
+        <v>148</v>
       </c>
       <c r="C64" t="s">
-        <v>420</v>
+        <v>281</v>
       </c>
       <c r="D64" t="s">
-        <v>421</v>
+        <v>46</v>
       </c>
       <c r="E64" t="s">
-        <v>422</v>
+        <v>282</v>
+      </c>
+      <c r="G64" t="s">
+        <v>283</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="I64" t="s">
-        <v>423</v>
+        <v>285</v>
       </c>
       <c r="J64" t="s">
-        <v>424</v>
+        <v>286</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>425</v>
+        <v>287</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>218</v>
       </c>
       <c r="R64" t="s">
-        <v>405</v>
-      </c>
-      <c r="S64" t="s">
-        <v>426</v>
-      </c>
-      <c r="V64" s="3">
-        <v>2</v>
+        <v>28</v>
+      </c>
+      <c r="S64">
+        <v>85</v>
+      </c>
+      <c r="T64">
+        <v>193</v>
+      </c>
+      <c r="V64" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>409</v>
+        <v>151</v>
       </c>
       <c r="B65" t="s">
-        <v>410</v>
+        <v>152</v>
       </c>
       <c r="C65" t="s">
-        <v>427</v>
+        <v>153</v>
       </c>
       <c r="D65" t="s">
-        <v>428</v>
+        <v>154</v>
       </c>
       <c r="E65" t="s">
-        <v>429</v>
+        <v>155</v>
       </c>
       <c r="I65" t="s">
-        <v>430</v>
-      </c>
-      <c r="J65" t="s">
-        <v>431</v>
+        <v>156</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>432</v>
+        <v>157</v>
       </c>
       <c r="R65" t="s">
-        <v>433</v>
-      </c>
-      <c r="S65" t="s">
-        <v>434</v>
-      </c>
-      <c r="V65" s="3">
-        <v>2</v>
+        <v>158</v>
+      </c>
+      <c r="V65" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>409</v>
+        <v>115</v>
       </c>
       <c r="B66" t="s">
-        <v>410</v>
+        <v>159</v>
       </c>
       <c r="C66" t="s">
-        <v>435</v>
+        <v>160</v>
       </c>
       <c r="D66" t="s">
-        <v>436</v>
+        <v>135</v>
       </c>
       <c r="E66" t="s">
-        <v>437</v>
+        <v>161</v>
+      </c>
+      <c r="G66" t="s">
+        <v>579</v>
       </c>
       <c r="I66" t="s">
-        <v>438</v>
+        <v>580</v>
       </c>
       <c r="J66" t="s">
-        <v>439</v>
+        <v>581</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>440</v>
+        <v>162</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>582</v>
       </c>
       <c r="R66" t="s">
         <v>36</v>
       </c>
       <c r="S66" t="s">
-        <v>441</v>
-      </c>
-      <c r="V66" s="3">
-        <v>2</v>
+        <v>583</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>409</v>
+        <v>115</v>
       </c>
       <c r="B67" t="s">
-        <v>410</v>
+        <v>159</v>
       </c>
       <c r="C67" t="s">
-        <v>383</v>
+        <v>584</v>
       </c>
       <c r="D67" t="s">
-        <v>442</v>
+        <v>585</v>
       </c>
       <c r="E67" t="s">
-        <v>443</v>
+        <v>586</v>
+      </c>
+      <c r="G67" t="s">
+        <v>587</v>
       </c>
       <c r="I67" t="s">
-        <v>444</v>
+        <v>588</v>
       </c>
       <c r="J67" t="s">
-        <v>445</v>
+        <v>589</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>446</v>
+        <v>590</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>591</v>
       </c>
       <c r="R67" t="s">
-        <v>447</v>
+        <v>36</v>
       </c>
       <c r="S67" t="s">
-        <v>448</v>
-      </c>
-      <c r="V67" s="3">
-        <v>2</v>
+        <v>592</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="B68" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C68" t="s">
-        <v>180</v>
+        <v>593</v>
       </c>
       <c r="D68" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="E68" t="s">
-        <v>181</v>
+        <v>119</v>
+      </c>
+      <c r="G68" t="s">
+        <v>594</v>
       </c>
       <c r="I68" t="s">
-        <v>182</v>
+        <v>595</v>
+      </c>
+      <c r="J68" t="s">
+        <v>596</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>183</v>
+        <v>597</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>582</v>
       </c>
       <c r="R68" t="s">
         <v>36</v>
       </c>
-      <c r="V68" s="3">
-        <v>3</v>
+      <c r="S68" t="s">
+        <v>598</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
       <c r="C69" t="s">
-        <v>185</v>
+        <v>599</v>
       </c>
       <c r="D69" t="s">
-        <v>46</v>
+        <v>600</v>
       </c>
       <c r="E69" t="s">
-        <v>53</v>
+        <v>601</v>
+      </c>
+      <c r="G69" t="s">
+        <v>602</v>
       </c>
       <c r="I69" t="s">
-        <v>186</v>
+        <v>603</v>
+      </c>
+      <c r="J69" t="s">
+        <v>604</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>187</v>
+        <v>605</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>582</v>
       </c>
       <c r="R69" t="s">
-        <v>36</v>
-      </c>
-      <c r="V69" s="3">
-        <v>3</v>
+        <v>606</v>
+      </c>
+      <c r="S69" t="s">
+        <v>607</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>188</v>
+        <v>163</v>
       </c>
       <c r="B70" t="s">
-        <v>189</v>
+        <v>164</v>
       </c>
       <c r="C70" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="D70" t="s">
-        <v>191</v>
+        <v>24</v>
       </c>
       <c r="E70" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="I70" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="R70" t="s">
-        <v>195</v>
-      </c>
-      <c r="V70" s="3">
-        <v>2</v>
+        <v>36</v>
+      </c>
+      <c r="V70" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C71" t="s">
-        <v>383</v>
+        <v>171</v>
       </c>
       <c r="D71" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="E71" t="s">
-        <v>384</v>
+        <v>173</v>
       </c>
       <c r="I71" t="s">
-        <v>385</v>
+        <v>608</v>
       </c>
       <c r="J71" t="s">
-        <v>386</v>
+        <v>609</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>387</v>
+        <v>174</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>610</v>
       </c>
       <c r="R71" t="s">
-        <v>388</v>
-      </c>
-      <c r="V71" s="3">
-        <v>2</v>
+        <v>84</v>
+      </c>
+      <c r="V71" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B72" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C72" t="s">
-        <v>389</v>
+        <v>611</v>
       </c>
       <c r="D72" t="s">
-        <v>191</v>
+        <v>612</v>
       </c>
       <c r="E72" t="s">
-        <v>390</v>
+        <v>613</v>
       </c>
       <c r="I72" t="s">
-        <v>391</v>
+        <v>614</v>
       </c>
       <c r="J72" t="s">
-        <v>392</v>
+        <v>609</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>393</v>
+        <v>615</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>610</v>
       </c>
       <c r="R72" t="s">
-        <v>28</v>
-      </c>
-      <c r="V72" s="3">
-        <v>2</v>
+        <v>84</v>
+      </c>
+      <c r="V72" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B73" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C73" t="s">
-        <v>394</v>
+        <v>616</v>
       </c>
       <c r="D73" t="s">
-        <v>191</v>
+        <v>172</v>
       </c>
       <c r="E73" t="s">
-        <v>192</v>
+        <v>617</v>
+      </c>
+      <c r="G73" t="s">
+        <v>618</v>
       </c>
       <c r="I73" t="s">
-        <v>395</v>
+        <v>619</v>
       </c>
       <c r="J73" t="s">
-        <v>396</v>
+        <v>620</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="L73" s="1" t="s">
-        <v>398</v>
+        <v>621</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>610</v>
       </c>
       <c r="R73" t="s">
-        <v>399</v>
-      </c>
-      <c r="V73" s="3">
-        <v>2</v>
+        <v>84</v>
+      </c>
+      <c r="V73" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="B74" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="C74" t="s">
-        <v>400</v>
+        <v>622</v>
       </c>
       <c r="D74" t="s">
-        <v>156</v>
+        <v>585</v>
       </c>
       <c r="E74" t="s">
-        <v>401</v>
+        <v>623</v>
+      </c>
+      <c r="G74" t="s">
+        <v>624</v>
       </c>
       <c r="I74" t="s">
-        <v>402</v>
+        <v>614</v>
       </c>
       <c r="J74" t="s">
-        <v>403</v>
+        <v>609</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>404</v>
+        <v>625</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>610</v>
       </c>
       <c r="R74" t="s">
-        <v>405</v>
-      </c>
-      <c r="V74" s="3">
-        <v>2</v>
+        <v>84</v>
+      </c>
+      <c r="V74" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>404</v>
+      </c>
+      <c r="B75" t="s">
+        <v>405</v>
+      </c>
+      <c r="C75" t="s">
+        <v>406</v>
+      </c>
+      <c r="D75" t="s">
+        <v>407</v>
+      </c>
+      <c r="E75" t="s">
+        <v>408</v>
+      </c>
+      <c r="I75" t="s">
+        <v>409</v>
+      </c>
+      <c r="J75" t="s">
+        <v>410</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="R75" t="s">
+        <v>413</v>
+      </c>
+      <c r="S75" t="s">
+        <v>414</v>
+      </c>
+      <c r="V75" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>404</v>
+      </c>
+      <c r="B76" t="s">
+        <v>405</v>
+      </c>
+      <c r="C76" t="s">
+        <v>415</v>
+      </c>
+      <c r="D76" t="s">
+        <v>416</v>
+      </c>
+      <c r="E76" t="s">
+        <v>417</v>
+      </c>
+      <c r="I76" t="s">
+        <v>418</v>
+      </c>
+      <c r="J76" t="s">
+        <v>419</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="R76" t="s">
+        <v>400</v>
+      </c>
+      <c r="S76" t="s">
+        <v>421</v>
+      </c>
+      <c r="V76" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>404</v>
+      </c>
+      <c r="B77" t="s">
+        <v>405</v>
+      </c>
+      <c r="C77" t="s">
+        <v>422</v>
+      </c>
+      <c r="D77" t="s">
+        <v>423</v>
+      </c>
+      <c r="E77" t="s">
+        <v>424</v>
+      </c>
+      <c r="I77" t="s">
+        <v>425</v>
+      </c>
+      <c r="J77" t="s">
+        <v>426</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="R77" t="s">
+        <v>428</v>
+      </c>
+      <c r="S77" t="s">
+        <v>429</v>
+      </c>
+      <c r="V77" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>404</v>
+      </c>
+      <c r="B78" t="s">
+        <v>405</v>
+      </c>
+      <c r="C78" t="s">
+        <v>430</v>
+      </c>
+      <c r="D78" t="s">
+        <v>431</v>
+      </c>
+      <c r="E78" t="s">
+        <v>432</v>
+      </c>
+      <c r="I78" t="s">
+        <v>433</v>
+      </c>
+      <c r="J78" t="s">
+        <v>434</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="R78" t="s">
+        <v>36</v>
+      </c>
+      <c r="S78" t="s">
+        <v>436</v>
+      </c>
+      <c r="V78" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>404</v>
+      </c>
+      <c r="B79" t="s">
+        <v>405</v>
+      </c>
+      <c r="C79" t="s">
+        <v>378</v>
+      </c>
+      <c r="D79" t="s">
+        <v>437</v>
+      </c>
+      <c r="E79" t="s">
+        <v>438</v>
+      </c>
+      <c r="I79" t="s">
+        <v>439</v>
+      </c>
+      <c r="J79" t="s">
+        <v>440</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="R79" t="s">
+        <v>442</v>
+      </c>
+      <c r="S79" t="s">
+        <v>443</v>
+      </c>
+      <c r="V79" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>68</v>
+      </c>
+      <c r="B80" t="s">
+        <v>175</v>
+      </c>
+      <c r="C80" t="s">
+        <v>176</v>
+      </c>
+      <c r="D80" t="s">
+        <v>46</v>
+      </c>
+      <c r="E80" t="s">
+        <v>177</v>
+      </c>
+      <c r="I80" t="s">
+        <v>528</v>
+      </c>
+      <c r="J80" t="s">
+        <v>529</v>
+      </c>
+      <c r="K80" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>324</v>
+      </c>
+      <c r="R80" t="s">
+        <v>36</v>
+      </c>
+      <c r="V80" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>68</v>
+      </c>
+      <c r="B81" t="s">
+        <v>175</v>
+      </c>
+      <c r="C81">
+        <v>1456</v>
+      </c>
+      <c r="D81" t="s">
+        <v>530</v>
+      </c>
+      <c r="E81" t="s">
+        <v>531</v>
+      </c>
+      <c r="I81" t="s">
+        <v>532</v>
+      </c>
+      <c r="J81" t="s">
+        <v>533</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>317</v>
+      </c>
+      <c r="R81" t="s">
+        <v>36</v>
+      </c>
+      <c r="S81">
+        <v>58</v>
+      </c>
+      <c r="T81">
+        <v>51</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>68</v>
+      </c>
+      <c r="B82" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" t="s">
+        <v>160</v>
+      </c>
+      <c r="D82" t="s">
+        <v>46</v>
+      </c>
+      <c r="E82" t="s">
+        <v>47</v>
+      </c>
+      <c r="I82" t="s">
+        <v>535</v>
+      </c>
+      <c r="J82" t="s">
+        <v>536</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>317</v>
+      </c>
+      <c r="R82" t="s">
+        <v>36</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>68</v>
+      </c>
+      <c r="B83" t="s">
+        <v>175</v>
+      </c>
+      <c r="C83" t="s">
+        <v>538</v>
+      </c>
+      <c r="D83" t="s">
+        <v>539</v>
+      </c>
+      <c r="E83" t="s">
+        <v>540</v>
+      </c>
+      <c r="I83" t="s">
+        <v>541</v>
+      </c>
+      <c r="J83" t="s">
+        <v>542</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>544</v>
+      </c>
+      <c r="R83" t="s">
+        <v>84</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>68</v>
+      </c>
+      <c r="B84" t="s">
+        <v>175</v>
+      </c>
+      <c r="C84" t="s">
+        <v>176</v>
+      </c>
+      <c r="D84" t="s">
+        <v>46</v>
+      </c>
+      <c r="E84" t="s">
+        <v>177</v>
+      </c>
+      <c r="I84" t="s">
+        <v>178</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="R84" t="s">
+        <v>36</v>
+      </c>
+      <c r="V84" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>180</v>
+      </c>
+      <c r="B85" t="s">
+        <v>175</v>
+      </c>
+      <c r="C85" t="s">
+        <v>181</v>
+      </c>
+      <c r="D85" t="s">
+        <v>46</v>
+      </c>
+      <c r="E85" t="s">
+        <v>52</v>
+      </c>
+      <c r="G85" t="s">
+        <v>497</v>
+      </c>
+      <c r="I85" t="s">
+        <v>498</v>
+      </c>
+      <c r="J85" t="s">
+        <v>499</v>
+      </c>
+      <c r="K85" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>324</v>
+      </c>
+      <c r="R85" t="s">
+        <v>500</v>
+      </c>
+      <c r="S85" t="s">
+        <v>501</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>180</v>
+      </c>
+      <c r="B86" t="s">
+        <v>175</v>
+      </c>
+      <c r="C86" t="s">
+        <v>503</v>
+      </c>
+      <c r="D86" t="s">
+        <v>504</v>
+      </c>
+      <c r="E86" t="s">
+        <v>505</v>
+      </c>
+      <c r="G86" t="s">
+        <v>506</v>
+      </c>
+      <c r="I86" t="s">
+        <v>507</v>
+      </c>
+      <c r="J86" t="s">
+        <v>508</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>510</v>
+      </c>
+      <c r="R86" t="s">
+        <v>511</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>180</v>
+      </c>
+      <c r="B87" t="s">
+        <v>175</v>
+      </c>
+      <c r="C87" t="s">
+        <v>512</v>
+      </c>
+      <c r="D87" t="s">
+        <v>46</v>
+      </c>
+      <c r="E87" t="s">
+        <v>513</v>
+      </c>
+      <c r="G87" t="s">
+        <v>514</v>
+      </c>
+      <c r="I87" t="s">
+        <v>515</v>
+      </c>
+      <c r="J87" t="s">
+        <v>516</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>518</v>
+      </c>
+      <c r="R87" t="s">
+        <v>519</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>180</v>
+      </c>
+      <c r="B88" t="s">
+        <v>175</v>
+      </c>
+      <c r="C88" t="s">
+        <v>520</v>
+      </c>
+      <c r="D88" t="s">
+        <v>521</v>
+      </c>
+      <c r="E88" t="s">
+        <v>522</v>
+      </c>
+      <c r="G88" t="s">
+        <v>523</v>
+      </c>
+      <c r="I88" t="s">
+        <v>524</v>
+      </c>
+      <c r="J88" t="s">
+        <v>525</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>324</v>
+      </c>
+      <c r="R88" t="s">
+        <v>36</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>183</v>
+      </c>
+      <c r="B89" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89" t="s">
+        <v>185</v>
+      </c>
+      <c r="D89" t="s">
+        <v>186</v>
+      </c>
+      <c r="E89" t="s">
+        <v>187</v>
+      </c>
+      <c r="I89" t="s">
         <v>188</v>
       </c>
-      <c r="B75" t="s">
+      <c r="K89" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="C75" t="s">
+      <c r="R89" t="s">
+        <v>190</v>
+      </c>
+      <c r="V89" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>183</v>
+      </c>
+      <c r="B90" t="s">
+        <v>184</v>
+      </c>
+      <c r="C90" t="s">
+        <v>378</v>
+      </c>
+      <c r="D90" t="s">
+        <v>186</v>
+      </c>
+      <c r="E90" t="s">
+        <v>379</v>
+      </c>
+      <c r="I90" t="s">
+        <v>380</v>
+      </c>
+      <c r="J90" t="s">
+        <v>381</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="R90" t="s">
         <v>383</v>
       </c>
-      <c r="D75" t="s">
-        <v>191</v>
-      </c>
-      <c r="E75" t="s">
+      <c r="V90" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>183</v>
+      </c>
+      <c r="B91" t="s">
+        <v>184</v>
+      </c>
+      <c r="C91" t="s">
         <v>384</v>
       </c>
-      <c r="I75" t="s">
-        <v>406</v>
-      </c>
-      <c r="J75" t="s">
-        <v>407</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="R75" t="s">
+      <c r="D91" t="s">
+        <v>186</v>
+      </c>
+      <c r="E91" t="s">
+        <v>385</v>
+      </c>
+      <c r="I91" t="s">
+        <v>386</v>
+      </c>
+      <c r="J91" t="s">
+        <v>387</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="R91" t="s">
+        <v>28</v>
+      </c>
+      <c r="V91" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>183</v>
+      </c>
+      <c r="B92" t="s">
+        <v>184</v>
+      </c>
+      <c r="C92" t="s">
+        <v>389</v>
+      </c>
+      <c r="D92" t="s">
+        <v>186</v>
+      </c>
+      <c r="E92" t="s">
+        <v>187</v>
+      </c>
+      <c r="I92" t="s">
+        <v>390</v>
+      </c>
+      <c r="J92" t="s">
+        <v>391</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="L92" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="R92" t="s">
+        <v>394</v>
+      </c>
+      <c r="V92" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>183</v>
+      </c>
+      <c r="B93" t="s">
+        <v>184</v>
+      </c>
+      <c r="C93" t="s">
+        <v>395</v>
+      </c>
+      <c r="D93" t="s">
+        <v>154</v>
+      </c>
+      <c r="E93" t="s">
+        <v>396</v>
+      </c>
+      <c r="I93" t="s">
+        <v>397</v>
+      </c>
+      <c r="J93" t="s">
+        <v>398</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="R93" t="s">
+        <v>400</v>
+      </c>
+      <c r="V93" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>183</v>
+      </c>
+      <c r="B94" t="s">
+        <v>184</v>
+      </c>
+      <c r="C94" t="s">
+        <v>378</v>
+      </c>
+      <c r="D94" t="s">
+        <v>186</v>
+      </c>
+      <c r="E94" t="s">
+        <v>379</v>
+      </c>
+      <c r="I94" t="s">
+        <v>401</v>
+      </c>
+      <c r="J94" t="s">
+        <v>402</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="R94" t="s">
         <v>36</v>
       </c>
-      <c r="V75" s="3">
+      <c r="V94" s="2">
         <v>2</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="K5" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="K6" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="K11" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="K12" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="K21" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K28" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="K37" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K38" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="K39" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K40" r:id="rId13" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K68" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K69" r:id="rId15" xr:uid="{00000000-0004-0000-0000-00001A000000}"/>
-    <hyperlink ref="K70" r:id="rId16" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K62" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000018000000}"/>
-    <hyperlink ref="K61" r:id="rId18" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K60" r:id="rId19" xr:uid="{00000000-0004-0000-0000-000016000000}"/>
-    <hyperlink ref="K59" r:id="rId20" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K50" r:id="rId21" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K49" r:id="rId22" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K41" r:id="rId23" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
-    <hyperlink ref="K42" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
-    <hyperlink ref="K43" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
-    <hyperlink ref="K44" r:id="rId26" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
-    <hyperlink ref="K45" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
-    <hyperlink ref="M45" r:id="rId28" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
-    <hyperlink ref="K46" r:id="rId29" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
-    <hyperlink ref="K47" r:id="rId30" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
-    <hyperlink ref="K48" r:id="rId31" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
-    <hyperlink ref="K51" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
-    <hyperlink ref="M51" r:id="rId33" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
-    <hyperlink ref="O51" r:id="rId34" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
-    <hyperlink ref="K52" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
-    <hyperlink ref="M52" r:id="rId36" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
-    <hyperlink ref="K53" r:id="rId37" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
-    <hyperlink ref="M53" r:id="rId38" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
-    <hyperlink ref="K54" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
-    <hyperlink ref="F53" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
-    <hyperlink ref="F54:F55" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
-    <hyperlink ref="M54" r:id="rId42" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
-    <hyperlink ref="M55" r:id="rId43" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
-    <hyperlink ref="K55" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
-    <hyperlink ref="K56" r:id="rId45" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
-    <hyperlink ref="F56" r:id="rId46" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
-    <hyperlink ref="F57" r:id="rId47" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
-    <hyperlink ref="K57" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
-    <hyperlink ref="K58" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
-    <hyperlink ref="H58" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
-    <hyperlink ref="K13" r:id="rId51" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
-    <hyperlink ref="K14" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
-    <hyperlink ref="M14" r:id="rId53" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
-    <hyperlink ref="F14" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
-    <hyperlink ref="K15" r:id="rId55" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
-    <hyperlink ref="K16" r:id="rId56" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
-    <hyperlink ref="K17" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
-    <hyperlink ref="K18" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
-    <hyperlink ref="K19" r:id="rId59" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
-    <hyperlink ref="K20" r:id="rId60" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
-    <hyperlink ref="K30" r:id="rId61" xr:uid="{C61A9D98-CECD-4B5E-B96E-4289BBC0D262}"/>
-    <hyperlink ref="K31" r:id="rId62" xr:uid="{EB7CB685-E0C1-4945-9E14-9CA8A1A342EC}"/>
-    <hyperlink ref="K32" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F065AADE-42A0-4C3C-B801-4BE9B5FA9BEB}"/>
-    <hyperlink ref="K33" r:id="rId64" xr:uid="{819ABFBD-4499-4FE6-9CDB-0A9FE7A07280}"/>
-    <hyperlink ref="K34" r:id="rId65" xr:uid="{48E832D6-CC6D-436E-BC8A-74B5489EE9B1}"/>
-    <hyperlink ref="K35" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8CE24E7-04FD-4348-88B3-8498A10C097C}"/>
-    <hyperlink ref="K36" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5381B954-6617-4930-A5BC-415052E36793}"/>
-    <hyperlink ref="L35" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCF513E3-779E-478B-83FF-5E58604AFA16}"/>
-    <hyperlink ref="H36" r:id="rId69" xr:uid="{B822FBF8-7DC0-48FD-BCB2-A7B3FC9F1F52}"/>
-    <hyperlink ref="F36" r:id="rId70" xr:uid="{3D8C3557-F6D2-4A3A-BE13-D18D5DD3FB6A}"/>
-    <hyperlink ref="K29" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
-    <hyperlink ref="K71" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
-    <hyperlink ref="L73" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
-    <hyperlink ref="K73" r:id="rId74" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
-    <hyperlink ref="K72" r:id="rId75" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
-    <hyperlink ref="K75" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
-    <hyperlink ref="K74" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
-    <hyperlink ref="M63" r:id="rId78" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
-    <hyperlink ref="K63" r:id="rId79" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
-    <hyperlink ref="K64" r:id="rId80" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
-    <hyperlink ref="K67" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
-    <hyperlink ref="K66" r:id="rId82" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
-    <hyperlink ref="K65" r:id="rId83" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
-    <hyperlink ref="K22" r:id="rId84" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
-    <hyperlink ref="K23" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
-    <hyperlink ref="K24" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
-    <hyperlink ref="K25" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
-    <hyperlink ref="K26" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
-    <hyperlink ref="K27" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
-    <hyperlink ref="K7" r:id="rId90" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
-    <hyperlink ref="K8" r:id="rId91" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
-    <hyperlink ref="K9" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
-    <hyperlink ref="K10" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
+    <hyperlink ref="K17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="K18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K27" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="K34" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="K43" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K44" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K45" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K46" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K84" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K89" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K70" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K65" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
+    <hyperlink ref="K56" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
+    <hyperlink ref="K55" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
+    <hyperlink ref="K47" r:id="rId18" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
+    <hyperlink ref="K48" r:id="rId19" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
+    <hyperlink ref="K49" r:id="rId20" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
+    <hyperlink ref="K50" r:id="rId21" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
+    <hyperlink ref="K51" r:id="rId22" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
+    <hyperlink ref="M51" r:id="rId23" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
+    <hyperlink ref="K52" r:id="rId24" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
+    <hyperlink ref="K53" r:id="rId25" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
+    <hyperlink ref="K54" r:id="rId26" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
+    <hyperlink ref="K57" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
+    <hyperlink ref="M57" r:id="rId28" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
+    <hyperlink ref="O57" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
+    <hyperlink ref="K58" r:id="rId30" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
+    <hyperlink ref="M58" r:id="rId31" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
+    <hyperlink ref="K59" r:id="rId32" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
+    <hyperlink ref="M59" r:id="rId33" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
+    <hyperlink ref="K60" r:id="rId34" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
+    <hyperlink ref="F59" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
+    <hyperlink ref="F60:F61" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
+    <hyperlink ref="M60" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
+    <hyperlink ref="M61" r:id="rId38" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
+    <hyperlink ref="K61" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
+    <hyperlink ref="K62" r:id="rId40" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
+    <hyperlink ref="F62" r:id="rId41" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
+    <hyperlink ref="F63" r:id="rId42" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
+    <hyperlink ref="K63" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
+    <hyperlink ref="K64" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
+    <hyperlink ref="H64" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
+    <hyperlink ref="K19" r:id="rId46" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
+    <hyperlink ref="K20" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
+    <hyperlink ref="M20" r:id="rId48" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
+    <hyperlink ref="F20" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
+    <hyperlink ref="K21" r:id="rId50" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
+    <hyperlink ref="K22" r:id="rId51" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
+    <hyperlink ref="K23" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
+    <hyperlink ref="K24" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
+    <hyperlink ref="K25" r:id="rId54" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
+    <hyperlink ref="K26" r:id="rId55" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
+    <hyperlink ref="K36" r:id="rId56" xr:uid="{C61A9D98-CECD-4B5E-B96E-4289BBC0D262}"/>
+    <hyperlink ref="K37" r:id="rId57" xr:uid="{EB7CB685-E0C1-4945-9E14-9CA8A1A342EC}"/>
+    <hyperlink ref="K38" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F065AADE-42A0-4C3C-B801-4BE9B5FA9BEB}"/>
+    <hyperlink ref="K39" r:id="rId59" xr:uid="{819ABFBD-4499-4FE6-9CDB-0A9FE7A07280}"/>
+    <hyperlink ref="K40" r:id="rId60" xr:uid="{48E832D6-CC6D-436E-BC8A-74B5489EE9B1}"/>
+    <hyperlink ref="K41" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8CE24E7-04FD-4348-88B3-8498A10C097C}"/>
+    <hyperlink ref="K42" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5381B954-6617-4930-A5BC-415052E36793}"/>
+    <hyperlink ref="L41" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCF513E3-779E-478B-83FF-5E58604AFA16}"/>
+    <hyperlink ref="H42" r:id="rId64" xr:uid="{B822FBF8-7DC0-48FD-BCB2-A7B3FC9F1F52}"/>
+    <hyperlink ref="F42" r:id="rId65" xr:uid="{3D8C3557-F6D2-4A3A-BE13-D18D5DD3FB6A}"/>
+    <hyperlink ref="K35" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
+    <hyperlink ref="K90" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
+    <hyperlink ref="L92" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
+    <hyperlink ref="K92" r:id="rId69" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
+    <hyperlink ref="K91" r:id="rId70" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
+    <hyperlink ref="K94" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
+    <hyperlink ref="K93" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
+    <hyperlink ref="M75" r:id="rId73" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
+    <hyperlink ref="K75" r:id="rId74" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
+    <hyperlink ref="K76" r:id="rId75" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
+    <hyperlink ref="K79" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
+    <hyperlink ref="K78" r:id="rId77" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
+    <hyperlink ref="K77" r:id="rId78" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
+    <hyperlink ref="K28" r:id="rId79" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
+    <hyperlink ref="K29" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
+    <hyperlink ref="K30" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
+    <hyperlink ref="K31" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
+    <hyperlink ref="K32" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
+    <hyperlink ref="K33" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
+    <hyperlink ref="K15" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
+    <hyperlink ref="K16" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
+    <hyperlink ref="K85" r:id="rId87" xr:uid="{27E4829F-4D6C-4205-815B-E30709FE0551}"/>
+    <hyperlink ref="K86" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0C3D8311-8886-4EE9-8346-59E9A2212818}"/>
+    <hyperlink ref="K87" r:id="rId89" xr:uid="{6CB3210A-C53D-42FD-ADF5-DB6CD788DE2A}"/>
+    <hyperlink ref="K88" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B28112-49B9-4A12-A9FC-6929194008BD}"/>
+    <hyperlink ref="M88" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B81923-B3F5-4D27-8C90-D607D23DCA1E}"/>
+    <hyperlink ref="K80" r:id="rId92" xr:uid="{48F768EA-5F6B-4721-BE10-3381CFFF7617}"/>
+    <hyperlink ref="K81" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB3AA346-9023-4C65-A326-45854C985AC3}"/>
+    <hyperlink ref="K82" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3E9D42C5-EF64-4F37-BDFD-EF645728FB63}"/>
+    <hyperlink ref="K83" r:id="rId95" xr:uid="{D140917F-D470-4295-AC16-135E62B59912}"/>
+    <hyperlink ref="K14" r:id="rId96" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
+    <hyperlink ref="K13" r:id="rId97" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
+    <hyperlink ref="K5" r:id="rId98" xr:uid="{09752CE0-E1D3-4BF8-9D97-A49E8D002FC7}"/>
+    <hyperlink ref="K6" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{63C98BDE-FB8F-4FF9-A55C-03BAC1A02C63}"/>
+    <hyperlink ref="K7" r:id="rId100" xr:uid="{2380B890-0042-45CC-BEA4-783EA390EBF7}"/>
+    <hyperlink ref="K8" r:id="rId101" xr:uid="{AD077303-0EE9-4440-AAE6-BB84613C92BA}"/>
+    <hyperlink ref="K9" r:id="rId102" xr:uid="{8F9EE820-D8AA-4884-BB24-82C0C5D3CE2E}"/>
+    <hyperlink ref="K10" r:id="rId103" xr:uid="{22252FF4-27CC-40A3-8165-FA7B5CD19CDC}"/>
+    <hyperlink ref="K11" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96212E21-386F-4FCF-9A25-36D60D8078DF}"/>
+    <hyperlink ref="K12" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D9725C5-E9A1-4F23-B790-C7DC385208E5}"/>
+    <hyperlink ref="K66" r:id="rId106" xr:uid="{11A9B442-D6DF-429E-912B-50308BFE8E3D}"/>
+    <hyperlink ref="K67" r:id="rId107" xr:uid="{9A607AD9-733B-410B-B2B3-EFB415EA956D}"/>
+    <hyperlink ref="K68" r:id="rId108" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB732E30-93A4-4501-9799-59B7A6245041}"/>
+    <hyperlink ref="K69" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27EBDD53-9DEC-466F-B000-1FDCDA134FDC}"/>
+    <hyperlink ref="K71" r:id="rId110" xr:uid="{AA5F7287-2A04-4E9B-90FB-8E7A60BA0E9F}"/>
+    <hyperlink ref="K72" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4EF3173-817E-4A91-848F-7D2C11831473}"/>
+    <hyperlink ref="K73" r:id="rId112" xr:uid="{6284D82A-10EF-49D7-940E-00897AA75BB5}"/>
+    <hyperlink ref="K74" r:id="rId113" xr:uid="{DBEE44C4-CCCA-45E8-A66C-BF94EC30E034}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21BB33D7-557D-41A8-83A7-EC4F0C087499}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B9584-512E-4C34-8A73-A9EACF7C6F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="658">
   <si>
     <t>Patronyme artiste</t>
   </si>
@@ -113,9 +113,6 @@
     <t>Museo Correr</t>
   </si>
   <si>
-    <t>"David avec la tête de Goliath (bronze)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/d9/%28Venice%29_Davide_con_la_testa_di_Golia%2C_fine_secolo_XV_-_Museo_Correr.jpg/1280px-%28Venice%29_Davide_con_la_testa_di_Golia%2C_fine_secolo_XV_-_Museo_Correr.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -125,24 +122,9 @@
     <t>Andrea</t>
   </si>
   <si>
-    <t>BREGNO</t>
-  </si>
-  <si>
-    <t>1474-1477 environ</t>
-  </si>
-  <si>
     <t>Rome</t>
   </si>
   <si>
-    <t>Basilique Santi Apostoli</t>
-  </si>
-  <si>
-    <t>"Tombeau du cardinal Pietro Riario"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Dodici_Apostoli_Pietro_Riario_1.jpg/1280px-Dodici_Apostoli_Pietro_Riario_1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Marbre</t>
   </si>
   <si>
@@ -155,12 +137,6 @@
     <t>1472</t>
   </si>
   <si>
-    <t>Cathédrale de Lucques</t>
-  </si>
-  <si>
-    <t>"Tombeau de Pietro da Noceto"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fc/Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG/1280px-Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -215,36 +191,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG/1280px-Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Gil</t>
-  </si>
-  <si>
-    <t>de SILOÉ</t>
-  </si>
-  <si>
-    <t>1489-1493</t>
-  </si>
-  <si>
-    <t>Burgos</t>
-  </si>
-  <si>
-    <t>Chartreuse de Miraflores</t>
-  </si>
-  <si>
-    <t>"Tombeau de Jean II de Castille et Isabelle de Portugal"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/8/8a/Cartuja_de_Miraflores_%28Burgos%29_-_Tumba_de_Juan_II.jpg/1280px-Cartuja_de_Miraflores_%28Burgos%29_-_Tumba_de_Juan_II.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Albâtre</t>
-  </si>
-  <si>
     <t>Antonio</t>
   </si>
   <si>
-    <t>del POLLAIOLO</t>
-  </si>
-  <si>
     <t>1484-1493</t>
   </si>
   <si>
@@ -281,9 +230,6 @@
     <t>Chiesa di Santa Maria della Vita</t>
   </si>
   <si>
-    <t>"Compianto sul Cristo morto"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -431,51 +377,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Domenico</t>
-  </si>
-  <si>
-    <t>GAGINI</t>
-  </si>
-  <si>
-    <t>1470 environ</t>
-  </si>
-  <si>
     <t>Palerme</t>
   </si>
   <si>
-    <t>Chiesa San Domenico</t>
-  </si>
-  <si>
-    <t>"Pietà"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/23/Chiesa_San_Domenico_%28Palermo%29_Pieta_von_Domenico_Gagini.jpg/1280px-Chiesa_San_Domenico_%28Palermo%29_Pieta_von_Domenico_Gagini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Nicolas</t>
-  </si>
-  <si>
-    <t>GERHAERT van LEYDEN</t>
-  </si>
-  <si>
-    <t>1463 environ</t>
-  </si>
-  <si>
-    <t>Strasbourg</t>
-  </si>
-  <si>
-    <t>Musée de l'Œuvre Notre-Dame</t>
-  </si>
-  <si>
-    <t>"Buste d'homme accoudé (autoportrait présumé)"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/13/Nicolaus_von_Leyden%2C_Self-portrait.JPG/1280px-Nicolaus_von_Leyden%2C_Self-portrait.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Grès polychrome</t>
-  </si>
-  <si>
     <t>Lorenzo</t>
   </si>
   <si>
@@ -488,30 +392,9 @@
     <t>Bronze doré</t>
   </si>
   <si>
-    <t>Adam</t>
-  </si>
-  <si>
-    <t>KRAFT</t>
-  </si>
-  <si>
-    <t>1493-1496</t>
-  </si>
-  <si>
     <t>Nuremberg</t>
   </si>
   <si>
-    <t>Église Saint-Laurent</t>
-  </si>
-  <si>
-    <t>"Le Ciboire (Sakramentshaus)"</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/30/N%C3%BCrnberg_St._Lorenz_Sakramentshaus_Adam_Kraft_01.jpg/1280px-N%C3%BCrnberg_St._Lorenz_Sakramentshaus_Adam_Kraft_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Pierre</t>
-  </si>
-  <si>
     <t>LAURANA</t>
   </si>
   <si>
@@ -1911,6 +1794,219 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg/1280px-GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>David avec la tête de Goliath (bronze)</t>
+  </si>
+  <si>
+    <t>David con la testa di Golia</t>
+  </si>
+  <si>
+    <t>Basilique de San Zanipolo</t>
+  </si>
+  <si>
+    <t>Retable de la chapelle de Marie Madeleine</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg/960px-Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Retable</t>
+  </si>
+  <si>
+    <t>Marbre et stuc</t>
+  </si>
+  <si>
+    <t>v. 1490</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>National Gallery of Art</t>
+  </si>
+  <si>
+    <t>Le Christ en piété soutenu par deux anges</t>
+  </si>
+  <si>
+    <t>Cristo in pietà sorretto da due angeli</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg/960px-Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Victoria and Albert Museum</t>
+  </si>
+  <si>
+    <t>Lamentation sur le Christ mort</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Victoria_and_Albert_Museum_DSCF6184_05.jpg/1280px-Victoria_and_Albert_Museum_DSCF6184_05.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Tombeau de Pietro da Noceto</t>
+  </si>
+  <si>
+    <t>Tomba di Pietro da Noceto</t>
+  </si>
+  <si>
+    <t>1479</t>
+  </si>
+  <si>
+    <t>Tombeau de Domenico Bertini</t>
+  </si>
+  <si>
+    <t>Tomba di Domenico Bertini</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1484</t>
+  </si>
+  <si>
+    <t>Tempietto du Volto Santo</t>
+  </si>
+  <si>
+    <t>Tempietto del Volto Santo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Marbre de Carrare</t>
+  </si>
+  <si>
+    <t>Autel de Saint Régule</t>
+  </si>
+  <si>
+    <t>Altare di San Regolo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1492-1498</t>
+  </si>
+  <si>
+    <t>Basilique Saint-Pierre</t>
+  </si>
+  <si>
+    <t>Tombeau du pape Innocent VIII</t>
+  </si>
+  <si>
+    <t>Sepolcro di Innocenzo VIII</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>549</t>
+  </si>
+  <si>
+    <t>Musée national du Bargello</t>
+  </si>
+  <si>
+    <t>Hercule et Antée</t>
+  </si>
+  <si>
+    <t>Ercole e Anteo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b9/Antonio_del_pollaiolo%2C_ercole_e_anteo%2C_01.JPG/960px-Antonio_del_pollaiolo%2C_ercole_e_anteo%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>1470</t>
+  </si>
+  <si>
+    <t>Buste de jeune homme en armure</t>
+  </si>
+  <si>
+    <t>Busto de jeune homme en armure</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg/960px-Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Terre cuite</t>
+  </si>
+  <si>
+    <t>51</t>
+  </si>
+  <si>
+    <t>1457-1459</t>
+  </si>
+  <si>
+    <t>Musée de l'Œuvre du Duomo</t>
+  </si>
+  <si>
+    <t>Croix de Saint Jean (Reliquaire en collaboration)</t>
+  </si>
+  <si>
+    <t>Croce del Tesoro di San Giovanni</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Betto_di_francesco_betti%2C_antonio_pollaiolo_e_domenico_dei%2C_croce_1457-59_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Argent, émaux et bois</t>
+  </si>
+  <si>
+    <t>c. 1480</t>
+  </si>
+  <si>
+    <t>Hercule au repos</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f6/Berlin_-_Gem%C3%A4ldegalerie_9414.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>del POLLAIUOLO</t>
+  </si>
+  <si>
+    <t>1469-1473</t>
+  </si>
+  <si>
+    <t>Basilique San Domenico</t>
+  </si>
+  <si>
+    <t>Arca di San Domenico (Cimaise)</t>
+  </si>
+  <si>
+    <t>Dieu le Père bénissant le monde</t>
+  </si>
+  <si>
+    <t>Dio Padre benedicente il mondo</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Musée de la Basilique San Domenico</t>
+  </si>
+  <si>
+    <t>Buste de saint Dominique</t>
+  </si>
+  <si>
+    <t>Busto di san Domenico</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Galleria Estense</t>
+  </si>
+  <si>
+    <t>Sainte Monique</t>
+  </si>
+  <si>
+    <t>Santa Monica</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -1963,12 +2059,13 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2274,7 +2371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V94"/>
+  <dimension ref="A1:V103"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
@@ -2283,6 +2380,7 @@
     <col min="9" max="9" width="36.28515625" customWidth="1"/>
     <col min="16" max="16" width="1" customWidth="1"/>
     <col min="17" max="17" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="19" max="21" width="9.140625" style="3"/>
     <col min="22" max="22" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -2338,13 +2436,13 @@
       <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" t="s">
+      <c r="S1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="T1" t="s">
+      <c r="T1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" s="3" t="s">
         <v>19</v>
       </c>
       <c r="V1" s="2" t="s">
@@ -2368,13 +2466,19 @@
         <v>25</v>
       </c>
       <c r="I2" t="s">
+        <v>587</v>
+      </c>
+      <c r="J2" t="s">
+        <v>588</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="Q2" t="s">
+        <v>532</v>
+      </c>
+      <c r="R2" t="s">
         <v>27</v>
-      </c>
-      <c r="R2" t="s">
-        <v>28</v>
       </c>
       <c r="V2" s="2">
         <v>3</v>
@@ -2382,28 +2486,31 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>589</v>
       </c>
       <c r="I3" t="s">
-        <v>34</v>
+        <v>590</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>35</v>
+        <v>591</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>592</v>
       </c>
       <c r="R3" t="s">
-        <v>36</v>
+        <v>593</v>
       </c>
       <c r="V3" s="2">
         <v>3</v>
@@ -2411,25 +2518,40 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>594</v>
+      </c>
+      <c r="D4" t="s">
+        <v>595</v>
       </c>
       <c r="E4" t="s">
-        <v>40</v>
+        <v>596</v>
       </c>
       <c r="I4" t="s">
-        <v>41</v>
+        <v>597</v>
+      </c>
+      <c r="J4" t="s">
+        <v>598</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>42</v>
+        <v>599</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>179</v>
       </c>
       <c r="R4" t="s">
-        <v>36</v>
+        <v>118</v>
+      </c>
+      <c r="S4" s="3">
+        <v>24</v>
+      </c>
+      <c r="T4" s="3">
+        <v>18</v>
       </c>
       <c r="V4" s="2">
         <v>3</v>
@@ -2437,364 +2559,346 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>45</v>
+        <v>534</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>491</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>600</v>
       </c>
       <c r="I5" t="s">
-        <v>545</v>
+        <v>601</v>
       </c>
       <c r="J5" t="s">
-        <v>546</v>
+        <v>570</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>48</v>
+        <v>602</v>
       </c>
       <c r="Q5" t="s">
-        <v>547</v>
+        <v>505</v>
       </c>
       <c r="R5" t="s">
-        <v>36</v>
-      </c>
-      <c r="S5" t="s">
-        <v>548</v>
+        <v>30</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>549</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>46</v>
+        <v>410</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>411</v>
       </c>
       <c r="I6" t="s">
-        <v>550</v>
+        <v>603</v>
       </c>
       <c r="J6" t="s">
-        <v>551</v>
+        <v>604</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>547</v>
+        <v>34</v>
       </c>
       <c r="R6" t="s">
-        <v>36</v>
-      </c>
-      <c r="S6" t="s">
-        <v>553</v>
+        <v>30</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B7" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>554</v>
+        <v>605</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>410</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>411</v>
       </c>
       <c r="I7" t="s">
-        <v>555</v>
+        <v>606</v>
       </c>
       <c r="J7" t="s">
-        <v>556</v>
+        <v>607</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>557</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>547</v>
+        <v>608</v>
       </c>
       <c r="R7" t="s">
-        <v>36</v>
-      </c>
-      <c r="S7" t="s">
-        <v>558</v>
+        <v>30</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C8" t="s">
-        <v>559</v>
+        <v>609</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>410</v>
       </c>
       <c r="E8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G8" t="s">
-        <v>560</v>
+        <v>411</v>
       </c>
       <c r="I8" t="s">
-        <v>561</v>
+        <v>610</v>
       </c>
       <c r="J8" t="s">
-        <v>562</v>
+        <v>611</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>324</v>
+        <v>612</v>
       </c>
       <c r="R8" t="s">
-        <v>36</v>
+        <v>613</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>609</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>410</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>411</v>
       </c>
       <c r="I9" t="s">
-        <v>564</v>
+        <v>614</v>
       </c>
       <c r="J9" t="s">
-        <v>565</v>
+        <v>615</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>53</v>
+        <v>616</v>
       </c>
       <c r="R9" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>566</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>567</v>
+        <v>506</v>
       </c>
       <c r="J10" t="s">
-        <v>568</v>
+        <v>507</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>569</v>
+        <v>40</v>
       </c>
       <c r="Q10" t="s">
-        <v>317</v>
+        <v>508</v>
       </c>
       <c r="R10" t="s">
-        <v>36</v>
-      </c>
-      <c r="S10" t="s">
-        <v>548</v>
+        <v>30</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>509</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>313</v>
+        <v>510</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>306</v>
+        <v>39</v>
       </c>
       <c r="I11" t="s">
-        <v>254</v>
+        <v>511</v>
       </c>
       <c r="J11" t="s">
-        <v>255</v>
+        <v>512</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>570</v>
+        <v>513</v>
       </c>
       <c r="Q11" t="s">
-        <v>571</v>
+        <v>508</v>
       </c>
       <c r="R11" t="s">
-        <v>36</v>
-      </c>
-      <c r="S11" t="s">
-        <v>572</v>
+        <v>30</v>
+      </c>
+      <c r="S11" s="3" t="s">
+        <v>514</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C12" t="s">
-        <v>573</v>
+        <v>515</v>
       </c>
       <c r="D12" t="s">
-        <v>574</v>
+        <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>575</v>
+        <v>39</v>
       </c>
       <c r="I12" t="s">
-        <v>576</v>
+        <v>516</v>
       </c>
       <c r="J12" t="s">
-        <v>577</v>
+        <v>517</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>578</v>
+        <v>518</v>
       </c>
       <c r="Q12" t="s">
-        <v>324</v>
+        <v>508</v>
       </c>
       <c r="R12" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>519</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>520</v>
       </c>
       <c r="D13" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>58</v>
+        <v>44</v>
+      </c>
+      <c r="G13" t="s">
+        <v>521</v>
       </c>
       <c r="I13" t="s">
-        <v>480</v>
+        <v>522</v>
       </c>
       <c r="J13" t="s">
-        <v>481</v>
+        <v>523</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>59</v>
+        <v>524</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>285</v>
       </c>
       <c r="R13" t="s">
-        <v>36</v>
-      </c>
-      <c r="S13" t="s">
-        <v>482</v>
-      </c>
-      <c r="V13" s="2">
-        <v>3</v>
+        <v>30</v>
+      </c>
+      <c r="V13" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>483</v>
+        <v>43</v>
       </c>
       <c r="D14" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E14" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>484</v>
+        <v>525</v>
       </c>
       <c r="J14" t="s">
-        <v>485</v>
+        <v>526</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>486</v>
+        <v>45</v>
       </c>
       <c r="R14" t="s">
-        <v>36</v>
-      </c>
-      <c r="S14" t="s">
-        <v>487</v>
+        <v>30</v>
       </c>
       <c r="V14" s="2">
         <v>3</v>
@@ -2802,31 +2906,37 @@
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
-        <v>488</v>
+        <v>527</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>319</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>489</v>
+        <v>528</v>
       </c>
       <c r="J15" t="s">
-        <v>490</v>
+        <v>529</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>491</v>
+        <v>530</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>278</v>
       </c>
       <c r="R15" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>509</v>
       </c>
       <c r="V15" s="2">
         <v>3</v>
@@ -2834,34 +2944,37 @@
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C16" t="s">
-        <v>492</v>
+        <v>274</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>267</v>
       </c>
       <c r="I16" t="s">
-        <v>493</v>
+        <v>215</v>
       </c>
       <c r="J16" t="s">
-        <v>494</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>495</v>
+        <v>531</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>532</v>
       </c>
       <c r="R16" t="s">
-        <v>36</v>
-      </c>
-      <c r="S16" t="s">
-        <v>496</v>
+        <v>30</v>
+      </c>
+      <c r="S16" s="3" t="s">
+        <v>533</v>
       </c>
       <c r="V16" s="2">
         <v>3</v>
@@ -2869,57 +2982,69 @@
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>534</v>
       </c>
       <c r="D17" t="s">
-        <v>63</v>
+        <v>535</v>
       </c>
       <c r="E17" t="s">
-        <v>64</v>
+        <v>536</v>
       </c>
       <c r="I17" t="s">
-        <v>65</v>
+        <v>537</v>
+      </c>
+      <c r="J17" t="s">
+        <v>538</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>66</v>
+        <v>539</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>285</v>
       </c>
       <c r="R17" t="s">
-        <v>67</v>
+        <v>30</v>
       </c>
       <c r="V17" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="B18" t="s">
-        <v>69</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>49</v>
       </c>
       <c r="E18" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="I18" t="s">
-        <v>73</v>
+        <v>441</v>
+      </c>
+      <c r="J18" t="s">
+        <v>442</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="R18" t="s">
-        <v>28</v>
+        <v>30</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>443</v>
       </c>
       <c r="V18" s="2">
         <v>1</v>
@@ -2927,587 +3052,542 @@
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>76</v>
+        <v>444</v>
       </c>
       <c r="D19" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E19" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="I19" t="s">
-        <v>191</v>
+        <v>445</v>
       </c>
       <c r="J19" t="s">
-        <v>192</v>
+        <v>446</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>193</v>
+        <v>447</v>
       </c>
       <c r="R19" t="s">
-        <v>28</v>
-      </c>
-      <c r="S19" t="s">
-        <v>289</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>195</v>
+        <v>30</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="V19" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>290</v>
+        <v>449</v>
       </c>
       <c r="D20" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>206</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="I20" t="s">
-        <v>291</v>
+        <v>450</v>
       </c>
       <c r="J20" t="s">
-        <v>292</v>
+        <v>451</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>293</v>
-      </c>
-      <c r="L20" t="s">
-        <v>294</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>295</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>296</v>
+        <v>452</v>
       </c>
       <c r="R20" t="s">
-        <v>28</v>
-      </c>
-      <c r="S20" t="s">
-        <v>297</v>
+        <v>30</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>298</v>
+        <v>453</v>
       </c>
       <c r="D21" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>299</v>
+        <v>39</v>
       </c>
       <c r="I21" t="s">
-        <v>300</v>
+        <v>454</v>
       </c>
       <c r="J21" t="s">
-        <v>301</v>
+        <v>455</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>303</v>
+        <v>456</v>
       </c>
       <c r="R21" t="s">
-        <v>28</v>
-      </c>
-      <c r="S21" t="s">
-        <v>304</v>
-      </c>
-      <c r="T21">
-        <v>380</v>
+        <v>30</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>457</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>643</v>
       </c>
       <c r="C22" t="s">
-        <v>305</v>
+        <v>53</v>
       </c>
       <c r="D22" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>306</v>
+        <v>55</v>
       </c>
       <c r="I22" t="s">
-        <v>307</v>
-      </c>
-      <c r="J22" t="s">
-        <v>308</v>
+        <v>56</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="L22" t="s">
-        <v>310</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>311</v>
+        <v>57</v>
       </c>
       <c r="R22" t="s">
-        <v>28</v>
-      </c>
-      <c r="S22" t="s">
-        <v>312</v>
+        <v>27</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" t="s">
+        <v>643</v>
+      </c>
+      <c r="C23" t="s">
+        <v>617</v>
+      </c>
+      <c r="D23" t="s">
         <v>29</v>
       </c>
-      <c r="B23" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" t="s">
-        <v>313</v>
-      </c>
-      <c r="D23" t="s">
-        <v>46</v>
-      </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>618</v>
       </c>
       <c r="I23" t="s">
-        <v>314</v>
+        <v>619</v>
       </c>
       <c r="J23" t="s">
-        <v>315</v>
+        <v>620</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>317</v>
+        <v>621</v>
       </c>
       <c r="R23" t="s">
-        <v>36</v>
-      </c>
-      <c r="S23" t="s">
-        <v>219</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>195</v>
+        <v>27</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="V23" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>643</v>
       </c>
       <c r="C24" t="s">
-        <v>318</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>319</v>
-      </c>
-      <c r="G24" t="s">
-        <v>320</v>
+        <v>623</v>
       </c>
       <c r="I24" t="s">
-        <v>321</v>
+        <v>624</v>
       </c>
       <c r="J24" t="s">
-        <v>322</v>
+        <v>625</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>324</v>
+        <v>626</v>
       </c>
       <c r="R24" t="s">
-        <v>325</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>195</v>
+        <v>27</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="V24" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>643</v>
       </c>
       <c r="C25" t="s">
-        <v>326</v>
+        <v>628</v>
       </c>
       <c r="D25" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>47</v>
+        <v>623</v>
       </c>
       <c r="I25" t="s">
-        <v>327</v>
+        <v>629</v>
       </c>
       <c r="J25" t="s">
-        <v>328</v>
+        <v>630</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>317</v>
+        <v>631</v>
       </c>
       <c r="R25" t="s">
-        <v>330</v>
-      </c>
-      <c r="S25" t="s">
-        <v>331</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>195</v>
+        <v>632</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="V25" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>643</v>
       </c>
       <c r="C26" t="s">
-        <v>332</v>
+        <v>634</v>
       </c>
       <c r="D26" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E26" t="s">
-        <v>99</v>
+        <v>635</v>
       </c>
       <c r="I26" t="s">
-        <v>333</v>
+        <v>636</v>
       </c>
       <c r="J26" t="s">
-        <v>334</v>
+        <v>637</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="L26" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>218</v>
+        <v>638</v>
       </c>
       <c r="R26" t="s">
-        <v>337</v>
-      </c>
-      <c r="S26" t="s">
-        <v>338</v>
-      </c>
-      <c r="T26" t="s">
-        <v>339</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>195</v>
+        <v>639</v>
+      </c>
+      <c r="V26" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>643</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>640</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="I27" t="s">
-        <v>82</v>
+        <v>641</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>83</v>
+        <v>642</v>
       </c>
       <c r="R27" t="s">
-        <v>84</v>
+        <v>27</v>
+      </c>
+      <c r="S27" s="3">
+        <v>40</v>
       </c>
       <c r="V27" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>59</v>
       </c>
       <c r="D28" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>89</v>
-      </c>
-      <c r="G28" t="s">
-        <v>444</v>
+        <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>445</v>
+        <v>152</v>
       </c>
       <c r="J28" t="s">
-        <v>446</v>
+        <v>153</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>90</v>
+        <v>249</v>
       </c>
       <c r="Q28" t="s">
-        <v>447</v>
+        <v>154</v>
       </c>
       <c r="R28" t="s">
-        <v>36</v>
-      </c>
-      <c r="V28" s="2">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="V28" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C29" t="s">
-        <v>448</v>
+        <v>251</v>
       </c>
       <c r="D29" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>450</v>
+        <v>167</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="I29" t="s">
-        <v>451</v>
+        <v>252</v>
       </c>
       <c r="J29" t="s">
-        <v>452</v>
+        <v>253</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>453</v>
+        <v>254</v>
+      </c>
+      <c r="L29" t="s">
+        <v>255</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="Q29" t="s">
-        <v>454</v>
+        <v>257</v>
       </c>
       <c r="R29" t="s">
-        <v>36</v>
-      </c>
-      <c r="V29" s="2">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="V29" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>455</v>
+        <v>259</v>
       </c>
       <c r="D30" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>456</v>
-      </c>
-      <c r="G30" t="s">
-        <v>457</v>
+        <v>260</v>
       </c>
       <c r="I30" t="s">
-        <v>458</v>
+        <v>261</v>
       </c>
       <c r="J30" t="s">
-        <v>459</v>
+        <v>262</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>460</v>
+        <v>263</v>
       </c>
       <c r="Q30" t="s">
-        <v>461</v>
+        <v>264</v>
       </c>
       <c r="R30" t="s">
-        <v>462</v>
-      </c>
-      <c r="V30" s="2">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="T30" s="3">
+        <v>380</v>
+      </c>
+      <c r="V30" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C31" t="s">
-        <v>463</v>
+        <v>266</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="E31" t="s">
-        <v>456</v>
-      </c>
-      <c r="G31" t="s">
-        <v>459</v>
+        <v>267</v>
       </c>
       <c r="I31" t="s">
-        <v>464</v>
+        <v>268</v>
       </c>
       <c r="J31" t="s">
-        <v>465</v>
+        <v>269</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>466</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s">
-        <v>459</v>
+        <v>271</v>
       </c>
       <c r="Q31" t="s">
-        <v>467</v>
+        <v>272</v>
       </c>
       <c r="R31" t="s">
-        <v>462</v>
-      </c>
-      <c r="S31" t="s">
-        <v>468</v>
-      </c>
-      <c r="T31" t="s">
-        <v>469</v>
-      </c>
-      <c r="V31" s="2">
-        <v>2</v>
+        <v>27</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="V31" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C32" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="D32" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
       <c r="E32" t="s">
-        <v>470</v>
-      </c>
-      <c r="G32" t="s">
-        <v>471</v>
+        <v>39</v>
       </c>
       <c r="I32" t="s">
-        <v>472</v>
+        <v>275</v>
       </c>
       <c r="J32" t="s">
-        <v>473</v>
+        <v>276</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>474</v>
+        <v>277</v>
       </c>
       <c r="Q32" t="s">
-        <v>475</v>
+        <v>278</v>
       </c>
       <c r="R32" t="s">
-        <v>36</v>
+        <v>30</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="V32" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="C33" t="s">
-        <v>205</v>
+        <v>279</v>
       </c>
       <c r="D33" t="s">
-        <v>449</v>
+        <v>38</v>
       </c>
       <c r="E33" t="s">
-        <v>470</v>
+        <v>280</v>
       </c>
       <c r="G33" t="s">
-        <v>471</v>
+        <v>281</v>
       </c>
       <c r="I33" t="s">
-        <v>476</v>
+        <v>282</v>
       </c>
       <c r="J33" t="s">
-        <v>477</v>
+        <v>283</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>478</v>
+        <v>284</v>
       </c>
       <c r="Q33" t="s">
-        <v>479</v>
+        <v>285</v>
       </c>
       <c r="R33" t="s">
-        <v>36</v>
+        <v>286</v>
       </c>
       <c r="V33" s="2">
         <v>2</v>
@@ -3515,421 +3595,487 @@
     </row>
     <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C34" t="s">
-        <v>92</v>
+        <v>287</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>93</v>
+        <v>39</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>288</v>
+      </c>
+      <c r="J34" t="s">
+        <v>289</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>95</v>
+        <v>290</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>278</v>
       </c>
       <c r="R34" t="s">
-        <v>96</v>
+        <v>291</v>
+      </c>
+      <c r="S34" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="V34" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C35" t="s">
-        <v>374</v>
+        <v>293</v>
       </c>
       <c r="D35" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="I35" t="s">
-        <v>375</v>
+        <v>294</v>
       </c>
       <c r="J35" t="s">
-        <v>376</v>
+        <v>295</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>377</v>
+        <v>296</v>
+      </c>
+      <c r="L35" t="s">
+        <v>297</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>179</v>
       </c>
       <c r="R35" t="s">
-        <v>348</v>
-      </c>
-      <c r="S35">
-        <v>118</v>
-      </c>
-      <c r="T35">
-        <v>73</v>
-      </c>
-      <c r="U35">
-        <v>16</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>195</v>
+        <v>298</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="V35" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>98</v>
+        <v>62</v>
       </c>
       <c r="D36" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E36" t="s">
-        <v>99</v>
+        <v>64</v>
       </c>
       <c r="I36" t="s">
-        <v>340</v>
+        <v>570</v>
       </c>
       <c r="J36" t="s">
-        <v>341</v>
+        <v>570</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R36" t="s">
-        <v>36</v>
-      </c>
-      <c r="S36" t="s">
-        <v>342</v>
-      </c>
-      <c r="T36" t="s">
-        <v>343</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="S36"/>
+      <c r="T36"/>
+      <c r="U36"/>
       <c r="V36" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="B37" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
-        <v>344</v>
+        <v>644</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E37" t="s">
-        <v>282</v>
+        <v>645</v>
+      </c>
+      <c r="G37" t="s">
+        <v>646</v>
       </c>
       <c r="I37" t="s">
-        <v>345</v>
+        <v>647</v>
       </c>
       <c r="J37" t="s">
-        <v>346</v>
+        <v>648</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>347</v>
+        <v>649</v>
       </c>
       <c r="R37" t="s">
-        <v>348</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37"/>
       <c r="V37" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
-        <v>349</v>
+        <v>527</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E38" t="s">
-        <v>282</v>
+        <v>650</v>
       </c>
       <c r="I38" t="s">
-        <v>350</v>
+        <v>651</v>
       </c>
       <c r="J38" t="s">
-        <v>351</v>
+        <v>652</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>352</v>
+        <v>653</v>
       </c>
       <c r="R38" t="s">
-        <v>28</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="S38"/>
+      <c r="T38"/>
+      <c r="U38"/>
       <c r="V38" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>353</v>
+        <v>293</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s">
-        <v>354</v>
+        <v>654</v>
       </c>
       <c r="I39" t="s">
-        <v>355</v>
+        <v>655</v>
       </c>
       <c r="J39" t="s">
-        <v>356</v>
+        <v>656</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>357</v>
+        <v>657</v>
       </c>
       <c r="R39" t="s">
-        <v>358</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="S39"/>
+      <c r="T39"/>
+      <c r="U39"/>
       <c r="V39" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C40" t="s">
-        <v>176</v>
+        <v>69</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="E40" t="s">
-        <v>354</v>
+        <v>71</v>
+      </c>
+      <c r="G40" t="s">
+        <v>405</v>
       </c>
       <c r="I40" t="s">
-        <v>359</v>
+        <v>406</v>
       </c>
       <c r="J40" t="s">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>361</v>
+        <v>72</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>408</v>
       </c>
       <c r="R40" t="s">
-        <v>348</v>
+        <v>30</v>
       </c>
       <c r="V40" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C41" t="s">
-        <v>181</v>
+        <v>409</v>
       </c>
       <c r="D41" t="s">
-        <v>362</v>
+        <v>410</v>
       </c>
       <c r="E41" t="s">
-        <v>363</v>
+        <v>411</v>
       </c>
       <c r="I41" t="s">
-        <v>364</v>
+        <v>412</v>
       </c>
       <c r="J41" t="s">
-        <v>365</v>
+        <v>413</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>367</v>
+        <v>414</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>415</v>
       </c>
       <c r="R41" t="s">
-        <v>348</v>
-      </c>
-      <c r="V41" s="2" t="s">
-        <v>195</v>
+        <v>30</v>
+      </c>
+      <c r="V41" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
+        <v>416</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="E42" t="s">
-        <v>368</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>370</v>
+        <v>417</v>
+      </c>
+      <c r="G42" t="s">
+        <v>418</v>
       </c>
       <c r="I42" t="s">
-        <v>371</v>
+        <v>419</v>
       </c>
       <c r="J42" t="s">
-        <v>372</v>
+        <v>420</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>373</v>
+        <v>421</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>422</v>
       </c>
       <c r="R42" t="s">
-        <v>348</v>
-      </c>
-      <c r="V42" s="2" t="s">
-        <v>195</v>
+        <v>423</v>
+      </c>
+      <c r="V42" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>103</v>
+        <v>424</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
       </c>
       <c r="E43" t="s">
-        <v>104</v>
+        <v>417</v>
+      </c>
+      <c r="G43" t="s">
+        <v>420</v>
       </c>
       <c r="I43" t="s">
-        <v>105</v>
+        <v>425</v>
+      </c>
+      <c r="J43" t="s">
+        <v>426</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>106</v>
+        <v>427</v>
+      </c>
+      <c r="L43" t="s">
+        <v>420</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>428</v>
       </c>
       <c r="R43" t="s">
-        <v>107</v>
+        <v>423</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>430</v>
       </c>
       <c r="V43" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>108</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>109</v>
+        <v>68</v>
       </c>
       <c r="C44" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="D44" t="s">
-        <v>111</v>
+        <v>410</v>
       </c>
       <c r="E44" t="s">
-        <v>112</v>
+        <v>431</v>
+      </c>
+      <c r="G44" t="s">
+        <v>432</v>
       </c>
       <c r="I44" t="s">
-        <v>113</v>
+        <v>433</v>
+      </c>
+      <c r="J44" t="s">
+        <v>434</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>114</v>
+        <v>435</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>436</v>
       </c>
       <c r="R44" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="V44" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>115</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>68</v>
       </c>
       <c r="C45" t="s">
-        <v>117</v>
+        <v>166</v>
       </c>
       <c r="D45" t="s">
-        <v>118</v>
+        <v>410</v>
       </c>
       <c r="E45" t="s">
-        <v>119</v>
+        <v>431</v>
+      </c>
+      <c r="G45" t="s">
+        <v>432</v>
       </c>
       <c r="I45" t="s">
-        <v>120</v>
+        <v>437</v>
+      </c>
+      <c r="J45" t="s">
+        <v>438</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>121</v>
+        <v>439</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>440</v>
       </c>
       <c r="R45" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="V45" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E46" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="I46" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="R46" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="V46" s="2">
         <v>3</v>
@@ -3937,81 +4083,78 @@
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>128</v>
+        <v>28</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C47" t="s">
-        <v>130</v>
+        <v>335</v>
       </c>
       <c r="D47" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="E47" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="I47" t="s">
-        <v>191</v>
+        <v>336</v>
       </c>
       <c r="J47" t="s">
-        <v>192</v>
+        <v>337</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="R47" t="s">
-        <v>28</v>
-      </c>
-      <c r="S47" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="T47" s="2">
-        <v>51</v>
+        <v>309</v>
+      </c>
+      <c r="S47" s="3">
+        <v>118</v>
+      </c>
+      <c r="T47" s="3">
+        <v>73</v>
+      </c>
+      <c r="U47" s="3">
+        <v>16</v>
       </c>
       <c r="V47" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B48" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C48" t="s">
-        <v>196</v>
+        <v>80</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E48" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="I48" t="s">
-        <v>191</v>
+        <v>301</v>
       </c>
       <c r="J48" t="s">
-        <v>197</v>
+        <v>302</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>193</v>
+        <v>82</v>
       </c>
       <c r="R48" t="s">
-        <v>36</v>
-      </c>
-      <c r="S48" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="T48" s="2">
-        <v>57</v>
+        <v>30</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="V48" s="2">
         <v>1</v>
@@ -4019,268 +4162,226 @@
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B49" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C49" t="s">
-        <v>200</v>
+        <v>305</v>
       </c>
       <c r="D49" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E49" t="s">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="I49" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="J49" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>193</v>
+        <v>308</v>
       </c>
       <c r="R49" t="s">
-        <v>36</v>
-      </c>
-      <c r="S49" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="T49" s="2"/>
+        <v>309</v>
+      </c>
       <c r="V49" s="2" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B50" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>310</v>
       </c>
       <c r="D50" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E50" t="s">
-        <v>206</v>
+        <v>243</v>
       </c>
       <c r="I50" t="s">
-        <v>207</v>
+        <v>311</v>
       </c>
       <c r="J50" t="s">
-        <v>208</v>
+        <v>312</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>193</v>
+        <v>313</v>
       </c>
       <c r="R50" t="s">
-        <v>36</v>
-      </c>
-      <c r="S50" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="T50" s="2"/>
+        <v>27</v>
+      </c>
       <c r="V50" s="2" t="s">
-        <v>195</v>
+        <v>156</v>
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B51" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>211</v>
+        <v>314</v>
       </c>
       <c r="D51" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E51" t="s">
-        <v>212</v>
+        <v>315</v>
       </c>
       <c r="I51" t="s">
-        <v>213</v>
+        <v>316</v>
       </c>
       <c r="J51" t="s">
-        <v>214</v>
+        <v>317</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="L51" t="s">
-        <v>216</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>218</v>
+        <v>318</v>
       </c>
       <c r="R51" t="s">
-        <v>150</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="T51" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="V51" s="2" t="s">
-        <v>195</v>
+        <v>319</v>
+      </c>
+      <c r="V51" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C52" t="s">
-        <v>220</v>
+        <v>137</v>
       </c>
       <c r="D52" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E52" t="s">
-        <v>52</v>
+        <v>315</v>
       </c>
       <c r="I52" t="s">
-        <v>221</v>
+        <v>320</v>
       </c>
       <c r="J52" t="s">
-        <v>222</v>
+        <v>321</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>223</v>
+        <v>322</v>
       </c>
       <c r="R52" t="s">
-        <v>224</v>
-      </c>
-      <c r="S52" s="2">
-        <v>420</v>
-      </c>
-      <c r="T52" s="2">
-        <v>274</v>
-      </c>
-      <c r="U52">
-        <v>30</v>
-      </c>
-      <c r="V52" s="2" t="s">
-        <v>195</v>
+        <v>309</v>
+      </c>
+      <c r="V52" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B53" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C53" t="s">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="D53" t="s">
-        <v>226</v>
+        <v>323</v>
       </c>
       <c r="E53" t="s">
-        <v>227</v>
+        <v>324</v>
       </c>
       <c r="I53" t="s">
-        <v>228</v>
+        <v>325</v>
       </c>
       <c r="J53" t="s">
-        <v>229</v>
+        <v>326</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>230</v>
+        <v>327</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>328</v>
       </c>
       <c r="R53" t="s">
-        <v>28</v>
-      </c>
-      <c r="S53" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="T53" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="V53" s="2" t="s">
-        <v>195</v>
+        <v>309</v>
+      </c>
+      <c r="V53" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="C54" t="s">
-        <v>233</v>
+        <v>62</v>
       </c>
       <c r="D54" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E54" t="s">
-        <v>99</v>
+        <v>329</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>331</v>
       </c>
       <c r="I54" t="s">
-        <v>234</v>
+        <v>332</v>
       </c>
       <c r="J54" t="s">
-        <v>235</v>
+        <v>333</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="R54" t="s">
-        <v>237</v>
-      </c>
-      <c r="S54" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="T54" s="2"/>
-      <c r="V54" s="2" t="s">
-        <v>195</v>
+        <v>309</v>
+      </c>
+      <c r="V54" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
-      </c>
-      <c r="D55" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="E55" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="I55" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="K55" s="1" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="R55" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="V55" s="2">
         <v>3</v>
@@ -4288,28 +4389,28 @@
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="B56" t="s">
-        <v>140</v>
+        <v>91</v>
       </c>
       <c r="C56" t="s">
-        <v>141</v>
+        <v>92</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="E56" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="K56" s="1" t="s">
-        <v>145</v>
+        <v>96</v>
       </c>
       <c r="R56" t="s">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="V56" s="2">
         <v>3</v>
@@ -4317,442 +4418,379 @@
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="C57" t="s">
-        <v>149</v>
+        <v>99</v>
       </c>
       <c r="D57" t="s">
-        <v>46</v>
+        <v>100</v>
       </c>
       <c r="E57" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I57" t="s">
-        <v>239</v>
-      </c>
-      <c r="J57" t="s">
-        <v>240</v>
+        <v>102</v>
       </c>
       <c r="K57" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>218</v>
+        <v>103</v>
       </c>
       <c r="R57" t="s">
-        <v>150</v>
-      </c>
-      <c r="S57" t="s">
-        <v>244</v>
-      </c>
-      <c r="T57" t="s">
-        <v>245</v>
-      </c>
-      <c r="U57">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="V57" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>147</v>
+        <v>105</v>
       </c>
       <c r="B58" t="s">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
-        <v>246</v>
+        <v>107</v>
       </c>
       <c r="D58" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E58" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="I58" t="s">
-        <v>247</v>
-      </c>
-      <c r="J58" t="s">
-        <v>248</v>
+        <v>108</v>
       </c>
       <c r="K58" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q58" t="s">
-        <v>218</v>
+        <v>109</v>
       </c>
       <c r="R58" t="s">
-        <v>28</v>
-      </c>
-      <c r="S58" t="s">
-        <v>250</v>
-      </c>
-      <c r="T58" t="s">
-        <v>251</v>
+        <v>27</v>
       </c>
       <c r="V58" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B59" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C59" t="s">
-        <v>252</v>
+        <v>112</v>
       </c>
       <c r="D59" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E59" t="s">
-        <v>206</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>253</v>
+        <v>39</v>
       </c>
       <c r="I59" t="s">
-        <v>254</v>
+        <v>152</v>
       </c>
       <c r="J59" t="s">
-        <v>255</v>
+        <v>153</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="L59" t="s">
-        <v>257</v>
-      </c>
-      <c r="M59" s="1" t="s">
-        <v>258</v>
+        <v>113</v>
       </c>
       <c r="Q59" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="R59" t="s">
-        <v>28</v>
-      </c>
-      <c r="S59" t="s">
-        <v>259</v>
-      </c>
-      <c r="V59" s="2">
-        <v>1</v>
+        <v>27</v>
+      </c>
+      <c r="S59" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="T59" s="3">
+        <v>51</v>
+      </c>
+      <c r="V59" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B60" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C60" t="s">
-        <v>260</v>
+        <v>157</v>
       </c>
       <c r="D60" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E60" t="s">
-        <v>206</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>253</v>
+        <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>261</v>
+        <v>152</v>
       </c>
       <c r="J60" t="s">
-        <v>262</v>
+        <v>158</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="L60" t="s">
-        <v>264</v>
-      </c>
-      <c r="M60" s="1" t="s">
-        <v>265</v>
+        <v>159</v>
       </c>
       <c r="Q60" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="R60" t="s">
-        <v>28</v>
-      </c>
-      <c r="S60" t="s">
-        <v>251</v>
-      </c>
-      <c r="V60" s="2">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="S60" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="T60" s="3">
+        <v>57</v>
+      </c>
+      <c r="V60" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B61" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C61" t="s">
-        <v>266</v>
+        <v>161</v>
       </c>
       <c r="D61" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E61" t="s">
-        <v>206</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>253</v>
+        <v>39</v>
       </c>
       <c r="I61" t="s">
-        <v>267</v>
+        <v>162</v>
       </c>
       <c r="J61" t="s">
-        <v>268</v>
+        <v>163</v>
       </c>
       <c r="K61" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="L61" t="s">
-        <v>270</v>
-      </c>
-      <c r="M61" s="1" t="s">
-        <v>271</v>
+        <v>164</v>
       </c>
       <c r="Q61" t="s">
-        <v>193</v>
+        <v>154</v>
       </c>
       <c r="R61" t="s">
-        <v>28</v>
-      </c>
-      <c r="S61" t="s">
-        <v>272</v>
-      </c>
-      <c r="V61" s="2">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="S61" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B62" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C62" t="s">
-        <v>273</v>
+        <v>166</v>
       </c>
       <c r="D62" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="E62" t="s">
-        <v>212</v>
-      </c>
-      <c r="F62" s="1" t="s">
-        <v>274</v>
+        <v>167</v>
       </c>
       <c r="I62" t="s">
-        <v>275</v>
+        <v>168</v>
       </c>
       <c r="J62" t="s">
-        <v>276</v>
+        <v>169</v>
       </c>
       <c r="K62" s="1" t="s">
-        <v>277</v>
+        <v>170</v>
       </c>
       <c r="Q62" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="R62" t="s">
-        <v>150</v>
-      </c>
-      <c r="S62" t="s">
-        <v>219</v>
-      </c>
-      <c r="T62" t="s">
-        <v>219</v>
-      </c>
-      <c r="V62" s="2">
-        <v>1</v>
+        <v>30</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B63" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C63" t="s">
-        <v>273</v>
+        <v>172</v>
       </c>
       <c r="D63" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="E63" t="s">
-        <v>212</v>
-      </c>
-      <c r="F63" s="1" t="s">
-        <v>274</v>
+        <v>173</v>
       </c>
       <c r="I63" t="s">
-        <v>278</v>
+        <v>174</v>
       </c>
       <c r="J63" t="s">
-        <v>279</v>
+        <v>175</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>280</v>
+        <v>176</v>
+      </c>
+      <c r="L63" t="s">
+        <v>177</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="Q63" t="s">
-        <v>218</v>
+        <v>179</v>
       </c>
       <c r="R63" t="s">
-        <v>150</v>
-      </c>
-      <c r="S63" t="s">
-        <v>219</v>
-      </c>
-      <c r="T63" t="s">
-        <v>219</v>
+        <v>118</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="T63" s="3" t="s">
+        <v>180</v>
       </c>
       <c r="V63" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>147</v>
+        <v>110</v>
       </c>
       <c r="B64" t="s">
-        <v>148</v>
+        <v>111</v>
       </c>
       <c r="C64" t="s">
-        <v>281</v>
+        <v>181</v>
       </c>
       <c r="D64" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="E64" t="s">
-        <v>282</v>
-      </c>
-      <c r="G64" t="s">
-        <v>283</v>
-      </c>
-      <c r="H64" s="1" t="s">
-        <v>284</v>
+        <v>44</v>
       </c>
       <c r="I64" t="s">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="J64" t="s">
-        <v>286</v>
+        <v>183</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="Q64" t="s">
-        <v>218</v>
+        <v>184</v>
       </c>
       <c r="R64" t="s">
-        <v>28</v>
-      </c>
-      <c r="S64">
-        <v>85</v>
-      </c>
-      <c r="T64">
-        <v>193</v>
+        <v>185</v>
+      </c>
+      <c r="S64" s="3">
+        <v>420</v>
+      </c>
+      <c r="T64" s="3">
+        <v>274</v>
+      </c>
+      <c r="U64" s="3">
+        <v>30</v>
       </c>
       <c r="V64" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>151</v>
+        <v>110</v>
       </c>
       <c r="B65" t="s">
-        <v>152</v>
+        <v>111</v>
       </c>
       <c r="C65" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
       <c r="E65" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="I65" t="s">
-        <v>156</v>
+        <v>189</v>
+      </c>
+      <c r="J65" t="s">
+        <v>190</v>
       </c>
       <c r="K65" s="1" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="R65" t="s">
-        <v>158</v>
+        <v>27</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="T65" s="3" t="s">
+        <v>193</v>
       </c>
       <c r="V65" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B66" t="s">
-        <v>159</v>
+        <v>111</v>
       </c>
       <c r="C66" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="D66" t="s">
-        <v>135</v>
+        <v>38</v>
       </c>
       <c r="E66" t="s">
-        <v>161</v>
-      </c>
-      <c r="G66" t="s">
-        <v>579</v>
+        <v>81</v>
       </c>
       <c r="I66" t="s">
-        <v>580</v>
+        <v>195</v>
       </c>
       <c r="J66" t="s">
-        <v>581</v>
+        <v>196</v>
       </c>
       <c r="K66" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="Q66" t="s">
-        <v>582</v>
+        <v>197</v>
       </c>
       <c r="R66" t="s">
-        <v>36</v>
-      </c>
-      <c r="S66" t="s">
-        <v>583</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>502</v>
+        <v>198</v>
+      </c>
+      <c r="S66" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="V66" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:22" x14ac:dyDescent="0.25">
@@ -4760,40 +4798,49 @@
         <v>115</v>
       </c>
       <c r="B67" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C67" t="s">
-        <v>584</v>
+        <v>117</v>
       </c>
       <c r="D67" t="s">
-        <v>585</v>
+        <v>38</v>
       </c>
       <c r="E67" t="s">
-        <v>586</v>
-      </c>
-      <c r="G67" t="s">
-        <v>587</v>
+        <v>81</v>
       </c>
       <c r="I67" t="s">
-        <v>588</v>
+        <v>200</v>
       </c>
       <c r="J67" t="s">
-        <v>589</v>
+        <v>201</v>
       </c>
       <c r="K67" s="1" t="s">
-        <v>590</v>
+        <v>202</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="Q67" t="s">
-        <v>591</v>
+        <v>179</v>
       </c>
       <c r="R67" t="s">
-        <v>36</v>
-      </c>
-      <c r="S67" t="s">
-        <v>592</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>502</v>
+        <v>118</v>
+      </c>
+      <c r="S67" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="T67" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="U67" s="3">
+        <v>11</v>
+      </c>
+      <c r="V67" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.25">
@@ -4801,40 +4848,43 @@
         <v>115</v>
       </c>
       <c r="B68" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C68" t="s">
-        <v>593</v>
+        <v>207</v>
       </c>
       <c r="D68" t="s">
-        <v>118</v>
+        <v>38</v>
       </c>
       <c r="E68" t="s">
-        <v>119</v>
-      </c>
-      <c r="G68" t="s">
-        <v>594</v>
+        <v>81</v>
       </c>
       <c r="I68" t="s">
-        <v>595</v>
+        <v>208</v>
       </c>
       <c r="J68" t="s">
-        <v>596</v>
+        <v>209</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>597</v>
+        <v>210</v>
+      </c>
+      <c r="M68" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="Q68" t="s">
-        <v>582</v>
+        <v>179</v>
       </c>
       <c r="R68" t="s">
-        <v>36</v>
-      </c>
-      <c r="S68" t="s">
-        <v>598</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>502</v>
+        <v>27</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="T68" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="V68" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.25">
@@ -4842,1036 +4892,1444 @@
         <v>115</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="C69" t="s">
-        <v>599</v>
+        <v>213</v>
       </c>
       <c r="D69" t="s">
-        <v>600</v>
+        <v>38</v>
       </c>
       <c r="E69" t="s">
-        <v>601</v>
-      </c>
-      <c r="G69" t="s">
-        <v>602</v>
+        <v>167</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="I69" t="s">
-        <v>603</v>
+        <v>215</v>
       </c>
       <c r="J69" t="s">
-        <v>604</v>
+        <v>216</v>
       </c>
       <c r="K69" s="1" t="s">
-        <v>605</v>
+        <v>217</v>
+      </c>
+      <c r="L69" t="s">
+        <v>218</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="Q69" t="s">
-        <v>582</v>
+        <v>154</v>
       </c>
       <c r="R69" t="s">
-        <v>606</v>
-      </c>
-      <c r="S69" t="s">
-        <v>607</v>
-      </c>
-      <c r="V69" s="2" t="s">
-        <v>502</v>
+        <v>27</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="V69" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="B70" t="s">
-        <v>164</v>
+        <v>116</v>
       </c>
       <c r="C70" t="s">
-        <v>165</v>
+        <v>221</v>
       </c>
       <c r="D70" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="E70" t="s">
-        <v>166</v>
+        <v>167</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="I70" t="s">
-        <v>167</v>
+        <v>222</v>
+      </c>
+      <c r="J70" t="s">
+        <v>223</v>
       </c>
       <c r="K70" s="1" t="s">
-        <v>168</v>
+        <v>224</v>
+      </c>
+      <c r="L70" t="s">
+        <v>225</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>154</v>
       </c>
       <c r="R70" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="S70" s="3" t="s">
+        <v>212</v>
       </c>
       <c r="V70" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="B71" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="C71" t="s">
-        <v>171</v>
+        <v>227</v>
       </c>
       <c r="D71" t="s">
-        <v>172</v>
+        <v>38</v>
       </c>
       <c r="E71" t="s">
-        <v>173</v>
+        <v>167</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="I71" t="s">
-        <v>608</v>
+        <v>228</v>
       </c>
       <c r="J71" t="s">
-        <v>609</v>
+        <v>229</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>174</v>
+        <v>230</v>
+      </c>
+      <c r="L71" t="s">
+        <v>231</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="Q71" t="s">
-        <v>610</v>
+        <v>154</v>
       </c>
       <c r="R71" t="s">
-        <v>84</v>
-      </c>
-      <c r="V71" t="s">
-        <v>502</v>
+        <v>27</v>
+      </c>
+      <c r="S71" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="V71" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="B72" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="C72" t="s">
-        <v>611</v>
+        <v>234</v>
       </c>
       <c r="D72" t="s">
-        <v>612</v>
+        <v>70</v>
       </c>
       <c r="E72" t="s">
-        <v>613</v>
+        <v>173</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I72" t="s">
-        <v>614</v>
+        <v>236</v>
       </c>
       <c r="J72" t="s">
-        <v>609</v>
+        <v>237</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>615</v>
+        <v>238</v>
       </c>
       <c r="Q72" t="s">
-        <v>610</v>
+        <v>179</v>
       </c>
       <c r="R72" t="s">
-        <v>84</v>
-      </c>
-      <c r="V72" t="s">
-        <v>502</v>
+        <v>118</v>
+      </c>
+      <c r="S72" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="V72" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="B73" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="C73" t="s">
-        <v>616</v>
+        <v>234</v>
       </c>
       <c r="D73" t="s">
-        <v>172</v>
+        <v>70</v>
       </c>
       <c r="E73" t="s">
-        <v>617</v>
-      </c>
-      <c r="G73" t="s">
-        <v>618</v>
+        <v>173</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="I73" t="s">
-        <v>619</v>
+        <v>239</v>
       </c>
       <c r="J73" t="s">
-        <v>620</v>
+        <v>240</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>621</v>
+        <v>241</v>
       </c>
       <c r="Q73" t="s">
-        <v>610</v>
+        <v>179</v>
       </c>
       <c r="R73" t="s">
-        <v>84</v>
-      </c>
-      <c r="V73" t="s">
-        <v>502</v>
+        <v>118</v>
+      </c>
+      <c r="S73" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="T73" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="V73" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>169</v>
+        <v>115</v>
       </c>
       <c r="B74" t="s">
-        <v>170</v>
+        <v>116</v>
       </c>
       <c r="C74" t="s">
-        <v>622</v>
+        <v>242</v>
       </c>
       <c r="D74" t="s">
-        <v>585</v>
+        <v>38</v>
       </c>
       <c r="E74" t="s">
-        <v>623</v>
+        <v>243</v>
       </c>
       <c r="G74" t="s">
-        <v>624</v>
+        <v>244</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="I74" t="s">
-        <v>614</v>
+        <v>246</v>
       </c>
       <c r="J74" t="s">
-        <v>609</v>
+        <v>247</v>
       </c>
       <c r="K74" s="1" t="s">
-        <v>625</v>
+        <v>248</v>
       </c>
       <c r="Q74" t="s">
-        <v>610</v>
+        <v>179</v>
       </c>
       <c r="R74" t="s">
-        <v>84</v>
-      </c>
-      <c r="V74" t="s">
-        <v>502</v>
+        <v>27</v>
+      </c>
+      <c r="S74" s="3">
+        <v>85</v>
+      </c>
+      <c r="T74" s="3">
+        <v>193</v>
+      </c>
+      <c r="V74" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>404</v>
+        <v>97</v>
       </c>
       <c r="B75" t="s">
-        <v>405</v>
+        <v>120</v>
       </c>
       <c r="C75" t="s">
-        <v>406</v>
+        <v>121</v>
       </c>
       <c r="D75" t="s">
-        <v>407</v>
+        <v>114</v>
       </c>
       <c r="E75" t="s">
-        <v>408</v>
+        <v>122</v>
+      </c>
+      <c r="G75" t="s">
+        <v>540</v>
       </c>
       <c r="I75" t="s">
-        <v>409</v>
+        <v>541</v>
       </c>
       <c r="J75" t="s">
-        <v>410</v>
+        <v>542</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>412</v>
+        <v>123</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>543</v>
       </c>
       <c r="R75" t="s">
-        <v>413</v>
-      </c>
-      <c r="S75" t="s">
-        <v>414</v>
+        <v>30</v>
+      </c>
+      <c r="S75" s="3" t="s">
+        <v>544</v>
       </c>
       <c r="V75" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>404</v>
+        <v>97</v>
       </c>
       <c r="B76" t="s">
-        <v>405</v>
+        <v>120</v>
       </c>
       <c r="C76" t="s">
-        <v>415</v>
+        <v>545</v>
       </c>
       <c r="D76" t="s">
-        <v>416</v>
+        <v>546</v>
       </c>
       <c r="E76" t="s">
-        <v>417</v>
+        <v>547</v>
+      </c>
+      <c r="G76" t="s">
+        <v>548</v>
       </c>
       <c r="I76" t="s">
-        <v>418</v>
+        <v>549</v>
       </c>
       <c r="J76" t="s">
-        <v>419</v>
+        <v>550</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>420</v>
+        <v>551</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>552</v>
       </c>
       <c r="R76" t="s">
-        <v>400</v>
-      </c>
-      <c r="S76" t="s">
-        <v>421</v>
-      </c>
-      <c r="V76" s="2">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="S76" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="77" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>404</v>
+        <v>97</v>
       </c>
       <c r="B77" t="s">
-        <v>405</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>422</v>
+        <v>554</v>
       </c>
       <c r="D77" t="s">
-        <v>423</v>
+        <v>100</v>
       </c>
       <c r="E77" t="s">
-        <v>424</v>
+        <v>101</v>
+      </c>
+      <c r="G77" t="s">
+        <v>555</v>
       </c>
       <c r="I77" t="s">
-        <v>425</v>
+        <v>556</v>
       </c>
       <c r="J77" t="s">
-        <v>426</v>
+        <v>557</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>427</v>
+        <v>558</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>543</v>
       </c>
       <c r="R77" t="s">
-        <v>428</v>
-      </c>
-      <c r="S77" t="s">
-        <v>429</v>
-      </c>
-      <c r="V77" s="2">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="S77" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>404</v>
+        <v>97</v>
       </c>
       <c r="B78" t="s">
-        <v>405</v>
+        <v>120</v>
       </c>
       <c r="C78" t="s">
-        <v>430</v>
+        <v>560</v>
       </c>
       <c r="D78" t="s">
-        <v>431</v>
+        <v>561</v>
       </c>
       <c r="E78" t="s">
-        <v>432</v>
+        <v>562</v>
+      </c>
+      <c r="G78" t="s">
+        <v>563</v>
       </c>
       <c r="I78" t="s">
-        <v>433</v>
+        <v>564</v>
       </c>
       <c r="J78" t="s">
-        <v>434</v>
+        <v>565</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>435</v>
+        <v>566</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>543</v>
       </c>
       <c r="R78" t="s">
-        <v>36</v>
-      </c>
-      <c r="S78" t="s">
-        <v>436</v>
-      </c>
-      <c r="V78" s="2">
-        <v>2</v>
+        <v>567</v>
+      </c>
+      <c r="S78" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="V78" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="79" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>404</v>
+        <v>124</v>
       </c>
       <c r="B79" t="s">
-        <v>405</v>
+        <v>125</v>
       </c>
       <c r="C79" t="s">
-        <v>378</v>
+        <v>126</v>
       </c>
       <c r="D79" t="s">
-        <v>437</v>
+        <v>24</v>
       </c>
       <c r="E79" t="s">
-        <v>438</v>
+        <v>127</v>
       </c>
       <c r="I79" t="s">
-        <v>439</v>
-      </c>
-      <c r="J79" t="s">
-        <v>440</v>
+        <v>128</v>
       </c>
       <c r="K79" s="1" t="s">
-        <v>441</v>
+        <v>129</v>
       </c>
       <c r="R79" t="s">
-        <v>442</v>
-      </c>
-      <c r="S79" t="s">
-        <v>443</v>
-      </c>
-      <c r="V79" s="2">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="80" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="B80" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="C80" t="s">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="D80" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E80" t="s">
-        <v>177</v>
+        <v>134</v>
       </c>
       <c r="I80" t="s">
-        <v>528</v>
+        <v>569</v>
       </c>
       <c r="J80" t="s">
-        <v>529</v>
+        <v>570</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="Q80" t="s">
-        <v>324</v>
+        <v>571</v>
       </c>
       <c r="R80" t="s">
-        <v>36</v>
-      </c>
-      <c r="V80" s="2">
-        <v>3</v>
+        <v>66</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="81" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="B81" t="s">
-        <v>175</v>
-      </c>
-      <c r="C81">
-        <v>1456</v>
+        <v>131</v>
+      </c>
+      <c r="C81" t="s">
+        <v>572</v>
       </c>
       <c r="D81" t="s">
-        <v>530</v>
+        <v>573</v>
       </c>
       <c r="E81" t="s">
-        <v>531</v>
+        <v>574</v>
       </c>
       <c r="I81" t="s">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="J81" t="s">
-        <v>533</v>
+        <v>570</v>
       </c>
       <c r="K81" s="1" t="s">
-        <v>534</v>
+        <v>576</v>
       </c>
       <c r="Q81" t="s">
-        <v>317</v>
+        <v>571</v>
       </c>
       <c r="R81" t="s">
-        <v>36</v>
-      </c>
-      <c r="S81">
-        <v>58</v>
-      </c>
-      <c r="T81">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="V81" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="82" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="B82" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="C82" t="s">
-        <v>160</v>
+        <v>577</v>
       </c>
       <c r="D82" t="s">
-        <v>46</v>
+        <v>133</v>
       </c>
       <c r="E82" t="s">
-        <v>47</v>
+        <v>578</v>
+      </c>
+      <c r="G82" t="s">
+        <v>579</v>
       </c>
       <c r="I82" t="s">
-        <v>535</v>
+        <v>580</v>
       </c>
       <c r="J82" t="s">
-        <v>536</v>
+        <v>581</v>
       </c>
       <c r="K82" s="1" t="s">
-        <v>537</v>
+        <v>582</v>
       </c>
       <c r="Q82" t="s">
-        <v>317</v>
+        <v>571</v>
       </c>
       <c r="R82" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
       <c r="V82" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="83" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>68</v>
+        <v>130</v>
       </c>
       <c r="B83" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="C83" t="s">
-        <v>538</v>
+        <v>583</v>
       </c>
       <c r="D83" t="s">
-        <v>539</v>
+        <v>546</v>
       </c>
       <c r="E83" t="s">
-        <v>540</v>
+        <v>584</v>
+      </c>
+      <c r="G83" t="s">
+        <v>585</v>
       </c>
       <c r="I83" t="s">
-        <v>541</v>
+        <v>575</v>
       </c>
       <c r="J83" t="s">
-        <v>542</v>
+        <v>570</v>
       </c>
       <c r="K83" s="1" t="s">
-        <v>543</v>
+        <v>586</v>
       </c>
       <c r="Q83" t="s">
-        <v>544</v>
+        <v>571</v>
       </c>
       <c r="R83" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="84" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>68</v>
+        <v>365</v>
       </c>
       <c r="B84" t="s">
-        <v>175</v>
+        <v>366</v>
       </c>
       <c r="C84" t="s">
-        <v>176</v>
+        <v>367</v>
       </c>
       <c r="D84" t="s">
-        <v>46</v>
+        <v>368</v>
       </c>
       <c r="E84" t="s">
-        <v>177</v>
+        <v>369</v>
       </c>
       <c r="I84" t="s">
-        <v>178</v>
+        <v>370</v>
+      </c>
+      <c r="J84" t="s">
+        <v>371</v>
       </c>
       <c r="K84" s="1" t="s">
-        <v>179</v>
+        <v>372</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>373</v>
       </c>
       <c r="R84" t="s">
-        <v>36</v>
+        <v>374</v>
+      </c>
+      <c r="S84" s="3" t="s">
+        <v>375</v>
       </c>
       <c r="V84" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>180</v>
+        <v>365</v>
       </c>
       <c r="B85" t="s">
-        <v>175</v>
+        <v>366</v>
       </c>
       <c r="C85" t="s">
-        <v>181</v>
+        <v>376</v>
       </c>
       <c r="D85" t="s">
-        <v>46</v>
+        <v>377</v>
       </c>
       <c r="E85" t="s">
-        <v>52</v>
-      </c>
-      <c r="G85" t="s">
-        <v>497</v>
+        <v>378</v>
       </c>
       <c r="I85" t="s">
-        <v>498</v>
+        <v>379</v>
       </c>
       <c r="J85" t="s">
-        <v>499</v>
+        <v>380</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="Q85" t="s">
-        <v>324</v>
+        <v>381</v>
       </c>
       <c r="R85" t="s">
-        <v>500</v>
-      </c>
-      <c r="S85" t="s">
-        <v>501</v>
-      </c>
-      <c r="V85" s="2" t="s">
-        <v>502</v>
+        <v>361</v>
+      </c>
+      <c r="S85" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="V85" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="86" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>180</v>
+        <v>365</v>
       </c>
       <c r="B86" t="s">
-        <v>175</v>
+        <v>366</v>
       </c>
       <c r="C86" t="s">
-        <v>503</v>
+        <v>383</v>
       </c>
       <c r="D86" t="s">
-        <v>504</v>
+        <v>384</v>
       </c>
       <c r="E86" t="s">
-        <v>505</v>
-      </c>
-      <c r="G86" t="s">
-        <v>506</v>
+        <v>385</v>
       </c>
       <c r="I86" t="s">
-        <v>507</v>
+        <v>386</v>
       </c>
       <c r="J86" t="s">
-        <v>508</v>
+        <v>387</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="Q86" t="s">
-        <v>510</v>
+        <v>388</v>
       </c>
       <c r="R86" t="s">
-        <v>511</v>
+        <v>389</v>
+      </c>
+      <c r="S86" s="3" t="s">
+        <v>390</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="87" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>180</v>
+        <v>365</v>
       </c>
       <c r="B87" t="s">
-        <v>175</v>
+        <v>366</v>
       </c>
       <c r="C87" t="s">
-        <v>512</v>
+        <v>391</v>
       </c>
       <c r="D87" t="s">
-        <v>46</v>
+        <v>392</v>
       </c>
       <c r="E87" t="s">
-        <v>513</v>
-      </c>
-      <c r="G87" t="s">
-        <v>514</v>
+        <v>393</v>
       </c>
       <c r="I87" t="s">
-        <v>515</v>
+        <v>394</v>
       </c>
       <c r="J87" t="s">
-        <v>516</v>
+        <v>395</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>518</v>
+        <v>396</v>
       </c>
       <c r="R87" t="s">
-        <v>519</v>
+        <v>30</v>
+      </c>
+      <c r="S87" s="3" t="s">
+        <v>397</v>
       </c>
       <c r="V87" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="88" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>180</v>
+        <v>365</v>
       </c>
       <c r="B88" t="s">
-        <v>175</v>
+        <v>366</v>
       </c>
       <c r="C88" t="s">
-        <v>520</v>
+        <v>339</v>
       </c>
       <c r="D88" t="s">
-        <v>521</v>
+        <v>398</v>
       </c>
       <c r="E88" t="s">
-        <v>522</v>
-      </c>
-      <c r="G88" t="s">
-        <v>523</v>
+        <v>399</v>
       </c>
       <c r="I88" t="s">
-        <v>524</v>
+        <v>400</v>
       </c>
       <c r="J88" t="s">
-        <v>525</v>
+        <v>401</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>526</v>
-      </c>
-      <c r="M88" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>324</v>
+        <v>402</v>
       </c>
       <c r="R88" t="s">
-        <v>36</v>
+        <v>403</v>
+      </c>
+      <c r="S88" s="3" t="s">
+        <v>404</v>
       </c>
       <c r="V88" s="2" t="s">
-        <v>502</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="C89" t="s">
-        <v>185</v>
+        <v>137</v>
       </c>
       <c r="D89" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="E89" t="s">
-        <v>187</v>
+        <v>138</v>
       </c>
       <c r="I89" t="s">
-        <v>188</v>
+        <v>489</v>
+      </c>
+      <c r="J89" t="s">
+        <v>490</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>189</v>
+        <v>140</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>285</v>
       </c>
       <c r="R89" t="s">
-        <v>190</v>
+        <v>30</v>
       </c>
       <c r="V89" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="90" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
-      </c>
-      <c r="C90" t="s">
-        <v>378</v>
+        <v>136</v>
+      </c>
+      <c r="C90">
+        <v>1456</v>
       </c>
       <c r="D90" t="s">
-        <v>186</v>
+        <v>491</v>
       </c>
       <c r="E90" t="s">
-        <v>379</v>
+        <v>492</v>
       </c>
       <c r="I90" t="s">
-        <v>380</v>
+        <v>493</v>
       </c>
       <c r="J90" t="s">
-        <v>381</v>
+        <v>494</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>382</v>
+        <v>495</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>278</v>
       </c>
       <c r="R90" t="s">
-        <v>383</v>
-      </c>
-      <c r="V90" s="2">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="S90" s="3">
+        <v>58</v>
+      </c>
+      <c r="T90" s="3">
+        <v>51</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="91" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="C91" t="s">
-        <v>384</v>
+        <v>121</v>
       </c>
       <c r="D91" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="E91" t="s">
-        <v>385</v>
+        <v>39</v>
       </c>
       <c r="I91" t="s">
-        <v>386</v>
+        <v>496</v>
       </c>
       <c r="J91" t="s">
-        <v>387</v>
+        <v>497</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>388</v>
+        <v>498</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>278</v>
       </c>
       <c r="R91" t="s">
-        <v>28</v>
-      </c>
-      <c r="V91" s="2">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="V91" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="92" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="B92" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="C92" t="s">
-        <v>389</v>
+        <v>499</v>
       </c>
       <c r="D92" t="s">
-        <v>186</v>
+        <v>500</v>
       </c>
       <c r="E92" t="s">
-        <v>187</v>
+        <v>501</v>
       </c>
       <c r="I92" t="s">
-        <v>390</v>
+        <v>502</v>
       </c>
       <c r="J92" t="s">
-        <v>391</v>
+        <v>503</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>392</v>
-      </c>
-      <c r="L92" s="1" t="s">
-        <v>393</v>
+        <v>504</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>505</v>
       </c>
       <c r="R92" t="s">
-        <v>394</v>
-      </c>
-      <c r="V92" s="2">
-        <v>2</v>
+        <v>66</v>
+      </c>
+      <c r="V92" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="93" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>183</v>
+        <v>52</v>
       </c>
       <c r="B93" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="C93" t="s">
-        <v>395</v>
+        <v>137</v>
       </c>
       <c r="D93" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="E93" t="s">
-        <v>396</v>
+        <v>138</v>
       </c>
       <c r="I93" t="s">
-        <v>397</v>
-      </c>
-      <c r="J93" t="s">
-        <v>398</v>
+        <v>139</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>399</v>
+        <v>140</v>
       </c>
       <c r="R93" t="s">
-        <v>400</v>
-      </c>
-      <c r="V93" s="2">
-        <v>2</v>
+        <v>30</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>463</v>
       </c>
     </row>
     <row r="94" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="B94" t="s">
-        <v>184</v>
+        <v>136</v>
       </c>
       <c r="C94" t="s">
-        <v>378</v>
+        <v>142</v>
       </c>
       <c r="D94" t="s">
-        <v>186</v>
+        <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>379</v>
+        <v>44</v>
+      </c>
+      <c r="G94" t="s">
+        <v>458</v>
       </c>
       <c r="I94" t="s">
-        <v>401</v>
+        <v>459</v>
       </c>
       <c r="J94" t="s">
-        <v>402</v>
+        <v>460</v>
       </c>
       <c r="K94" s="1" t="s">
-        <v>403</v>
+        <v>143</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>285</v>
       </c>
       <c r="R94" t="s">
-        <v>36</v>
+        <v>461</v>
+      </c>
+      <c r="S94" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="V94" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>141</v>
+      </c>
+      <c r="B95" t="s">
+        <v>136</v>
+      </c>
+      <c r="C95" t="s">
+        <v>464</v>
+      </c>
+      <c r="D95" t="s">
+        <v>465</v>
+      </c>
+      <c r="E95" t="s">
+        <v>466</v>
+      </c>
+      <c r="G95" t="s">
+        <v>467</v>
+      </c>
+      <c r="I95" t="s">
+        <v>468</v>
+      </c>
+      <c r="J95" t="s">
+        <v>469</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>471</v>
+      </c>
+      <c r="R95" t="s">
+        <v>472</v>
+      </c>
+      <c r="V95" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>141</v>
+      </c>
+      <c r="B96" t="s">
+        <v>136</v>
+      </c>
+      <c r="C96" t="s">
+        <v>473</v>
+      </c>
+      <c r="D96" t="s">
+        <v>38</v>
+      </c>
+      <c r="E96" t="s">
+        <v>474</v>
+      </c>
+      <c r="G96" t="s">
+        <v>475</v>
+      </c>
+      <c r="I96" t="s">
+        <v>476</v>
+      </c>
+      <c r="J96" t="s">
+        <v>477</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>479</v>
+      </c>
+      <c r="R96" t="s">
+        <v>480</v>
+      </c>
+      <c r="V96" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>141</v>
+      </c>
+      <c r="B97" t="s">
+        <v>136</v>
+      </c>
+      <c r="C97" t="s">
+        <v>481</v>
+      </c>
+      <c r="D97" t="s">
+        <v>482</v>
+      </c>
+      <c r="E97" t="s">
+        <v>483</v>
+      </c>
+      <c r="G97" t="s">
+        <v>484</v>
+      </c>
+      <c r="I97" t="s">
+        <v>485</v>
+      </c>
+      <c r="J97" t="s">
+        <v>486</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>285</v>
+      </c>
+      <c r="R97" t="s">
+        <v>30</v>
+      </c>
+      <c r="V97" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>144</v>
+      </c>
+      <c r="B98" t="s">
+        <v>145</v>
+      </c>
+      <c r="C98" t="s">
+        <v>146</v>
+      </c>
+      <c r="D98" t="s">
+        <v>147</v>
+      </c>
+      <c r="E98" t="s">
+        <v>148</v>
+      </c>
+      <c r="I98" t="s">
+        <v>149</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="R98" t="s">
+        <v>151</v>
+      </c>
+      <c r="V98" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>144</v>
+      </c>
+      <c r="B99" t="s">
+        <v>145</v>
+      </c>
+      <c r="C99" t="s">
+        <v>339</v>
+      </c>
+      <c r="D99" t="s">
+        <v>147</v>
+      </c>
+      <c r="E99" t="s">
+        <v>340</v>
+      </c>
+      <c r="I99" t="s">
+        <v>341</v>
+      </c>
+      <c r="J99" t="s">
+        <v>342</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="R99" t="s">
+        <v>344</v>
+      </c>
+      <c r="V99" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>144</v>
+      </c>
+      <c r="B100" t="s">
+        <v>145</v>
+      </c>
+      <c r="C100" t="s">
+        <v>345</v>
+      </c>
+      <c r="D100" t="s">
+        <v>147</v>
+      </c>
+      <c r="E100" t="s">
+        <v>346</v>
+      </c>
+      <c r="I100" t="s">
+        <v>347</v>
+      </c>
+      <c r="J100" t="s">
+        <v>348</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="R100" t="s">
+        <v>27</v>
+      </c>
+      <c r="V100" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>144</v>
+      </c>
+      <c r="B101" t="s">
+        <v>145</v>
+      </c>
+      <c r="C101" t="s">
+        <v>350</v>
+      </c>
+      <c r="D101" t="s">
+        <v>147</v>
+      </c>
+      <c r="E101" t="s">
+        <v>148</v>
+      </c>
+      <c r="I101" t="s">
+        <v>351</v>
+      </c>
+      <c r="J101" t="s">
+        <v>352</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="L101" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="R101" t="s">
+        <v>355</v>
+      </c>
+      <c r="V101" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>144</v>
+      </c>
+      <c r="B102" t="s">
+        <v>145</v>
+      </c>
+      <c r="C102" t="s">
+        <v>356</v>
+      </c>
+      <c r="D102" t="s">
+        <v>119</v>
+      </c>
+      <c r="E102" t="s">
+        <v>357</v>
+      </c>
+      <c r="I102" t="s">
+        <v>358</v>
+      </c>
+      <c r="J102" t="s">
+        <v>359</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="R102" t="s">
+        <v>361</v>
+      </c>
+      <c r="V102" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>144</v>
+      </c>
+      <c r="B103" t="s">
+        <v>145</v>
+      </c>
+      <c r="C103" t="s">
+        <v>339</v>
+      </c>
+      <c r="D103" t="s">
+        <v>147</v>
+      </c>
+      <c r="E103" t="s">
+        <v>340</v>
+      </c>
+      <c r="I103" t="s">
+        <v>362</v>
+      </c>
+      <c r="J103" t="s">
+        <v>363</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="R103" t="s">
+        <v>30</v>
+      </c>
+      <c r="V103" s="2">
         <v>2</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="K2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="K3" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="K4" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="K17" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="K18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="K27" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="K34" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="K43" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K44" r:id="rId9" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="K45" r:id="rId10" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K46" r:id="rId11" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K84" r:id="rId12" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K89" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K70" r:id="rId14" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K65" r:id="rId15" xr:uid="{00000000-0004-0000-0000-000015000000}"/>
-    <hyperlink ref="K56" r:id="rId16" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="K55" r:id="rId17" xr:uid="{00000000-0004-0000-0000-000012000000}"/>
-    <hyperlink ref="K47" r:id="rId18" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
-    <hyperlink ref="K48" r:id="rId19" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
-    <hyperlink ref="K49" r:id="rId20" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
-    <hyperlink ref="K50" r:id="rId21" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
-    <hyperlink ref="K51" r:id="rId22" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
-    <hyperlink ref="M51" r:id="rId23" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
-    <hyperlink ref="K52" r:id="rId24" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
-    <hyperlink ref="K53" r:id="rId25" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
-    <hyperlink ref="K54" r:id="rId26" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
-    <hyperlink ref="K57" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
-    <hyperlink ref="M57" r:id="rId28" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
-    <hyperlink ref="O57" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
-    <hyperlink ref="K58" r:id="rId30" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
-    <hyperlink ref="M58" r:id="rId31" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
-    <hyperlink ref="K59" r:id="rId32" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
-    <hyperlink ref="M59" r:id="rId33" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
-    <hyperlink ref="K60" r:id="rId34" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
-    <hyperlink ref="F59" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
-    <hyperlink ref="F60:F61" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
-    <hyperlink ref="M60" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
-    <hyperlink ref="M61" r:id="rId38" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
-    <hyperlink ref="K61" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
-    <hyperlink ref="K62" r:id="rId40" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
-    <hyperlink ref="F62" r:id="rId41" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
-    <hyperlink ref="F63" r:id="rId42" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
-    <hyperlink ref="K63" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
-    <hyperlink ref="K64" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
-    <hyperlink ref="H64" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
-    <hyperlink ref="K19" r:id="rId46" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
-    <hyperlink ref="K20" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
-    <hyperlink ref="M20" r:id="rId48" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
-    <hyperlink ref="F20" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
-    <hyperlink ref="K21" r:id="rId50" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
-    <hyperlink ref="K22" r:id="rId51" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
-    <hyperlink ref="K23" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
-    <hyperlink ref="K24" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
-    <hyperlink ref="K25" r:id="rId54" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
-    <hyperlink ref="K26" r:id="rId55" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
-    <hyperlink ref="K36" r:id="rId56" xr:uid="{C61A9D98-CECD-4B5E-B96E-4289BBC0D262}"/>
-    <hyperlink ref="K37" r:id="rId57" xr:uid="{EB7CB685-E0C1-4945-9E14-9CA8A1A342EC}"/>
-    <hyperlink ref="K38" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F065AADE-42A0-4C3C-B801-4BE9B5FA9BEB}"/>
-    <hyperlink ref="K39" r:id="rId59" xr:uid="{819ABFBD-4499-4FE6-9CDB-0A9FE7A07280}"/>
-    <hyperlink ref="K40" r:id="rId60" xr:uid="{48E832D6-CC6D-436E-BC8A-74B5489EE9B1}"/>
-    <hyperlink ref="K41" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8CE24E7-04FD-4348-88B3-8498A10C097C}"/>
-    <hyperlink ref="K42" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5381B954-6617-4930-A5BC-415052E36793}"/>
-    <hyperlink ref="L41" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCF513E3-779E-478B-83FF-5E58604AFA16}"/>
-    <hyperlink ref="H42" r:id="rId64" xr:uid="{B822FBF8-7DC0-48FD-BCB2-A7B3FC9F1F52}"/>
-    <hyperlink ref="F42" r:id="rId65" xr:uid="{3D8C3557-F6D2-4A3A-BE13-D18D5DD3FB6A}"/>
-    <hyperlink ref="K35" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
-    <hyperlink ref="K90" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
-    <hyperlink ref="L92" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
-    <hyperlink ref="K92" r:id="rId69" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
-    <hyperlink ref="K91" r:id="rId70" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
-    <hyperlink ref="K94" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
-    <hyperlink ref="K93" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
-    <hyperlink ref="M75" r:id="rId73" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
-    <hyperlink ref="K75" r:id="rId74" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
-    <hyperlink ref="K76" r:id="rId75" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
-    <hyperlink ref="K79" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
-    <hyperlink ref="K78" r:id="rId77" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
-    <hyperlink ref="K77" r:id="rId78" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
-    <hyperlink ref="K28" r:id="rId79" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
-    <hyperlink ref="K29" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
-    <hyperlink ref="K30" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
-    <hyperlink ref="K31" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
-    <hyperlink ref="K32" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
-    <hyperlink ref="K33" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
-    <hyperlink ref="K15" r:id="rId85" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
-    <hyperlink ref="K16" r:id="rId86" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
-    <hyperlink ref="K85" r:id="rId87" xr:uid="{27E4829F-4D6C-4205-815B-E30709FE0551}"/>
-    <hyperlink ref="K86" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0C3D8311-8886-4EE9-8346-59E9A2212818}"/>
-    <hyperlink ref="K87" r:id="rId89" xr:uid="{6CB3210A-C53D-42FD-ADF5-DB6CD788DE2A}"/>
-    <hyperlink ref="K88" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B28112-49B9-4A12-A9FC-6929194008BD}"/>
-    <hyperlink ref="M88" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B81923-B3F5-4D27-8C90-D607D23DCA1E}"/>
-    <hyperlink ref="K80" r:id="rId92" xr:uid="{48F768EA-5F6B-4721-BE10-3381CFFF7617}"/>
-    <hyperlink ref="K81" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB3AA346-9023-4C65-A326-45854C985AC3}"/>
-    <hyperlink ref="K82" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3E9D42C5-EF64-4F37-BDFD-EF645728FB63}"/>
-    <hyperlink ref="K83" r:id="rId95" xr:uid="{D140917F-D470-4295-AC16-135E62B59912}"/>
-    <hyperlink ref="K14" r:id="rId96" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
-    <hyperlink ref="K13" r:id="rId97" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
-    <hyperlink ref="K5" r:id="rId98" xr:uid="{09752CE0-E1D3-4BF8-9D97-A49E8D002FC7}"/>
-    <hyperlink ref="K6" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{63C98BDE-FB8F-4FF9-A55C-03BAC1A02C63}"/>
-    <hyperlink ref="K7" r:id="rId100" xr:uid="{2380B890-0042-45CC-BEA4-783EA390EBF7}"/>
-    <hyperlink ref="K8" r:id="rId101" xr:uid="{AD077303-0EE9-4440-AAE6-BB84613C92BA}"/>
-    <hyperlink ref="K9" r:id="rId102" xr:uid="{8F9EE820-D8AA-4884-BB24-82C0C5D3CE2E}"/>
-    <hyperlink ref="K10" r:id="rId103" xr:uid="{22252FF4-27CC-40A3-8165-FA7B5CD19CDC}"/>
-    <hyperlink ref="K11" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96212E21-386F-4FCF-9A25-36D60D8078DF}"/>
-    <hyperlink ref="K12" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D9725C5-E9A1-4F23-B790-C7DC385208E5}"/>
-    <hyperlink ref="K66" r:id="rId106" xr:uid="{11A9B442-D6DF-429E-912B-50308BFE8E3D}"/>
-    <hyperlink ref="K67" r:id="rId107" xr:uid="{9A607AD9-733B-410B-B2B3-EFB415EA956D}"/>
-    <hyperlink ref="K68" r:id="rId108" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB732E30-93A4-4501-9799-59B7A6245041}"/>
-    <hyperlink ref="K69" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27EBDD53-9DEC-466F-B000-1FDCDA134FDC}"/>
-    <hyperlink ref="K71" r:id="rId110" xr:uid="{AA5F7287-2A04-4E9B-90FB-8E7A60BA0E9F}"/>
-    <hyperlink ref="K72" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4EF3173-817E-4A91-848F-7D2C11831473}"/>
-    <hyperlink ref="K73" r:id="rId112" xr:uid="{6284D82A-10EF-49D7-940E-00897AA75BB5}"/>
-    <hyperlink ref="K74" r:id="rId113" xr:uid="{DBEE44C4-CCCA-45E8-A66C-BF94EC30E034}"/>
+    <hyperlink ref="K22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="K46" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="K55" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K56" r:id="rId4" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K57" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K58" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K93" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
+    <hyperlink ref="K98" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K79" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K59" r:id="rId10" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
+    <hyperlink ref="K60" r:id="rId11" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
+    <hyperlink ref="K61" r:id="rId12" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
+    <hyperlink ref="K62" r:id="rId13" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
+    <hyperlink ref="K63" r:id="rId14" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
+    <hyperlink ref="M63" r:id="rId15" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
+    <hyperlink ref="K64" r:id="rId16" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
+    <hyperlink ref="K65" r:id="rId17" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
+    <hyperlink ref="K66" r:id="rId18" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
+    <hyperlink ref="K67" r:id="rId19" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
+    <hyperlink ref="M67" r:id="rId20" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
+    <hyperlink ref="O67" r:id="rId21" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
+    <hyperlink ref="K68" r:id="rId22" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
+    <hyperlink ref="M68" r:id="rId23" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
+    <hyperlink ref="K69" r:id="rId24" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
+    <hyperlink ref="M69" r:id="rId25" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
+    <hyperlink ref="K70" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
+    <hyperlink ref="F69" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
+    <hyperlink ref="F70:F71" r:id="rId28" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
+    <hyperlink ref="M70" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
+    <hyperlink ref="M71" r:id="rId30" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
+    <hyperlink ref="K71" r:id="rId31" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
+    <hyperlink ref="K72" r:id="rId32" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
+    <hyperlink ref="F72" r:id="rId33" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
+    <hyperlink ref="F73" r:id="rId34" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
+    <hyperlink ref="K73" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
+    <hyperlink ref="K74" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
+    <hyperlink ref="H74" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
+    <hyperlink ref="K33" r:id="rId38" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
+    <hyperlink ref="K34" r:id="rId39" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
+    <hyperlink ref="K35" r:id="rId40" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
+    <hyperlink ref="K48" r:id="rId41" xr:uid="{C61A9D98-CECD-4B5E-B96E-4289BBC0D262}"/>
+    <hyperlink ref="K49" r:id="rId42" xr:uid="{EB7CB685-E0C1-4945-9E14-9CA8A1A342EC}"/>
+    <hyperlink ref="K50" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F065AADE-42A0-4C3C-B801-4BE9B5FA9BEB}"/>
+    <hyperlink ref="K51" r:id="rId44" xr:uid="{819ABFBD-4499-4FE6-9CDB-0A9FE7A07280}"/>
+    <hyperlink ref="K52" r:id="rId45" xr:uid="{48E832D6-CC6D-436E-BC8A-74B5489EE9B1}"/>
+    <hyperlink ref="K53" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8CE24E7-04FD-4348-88B3-8498A10C097C}"/>
+    <hyperlink ref="K54" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5381B954-6617-4930-A5BC-415052E36793}"/>
+    <hyperlink ref="L53" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCF513E3-779E-478B-83FF-5E58604AFA16}"/>
+    <hyperlink ref="H54" r:id="rId49" xr:uid="{B822FBF8-7DC0-48FD-BCB2-A7B3FC9F1F52}"/>
+    <hyperlink ref="F54" r:id="rId50" xr:uid="{3D8C3557-F6D2-4A3A-BE13-D18D5DD3FB6A}"/>
+    <hyperlink ref="K47" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
+    <hyperlink ref="K99" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
+    <hyperlink ref="L101" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
+    <hyperlink ref="K101" r:id="rId54" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
+    <hyperlink ref="K100" r:id="rId55" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
+    <hyperlink ref="K103" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
+    <hyperlink ref="K102" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
+    <hyperlink ref="M84" r:id="rId58" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
+    <hyperlink ref="K84" r:id="rId59" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
+    <hyperlink ref="K85" r:id="rId60" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
+    <hyperlink ref="K88" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
+    <hyperlink ref="K87" r:id="rId62" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
+    <hyperlink ref="K86" r:id="rId63" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
+    <hyperlink ref="K40" r:id="rId64" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
+    <hyperlink ref="K41" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
+    <hyperlink ref="K42" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
+    <hyperlink ref="K43" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
+    <hyperlink ref="K44" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
+    <hyperlink ref="K45" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
+    <hyperlink ref="K20" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
+    <hyperlink ref="K21" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
+    <hyperlink ref="K94" r:id="rId72" xr:uid="{27E4829F-4D6C-4205-815B-E30709FE0551}"/>
+    <hyperlink ref="K95" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0C3D8311-8886-4EE9-8346-59E9A2212818}"/>
+    <hyperlink ref="K96" r:id="rId74" xr:uid="{6CB3210A-C53D-42FD-ADF5-DB6CD788DE2A}"/>
+    <hyperlink ref="K97" r:id="rId75" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B28112-49B9-4A12-A9FC-6929194008BD}"/>
+    <hyperlink ref="M97" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B81923-B3F5-4D27-8C90-D607D23DCA1E}"/>
+    <hyperlink ref="K89" r:id="rId77" xr:uid="{48F768EA-5F6B-4721-BE10-3381CFFF7617}"/>
+    <hyperlink ref="K90" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB3AA346-9023-4C65-A326-45854C985AC3}"/>
+    <hyperlink ref="K91" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3E9D42C5-EF64-4F37-BDFD-EF645728FB63}"/>
+    <hyperlink ref="K92" r:id="rId80" xr:uid="{D140917F-D470-4295-AC16-135E62B59912}"/>
+    <hyperlink ref="K19" r:id="rId81" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
+    <hyperlink ref="K18" r:id="rId82" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
+    <hyperlink ref="K10" r:id="rId83" xr:uid="{09752CE0-E1D3-4BF8-9D97-A49E8D002FC7}"/>
+    <hyperlink ref="K11" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{63C98BDE-FB8F-4FF9-A55C-03BAC1A02C63}"/>
+    <hyperlink ref="K12" r:id="rId85" xr:uid="{2380B890-0042-45CC-BEA4-783EA390EBF7}"/>
+    <hyperlink ref="K13" r:id="rId86" xr:uid="{AD077303-0EE9-4440-AAE6-BB84613C92BA}"/>
+    <hyperlink ref="K14" r:id="rId87" xr:uid="{8F9EE820-D8AA-4884-BB24-82C0C5D3CE2E}"/>
+    <hyperlink ref="K15" r:id="rId88" xr:uid="{22252FF4-27CC-40A3-8165-FA7B5CD19CDC}"/>
+    <hyperlink ref="K16" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96212E21-386F-4FCF-9A25-36D60D8078DF}"/>
+    <hyperlink ref="K17" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D9725C5-E9A1-4F23-B790-C7DC385208E5}"/>
+    <hyperlink ref="K75" r:id="rId91" xr:uid="{11A9B442-D6DF-429E-912B-50308BFE8E3D}"/>
+    <hyperlink ref="K76" r:id="rId92" xr:uid="{9A607AD9-733B-410B-B2B3-EFB415EA956D}"/>
+    <hyperlink ref="K77" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB732E30-93A4-4501-9799-59B7A6245041}"/>
+    <hyperlink ref="K78" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27EBDD53-9DEC-466F-B000-1FDCDA134FDC}"/>
+    <hyperlink ref="K80" r:id="rId95" xr:uid="{AA5F7287-2A04-4E9B-90FB-8E7A60BA0E9F}"/>
+    <hyperlink ref="K81" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4EF3173-817E-4A91-848F-7D2C11831473}"/>
+    <hyperlink ref="K82" r:id="rId97" xr:uid="{6284D82A-10EF-49D7-940E-00897AA75BB5}"/>
+    <hyperlink ref="K83" r:id="rId98" xr:uid="{DBEE44C4-CCCA-45E8-A66C-BF94EC30E034}"/>
+    <hyperlink ref="K2" r:id="rId99" xr:uid="{8B065BCD-2734-4507-991F-BC964964CB18}"/>
+    <hyperlink ref="K4" r:id="rId100" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg/960px-Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FEA8008D-9F5B-441C-84F7-155CCAB3D5BF}"/>
+    <hyperlink ref="K3" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg/960px-Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5621AFEB-68F3-4B18-95B3-0E55B258835D}"/>
+    <hyperlink ref="K5" r:id="rId102" xr:uid="{D324CD68-7A4C-4682-B6C0-EB2DEBD82B3E}"/>
+    <hyperlink ref="K6" r:id="rId103" xr:uid="{124DD613-D9C5-45A6-9C6E-5A94A110D732}"/>
+    <hyperlink ref="K7" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5CFEE07F-3AE1-4E17-8717-F5A1FACB33B9}"/>
+    <hyperlink ref="K8" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E585144F-91F4-4BE2-B00E-5A17CFAAEE37}"/>
+    <hyperlink ref="K9" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5286F62C-4DD5-41F9-8A33-916D65A4CBCB}"/>
+    <hyperlink ref="K32" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
+    <hyperlink ref="K31" r:id="rId108" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
+    <hyperlink ref="K30" r:id="rId109" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
+    <hyperlink ref="F29" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
+    <hyperlink ref="M29" r:id="rId111" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
+    <hyperlink ref="K29" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
+    <hyperlink ref="K28" r:id="rId113" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
+    <hyperlink ref="K23" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA50FD28-25AB-4C16-B704-4C1D4E291FC6}"/>
+    <hyperlink ref="K24" r:id="rId115" xr:uid="{AB5A3565-A8C2-4EB1-BF08-09469169F49B}"/>
+    <hyperlink ref="K25" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg/960px-Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{16AB1331-79AB-4AD1-82BF-411A6047FFC8}"/>
+    <hyperlink ref="K26" r:id="rId117" xr:uid="{8C66FE78-AD95-48B9-AFFB-A7A961701AB6}"/>
+    <hyperlink ref="K27" r:id="rId118" xr:uid="{BA7D0C74-4085-47D1-B949-A4D37E1B604C}"/>
+    <hyperlink ref="K36" r:id="rId119" xr:uid="{138404FE-5360-483C-9B6C-779679C072A6}"/>
+    <hyperlink ref="K37" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D549C045-BC59-46A9-BA82-994248896840}"/>
+    <hyperlink ref="K38" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD01D10D-9209-4700-8601-3904D1E7F113}"/>
+    <hyperlink ref="K39" r:id="rId122" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FA474B3-EF83-44FF-82A9-671D8D2F0D05}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{925B9584-512E-4C34-8A73-A9EACF7C6F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A07B39-EEBB-4303-B4AC-457EFB9314C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1121" uniqueCount="658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="647">
   <si>
     <t>Patronyme artiste</t>
   </si>
@@ -191,6 +191,9 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG/1280px-Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
+    <t>Albâtre</t>
+  </si>
+  <si>
     <t>Antonio</t>
   </si>
   <si>
@@ -227,9 +230,6 @@
     <t>Bologne</t>
   </si>
   <si>
-    <t>Chiesa di Santa Maria della Vita</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -263,9 +263,6 @@
     <t>Ospedale degli Innocenti</t>
   </si>
   <si>
-    <t>"Tondi des Innocents (terre cuite vernissée)"</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -296,9 +293,6 @@
     <t>Baptistère de Florence</t>
   </si>
   <si>
-    <t>"Tombeau du pape (anti-pape) Jean XXIII (avec Donatello)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Grabmaljohannes13.jpg/1280px-Grabmaljohannes13.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -320,9 +314,6 @@
     <t>Tempio Malatestiano</t>
   </si>
   <si>
-    <t>"Allégorie (reliefs du Tempio Malatestiano)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg/1280px-Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -341,9 +332,6 @@
     <t>Musée du Louvre</t>
   </si>
   <si>
-    <t>"Saint Christophe (bois polychrome et doré)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG/1280px-Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -359,9 +347,6 @@
     <t>1475-1480</t>
   </si>
   <si>
-    <t>"Orphée ou Apollon (statuette en bronze)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7f/Bertoldo_di_giovanni%2C_orfeo_o_apollo%2C_1475-80_01.JPG/1280px-Bertoldo_di_giovanni%2C_orfeo_o_apollo%2C_1475-80_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -452,9 +437,6 @@
     <t>Chiesa di San Miniato al Monte</t>
   </si>
   <si>
-    <t>"Tombeau du cardinal de Portugal (Jacques de Lusitanie)"</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG/1280px-Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
@@ -548,9 +530,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>236 cm</t>
-  </si>
-  <si>
     <t>1423-1425</t>
   </si>
   <si>
@@ -611,9 +590,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>340 cm</t>
-  </si>
-  <si>
     <t>390 cm</t>
   </si>
   <si>
@@ -647,9 +623,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>520 cm</t>
   </si>
   <si>
@@ -734,9 +707,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5c/St_Stephen_Ghiberti_Orsanmichele.jpg/960px-St_Stephen_Ghiberti_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>242 cm</t>
-  </si>
-  <si>
     <t>1417-1427</t>
   </si>
   <si>
@@ -785,9 +755,6 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg</t>
   </si>
   <si>
-    <t>126 cm</t>
-  </si>
-  <si>
     <t>1467-1483</t>
   </si>
   <si>
@@ -809,9 +776,6 @@
     <t>Groupe Ronde-bosse</t>
   </si>
   <si>
-    <t>230 cm</t>
-  </si>
-  <si>
     <t>1480-1488</t>
   </si>
   <si>
@@ -830,9 +794,6 @@
     <t>Statue équestre</t>
   </si>
   <si>
-    <t>395 cm</t>
-  </si>
-  <si>
     <t>vers 1470</t>
   </si>
   <si>
@@ -854,9 +815,6 @@
     <t>Statue de fontaine</t>
   </si>
   <si>
-    <t>67 cm</t>
-  </si>
-  <si>
     <t>1475</t>
   </si>
   <si>
@@ -899,9 +857,6 @@
     <t>vers 1475</t>
   </si>
   <si>
-    <t>Buste de Giuliano de' Medici</t>
-  </si>
-  <si>
     <t>Busto di Giuliano de' Medici</t>
   </si>
   <si>
@@ -911,9 +866,6 @@
     <t>Terre cuite peinte</t>
   </si>
   <si>
-    <t>61 cm</t>
-  </si>
-  <si>
     <t>1478-1480</t>
   </si>
   <si>
@@ -932,24 +884,12 @@
     <t>Argent</t>
   </si>
   <si>
-    <t>31 cm</t>
-  </si>
-  <si>
-    <t>42 cm</t>
-  </si>
-  <si>
     <t>La Cantoria</t>
   </si>
   <si>
     <t>Cantoria</t>
   </si>
   <si>
-    <t>328 cm</t>
-  </si>
-  <si>
-    <t>560 cm</t>
-  </si>
-  <si>
     <t>1442-1444</t>
   </si>
   <si>
@@ -977,24 +917,9 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>1454-1455</t>
-  </si>
-  <si>
     <t>Basilique San Miniato al Monte</t>
   </si>
   <si>
-    <t>Tombeau du cardinal du Portugal</t>
-  </si>
-  <si>
-    <t>Monumento funebre del cardinale del Portogallo</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/A_Rossellino_Tumba_del_Cardenal_de_Portugal_San_Miniato_Florencia.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Marbre et terre cuite</t>
-  </si>
-  <si>
     <t>Les Quatre Vertus Cardinales</t>
   </si>
   <si>
@@ -1022,24 +947,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Spedale degli Innocenti</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a6/Spedale_innocenti%2C_veduta_01.JPG/1280px-Spedale_innocenti%2C_veduta_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bc/Spedale-degli-innocenti-tondi-eingang-rechts.jpg/1280px-Spedale-degli-innocenti-tondi-eingang-rechts.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Médaillons des Enfants Trouvés</t>
-  </si>
-  <si>
-    <t>Putti degli Innocenti</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>1450 environ</t>
   </si>
   <si>
@@ -1070,9 +977,6 @@
     <t>Marbre rouge de Salzbourg</t>
   </si>
   <si>
-    <t>v. 1495</t>
-  </si>
-  <si>
     <t>Église des Dominicains</t>
   </si>
   <si>
@@ -1103,15 +1007,9 @@
     <t>Pierre calcaire</t>
   </si>
   <si>
-    <t>v. 1495-1500</t>
-  </si>
-  <si>
     <t>Musée National Germanique</t>
   </si>
   <si>
-    <t>Vierge à l'Enfant (Vierge de Nuremberg)</t>
-  </si>
-  <si>
     <t>Nürnberger Madonna</t>
   </si>
   <si>
@@ -1181,9 +1079,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Environ 250 cm</t>
-  </si>
-  <si>
     <t>1496</t>
   </si>
   <si>
@@ -1205,9 +1100,6 @@
     <t>Bois de tilleul polychrome</t>
   </si>
   <si>
-    <t>Environ 160 cm</t>
-  </si>
-  <si>
     <t>1499</t>
   </si>
   <si>
@@ -1226,9 +1118,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/BambergDom-GrabHeinrichKunigunde.JPG/1280px-BambergDom-GrabHeinrichKunigunde.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Monumental</t>
-  </si>
-  <si>
     <t>Cleveland</t>
   </si>
   <si>
@@ -1244,18 +1133,9 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Alabâtre</t>
-  </si>
-  <si>
-    <t>38 cm</t>
-  </si>
-  <si>
     <t>Santa Maria della Scala (originaux)</t>
   </si>
   <si>
-    <t>La Fonte Gaia</t>
-  </si>
-  <si>
     <t>Fonte Gaia</t>
   </si>
   <si>
@@ -1292,9 +1172,6 @@
     <t>Portail central</t>
   </si>
   <si>
-    <t>Portail de San Petronio (Porta Magna)</t>
-  </si>
-  <si>
     <t>Porta Magna</t>
   </si>
   <si>
@@ -1322,12 +1199,6 @@
     <t>Relief</t>
   </si>
   <si>
-    <t>99 cm environ</t>
-  </si>
-  <si>
-    <t>92 cm environ</t>
-  </si>
-  <si>
     <t>Basilique San Frediano</t>
   </si>
   <si>
@@ -1364,9 +1235,6 @@
     <t>Ritratto di Marietta Strozzi</t>
   </si>
   <si>
-    <t>52.5 cm</t>
-  </si>
-  <si>
     <t>1450-1455</t>
   </si>
   <si>
@@ -1379,9 +1247,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG/960px-Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>environ 600 cm</t>
-  </si>
-  <si>
     <t>1461</t>
   </si>
   <si>
@@ -1394,24 +1259,9 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>1455-1460 environ</t>
-  </si>
-  <si>
-    <t>Saint Jean-Baptiste enfant (Buste)</t>
-  </si>
-  <si>
-    <t>San Giovannino (Busto)</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>50 cm</t>
-  </si>
-  <si>
-    <t>Nef</t>
-  </si>
-  <si>
     <t>Tombeau de Leonardo Bruni</t>
   </si>
   <si>
@@ -1421,9 +1271,6 @@
     <t>Marbre scuplté et polychromie</t>
   </si>
   <si>
-    <t>610 cm</t>
-  </si>
-  <si>
     <t>3</t>
   </si>
   <si>
@@ -1436,12 +1283,6 @@
     <t>Palazzo della Fraternita dei Laici</t>
   </si>
   <si>
-    <t>Façade</t>
-  </si>
-  <si>
-    <t>Vierge de miséricorde et bas-reliefs de la façade</t>
-  </si>
-  <si>
     <t>Madonna della Misericordia</t>
   </si>
   <si>
@@ -1454,30 +1295,6 @@
     <t>Marbre et pierre</t>
   </si>
   <si>
-    <t>1447</t>
-  </si>
-  <si>
-    <t>Palazzo Publico / Badia Fiorentina</t>
-  </si>
-  <si>
-    <t>Portail</t>
-  </si>
-  <si>
-    <t>Portail de la Badia Fiorentina</t>
-  </si>
-  <si>
-    <t>Portale de la Badia Fiorentina</t>
-  </si>
-  <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Badia_fiorentina%2C_portale%2C_01.JPG/960px-Badia_fiorentina%2C_portale%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
-    <t>Portail architectural</t>
-  </si>
-  <si>
-    <t>Marbre sculpté</t>
-  </si>
-  <si>
     <t>1451-1452</t>
   </si>
   <si>
@@ -1532,9 +1349,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>v. 1470</t>
-  </si>
-  <si>
     <t>New York</t>
   </si>
   <si>
@@ -1562,9 +1376,6 @@
     <t>Buste portrait</t>
   </si>
   <si>
-    <t>51 cm</t>
-  </si>
-  <si>
     <t>1454</t>
   </si>
   <si>
@@ -1577,9 +1388,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>52 cm</t>
-  </si>
-  <si>
     <t>1456</t>
   </si>
   <si>
@@ -1592,15 +1400,9 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ef/A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg/1280px-A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>49 cm</t>
-  </si>
-  <si>
     <t>1464</t>
   </si>
   <si>
-    <t>Chapelle Giugni</t>
-  </si>
-  <si>
     <t>Tombeau de Bernardo Giugni</t>
   </si>
   <si>
@@ -1634,18 +1436,12 @@
     <t>Statue</t>
   </si>
   <si>
-    <t>135 cm</t>
-  </si>
-  <si>
     <t>1470-1475</t>
   </si>
   <si>
     <t>Faenza</t>
   </si>
   <si>
-    <t>Cathédrale de Faenza</t>
-  </si>
-  <si>
     <t>Tombe de Saint Savin</t>
   </si>
   <si>
@@ -1667,9 +1463,6 @@
     <t>Buste de portrait</t>
   </si>
   <si>
-    <t>around 43 cm</t>
-  </si>
-  <si>
     <t>1471-1474</t>
   </si>
   <si>
@@ -1682,9 +1475,6 @@
     <t>Arc de triomphe d'Alphonse d'Aragon</t>
   </si>
   <si>
-    <t>Le Triomphe d'Alphonse d'Aragon (Reliefs)</t>
-  </si>
-  <si>
     <t>Il Trionfo di Alfonso d'Aragona</t>
   </si>
   <si>
@@ -1694,30 +1484,15 @@
     <t>Relief monumental architectural</t>
   </si>
   <si>
-    <t>around 150 cm</t>
-  </si>
-  <si>
-    <t>v. 1475</t>
-  </si>
-  <si>
     <t>Département des Sculptures</t>
   </si>
   <si>
-    <t>Buste de Marie de Sicile</t>
-  </si>
-  <si>
     <t>Busto di Maria di Sicilia</t>
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>around 44 cm</t>
-  </si>
-  <si>
-    <t>v. 1474-1475</t>
-  </si>
-  <si>
     <t>Vienne</t>
   </si>
   <si>
@@ -1739,12 +1514,6 @@
     <t>Marbre polychrome</t>
   </si>
   <si>
-    <t>around 40 cm</t>
-  </si>
-  <si>
-    <t>Compianto sul Cristo morto (groupe en terre cuite polychrome)</t>
-  </si>
-  <si>
     <t>Compianto sul Cristo morto</t>
   </si>
   <si>
@@ -1757,9 +1526,6 @@
     <t>Ferrare</t>
   </si>
   <si>
-    <t>Église Gesù</t>
-  </si>
-  <si>
     <t>Déploration sur le Christ mort</t>
   </si>
   <si>
@@ -1775,9 +1541,6 @@
     <t>Crypta</t>
   </si>
   <si>
-    <t>L'Adoration des bergers (Crèche)</t>
-  </si>
-  <si>
     <t>Presepio (Adorazione dei pastori)</t>
   </si>
   <si>
@@ -1796,9 +1559,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg/1280px-GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>David avec la tête de Goliath (bronze)</t>
-  </si>
-  <si>
     <t>David con la testa di Golia</t>
   </si>
   <si>
@@ -1817,9 +1577,6 @@
     <t>Marbre et stuc</t>
   </si>
   <si>
-    <t>v. 1490</t>
-  </si>
-  <si>
     <t>Washington</t>
   </si>
   <si>
@@ -1934,18 +1691,12 @@
     <t>Terre cuite</t>
   </si>
   <si>
-    <t>51</t>
-  </si>
-  <si>
     <t>1457-1459</t>
   </si>
   <si>
     <t>Musée de l'Œuvre du Duomo</t>
   </si>
   <si>
-    <t>Croix de Saint Jean (Reliquaire en collaboration)</t>
-  </si>
-  <si>
     <t>Croce del Tesoro di San Giovanni</t>
   </si>
   <si>
@@ -1955,9 +1706,6 @@
     <t>Argent, émaux et bois</t>
   </si>
   <si>
-    <t>c. 1480</t>
-  </si>
-  <si>
     <t>Hercule au repos</t>
   </si>
   <si>
@@ -2007,6 +1755,225 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Croix de Saint Jean </t>
+  </si>
+  <si>
+    <t>Objet liturgique</t>
+  </si>
+  <si>
+    <t>"Tondi des Innocents"</t>
+  </si>
+  <si>
+    <t>Elément architectural</t>
+  </si>
+  <si>
+    <t>"Allégorie "</t>
+  </si>
+  <si>
+    <t>Ensemble architectural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'Adoration des bergers </t>
+  </si>
+  <si>
+    <t>Le Triomphe d'Alphonse d'Aragon</t>
+  </si>
+  <si>
+    <t>"Orphée ou Apollon "</t>
+  </si>
+  <si>
+    <t>"Saint Christophe"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David avec la tête de Goliath </t>
+  </si>
+  <si>
+    <t>Badia Fiorentina</t>
+  </si>
+  <si>
+    <t>Cathédrale Saint-Pierre Apôtre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Saint Jean-Baptiste enfant </t>
+  </si>
+  <si>
+    <t>1460 environ</t>
+  </si>
+  <si>
+    <t>395 (statue) 400 (socle)</t>
+  </si>
+  <si>
+    <t>Buste de Giuliano de Medici</t>
+  </si>
+  <si>
+    <t>Haut-relief intégrant des éléments de ronde-bosse</t>
+  </si>
+  <si>
+    <t>Église du Gesù</t>
+  </si>
+  <si>
+    <t>Eglise Santa Maria della Vita</t>
+  </si>
+  <si>
+    <t>Groupe en ronde-bosse de sept statues</t>
+  </si>
+  <si>
+    <t>Fontaine de la Joie</t>
+  </si>
+  <si>
+    <t>Monument sculpté en haut-relief</t>
+  </si>
+  <si>
+    <t>Portail de San Petronio  dit Porta Magna</t>
+  </si>
+  <si>
+    <t>Monument mixte en haut-relief et ronde-bosse</t>
+  </si>
+  <si>
+    <t>Mobilier liturgique</t>
+  </si>
+  <si>
+    <t>Edicule monumental</t>
+  </si>
+  <si>
+    <t>Monument funéraire en bas-relief</t>
+  </si>
+  <si>
+    <t>Séville</t>
+  </si>
+  <si>
+    <t>Musée des Beaux-Arts</t>
+  </si>
+  <si>
+    <t>Vierge au Coussin</t>
+  </si>
+  <si>
+    <t>Madonna del Cuscino</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Autel des Médicis</t>
+  </si>
+  <si>
+    <t>Altare Medici</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Prato</t>
+  </si>
+  <si>
+    <t>Cathédrale Saint-Étienne</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/Duomo_Prato_01.jpg/1280px-Duomo_Prato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Lunette de la Vierge Marie et l'Enfant Jésus entourés de saint Étienne et de saint Laurent.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>1490-1495</t>
+  </si>
+  <si>
+    <t>La Verna</t>
+  </si>
+  <si>
+    <t>Sanctuaire de la Verna</t>
+  </si>
+  <si>
+    <t>L'Annonciation</t>
+  </si>
+  <si>
+    <t>Annunciazione</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>Cathédrale Saints-Donat-et-Pierre</t>
+  </si>
+  <si>
+    <t>Retable de la Trinité</t>
+  </si>
+  <si>
+    <t>Polittico de la Trinità</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t> Museo dell’Opera del Duomo</t>
+  </si>
+  <si>
+    <t>Lunette avec la Vierge à l'Enfant et anges</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>10 panneaux en bas-relief</t>
+  </si>
+  <si>
+    <t>Médaillons en haut-relief</t>
+  </si>
+  <si>
+    <t>Vierge à la pomme</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>96 bas-reliefs</t>
+  </si>
+  <si>
+    <t>110 à 120</t>
+  </si>
+  <si>
+    <t>65 à 75</t>
+  </si>
+  <si>
+    <t>340 (statue) 800 (socle)</t>
+  </si>
+  <si>
+    <t>Buste de jeune femme</t>
+  </si>
+  <si>
+    <t>Monument funéraire avec 17 ronde-bosses</t>
+  </si>
+  <si>
+    <t>Groupe de 8 ronde-bosses</t>
+  </si>
+  <si>
+    <t>Groupe de 5 ronde-bosses</t>
+  </si>
+  <si>
+    <t>Lunette de la Vierge de miséricorde</t>
+  </si>
+  <si>
+    <t>Cathédrale de Wloclaweck</t>
+  </si>
+  <si>
+    <t>1495-1500</t>
+  </si>
+  <si>
+    <t>1474-1475</t>
+  </si>
+  <si>
+    <t>"Tombeau du pape  Jean XXIII "</t>
   </si>
 </sst>
 </file>
@@ -2059,13 +2026,25 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2371,24 +2350,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V103"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:V108"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="43.140625" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" customWidth="1"/>
-    <col min="9" max="9" width="36.28515625" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
+    <col min="9" max="9" width="47" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="3" customWidth="1"/>
+    <col min="15" max="15" width="16.28515625" customWidth="1"/>
     <col min="16" max="16" width="1" customWidth="1"/>
     <col min="17" max="17" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="19" max="21" width="9.140625" style="3"/>
-    <col min="22" max="22" width="9.140625" style="2"/>
+    <col min="19" max="22" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
@@ -2412,7 +2393,7 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="3" t="s">
         <v>9</v>
       </c>
       <c r="L1" t="s">
@@ -2436,27 +2417,27 @@
       <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="U1" s="2" t="s">
         <v>19</v>
       </c>
       <c r="V1" s="2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D2" t="s">
@@ -2466,420 +2447,495 @@
         <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="J2" t="s">
-        <v>588</v>
-      </c>
-      <c r="K2" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
+      <c r="O2" t="s">
+        <v>148</v>
+      </c>
       <c r="Q2" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="R2" t="s">
         <v>27</v>
       </c>
+      <c r="S2" s="2">
+        <v>29</v>
+      </c>
+      <c r="T2" s="2">
+        <v>13</v>
+      </c>
+      <c r="U2" s="2">
+        <v>12</v>
+      </c>
       <c r="V2" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>21</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>589</v>
+        <v>509</v>
       </c>
       <c r="I3" t="s">
-        <v>590</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>591</v>
+        <v>510</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="O3" t="s">
+        <v>599</v>
       </c>
       <c r="Q3" t="s">
-        <v>592</v>
+        <v>512</v>
       </c>
       <c r="R3" t="s">
-        <v>593</v>
+        <v>513</v>
+      </c>
+      <c r="S3" s="2">
+        <v>400</v>
       </c>
       <c r="V3" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="s">
-        <v>594</v>
+      <c r="C4" s="5">
+        <v>1490</v>
       </c>
       <c r="D4" t="s">
-        <v>595</v>
+        <v>514</v>
       </c>
       <c r="E4" t="s">
-        <v>596</v>
+        <v>515</v>
       </c>
       <c r="I4" t="s">
-        <v>597</v>
+        <v>516</v>
       </c>
       <c r="J4" t="s">
-        <v>598</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>599</v>
+        <v>517</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="O4" t="s">
+        <v>172</v>
       </c>
       <c r="Q4" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="R4" t="s">
-        <v>118</v>
-      </c>
-      <c r="S4" s="3">
+        <v>113</v>
+      </c>
+      <c r="S4" s="2">
         <v>24</v>
       </c>
-      <c r="T4" s="3">
+      <c r="T4" s="2">
         <v>18</v>
       </c>
       <c r="V4" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>21</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="s">
-        <v>534</v>
+      <c r="C5" s="5" t="s">
+        <v>467</v>
       </c>
       <c r="D5" t="s">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="E5" t="s">
-        <v>600</v>
+        <v>519</v>
       </c>
       <c r="I5" t="s">
-        <v>601</v>
+        <v>520</v>
       </c>
       <c r="J5" t="s">
-        <v>570</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>602</v>
+        <v>493</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="O5" t="s">
+        <v>443</v>
       </c>
       <c r="Q5" t="s">
-        <v>505</v>
+        <v>443</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
       </c>
+      <c r="S5" s="2">
+        <v>102</v>
+      </c>
+      <c r="T5" s="2">
+        <v>112</v>
+      </c>
+      <c r="U5" s="2">
+        <v>15</v>
+      </c>
       <c r="V5" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>31</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="E6" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="I6" t="s">
-        <v>603</v>
+        <v>522</v>
       </c>
       <c r="J6" t="s">
-        <v>604</v>
-      </c>
-      <c r="K6" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="K6" s="4" t="s">
         <v>34</v>
+      </c>
+      <c r="O6" t="s">
+        <v>271</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
       </c>
+      <c r="S6" s="2">
+        <v>600</v>
+      </c>
+      <c r="T6" s="2">
+        <v>300</v>
+      </c>
       <c r="V6" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>31</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
-      <c r="C7" t="s">
-        <v>605</v>
+      <c r="C7" s="5" t="s">
+        <v>524</v>
       </c>
       <c r="D7" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="E7" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="I7" t="s">
-        <v>606</v>
+        <v>525</v>
       </c>
       <c r="J7" t="s">
-        <v>607</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>608</v>
+        <v>526</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="O7" t="s">
+        <v>271</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>31</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
-      <c r="C8" t="s">
-        <v>609</v>
+      <c r="C8" s="5" t="s">
+        <v>528</v>
       </c>
       <c r="D8" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="E8" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="I8" t="s">
-        <v>610</v>
+        <v>529</v>
       </c>
       <c r="J8" t="s">
-        <v>611</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>612</v>
+        <v>530</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="O8" t="s">
+        <v>600</v>
       </c>
       <c r="R8" t="s">
-        <v>613</v>
+        <v>532</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
-      <c r="C9" t="s">
-        <v>609</v>
+      <c r="C9" s="5" t="s">
+        <v>528</v>
       </c>
       <c r="D9" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="E9" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="I9" t="s">
-        <v>614</v>
+        <v>533</v>
       </c>
       <c r="J9" t="s">
-        <v>615</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>616</v>
+        <v>534</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="O9" t="s">
+        <v>599</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>35</v>
       </c>
       <c r="B10" t="s">
         <v>36</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D10" t="s">
         <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I10" t="s">
-        <v>506</v>
+        <v>444</v>
       </c>
       <c r="J10" t="s">
-        <v>507</v>
-      </c>
-      <c r="K10" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>40</v>
       </c>
+      <c r="O10" t="s">
+        <v>148</v>
+      </c>
       <c r="Q10" t="s">
-        <v>508</v>
+        <v>446</v>
       </c>
       <c r="R10" t="s">
         <v>30</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>509</v>
+      <c r="S10" s="2">
+        <v>55</v>
+      </c>
+      <c r="T10" s="2">
+        <v>48</v>
+      </c>
+      <c r="U10" s="2">
+        <v>23</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
       <c r="B11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
-        <v>510</v>
+      <c r="C11" s="5" t="s">
+        <v>447</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I11" t="s">
-        <v>511</v>
+        <v>448</v>
       </c>
       <c r="J11" t="s">
-        <v>512</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>513</v>
+        <v>449</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="O11" t="s">
+        <v>148</v>
       </c>
       <c r="Q11" t="s">
-        <v>508</v>
+        <v>446</v>
       </c>
       <c r="R11" t="s">
         <v>30</v>
       </c>
-      <c r="S11" s="3" t="s">
-        <v>514</v>
+      <c r="S11" s="2">
+        <v>54</v>
+      </c>
+      <c r="T11" s="2">
+        <v>56</v>
+      </c>
+      <c r="U11" s="2">
+        <v>24</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" t="s">
         <v>36</v>
       </c>
-      <c r="C12" t="s">
-        <v>515</v>
+      <c r="C12" s="5" t="s">
+        <v>451</v>
       </c>
       <c r="D12" t="s">
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I12" t="s">
-        <v>516</v>
+        <v>452</v>
       </c>
       <c r="J12" t="s">
-        <v>517</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>518</v>
+        <v>453</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="O12" t="s">
+        <v>148</v>
       </c>
       <c r="Q12" t="s">
-        <v>508</v>
+        <v>446</v>
       </c>
       <c r="R12" t="s">
         <v>30</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>519</v>
+      <c r="S12" s="2">
+        <v>37</v>
+      </c>
+      <c r="T12" s="2">
+        <v>40</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>35</v>
       </c>
       <c r="B13" t="s">
         <v>36</v>
       </c>
-      <c r="C13" t="s">
-        <v>520</v>
+      <c r="C13" s="5" t="s">
+        <v>455</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>44</v>
-      </c>
-      <c r="G13" t="s">
-        <v>521</v>
+        <v>585</v>
       </c>
       <c r="I13" t="s">
-        <v>522</v>
+        <v>456</v>
       </c>
       <c r="J13" t="s">
-        <v>523</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>524</v>
+        <v>457</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="O13" t="s">
+        <v>271</v>
       </c>
       <c r="Q13" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="R13" t="s">
         <v>30</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D14" t="s">
@@ -2889,140 +2945,167 @@
         <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>525</v>
+        <v>459</v>
       </c>
       <c r="J14" t="s">
-        <v>526</v>
-      </c>
-      <c r="K14" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="K14" s="4" t="s">
         <v>45</v>
+      </c>
+      <c r="O14" t="s">
+        <v>599</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
       </c>
+      <c r="S14" s="2">
+        <v>254</v>
+      </c>
+      <c r="T14" s="2">
+        <v>179</v>
+      </c>
+      <c r="U14" s="2">
+        <v>140</v>
+      </c>
       <c r="V14" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>41</v>
       </c>
       <c r="B15" t="s">
         <v>42</v>
       </c>
-      <c r="C15" t="s">
-        <v>527</v>
+      <c r="C15" s="5" t="s">
+        <v>461</v>
       </c>
       <c r="D15" t="s">
         <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I15" t="s">
-        <v>528</v>
+        <v>462</v>
       </c>
       <c r="J15" t="s">
-        <v>529</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>530</v>
+        <v>463</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="O15" t="s">
+        <v>148</v>
       </c>
       <c r="Q15" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
       </c>
-      <c r="S15" s="3" t="s">
-        <v>509</v>
+      <c r="S15" s="2">
+        <v>54</v>
+      </c>
+      <c r="T15" s="2">
+        <v>60</v>
       </c>
       <c r="V15" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>41</v>
       </c>
       <c r="B16" t="s">
         <v>42</v>
       </c>
-      <c r="C16" t="s">
-        <v>274</v>
+      <c r="C16" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="D16" t="s">
         <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="I16" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="J16" t="s">
-        <v>216</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>531</v>
+        <v>207</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="O16" t="s">
+        <v>148</v>
       </c>
       <c r="Q16" t="s">
-        <v>532</v>
+        <v>466</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
-      <c r="S16" s="3" t="s">
-        <v>533</v>
+      <c r="S16" s="2">
+        <v>144</v>
       </c>
       <c r="V16" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>41</v>
       </c>
       <c r="B17" t="s">
         <v>42</v>
       </c>
-      <c r="C17" t="s">
-        <v>534</v>
+      <c r="C17" s="5" t="s">
+        <v>467</v>
       </c>
       <c r="D17" t="s">
-        <v>535</v>
+        <v>468</v>
       </c>
       <c r="E17" t="s">
-        <v>536</v>
+        <v>586</v>
       </c>
       <c r="I17" t="s">
-        <v>537</v>
+        <v>469</v>
       </c>
       <c r="J17" t="s">
-        <v>538</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>539</v>
+        <v>470</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="O17" t="s">
+        <v>271</v>
       </c>
       <c r="Q17" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="R17" t="s">
         <v>30</v>
       </c>
+      <c r="S17" s="2">
+        <v>370</v>
+      </c>
       <c r="V17" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>46</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D18" t="s">
@@ -3032,33 +3115,42 @@
         <v>50</v>
       </c>
       <c r="I18" t="s">
-        <v>441</v>
+        <v>398</v>
       </c>
       <c r="J18" t="s">
-        <v>442</v>
-      </c>
-      <c r="K18" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>51</v>
+      </c>
+      <c r="O18" t="s">
+        <v>148</v>
       </c>
       <c r="R18" t="s">
         <v>30</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>443</v>
+      <c r="S18" s="2">
+        <v>53</v>
+      </c>
+      <c r="T18" s="2">
+        <v>48</v>
+      </c>
+      <c r="U18" s="2">
+        <v>24</v>
       </c>
       <c r="V18" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>46</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="s">
-        <v>444</v>
+      <c r="C19" s="5" t="s">
+        <v>400</v>
       </c>
       <c r="D19" t="s">
         <v>38</v>
@@ -3067,266 +3159,335 @@
         <v>44</v>
       </c>
       <c r="I19" t="s">
-        <v>445</v>
+        <v>401</v>
       </c>
       <c r="J19" t="s">
-        <v>446</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>447</v>
+        <v>402</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="O19" t="s">
+        <v>271</v>
       </c>
       <c r="R19" t="s">
         <v>30</v>
       </c>
-      <c r="S19" s="3" t="s">
-        <v>448</v>
+      <c r="S19" s="2">
+        <v>601</v>
+      </c>
+      <c r="T19" s="2">
+        <v>358</v>
       </c>
       <c r="V19" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>46</v>
       </c>
       <c r="B20" t="s">
         <v>47</v>
       </c>
-      <c r="C20" t="s">
-        <v>449</v>
+      <c r="C20" s="5" t="s">
+        <v>404</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="I20" t="s">
-        <v>450</v>
+        <v>405</v>
       </c>
       <c r="J20" t="s">
-        <v>451</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>452</v>
+        <v>406</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="O20" t="s">
+        <v>599</v>
       </c>
       <c r="R20" t="s">
         <v>30</v>
       </c>
-      <c r="V20" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S20" s="2">
+        <v>447</v>
+      </c>
+      <c r="T20" s="2">
+        <v>140</v>
+      </c>
+      <c r="V20" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>46</v>
       </c>
       <c r="B21" t="s">
         <v>47</v>
       </c>
-      <c r="C21" t="s">
-        <v>453</v>
+      <c r="C21" s="5" t="s">
+        <v>588</v>
       </c>
       <c r="D21" t="s">
         <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I21" t="s">
-        <v>454</v>
-      </c>
-      <c r="J21" t="s">
-        <v>455</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>456</v>
+        <v>587</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="O21" t="s">
+        <v>148</v>
       </c>
       <c r="R21" t="s">
         <v>30</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S21" s="2">
+        <v>173</v>
+      </c>
+      <c r="T21" s="2">
+        <v>54</v>
+      </c>
+      <c r="V21" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>643</v>
-      </c>
-      <c r="C22" t="s">
-        <v>53</v>
+        <v>559</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="D22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I22" t="s">
-        <v>56</v>
-      </c>
-      <c r="K22" s="1" t="s">
         <v>57</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O22" t="s">
+        <v>271</v>
       </c>
       <c r="R22" t="s">
         <v>27</v>
       </c>
-      <c r="V22" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S22" s="2">
+        <v>65</v>
+      </c>
+      <c r="T22" s="2">
+        <v>445</v>
+      </c>
+      <c r="U22" s="2">
+        <v>210</v>
+      </c>
+      <c r="V22" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>643</v>
-      </c>
-      <c r="C23" t="s">
-        <v>617</v>
+        <v>559</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>536</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>618</v>
+        <v>537</v>
       </c>
       <c r="I23" t="s">
-        <v>619</v>
+        <v>538</v>
       </c>
       <c r="J23" t="s">
-        <v>620</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>621</v>
+        <v>539</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="O23" t="s">
+        <v>271</v>
       </c>
       <c r="R23" t="s">
         <v>27</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>622</v>
+      <c r="S23" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="T23" s="2">
+        <v>230</v>
+      </c>
+      <c r="U23" s="2">
+        <v>80</v>
       </c>
       <c r="V23" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>643</v>
-      </c>
-      <c r="C24" t="s">
-        <v>107</v>
+        <v>559</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="D24" t="s">
         <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>623</v>
+        <v>542</v>
       </c>
       <c r="I24" t="s">
-        <v>624</v>
+        <v>543</v>
       </c>
       <c r="J24" t="s">
-        <v>625</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>626</v>
+        <v>544</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="O24" t="s">
+        <v>148</v>
       </c>
       <c r="R24" t="s">
         <v>27</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>627</v>
+      <c r="S24" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="T24" s="2">
+        <v>34</v>
+      </c>
+      <c r="U24" s="2">
+        <v>30</v>
       </c>
       <c r="V24" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>643</v>
-      </c>
-      <c r="C25" t="s">
-        <v>628</v>
+        <v>559</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>547</v>
       </c>
       <c r="D25" t="s">
         <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>623</v>
+        <v>542</v>
       </c>
       <c r="I25" t="s">
-        <v>629</v>
+        <v>548</v>
       </c>
       <c r="J25" t="s">
-        <v>630</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>631</v>
+        <v>549</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="O25" t="s">
+        <v>148</v>
       </c>
       <c r="R25" t="s">
-        <v>632</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>633</v>
+        <v>551</v>
+      </c>
+      <c r="S25" s="2">
+        <v>52</v>
+      </c>
+      <c r="T25" s="2">
+        <v>31</v>
+      </c>
+      <c r="U25" s="2">
+        <v>22</v>
       </c>
       <c r="V25" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>643</v>
-      </c>
-      <c r="C26" t="s">
-        <v>634</v>
+        <v>559</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>552</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
       </c>
       <c r="E26" t="s">
-        <v>635</v>
+        <v>553</v>
       </c>
       <c r="I26" t="s">
-        <v>636</v>
+        <v>574</v>
       </c>
       <c r="J26" t="s">
-        <v>637</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>638</v>
+        <v>554</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="O26" t="s">
+        <v>575</v>
       </c>
       <c r="R26" t="s">
-        <v>639</v>
+        <v>556</v>
+      </c>
+      <c r="S26" s="2">
+        <v>193</v>
+      </c>
+      <c r="T26" s="2">
+        <v>88</v>
+      </c>
+      <c r="U26" s="2">
+        <v>50</v>
       </c>
       <c r="V26" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>643</v>
-      </c>
-      <c r="C27" t="s">
-        <v>640</v>
+        <v>559</v>
+      </c>
+      <c r="C27" s="5">
+        <v>1480</v>
       </c>
       <c r="D27" t="s">
         <v>49</v>
@@ -3335,497 +3496,608 @@
         <v>50</v>
       </c>
       <c r="I27" t="s">
-        <v>641</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>642</v>
+        <v>557</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="O27" t="s">
+        <v>148</v>
       </c>
       <c r="R27" t="s">
         <v>27</v>
       </c>
-      <c r="S27" s="3">
+      <c r="S27" s="2">
         <v>40</v>
+      </c>
+      <c r="T27" s="2">
+        <v>16</v>
+      </c>
+      <c r="U27" s="2">
+        <v>15</v>
       </c>
       <c r="V27" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" t="s">
         <v>59</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="D28" t="s">
         <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I28" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J28" t="s">
-        <v>153</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>249</v>
+        <v>147</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="O28" t="s">
+        <v>148</v>
       </c>
       <c r="Q28" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="R28" t="s">
         <v>27</v>
       </c>
-      <c r="S28" s="3" t="s">
-        <v>250</v>
+      <c r="S28" s="2">
+        <v>126</v>
+      </c>
+      <c r="T28" s="2">
+        <v>56</v>
+      </c>
+      <c r="U28" s="2">
+        <v>41</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" t="s">
-        <v>251</v>
+        <v>59</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>240</v>
       </c>
       <c r="D29" t="s">
         <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="I29" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="J29" t="s">
-        <v>253</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>254</v>
+        <v>242</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>243</v>
       </c>
       <c r="L29" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>256</v>
+        <v>245</v>
+      </c>
+      <c r="O29" t="s">
+        <v>148</v>
       </c>
       <c r="Q29" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="R29" t="s">
         <v>27</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>258</v>
+      <c r="S29" s="2">
+        <v>241</v>
+      </c>
+      <c r="T29" s="2">
+        <v>120</v>
+      </c>
+      <c r="U29" s="2">
+        <v>75</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" t="s">
-        <v>259</v>
+        <v>59</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>247</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="I30" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="J30" t="s">
-        <v>262</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>263</v>
+        <v>250</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="O30" t="s">
+        <v>148</v>
       </c>
       <c r="Q30" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="R30" t="s">
         <v>27</v>
       </c>
-      <c r="S30" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="T30" s="3">
+      <c r="S30" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="T30" s="2">
         <v>380</v>
       </c>
+      <c r="U30" s="2">
+        <v>145</v>
+      </c>
       <c r="V30" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" t="s">
-        <v>266</v>
+        <v>59</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>253</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
       </c>
       <c r="E31" t="s">
-        <v>267</v>
+        <v>254</v>
       </c>
       <c r="I31" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="J31" t="s">
-        <v>269</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>270</v>
+        <v>256</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>257</v>
       </c>
       <c r="L31" t="s">
-        <v>271</v>
+        <v>258</v>
+      </c>
+      <c r="O31" t="s">
+        <v>148</v>
       </c>
       <c r="Q31" t="s">
-        <v>272</v>
+        <v>259</v>
       </c>
       <c r="R31" t="s">
         <v>27</v>
       </c>
-      <c r="S31" s="3" t="s">
-        <v>273</v>
+      <c r="S31" s="2">
+        <v>67</v>
+      </c>
+      <c r="T31" s="2">
+        <v>35</v>
+      </c>
+      <c r="U31" s="2">
+        <v>45</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" t="s">
-        <v>274</v>
+        <v>59</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>260</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
       </c>
       <c r="E32" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I32" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="J32" t="s">
-        <v>276</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>277</v>
+        <v>262</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="O32" t="s">
+        <v>148</v>
       </c>
       <c r="Q32" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="R32" t="s">
         <v>30</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>180</v>
+      <c r="S32" s="2">
+        <v>59</v>
+      </c>
+      <c r="T32" s="2">
+        <v>46</v>
+      </c>
+      <c r="U32" s="2">
+        <v>24</v>
       </c>
       <c r="V32" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
       <c r="B33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C33" t="s">
-        <v>279</v>
+        <v>59</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
       </c>
       <c r="E33" t="s">
-        <v>280</v>
+        <v>266</v>
       </c>
       <c r="G33" t="s">
-        <v>281</v>
+        <v>267</v>
       </c>
       <c r="I33" t="s">
-        <v>282</v>
+        <v>268</v>
       </c>
       <c r="J33" t="s">
-        <v>283</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>284</v>
+        <v>269</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="O33" t="s">
+        <v>271</v>
       </c>
       <c r="Q33" t="s">
-        <v>285</v>
+        <v>271</v>
       </c>
       <c r="R33" t="s">
-        <v>286</v>
+        <v>272</v>
+      </c>
+      <c r="S33" s="2">
+        <v>540</v>
+      </c>
+      <c r="T33" s="2">
+        <v>358</v>
       </c>
       <c r="V33" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C34" t="s">
-        <v>287</v>
+        <v>59</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>273</v>
       </c>
       <c r="D34" t="s">
         <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>39</v>
+        <v>542</v>
       </c>
       <c r="I34" t="s">
-        <v>288</v>
+        <v>590</v>
       </c>
       <c r="J34" t="s">
-        <v>289</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>290</v>
+        <v>274</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="O34" t="s">
+        <v>148</v>
       </c>
       <c r="Q34" t="s">
-        <v>278</v>
+        <v>264</v>
       </c>
       <c r="R34" t="s">
-        <v>291</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>292</v>
+        <v>276</v>
+      </c>
+      <c r="S34" s="2">
+        <v>61</v>
+      </c>
+      <c r="T34" s="2">
+        <v>66</v>
+      </c>
+      <c r="U34" s="2">
+        <v>28</v>
       </c>
       <c r="V34" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" t="s">
-        <v>293</v>
+        <v>59</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="D35" t="s">
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="I35" t="s">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="J35" t="s">
-        <v>295</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>296</v>
+        <v>279</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>280</v>
       </c>
       <c r="L35" t="s">
-        <v>297</v>
+        <v>281</v>
+      </c>
+      <c r="O35" t="s">
+        <v>591</v>
       </c>
       <c r="Q35" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="R35" t="s">
-        <v>298</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>300</v>
+        <v>282</v>
+      </c>
+      <c r="S35" s="2">
+        <v>21</v>
+      </c>
+      <c r="T35" s="2">
+        <v>42</v>
+      </c>
+      <c r="U35" s="2">
+        <v>5</v>
       </c>
       <c r="V35" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>61</v>
-      </c>
-      <c r="C36" t="s">
         <v>62</v>
       </c>
+      <c r="C36" s="5" t="s">
+        <v>63</v>
+      </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E36" t="s">
-        <v>64</v>
+        <v>593</v>
       </c>
       <c r="I36" t="s">
-        <v>570</v>
+        <v>520</v>
       </c>
       <c r="J36" t="s">
-        <v>570</v>
-      </c>
-      <c r="K36" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>65</v>
+      </c>
+      <c r="O36" t="s">
+        <v>594</v>
       </c>
       <c r="R36" t="s">
         <v>66</v>
       </c>
-      <c r="S36"/>
-      <c r="T36"/>
-      <c r="U36"/>
+      <c r="S36" s="2">
+        <v>165</v>
+      </c>
+      <c r="T36" s="2">
+        <v>350</v>
+      </c>
+      <c r="U36" s="2">
+        <v>250</v>
+      </c>
       <c r="V36" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>61</v>
-      </c>
-      <c r="C37" t="s">
-        <v>644</v>
+        <v>62</v>
+      </c>
+      <c r="C37" s="5" t="s">
+        <v>560</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>645</v>
+        <v>561</v>
       </c>
       <c r="G37" t="s">
-        <v>646</v>
+        <v>562</v>
       </c>
       <c r="I37" t="s">
-        <v>647</v>
+        <v>563</v>
       </c>
       <c r="J37" t="s">
-        <v>648</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>649</v>
+        <v>564</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="O37" t="s">
+        <v>148</v>
       </c>
       <c r="R37" t="s">
         <v>30</v>
       </c>
-      <c r="S37"/>
-      <c r="T37"/>
-      <c r="U37"/>
+      <c r="S37" s="2">
+        <v>50</v>
+      </c>
+      <c r="T37" s="2">
+        <v>20</v>
+      </c>
+      <c r="U37" s="2">
+        <v>20</v>
+      </c>
       <c r="V37" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" t="s">
-        <v>527</v>
+        <v>62</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>461</v>
       </c>
       <c r="D38" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E38" t="s">
-        <v>650</v>
+        <v>566</v>
       </c>
       <c r="I38" t="s">
-        <v>651</v>
+        <v>567</v>
       </c>
       <c r="J38" t="s">
-        <v>652</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>653</v>
+        <v>568</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="O38" t="s">
+        <v>148</v>
       </c>
       <c r="R38" t="s">
         <v>66</v>
       </c>
-      <c r="S38"/>
-      <c r="T38"/>
-      <c r="U38"/>
+      <c r="S38" s="2">
+        <v>55</v>
+      </c>
+      <c r="T38" s="2">
+        <v>40</v>
+      </c>
+      <c r="U38" s="2">
+        <v>30</v>
+      </c>
       <c r="V38" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" t="s">
-        <v>293</v>
+        <v>62</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>277</v>
       </c>
       <c r="D39" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E39" t="s">
-        <v>654</v>
+        <v>570</v>
       </c>
       <c r="I39" t="s">
-        <v>655</v>
+        <v>571</v>
       </c>
       <c r="J39" t="s">
-        <v>656</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>657</v>
+        <v>572</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="O39" t="s">
+        <v>148</v>
       </c>
       <c r="R39" t="s">
         <v>66</v>
       </c>
-      <c r="S39"/>
-      <c r="T39"/>
-      <c r="U39"/>
+      <c r="S39" s="2">
+        <v>50</v>
+      </c>
+      <c r="T39" s="2">
+        <v>40</v>
+      </c>
+      <c r="U39" s="2">
+        <v>25</v>
+      </c>
       <c r="V39" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>67</v>
       </c>
       <c r="B40" t="s">
         <v>68</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C40" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D40" t="s">
@@ -3835,231 +4107,291 @@
         <v>71</v>
       </c>
       <c r="G40" t="s">
-        <v>405</v>
+        <v>366</v>
       </c>
       <c r="I40" t="s">
-        <v>406</v>
+        <v>595</v>
       </c>
       <c r="J40" t="s">
-        <v>407</v>
-      </c>
-      <c r="K40" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="K40" s="4" t="s">
         <v>72</v>
       </c>
+      <c r="O40" t="s">
+        <v>596</v>
+      </c>
       <c r="Q40" t="s">
-        <v>408</v>
+        <v>368</v>
       </c>
       <c r="R40" t="s">
         <v>30</v>
       </c>
+      <c r="S40" s="2">
+        <v>210</v>
+      </c>
+      <c r="T40" s="2">
+        <v>1020</v>
+      </c>
+      <c r="U40" s="2">
+        <v>610</v>
+      </c>
       <c r="V40" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>67</v>
       </c>
       <c r="B41" t="s">
         <v>68</v>
       </c>
-      <c r="C41" t="s">
-        <v>409</v>
+      <c r="C41" s="5" t="s">
+        <v>369</v>
       </c>
       <c r="D41" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="E41" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="I41" t="s">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="J41" t="s">
-        <v>413</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>414</v>
+        <v>373</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="O41" t="s">
+        <v>271</v>
       </c>
       <c r="Q41" t="s">
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="R41" t="s">
         <v>30</v>
       </c>
+      <c r="S41" s="2">
+        <v>76</v>
+      </c>
+      <c r="T41" s="2">
+        <v>214</v>
+      </c>
+      <c r="U41" s="2">
+        <v>83</v>
+      </c>
       <c r="V41" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>67</v>
       </c>
       <c r="B42" t="s">
         <v>68</v>
       </c>
-      <c r="C42" t="s">
-        <v>416</v>
+      <c r="C42" s="5" t="s">
+        <v>376</v>
       </c>
       <c r="D42" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E42" t="s">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="G42" t="s">
-        <v>418</v>
+        <v>378</v>
       </c>
       <c r="I42" t="s">
-        <v>419</v>
+        <v>597</v>
       </c>
       <c r="J42" t="s">
-        <v>420</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>421</v>
+        <v>379</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="O42" t="s">
+        <v>598</v>
       </c>
       <c r="Q42" t="s">
-        <v>422</v>
+        <v>381</v>
       </c>
       <c r="R42" t="s">
-        <v>423</v>
+        <v>382</v>
+      </c>
+      <c r="S42" s="2">
+        <v>1800</v>
+      </c>
+      <c r="T42" s="2">
+        <v>900</v>
+      </c>
+      <c r="U42" s="2">
+        <v>300</v>
       </c>
       <c r="V42" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>67</v>
       </c>
       <c r="B43" t="s">
         <v>68</v>
       </c>
-      <c r="C43" t="s">
-        <v>424</v>
+      <c r="C43" s="5" t="s">
+        <v>383</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>417</v>
+        <v>377</v>
       </c>
       <c r="G43" t="s">
-        <v>420</v>
+        <v>379</v>
       </c>
       <c r="I43" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="J43" t="s">
-        <v>426</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>427</v>
+        <v>385</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>386</v>
       </c>
       <c r="L43" t="s">
-        <v>420</v>
+        <v>379</v>
+      </c>
+      <c r="O43" t="s">
+        <v>443</v>
       </c>
       <c r="Q43" t="s">
-        <v>428</v>
+        <v>387</v>
       </c>
       <c r="R43" t="s">
-        <v>423</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>430</v>
+        <v>382</v>
+      </c>
+      <c r="S43" s="2">
+        <v>99</v>
+      </c>
+      <c r="T43" s="2">
+        <v>92</v>
+      </c>
+      <c r="U43" s="2">
+        <v>10</v>
       </c>
       <c r="V43" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>67</v>
       </c>
       <c r="B44" t="s">
         <v>68</v>
       </c>
-      <c r="C44" t="s">
-        <v>166</v>
+      <c r="C44" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="D44" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="E44" t="s">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="G44" t="s">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="I44" t="s">
-        <v>433</v>
+        <v>390</v>
       </c>
       <c r="J44" t="s">
-        <v>434</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>435</v>
+        <v>391</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="O44" t="s">
+        <v>599</v>
       </c>
       <c r="Q44" t="s">
-        <v>436</v>
+        <v>393</v>
       </c>
       <c r="R44" t="s">
         <v>30</v>
       </c>
+      <c r="S44" s="2">
+        <v>439</v>
+      </c>
+      <c r="T44" s="2">
+        <v>321</v>
+      </c>
       <c r="V44" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>67</v>
       </c>
       <c r="B45" t="s">
         <v>68</v>
       </c>
-      <c r="C45" t="s">
-        <v>166</v>
+      <c r="C45" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="D45" t="s">
-        <v>410</v>
+        <v>370</v>
       </c>
       <c r="E45" t="s">
-        <v>431</v>
+        <v>388</v>
       </c>
       <c r="G45" t="s">
-        <v>432</v>
+        <v>389</v>
       </c>
       <c r="I45" t="s">
-        <v>437</v>
+        <v>394</v>
       </c>
       <c r="J45" t="s">
-        <v>438</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>439</v>
+        <v>395</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="O45" t="s">
+        <v>601</v>
       </c>
       <c r="Q45" t="s">
-        <v>440</v>
+        <v>397</v>
       </c>
       <c r="R45" t="s">
         <v>30</v>
       </c>
+      <c r="S45" s="2">
+        <v>244</v>
+      </c>
+      <c r="T45" s="2">
+        <v>246</v>
+      </c>
       <c r="V45" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>28</v>
       </c>
       <c r="B46" t="s">
         <v>73</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C46" s="5" t="s">
         <v>74</v>
       </c>
       <c r="D46" t="s">
@@ -4069,461 +4401,608 @@
         <v>75</v>
       </c>
       <c r="I46" t="s">
+        <v>576</v>
+      </c>
+      <c r="K46" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="O46" t="s">
+        <v>443</v>
+      </c>
+      <c r="R46" t="s">
         <v>77</v>
       </c>
-      <c r="R46" t="s">
-        <v>78</v>
+      <c r="S46" s="2">
+        <v>100</v>
+      </c>
+      <c r="T46" s="2">
+        <v>100</v>
+      </c>
+      <c r="U46" s="2">
+        <v>20</v>
       </c>
       <c r="V46" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>28</v>
       </c>
       <c r="B47" t="s">
         <v>73</v>
       </c>
-      <c r="C47" t="s">
-        <v>335</v>
+      <c r="C47" s="5" t="s">
+        <v>304</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="E47" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="I47" t="s">
-        <v>336</v>
+        <v>305</v>
       </c>
       <c r="J47" t="s">
-        <v>337</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>338</v>
+        <v>306</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="O47" t="s">
+        <v>443</v>
       </c>
       <c r="R47" t="s">
-        <v>309</v>
-      </c>
-      <c r="S47" s="3">
+        <v>289</v>
+      </c>
+      <c r="S47" s="2">
         <v>118</v>
       </c>
-      <c r="T47" s="3">
+      <c r="T47" s="2">
         <v>73</v>
       </c>
-      <c r="U47" s="3">
+      <c r="U47" s="2">
         <v>16</v>
       </c>
       <c r="V47" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B48" t="s">
         <v>73</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="5">
+        <v>1475</v>
+      </c>
+      <c r="D48" t="s">
+        <v>602</v>
+      </c>
+      <c r="E48" t="s">
+        <v>603</v>
+      </c>
+      <c r="I48" t="s">
+        <v>604</v>
+      </c>
+      <c r="J48" t="s">
+        <v>605</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>606</v>
+      </c>
+      <c r="O48" t="s">
+        <v>443</v>
+      </c>
+      <c r="R48" t="s">
+        <v>289</v>
+      </c>
+      <c r="S48" s="2">
         <v>80</v>
       </c>
-      <c r="D48" t="s">
-        <v>38</v>
-      </c>
-      <c r="E48" t="s">
-        <v>81</v>
-      </c>
-      <c r="I48" t="s">
-        <v>301</v>
-      </c>
-      <c r="J48" t="s">
-        <v>302</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="R48" t="s">
-        <v>30</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="T48" s="3" t="s">
-        <v>304</v>
+      <c r="T48" s="2">
+        <v>70</v>
+      </c>
+      <c r="U48" s="2">
+        <v>12</v>
       </c>
       <c r="V48" s="2">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B49" t="s">
         <v>73</v>
       </c>
-      <c r="C49" t="s">
-        <v>305</v>
+      <c r="C49" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="D49" t="s">
         <v>38</v>
       </c>
       <c r="E49" t="s">
-        <v>243</v>
+        <v>44</v>
       </c>
       <c r="I49" t="s">
-        <v>306</v>
+        <v>607</v>
       </c>
       <c r="J49" t="s">
-        <v>307</v>
+        <v>608</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>308</v>
+        <v>609</v>
+      </c>
+      <c r="O49" t="s">
+        <v>443</v>
       </c>
       <c r="R49" t="s">
-        <v>309</v>
-      </c>
-      <c r="V49" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="S49" s="2">
+        <v>270</v>
+      </c>
+      <c r="T49" s="2">
+        <v>230</v>
+      </c>
+      <c r="U49" s="2">
+        <v>18</v>
+      </c>
+      <c r="V49" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B50" t="s">
         <v>73</v>
       </c>
-      <c r="C50" t="s">
-        <v>310</v>
+      <c r="C50" s="5">
+        <v>1489</v>
       </c>
       <c r="D50" t="s">
-        <v>38</v>
+        <v>610</v>
       </c>
       <c r="E50" t="s">
-        <v>243</v>
+        <v>611</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>612</v>
       </c>
       <c r="I50" t="s">
-        <v>311</v>
-      </c>
-      <c r="J50" t="s">
-        <v>312</v>
+        <v>613</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>313</v>
+        <v>614</v>
+      </c>
+      <c r="O50" t="s">
+        <v>443</v>
       </c>
       <c r="R50" t="s">
-        <v>27</v>
-      </c>
-      <c r="V50" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="S50" s="2">
+        <v>163</v>
+      </c>
+      <c r="T50" s="2">
+        <v>263</v>
+      </c>
+      <c r="U50" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B51" t="s">
         <v>73</v>
       </c>
-      <c r="C51" t="s">
-        <v>314</v>
+      <c r="C51" s="5" t="s">
+        <v>615</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>616</v>
       </c>
       <c r="E51" t="s">
-        <v>315</v>
+        <v>617</v>
       </c>
       <c r="I51" t="s">
-        <v>316</v>
+        <v>618</v>
       </c>
       <c r="J51" t="s">
-        <v>317</v>
+        <v>619</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>318</v>
+        <v>620</v>
+      </c>
+      <c r="O51" t="s">
+        <v>443</v>
       </c>
       <c r="R51" t="s">
-        <v>319</v>
+        <v>289</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="T51" s="2">
+        <v>210</v>
+      </c>
+      <c r="U51" s="2">
+        <v>18</v>
       </c>
       <c r="V51" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
         <v>73</v>
       </c>
-      <c r="C52" t="s">
-        <v>137</v>
+      <c r="C52" s="5" t="s">
+        <v>528</v>
       </c>
       <c r="D52" t="s">
-        <v>38</v>
+        <v>414</v>
       </c>
       <c r="E52" t="s">
-        <v>315</v>
+        <v>622</v>
       </c>
       <c r="I52" t="s">
-        <v>320</v>
+        <v>623</v>
       </c>
       <c r="J52" t="s">
-        <v>321</v>
+        <v>624</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>322</v>
+        <v>625</v>
+      </c>
+      <c r="O52" t="s">
+        <v>443</v>
       </c>
       <c r="R52" t="s">
-        <v>309</v>
+        <v>289</v>
+      </c>
+      <c r="S52" s="2">
+        <v>370</v>
+      </c>
+      <c r="T52" s="2">
+        <v>260</v>
+      </c>
+      <c r="U52" s="2">
+        <v>20</v>
       </c>
       <c r="V52" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>79</v>
+        <v>28</v>
       </c>
       <c r="B53" t="s">
         <v>73</v>
       </c>
-      <c r="C53" t="s">
-        <v>142</v>
+      <c r="C53" s="5">
+        <v>1489</v>
       </c>
       <c r="D53" t="s">
-        <v>323</v>
+        <v>38</v>
       </c>
       <c r="E53" t="s">
-        <v>324</v>
+        <v>626</v>
       </c>
       <c r="I53" t="s">
-        <v>325</v>
-      </c>
-      <c r="J53" t="s">
-        <v>326</v>
+        <v>627</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>328</v>
+        <v>628</v>
+      </c>
+      <c r="O53" t="s">
+        <v>443</v>
       </c>
       <c r="R53" t="s">
-        <v>309</v>
+        <v>289</v>
+      </c>
+      <c r="S53" s="2">
+        <v>44</v>
+      </c>
+      <c r="T53" s="2">
+        <v>92</v>
+      </c>
+      <c r="U53" s="2">
+        <v>18</v>
       </c>
       <c r="V53" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B54" t="s">
         <v>73</v>
       </c>
-      <c r="C54" t="s">
-        <v>62</v>
+      <c r="C54" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="D54" t="s">
         <v>38</v>
       </c>
       <c r="E54" t="s">
-        <v>329</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="H54" s="1" t="s">
-        <v>331</v>
+        <v>80</v>
       </c>
       <c r="I54" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="J54" t="s">
-        <v>333</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>334</v>
+        <v>284</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="O54" t="s">
+        <v>577</v>
       </c>
       <c r="R54" t="s">
-        <v>309</v>
+        <v>30</v>
+      </c>
+      <c r="S54" s="2">
+        <v>348</v>
+      </c>
+      <c r="T54" s="2">
+        <v>560</v>
+      </c>
+      <c r="U54" s="2">
+        <v>40</v>
       </c>
       <c r="V54" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" t="s">
-        <v>85</v>
+        <v>73</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="D55" t="s">
+        <v>38</v>
       </c>
       <c r="E55" t="s">
-        <v>86</v>
+        <v>233</v>
       </c>
       <c r="I55" t="s">
-        <v>87</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>88</v>
+        <v>286</v>
+      </c>
+      <c r="J55" t="s">
+        <v>287</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="O55" t="s">
+        <v>443</v>
       </c>
       <c r="R55" t="s">
-        <v>89</v>
-      </c>
-      <c r="V55" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="S55" s="2">
+        <v>200</v>
+      </c>
+      <c r="T55" s="2">
+        <v>265</v>
+      </c>
+      <c r="U55" s="2">
+        <v>18</v>
+      </c>
+      <c r="V55" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="B56" t="s">
-        <v>91</v>
-      </c>
-      <c r="C56" t="s">
-        <v>92</v>
+        <v>73</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>290</v>
       </c>
       <c r="D56" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>94</v>
+        <v>233</v>
       </c>
       <c r="I56" t="s">
-        <v>95</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>96</v>
+        <v>291</v>
+      </c>
+      <c r="J56" t="s">
+        <v>292</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="O56" t="s">
+        <v>630</v>
       </c>
       <c r="R56" t="s">
-        <v>30</v>
-      </c>
-      <c r="V56" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="S56" s="2">
+        <v>420</v>
+      </c>
+      <c r="T56" s="2">
+        <v>200</v>
+      </c>
+      <c r="U56" s="2">
+        <v>8</v>
+      </c>
+      <c r="V56" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>78</v>
+      </c>
+      <c r="B57" t="s">
+        <v>73</v>
+      </c>
+      <c r="C57" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D57" t="s">
+        <v>38</v>
+      </c>
+      <c r="E57" t="s">
+        <v>294</v>
+      </c>
+      <c r="I57" t="s">
+        <v>295</v>
+      </c>
+      <c r="J57" t="s">
+        <v>296</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="O57" t="s">
+        <v>631</v>
+      </c>
+      <c r="R57" t="s">
+        <v>289</v>
+      </c>
+      <c r="T57" s="2">
+        <v>120</v>
+      </c>
+      <c r="U57" s="2">
+        <v>12</v>
+      </c>
+      <c r="V57" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" t="s">
+        <v>73</v>
+      </c>
+      <c r="C58" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D58" t="s">
+        <v>298</v>
+      </c>
+      <c r="E58" t="s">
+        <v>299</v>
+      </c>
+      <c r="I58" t="s">
+        <v>300</v>
+      </c>
+      <c r="J58" t="s">
+        <v>301</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="L58" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="O58" t="s">
+        <v>599</v>
+      </c>
+      <c r="R58" t="s">
+        <v>289</v>
+      </c>
+      <c r="S58" s="2">
+        <v>150</v>
+      </c>
+      <c r="T58" s="2">
+        <v>65</v>
+      </c>
+      <c r="U58" s="2">
+        <v>15</v>
+      </c>
+      <c r="V58" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>78</v>
+      </c>
+      <c r="B59" t="s">
+        <v>73</v>
+      </c>
+      <c r="C59" t="s">
+        <v>304</v>
+      </c>
+      <c r="D59" t="s">
         <v>97</v>
       </c>
-      <c r="B57" t="s">
+      <c r="E59" t="s">
         <v>98</v>
       </c>
-      <c r="C57" t="s">
-        <v>99</v>
-      </c>
-      <c r="D57" t="s">
-        <v>100</v>
-      </c>
-      <c r="E57" t="s">
-        <v>101</v>
-      </c>
-      <c r="I57" t="s">
-        <v>102</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="R57" t="s">
-        <v>104</v>
-      </c>
-      <c r="V57" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>105</v>
-      </c>
-      <c r="B58" t="s">
-        <v>106</v>
-      </c>
-      <c r="C58" t="s">
-        <v>107</v>
-      </c>
-      <c r="D58" t="s">
-        <v>38</v>
-      </c>
-      <c r="E58" t="s">
-        <v>39</v>
-      </c>
-      <c r="I58" t="s">
-        <v>108</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="R58" t="s">
-        <v>27</v>
-      </c>
-      <c r="V58" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>110</v>
-      </c>
-      <c r="B59" t="s">
-        <v>111</v>
-      </c>
-      <c r="C59" t="s">
-        <v>112</v>
-      </c>
-      <c r="D59" t="s">
-        <v>38</v>
-      </c>
-      <c r="E59" t="s">
-        <v>39</v>
-      </c>
       <c r="I59" t="s">
-        <v>152</v>
+        <v>305</v>
       </c>
       <c r="J59" t="s">
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q59" t="s">
-        <v>154</v>
+        <v>307</v>
+      </c>
+      <c r="O59" t="s">
+        <v>443</v>
       </c>
       <c r="R59" t="s">
-        <v>27</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="T59" s="3">
-        <v>51</v>
+        <v>289</v>
+      </c>
+      <c r="S59" s="2">
+        <v>118</v>
+      </c>
+      <c r="T59" s="2">
+        <v>73</v>
+      </c>
+      <c r="U59" s="2">
+        <v>16</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C60" t="s">
-        <v>157</v>
+        <v>304</v>
       </c>
       <c r="D60" t="s">
         <v>38</v>
@@ -4532,39 +5011,36 @@
         <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>152</v>
+        <v>440</v>
       </c>
       <c r="J60" t="s">
-        <v>158</v>
+        <v>441</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q60" t="s">
-        <v>154</v>
+        <v>629</v>
+      </c>
+      <c r="O60" t="s">
+        <v>443</v>
       </c>
       <c r="R60" t="s">
-        <v>30</v>
-      </c>
-      <c r="S60" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="T60" s="3">
+        <v>289</v>
+      </c>
+      <c r="S60" s="2">
         <v>57</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>161</v>
+        <v>285</v>
       </c>
       <c r="D61" t="s">
         <v>38</v>
@@ -4573,1635 +5049,2179 @@
         <v>39</v>
       </c>
       <c r="I61" t="s">
-        <v>162</v>
+        <v>632</v>
       </c>
       <c r="J61" t="s">
-        <v>163</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q61" t="s">
-        <v>154</v>
+        <v>441</v>
+      </c>
+      <c r="K61" s="6" t="s">
+        <v>633</v>
+      </c>
+      <c r="O61" t="s">
+        <v>443</v>
       </c>
       <c r="R61" t="s">
+        <v>289</v>
+      </c>
+      <c r="S61" s="2">
+        <v>70</v>
+      </c>
+      <c r="T61" s="2">
+        <v>52</v>
+      </c>
+      <c r="V61" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" t="s">
+        <v>83</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E62" t="s">
+        <v>85</v>
+      </c>
+      <c r="I62" t="s">
+        <v>646</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="O62" t="s">
+        <v>271</v>
+      </c>
+      <c r="R62" t="s">
+        <v>87</v>
+      </c>
+      <c r="S62" s="2">
+        <v>732</v>
+      </c>
+      <c r="T62" s="2">
+        <v>250</v>
+      </c>
+      <c r="U62" s="2">
+        <v>95</v>
+      </c>
+      <c r="V62" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>88</v>
+      </c>
+      <c r="B63" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D63" t="s">
+        <v>91</v>
+      </c>
+      <c r="E63" t="s">
+        <v>92</v>
+      </c>
+      <c r="I63" t="s">
+        <v>578</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="O63" t="s">
+        <v>634</v>
+      </c>
+      <c r="R63" t="s">
         <v>30</v>
       </c>
-      <c r="S61" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="V61" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>110</v>
-      </c>
-      <c r="B62" t="s">
-        <v>111</v>
-      </c>
-      <c r="C62" t="s">
-        <v>166</v>
-      </c>
-      <c r="D62" t="s">
-        <v>38</v>
-      </c>
-      <c r="E62" t="s">
-        <v>167</v>
-      </c>
-      <c r="I62" t="s">
-        <v>168</v>
-      </c>
-      <c r="J62" t="s">
-        <v>169</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q62" t="s">
-        <v>154</v>
-      </c>
-      <c r="R62" t="s">
-        <v>30</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="V62" s="2" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>110</v>
-      </c>
-      <c r="B63" t="s">
-        <v>111</v>
-      </c>
-      <c r="C63" t="s">
-        <v>172</v>
-      </c>
-      <c r="D63" t="s">
-        <v>70</v>
-      </c>
-      <c r="E63" t="s">
-        <v>173</v>
-      </c>
-      <c r="I63" t="s">
-        <v>174</v>
-      </c>
-      <c r="J63" t="s">
-        <v>175</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="L63" t="s">
-        <v>177</v>
-      </c>
-      <c r="M63" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>179</v>
-      </c>
-      <c r="R63" t="s">
-        <v>118</v>
-      </c>
-      <c r="S63" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="T63" s="3" t="s">
-        <v>180</v>
+      <c r="S63" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="T63" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="U63" s="2">
+        <v>4</v>
       </c>
       <c r="V63" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
-        <v>111</v>
-      </c>
-      <c r="C64" t="s">
-        <v>181</v>
+        <v>95</v>
+      </c>
+      <c r="C64" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="D64" t="s">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="E64" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="I64" t="s">
-        <v>182</v>
-      </c>
-      <c r="J64" t="s">
-        <v>183</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>184</v>
+        <v>583</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="O64" t="s">
+        <v>148</v>
       </c>
       <c r="R64" t="s">
-        <v>185</v>
-      </c>
-      <c r="S64" s="3">
-        <v>420</v>
-      </c>
-      <c r="T64" s="3">
-        <v>274</v>
-      </c>
-      <c r="U64" s="3">
-        <v>30</v>
+        <v>100</v>
+      </c>
+      <c r="S64" s="2">
+        <v>163</v>
+      </c>
+      <c r="T64" s="2">
+        <v>55</v>
+      </c>
+      <c r="U64" s="2">
+        <v>53</v>
       </c>
       <c r="V64" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
-        <v>111</v>
-      </c>
-      <c r="C65" t="s">
-        <v>186</v>
+        <v>102</v>
+      </c>
+      <c r="C65" s="5" t="s">
+        <v>103</v>
       </c>
       <c r="D65" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>188</v>
+        <v>542</v>
       </c>
       <c r="I65" t="s">
-        <v>189</v>
-      </c>
-      <c r="J65" t="s">
-        <v>190</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>191</v>
+        <v>582</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="O65" t="s">
+        <v>148</v>
       </c>
       <c r="R65" t="s">
         <v>27</v>
       </c>
-      <c r="S65" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="T65" s="3" t="s">
-        <v>193</v>
+      <c r="S65" s="2">
+        <v>44</v>
+      </c>
+      <c r="T65" s="2">
+        <v>22</v>
+      </c>
+      <c r="U65" s="2">
+        <v>15</v>
       </c>
       <c r="V65" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
-      </c>
-      <c r="C66" t="s">
-        <v>194</v>
+        <v>106</v>
+      </c>
+      <c r="C66" s="5" t="s">
+        <v>107</v>
       </c>
       <c r="D66" t="s">
         <v>38</v>
       </c>
       <c r="E66" t="s">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="I66" t="s">
-        <v>195</v>
+        <v>146</v>
       </c>
       <c r="J66" t="s">
-        <v>196</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>197</v>
+        <v>147</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="O66" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>148</v>
       </c>
       <c r="R66" t="s">
-        <v>198</v>
-      </c>
-      <c r="S66" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="V66" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="S66" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="T66" s="2">
+        <v>51</v>
+      </c>
+      <c r="U66" s="2">
+        <v>42</v>
+      </c>
+      <c r="V66" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
-      </c>
-      <c r="C67" t="s">
-        <v>117</v>
+        <v>106</v>
+      </c>
+      <c r="C67" s="5" t="s">
+        <v>151</v>
       </c>
       <c r="D67" t="s">
         <v>38</v>
       </c>
       <c r="E67" t="s">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="I67" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="J67" t="s">
-        <v>201</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>204</v>
+        <v>152</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="O67" t="s">
+        <v>148</v>
       </c>
       <c r="Q67" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="R67" t="s">
-        <v>118</v>
-      </c>
-      <c r="S67" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="T67" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="U67" s="3">
-        <v>11</v>
-      </c>
-      <c r="V67" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="S67" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="T67" s="2">
+        <v>57</v>
+      </c>
+      <c r="V67" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B68" t="s">
-        <v>116</v>
-      </c>
-      <c r="C68" t="s">
-        <v>207</v>
+        <v>106</v>
+      </c>
+      <c r="C68" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="D68" t="s">
         <v>38</v>
       </c>
       <c r="E68" t="s">
-        <v>81</v>
+        <v>542</v>
       </c>
       <c r="I68" t="s">
-        <v>208</v>
+        <v>156</v>
       </c>
       <c r="J68" t="s">
-        <v>209</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>203</v>
+        <v>157</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="O68" t="s">
+        <v>148</v>
       </c>
       <c r="Q68" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="R68" t="s">
-        <v>27</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="T68" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="V68" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="S68" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T68" s="2">
+        <v>64</v>
+      </c>
+      <c r="U68" s="2">
+        <v>53</v>
+      </c>
+      <c r="V68" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B69" t="s">
-        <v>116</v>
-      </c>
-      <c r="C69" t="s">
-        <v>213</v>
+        <v>106</v>
+      </c>
+      <c r="C69" s="5" t="s">
+        <v>160</v>
       </c>
       <c r="D69" t="s">
         <v>38</v>
       </c>
       <c r="E69" t="s">
+        <v>161</v>
+      </c>
+      <c r="I69" t="s">
+        <v>162</v>
+      </c>
+      <c r="J69" t="s">
+        <v>163</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O69" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>148</v>
+      </c>
+      <c r="R69" t="s">
+        <v>30</v>
+      </c>
+      <c r="S69" s="2">
+        <v>248</v>
+      </c>
+      <c r="T69" s="2">
+        <v>74</v>
+      </c>
+      <c r="U69" s="2">
+        <v>60</v>
+      </c>
+      <c r="V69" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="D70" t="s">
+        <v>70</v>
+      </c>
+      <c r="E70" t="s">
+        <v>166</v>
+      </c>
+      <c r="I70" t="s">
         <v>167</v>
       </c>
-      <c r="F69" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="I69" t="s">
-        <v>215</v>
-      </c>
-      <c r="J69" t="s">
-        <v>216</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="L69" t="s">
-        <v>218</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>154</v>
-      </c>
-      <c r="R69" t="s">
-        <v>27</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="V69" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>115</v>
-      </c>
-      <c r="B70" t="s">
-        <v>116</v>
-      </c>
-      <c r="C70" t="s">
-        <v>221</v>
-      </c>
-      <c r="D70" t="s">
-        <v>38</v>
-      </c>
-      <c r="E70" t="s">
-        <v>167</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="I70" t="s">
-        <v>222</v>
-      </c>
       <c r="J70" t="s">
-        <v>223</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>224</v>
+        <v>168</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>169</v>
       </c>
       <c r="L70" t="s">
-        <v>225</v>
+        <v>170</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>226</v>
+        <v>171</v>
+      </c>
+      <c r="O70" t="s">
+        <v>443</v>
       </c>
       <c r="Q70" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="R70" t="s">
-        <v>27</v>
-      </c>
-      <c r="S70" s="3" t="s">
-        <v>212</v>
+        <v>113</v>
+      </c>
+      <c r="S70" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="T70" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="U70" s="2">
+        <v>7</v>
       </c>
       <c r="V70" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B71" t="s">
-        <v>116</v>
-      </c>
-      <c r="C71" t="s">
-        <v>227</v>
+        <v>106</v>
+      </c>
+      <c r="C71" s="5" t="s">
+        <v>174</v>
       </c>
       <c r="D71" t="s">
         <v>38</v>
       </c>
       <c r="E71" t="s">
-        <v>167</v>
-      </c>
-      <c r="F71" s="1" t="s">
-        <v>214</v>
+        <v>44</v>
       </c>
       <c r="I71" t="s">
-        <v>228</v>
+        <v>175</v>
       </c>
       <c r="J71" t="s">
-        <v>229</v>
-      </c>
-      <c r="K71" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="L71" t="s">
-        <v>231</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="Q71" t="s">
-        <v>154</v>
+        <v>176</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="O71" t="s">
+        <v>148</v>
       </c>
       <c r="R71" t="s">
-        <v>27</v>
-      </c>
-      <c r="S71" s="3" t="s">
-        <v>233</v>
+        <v>178</v>
+      </c>
+      <c r="S71" s="2">
+        <v>420</v>
+      </c>
+      <c r="T71" s="2">
+        <v>274</v>
+      </c>
+      <c r="U71" s="2">
+        <v>30</v>
       </c>
       <c r="V71" s="2">
         <v>3</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B72" t="s">
-        <v>116</v>
-      </c>
-      <c r="C72" t="s">
-        <v>234</v>
+        <v>106</v>
+      </c>
+      <c r="C72" s="5" t="s">
+        <v>179</v>
       </c>
       <c r="D72" t="s">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="E72" t="s">
-        <v>173</v>
-      </c>
-      <c r="F72" s="1" t="s">
-        <v>235</v>
+        <v>181</v>
       </c>
       <c r="I72" t="s">
-        <v>236</v>
+        <v>182</v>
       </c>
       <c r="J72" t="s">
-        <v>237</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q72" t="s">
-        <v>179</v>
+        <v>183</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O72" t="s">
+        <v>148</v>
       </c>
       <c r="R72" t="s">
-        <v>118</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="V72" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="S72" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="T72" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="V72" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B73" t="s">
-        <v>116</v>
-      </c>
-      <c r="C73" t="s">
-        <v>234</v>
+        <v>106</v>
+      </c>
+      <c r="C73" s="5" t="s">
+        <v>186</v>
       </c>
       <c r="D73" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="E73" t="s">
-        <v>173</v>
-      </c>
-      <c r="F73" s="1" t="s">
-        <v>235</v>
+        <v>80</v>
       </c>
       <c r="I73" t="s">
-        <v>239</v>
+        <v>187</v>
       </c>
       <c r="J73" t="s">
-        <v>240</v>
-      </c>
-      <c r="K73" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q73" t="s">
-        <v>179</v>
+        <v>188</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="O73" t="s">
+        <v>148</v>
       </c>
       <c r="R73" t="s">
-        <v>118</v>
-      </c>
-      <c r="S73" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="T73" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="V73" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+        <v>190</v>
+      </c>
+      <c r="S73" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="T73" s="2">
+        <v>51</v>
+      </c>
+      <c r="U73" s="2">
+        <v>45</v>
+      </c>
+      <c r="V73" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B74" t="s">
-        <v>116</v>
-      </c>
-      <c r="C74" t="s">
-        <v>242</v>
+        <v>111</v>
+      </c>
+      <c r="C74" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="D74" t="s">
         <v>38</v>
       </c>
       <c r="E74" t="s">
-        <v>243</v>
-      </c>
-      <c r="G74" t="s">
-        <v>244</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>245</v>
+        <v>80</v>
       </c>
       <c r="I74" t="s">
+        <v>192</v>
+      </c>
+      <c r="J74" t="s">
+        <v>193</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O74" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>172</v>
+      </c>
+      <c r="R74" t="s">
+        <v>113</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="T74" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="U74" s="2">
+        <v>11</v>
+      </c>
+      <c r="V74" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>110</v>
+      </c>
+      <c r="B75" t="s">
+        <v>111</v>
+      </c>
+      <c r="C75" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="D75" t="s">
+        <v>38</v>
+      </c>
+      <c r="E75" t="s">
+        <v>80</v>
+      </c>
+      <c r="I75" t="s">
+        <v>199</v>
+      </c>
+      <c r="J75" t="s">
+        <v>200</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="O75" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>172</v>
+      </c>
+      <c r="R75" t="s">
+        <v>27</v>
+      </c>
+      <c r="S75" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="T75" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="V75" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>110</v>
+      </c>
+      <c r="B76" t="s">
+        <v>111</v>
+      </c>
+      <c r="C76" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="D76" t="s">
+        <v>38</v>
+      </c>
+      <c r="E76" t="s">
+        <v>161</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I76" t="s">
+        <v>206</v>
+      </c>
+      <c r="J76" t="s">
+        <v>207</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="L76" t="s">
+        <v>209</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="O76" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>148</v>
+      </c>
+      <c r="R76" t="s">
+        <v>27</v>
+      </c>
+      <c r="S76" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="V76" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>110</v>
+      </c>
+      <c r="B77" t="s">
+        <v>111</v>
+      </c>
+      <c r="C77" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="D77" t="s">
+        <v>38</v>
+      </c>
+      <c r="E77" t="s">
+        <v>161</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I77" t="s">
+        <v>213</v>
+      </c>
+      <c r="J77" t="s">
+        <v>214</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="L77" t="s">
+        <v>216</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="O77" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>148</v>
+      </c>
+      <c r="R77" t="s">
+        <v>27</v>
+      </c>
+      <c r="S77" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="T77" s="2">
+        <v>100</v>
+      </c>
+      <c r="U77" s="2">
+        <v>60</v>
+      </c>
+      <c r="V77" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78" t="s">
+        <v>111</v>
+      </c>
+      <c r="C78" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="D78" t="s">
+        <v>38</v>
+      </c>
+      <c r="E78" t="s">
+        <v>161</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I78" t="s">
+        <v>219</v>
+      </c>
+      <c r="J78" t="s">
+        <v>220</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="L78" t="s">
+        <v>222</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="O78" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>148</v>
+      </c>
+      <c r="R78" t="s">
+        <v>27</v>
+      </c>
+      <c r="S78" s="2">
+        <v>237</v>
+      </c>
+      <c r="T78" s="2">
+        <v>105</v>
+      </c>
+      <c r="U78" s="2">
+        <v>70</v>
+      </c>
+      <c r="V78" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>110</v>
+      </c>
+      <c r="B79" t="s">
+        <v>111</v>
+      </c>
+      <c r="C79" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D79" t="s">
+        <v>70</v>
+      </c>
+      <c r="E79" t="s">
+        <v>166</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I79" t="s">
+        <v>226</v>
+      </c>
+      <c r="J79" t="s">
+        <v>227</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="O79" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>172</v>
+      </c>
+      <c r="R79" t="s">
+        <v>113</v>
+      </c>
+      <c r="S79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="T79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="U79" s="2">
+        <v>8</v>
+      </c>
+      <c r="V79" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>110</v>
+      </c>
+      <c r="B80" t="s">
+        <v>111</v>
+      </c>
+      <c r="C80" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="D80" t="s">
+        <v>70</v>
+      </c>
+      <c r="E80" t="s">
+        <v>166</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="I80" t="s">
+        <v>229</v>
+      </c>
+      <c r="J80" t="s">
+        <v>230</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="O80" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>172</v>
+      </c>
+      <c r="R80" t="s">
+        <v>113</v>
+      </c>
+      <c r="S80" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="U80" s="2">
+        <v>8</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>110</v>
+      </c>
+      <c r="B81" t="s">
+        <v>111</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="D81" t="s">
+        <v>38</v>
+      </c>
+      <c r="E81" t="s">
+        <v>233</v>
+      </c>
+      <c r="G81" t="s">
+        <v>234</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I81" t="s">
+        <v>236</v>
+      </c>
+      <c r="J81" t="s">
+        <v>237</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="O81" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>172</v>
+      </c>
+      <c r="R81" t="s">
+        <v>27</v>
+      </c>
+      <c r="S81" s="2">
+        <v>85</v>
+      </c>
+      <c r="T81" s="2">
+        <v>193</v>
+      </c>
+      <c r="V81" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="82" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>94</v>
+      </c>
+      <c r="B82" t="s">
+        <v>115</v>
+      </c>
+      <c r="C82" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D82" t="s">
+        <v>109</v>
+      </c>
+      <c r="E82" t="s">
+        <v>117</v>
+      </c>
+      <c r="G82" t="s">
+        <v>472</v>
+      </c>
+      <c r="I82" t="s">
+        <v>473</v>
+      </c>
+      <c r="J82" t="s">
+        <v>474</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="O82" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>475</v>
+      </c>
+      <c r="R82" t="s">
+        <v>30</v>
+      </c>
+      <c r="S82" s="2">
+        <v>50</v>
+      </c>
+      <c r="T82" s="2">
+        <v>48</v>
+      </c>
+      <c r="U82" s="2">
+        <v>24</v>
+      </c>
+      <c r="V82" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
+      <c r="B83" t="s">
+        <v>115</v>
+      </c>
+      <c r="C83" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D83" t="s">
+        <v>477</v>
+      </c>
+      <c r="E83" t="s">
+        <v>478</v>
+      </c>
+      <c r="G83" t="s">
+        <v>479</v>
+      </c>
+      <c r="I83" t="s">
+        <v>581</v>
+      </c>
+      <c r="J83" t="s">
+        <v>480</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="O83" t="s">
+        <v>579</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>482</v>
+      </c>
+      <c r="R83" t="s">
+        <v>30</v>
+      </c>
+      <c r="S83" s="2">
+        <v>3500</v>
+      </c>
+      <c r="T83" s="2">
+        <v>1000</v>
+      </c>
+      <c r="V83" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="84" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" t="s">
+        <v>115</v>
+      </c>
+      <c r="C84" s="5">
+        <v>1475</v>
+      </c>
+      <c r="D84" t="s">
+        <v>97</v>
+      </c>
+      <c r="E84" t="s">
+        <v>98</v>
+      </c>
+      <c r="G84" t="s">
+        <v>483</v>
+      </c>
+      <c r="I84" t="s">
+        <v>638</v>
+      </c>
+      <c r="J84" t="s">
+        <v>484</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="O84" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>475</v>
+      </c>
+      <c r="R84" t="s">
+        <v>30</v>
+      </c>
+      <c r="S84" s="2">
+        <v>44</v>
+      </c>
+      <c r="T84" s="2">
+        <v>41</v>
+      </c>
+      <c r="U84" s="2">
+        <v>24</v>
+      </c>
+      <c r="V84" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" t="s">
+        <v>115</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>645</v>
+      </c>
+      <c r="D85" t="s">
+        <v>486</v>
+      </c>
+      <c r="E85" t="s">
+        <v>487</v>
+      </c>
+      <c r="G85" t="s">
+        <v>488</v>
+      </c>
+      <c r="I85" t="s">
+        <v>489</v>
+      </c>
+      <c r="J85" t="s">
+        <v>490</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="O85" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>475</v>
+      </c>
+      <c r="R85" t="s">
+        <v>492</v>
+      </c>
+      <c r="S85" s="2">
+        <v>44</v>
+      </c>
+      <c r="T85" s="2">
+        <v>42</v>
+      </c>
+      <c r="V85" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>119</v>
+      </c>
+      <c r="B86" t="s">
+        <v>120</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D86" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" t="s">
+        <v>122</v>
+      </c>
+      <c r="I86" t="s">
+        <v>123</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="O86" t="s">
+        <v>639</v>
+      </c>
+      <c r="R86" t="s">
+        <v>30</v>
+      </c>
+      <c r="S86" s="2">
+        <v>1200</v>
+      </c>
+      <c r="T86" s="2">
+        <v>700</v>
+      </c>
+      <c r="V86" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>125</v>
+      </c>
+      <c r="B87" t="s">
+        <v>126</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D87" t="s">
+        <v>128</v>
+      </c>
+      <c r="E87" t="s">
+        <v>129</v>
+      </c>
+      <c r="I87" t="s">
+        <v>520</v>
+      </c>
+      <c r="J87" t="s">
+        <v>493</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="O87" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>494</v>
+      </c>
+      <c r="R87" t="s">
+        <v>66</v>
+      </c>
+      <c r="S87" s="2">
+        <v>180</v>
+      </c>
+      <c r="T87" s="2">
+        <v>400</v>
+      </c>
+      <c r="V87" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="88" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>125</v>
+      </c>
+      <c r="B88" t="s">
+        <v>126</v>
+      </c>
+      <c r="C88" s="5" t="s">
+        <v>495</v>
+      </c>
+      <c r="D88" t="s">
+        <v>496</v>
+      </c>
+      <c r="E88" t="s">
+        <v>592</v>
+      </c>
+      <c r="I88" t="s">
+        <v>497</v>
+      </c>
+      <c r="J88" t="s">
+        <v>493</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="O88" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>494</v>
+      </c>
+      <c r="R88" t="s">
+        <v>66</v>
+      </c>
+      <c r="S88" s="2">
+        <v>175</v>
+      </c>
+      <c r="T88" s="2">
+        <v>500</v>
+      </c>
+      <c r="U88" s="2">
+        <v>200</v>
+      </c>
+      <c r="V88" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="89" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>125</v>
+      </c>
+      <c r="B89" t="s">
+        <v>126</v>
+      </c>
+      <c r="C89" s="5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D89" t="s">
+        <v>128</v>
+      </c>
+      <c r="E89" t="s">
+        <v>500</v>
+      </c>
+      <c r="G89" t="s">
+        <v>501</v>
+      </c>
+      <c r="I89" t="s">
+        <v>580</v>
+      </c>
+      <c r="J89" t="s">
+        <v>502</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="O89" t="s">
+        <v>641</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>494</v>
+      </c>
+      <c r="R89" t="s">
+        <v>66</v>
+      </c>
+      <c r="S89" s="2">
+        <v>180</v>
+      </c>
+      <c r="T89" s="2">
+        <v>220</v>
+      </c>
+      <c r="U89" s="2">
+        <v>110</v>
+      </c>
+      <c r="V89" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="90" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>125</v>
+      </c>
+      <c r="B90" t="s">
+        <v>126</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="D90" t="s">
+        <v>477</v>
+      </c>
+      <c r="E90" t="s">
+        <v>505</v>
+      </c>
+      <c r="G90" t="s">
+        <v>506</v>
+      </c>
+      <c r="I90" t="s">
+        <v>497</v>
+      </c>
+      <c r="J90" t="s">
+        <v>493</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="O90" t="s">
+        <v>640</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>494</v>
+      </c>
+      <c r="R90" t="s">
+        <v>66</v>
+      </c>
+      <c r="S90" s="2">
+        <v>180</v>
+      </c>
+      <c r="T90" s="2">
+        <v>450</v>
+      </c>
+      <c r="U90" s="2">
+        <v>250</v>
+      </c>
+      <c r="V90" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="91" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>331</v>
+      </c>
+      <c r="B91" t="s">
+        <v>332</v>
+      </c>
+      <c r="C91" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="D91" t="s">
+        <v>334</v>
+      </c>
+      <c r="E91" t="s">
+        <v>335</v>
+      </c>
+      <c r="I91" t="s">
+        <v>336</v>
+      </c>
+      <c r="J91" t="s">
+        <v>337</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="O91" t="s">
         <v>246</v>
       </c>
-      <c r="J74" t="s">
-        <v>247</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>179</v>
-      </c>
-      <c r="R74" t="s">
-        <v>27</v>
-      </c>
-      <c r="S74" s="3">
-        <v>85</v>
-      </c>
-      <c r="T74" s="3">
-        <v>193</v>
-      </c>
-      <c r="V74" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>97</v>
-      </c>
-      <c r="B75" t="s">
-        <v>120</v>
-      </c>
-      <c r="C75" t="s">
-        <v>121</v>
-      </c>
-      <c r="D75" t="s">
-        <v>114</v>
-      </c>
-      <c r="E75" t="s">
-        <v>122</v>
-      </c>
-      <c r="G75" t="s">
-        <v>540</v>
-      </c>
-      <c r="I75" t="s">
-        <v>541</v>
-      </c>
-      <c r="J75" t="s">
-        <v>542</v>
-      </c>
-      <c r="K75" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>543</v>
-      </c>
-      <c r="R75" t="s">
+      <c r="R91" t="s">
+        <v>340</v>
+      </c>
+      <c r="S91" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="T91" s="2">
+        <v>55</v>
+      </c>
+      <c r="U91" s="2">
+        <v>35</v>
+      </c>
+      <c r="V91" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>331</v>
+      </c>
+      <c r="B92" t="s">
+        <v>332</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="D92" t="s">
+        <v>343</v>
+      </c>
+      <c r="E92" t="s">
+        <v>344</v>
+      </c>
+      <c r="I92" t="s">
+        <v>345</v>
+      </c>
+      <c r="J92" t="s">
+        <v>346</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="O92" t="s">
+        <v>599</v>
+      </c>
+      <c r="R92" t="s">
+        <v>327</v>
+      </c>
+      <c r="S92" s="2">
+        <v>1200</v>
+      </c>
+      <c r="T92" s="2">
+        <v>370</v>
+      </c>
+      <c r="V92" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>331</v>
+      </c>
+      <c r="B93" t="s">
+        <v>332</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>348</v>
+      </c>
+      <c r="D93" t="s">
+        <v>349</v>
+      </c>
+      <c r="E93" t="s">
+        <v>350</v>
+      </c>
+      <c r="I93" t="s">
+        <v>351</v>
+      </c>
+      <c r="J93" t="s">
+        <v>352</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="O93" t="s">
+        <v>599</v>
+      </c>
+      <c r="R93" t="s">
+        <v>354</v>
+      </c>
+      <c r="S93" s="2">
+        <v>150</v>
+      </c>
+      <c r="T93" s="2">
+        <v>250</v>
+      </c>
+      <c r="V93" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="94" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>331</v>
+      </c>
+      <c r="B94" t="s">
+        <v>332</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="D94" t="s">
+        <v>356</v>
+      </c>
+      <c r="E94" t="s">
+        <v>357</v>
+      </c>
+      <c r="I94" t="s">
+        <v>358</v>
+      </c>
+      <c r="J94" t="s">
+        <v>359</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="O94" t="s">
+        <v>271</v>
+      </c>
+      <c r="R94" t="s">
         <v>30</v>
       </c>
-      <c r="S75" s="3" t="s">
-        <v>544</v>
-      </c>
-      <c r="V75" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>97</v>
-      </c>
-      <c r="B76" t="s">
-        <v>120</v>
-      </c>
-      <c r="C76" t="s">
-        <v>545</v>
-      </c>
-      <c r="D76" t="s">
-        <v>546</v>
-      </c>
-      <c r="E76" t="s">
-        <v>547</v>
-      </c>
-      <c r="G76" t="s">
-        <v>548</v>
-      </c>
-      <c r="I76" t="s">
-        <v>549</v>
-      </c>
-      <c r="J76" t="s">
-        <v>550</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="Q76" t="s">
-        <v>552</v>
-      </c>
-      <c r="R76" t="s">
-        <v>30</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="V76" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>97</v>
-      </c>
-      <c r="B77" t="s">
-        <v>120</v>
-      </c>
-      <c r="C77" t="s">
-        <v>554</v>
-      </c>
-      <c r="D77" t="s">
-        <v>100</v>
-      </c>
-      <c r="E77" t="s">
-        <v>101</v>
-      </c>
-      <c r="G77" t="s">
-        <v>555</v>
-      </c>
-      <c r="I77" t="s">
-        <v>556</v>
-      </c>
-      <c r="J77" t="s">
-        <v>557</v>
-      </c>
-      <c r="K77" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="Q77" t="s">
-        <v>543</v>
-      </c>
-      <c r="R77" t="s">
-        <v>30</v>
-      </c>
-      <c r="S77" s="3" t="s">
-        <v>559</v>
-      </c>
-      <c r="V77" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>97</v>
-      </c>
-      <c r="B78" t="s">
-        <v>120</v>
-      </c>
-      <c r="C78" t="s">
-        <v>560</v>
-      </c>
-      <c r="D78" t="s">
-        <v>561</v>
-      </c>
-      <c r="E78" t="s">
-        <v>562</v>
-      </c>
-      <c r="G78" t="s">
-        <v>563</v>
-      </c>
-      <c r="I78" t="s">
-        <v>564</v>
-      </c>
-      <c r="J78" t="s">
-        <v>565</v>
-      </c>
-      <c r="K78" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="Q78" t="s">
-        <v>543</v>
-      </c>
-      <c r="R78" t="s">
-        <v>567</v>
-      </c>
-      <c r="S78" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="V78" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>124</v>
-      </c>
-      <c r="B79" t="s">
-        <v>125</v>
-      </c>
-      <c r="C79" t="s">
-        <v>126</v>
-      </c>
-      <c r="D79" t="s">
-        <v>24</v>
-      </c>
-      <c r="E79" t="s">
-        <v>127</v>
-      </c>
-      <c r="I79" t="s">
-        <v>128</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="R79" t="s">
-        <v>30</v>
-      </c>
-      <c r="V79" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>130</v>
-      </c>
-      <c r="B80" t="s">
+      <c r="S94" s="2">
+        <v>170</v>
+      </c>
+      <c r="T94" s="2">
+        <v>340</v>
+      </c>
+      <c r="U94" s="2">
+        <v>220</v>
+      </c>
+      <c r="V94" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>331</v>
+      </c>
+      <c r="B95" t="s">
+        <v>332</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D95" t="s">
+        <v>361</v>
+      </c>
+      <c r="E95" t="s">
+        <v>362</v>
+      </c>
+      <c r="I95" t="s">
+        <v>363</v>
+      </c>
+      <c r="J95" t="s">
+        <v>364</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="O95" t="s">
+        <v>148</v>
+      </c>
+      <c r="R95" t="s">
+        <v>52</v>
+      </c>
+      <c r="S95" s="2">
+        <v>38</v>
+      </c>
+      <c r="T95" s="2">
+        <v>28</v>
+      </c>
+      <c r="U95" s="2">
+        <v>16</v>
+      </c>
+      <c r="V95" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="96" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>53</v>
+      </c>
+      <c r="B96" t="s">
         <v>131</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C96" s="5" t="s">
         <v>132</v>
-      </c>
-      <c r="D80" t="s">
-        <v>133</v>
-      </c>
-      <c r="E80" t="s">
-        <v>134</v>
-      </c>
-      <c r="I80" t="s">
-        <v>569</v>
-      </c>
-      <c r="J80" t="s">
-        <v>570</v>
-      </c>
-      <c r="K80" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q80" t="s">
-        <v>571</v>
-      </c>
-      <c r="R80" t="s">
-        <v>66</v>
-      </c>
-      <c r="V80" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>130</v>
-      </c>
-      <c r="B81" t="s">
-        <v>131</v>
-      </c>
-      <c r="C81" t="s">
-        <v>572</v>
-      </c>
-      <c r="D81" t="s">
-        <v>573</v>
-      </c>
-      <c r="E81" t="s">
-        <v>574</v>
-      </c>
-      <c r="I81" t="s">
-        <v>575</v>
-      </c>
-      <c r="J81" t="s">
-        <v>570</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="Q81" t="s">
-        <v>571</v>
-      </c>
-      <c r="R81" t="s">
-        <v>66</v>
-      </c>
-      <c r="V81" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>130</v>
-      </c>
-      <c r="B82" t="s">
-        <v>131</v>
-      </c>
-      <c r="C82" t="s">
-        <v>577</v>
-      </c>
-      <c r="D82" t="s">
-        <v>133</v>
-      </c>
-      <c r="E82" t="s">
-        <v>578</v>
-      </c>
-      <c r="G82" t="s">
-        <v>579</v>
-      </c>
-      <c r="I82" t="s">
-        <v>580</v>
-      </c>
-      <c r="J82" t="s">
-        <v>581</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>582</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>571</v>
-      </c>
-      <c r="R82" t="s">
-        <v>66</v>
-      </c>
-      <c r="V82" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>130</v>
-      </c>
-      <c r="B83" t="s">
-        <v>131</v>
-      </c>
-      <c r="C83" t="s">
-        <v>583</v>
-      </c>
-      <c r="D83" t="s">
-        <v>546</v>
-      </c>
-      <c r="E83" t="s">
-        <v>584</v>
-      </c>
-      <c r="G83" t="s">
-        <v>585</v>
-      </c>
-      <c r="I83" t="s">
-        <v>575</v>
-      </c>
-      <c r="J83" t="s">
-        <v>570</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>586</v>
-      </c>
-      <c r="Q83" t="s">
-        <v>571</v>
-      </c>
-      <c r="R83" t="s">
-        <v>66</v>
-      </c>
-      <c r="V83" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" t="s">
-        <v>366</v>
-      </c>
-      <c r="C84" t="s">
-        <v>367</v>
-      </c>
-      <c r="D84" t="s">
-        <v>368</v>
-      </c>
-      <c r="E84" t="s">
-        <v>369</v>
-      </c>
-      <c r="I84" t="s">
-        <v>370</v>
-      </c>
-      <c r="J84" t="s">
-        <v>371</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="M84" s="1" t="s">
-        <v>373</v>
-      </c>
-      <c r="R84" t="s">
-        <v>374</v>
-      </c>
-      <c r="S84" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="V84" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>365</v>
-      </c>
-      <c r="B85" t="s">
-        <v>366</v>
-      </c>
-      <c r="C85" t="s">
-        <v>376</v>
-      </c>
-      <c r="D85" t="s">
-        <v>377</v>
-      </c>
-      <c r="E85" t="s">
-        <v>378</v>
-      </c>
-      <c r="I85" t="s">
-        <v>379</v>
-      </c>
-      <c r="J85" t="s">
-        <v>380</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="R85" t="s">
-        <v>361</v>
-      </c>
-      <c r="S85" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="V85" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>365</v>
-      </c>
-      <c r="B86" t="s">
-        <v>366</v>
-      </c>
-      <c r="C86" t="s">
-        <v>383</v>
-      </c>
-      <c r="D86" t="s">
-        <v>384</v>
-      </c>
-      <c r="E86" t="s">
-        <v>385</v>
-      </c>
-      <c r="I86" t="s">
-        <v>386</v>
-      </c>
-      <c r="J86" t="s">
-        <v>387</v>
-      </c>
-      <c r="K86" s="1" t="s">
-        <v>388</v>
-      </c>
-      <c r="R86" t="s">
-        <v>389</v>
-      </c>
-      <c r="S86" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="V86" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>365</v>
-      </c>
-      <c r="B87" t="s">
-        <v>366</v>
-      </c>
-      <c r="C87" t="s">
-        <v>391</v>
-      </c>
-      <c r="D87" t="s">
-        <v>392</v>
-      </c>
-      <c r="E87" t="s">
-        <v>393</v>
-      </c>
-      <c r="I87" t="s">
-        <v>394</v>
-      </c>
-      <c r="J87" t="s">
-        <v>395</v>
-      </c>
-      <c r="K87" s="1" t="s">
-        <v>396</v>
-      </c>
-      <c r="R87" t="s">
-        <v>30</v>
-      </c>
-      <c r="S87" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="V87" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>365</v>
-      </c>
-      <c r="B88" t="s">
-        <v>366</v>
-      </c>
-      <c r="C88" t="s">
-        <v>339</v>
-      </c>
-      <c r="D88" t="s">
-        <v>398</v>
-      </c>
-      <c r="E88" t="s">
-        <v>399</v>
-      </c>
-      <c r="I88" t="s">
-        <v>400</v>
-      </c>
-      <c r="J88" t="s">
-        <v>401</v>
-      </c>
-      <c r="K88" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="R88" t="s">
-        <v>403</v>
-      </c>
-      <c r="S88" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="V88" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>52</v>
-      </c>
-      <c r="B89" t="s">
-        <v>136</v>
-      </c>
-      <c r="C89" t="s">
-        <v>137</v>
-      </c>
-      <c r="D89" t="s">
-        <v>38</v>
-      </c>
-      <c r="E89" t="s">
-        <v>138</v>
-      </c>
-      <c r="I89" t="s">
-        <v>489</v>
-      </c>
-      <c r="J89" t="s">
-        <v>490</v>
-      </c>
-      <c r="K89" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>285</v>
-      </c>
-      <c r="R89" t="s">
-        <v>30</v>
-      </c>
-      <c r="V89" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>52</v>
-      </c>
-      <c r="B90" t="s">
-        <v>136</v>
-      </c>
-      <c r="C90">
-        <v>1456</v>
-      </c>
-      <c r="D90" t="s">
-        <v>491</v>
-      </c>
-      <c r="E90" t="s">
-        <v>492</v>
-      </c>
-      <c r="I90" t="s">
-        <v>493</v>
-      </c>
-      <c r="J90" t="s">
-        <v>494</v>
-      </c>
-      <c r="K90" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>278</v>
-      </c>
-      <c r="R90" t="s">
-        <v>30</v>
-      </c>
-      <c r="S90" s="3">
-        <v>58</v>
-      </c>
-      <c r="T90" s="3">
-        <v>51</v>
-      </c>
-      <c r="V90" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>52</v>
-      </c>
-      <c r="B91" t="s">
-        <v>136</v>
-      </c>
-      <c r="C91" t="s">
-        <v>121</v>
-      </c>
-      <c r="D91" t="s">
-        <v>38</v>
-      </c>
-      <c r="E91" t="s">
-        <v>39</v>
-      </c>
-      <c r="I91" t="s">
-        <v>496</v>
-      </c>
-      <c r="J91" t="s">
-        <v>497</v>
-      </c>
-      <c r="K91" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="Q91" t="s">
-        <v>278</v>
-      </c>
-      <c r="R91" t="s">
-        <v>30</v>
-      </c>
-      <c r="V91" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>52</v>
-      </c>
-      <c r="B92" t="s">
-        <v>136</v>
-      </c>
-      <c r="C92" t="s">
-        <v>499</v>
-      </c>
-      <c r="D92" t="s">
-        <v>500</v>
-      </c>
-      <c r="E92" t="s">
-        <v>501</v>
-      </c>
-      <c r="I92" t="s">
-        <v>502</v>
-      </c>
-      <c r="J92" t="s">
-        <v>503</v>
-      </c>
-      <c r="K92" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="Q92" t="s">
-        <v>505</v>
-      </c>
-      <c r="R92" t="s">
-        <v>66</v>
-      </c>
-      <c r="V92" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>52</v>
-      </c>
-      <c r="B93" t="s">
-        <v>136</v>
-      </c>
-      <c r="C93" t="s">
-        <v>137</v>
-      </c>
-      <c r="D93" t="s">
-        <v>38</v>
-      </c>
-      <c r="E93" t="s">
-        <v>138</v>
-      </c>
-      <c r="I93" t="s">
-        <v>139</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="R93" t="s">
-        <v>30</v>
-      </c>
-      <c r="V93" s="2" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>141</v>
-      </c>
-      <c r="B94" t="s">
-        <v>136</v>
-      </c>
-      <c r="C94" t="s">
-        <v>142</v>
-      </c>
-      <c r="D94" t="s">
-        <v>38</v>
-      </c>
-      <c r="E94" t="s">
-        <v>44</v>
-      </c>
-      <c r="G94" t="s">
-        <v>458</v>
-      </c>
-      <c r="I94" t="s">
-        <v>459</v>
-      </c>
-      <c r="J94" t="s">
-        <v>460</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="Q94" t="s">
-        <v>285</v>
-      </c>
-      <c r="R94" t="s">
-        <v>461</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="V94" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>141</v>
-      </c>
-      <c r="B95" t="s">
-        <v>136</v>
-      </c>
-      <c r="C95" t="s">
-        <v>464</v>
-      </c>
-      <c r="D95" t="s">
-        <v>465</v>
-      </c>
-      <c r="E95" t="s">
-        <v>466</v>
-      </c>
-      <c r="G95" t="s">
-        <v>467</v>
-      </c>
-      <c r="I95" t="s">
-        <v>468</v>
-      </c>
-      <c r="J95" t="s">
-        <v>469</v>
-      </c>
-      <c r="K95" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="Q95" t="s">
-        <v>471</v>
-      </c>
-      <c r="R95" t="s">
-        <v>472</v>
-      </c>
-      <c r="V95" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>141</v>
-      </c>
-      <c r="B96" t="s">
-        <v>136</v>
-      </c>
-      <c r="C96" t="s">
-        <v>473</v>
       </c>
       <c r="D96" t="s">
         <v>38</v>
       </c>
       <c r="E96" t="s">
-        <v>474</v>
-      </c>
-      <c r="G96" t="s">
-        <v>475</v>
+        <v>133</v>
       </c>
       <c r="I96" t="s">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="J96" t="s">
-        <v>477</v>
-      </c>
-      <c r="K96" s="1" t="s">
-        <v>478</v>
+        <v>429</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="O96" t="s">
+        <v>271</v>
       </c>
       <c r="Q96" t="s">
-        <v>479</v>
+        <v>271</v>
       </c>
       <c r="R96" t="s">
+        <v>30</v>
+      </c>
+      <c r="S96" s="2">
+        <v>400</v>
+      </c>
+      <c r="T96" s="2">
         <v>480</v>
       </c>
       <c r="V96" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>141</v>
+        <v>53</v>
       </c>
       <c r="B97" t="s">
-        <v>136</v>
-      </c>
-      <c r="C97" t="s">
-        <v>481</v>
+        <v>131</v>
+      </c>
+      <c r="C97" s="5">
+        <v>1456</v>
       </c>
       <c r="D97" t="s">
-        <v>482</v>
+        <v>430</v>
       </c>
       <c r="E97" t="s">
-        <v>483</v>
-      </c>
-      <c r="G97" t="s">
-        <v>484</v>
+        <v>431</v>
       </c>
       <c r="I97" t="s">
-        <v>485</v>
+        <v>432</v>
       </c>
       <c r="J97" t="s">
-        <v>486</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="M97" s="1" t="s">
-        <v>488</v>
+        <v>433</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="O97" t="s">
+        <v>148</v>
       </c>
       <c r="Q97" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="R97" t="s">
         <v>30</v>
       </c>
-      <c r="V97" s="2">
+      <c r="S97" s="2">
+        <v>58</v>
+      </c>
+      <c r="T97" s="2">
+        <v>51</v>
+      </c>
+      <c r="U97" s="2">
+        <v>30</v>
+      </c>
+      <c r="V97" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="98" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>53</v>
+      </c>
+      <c r="B98" t="s">
+        <v>131</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D98" t="s">
+        <v>38</v>
+      </c>
+      <c r="E98" t="s">
+        <v>542</v>
+      </c>
+      <c r="I98" t="s">
+        <v>435</v>
+      </c>
+      <c r="J98" t="s">
+        <v>436</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="O98" t="s">
+        <v>148</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>264</v>
+      </c>
+      <c r="R98" t="s">
+        <v>30</v>
+      </c>
+      <c r="S98" s="2">
+        <v>53</v>
+      </c>
+      <c r="T98" s="2">
+        <v>57</v>
+      </c>
+      <c r="V98" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="99" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>53</v>
+      </c>
+      <c r="B99" t="s">
+        <v>131</v>
+      </c>
+      <c r="C99" s="5">
+        <v>1470</v>
+      </c>
+      <c r="D99" t="s">
+        <v>438</v>
+      </c>
+      <c r="E99" t="s">
+        <v>439</v>
+      </c>
+      <c r="I99" t="s">
+        <v>440</v>
+      </c>
+      <c r="J99" t="s">
+        <v>441</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="O99" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>443</v>
+      </c>
+      <c r="R99" t="s">
+        <v>66</v>
+      </c>
+      <c r="S99" s="2">
+        <v>73</v>
+      </c>
+      <c r="T99" s="2">
+        <v>53</v>
+      </c>
+      <c r="V99" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="100" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>135</v>
+      </c>
+      <c r="B100" t="s">
+        <v>131</v>
+      </c>
+      <c r="C100" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="D100" t="s">
+        <v>38</v>
+      </c>
+      <c r="E100" t="s">
+        <v>44</v>
+      </c>
+      <c r="I100" t="s">
+        <v>409</v>
+      </c>
+      <c r="J100" t="s">
+        <v>410</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="O100" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>271</v>
+      </c>
+      <c r="R100" t="s">
+        <v>411</v>
+      </c>
+      <c r="S100" s="2">
+        <v>715</v>
+      </c>
+      <c r="T100" s="2">
+        <v>316</v>
+      </c>
+      <c r="V100" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="101" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>135</v>
+      </c>
+      <c r="B101" t="s">
+        <v>131</v>
+      </c>
+      <c r="C101" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="D101" t="s">
+        <v>414</v>
+      </c>
+      <c r="E101" t="s">
+        <v>415</v>
+      </c>
+      <c r="I101" t="s">
+        <v>642</v>
+      </c>
+      <c r="J101" t="s">
+        <v>416</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="O101" t="s">
+        <v>443</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>418</v>
+      </c>
+      <c r="R101" t="s">
+        <v>419</v>
+      </c>
+      <c r="S101" s="2">
+        <v>250</v>
+      </c>
+      <c r="T101" s="2">
+        <v>300</v>
+      </c>
+      <c r="V101" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="102" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>135</v>
+      </c>
+      <c r="B102" t="s">
+        <v>131</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="D102" t="s">
+        <v>421</v>
+      </c>
+      <c r="E102" t="s">
+        <v>422</v>
+      </c>
+      <c r="G102" t="s">
+        <v>423</v>
+      </c>
+      <c r="I102" t="s">
+        <v>424</v>
+      </c>
+      <c r="J102" t="s">
+        <v>425</v>
+      </c>
+      <c r="K102" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="O102" t="s">
+        <v>271</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>271</v>
+      </c>
+      <c r="R102" t="s">
+        <v>30</v>
+      </c>
+      <c r="S102" s="2">
+        <v>466</v>
+      </c>
+      <c r="T102" s="2">
+        <v>233</v>
+      </c>
+      <c r="U102" s="2">
+        <v>50</v>
+      </c>
+      <c r="V102" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="103" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>138</v>
+      </c>
+      <c r="B103" t="s">
+        <v>139</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D103" t="s">
+        <v>141</v>
+      </c>
+      <c r="E103" t="s">
+        <v>142</v>
+      </c>
+      <c r="I103" t="s">
+        <v>143</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="O103" t="s">
+        <v>599</v>
+      </c>
+      <c r="R103" t="s">
+        <v>145</v>
+      </c>
+      <c r="S103" s="2">
+        <v>1300</v>
+      </c>
+      <c r="T103" s="2">
+        <v>1100</v>
+      </c>
+      <c r="V103" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>144</v>
-      </c>
-      <c r="B98" t="s">
-        <v>145</v>
-      </c>
-      <c r="C98" t="s">
-        <v>146</v>
-      </c>
-      <c r="D98" t="s">
-        <v>147</v>
-      </c>
-      <c r="E98" t="s">
+    <row r="104" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>138</v>
+      </c>
+      <c r="B104" t="s">
+        <v>139</v>
+      </c>
+      <c r="C104" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D104" t="s">
+        <v>141</v>
+      </c>
+      <c r="E104" t="s">
+        <v>309</v>
+      </c>
+      <c r="I104" t="s">
+        <v>310</v>
+      </c>
+      <c r="J104" t="s">
+        <v>311</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="O104" t="s">
+        <v>271</v>
+      </c>
+      <c r="R104" t="s">
+        <v>313</v>
+      </c>
+      <c r="S104" s="2">
+        <v>386</v>
+      </c>
+      <c r="T104" s="2">
+        <v>280</v>
+      </c>
+      <c r="U104" s="2">
+        <v>162</v>
+      </c>
+      <c r="V104" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="105" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>138</v>
+      </c>
+      <c r="B105" t="s">
+        <v>139</v>
+      </c>
+      <c r="C105" s="5">
+        <v>1495</v>
+      </c>
+      <c r="D105" t="s">
+        <v>141</v>
+      </c>
+      <c r="E105" t="s">
+        <v>314</v>
+      </c>
+      <c r="I105" t="s">
+        <v>315</v>
+      </c>
+      <c r="J105" t="s">
+        <v>316</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="O105" t="s">
+        <v>172</v>
+      </c>
+      <c r="R105" t="s">
+        <v>27</v>
+      </c>
+      <c r="S105" s="2">
+        <v>198</v>
+      </c>
+      <c r="T105" s="2">
+        <v>114</v>
+      </c>
+      <c r="U105" s="2">
+        <v>8</v>
+      </c>
+      <c r="V105" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="106" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>138</v>
+      </c>
+      <c r="B106" t="s">
+        <v>139</v>
+      </c>
+      <c r="C106" s="5" t="s">
+        <v>318</v>
+      </c>
+      <c r="D106" t="s">
+        <v>141</v>
+      </c>
+      <c r="E106" t="s">
+        <v>142</v>
+      </c>
+      <c r="I106" t="s">
+        <v>319</v>
+      </c>
+      <c r="J106" t="s">
+        <v>320</v>
+      </c>
+      <c r="K106" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="L106" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="O106" t="s">
+        <v>575</v>
+      </c>
+      <c r="R106" t="s">
+        <v>323</v>
+      </c>
+      <c r="S106" s="2">
+        <v>250</v>
+      </c>
+      <c r="V106" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>138</v>
+      </c>
+      <c r="B107" t="s">
+        <v>139</v>
+      </c>
+      <c r="C107" s="5" t="s">
+        <v>644</v>
+      </c>
+      <c r="D107" t="s">
+        <v>114</v>
+      </c>
+      <c r="E107" t="s">
+        <v>324</v>
+      </c>
+      <c r="I107" t="s">
+        <v>440</v>
+      </c>
+      <c r="J107" t="s">
+        <v>325</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="O107" t="s">
         <v>148</v>
       </c>
-      <c r="I98" t="s">
-        <v>149</v>
-      </c>
-      <c r="K98" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="R98" t="s">
-        <v>151</v>
-      </c>
-      <c r="V98" s="2">
+      <c r="R107" t="s">
+        <v>327</v>
+      </c>
+      <c r="S107" s="2">
+        <v>140</v>
+      </c>
+      <c r="T107" s="2">
+        <v>40</v>
+      </c>
+      <c r="U107" s="2">
+        <v>37</v>
+      </c>
+      <c r="V107" s="2">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>144</v>
-      </c>
-      <c r="B99" t="s">
-        <v>145</v>
-      </c>
-      <c r="C99" t="s">
-        <v>339</v>
-      </c>
-      <c r="D99" t="s">
-        <v>147</v>
-      </c>
-      <c r="E99" t="s">
-        <v>340</v>
-      </c>
-      <c r="I99" t="s">
-        <v>341</v>
-      </c>
-      <c r="J99" t="s">
-        <v>342</v>
-      </c>
-      <c r="K99" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="R99" t="s">
-        <v>344</v>
-      </c>
-      <c r="V99" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>144</v>
-      </c>
-      <c r="B100" t="s">
-        <v>145</v>
-      </c>
-      <c r="C100" t="s">
-        <v>345</v>
-      </c>
-      <c r="D100" t="s">
-        <v>147</v>
-      </c>
-      <c r="E100" t="s">
-        <v>346</v>
-      </c>
-      <c r="I100" t="s">
-        <v>347</v>
-      </c>
-      <c r="J100" t="s">
-        <v>348</v>
-      </c>
-      <c r="K100" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="R100" t="s">
-        <v>27</v>
-      </c>
-      <c r="V100" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>144</v>
-      </c>
-      <c r="B101" t="s">
-        <v>145</v>
-      </c>
-      <c r="C101" t="s">
-        <v>350</v>
-      </c>
-      <c r="D101" t="s">
-        <v>147</v>
-      </c>
-      <c r="E101" t="s">
-        <v>148</v>
-      </c>
-      <c r="I101" t="s">
-        <v>351</v>
-      </c>
-      <c r="J101" t="s">
-        <v>352</v>
-      </c>
-      <c r="K101" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="L101" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="R101" t="s">
-        <v>355</v>
-      </c>
-      <c r="V101" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>144</v>
-      </c>
-      <c r="B102" t="s">
-        <v>145</v>
-      </c>
-      <c r="C102" t="s">
-        <v>356</v>
-      </c>
-      <c r="D102" t="s">
-        <v>119</v>
-      </c>
-      <c r="E102" t="s">
-        <v>357</v>
-      </c>
-      <c r="I102" t="s">
-        <v>358</v>
-      </c>
-      <c r="J102" t="s">
-        <v>359</v>
-      </c>
-      <c r="K102" s="1" t="s">
-        <v>360</v>
-      </c>
-      <c r="R102" t="s">
-        <v>361</v>
-      </c>
-      <c r="V102" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>144</v>
-      </c>
-      <c r="B103" t="s">
-        <v>145</v>
-      </c>
-      <c r="C103" t="s">
-        <v>339</v>
-      </c>
-      <c r="D103" t="s">
-        <v>147</v>
-      </c>
-      <c r="E103" t="s">
-        <v>340</v>
-      </c>
-      <c r="I103" t="s">
-        <v>362</v>
-      </c>
-      <c r="J103" t="s">
-        <v>363</v>
-      </c>
-      <c r="K103" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="R103" t="s">
+    <row r="108" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>138</v>
+      </c>
+      <c r="B108" t="s">
+        <v>139</v>
+      </c>
+      <c r="C108" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="D108" t="s">
+        <v>141</v>
+      </c>
+      <c r="E108" t="s">
+        <v>643</v>
+      </c>
+      <c r="I108" t="s">
+        <v>328</v>
+      </c>
+      <c r="J108" t="s">
+        <v>329</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="O108" t="s">
+        <v>271</v>
+      </c>
+      <c r="R108" t="s">
         <v>30</v>
       </c>
-      <c r="V103" s="2">
+      <c r="S108" s="2">
+        <v>112</v>
+      </c>
+      <c r="T108" s="2">
+        <v>217</v>
+      </c>
+      <c r="U108" s="2">
+        <v>70</v>
+      </c>
+      <c r="V108" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6210,126 +7230,129 @@
   <hyperlinks>
     <hyperlink ref="K22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="K46" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="K55" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K56" r:id="rId4" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="K57" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K58" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K93" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000019000000}"/>
-    <hyperlink ref="K98" r:id="rId8" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K79" r:id="rId9" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K59" r:id="rId10" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
-    <hyperlink ref="K60" r:id="rId11" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
-    <hyperlink ref="K61" r:id="rId12" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
-    <hyperlink ref="K62" r:id="rId13" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
-    <hyperlink ref="K63" r:id="rId14" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
-    <hyperlink ref="M63" r:id="rId15" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
-    <hyperlink ref="K64" r:id="rId16" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
-    <hyperlink ref="K65" r:id="rId17" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
-    <hyperlink ref="K66" r:id="rId18" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
-    <hyperlink ref="K67" r:id="rId19" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
-    <hyperlink ref="M67" r:id="rId20" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
-    <hyperlink ref="O67" r:id="rId21" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg/960px-Firenze%2C_battistero_di_san_giovanni%2C_porta_del_paradiso_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3EEC43AF-90EA-41CF-AF24-FC2068008E5F}"/>
-    <hyperlink ref="K68" r:id="rId22" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
-    <hyperlink ref="M68" r:id="rId23" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
-    <hyperlink ref="K69" r:id="rId24" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
-    <hyperlink ref="M69" r:id="rId25" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
-    <hyperlink ref="K70" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
-    <hyperlink ref="F69" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
-    <hyperlink ref="F70:F71" r:id="rId28" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
-    <hyperlink ref="M70" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
-    <hyperlink ref="M71" r:id="rId30" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
-    <hyperlink ref="K71" r:id="rId31" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
-    <hyperlink ref="K72" r:id="rId32" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
-    <hyperlink ref="F72" r:id="rId33" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
-    <hyperlink ref="F73" r:id="rId34" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
-    <hyperlink ref="K73" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
-    <hyperlink ref="K74" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
-    <hyperlink ref="H74" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
-    <hyperlink ref="K33" r:id="rId38" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
-    <hyperlink ref="K34" r:id="rId39" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
-    <hyperlink ref="K35" r:id="rId40" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
-    <hyperlink ref="K48" r:id="rId41" xr:uid="{C61A9D98-CECD-4B5E-B96E-4289BBC0D262}"/>
-    <hyperlink ref="K49" r:id="rId42" xr:uid="{EB7CB685-E0C1-4945-9E14-9CA8A1A342EC}"/>
-    <hyperlink ref="K50" r:id="rId43" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F065AADE-42A0-4C3C-B801-4BE9B5FA9BEB}"/>
-    <hyperlink ref="K51" r:id="rId44" xr:uid="{819ABFBD-4499-4FE6-9CDB-0A9FE7A07280}"/>
-    <hyperlink ref="K52" r:id="rId45" xr:uid="{48E832D6-CC6D-436E-BC8A-74B5489EE9B1}"/>
-    <hyperlink ref="K53" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D8CE24E7-04FD-4348-88B3-8498A10C097C}"/>
-    <hyperlink ref="K54" r:id="rId47" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f1/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5381B954-6617-4930-A5BC-415052E36793}"/>
-    <hyperlink ref="L53" r:id="rId48" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCF513E3-779E-478B-83FF-5E58604AFA16}"/>
-    <hyperlink ref="H54" r:id="rId49" xr:uid="{B822FBF8-7DC0-48FD-BCB2-A7B3FC9F1F52}"/>
-    <hyperlink ref="F54" r:id="rId50" xr:uid="{3D8C3557-F6D2-4A3A-BE13-D18D5DD3FB6A}"/>
-    <hyperlink ref="K47" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
-    <hyperlink ref="K99" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
-    <hyperlink ref="L101" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
-    <hyperlink ref="K101" r:id="rId54" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
-    <hyperlink ref="K100" r:id="rId55" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
-    <hyperlink ref="K103" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
-    <hyperlink ref="K102" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
-    <hyperlink ref="M84" r:id="rId58" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
-    <hyperlink ref="K84" r:id="rId59" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
-    <hyperlink ref="K85" r:id="rId60" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
-    <hyperlink ref="K88" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
-    <hyperlink ref="K87" r:id="rId62" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
-    <hyperlink ref="K86" r:id="rId63" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
-    <hyperlink ref="K40" r:id="rId64" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
-    <hyperlink ref="K41" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
-    <hyperlink ref="K42" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
-    <hyperlink ref="K43" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
-    <hyperlink ref="K44" r:id="rId68" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
-    <hyperlink ref="K45" r:id="rId69" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
-    <hyperlink ref="K20" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
-    <hyperlink ref="K21" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
-    <hyperlink ref="K94" r:id="rId72" xr:uid="{27E4829F-4D6C-4205-815B-E30709FE0551}"/>
-    <hyperlink ref="K95" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0C3D8311-8886-4EE9-8346-59E9A2212818}"/>
-    <hyperlink ref="K96" r:id="rId74" xr:uid="{6CB3210A-C53D-42FD-ADF5-DB6CD788DE2A}"/>
-    <hyperlink ref="K97" r:id="rId75" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B28112-49B9-4A12-A9FC-6929194008BD}"/>
-    <hyperlink ref="M97" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B81923-B3F5-4D27-8C90-D607D23DCA1E}"/>
-    <hyperlink ref="K89" r:id="rId77" xr:uid="{48F768EA-5F6B-4721-BE10-3381CFFF7617}"/>
-    <hyperlink ref="K90" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB3AA346-9023-4C65-A326-45854C985AC3}"/>
-    <hyperlink ref="K91" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3E9D42C5-EF64-4F37-BDFD-EF645728FB63}"/>
-    <hyperlink ref="K92" r:id="rId80" xr:uid="{D140917F-D470-4295-AC16-135E62B59912}"/>
-    <hyperlink ref="K19" r:id="rId81" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
-    <hyperlink ref="K18" r:id="rId82" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
-    <hyperlink ref="K10" r:id="rId83" xr:uid="{09752CE0-E1D3-4BF8-9D97-A49E8D002FC7}"/>
-    <hyperlink ref="K11" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{63C98BDE-FB8F-4FF9-A55C-03BAC1A02C63}"/>
-    <hyperlink ref="K12" r:id="rId85" xr:uid="{2380B890-0042-45CC-BEA4-783EA390EBF7}"/>
-    <hyperlink ref="K13" r:id="rId86" xr:uid="{AD077303-0EE9-4440-AAE6-BB84613C92BA}"/>
-    <hyperlink ref="K14" r:id="rId87" xr:uid="{8F9EE820-D8AA-4884-BB24-82C0C5D3CE2E}"/>
-    <hyperlink ref="K15" r:id="rId88" xr:uid="{22252FF4-27CC-40A3-8165-FA7B5CD19CDC}"/>
-    <hyperlink ref="K16" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96212E21-386F-4FCF-9A25-36D60D8078DF}"/>
-    <hyperlink ref="K17" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D9725C5-E9A1-4F23-B790-C7DC385208E5}"/>
-    <hyperlink ref="K75" r:id="rId91" xr:uid="{11A9B442-D6DF-429E-912B-50308BFE8E3D}"/>
-    <hyperlink ref="K76" r:id="rId92" xr:uid="{9A607AD9-733B-410B-B2B3-EFB415EA956D}"/>
-    <hyperlink ref="K77" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB732E30-93A4-4501-9799-59B7A6245041}"/>
-    <hyperlink ref="K78" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27EBDD53-9DEC-466F-B000-1FDCDA134FDC}"/>
-    <hyperlink ref="K80" r:id="rId95" xr:uid="{AA5F7287-2A04-4E9B-90FB-8E7A60BA0E9F}"/>
-    <hyperlink ref="K81" r:id="rId96" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4EF3173-817E-4A91-848F-7D2C11831473}"/>
-    <hyperlink ref="K82" r:id="rId97" xr:uid="{6284D82A-10EF-49D7-940E-00897AA75BB5}"/>
-    <hyperlink ref="K83" r:id="rId98" xr:uid="{DBEE44C4-CCCA-45E8-A66C-BF94EC30E034}"/>
-    <hyperlink ref="K2" r:id="rId99" xr:uid="{8B065BCD-2734-4507-991F-BC964964CB18}"/>
-    <hyperlink ref="K4" r:id="rId100" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg/960px-Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FEA8008D-9F5B-441C-84F7-155CCAB3D5BF}"/>
-    <hyperlink ref="K3" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg/960px-Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5621AFEB-68F3-4B18-95B3-0E55B258835D}"/>
-    <hyperlink ref="K5" r:id="rId102" xr:uid="{D324CD68-7A4C-4682-B6C0-EB2DEBD82B3E}"/>
-    <hyperlink ref="K6" r:id="rId103" xr:uid="{124DD613-D9C5-45A6-9C6E-5A94A110D732}"/>
-    <hyperlink ref="K7" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5CFEE07F-3AE1-4E17-8717-F5A1FACB33B9}"/>
-    <hyperlink ref="K8" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E585144F-91F4-4BE2-B00E-5A17CFAAEE37}"/>
-    <hyperlink ref="K9" r:id="rId106" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5286F62C-4DD5-41F9-8A33-916D65A4CBCB}"/>
-    <hyperlink ref="K32" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
-    <hyperlink ref="K31" r:id="rId108" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
-    <hyperlink ref="K30" r:id="rId109" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
-    <hyperlink ref="F29" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
-    <hyperlink ref="M29" r:id="rId111" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
-    <hyperlink ref="K29" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
-    <hyperlink ref="K28" r:id="rId113" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
-    <hyperlink ref="K23" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA50FD28-25AB-4C16-B704-4C1D4E291FC6}"/>
-    <hyperlink ref="K24" r:id="rId115" xr:uid="{AB5A3565-A8C2-4EB1-BF08-09469169F49B}"/>
-    <hyperlink ref="K25" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg/960px-Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{16AB1331-79AB-4AD1-82BF-411A6047FFC8}"/>
-    <hyperlink ref="K26" r:id="rId117" xr:uid="{8C66FE78-AD95-48B9-AFFB-A7A961701AB6}"/>
-    <hyperlink ref="K27" r:id="rId118" xr:uid="{BA7D0C74-4085-47D1-B949-A4D37E1B604C}"/>
-    <hyperlink ref="K36" r:id="rId119" xr:uid="{138404FE-5360-483C-9B6C-779679C072A6}"/>
-    <hyperlink ref="K37" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D549C045-BC59-46A9-BA82-994248896840}"/>
-    <hyperlink ref="K38" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD01D10D-9209-4700-8601-3904D1E7F113}"/>
-    <hyperlink ref="K39" r:id="rId122" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FA474B3-EF83-44FF-82A9-671D8D2F0D05}"/>
+    <hyperlink ref="K62" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="K63" r:id="rId4" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
+    <hyperlink ref="K64" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
+    <hyperlink ref="K65" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
+    <hyperlink ref="K103" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K86" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K66" r:id="rId9" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
+    <hyperlink ref="K67" r:id="rId10" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
+    <hyperlink ref="K68" r:id="rId11" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
+    <hyperlink ref="K69" r:id="rId12" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
+    <hyperlink ref="K70" r:id="rId13" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
+    <hyperlink ref="M70" r:id="rId14" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
+    <hyperlink ref="K71" r:id="rId15" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
+    <hyperlink ref="K72" r:id="rId16" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
+    <hyperlink ref="K73" r:id="rId17" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
+    <hyperlink ref="K74" r:id="rId18" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
+    <hyperlink ref="M74" r:id="rId19" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
+    <hyperlink ref="K75" r:id="rId20" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
+    <hyperlink ref="M75" r:id="rId21" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
+    <hyperlink ref="K76" r:id="rId22" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
+    <hyperlink ref="M76" r:id="rId23" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
+    <hyperlink ref="K77" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
+    <hyperlink ref="F76" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
+    <hyperlink ref="F77:F78" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
+    <hyperlink ref="M77" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
+    <hyperlink ref="M78" r:id="rId28" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
+    <hyperlink ref="K78" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
+    <hyperlink ref="K79" r:id="rId30" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
+    <hyperlink ref="F79" r:id="rId31" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
+    <hyperlink ref="F80" r:id="rId32" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
+    <hyperlink ref="K80" r:id="rId33" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
+    <hyperlink ref="K81" r:id="rId34" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
+    <hyperlink ref="H81" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
+    <hyperlink ref="K33" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
+    <hyperlink ref="K34" r:id="rId37" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
+    <hyperlink ref="K35" r:id="rId38" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
+    <hyperlink ref="K47" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
+    <hyperlink ref="K104" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
+    <hyperlink ref="L106" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
+    <hyperlink ref="K106" r:id="rId42" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
+    <hyperlink ref="K105" r:id="rId43" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
+    <hyperlink ref="K108" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
+    <hyperlink ref="K107" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
+    <hyperlink ref="M91" r:id="rId46" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
+    <hyperlink ref="K91" r:id="rId47" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
+    <hyperlink ref="K92" r:id="rId48" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
+    <hyperlink ref="K95" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
+    <hyperlink ref="K94" r:id="rId50" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
+    <hyperlink ref="K93" r:id="rId51" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
+    <hyperlink ref="K40" r:id="rId52" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
+    <hyperlink ref="K41" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
+    <hyperlink ref="K42" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
+    <hyperlink ref="K43" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
+    <hyperlink ref="K44" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
+    <hyperlink ref="K45" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
+    <hyperlink ref="K20" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
+    <hyperlink ref="K21" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
+    <hyperlink ref="K100" r:id="rId60" xr:uid="{27E4829F-4D6C-4205-815B-E30709FE0551}"/>
+    <hyperlink ref="K101" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0C3D8311-8886-4EE9-8346-59E9A2212818}"/>
+    <hyperlink ref="K102" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B28112-49B9-4A12-A9FC-6929194008BD}"/>
+    <hyperlink ref="M102" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B81923-B3F5-4D27-8C90-D607D23DCA1E}"/>
+    <hyperlink ref="K96" r:id="rId64" xr:uid="{48F768EA-5F6B-4721-BE10-3381CFFF7617}"/>
+    <hyperlink ref="K97" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB3AA346-9023-4C65-A326-45854C985AC3}"/>
+    <hyperlink ref="K98" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3E9D42C5-EF64-4F37-BDFD-EF645728FB63}"/>
+    <hyperlink ref="K99" r:id="rId67" xr:uid="{D140917F-D470-4295-AC16-135E62B59912}"/>
+    <hyperlink ref="K19" r:id="rId68" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
+    <hyperlink ref="K18" r:id="rId69" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
+    <hyperlink ref="K10" r:id="rId70" xr:uid="{09752CE0-E1D3-4BF8-9D97-A49E8D002FC7}"/>
+    <hyperlink ref="K11" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{63C98BDE-FB8F-4FF9-A55C-03BAC1A02C63}"/>
+    <hyperlink ref="K12" r:id="rId72" xr:uid="{2380B890-0042-45CC-BEA4-783EA390EBF7}"/>
+    <hyperlink ref="K13" r:id="rId73" xr:uid="{AD077303-0EE9-4440-AAE6-BB84613C92BA}"/>
+    <hyperlink ref="K14" r:id="rId74" xr:uid="{8F9EE820-D8AA-4884-BB24-82C0C5D3CE2E}"/>
+    <hyperlink ref="K15" r:id="rId75" xr:uid="{22252FF4-27CC-40A3-8165-FA7B5CD19CDC}"/>
+    <hyperlink ref="K16" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96212E21-386F-4FCF-9A25-36D60D8078DF}"/>
+    <hyperlink ref="K17" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D9725C5-E9A1-4F23-B790-C7DC385208E5}"/>
+    <hyperlink ref="K82" r:id="rId78" xr:uid="{11A9B442-D6DF-429E-912B-50308BFE8E3D}"/>
+    <hyperlink ref="K83" r:id="rId79" xr:uid="{9A607AD9-733B-410B-B2B3-EFB415EA956D}"/>
+    <hyperlink ref="K84" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB732E30-93A4-4501-9799-59B7A6245041}"/>
+    <hyperlink ref="K85" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27EBDD53-9DEC-466F-B000-1FDCDA134FDC}"/>
+    <hyperlink ref="K87" r:id="rId82" xr:uid="{AA5F7287-2A04-4E9B-90FB-8E7A60BA0E9F}"/>
+    <hyperlink ref="K88" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4EF3173-817E-4A91-848F-7D2C11831473}"/>
+    <hyperlink ref="K89" r:id="rId84" xr:uid="{6284D82A-10EF-49D7-940E-00897AA75BB5}"/>
+    <hyperlink ref="K90" r:id="rId85" xr:uid="{DBEE44C4-CCCA-45E8-A66C-BF94EC30E034}"/>
+    <hyperlink ref="K2" r:id="rId86" xr:uid="{8B065BCD-2734-4507-991F-BC964964CB18}"/>
+    <hyperlink ref="K4" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg/960px-Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FEA8008D-9F5B-441C-84F7-155CCAB3D5BF}"/>
+    <hyperlink ref="K3" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg/960px-Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5621AFEB-68F3-4B18-95B3-0E55B258835D}"/>
+    <hyperlink ref="K5" r:id="rId89" xr:uid="{D324CD68-7A4C-4682-B6C0-EB2DEBD82B3E}"/>
+    <hyperlink ref="K6" r:id="rId90" xr:uid="{124DD613-D9C5-45A6-9C6E-5A94A110D732}"/>
+    <hyperlink ref="K7" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5CFEE07F-3AE1-4E17-8717-F5A1FACB33B9}"/>
+    <hyperlink ref="K8" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E585144F-91F4-4BE2-B00E-5A17CFAAEE37}"/>
+    <hyperlink ref="K9" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5286F62C-4DD5-41F9-8A33-916D65A4CBCB}"/>
+    <hyperlink ref="K32" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
+    <hyperlink ref="K31" r:id="rId95" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
+    <hyperlink ref="K30" r:id="rId96" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
+    <hyperlink ref="F29" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
+    <hyperlink ref="M29" r:id="rId98" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
+    <hyperlink ref="K29" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
+    <hyperlink ref="K28" r:id="rId100" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
+    <hyperlink ref="K23" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA50FD28-25AB-4C16-B704-4C1D4E291FC6}"/>
+    <hyperlink ref="K24" r:id="rId102" xr:uid="{AB5A3565-A8C2-4EB1-BF08-09469169F49B}"/>
+    <hyperlink ref="K25" r:id="rId103" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg/960px-Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{16AB1331-79AB-4AD1-82BF-411A6047FFC8}"/>
+    <hyperlink ref="K26" r:id="rId104" xr:uid="{8C66FE78-AD95-48B9-AFFB-A7A961701AB6}"/>
+    <hyperlink ref="K27" r:id="rId105" xr:uid="{BA7D0C74-4085-47D1-B949-A4D37E1B604C}"/>
+    <hyperlink ref="K36" r:id="rId106" xr:uid="{138404FE-5360-483C-9B6C-779679C072A6}"/>
+    <hyperlink ref="K37" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D549C045-BC59-46A9-BA82-994248896840}"/>
+    <hyperlink ref="K38" r:id="rId108" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD01D10D-9209-4700-8601-3904D1E7F113}"/>
+    <hyperlink ref="K39" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FA474B3-EF83-44FF-82A9-671D8D2F0D05}"/>
+    <hyperlink ref="K48" r:id="rId110" xr:uid="{1102F7BD-BEB3-432C-BF66-1C542DA92A11}"/>
+    <hyperlink ref="K49" r:id="rId111" xr:uid="{E941035A-743A-4BB3-A198-E2C6C64768DE}"/>
+    <hyperlink ref="F50" r:id="rId112" xr:uid="{186096D7-8290-4E00-8A51-8F4DB6772A92}"/>
+    <hyperlink ref="K50" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DC007C0B-FC91-4D70-81C6-71AE180A6066}"/>
+    <hyperlink ref="K51" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{35475F33-DD52-4341-99A6-9FFFE0CE1407}"/>
+    <hyperlink ref="K52" r:id="rId115" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C95CE775-1BC4-448D-9BB5-A5F3AFF37602}"/>
+    <hyperlink ref="K53" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{28199704-DE62-4BF7-B087-8CA8F092680B}"/>
+    <hyperlink ref="K59" r:id="rId117" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{55915C9C-9DC5-4CBC-B294-CD0B4A57EB54}"/>
+    <hyperlink ref="K54" r:id="rId118" xr:uid="{D3AA1374-31B4-4C29-B3A8-2E62C72FE201}"/>
+    <hyperlink ref="K55" r:id="rId119" xr:uid="{718C90F6-4372-4C83-A3C0-372E7FA8C808}"/>
+    <hyperlink ref="K56" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E0266C44-5AAB-4155-8828-7810F8578068}"/>
+    <hyperlink ref="K57" r:id="rId121" xr:uid="{539A4D92-FAE4-47BE-9310-74149CD0754F}"/>
+    <hyperlink ref="K58" r:id="rId122" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A48AEBF3-B9CB-496A-9E64-FA4CBAB7718D}"/>
+    <hyperlink ref="L58" r:id="rId123" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{70F574BF-300A-4254-A4F5-2106359EEC2E}"/>
+    <hyperlink ref="K60" r:id="rId124" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9CA4BFBE-18AF-4C1E-93E7-366981D9081F}"/>
+    <hyperlink ref="K61" r:id="rId125" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{74906672-F576-4302-94A7-8CFF8BC00900}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07A07B39-EEBB-4303-B4AC-457EFB9314C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{715BB256-BA64-4E65-B10F-A0618A55CA7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="647">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1192" uniqueCount="621">
   <si>
     <t>Patronyme artiste</t>
   </si>
@@ -281,75 +281,18 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
   <si>
-    <t>Michelozzo</t>
-  </si>
-  <si>
-    <t>di BARTOLOMEO</t>
-  </si>
-  <si>
-    <t>1422-1428</t>
-  </si>
-  <si>
-    <t>Baptistère de Florence</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/69/Grabmaljohannes13.jpg/1280px-Grabmaljohannes13.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Bronze et marbre</t>
-  </si>
-  <si>
-    <t>Agostino</t>
-  </si>
-  <si>
-    <t>di DUCCIO</t>
-  </si>
-  <si>
-    <t>1450s</t>
-  </si>
-  <si>
-    <t>Rimini</t>
-  </si>
-  <si>
-    <t>Tempio Malatestiano</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/d/db/Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg/1280px-Milano_-_Agostino_di_Duccio_%281418-1481%29_-_Allegoria_-_dal_Tempio_Malatestiano_-_Foto_Giovanni_Dall%27Orto_-_6-jan-2007_-_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Francesco</t>
   </si>
   <si>
-    <t>di GIORGIO MARTINI</t>
-  </si>
-  <si>
-    <t>1488-1490</t>
-  </si>
-  <si>
     <t>Paris</t>
   </si>
   <si>
     <t>Musée du Louvre</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/3/39/Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG/1280px-Francesco_di_giorgio_martini%2C_san_cristoforo%2C_1488-90%2C_da_s._agostino_a_siena.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Bois polychrome et doré</t>
-  </si>
-  <si>
-    <t>Bertoldo</t>
-  </si>
-  <si>
-    <t>di GIOVANNI</t>
-  </si>
-  <si>
     <t>1475-1480</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/7f/Bertoldo_di_giovanni%2C_orfeo_o_apollo%2C_1475-80_01.JPG/1280px-Bertoldo_di_giovanni%2C_orfeo_o_apollo%2C_1475-80_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
     <t>Donato</t>
   </si>
   <si>
@@ -1769,9 +1712,6 @@
     <t>Elément architectural</t>
   </si>
   <si>
-    <t>"Allégorie "</t>
-  </si>
-  <si>
     <t>Ensemble architectural</t>
   </si>
   <si>
@@ -1781,12 +1721,6 @@
     <t>Le Triomphe d'Alphonse d'Aragon</t>
   </si>
   <si>
-    <t>"Orphée ou Apollon "</t>
-  </si>
-  <si>
-    <t>"Saint Christophe"</t>
-  </si>
-  <si>
     <t xml:space="preserve">David avec la tête de Goliath </t>
   </si>
   <si>
@@ -1937,15 +1871,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>96 bas-reliefs</t>
-  </si>
-  <si>
-    <t>110 à 120</t>
-  </si>
-  <si>
-    <t>65 à 75</t>
-  </si>
-  <si>
     <t>340 (statue) 800 (socle)</t>
   </si>
   <si>
@@ -1971,9 +1896,6 @@
   </si>
   <si>
     <t>1474-1475</t>
-  </si>
-  <si>
-    <t>"Tombeau du pape  Jean XXIII "</t>
   </si>
 </sst>
 </file>
@@ -2350,19 +2272,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V108"/>
+  <dimension ref="A1:V104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.140625" customWidth="1"/>
-    <col min="2" max="2" width="24.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.42578125" style="5" customWidth="1"/>
-    <col min="9" max="9" width="47" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="3" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="1.85546875" customWidth="1"/>
+    <col min="7" max="7" width="1.85546875" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" customWidth="1"/>
+    <col min="10" max="10" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="2.7109375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.5703125" customWidth="1"/>
+    <col min="13" max="13" width="2.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="9.42578125" customWidth="1"/>
     <col min="16" max="16" width="1" customWidth="1"/>
     <col min="17" max="17" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="19" max="22" width="9.140625" style="2"/>
+    <col min="18" max="18" width="6.140625" customWidth="1"/>
+    <col min="19" max="19" width="2.140625" style="2" customWidth="1"/>
+    <col min="20" max="22" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2447,19 +2377,19 @@
         <v>25</v>
       </c>
       <c r="I2" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="J2" t="s">
-        <v>508</v>
+        <v>489</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>26</v>
       </c>
       <c r="O2" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q2" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="R2" t="s">
         <v>27</v>
@@ -2491,22 +2421,22 @@
         <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>509</v>
+        <v>490</v>
       </c>
       <c r="I3" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>511</v>
+        <v>492</v>
       </c>
       <c r="O3" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="Q3" t="s">
-        <v>512</v>
+        <v>493</v>
       </c>
       <c r="R3" t="s">
-        <v>513</v>
+        <v>494</v>
       </c>
       <c r="S3" s="2">
         <v>400</v>
@@ -2526,28 +2456,28 @@
         <v>1490</v>
       </c>
       <c r="D4" t="s">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="E4" t="s">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="I4" t="s">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="J4" t="s">
-        <v>517</v>
+        <v>498</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="O4" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="Q4" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="R4" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="S4" s="2">
         <v>24</v>
@@ -2567,28 +2497,28 @@
         <v>22</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="D5" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="E5" t="s">
-        <v>519</v>
+        <v>500</v>
       </c>
       <c r="I5" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="J5" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>521</v>
+        <v>502</v>
       </c>
       <c r="O5" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="Q5" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R5" t="s">
         <v>30</v>
@@ -2603,7 +2533,7 @@
         <v>15</v>
       </c>
       <c r="V5" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2617,22 +2547,22 @@
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="E6" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="I6" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="J6" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>34</v>
       </c>
       <c r="O6" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R6" t="s">
         <v>30</v>
@@ -2644,7 +2574,7 @@
         <v>300</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2655,31 +2585,31 @@
         <v>32</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>524</v>
+        <v>505</v>
       </c>
       <c r="D7" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="E7" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="I7" t="s">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="J7" t="s">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="O7" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R7" t="s">
         <v>30</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2690,31 +2620,31 @@
         <v>32</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="D8" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="E8" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="I8" t="s">
-        <v>529</v>
+        <v>510</v>
       </c>
       <c r="J8" t="s">
-        <v>530</v>
+        <v>511</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>531</v>
+        <v>512</v>
       </c>
       <c r="O8" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="R8" t="s">
-        <v>532</v>
+        <v>513</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2725,31 +2655,31 @@
         <v>32</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="D9" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="E9" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="I9" t="s">
-        <v>533</v>
+        <v>514</v>
       </c>
       <c r="J9" t="s">
-        <v>534</v>
+        <v>515</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>535</v>
+        <v>516</v>
       </c>
       <c r="O9" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2766,22 +2696,22 @@
         <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I10" t="s">
-        <v>444</v>
+        <v>425</v>
       </c>
       <c r="J10" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>40</v>
       </c>
       <c r="O10" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q10" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="R10" t="s">
         <v>30</v>
@@ -2796,7 +2726,7 @@
         <v>23</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2807,28 +2737,28 @@
         <v>36</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>447</v>
+        <v>428</v>
       </c>
       <c r="D11" t="s">
         <v>38</v>
       </c>
       <c r="E11" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I11" t="s">
-        <v>448</v>
+        <v>429</v>
       </c>
       <c r="J11" t="s">
-        <v>449</v>
+        <v>430</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>450</v>
+        <v>431</v>
       </c>
       <c r="O11" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q11" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="R11" t="s">
         <v>30</v>
@@ -2843,7 +2773,7 @@
         <v>24</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2854,28 +2784,28 @@
         <v>36</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="D12" t="s">
         <v>38</v>
       </c>
       <c r="E12" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I12" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="J12" t="s">
-        <v>453</v>
+        <v>434</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>454</v>
+        <v>435</v>
       </c>
       <c r="O12" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q12" t="s">
-        <v>446</v>
+        <v>427</v>
       </c>
       <c r="R12" t="s">
         <v>30</v>
@@ -2887,7 +2817,7 @@
         <v>40</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2898,34 +2828,34 @@
         <v>36</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>455</v>
+        <v>436</v>
       </c>
       <c r="D13" t="s">
         <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="I13" t="s">
-        <v>456</v>
+        <v>437</v>
       </c>
       <c r="J13" t="s">
-        <v>457</v>
+        <v>438</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>458</v>
+        <v>439</v>
       </c>
       <c r="O13" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="Q13" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R13" t="s">
         <v>30</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2945,16 +2875,16 @@
         <v>44</v>
       </c>
       <c r="I14" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="J14" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>45</v>
       </c>
       <c r="O14" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
@@ -2980,28 +2910,28 @@
         <v>42</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="D15" t="s">
         <v>38</v>
       </c>
       <c r="E15" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I15" t="s">
-        <v>462</v>
+        <v>443</v>
       </c>
       <c r="J15" t="s">
-        <v>463</v>
+        <v>444</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>464</v>
+        <v>445</v>
       </c>
       <c r="O15" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q15" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
@@ -3024,28 +2954,28 @@
         <v>42</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="D16" t="s">
         <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="I16" t="s">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="J16" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>465</v>
+        <v>446</v>
       </c>
       <c r="O16" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q16" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
@@ -3065,28 +2995,28 @@
         <v>42</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>467</v>
+        <v>448</v>
       </c>
       <c r="D17" t="s">
-        <v>468</v>
+        <v>449</v>
       </c>
       <c r="E17" t="s">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="I17" t="s">
-        <v>469</v>
+        <v>450</v>
       </c>
       <c r="J17" t="s">
-        <v>470</v>
+        <v>451</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>471</v>
+        <v>452</v>
       </c>
       <c r="O17" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="Q17" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R17" t="s">
         <v>30</v>
@@ -3115,16 +3045,16 @@
         <v>50</v>
       </c>
       <c r="I18" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="J18" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>51</v>
       </c>
       <c r="O18" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R18" t="s">
         <v>30</v>
@@ -3150,7 +3080,7 @@
         <v>47</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>400</v>
+        <v>381</v>
       </c>
       <c r="D19" t="s">
         <v>38</v>
@@ -3159,16 +3089,16 @@
         <v>44</v>
       </c>
       <c r="I19" t="s">
-        <v>401</v>
+        <v>382</v>
       </c>
       <c r="J19" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>403</v>
+        <v>384</v>
       </c>
       <c r="O19" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R19" t="s">
         <v>30</v>
@@ -3191,25 +3121,25 @@
         <v>47</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="D20" t="s">
         <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="I20" t="s">
-        <v>405</v>
+        <v>386</v>
       </c>
       <c r="J20" t="s">
-        <v>406</v>
+        <v>387</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>407</v>
+        <v>388</v>
       </c>
       <c r="O20" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="R20" t="s">
         <v>30</v>
@@ -3232,22 +3162,22 @@
         <v>47</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>588</v>
+        <v>566</v>
       </c>
       <c r="D21" t="s">
         <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I21" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>408</v>
+        <v>389</v>
       </c>
       <c r="O21" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R21" t="s">
         <v>30</v>
@@ -3267,7 +3197,7 @@
         <v>53</v>
       </c>
       <c r="B22" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>54</v>
@@ -3285,7 +3215,7 @@
         <v>58</v>
       </c>
       <c r="O22" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R22" t="s">
         <v>27</v>
@@ -3308,34 +3238,34 @@
         <v>53</v>
       </c>
       <c r="B23" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>536</v>
+        <v>517</v>
       </c>
       <c r="D23" t="s">
         <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>537</v>
+        <v>518</v>
       </c>
       <c r="I23" t="s">
-        <v>538</v>
+        <v>519</v>
       </c>
       <c r="J23" t="s">
-        <v>539</v>
+        <v>520</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>540</v>
+        <v>521</v>
       </c>
       <c r="O23" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R23" t="s">
         <v>27</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>541</v>
+        <v>522</v>
       </c>
       <c r="T23" s="2">
         <v>230</v>
@@ -3352,34 +3282,34 @@
         <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D24" t="s">
         <v>38</v>
       </c>
       <c r="E24" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I24" t="s">
-        <v>543</v>
+        <v>524</v>
       </c>
       <c r="J24" t="s">
-        <v>544</v>
+        <v>525</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>545</v>
+        <v>526</v>
       </c>
       <c r="O24" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R24" t="s">
         <v>27</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>546</v>
+        <v>527</v>
       </c>
       <c r="T24" s="2">
         <v>34</v>
@@ -3396,31 +3326,31 @@
         <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>547</v>
+        <v>528</v>
       </c>
       <c r="D25" t="s">
         <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I25" t="s">
-        <v>548</v>
+        <v>529</v>
       </c>
       <c r="J25" t="s">
-        <v>549</v>
+        <v>530</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="O25" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R25" t="s">
-        <v>551</v>
+        <v>532</v>
       </c>
       <c r="S25" s="2">
         <v>52</v>
@@ -3440,31 +3370,31 @@
         <v>53</v>
       </c>
       <c r="B26" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>552</v>
+        <v>533</v>
       </c>
       <c r="D26" t="s">
         <v>38</v>
       </c>
       <c r="E26" t="s">
-        <v>553</v>
+        <v>534</v>
       </c>
       <c r="I26" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="J26" t="s">
-        <v>554</v>
+        <v>535</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="O26" t="s">
-        <v>575</v>
+        <v>556</v>
       </c>
       <c r="R26" t="s">
-        <v>556</v>
+        <v>537</v>
       </c>
       <c r="S26" s="2">
         <v>193</v>
@@ -3484,7 +3414,7 @@
         <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>559</v>
+        <v>540</v>
       </c>
       <c r="C27" s="5">
         <v>1480</v>
@@ -3496,13 +3426,13 @@
         <v>50</v>
       </c>
       <c r="I27" t="s">
-        <v>557</v>
+        <v>538</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>558</v>
+        <v>539</v>
       </c>
       <c r="O27" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R27" t="s">
         <v>27</v>
@@ -3534,22 +3464,22 @@
         <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I28" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="J28" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="O28" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q28" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R28" t="s">
         <v>27</v>
@@ -3564,7 +3494,7 @@
         <v>41</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3575,37 +3505,37 @@
         <v>59</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>240</v>
+        <v>221</v>
       </c>
       <c r="D29" t="s">
         <v>38</v>
       </c>
       <c r="E29" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>205</v>
+        <v>186</v>
       </c>
       <c r="I29" t="s">
-        <v>241</v>
+        <v>222</v>
       </c>
       <c r="J29" t="s">
-        <v>242</v>
+        <v>223</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>243</v>
+        <v>224</v>
       </c>
       <c r="L29" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="O29" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q29" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="R29" t="s">
         <v>27</v>
@@ -3620,7 +3550,7 @@
         <v>75</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3631,34 +3561,34 @@
         <v>59</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="D30" t="s">
         <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="I30" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="J30" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="O30" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q30" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="R30" t="s">
         <v>27</v>
       </c>
       <c r="S30" s="2" t="s">
-        <v>589</v>
+        <v>567</v>
       </c>
       <c r="T30" s="2">
         <v>380</v>
@@ -3667,7 +3597,7 @@
         <v>145</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3678,31 +3608,31 @@
         <v>59</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>253</v>
+        <v>234</v>
       </c>
       <c r="D31" t="s">
         <v>38</v>
       </c>
       <c r="E31" t="s">
-        <v>254</v>
+        <v>235</v>
       </c>
       <c r="I31" t="s">
-        <v>255</v>
+        <v>236</v>
       </c>
       <c r="J31" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="L31" t="s">
-        <v>258</v>
+        <v>239</v>
       </c>
       <c r="O31" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q31" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="R31" t="s">
         <v>27</v>
@@ -3717,7 +3647,7 @@
         <v>45</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3728,28 +3658,28 @@
         <v>59</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="D32" t="s">
         <v>38</v>
       </c>
       <c r="E32" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I32" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="J32" t="s">
-        <v>262</v>
+        <v>243</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>263</v>
+        <v>244</v>
       </c>
       <c r="O32" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q32" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="R32" t="s">
         <v>30</v>
@@ -3775,34 +3705,34 @@
         <v>59</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>265</v>
+        <v>246</v>
       </c>
       <c r="D33" t="s">
         <v>38</v>
       </c>
       <c r="E33" t="s">
-        <v>266</v>
+        <v>247</v>
       </c>
       <c r="G33" t="s">
-        <v>267</v>
+        <v>248</v>
       </c>
       <c r="I33" t="s">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="J33" t="s">
-        <v>269</v>
+        <v>250</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>270</v>
+        <v>251</v>
       </c>
       <c r="O33" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="Q33" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R33" t="s">
-        <v>272</v>
+        <v>253</v>
       </c>
       <c r="S33" s="2">
         <v>540</v>
@@ -3822,31 +3752,31 @@
         <v>59</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>273</v>
+        <v>254</v>
       </c>
       <c r="D34" t="s">
         <v>38</v>
       </c>
       <c r="E34" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I34" t="s">
-        <v>590</v>
+        <v>568</v>
       </c>
       <c r="J34" t="s">
-        <v>274</v>
+        <v>255</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>275</v>
+        <v>256</v>
       </c>
       <c r="O34" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q34" t="s">
-        <v>264</v>
+        <v>245</v>
       </c>
       <c r="R34" t="s">
-        <v>276</v>
+        <v>257</v>
       </c>
       <c r="S34" s="2">
         <v>61</v>
@@ -3869,34 +3799,34 @@
         <v>59</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="D35" t="s">
         <v>38</v>
       </c>
       <c r="E35" t="s">
-        <v>542</v>
+        <v>523</v>
       </c>
       <c r="I35" t="s">
-        <v>278</v>
+        <v>259</v>
       </c>
       <c r="J35" t="s">
-        <v>279</v>
+        <v>260</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="L35" t="s">
-        <v>281</v>
+        <v>262</v>
       </c>
       <c r="O35" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="Q35" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="R35" t="s">
-        <v>282</v>
+        <v>263</v>
       </c>
       <c r="S35" s="2">
         <v>21</v>
@@ -3925,19 +3855,19 @@
         <v>64</v>
       </c>
       <c r="E36" t="s">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="I36" t="s">
-        <v>520</v>
+        <v>501</v>
       </c>
       <c r="J36" t="s">
-        <v>493</v>
+        <v>474</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>65</v>
       </c>
       <c r="O36" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="R36" t="s">
         <v>66</v>
@@ -3963,28 +3893,28 @@
         <v>62</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>560</v>
+        <v>541</v>
       </c>
       <c r="D37" t="s">
         <v>64</v>
       </c>
       <c r="E37" t="s">
-        <v>561</v>
+        <v>542</v>
       </c>
       <c r="G37" t="s">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="I37" t="s">
-        <v>563</v>
+        <v>544</v>
       </c>
       <c r="J37" t="s">
-        <v>564</v>
+        <v>545</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>565</v>
+        <v>546</v>
       </c>
       <c r="O37" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R37" t="s">
         <v>30</v>
@@ -4010,25 +3940,25 @@
         <v>62</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="D38" t="s">
         <v>64</v>
       </c>
       <c r="E38" t="s">
-        <v>566</v>
+        <v>547</v>
       </c>
       <c r="I38" t="s">
-        <v>567</v>
+        <v>548</v>
       </c>
       <c r="J38" t="s">
-        <v>568</v>
+        <v>549</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
       <c r="O38" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R38" t="s">
         <v>66</v>
@@ -4054,25 +3984,25 @@
         <v>62</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>277</v>
+        <v>258</v>
       </c>
       <c r="D39" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>570</v>
+        <v>551</v>
       </c>
       <c r="I39" t="s">
-        <v>571</v>
+        <v>552</v>
       </c>
       <c r="J39" t="s">
-        <v>572</v>
+        <v>553</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>573</v>
+        <v>554</v>
       </c>
       <c r="O39" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R39" t="s">
         <v>66</v>
@@ -4107,22 +4037,22 @@
         <v>71</v>
       </c>
       <c r="G40" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="I40" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="J40" t="s">
-        <v>367</v>
+        <v>348</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>72</v>
       </c>
       <c r="O40" t="s">
-        <v>596</v>
+        <v>574</v>
       </c>
       <c r="Q40" t="s">
-        <v>368</v>
+        <v>349</v>
       </c>
       <c r="R40" t="s">
         <v>30</v>
@@ -4148,28 +4078,28 @@
         <v>68</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="D41" t="s">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="E41" t="s">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="I41" t="s">
-        <v>372</v>
+        <v>353</v>
       </c>
       <c r="J41" t="s">
-        <v>373</v>
+        <v>354</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>374</v>
+        <v>355</v>
       </c>
       <c r="O41" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="Q41" t="s">
-        <v>375</v>
+        <v>356</v>
       </c>
       <c r="R41" t="s">
         <v>30</v>
@@ -4195,34 +4125,34 @@
         <v>68</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="D42" t="s">
         <v>64</v>
       </c>
       <c r="E42" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="G42" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="I42" t="s">
-        <v>597</v>
+        <v>575</v>
       </c>
       <c r="J42" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="O42" t="s">
-        <v>598</v>
+        <v>576</v>
       </c>
       <c r="Q42" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="R42" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="S42" s="2">
         <v>1800</v>
@@ -4245,37 +4175,37 @@
         <v>68</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="D43" t="s">
         <v>64</v>
       </c>
       <c r="E43" t="s">
-        <v>377</v>
+        <v>358</v>
       </c>
       <c r="G43" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="I43" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="J43" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="L43" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="O43" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="Q43" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="R43" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="S43" s="2">
         <v>99</v>
@@ -4298,31 +4228,31 @@
         <v>68</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="D44" t="s">
+        <v>351</v>
+      </c>
+      <c r="E44" t="s">
+        <v>369</v>
+      </c>
+      <c r="G44" t="s">
         <v>370</v>
       </c>
-      <c r="E44" t="s">
-        <v>388</v>
-      </c>
-      <c r="G44" t="s">
-        <v>389</v>
-      </c>
       <c r="I44" t="s">
-        <v>390</v>
+        <v>371</v>
       </c>
       <c r="J44" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>392</v>
+        <v>373</v>
       </c>
       <c r="O44" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="Q44" t="s">
-        <v>393</v>
+        <v>374</v>
       </c>
       <c r="R44" t="s">
         <v>30</v>
@@ -4345,31 +4275,31 @@
         <v>68</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="D45" t="s">
+        <v>351</v>
+      </c>
+      <c r="E45" t="s">
+        <v>369</v>
+      </c>
+      <c r="G45" t="s">
         <v>370</v>
       </c>
-      <c r="E45" t="s">
-        <v>388</v>
-      </c>
-      <c r="G45" t="s">
-        <v>389</v>
-      </c>
       <c r="I45" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="J45" t="s">
-        <v>395</v>
+        <v>376</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="O45" t="s">
-        <v>601</v>
+        <v>579</v>
       </c>
       <c r="Q45" t="s">
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="R45" t="s">
         <v>30</v>
@@ -4401,13 +4331,13 @@
         <v>75</v>
       </c>
       <c r="I46" t="s">
-        <v>576</v>
+        <v>557</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>76</v>
       </c>
       <c r="O46" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R46" t="s">
         <v>77</v>
@@ -4433,28 +4363,28 @@
         <v>73</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="D47" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E47" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I47" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="J47" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="O47" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R47" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S47" s="2">
         <v>118</v>
@@ -4480,25 +4410,25 @@
         <v>1475</v>
       </c>
       <c r="D48" t="s">
-        <v>602</v>
+        <v>580</v>
       </c>
       <c r="E48" t="s">
-        <v>603</v>
+        <v>581</v>
       </c>
       <c r="I48" t="s">
-        <v>604</v>
+        <v>582</v>
       </c>
       <c r="J48" t="s">
-        <v>605</v>
+        <v>583</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>606</v>
+        <v>584</v>
       </c>
       <c r="O48" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R48" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S48" s="2">
         <v>80</v>
@@ -4521,7 +4451,7 @@
         <v>73</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="D49" t="s">
         <v>38</v>
@@ -4530,19 +4460,19 @@
         <v>44</v>
       </c>
       <c r="I49" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="J49" t="s">
-        <v>608</v>
+        <v>586</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="O49" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R49" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S49" s="2">
         <v>270</v>
@@ -4568,25 +4498,25 @@
         <v>1489</v>
       </c>
       <c r="D50" t="s">
-        <v>610</v>
+        <v>588</v>
       </c>
       <c r="E50" t="s">
-        <v>611</v>
+        <v>589</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="I50" t="s">
-        <v>613</v>
+        <v>591</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>614</v>
+        <v>592</v>
       </c>
       <c r="O50" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R50" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S50" s="2">
         <v>163</v>
@@ -4609,31 +4539,31 @@
         <v>73</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>615</v>
+        <v>593</v>
       </c>
       <c r="D51" t="s">
-        <v>616</v>
+        <v>594</v>
       </c>
       <c r="E51" t="s">
-        <v>617</v>
+        <v>595</v>
       </c>
       <c r="I51" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="J51" t="s">
-        <v>619</v>
+        <v>597</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="O51" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R51" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S51" s="2" t="s">
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="T51" s="2">
         <v>210</v>
@@ -4653,28 +4583,28 @@
         <v>73</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>528</v>
+        <v>509</v>
       </c>
       <c r="D52" t="s">
-        <v>414</v>
+        <v>395</v>
       </c>
       <c r="E52" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="I52" t="s">
-        <v>623</v>
+        <v>601</v>
       </c>
       <c r="J52" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="O52" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R52" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S52" s="2">
         <v>370</v>
@@ -4703,19 +4633,19 @@
         <v>38</v>
       </c>
       <c r="E53" t="s">
-        <v>626</v>
+        <v>604</v>
       </c>
       <c r="I53" t="s">
-        <v>627</v>
+        <v>605</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="O53" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R53" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S53" s="2">
         <v>44</v>
@@ -4747,16 +4677,16 @@
         <v>80</v>
       </c>
       <c r="I54" t="s">
-        <v>283</v>
+        <v>264</v>
       </c>
       <c r="J54" t="s">
-        <v>284</v>
+        <v>265</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>81</v>
       </c>
       <c r="O54" t="s">
-        <v>577</v>
+        <v>558</v>
       </c>
       <c r="R54" t="s">
         <v>30</v>
@@ -4782,28 +4712,28 @@
         <v>73</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="D55" t="s">
         <v>38</v>
       </c>
       <c r="E55" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="I55" t="s">
-        <v>286</v>
+        <v>267</v>
       </c>
       <c r="J55" t="s">
-        <v>287</v>
+        <v>268</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>288</v>
+        <v>269</v>
       </c>
       <c r="O55" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R55" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S55" s="2">
         <v>200</v>
@@ -4815,7 +4745,7 @@
         <v>18</v>
       </c>
       <c r="V55" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="56" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4826,25 +4756,25 @@
         <v>73</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="D56" t="s">
         <v>38</v>
       </c>
       <c r="E56" t="s">
-        <v>233</v>
+        <v>214</v>
       </c>
       <c r="I56" t="s">
-        <v>291</v>
+        <v>272</v>
       </c>
       <c r="J56" t="s">
-        <v>292</v>
+        <v>273</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="O56" t="s">
-        <v>630</v>
+        <v>608</v>
       </c>
       <c r="R56" t="s">
         <v>27</v>
@@ -4859,7 +4789,7 @@
         <v>8</v>
       </c>
       <c r="V56" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="57" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4870,28 +4800,28 @@
         <v>73</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>132</v>
+        <v>113</v>
       </c>
       <c r="D57" t="s">
         <v>38</v>
       </c>
       <c r="E57" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="I57" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="J57" t="s">
-        <v>296</v>
+        <v>277</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>297</v>
+        <v>278</v>
       </c>
       <c r="O57" t="s">
-        <v>631</v>
+        <v>609</v>
       </c>
       <c r="R57" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="T57" s="2">
         <v>120</v>
@@ -4900,7 +4830,7 @@
         <v>12</v>
       </c>
       <c r="V57" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="58" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4911,31 +4841,31 @@
         <v>73</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D58" t="s">
-        <v>298</v>
+        <v>279</v>
       </c>
       <c r="E58" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="I58" t="s">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="J58" t="s">
-        <v>301</v>
+        <v>282</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>302</v>
+        <v>283</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="O58" t="s">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="R58" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S58" s="2">
         <v>150</v>
@@ -4947,7 +4877,7 @@
         <v>15</v>
       </c>
       <c r="V58" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="59" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -4958,28 +4888,28 @@
         <v>73</v>
       </c>
       <c r="C59" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="D59" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
       <c r="E59" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="I59" t="s">
-        <v>305</v>
+        <v>286</v>
       </c>
       <c r="J59" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>307</v>
+        <v>288</v>
       </c>
       <c r="O59" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R59" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S59" s="2">
         <v>118</v>
@@ -4991,7 +4921,7 @@
         <v>16</v>
       </c>
       <c r="V59" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="60" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5002,7 +4932,7 @@
         <v>73</v>
       </c>
       <c r="C60" t="s">
-        <v>304</v>
+        <v>285</v>
       </c>
       <c r="D60" t="s">
         <v>38</v>
@@ -5011,25 +4941,25 @@
         <v>39</v>
       </c>
       <c r="I60" t="s">
-        <v>440</v>
+        <v>421</v>
       </c>
       <c r="J60" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="K60" s="1" t="s">
-        <v>629</v>
+        <v>607</v>
       </c>
       <c r="O60" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R60" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S60" s="2">
         <v>57</v>
       </c>
       <c r="V60" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="61" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5040,7 +4970,7 @@
         <v>73</v>
       </c>
       <c r="C61" t="s">
-        <v>285</v>
+        <v>266</v>
       </c>
       <c r="D61" t="s">
         <v>38</v>
@@ -5049,19 +4979,19 @@
         <v>39</v>
       </c>
       <c r="I61" t="s">
-        <v>632</v>
+        <v>610</v>
       </c>
       <c r="J61" t="s">
-        <v>441</v>
+        <v>422</v>
       </c>
       <c r="K61" s="6" t="s">
-        <v>633</v>
+        <v>611</v>
       </c>
       <c r="O61" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="R61" t="s">
-        <v>289</v>
+        <v>270</v>
       </c>
       <c r="S61" s="2">
         <v>70</v>
@@ -5070,488 +5000,518 @@
         <v>52</v>
       </c>
       <c r="V61" s="2" t="s">
-        <v>150</v>
+        <v>131</v>
       </c>
     </row>
     <row r="62" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B62" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+      <c r="D62" t="s">
+        <v>38</v>
       </c>
       <c r="E62" t="s">
-        <v>85</v>
+        <v>523</v>
       </c>
       <c r="I62" t="s">
-        <v>646</v>
+        <v>127</v>
+      </c>
+      <c r="J62" t="s">
+        <v>128</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="O62" t="s">
-        <v>271</v>
+        <v>129</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>129</v>
       </c>
       <c r="R62" t="s">
-        <v>87</v>
-      </c>
-      <c r="S62" s="2">
-        <v>732</v>
+        <v>27</v>
+      </c>
+      <c r="S62" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="T62" s="2">
-        <v>250</v>
+        <v>51</v>
       </c>
       <c r="U62" s="2">
-        <v>95</v>
-      </c>
-      <c r="V62" s="2">
-        <v>3</v>
+        <v>42</v>
+      </c>
+      <c r="V62" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="63" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="D63" t="s">
-        <v>91</v>
+        <v>38</v>
       </c>
       <c r="E63" t="s">
-        <v>92</v>
+        <v>523</v>
       </c>
       <c r="I63" t="s">
-        <v>578</v>
+        <v>127</v>
+      </c>
+      <c r="J63" t="s">
+        <v>133</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>93</v>
+        <v>134</v>
       </c>
       <c r="O63" t="s">
-        <v>634</v>
+        <v>129</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>129</v>
       </c>
       <c r="R63" t="s">
         <v>30</v>
       </c>
       <c r="S63" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="T63" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="U63" s="2">
-        <v>4</v>
-      </c>
-      <c r="V63" s="2">
-        <v>3</v>
+        <v>135</v>
+      </c>
+      <c r="T63" s="2">
+        <v>57</v>
+      </c>
+      <c r="V63" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="64" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="B64" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="D64" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="E64" t="s">
-        <v>98</v>
+        <v>523</v>
       </c>
       <c r="I64" t="s">
-        <v>583</v>
+        <v>137</v>
+      </c>
+      <c r="J64" t="s">
+        <v>138</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="O64" t="s">
-        <v>148</v>
+        <v>129</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>129</v>
       </c>
       <c r="R64" t="s">
-        <v>100</v>
-      </c>
-      <c r="S64" s="2">
-        <v>163</v>
+        <v>30</v>
+      </c>
+      <c r="S64" s="2" t="s">
+        <v>140</v>
       </c>
       <c r="T64" s="2">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="U64" s="2">
         <v>53</v>
       </c>
-      <c r="V64" s="2">
-        <v>3</v>
+      <c r="V64" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="65" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="D65" t="s">
         <v>38</v>
       </c>
       <c r="E65" t="s">
-        <v>542</v>
+        <v>142</v>
       </c>
       <c r="I65" t="s">
-        <v>582</v>
+        <v>143</v>
+      </c>
+      <c r="J65" t="s">
+        <v>144</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="O65" t="s">
-        <v>148</v>
+        <v>129</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>129</v>
       </c>
       <c r="R65" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S65" s="2">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c r="T65" s="2">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="U65" s="2">
-        <v>15</v>
-      </c>
-      <c r="V65" s="2">
-        <v>3</v>
+        <v>60</v>
+      </c>
+      <c r="V65" s="2" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="66" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B66" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="D66" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E66" t="s">
-        <v>542</v>
+        <v>147</v>
       </c>
       <c r="I66" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="J66" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>108</v>
+        <v>150</v>
+      </c>
+      <c r="L66" t="s">
+        <v>151</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="O66" t="s">
-        <v>148</v>
+        <v>424</v>
       </c>
       <c r="Q66" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="R66" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="S66" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="T66" s="2">
-        <v>51</v>
+        <v>154</v>
+      </c>
+      <c r="T66" s="2" t="s">
+        <v>154</v>
       </c>
       <c r="U66" s="2">
-        <v>42</v>
-      </c>
-      <c r="V66" s="2" t="s">
-        <v>150</v>
+        <v>7</v>
+      </c>
+      <c r="V66" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D67" t="s">
         <v>38</v>
       </c>
       <c r="E67" t="s">
-        <v>542</v>
+        <v>44</v>
       </c>
       <c r="I67" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="J67" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O67" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q67" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R67" t="s">
+        <v>159</v>
+      </c>
+      <c r="S67" s="2">
+        <v>420</v>
+      </c>
+      <c r="T67" s="2">
+        <v>274</v>
+      </c>
+      <c r="U67" s="2">
         <v>30</v>
       </c>
-      <c r="S67" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="T67" s="2">
-        <v>57</v>
-      </c>
-      <c r="V67" s="2" t="s">
-        <v>150</v>
+      <c r="V67" s="2">
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B68" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="E68" t="s">
-        <v>542</v>
+        <v>162</v>
       </c>
       <c r="I68" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="J68" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="O68" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q68" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R68" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="S68" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="T68" s="2">
-        <v>64</v>
-      </c>
-      <c r="U68" s="2">
-        <v>53</v>
-      </c>
-      <c r="V68" s="2" t="s">
-        <v>150</v>
+        <v>612</v>
+      </c>
+      <c r="T68" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="V68" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>105</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="D69" t="s">
         <v>38</v>
       </c>
       <c r="E69" t="s">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="I69" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="J69" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="O69" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q69" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="R69" t="s">
-        <v>30</v>
-      </c>
-      <c r="S69" s="2">
-        <v>248</v>
+        <v>171</v>
+      </c>
+      <c r="S69" s="2" t="s">
+        <v>172</v>
       </c>
       <c r="T69" s="2">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="U69" s="2">
-        <v>60</v>
-      </c>
-      <c r="V69" s="2" t="s">
-        <v>150</v>
+        <v>45</v>
+      </c>
+      <c r="V69" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="D70" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="E70" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="I70" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J70" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="L70" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="O70" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="Q70" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="R70" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="S70" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="T70" s="2" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="U70" s="2">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="V70" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B71" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="D71" t="s">
         <v>38</v>
       </c>
       <c r="E71" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="I71" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J71" t="s">
+        <v>181</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="M71" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="K71" s="4" t="s">
-        <v>177</v>
-      </c>
       <c r="O71" t="s">
-        <v>148</v>
+        <v>424</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>153</v>
       </c>
       <c r="R71" t="s">
-        <v>178</v>
-      </c>
-      <c r="S71" s="2">
-        <v>420</v>
-      </c>
-      <c r="T71" s="2">
-        <v>274</v>
-      </c>
-      <c r="U71" s="2">
-        <v>30</v>
+        <v>27</v>
+      </c>
+      <c r="S71" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="T71" s="2" t="s">
+        <v>184</v>
       </c>
       <c r="V71" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="D72" t="s">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="E72" t="s">
-        <v>181</v>
+        <v>142</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="I72" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J72" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>184</v>
+        <v>189</v>
+      </c>
+      <c r="L72" t="s">
+        <v>190</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="O72" t="s">
-        <v>148</v>
+        <v>129</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>129</v>
       </c>
       <c r="R72" t="s">
         <v>27</v>
       </c>
       <c r="S72" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="T72" s="2" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="V72" s="2">
         <v>1</v>
@@ -5559,43 +5519,55 @@
     </row>
     <row r="73" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="B73" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="D73" t="s">
         <v>38</v>
       </c>
       <c r="E73" t="s">
-        <v>80</v>
+        <v>142</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="I73" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="J73" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>189</v>
+        <v>196</v>
+      </c>
+      <c r="L73" t="s">
+        <v>197</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="O73" t="s">
-        <v>148</v>
+        <v>129</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>129</v>
       </c>
       <c r="R73" t="s">
-        <v>190</v>
+        <v>27</v>
       </c>
       <c r="S73" s="2" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="T73" s="2">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="U73" s="2">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="V73" s="2">
         <v>1</v>
@@ -5603,258 +5575,255 @@
     </row>
     <row r="74" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="D74" t="s">
         <v>38</v>
       </c>
       <c r="E74" t="s">
-        <v>80</v>
+        <v>142</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="I74" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="J74" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>194</v>
+        <v>202</v>
+      </c>
+      <c r="L74" t="s">
+        <v>203</v>
       </c>
       <c r="M74" s="1" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="O74" t="s">
-        <v>443</v>
+        <v>129</v>
       </c>
       <c r="Q74" t="s">
-        <v>172</v>
+        <v>129</v>
       </c>
       <c r="R74" t="s">
-        <v>113</v>
-      </c>
-      <c r="S74" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="T74" s="2" t="s">
-        <v>197</v>
+        <v>27</v>
+      </c>
+      <c r="S74" s="2">
+        <v>237</v>
+      </c>
+      <c r="T74" s="2">
+        <v>105</v>
       </c>
       <c r="U74" s="2">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="V74" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="D75" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E75" t="s">
-        <v>80</v>
+        <v>147</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="I75" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="J75" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="M75" s="1" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="O75" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="Q75" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="R75" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="S75" s="2" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="V75" s="2">
-        <v>1</v>
+        <v>154</v>
+      </c>
+      <c r="U75" s="2">
+        <v>8</v>
+      </c>
+      <c r="V75" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="76" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B76" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D76" t="s">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="E76" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="I76" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J76" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="L76" t="s">
-        <v>209</v>
-      </c>
-      <c r="M76" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O76" t="s">
-        <v>148</v>
+        <v>424</v>
       </c>
       <c r="Q76" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="R76" t="s">
-        <v>27</v>
+        <v>94</v>
       </c>
       <c r="S76" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="V76" s="2">
-        <v>1</v>
+        <v>154</v>
+      </c>
+      <c r="T76" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="U76" s="2">
+        <v>8</v>
+      </c>
+      <c r="V76" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="77" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B77" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D77" t="s">
         <v>38</v>
       </c>
       <c r="E77" t="s">
-        <v>161</v>
-      </c>
-      <c r="F77" s="1" t="s">
-        <v>205</v>
+        <v>214</v>
+      </c>
+      <c r="G77" t="s">
+        <v>215</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="I77" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J77" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="L77" t="s">
-        <v>216</v>
-      </c>
-      <c r="M77" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="O77" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="Q77" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="R77" t="s">
         <v>27</v>
       </c>
-      <c r="S77" s="2" t="s">
-        <v>203</v>
+      <c r="S77" s="2">
+        <v>85</v>
       </c>
       <c r="T77" s="2">
-        <v>100</v>
-      </c>
-      <c r="U77" s="2">
-        <v>60</v>
-      </c>
-      <c r="V77" s="2">
-        <v>1</v>
+        <v>193</v>
+      </c>
+      <c r="V77" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="78" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="B78" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>218</v>
+        <v>97</v>
       </c>
       <c r="D78" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="E78" t="s">
-        <v>161</v>
-      </c>
-      <c r="F78" s="1" t="s">
-        <v>205</v>
+        <v>98</v>
+      </c>
+      <c r="G78" t="s">
+        <v>453</v>
       </c>
       <c r="I78" t="s">
-        <v>219</v>
+        <v>454</v>
       </c>
       <c r="J78" t="s">
-        <v>220</v>
+        <v>455</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="L78" t="s">
-        <v>222</v>
-      </c>
-      <c r="M78" s="1" t="s">
-        <v>223</v>
+        <v>99</v>
       </c>
       <c r="O78" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="Q78" t="s">
-        <v>148</v>
+        <v>456</v>
       </c>
       <c r="R78" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="S78" s="2">
-        <v>237</v>
+        <v>50</v>
       </c>
       <c r="T78" s="2">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="U78" s="2">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="V78" s="2">
         <v>3</v>
@@ -5862,619 +5831,589 @@
     </row>
     <row r="79" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="B79" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>224</v>
+        <v>457</v>
       </c>
       <c r="D79" t="s">
-        <v>70</v>
+        <v>458</v>
       </c>
       <c r="E79" t="s">
-        <v>166</v>
-      </c>
-      <c r="F79" s="1" t="s">
-        <v>225</v>
+        <v>459</v>
+      </c>
+      <c r="G79" t="s">
+        <v>460</v>
       </c>
       <c r="I79" t="s">
-        <v>226</v>
+        <v>561</v>
       </c>
       <c r="J79" t="s">
-        <v>227</v>
+        <v>461</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>228</v>
+        <v>462</v>
       </c>
       <c r="O79" t="s">
-        <v>443</v>
+        <v>559</v>
       </c>
       <c r="Q79" t="s">
-        <v>172</v>
+        <v>463</v>
       </c>
       <c r="R79" t="s">
-        <v>113</v>
-      </c>
-      <c r="S79" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="T79" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="U79" s="2">
-        <v>8</v>
+        <v>30</v>
+      </c>
+      <c r="S79" s="2">
+        <v>3500</v>
+      </c>
+      <c r="T79" s="2">
+        <v>1000</v>
       </c>
       <c r="V79" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="80" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="B80" t="s">
-        <v>111</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>224</v>
+        <v>96</v>
+      </c>
+      <c r="C80" s="5">
+        <v>1475</v>
       </c>
       <c r="D80" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="E80" t="s">
-        <v>166</v>
-      </c>
-      <c r="F80" s="1" t="s">
-        <v>225</v>
+        <v>84</v>
+      </c>
+      <c r="G80" t="s">
+        <v>464</v>
       </c>
       <c r="I80" t="s">
-        <v>229</v>
+        <v>613</v>
       </c>
       <c r="J80" t="s">
-        <v>230</v>
+        <v>465</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>231</v>
+        <v>466</v>
       </c>
       <c r="O80" t="s">
-        <v>443</v>
+        <v>129</v>
       </c>
       <c r="Q80" t="s">
-        <v>172</v>
+        <v>456</v>
       </c>
       <c r="R80" t="s">
-        <v>113</v>
-      </c>
-      <c r="S80" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="T80" s="2" t="s">
-        <v>173</v>
+        <v>30</v>
+      </c>
+      <c r="S80" s="2">
+        <v>44</v>
+      </c>
+      <c r="T80" s="2">
+        <v>41</v>
       </c>
       <c r="U80" s="2">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="V80" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="B81" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>232</v>
+        <v>620</v>
       </c>
       <c r="D81" t="s">
-        <v>38</v>
+        <v>467</v>
       </c>
       <c r="E81" t="s">
-        <v>233</v>
+        <v>468</v>
       </c>
       <c r="G81" t="s">
-        <v>234</v>
-      </c>
-      <c r="H81" s="1" t="s">
-        <v>235</v>
+        <v>469</v>
       </c>
       <c r="I81" t="s">
-        <v>236</v>
+        <v>470</v>
       </c>
       <c r="J81" t="s">
-        <v>237</v>
+        <v>471</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>238</v>
+        <v>472</v>
       </c>
       <c r="O81" t="s">
-        <v>271</v>
+        <v>129</v>
       </c>
       <c r="Q81" t="s">
-        <v>172</v>
+        <v>456</v>
       </c>
       <c r="R81" t="s">
-        <v>27</v>
+        <v>473</v>
       </c>
       <c r="S81" s="2">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="T81" s="2">
-        <v>193</v>
+        <v>42</v>
       </c>
       <c r="V81" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B82" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="D82" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="E82" t="s">
-        <v>117</v>
-      </c>
-      <c r="G82" t="s">
-        <v>472</v>
+        <v>103</v>
       </c>
       <c r="I82" t="s">
-        <v>473</v>
-      </c>
-      <c r="J82" t="s">
-        <v>474</v>
+        <v>104</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="O82" t="s">
-        <v>148</v>
-      </c>
-      <c r="Q82" t="s">
-        <v>475</v>
+        <v>614</v>
       </c>
       <c r="R82" t="s">
         <v>30</v>
       </c>
       <c r="S82" s="2">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="T82" s="2">
-        <v>48</v>
-      </c>
-      <c r="U82" s="2">
-        <v>24</v>
-      </c>
-      <c r="V82" s="2">
-        <v>3</v>
+        <v>700</v>
+      </c>
+      <c r="V82" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="83" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>476</v>
+        <v>108</v>
       </c>
       <c r="D83" t="s">
-        <v>477</v>
+        <v>109</v>
       </c>
       <c r="E83" t="s">
-        <v>478</v>
-      </c>
-      <c r="G83" t="s">
-        <v>479</v>
+        <v>110</v>
       </c>
       <c r="I83" t="s">
-        <v>581</v>
+        <v>501</v>
       </c>
       <c r="J83" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>481</v>
+        <v>111</v>
       </c>
       <c r="O83" t="s">
-        <v>579</v>
+        <v>615</v>
       </c>
       <c r="Q83" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="R83" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="S83" s="2">
-        <v>3500</v>
+        <v>180</v>
       </c>
       <c r="T83" s="2">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="V83" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
-      </c>
-      <c r="C84" s="5">
-        <v>1475</v>
+        <v>107</v>
+      </c>
+      <c r="C84" s="5" t="s">
+        <v>476</v>
       </c>
       <c r="D84" t="s">
-        <v>97</v>
+        <v>477</v>
       </c>
       <c r="E84" t="s">
-        <v>98</v>
-      </c>
-      <c r="G84" t="s">
-        <v>483</v>
+        <v>570</v>
       </c>
       <c r="I84" t="s">
-        <v>638</v>
+        <v>478</v>
       </c>
       <c r="J84" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="O84" t="s">
-        <v>148</v>
+        <v>615</v>
       </c>
       <c r="Q84" t="s">
         <v>475</v>
       </c>
       <c r="R84" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="S84" s="2">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="T84" s="2">
-        <v>41</v>
+        <v>500</v>
       </c>
       <c r="U84" s="2">
-        <v>24</v>
+        <v>200</v>
       </c>
       <c r="V84" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="85" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B85" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>645</v>
+        <v>480</v>
       </c>
       <c r="D85" t="s">
-        <v>486</v>
+        <v>109</v>
       </c>
       <c r="E85" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="G85" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="I85" t="s">
-        <v>489</v>
+        <v>560</v>
       </c>
       <c r="J85" t="s">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
       <c r="O85" t="s">
-        <v>148</v>
+        <v>616</v>
       </c>
       <c r="Q85" t="s">
         <v>475</v>
       </c>
       <c r="R85" t="s">
-        <v>492</v>
+        <v>66</v>
       </c>
       <c r="S85" s="2">
-        <v>44</v>
+        <v>180</v>
       </c>
       <c r="T85" s="2">
-        <v>42</v>
+        <v>220</v>
+      </c>
+      <c r="U85" s="2">
+        <v>110</v>
       </c>
       <c r="V85" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="86" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B86" t="s">
-        <v>120</v>
+        <v>107</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>121</v>
+        <v>485</v>
       </c>
       <c r="D86" t="s">
-        <v>24</v>
+        <v>458</v>
       </c>
       <c r="E86" t="s">
-        <v>122</v>
+        <v>486</v>
+      </c>
+      <c r="G86" t="s">
+        <v>487</v>
       </c>
       <c r="I86" t="s">
-        <v>123</v>
+        <v>478</v>
+      </c>
+      <c r="J86" t="s">
+        <v>474</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>124</v>
+        <v>488</v>
       </c>
       <c r="O86" t="s">
-        <v>639</v>
+        <v>615</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>475</v>
       </c>
       <c r="R86" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="S86" s="2">
-        <v>1200</v>
+        <v>180</v>
       </c>
       <c r="T86" s="2">
-        <v>700</v>
+        <v>450</v>
+      </c>
+      <c r="U86" s="2">
+        <v>250</v>
       </c>
       <c r="V86" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="87" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
       <c r="B87" t="s">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>127</v>
+        <v>314</v>
       </c>
       <c r="D87" t="s">
-        <v>128</v>
+        <v>315</v>
       </c>
       <c r="E87" t="s">
-        <v>129</v>
+        <v>316</v>
       </c>
       <c r="I87" t="s">
-        <v>520</v>
+        <v>317</v>
       </c>
       <c r="J87" t="s">
-        <v>493</v>
+        <v>318</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>130</v>
+        <v>319</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>320</v>
       </c>
       <c r="O87" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q87" t="s">
-        <v>494</v>
+        <v>227</v>
       </c>
       <c r="R87" t="s">
-        <v>66</v>
-      </c>
-      <c r="S87" s="2">
-        <v>180</v>
+        <v>321</v>
+      </c>
+      <c r="S87" s="2" t="s">
+        <v>322</v>
       </c>
       <c r="T87" s="2">
-        <v>400</v>
-      </c>
-      <c r="V87" s="2" t="s">
-        <v>412</v>
+        <v>55</v>
+      </c>
+      <c r="U87" s="2">
+        <v>35</v>
+      </c>
+      <c r="V87" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="88" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
       <c r="B88" t="s">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>495</v>
+        <v>323</v>
       </c>
       <c r="D88" t="s">
-        <v>496</v>
+        <v>324</v>
       </c>
       <c r="E88" t="s">
-        <v>592</v>
+        <v>325</v>
       </c>
       <c r="I88" t="s">
-        <v>497</v>
+        <v>326</v>
       </c>
       <c r="J88" t="s">
-        <v>493</v>
+        <v>327</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>498</v>
+        <v>328</v>
       </c>
       <c r="O88" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q88" t="s">
-        <v>494</v>
+        <v>577</v>
       </c>
       <c r="R88" t="s">
-        <v>66</v>
+        <v>308</v>
       </c>
       <c r="S88" s="2">
-        <v>175</v>
+        <v>1200</v>
       </c>
       <c r="T88" s="2">
-        <v>500</v>
-      </c>
-      <c r="U88" s="2">
-        <v>200</v>
-      </c>
-      <c r="V88" s="2" t="s">
-        <v>412</v>
+        <v>370</v>
+      </c>
+      <c r="V88" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="89" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
       <c r="B89" t="s">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>499</v>
+        <v>329</v>
       </c>
       <c r="D89" t="s">
-        <v>128</v>
+        <v>330</v>
       </c>
       <c r="E89" t="s">
-        <v>500</v>
-      </c>
-      <c r="G89" t="s">
-        <v>501</v>
+        <v>331</v>
       </c>
       <c r="I89" t="s">
-        <v>580</v>
+        <v>332</v>
       </c>
       <c r="J89" t="s">
-        <v>502</v>
+        <v>333</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>503</v>
+        <v>334</v>
       </c>
       <c r="O89" t="s">
-        <v>641</v>
-      </c>
-      <c r="Q89" t="s">
-        <v>494</v>
+        <v>577</v>
       </c>
       <c r="R89" t="s">
-        <v>66</v>
+        <v>335</v>
       </c>
       <c r="S89" s="2">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="T89" s="2">
-        <v>220</v>
-      </c>
-      <c r="U89" s="2">
-        <v>110</v>
-      </c>
-      <c r="V89" s="2" t="s">
-        <v>412</v>
+        <v>250</v>
+      </c>
+      <c r="V89" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="90" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
       <c r="B90" t="s">
-        <v>126</v>
+        <v>313</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>504</v>
+        <v>336</v>
       </c>
       <c r="D90" t="s">
-        <v>477</v>
+        <v>337</v>
       </c>
       <c r="E90" t="s">
-        <v>505</v>
-      </c>
-      <c r="G90" t="s">
-        <v>506</v>
+        <v>338</v>
       </c>
       <c r="I90" t="s">
-        <v>497</v>
+        <v>339</v>
       </c>
       <c r="J90" t="s">
-        <v>493</v>
+        <v>340</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>507</v>
+        <v>341</v>
       </c>
       <c r="O90" t="s">
-        <v>640</v>
-      </c>
-      <c r="Q90" t="s">
-        <v>494</v>
+        <v>252</v>
       </c>
       <c r="R90" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="S90" s="2">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="T90" s="2">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="U90" s="2">
-        <v>250</v>
-      </c>
-      <c r="V90" s="2" t="s">
-        <v>412</v>
+        <v>220</v>
+      </c>
+      <c r="V90" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="91" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>331</v>
+        <v>312</v>
       </c>
       <c r="B91" t="s">
-        <v>332</v>
+        <v>313</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>333</v>
+        <v>289</v>
       </c>
       <c r="D91" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="E91" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="I91" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="J91" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="M91" s="1" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="O91" t="s">
-        <v>246</v>
+        <v>129</v>
       </c>
       <c r="R91" t="s">
-        <v>340</v>
-      </c>
-      <c r="S91" s="2" t="s">
-        <v>341</v>
+        <v>52</v>
+      </c>
+      <c r="S91" s="2">
+        <v>38</v>
       </c>
       <c r="T91" s="2">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="U91" s="2">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="V91" s="2">
         <v>2</v>
@@ -6482,40 +6421,43 @@
     </row>
     <row r="92" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>331</v>
+        <v>53</v>
       </c>
       <c r="B92" t="s">
-        <v>332</v>
+        <v>112</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>342</v>
+        <v>113</v>
       </c>
       <c r="D92" t="s">
-        <v>343</v>
+        <v>38</v>
       </c>
       <c r="E92" t="s">
-        <v>344</v>
+        <v>114</v>
       </c>
       <c r="I92" t="s">
-        <v>345</v>
+        <v>409</v>
       </c>
       <c r="J92" t="s">
-        <v>346</v>
+        <v>410</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>347</v>
+        <v>115</v>
       </c>
       <c r="O92" t="s">
-        <v>599</v>
+        <v>252</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>252</v>
       </c>
       <c r="R92" t="s">
-        <v>327</v>
+        <v>30</v>
       </c>
       <c r="S92" s="2">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="T92" s="2">
-        <v>370</v>
+        <v>480</v>
       </c>
       <c r="V92" s="2">
         <v>3</v>
@@ -6523,486 +6465,486 @@
     </row>
     <row r="93" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>331</v>
+        <v>53</v>
       </c>
       <c r="B93" t="s">
-        <v>332</v>
-      </c>
-      <c r="C93" s="5" t="s">
-        <v>348</v>
+        <v>112</v>
+      </c>
+      <c r="C93" s="5">
+        <v>1456</v>
       </c>
       <c r="D93" t="s">
-        <v>349</v>
+        <v>411</v>
       </c>
       <c r="E93" t="s">
-        <v>350</v>
+        <v>412</v>
       </c>
       <c r="I93" t="s">
-        <v>351</v>
+        <v>413</v>
       </c>
       <c r="J93" t="s">
-        <v>352</v>
+        <v>414</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>353</v>
+        <v>415</v>
       </c>
       <c r="O93" t="s">
-        <v>599</v>
+        <v>129</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>245</v>
       </c>
       <c r="R93" t="s">
-        <v>354</v>
+        <v>30</v>
       </c>
       <c r="S93" s="2">
-        <v>150</v>
+        <v>58</v>
       </c>
       <c r="T93" s="2">
-        <v>250</v>
+        <v>51</v>
+      </c>
+      <c r="U93" s="2">
+        <v>30</v>
       </c>
       <c r="V93" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="94" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>331</v>
+        <v>53</v>
       </c>
       <c r="B94" t="s">
-        <v>332</v>
+        <v>112</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>355</v>
+        <v>97</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>38</v>
       </c>
       <c r="E94" t="s">
-        <v>357</v>
+        <v>523</v>
       </c>
       <c r="I94" t="s">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="J94" t="s">
-        <v>359</v>
+        <v>417</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="O94" t="s">
-        <v>271</v>
+        <v>129</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>245</v>
       </c>
       <c r="R94" t="s">
         <v>30</v>
       </c>
       <c r="S94" s="2">
-        <v>170</v>
+        <v>53</v>
       </c>
       <c r="T94" s="2">
-        <v>340</v>
-      </c>
-      <c r="U94" s="2">
-        <v>220</v>
+        <v>57</v>
       </c>
       <c r="V94" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="95" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>331</v>
+        <v>53</v>
       </c>
       <c r="B95" t="s">
-        <v>332</v>
-      </c>
-      <c r="C95" s="5" t="s">
-        <v>308</v>
+        <v>112</v>
+      </c>
+      <c r="C95" s="5">
+        <v>1470</v>
       </c>
       <c r="D95" t="s">
-        <v>361</v>
+        <v>419</v>
       </c>
       <c r="E95" t="s">
-        <v>362</v>
+        <v>420</v>
       </c>
       <c r="I95" t="s">
-        <v>363</v>
+        <v>421</v>
       </c>
       <c r="J95" t="s">
-        <v>364</v>
+        <v>422</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>365</v>
+        <v>423</v>
       </c>
       <c r="O95" t="s">
-        <v>148</v>
+        <v>424</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>424</v>
       </c>
       <c r="R95" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="S95" s="2">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="T95" s="2">
-        <v>28</v>
-      </c>
-      <c r="U95" s="2">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="V95" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="96" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B96" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D96" t="s">
         <v>38</v>
       </c>
       <c r="E96" t="s">
-        <v>133</v>
+        <v>44</v>
       </c>
       <c r="I96" t="s">
-        <v>428</v>
+        <v>390</v>
       </c>
       <c r="J96" t="s">
-        <v>429</v>
+        <v>391</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="O96" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="Q96" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R96" t="s">
-        <v>30</v>
+        <v>392</v>
       </c>
       <c r="S96" s="2">
-        <v>400</v>
+        <v>715</v>
       </c>
       <c r="T96" s="2">
-        <v>480</v>
-      </c>
-      <c r="V96" s="2">
-        <v>3</v>
+        <v>316</v>
+      </c>
+      <c r="V96" s="2" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="97" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B97" t="s">
-        <v>131</v>
-      </c>
-      <c r="C97" s="5">
-        <v>1456</v>
+        <v>112</v>
+      </c>
+      <c r="C97" s="5" t="s">
+        <v>394</v>
       </c>
       <c r="D97" t="s">
-        <v>430</v>
+        <v>395</v>
       </c>
       <c r="E97" t="s">
-        <v>431</v>
+        <v>396</v>
       </c>
       <c r="I97" t="s">
-        <v>432</v>
+        <v>617</v>
       </c>
       <c r="J97" t="s">
-        <v>433</v>
+        <v>397</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>434</v>
+        <v>398</v>
       </c>
       <c r="O97" t="s">
-        <v>148</v>
+        <v>424</v>
       </c>
       <c r="Q97" t="s">
-        <v>264</v>
+        <v>399</v>
       </c>
       <c r="R97" t="s">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="S97" s="2">
-        <v>58</v>
+        <v>250</v>
       </c>
       <c r="T97" s="2">
-        <v>51</v>
-      </c>
-      <c r="U97" s="2">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="V97" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="98" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>53</v>
+        <v>116</v>
       </c>
       <c r="B98" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>116</v>
+        <v>401</v>
       </c>
       <c r="D98" t="s">
-        <v>38</v>
+        <v>402</v>
       </c>
       <c r="E98" t="s">
-        <v>542</v>
+        <v>403</v>
+      </c>
+      <c r="G98" t="s">
+        <v>404</v>
       </c>
       <c r="I98" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="J98" t="s">
-        <v>436</v>
+        <v>406</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>437</v>
+        <v>407</v>
+      </c>
+      <c r="M98" s="1" t="s">
+        <v>408</v>
       </c>
       <c r="O98" t="s">
-        <v>148</v>
+        <v>252</v>
       </c>
       <c r="Q98" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="R98" t="s">
         <v>30</v>
       </c>
       <c r="S98" s="2">
-        <v>53</v>
+        <v>466</v>
       </c>
       <c r="T98" s="2">
-        <v>57</v>
+        <v>233</v>
+      </c>
+      <c r="U98" s="2">
+        <v>50</v>
       </c>
       <c r="V98" s="2" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
     </row>
     <row r="99" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="B99" t="s">
-        <v>131</v>
-      </c>
-      <c r="C99" s="5">
-        <v>1470</v>
+        <v>120</v>
+      </c>
+      <c r="C99" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="D99" t="s">
-        <v>438</v>
+        <v>122</v>
       </c>
       <c r="E99" t="s">
-        <v>439</v>
+        <v>123</v>
       </c>
       <c r="I99" t="s">
-        <v>440</v>
-      </c>
-      <c r="J99" t="s">
-        <v>441</v>
+        <v>124</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>442</v>
+        <v>125</v>
       </c>
       <c r="O99" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q99" t="s">
-        <v>443</v>
+        <v>577</v>
       </c>
       <c r="R99" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
       <c r="S99" s="2">
-        <v>73</v>
+        <v>1300</v>
       </c>
       <c r="T99" s="2">
-        <v>53</v>
-      </c>
-      <c r="V99" s="2" t="s">
-        <v>412</v>
+        <v>1100</v>
+      </c>
+      <c r="V99" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="100" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B100" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>136</v>
+        <v>289</v>
       </c>
       <c r="D100" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="E100" t="s">
-        <v>44</v>
+        <v>290</v>
       </c>
       <c r="I100" t="s">
-        <v>409</v>
+        <v>291</v>
       </c>
       <c r="J100" t="s">
-        <v>410</v>
+        <v>292</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>137</v>
+        <v>293</v>
       </c>
       <c r="O100" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q100" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R100" t="s">
-        <v>411</v>
+        <v>294</v>
       </c>
       <c r="S100" s="2">
-        <v>715</v>
+        <v>386</v>
       </c>
       <c r="T100" s="2">
-        <v>316</v>
-      </c>
-      <c r="V100" s="2" t="s">
-        <v>412</v>
+        <v>280</v>
+      </c>
+      <c r="U100" s="2">
+        <v>162</v>
+      </c>
+      <c r="V100" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="101" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B101" t="s">
-        <v>131</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>413</v>
+        <v>120</v>
+      </c>
+      <c r="C101" s="5">
+        <v>1495</v>
       </c>
       <c r="D101" t="s">
-        <v>414</v>
+        <v>122</v>
       </c>
       <c r="E101" t="s">
-        <v>415</v>
+        <v>295</v>
       </c>
       <c r="I101" t="s">
-        <v>642</v>
+        <v>296</v>
       </c>
       <c r="J101" t="s">
-        <v>416</v>
+        <v>297</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>417</v>
+        <v>298</v>
       </c>
       <c r="O101" t="s">
-        <v>443</v>
-      </c>
-      <c r="Q101" t="s">
-        <v>418</v>
+        <v>153</v>
       </c>
       <c r="R101" t="s">
-        <v>419</v>
+        <v>27</v>
       </c>
       <c r="S101" s="2">
-        <v>250</v>
+        <v>198</v>
       </c>
       <c r="T101" s="2">
-        <v>300</v>
-      </c>
-      <c r="V101" s="2" t="s">
-        <v>412</v>
+        <v>114</v>
+      </c>
+      <c r="U101" s="2">
+        <v>8</v>
+      </c>
+      <c r="V101" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="102" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B102" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>420</v>
+        <v>299</v>
       </c>
       <c r="D102" t="s">
-        <v>421</v>
+        <v>122</v>
       </c>
       <c r="E102" t="s">
-        <v>422</v>
-      </c>
-      <c r="G102" t="s">
-        <v>423</v>
+        <v>123</v>
       </c>
       <c r="I102" t="s">
-        <v>424</v>
+        <v>300</v>
       </c>
       <c r="J102" t="s">
-        <v>425</v>
+        <v>301</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>427</v>
+        <v>302</v>
+      </c>
+      <c r="L102" s="1" t="s">
+        <v>303</v>
       </c>
       <c r="O102" t="s">
-        <v>271</v>
-      </c>
-      <c r="Q102" t="s">
-        <v>271</v>
+        <v>556</v>
       </c>
       <c r="R102" t="s">
-        <v>30</v>
+        <v>304</v>
       </c>
       <c r="S102" s="2">
-        <v>466</v>
-      </c>
-      <c r="T102" s="2">
-        <v>233</v>
-      </c>
-      <c r="U102" s="2">
-        <v>50</v>
-      </c>
-      <c r="V102" s="2" t="s">
-        <v>412</v>
+        <v>250</v>
+      </c>
+      <c r="V102" s="2">
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C103" s="5" t="s">
+        <v>619</v>
+      </c>
+      <c r="D103" t="s">
+        <v>95</v>
+      </c>
+      <c r="E103" t="s">
+        <v>305</v>
+      </c>
+      <c r="I103" t="s">
+        <v>421</v>
+      </c>
+      <c r="J103" t="s">
+        <v>306</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="O103" t="s">
+        <v>129</v>
+      </c>
+      <c r="R103" t="s">
+        <v>308</v>
+      </c>
+      <c r="S103" s="2">
         <v>140</v>
       </c>
-      <c r="D103" t="s">
-        <v>141</v>
-      </c>
-      <c r="E103" t="s">
-        <v>142</v>
-      </c>
-      <c r="I103" t="s">
-        <v>143</v>
-      </c>
-      <c r="K103" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="O103" t="s">
-        <v>599</v>
-      </c>
-      <c r="R103" t="s">
-        <v>145</v>
-      </c>
-      <c r="S103" s="2">
-        <v>1300</v>
-      </c>
       <c r="T103" s="2">
-        <v>1100</v>
+        <v>40</v>
+      </c>
+      <c r="U103" s="2">
+        <v>37</v>
       </c>
       <c r="V103" s="2">
         <v>2</v>
@@ -7010,218 +6952,45 @@
     </row>
     <row r="104" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>308</v>
+        <v>289</v>
       </c>
       <c r="D104" t="s">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="E104" t="s">
+        <v>618</v>
+      </c>
+      <c r="I104" t="s">
         <v>309</v>
       </c>
-      <c r="I104" t="s">
+      <c r="J104" t="s">
         <v>310</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="K104" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="O104" t="s">
-        <v>271</v>
+        <v>252</v>
       </c>
       <c r="R104" t="s">
-        <v>313</v>
+        <v>30</v>
       </c>
       <c r="S104" s="2">
-        <v>386</v>
+        <v>112</v>
       </c>
       <c r="T104" s="2">
-        <v>280</v>
+        <v>217</v>
       </c>
       <c r="U104" s="2">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="V104" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>138</v>
-      </c>
-      <c r="B105" t="s">
-        <v>139</v>
-      </c>
-      <c r="C105" s="5">
-        <v>1495</v>
-      </c>
-      <c r="D105" t="s">
-        <v>141</v>
-      </c>
-      <c r="E105" t="s">
-        <v>314</v>
-      </c>
-      <c r="I105" t="s">
-        <v>315</v>
-      </c>
-      <c r="J105" t="s">
-        <v>316</v>
-      </c>
-      <c r="K105" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="O105" t="s">
-        <v>172</v>
-      </c>
-      <c r="R105" t="s">
-        <v>27</v>
-      </c>
-      <c r="S105" s="2">
-        <v>198</v>
-      </c>
-      <c r="T105" s="2">
-        <v>114</v>
-      </c>
-      <c r="U105" s="2">
-        <v>8</v>
-      </c>
-      <c r="V105" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="106" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>138</v>
-      </c>
-      <c r="B106" t="s">
-        <v>139</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>318</v>
-      </c>
-      <c r="D106" t="s">
-        <v>141</v>
-      </c>
-      <c r="E106" t="s">
-        <v>142</v>
-      </c>
-      <c r="I106" t="s">
-        <v>319</v>
-      </c>
-      <c r="J106" t="s">
-        <v>320</v>
-      </c>
-      <c r="K106" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="L106" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="O106" t="s">
-        <v>575</v>
-      </c>
-      <c r="R106" t="s">
-        <v>323</v>
-      </c>
-      <c r="S106" s="2">
-        <v>250</v>
-      </c>
-      <c r="V106" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>138</v>
-      </c>
-      <c r="B107" t="s">
-        <v>139</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="D107" t="s">
-        <v>114</v>
-      </c>
-      <c r="E107" t="s">
-        <v>324</v>
-      </c>
-      <c r="I107" t="s">
-        <v>440</v>
-      </c>
-      <c r="J107" t="s">
-        <v>325</v>
-      </c>
-      <c r="K107" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="O107" t="s">
-        <v>148</v>
-      </c>
-      <c r="R107" t="s">
-        <v>327</v>
-      </c>
-      <c r="S107" s="2">
-        <v>140</v>
-      </c>
-      <c r="T107" s="2">
-        <v>40</v>
-      </c>
-      <c r="U107" s="2">
-        <v>37</v>
-      </c>
-      <c r="V107" s="2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" spans="1:22" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>138</v>
-      </c>
-      <c r="B108" t="s">
-        <v>139</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="D108" t="s">
-        <v>141</v>
-      </c>
-      <c r="E108" t="s">
-        <v>643</v>
-      </c>
-      <c r="I108" t="s">
-        <v>328</v>
-      </c>
-      <c r="J108" t="s">
-        <v>329</v>
-      </c>
-      <c r="K108" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="O108" t="s">
-        <v>271</v>
-      </c>
-      <c r="R108" t="s">
-        <v>30</v>
-      </c>
-      <c r="S108" s="2">
-        <v>112</v>
-      </c>
-      <c r="T108" s="2">
-        <v>217</v>
-      </c>
-      <c r="U108" s="2">
-        <v>70</v>
-      </c>
-      <c r="V108" s="2">
         <v>2</v>
       </c>
     </row>
@@ -7230,129 +6999,125 @@
   <hyperlinks>
     <hyperlink ref="K22" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
     <hyperlink ref="K46" r:id="rId2" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="K62" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
-    <hyperlink ref="K63" r:id="rId4" xr:uid="{00000000-0004-0000-0000-00000E000000}"/>
-    <hyperlink ref="K64" r:id="rId5" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="K65" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000010000000}"/>
-    <hyperlink ref="K103" r:id="rId7" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
-    <hyperlink ref="K86" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
-    <hyperlink ref="K66" r:id="rId9" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
-    <hyperlink ref="K67" r:id="rId10" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
-    <hyperlink ref="K68" r:id="rId11" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
-    <hyperlink ref="K69" r:id="rId12" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
-    <hyperlink ref="K70" r:id="rId13" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
-    <hyperlink ref="M70" r:id="rId14" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
-    <hyperlink ref="K71" r:id="rId15" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
-    <hyperlink ref="K72" r:id="rId16" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
-    <hyperlink ref="K73" r:id="rId17" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
-    <hyperlink ref="K74" r:id="rId18" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
-    <hyperlink ref="M74" r:id="rId19" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
-    <hyperlink ref="K75" r:id="rId20" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
-    <hyperlink ref="M75" r:id="rId21" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
-    <hyperlink ref="K76" r:id="rId22" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
-    <hyperlink ref="M76" r:id="rId23" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
-    <hyperlink ref="K77" r:id="rId24" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
-    <hyperlink ref="F76" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
-    <hyperlink ref="F77:F78" r:id="rId26" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
-    <hyperlink ref="M77" r:id="rId27" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
-    <hyperlink ref="M78" r:id="rId28" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
-    <hyperlink ref="K78" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
-    <hyperlink ref="K79" r:id="rId30" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
-    <hyperlink ref="F79" r:id="rId31" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
-    <hyperlink ref="F80" r:id="rId32" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
-    <hyperlink ref="K80" r:id="rId33" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
-    <hyperlink ref="K81" r:id="rId34" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
-    <hyperlink ref="H81" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
-    <hyperlink ref="K33" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
-    <hyperlink ref="K34" r:id="rId37" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
-    <hyperlink ref="K35" r:id="rId38" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
-    <hyperlink ref="K47" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
-    <hyperlink ref="K104" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
-    <hyperlink ref="L106" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
-    <hyperlink ref="K106" r:id="rId42" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
-    <hyperlink ref="K105" r:id="rId43" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
-    <hyperlink ref="K108" r:id="rId44" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
-    <hyperlink ref="K107" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
-    <hyperlink ref="M91" r:id="rId46" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
-    <hyperlink ref="K91" r:id="rId47" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
-    <hyperlink ref="K92" r:id="rId48" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
-    <hyperlink ref="K95" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
-    <hyperlink ref="K94" r:id="rId50" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
-    <hyperlink ref="K93" r:id="rId51" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
-    <hyperlink ref="K40" r:id="rId52" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
-    <hyperlink ref="K41" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
-    <hyperlink ref="K42" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
-    <hyperlink ref="K43" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
-    <hyperlink ref="K44" r:id="rId56" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
-    <hyperlink ref="K45" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
-    <hyperlink ref="K20" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
-    <hyperlink ref="K21" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
-    <hyperlink ref="K100" r:id="rId60" xr:uid="{27E4829F-4D6C-4205-815B-E30709FE0551}"/>
-    <hyperlink ref="K101" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0C3D8311-8886-4EE9-8346-59E9A2212818}"/>
-    <hyperlink ref="K102" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B28112-49B9-4A12-A9FC-6929194008BD}"/>
-    <hyperlink ref="M102" r:id="rId63" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B81923-B3F5-4D27-8C90-D607D23DCA1E}"/>
-    <hyperlink ref="K96" r:id="rId64" xr:uid="{48F768EA-5F6B-4721-BE10-3381CFFF7617}"/>
-    <hyperlink ref="K97" r:id="rId65" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB3AA346-9023-4C65-A326-45854C985AC3}"/>
-    <hyperlink ref="K98" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3E9D42C5-EF64-4F37-BDFD-EF645728FB63}"/>
-    <hyperlink ref="K99" r:id="rId67" xr:uid="{D140917F-D470-4295-AC16-135E62B59912}"/>
-    <hyperlink ref="K19" r:id="rId68" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
-    <hyperlink ref="K18" r:id="rId69" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
-    <hyperlink ref="K10" r:id="rId70" xr:uid="{09752CE0-E1D3-4BF8-9D97-A49E8D002FC7}"/>
-    <hyperlink ref="K11" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{63C98BDE-FB8F-4FF9-A55C-03BAC1A02C63}"/>
-    <hyperlink ref="K12" r:id="rId72" xr:uid="{2380B890-0042-45CC-BEA4-783EA390EBF7}"/>
-    <hyperlink ref="K13" r:id="rId73" xr:uid="{AD077303-0EE9-4440-AAE6-BB84613C92BA}"/>
-    <hyperlink ref="K14" r:id="rId74" xr:uid="{8F9EE820-D8AA-4884-BB24-82C0C5D3CE2E}"/>
-    <hyperlink ref="K15" r:id="rId75" xr:uid="{22252FF4-27CC-40A3-8165-FA7B5CD19CDC}"/>
-    <hyperlink ref="K16" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96212E21-386F-4FCF-9A25-36D60D8078DF}"/>
-    <hyperlink ref="K17" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D9725C5-E9A1-4F23-B790-C7DC385208E5}"/>
-    <hyperlink ref="K82" r:id="rId78" xr:uid="{11A9B442-D6DF-429E-912B-50308BFE8E3D}"/>
-    <hyperlink ref="K83" r:id="rId79" xr:uid="{9A607AD9-733B-410B-B2B3-EFB415EA956D}"/>
-    <hyperlink ref="K84" r:id="rId80" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB732E30-93A4-4501-9799-59B7A6245041}"/>
-    <hyperlink ref="K85" r:id="rId81" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27EBDD53-9DEC-466F-B000-1FDCDA134FDC}"/>
-    <hyperlink ref="K87" r:id="rId82" xr:uid="{AA5F7287-2A04-4E9B-90FB-8E7A60BA0E9F}"/>
-    <hyperlink ref="K88" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4EF3173-817E-4A91-848F-7D2C11831473}"/>
-    <hyperlink ref="K89" r:id="rId84" xr:uid="{6284D82A-10EF-49D7-940E-00897AA75BB5}"/>
-    <hyperlink ref="K90" r:id="rId85" xr:uid="{DBEE44C4-CCCA-45E8-A66C-BF94EC30E034}"/>
-    <hyperlink ref="K2" r:id="rId86" xr:uid="{8B065BCD-2734-4507-991F-BC964964CB18}"/>
-    <hyperlink ref="K4" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg/960px-Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FEA8008D-9F5B-441C-84F7-155CCAB3D5BF}"/>
-    <hyperlink ref="K3" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg/960px-Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5621AFEB-68F3-4B18-95B3-0E55B258835D}"/>
-    <hyperlink ref="K5" r:id="rId89" xr:uid="{D324CD68-7A4C-4682-B6C0-EB2DEBD82B3E}"/>
-    <hyperlink ref="K6" r:id="rId90" xr:uid="{124DD613-D9C5-45A6-9C6E-5A94A110D732}"/>
-    <hyperlink ref="K7" r:id="rId91" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5CFEE07F-3AE1-4E17-8717-F5A1FACB33B9}"/>
-    <hyperlink ref="K8" r:id="rId92" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E585144F-91F4-4BE2-B00E-5A17CFAAEE37}"/>
-    <hyperlink ref="K9" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5286F62C-4DD5-41F9-8A33-916D65A4CBCB}"/>
-    <hyperlink ref="K32" r:id="rId94" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
-    <hyperlink ref="K31" r:id="rId95" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
-    <hyperlink ref="K30" r:id="rId96" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
-    <hyperlink ref="F29" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
-    <hyperlink ref="M29" r:id="rId98" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
-    <hyperlink ref="K29" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
-    <hyperlink ref="K28" r:id="rId100" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
-    <hyperlink ref="K23" r:id="rId101" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA50FD28-25AB-4C16-B704-4C1D4E291FC6}"/>
-    <hyperlink ref="K24" r:id="rId102" xr:uid="{AB5A3565-A8C2-4EB1-BF08-09469169F49B}"/>
-    <hyperlink ref="K25" r:id="rId103" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg/960px-Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{16AB1331-79AB-4AD1-82BF-411A6047FFC8}"/>
-    <hyperlink ref="K26" r:id="rId104" xr:uid="{8C66FE78-AD95-48B9-AFFB-A7A961701AB6}"/>
-    <hyperlink ref="K27" r:id="rId105" xr:uid="{BA7D0C74-4085-47D1-B949-A4D37E1B604C}"/>
-    <hyperlink ref="K36" r:id="rId106" xr:uid="{138404FE-5360-483C-9B6C-779679C072A6}"/>
-    <hyperlink ref="K37" r:id="rId107" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D549C045-BC59-46A9-BA82-994248896840}"/>
-    <hyperlink ref="K38" r:id="rId108" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD01D10D-9209-4700-8601-3904D1E7F113}"/>
-    <hyperlink ref="K39" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FA474B3-EF83-44FF-82A9-671D8D2F0D05}"/>
-    <hyperlink ref="K48" r:id="rId110" xr:uid="{1102F7BD-BEB3-432C-BF66-1C542DA92A11}"/>
-    <hyperlink ref="K49" r:id="rId111" xr:uid="{E941035A-743A-4BB3-A198-E2C6C64768DE}"/>
-    <hyperlink ref="F50" r:id="rId112" xr:uid="{186096D7-8290-4E00-8A51-8F4DB6772A92}"/>
-    <hyperlink ref="K50" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DC007C0B-FC91-4D70-81C6-71AE180A6066}"/>
-    <hyperlink ref="K51" r:id="rId114" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{35475F33-DD52-4341-99A6-9FFFE0CE1407}"/>
-    <hyperlink ref="K52" r:id="rId115" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C95CE775-1BC4-448D-9BB5-A5F3AFF37602}"/>
-    <hyperlink ref="K53" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{28199704-DE62-4BF7-B087-8CA8F092680B}"/>
-    <hyperlink ref="K59" r:id="rId117" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{55915C9C-9DC5-4CBC-B294-CD0B4A57EB54}"/>
-    <hyperlink ref="K54" r:id="rId118" xr:uid="{D3AA1374-31B4-4C29-B3A8-2E62C72FE201}"/>
-    <hyperlink ref="K55" r:id="rId119" xr:uid="{718C90F6-4372-4C83-A3C0-372E7FA8C808}"/>
-    <hyperlink ref="K56" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E0266C44-5AAB-4155-8828-7810F8578068}"/>
-    <hyperlink ref="K57" r:id="rId121" xr:uid="{539A4D92-FAE4-47BE-9310-74149CD0754F}"/>
-    <hyperlink ref="K58" r:id="rId122" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A48AEBF3-B9CB-496A-9E64-FA4CBAB7718D}"/>
-    <hyperlink ref="L58" r:id="rId123" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{70F574BF-300A-4254-A4F5-2106359EEC2E}"/>
-    <hyperlink ref="K60" r:id="rId124" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9CA4BFBE-18AF-4C1E-93E7-366981D9081F}"/>
-    <hyperlink ref="K61" r:id="rId125" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{74906672-F576-4302-94A7-8CFF8BC00900}"/>
+    <hyperlink ref="K99" r:id="rId3" xr:uid="{00000000-0004-0000-0000-00001C000000}"/>
+    <hyperlink ref="K82" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000017000000}"/>
+    <hyperlink ref="K62" r:id="rId5" xr:uid="{D3F35601-C457-4766-B32C-B208D63FC0A3}"/>
+    <hyperlink ref="K63" r:id="rId6" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{06BB428C-F7CC-4616-AAC0-87F9D9E5E360}"/>
+    <hyperlink ref="K64" r:id="rId7" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{BFA290D9-49C5-4116-A873-90B93BCDCE65}"/>
+    <hyperlink ref="K65" r:id="rId8" xr:uid="{2D42F89E-8C81-46B1-8EED-66F1635FB5B5}"/>
+    <hyperlink ref="K66" r:id="rId9" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DCC48CC8-15AC-4E69-BFCF-B10909C63B4A}"/>
+    <hyperlink ref="M66" r:id="rId10" xr:uid="{55770137-8582-4E99-BC07-CF47A71C3892}"/>
+    <hyperlink ref="K67" r:id="rId11" xr:uid="{CA71BA49-3783-492C-BCC7-F0B3333DA547}"/>
+    <hyperlink ref="K68" r:id="rId12" xr:uid="{FBA974C2-891A-40AB-9CB3-E1D7C5737803}"/>
+    <hyperlink ref="K69" r:id="rId13" xr:uid="{85D4AF33-D95A-4C54-BAD6-31B4FE594F20}"/>
+    <hyperlink ref="K70" r:id="rId14" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{CD856151-D9A4-4258-BAA6-E4B8B42BC113}"/>
+    <hyperlink ref="M70" r:id="rId15" xr:uid="{B940CC40-BA5B-495F-9FBD-E21A37FDB100}"/>
+    <hyperlink ref="K71" r:id="rId16" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{40932D0B-79BD-48D2-9F51-A0B9CD004C45}"/>
+    <hyperlink ref="M71" r:id="rId17" xr:uid="{E8E347DD-76F4-45A6-B05A-EA2827B0A62E}"/>
+    <hyperlink ref="K72" r:id="rId18" xr:uid="{A813F9A0-B51E-40A8-A8ED-CA145F346A99}"/>
+    <hyperlink ref="M72" r:id="rId19" xr:uid="{4D2D5B07-753D-4319-9F79-21C83AD7318B}"/>
+    <hyperlink ref="K73" r:id="rId20" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4259CCDF-9792-4AC2-B779-4E35CBF4CD54}"/>
+    <hyperlink ref="F72" r:id="rId21" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{64D91D57-ADEC-45F6-8DFE-B66920CE8733}"/>
+    <hyperlink ref="F73:F74" r:id="rId22" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FD1CB2DE-2F86-44A7-B0E3-D60E081A8E56}"/>
+    <hyperlink ref="M73" r:id="rId23" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E85E4789-C4E7-4B74-962B-6325B683155E}"/>
+    <hyperlink ref="M74" r:id="rId24" xr:uid="{1CBB1455-3D5A-49A5-B524-5216EF183E27}"/>
+    <hyperlink ref="K74" r:id="rId25" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FE2E0672-037C-4F2C-9297-CCBF3D9C6F1A}"/>
+    <hyperlink ref="K75" r:id="rId26" xr:uid="{0389333D-973E-410F-B780-7AA3C3570F2C}"/>
+    <hyperlink ref="F75" r:id="rId27" xr:uid="{660E3EF0-4039-49A0-8A42-FA551ADF35A2}"/>
+    <hyperlink ref="F76" r:id="rId28" xr:uid="{8C897CEC-10C3-4C4E-AD13-CC556F0966AB}"/>
+    <hyperlink ref="K76" r:id="rId29" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{698F96CB-F188-40BE-90C4-AE6FABDEB089}"/>
+    <hyperlink ref="K77" r:id="rId30" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E1B37662-D9DE-4C58-B289-1219B0D3451E}"/>
+    <hyperlink ref="H77" r:id="rId31" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7E4A55B5-DAEB-4B02-93B5-1907FBEAC36A}"/>
+    <hyperlink ref="K33" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{376A2963-7BE5-4602-B9BF-1839CAB838AD}"/>
+    <hyperlink ref="K34" r:id="rId33" xr:uid="{D4768A8B-5FAB-414D-ACAB-55AB7D475C8D}"/>
+    <hyperlink ref="K35" r:id="rId34" xr:uid="{736ACC8E-32FE-476B-AA17-C225754B2025}"/>
+    <hyperlink ref="K47" r:id="rId35" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4C6EE1F5-D474-4188-A913-38A21ED7BFAB}"/>
+    <hyperlink ref="K100" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{80FFCB4D-417A-4559-8423-B8943110979A}"/>
+    <hyperlink ref="L102" r:id="rId37" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{56D6A29C-F64D-4390-8D90-8916A38030C7}"/>
+    <hyperlink ref="K102" r:id="rId38" xr:uid="{A714E2BA-9BD5-4E88-8BF3-FA3E845FBF71}"/>
+    <hyperlink ref="K101" r:id="rId39" xr:uid="{A86D4ACF-1542-46FD-899E-F2778AA231DC}"/>
+    <hyperlink ref="K104" r:id="rId40" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5F1D592D-F667-45F1-B712-D5EA60506028}"/>
+    <hyperlink ref="K103" r:id="rId41" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{8535E10B-64C7-45CA-8451-56ADE03912F8}"/>
+    <hyperlink ref="M87" r:id="rId42" xr:uid="{A6420B88-B6A1-45D4-A4E1-73B93CFBE9F3}"/>
+    <hyperlink ref="K87" r:id="rId43" xr:uid="{554ACFB6-B9B5-4388-8C78-4F9DF46B48C0}"/>
+    <hyperlink ref="K88" r:id="rId44" xr:uid="{D3320329-A4CD-4740-B836-5AB7C9372A58}"/>
+    <hyperlink ref="K91" r:id="rId45" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF7CBAC5-7C86-4E68-AE0E-CE8F46F27C00}"/>
+    <hyperlink ref="K90" r:id="rId46" xr:uid="{0270AB34-A1EB-4297-8E4F-3994907F1901}"/>
+    <hyperlink ref="K89" r:id="rId47" xr:uid="{6C79C569-F0CF-4CBD-8ED8-4477CDA8B2F6}"/>
+    <hyperlink ref="K40" r:id="rId48" xr:uid="{B6FF6BBB-F9EA-49BC-896C-E2E708E51629}"/>
+    <hyperlink ref="K41" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DED68F44-D689-4D3E-8FD6-ED7B12A2F85D}"/>
+    <hyperlink ref="K42" r:id="rId50" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0B9501D4-A260-4500-BC9C-E6878F98627B}"/>
+    <hyperlink ref="K43" r:id="rId51" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6CDC3223-1DC7-4499-AB4C-A18506F25A9A}"/>
+    <hyperlink ref="K44" r:id="rId52" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0166B34A-156D-4D2D-8648-DA7ADE4DC2CA}"/>
+    <hyperlink ref="K45" r:id="rId53" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{EF31F671-7271-41C9-86B5-CF1673749B9D}"/>
+    <hyperlink ref="K20" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FBE7FEF9-D7C4-4BBA-9B73-BBE2136F1CDB}"/>
+    <hyperlink ref="K21" r:id="rId55" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A9A26AB1-639A-416B-9D03-ED71466D7B01}"/>
+    <hyperlink ref="K96" r:id="rId56" xr:uid="{27E4829F-4D6C-4205-815B-E30709FE0551}"/>
+    <hyperlink ref="K97" r:id="rId57" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{0C3D8311-8886-4EE9-8346-59E9A2212818}"/>
+    <hyperlink ref="K98" r:id="rId58" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{B7B28112-49B9-4A12-A9FC-6929194008BD}"/>
+    <hyperlink ref="M98" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{43B81923-B3F5-4D27-8C90-D607D23DCA1E}"/>
+    <hyperlink ref="K92" r:id="rId60" xr:uid="{48F768EA-5F6B-4721-BE10-3381CFFF7617}"/>
+    <hyperlink ref="K93" r:id="rId61" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB3AA346-9023-4C65-A326-45854C985AC3}"/>
+    <hyperlink ref="K94" r:id="rId62" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3E9D42C5-EF64-4F37-BDFD-EF645728FB63}"/>
+    <hyperlink ref="K95" r:id="rId63" xr:uid="{D140917F-D470-4295-AC16-135E62B59912}"/>
+    <hyperlink ref="K19" r:id="rId64" xr:uid="{3F6532EC-92D1-4D12-AC58-C467407C36FB}"/>
+    <hyperlink ref="K18" r:id="rId65" xr:uid="{8C1C47DA-876F-496C-9B28-E95D9AE0488F}"/>
+    <hyperlink ref="K10" r:id="rId66" xr:uid="{09752CE0-E1D3-4BF8-9D97-A49E8D002FC7}"/>
+    <hyperlink ref="K11" r:id="rId67" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{63C98BDE-FB8F-4FF9-A55C-03BAC1A02C63}"/>
+    <hyperlink ref="K12" r:id="rId68" xr:uid="{2380B890-0042-45CC-BEA4-783EA390EBF7}"/>
+    <hyperlink ref="K13" r:id="rId69" xr:uid="{AD077303-0EE9-4440-AAE6-BB84613C92BA}"/>
+    <hyperlink ref="K14" r:id="rId70" xr:uid="{8F9EE820-D8AA-4884-BB24-82C0C5D3CE2E}"/>
+    <hyperlink ref="K15" r:id="rId71" xr:uid="{22252FF4-27CC-40A3-8165-FA7B5CD19CDC}"/>
+    <hyperlink ref="K16" r:id="rId72" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{96212E21-386F-4FCF-9A25-36D60D8078DF}"/>
+    <hyperlink ref="K17" r:id="rId73" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4D9725C5-E9A1-4F23-B790-C7DC385208E5}"/>
+    <hyperlink ref="K78" r:id="rId74" xr:uid="{11A9B442-D6DF-429E-912B-50308BFE8E3D}"/>
+    <hyperlink ref="K79" r:id="rId75" xr:uid="{9A607AD9-733B-410B-B2B3-EFB415EA956D}"/>
+    <hyperlink ref="K80" r:id="rId76" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AB732E30-93A4-4501-9799-59B7A6245041}"/>
+    <hyperlink ref="K81" r:id="rId77" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{27EBDD53-9DEC-466F-B000-1FDCDA134FDC}"/>
+    <hyperlink ref="K83" r:id="rId78" xr:uid="{AA5F7287-2A04-4E9B-90FB-8E7A60BA0E9F}"/>
+    <hyperlink ref="K84" r:id="rId79" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A4EF3173-817E-4A91-848F-7D2C11831473}"/>
+    <hyperlink ref="K85" r:id="rId80" xr:uid="{6284D82A-10EF-49D7-940E-00897AA75BB5}"/>
+    <hyperlink ref="K86" r:id="rId81" xr:uid="{DBEE44C4-CCCA-45E8-A66C-BF94EC30E034}"/>
+    <hyperlink ref="K2" r:id="rId82" xr:uid="{8B065BCD-2734-4507-991F-BC964964CB18}"/>
+    <hyperlink ref="K4" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f6/Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg/960px-Bartolomeo_Bellano%2C_The_Dead_Christ_with_Two_Angels%2C_NGA_43859.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FEA8008D-9F5B-441C-84F7-155CCAB3D5BF}"/>
+    <hyperlink ref="K3" r:id="rId84" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg/960px-Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5621AFEB-68F3-4B18-95B3-0E55B258835D}"/>
+    <hyperlink ref="K5" r:id="rId85" xr:uid="{D324CD68-7A4C-4682-B6C0-EB2DEBD82B3E}"/>
+    <hyperlink ref="K6" r:id="rId86" xr:uid="{124DD613-D9C5-45A6-9C6E-5A94A110D732}"/>
+    <hyperlink ref="K7" r:id="rId87" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5CFEE07F-3AE1-4E17-8717-F5A1FACB33B9}"/>
+    <hyperlink ref="K8" r:id="rId88" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E585144F-91F4-4BE2-B00E-5A17CFAAEE37}"/>
+    <hyperlink ref="K9" r:id="rId89" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5286F62C-4DD5-41F9-8A33-916D65A4CBCB}"/>
+    <hyperlink ref="K32" r:id="rId90" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{333903E7-A6B1-4C73-8B9E-5E57EA810C60}"/>
+    <hyperlink ref="K31" r:id="rId91" xr:uid="{5A8DC8D6-0B7A-480C-90DD-5CACC799BAFA}"/>
+    <hyperlink ref="K30" r:id="rId92" xr:uid="{C00AB6CC-48A6-4796-841A-1F55D358EFE0}"/>
+    <hyperlink ref="F29" r:id="rId93" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{723A1D03-6CD9-4D46-B506-D42068F0EB0E}"/>
+    <hyperlink ref="M29" r:id="rId94" xr:uid="{4E59EDAF-67DA-4BA4-A888-A15978FC2C76}"/>
+    <hyperlink ref="K29" r:id="rId95" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{7B91CF63-2D0D-436A-AA6D-59E90F39E4CA}"/>
+    <hyperlink ref="K28" r:id="rId96" xr:uid="{4AC5E49A-027D-4B79-B49E-622634C5B8EA}"/>
+    <hyperlink ref="K23" r:id="rId97" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AA50FD28-25AB-4C16-B704-4C1D4E291FC6}"/>
+    <hyperlink ref="K24" r:id="rId98" xr:uid="{AB5A3565-A8C2-4EB1-BF08-09469169F49B}"/>
+    <hyperlink ref="K25" r:id="rId99" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg/960px-Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{16AB1331-79AB-4AD1-82BF-411A6047FFC8}"/>
+    <hyperlink ref="K26" r:id="rId100" xr:uid="{8C66FE78-AD95-48B9-AFFB-A7A961701AB6}"/>
+    <hyperlink ref="K27" r:id="rId101" xr:uid="{BA7D0C74-4085-47D1-B949-A4D37E1B604C}"/>
+    <hyperlink ref="K36" r:id="rId102" xr:uid="{138404FE-5360-483C-9B6C-779679C072A6}"/>
+    <hyperlink ref="K37" r:id="rId103" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D549C045-BC59-46A9-BA82-994248896840}"/>
+    <hyperlink ref="K38" r:id="rId104" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{BD01D10D-9209-4700-8601-3904D1E7F113}"/>
+    <hyperlink ref="K39" r:id="rId105" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{6FA474B3-EF83-44FF-82A9-671D8D2F0D05}"/>
+    <hyperlink ref="K48" r:id="rId106" xr:uid="{1102F7BD-BEB3-432C-BF66-1C542DA92A11}"/>
+    <hyperlink ref="K49" r:id="rId107" xr:uid="{E941035A-743A-4BB3-A198-E2C6C64768DE}"/>
+    <hyperlink ref="F50" r:id="rId108" xr:uid="{186096D7-8290-4E00-8A51-8F4DB6772A92}"/>
+    <hyperlink ref="K50" r:id="rId109" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{DC007C0B-FC91-4D70-81C6-71AE180A6066}"/>
+    <hyperlink ref="K51" r:id="rId110" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{35475F33-DD52-4341-99A6-9FFFE0CE1407}"/>
+    <hyperlink ref="K52" r:id="rId111" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C95CE775-1BC4-448D-9BB5-A5F3AFF37602}"/>
+    <hyperlink ref="K53" r:id="rId112" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{28199704-DE62-4BF7-B087-8CA8F092680B}"/>
+    <hyperlink ref="K59" r:id="rId113" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{55915C9C-9DC5-4CBC-B294-CD0B4A57EB54}"/>
+    <hyperlink ref="K54" r:id="rId114" xr:uid="{D3AA1374-31B4-4C29-B3A8-2E62C72FE201}"/>
+    <hyperlink ref="K55" r:id="rId115" xr:uid="{718C90F6-4372-4C83-A3C0-372E7FA8C808}"/>
+    <hyperlink ref="K56" r:id="rId116" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E0266C44-5AAB-4155-8828-7810F8578068}"/>
+    <hyperlink ref="K57" r:id="rId117" xr:uid="{539A4D92-FAE4-47BE-9310-74149CD0754F}"/>
+    <hyperlink ref="K58" r:id="rId118" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A48AEBF3-B9CB-496A-9E64-FA4CBAB7718D}"/>
+    <hyperlink ref="L58" r:id="rId119" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{70F574BF-300A-4254-A4F5-2106359EEC2E}"/>
+    <hyperlink ref="K60" r:id="rId120" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9CA4BFBE-18AF-4C1E-93E7-366981D9081F}"/>
+    <hyperlink ref="K61" r:id="rId121" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{74906672-F576-4302-94A7-8CFF8BC00900}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 3 - colonne Surnom\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A805CDE7-768D-4057-8A18-422F87859432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76245ACB-C2B3-4E12-BF39-01823B480FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1208" uniqueCount="623">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="625">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -97,9 +97,6 @@
     <t>BELLANO</t>
   </si>
   <si>
-    <t>fin du 15e siècle</t>
-  </si>
-  <si>
     <t>Venise</t>
   </si>
   <si>
@@ -454,6 +451,9 @@
     <t>Antonio</t>
   </si>
   <si>
+    <t>POLLAIUOLO</t>
+  </si>
+  <si>
     <t>1484-1493</t>
   </si>
   <si>
@@ -697,7 +697,13 @@
     <t>Argent</t>
   </si>
   <si>
-    <t>Niccolò</t>
+    <t>Niccolo</t>
+  </si>
+  <si>
+    <t>d'ANTONIO</t>
+  </si>
+  <si>
+    <t>Niccolo dell'ARCA</t>
   </si>
   <si>
     <t>1463</t>
@@ -715,6 +721,9 @@
     <t>Groupe en ronde-bosse de sept statues</t>
   </si>
   <si>
+    <t>Groupe sculptural</t>
+  </si>
+  <si>
     <t>Terre cuite polychrome</t>
   </si>
   <si>
@@ -898,6 +907,9 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
+    <t>Elément décoratif</t>
+  </si>
+  <si>
     <t>Terre cuite vernissée</t>
   </si>
   <si>
@@ -1516,9 +1528,6 @@
     <t>Groupe de 8 ronde-bosses</t>
   </si>
   <si>
-    <t>Groupe sculptural</t>
-  </si>
-  <si>
     <t>1480-1485</t>
   </si>
   <si>
@@ -1882,13 +1891,10 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>POLLAIUOLO</t>
-  </si>
-  <si>
-    <t>d'ANTONIO d'APULIA</t>
-  </si>
-  <si>
-    <t>Niccolo dell'ARCA</t>
+    <t>1470-1480</t>
+  </si>
+  <si>
+    <t>1490 environ</t>
   </si>
 </sst>
 </file>
@@ -1911,12 +1917,17 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1935,7 +1946,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1954,6 +1965,7 @@
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -2270,7 +2282,7 @@
     <col min="8" max="8" width="1.85546875" hidden="1" customWidth="1"/>
     <col min="9" max="9" width="9.140625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="5.5703125" customWidth="1"/>
-    <col min="11" max="11" width="9.5703125" customWidth="1"/>
+    <col min="11" max="11" width="49.28515625" customWidth="1"/>
     <col min="12" max="12" width="2.7109375" style="3" customWidth="1"/>
     <col min="13" max="13" width="5.5703125" customWidth="1"/>
     <col min="14" max="14" width="2.42578125" customWidth="1"/>
@@ -2279,7 +2291,7 @@
     <col min="17" max="17" width="1" customWidth="1"/>
     <col min="18" max="18" width="9.140625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="6.140625" customWidth="1"/>
-    <col min="20" max="20" width="2.140625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="6.85546875" style="2" customWidth="1"/>
     <col min="21" max="23" width="9.140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2362,31 +2374,31 @@
         <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>623</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>26</v>
       </c>
-      <c r="F2" t="s">
+      <c r="J2" t="s">
         <v>27</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="P2" t="s">
         <v>30</v>
       </c>
-      <c r="P2" t="s">
+      <c r="R2" t="s">
         <v>31</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>32</v>
-      </c>
-      <c r="S2" t="s">
-        <v>33</v>
       </c>
       <c r="T2" s="2">
         <v>29</v>
@@ -2409,28 +2421,28 @@
         <v>24</v>
       </c>
       <c r="D3" s="5" t="s">
+        <v>624</v>
+      </c>
+      <c r="E3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" t="s">
-        <v>26</v>
-      </c>
       <c r="F3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J3" t="s">
         <v>34</v>
       </c>
-      <c r="J3" t="s">
+      <c r="L3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="P3" t="s">
         <v>36</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>37</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>38</v>
-      </c>
-      <c r="S3" t="s">
-        <v>39</v>
       </c>
       <c r="T3" s="2">
         <v>400</v>
@@ -2450,28 +2462,28 @@
         <v>1490</v>
       </c>
       <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
         <v>40</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>41</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>42</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="P4" t="s">
         <v>44</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
+        <v>44</v>
+      </c>
+      <c r="S4" t="s">
         <v>45</v>
-      </c>
-      <c r="R4" t="s">
-        <v>45</v>
-      </c>
-      <c r="S4" t="s">
-        <v>46</v>
       </c>
       <c r="T4" s="2">
         <v>24</v>
@@ -2491,31 +2503,31 @@
         <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
         <v>47</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>48</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>49</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>50</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="P5" t="s">
         <v>52</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
+        <v>52</v>
+      </c>
+      <c r="S5" t="s">
         <v>53</v>
-      </c>
-      <c r="R5" t="s">
-        <v>53</v>
-      </c>
-      <c r="S5" t="s">
-        <v>54</v>
       </c>
       <c r="T5" s="2">
         <v>102</v>
@@ -2527,42 +2539,42 @@
         <v>15</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" t="s">
         <v>56</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" t="s">
         <v>58</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>59</v>
       </c>
-      <c r="F6" t="s">
+      <c r="J6" t="s">
         <v>60</v>
       </c>
-      <c r="J6" t="s">
+      <c r="K6" t="s">
         <v>61</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="P6" t="s">
         <v>63</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
         <v>64</v>
       </c>
-      <c r="R6" t="s">
-        <v>65</v>
-      </c>
       <c r="S6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T6" s="2">
         <v>600</v>
@@ -2571,150 +2583,156 @@
         <v>300</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" t="s">
-        <v>57</v>
-      </c>
       <c r="D7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" t="s">
+        <v>58</v>
+      </c>
+      <c r="F7" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" t="s">
         <v>66</v>
       </c>
-      <c r="E7" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" t="s">
-        <v>60</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>67</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="L7" s="4" t="s">
-        <v>69</v>
-      </c>
       <c r="P7" t="s">
+        <v>63</v>
+      </c>
+      <c r="R7" t="s">
         <v>64</v>
       </c>
-      <c r="R7" t="s">
-        <v>65</v>
-      </c>
       <c r="S7" t="s">
+        <v>53</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
         <v>56</v>
       </c>
-      <c r="B8" t="s">
-        <v>57</v>
-      </c>
       <c r="D8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" t="s">
         <v>70</v>
       </c>
-      <c r="E8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>71</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="P8" t="s">
         <v>73</v>
       </c>
-      <c r="P8" t="s">
+      <c r="R8" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" t="s">
         <v>74</v>
       </c>
-      <c r="S8" t="s">
-        <v>75</v>
-      </c>
       <c r="W8" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" t="s">
-        <v>57</v>
-      </c>
       <c r="D9" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" t="s">
         <v>59</v>
       </c>
-      <c r="F9" t="s">
-        <v>60</v>
-      </c>
       <c r="J9" t="s">
+        <v>75</v>
+      </c>
+      <c r="K9" t="s">
         <v>76</v>
       </c>
-      <c r="K9" t="s">
+      <c r="L9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="L9" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="P9" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="R9" t="s">
+        <v>36</v>
       </c>
       <c r="S9" t="s">
+        <v>53</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
         <v>79</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" t="s">
         <v>81</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>82</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
         <v>83</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>84</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="P10" t="s">
+        <v>30</v>
+      </c>
+      <c r="R10" t="s">
         <v>86</v>
       </c>
-      <c r="P10" t="s">
-        <v>31</v>
-      </c>
-      <c r="R10" t="s">
-        <v>87</v>
-      </c>
       <c r="S10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T10" s="2">
         <v>55</v>
@@ -2726,42 +2744,42 @@
         <v>23</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
         <v>79</v>
       </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
       <c r="D11" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+      <c r="F11" t="s">
+        <v>82</v>
+      </c>
+      <c r="J11" t="s">
         <v>88</v>
       </c>
-      <c r="E11" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" t="s">
-        <v>83</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>89</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>91</v>
-      </c>
       <c r="P11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R11" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T11" s="2">
         <v>54</v>
@@ -2773,42 +2791,42 @@
         <v>24</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
-        <v>80</v>
-      </c>
       <c r="D12" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>81</v>
+      </c>
+      <c r="F12" t="s">
+        <v>82</v>
+      </c>
+      <c r="J12" t="s">
         <v>92</v>
       </c>
-      <c r="E12" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" t="s">
-        <v>83</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>93</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="P12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S12" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T12" s="2">
         <v>37</v>
@@ -2817,77 +2835,80 @@
         <v>40</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
         <v>79</v>
       </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
       <c r="D13" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" t="s">
+        <v>81</v>
+      </c>
+      <c r="F13" t="s">
         <v>96</v>
       </c>
-      <c r="E13" t="s">
-        <v>82</v>
-      </c>
-      <c r="F13" t="s">
+      <c r="J13" t="s">
         <v>97</v>
       </c>
-      <c r="J13" t="s">
+      <c r="K13" t="s">
         <v>98</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>100</v>
-      </c>
       <c r="P13" t="s">
+        <v>63</v>
+      </c>
+      <c r="R13" t="s">
         <v>64</v>
       </c>
-      <c r="R13" t="s">
-        <v>65</v>
-      </c>
       <c r="S13" t="s">
+        <v>53</v>
+      </c>
+      <c r="W13" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>100</v>
+      </c>
+      <c r="B14" t="s">
         <v>101</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" t="s">
         <v>103</v>
       </c>
-      <c r="E14" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="J14" t="s">
         <v>104</v>
       </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>105</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="P14" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="R14" t="s">
+        <v>36</v>
       </c>
       <c r="S14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T14" s="2">
         <v>254</v>
@@ -2904,37 +2925,37 @@
     </row>
     <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s">
         <v>101</v>
       </c>
-      <c r="B15" t="s">
-        <v>102</v>
-      </c>
       <c r="D15" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" t="s">
+        <v>82</v>
+      </c>
+      <c r="J15" t="s">
         <v>108</v>
       </c>
-      <c r="E15" t="s">
-        <v>82</v>
-      </c>
-      <c r="F15" t="s">
-        <v>83</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>109</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="P15" t="s">
+        <v>30</v>
+      </c>
+      <c r="R15" t="s">
         <v>111</v>
       </c>
-      <c r="P15" t="s">
-        <v>31</v>
-      </c>
-      <c r="R15" t="s">
-        <v>112</v>
-      </c>
       <c r="S15" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T15" s="2">
         <v>54</v>
@@ -2948,37 +2969,37 @@
     </row>
     <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s">
         <v>101</v>
       </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
       <c r="D16" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" t="s">
         <v>113</v>
       </c>
-      <c r="E16" t="s">
-        <v>82</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="J16" t="s">
         <v>114</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>115</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="L16" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="P16" t="s">
+        <v>30</v>
+      </c>
+      <c r="R16" t="s">
         <v>31</v>
       </c>
-      <c r="R16" t="s">
-        <v>32</v>
-      </c>
       <c r="S16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T16" s="2">
         <v>144</v>
@@ -2989,37 +3010,37 @@
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s">
         <v>101</v>
       </c>
-      <c r="B17" t="s">
-        <v>102</v>
-      </c>
       <c r="D17" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E17" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" t="s">
         <v>118</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>119</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>120</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="L17" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="P17" t="s">
+        <v>63</v>
+      </c>
+      <c r="R17" t="s">
         <v>64</v>
       </c>
-      <c r="R17" t="s">
-        <v>65</v>
-      </c>
       <c r="S17" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T17" s="2">
         <v>370</v>
@@ -3030,34 +3051,37 @@
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" t="s">
         <v>123</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" t="s">
         <v>125</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>126</v>
       </c>
-      <c r="F18" t="s">
+      <c r="J18" t="s">
         <v>127</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>128</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>130</v>
-      </c>
       <c r="P18" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R18" t="s">
+        <v>111</v>
       </c>
       <c r="S18" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T18" s="2">
         <v>53</v>
@@ -3074,37 +3098,37 @@
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19" t="s">
         <v>123</v>
       </c>
-      <c r="B19" t="s">
-        <v>124</v>
-      </c>
       <c r="D19" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="F19" t="s">
+        <v>103</v>
+      </c>
+      <c r="J19" t="s">
         <v>131</v>
       </c>
-      <c r="E19" t="s">
-        <v>82</v>
-      </c>
-      <c r="F19" t="s">
-        <v>104</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>132</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="P19" t="s">
+        <v>63</v>
+      </c>
+      <c r="R19" t="s">
         <v>64</v>
       </c>
-      <c r="R19" t="s">
-        <v>65</v>
-      </c>
       <c r="S19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T19" s="2">
         <v>601</v>
@@ -3118,34 +3142,37 @@
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>122</v>
+      </c>
+      <c r="B20" t="s">
         <v>123</v>
       </c>
-      <c r="B20" t="s">
-        <v>124</v>
-      </c>
       <c r="D20" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+      <c r="F20" t="s">
         <v>135</v>
       </c>
-      <c r="E20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="J20" t="s">
         <v>136</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>137</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="P20" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="R20" t="s">
+        <v>36</v>
       </c>
       <c r="S20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T20" s="2">
         <v>447</v>
@@ -3159,31 +3186,34 @@
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" t="s">
         <v>123</v>
       </c>
-      <c r="B21" t="s">
-        <v>124</v>
-      </c>
       <c r="D21" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" t="s">
+        <v>82</v>
+      </c>
+      <c r="J21" t="s">
         <v>140</v>
       </c>
-      <c r="E21" t="s">
-        <v>82</v>
-      </c>
-      <c r="F21" t="s">
-        <v>83</v>
-      </c>
-      <c r="J21" t="s">
+      <c r="L21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>142</v>
-      </c>
       <c r="P21" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R21" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="S21" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T21" s="2">
         <v>173</v>
@@ -3197,10 +3227,10 @@
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B22" t="s">
         <v>143</v>
-      </c>
-      <c r="B22" t="s">
-        <v>620</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>144</v>
@@ -3218,13 +3248,13 @@
         <v>148</v>
       </c>
       <c r="P22" t="s">
+        <v>63</v>
+      </c>
+      <c r="R22" t="s">
         <v>64</v>
       </c>
-      <c r="R22" t="s">
-        <v>65</v>
-      </c>
       <c r="S22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T22" s="2">
         <v>65</v>
@@ -3241,10 +3271,10 @@
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" t="s">
         <v>143</v>
-      </c>
-      <c r="B23" t="s">
-        <v>620</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>149</v>
@@ -3265,13 +3295,13 @@
         <v>154</v>
       </c>
       <c r="P23" t="s">
+        <v>63</v>
+      </c>
+      <c r="R23" t="s">
         <v>64</v>
       </c>
-      <c r="R23" t="s">
-        <v>65</v>
-      </c>
       <c r="S23" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T23" s="2" t="s">
         <v>155</v>
@@ -3288,19 +3318,19 @@
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" t="s">
         <v>143</v>
-      </c>
-      <c r="B24" t="s">
-        <v>620</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>156</v>
       </c>
       <c r="E24" t="s">
+        <v>81</v>
+      </c>
+      <c r="F24" t="s">
         <v>82</v>
-      </c>
-      <c r="F24" t="s">
-        <v>83</v>
       </c>
       <c r="J24" t="s">
         <v>157</v>
@@ -3312,10 +3342,13 @@
         <v>159</v>
       </c>
       <c r="P24" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R24" t="s">
+        <v>30</v>
       </c>
       <c r="S24" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T24" s="2" t="s">
         <v>160</v>
@@ -3332,19 +3365,19 @@
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
         <v>143</v>
-      </c>
-      <c r="B25" t="s">
-        <v>620</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>161</v>
       </c>
       <c r="E25" t="s">
+        <v>81</v>
+      </c>
+      <c r="F25" t="s">
         <v>82</v>
-      </c>
-      <c r="F25" t="s">
-        <v>83</v>
       </c>
       <c r="J25" t="s">
         <v>162</v>
@@ -3356,7 +3389,10 @@
         <v>164</v>
       </c>
       <c r="P25" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R25" t="s">
+        <v>111</v>
       </c>
       <c r="S25" t="s">
         <v>165</v>
@@ -3376,16 +3412,16 @@
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" t="s">
         <v>143</v>
-      </c>
-      <c r="B26" t="s">
-        <v>620</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>166</v>
       </c>
       <c r="E26" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F26" t="s">
         <v>167</v>
@@ -3402,6 +3438,9 @@
       <c r="P26" t="s">
         <v>171</v>
       </c>
+      <c r="R26" s="7" t="s">
+        <v>171</v>
+      </c>
       <c r="S26" t="s">
         <v>172</v>
       </c>
@@ -3420,19 +3459,19 @@
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>142</v>
+      </c>
+      <c r="B27" t="s">
         <v>143</v>
-      </c>
-      <c r="B27" t="s">
-        <v>620</v>
       </c>
       <c r="D27" s="5">
         <v>1480</v>
       </c>
       <c r="E27" t="s">
+        <v>125</v>
+      </c>
+      <c r="F27" t="s">
         <v>126</v>
-      </c>
-      <c r="F27" t="s">
-        <v>127</v>
       </c>
       <c r="J27" t="s">
         <v>173</v>
@@ -3441,10 +3480,13 @@
         <v>174</v>
       </c>
       <c r="P27" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R27" t="s">
+        <v>30</v>
       </c>
       <c r="S27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T27" s="2">
         <v>40</v>
@@ -3470,10 +3512,10 @@
         <v>177</v>
       </c>
       <c r="E28" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" t="s">
         <v>82</v>
-      </c>
-      <c r="F28" t="s">
-        <v>83</v>
       </c>
       <c r="J28" t="s">
         <v>178</v>
@@ -3485,13 +3527,13 @@
         <v>180</v>
       </c>
       <c r="P28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S28" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T28" s="2">
         <v>126</v>
@@ -3517,7 +3559,7 @@
         <v>182</v>
       </c>
       <c r="E29" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F29" t="s">
         <v>183</v>
@@ -3541,13 +3583,13 @@
         <v>189</v>
       </c>
       <c r="P29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R29" t="s">
         <v>190</v>
       </c>
       <c r="S29" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T29" s="2">
         <v>241</v>
@@ -3573,7 +3615,7 @@
         <v>191</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
         <v>192</v>
@@ -3588,13 +3630,13 @@
         <v>195</v>
       </c>
       <c r="P30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R30" t="s">
         <v>196</v>
       </c>
       <c r="S30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T30" s="2" t="s">
         <v>197</v>
@@ -3620,10 +3662,10 @@
         <v>198</v>
       </c>
       <c r="E31" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F31" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J31" t="s">
         <v>199</v>
@@ -3638,13 +3680,13 @@
         <v>202</v>
       </c>
       <c r="P31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R31" t="s">
         <v>203</v>
       </c>
       <c r="S31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T31" s="2">
         <v>67</v>
@@ -3667,13 +3709,13 @@
         <v>176</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E32" t="s">
+        <v>81</v>
+      </c>
+      <c r="F32" t="s">
         <v>82</v>
-      </c>
-      <c r="F32" t="s">
-        <v>83</v>
       </c>
       <c r="J32" t="s">
         <v>204</v>
@@ -3685,13 +3727,13 @@
         <v>206</v>
       </c>
       <c r="P32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R32" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T32" s="2">
         <v>59</v>
@@ -3717,10 +3759,10 @@
         <v>207</v>
       </c>
       <c r="E33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F33" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H33" t="s">
         <v>208</v>
@@ -3735,10 +3777,10 @@
         <v>211</v>
       </c>
       <c r="P33" t="s">
+        <v>63</v>
+      </c>
+      <c r="R33" t="s">
         <v>64</v>
-      </c>
-      <c r="R33" t="s">
-        <v>65</v>
       </c>
       <c r="S33" t="s">
         <v>212</v>
@@ -3764,10 +3806,10 @@
         <v>213</v>
       </c>
       <c r="E34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F34" t="s">
         <v>82</v>
-      </c>
-      <c r="F34" t="s">
-        <v>83</v>
       </c>
       <c r="J34" t="s">
         <v>214</v>
@@ -3779,10 +3821,10 @@
         <v>216</v>
       </c>
       <c r="P34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S34" t="s">
         <v>217</v>
@@ -3811,10 +3853,10 @@
         <v>218</v>
       </c>
       <c r="E35" t="s">
+        <v>81</v>
+      </c>
+      <c r="F35" t="s">
         <v>82</v>
-      </c>
-      <c r="F35" t="s">
-        <v>83</v>
       </c>
       <c r="J35" t="s">
         <v>219</v>
@@ -3832,7 +3874,7 @@
         <v>223</v>
       </c>
       <c r="R35" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S35" t="s">
         <v>224</v>
@@ -3855,34 +3897,37 @@
         <v>225</v>
       </c>
       <c r="B36" t="s">
-        <v>621</v>
+        <v>226</v>
       </c>
       <c r="C36" t="s">
-        <v>622</v>
+        <v>227</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E36" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="J36" t="s">
+        <v>49</v>
+      </c>
+      <c r="K36" t="s">
         <v>50</v>
       </c>
-      <c r="K36" t="s">
-        <v>51</v>
-      </c>
       <c r="L36" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="P36" t="s">
-        <v>230</v>
+        <v>232</v>
+      </c>
+      <c r="R36" s="7" t="s">
+        <v>233</v>
       </c>
       <c r="S36" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T36" s="2">
         <v>165</v>
@@ -3902,37 +3947,40 @@
         <v>225</v>
       </c>
       <c r="B37" t="s">
-        <v>621</v>
+        <v>226</v>
       </c>
       <c r="C37" t="s">
-        <v>622</v>
+        <v>227</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E37" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F37" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="H37" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="J37" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="K37" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="P37" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="S37" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T37" s="2">
         <v>50</v>
@@ -3952,34 +4000,37 @@
         <v>225</v>
       </c>
       <c r="B38" t="s">
-        <v>621</v>
+        <v>226</v>
       </c>
       <c r="C38" t="s">
-        <v>622</v>
+        <v>227</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E38" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F38" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J38" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="K38" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="P38" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R38" t="s">
+        <v>111</v>
       </c>
       <c r="S38" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T38" s="2">
         <v>55</v>
@@ -3999,34 +4050,37 @@
         <v>225</v>
       </c>
       <c r="B39" t="s">
-        <v>621</v>
+        <v>226</v>
       </c>
       <c r="C39" t="s">
-        <v>622</v>
+        <v>227</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>218</v>
       </c>
       <c r="E39" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F39" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J39" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K39" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="P39" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R39" t="s">
+        <v>30</v>
       </c>
       <c r="S39" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T39" s="2">
         <v>50</v>
@@ -4043,40 +4097,40 @@
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B40" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="E40" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F40" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="H40" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J40" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="K40" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="P40" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="R40" t="s">
         <v>196</v>
       </c>
       <c r="S40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T40" s="2">
         <v>210</v>
@@ -4093,37 +4147,37 @@
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B41" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E41" t="s">
+        <v>58</v>
+      </c>
+      <c r="F41" t="s">
         <v>59</v>
       </c>
-      <c r="F41" t="s">
-        <v>60</v>
-      </c>
       <c r="J41" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="K41" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="P41" t="s">
+        <v>63</v>
+      </c>
+      <c r="R41" t="s">
         <v>64</v>
       </c>
-      <c r="R41" t="s">
-        <v>65</v>
-      </c>
       <c r="S41" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T41" s="2">
         <v>76</v>
@@ -4140,40 +4194,40 @@
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B42" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="E42" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F42" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H42" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="J42" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="K42" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="P42" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="R42" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="S42" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="T42" s="2">
         <v>1800</v>
@@ -4190,43 +4244,43 @@
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B43" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E43" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F43" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H43" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="J43" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K43" t="s">
+        <v>275</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="M43" t="s">
+        <v>268</v>
+      </c>
+      <c r="P43" t="s">
+        <v>52</v>
+      </c>
+      <c r="R43" t="s">
+        <v>277</v>
+      </c>
+      <c r="S43" t="s">
         <v>272</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="M43" t="s">
-        <v>265</v>
-      </c>
-      <c r="P43" t="s">
-        <v>53</v>
-      </c>
-      <c r="R43" t="s">
-        <v>274</v>
-      </c>
-      <c r="S43" t="s">
-        <v>269</v>
       </c>
       <c r="T43" s="2">
         <v>99</v>
@@ -4243,40 +4297,40 @@
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B44" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F44" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H44" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J44" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K44" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="P44" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R44" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="S44" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T44" s="2">
         <v>439</v>
@@ -4290,40 +4344,40 @@
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F45" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="H45" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="J45" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K45" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="P45" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="R45" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="S45" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T45" s="2">
         <v>244</v>
@@ -4340,28 +4394,31 @@
         <v>175</v>
       </c>
       <c r="B46" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E46" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F46" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J46" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="P46" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R46" s="7" t="s">
+        <v>295</v>
       </c>
       <c r="S46" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="T46" s="2">
         <v>100</v>
@@ -4381,31 +4438,34 @@
         <v>175</v>
       </c>
       <c r="B47" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E47" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F47" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J47" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K47" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="P47" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R47" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S47" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T47" s="2">
         <v>118</v>
@@ -4425,31 +4485,34 @@
         <v>175</v>
       </c>
       <c r="B48" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D48" s="5">
         <v>1475</v>
       </c>
       <c r="E48" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F48" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="J48" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K48" t="s">
+        <v>307</v>
+      </c>
+      <c r="L48" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="P48" t="s">
+        <v>52</v>
+      </c>
+      <c r="R48" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S48" t="s">
         <v>303</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="P48" t="s">
-        <v>53</v>
-      </c>
-      <c r="S48" t="s">
-        <v>299</v>
       </c>
       <c r="T48" s="2">
         <v>80</v>
@@ -4469,31 +4532,34 @@
         <v>175</v>
       </c>
       <c r="B49" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>156</v>
       </c>
       <c r="E49" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J49" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K49" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="P49" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R49" t="s">
+        <v>36</v>
       </c>
       <c r="S49" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T49" s="2">
         <v>270</v>
@@ -4513,31 +4579,34 @@
         <v>175</v>
       </c>
       <c r="B50" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D50" s="5">
         <v>1489</v>
       </c>
       <c r="E50" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F50" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="J50" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="P50" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R50" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S50" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T50" s="2">
         <v>163</v>
@@ -4557,34 +4626,37 @@
         <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F51" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J51" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="K51" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="L51" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="P51" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R51" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S51" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T51" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="U51" s="2">
         <v>210</v>
@@ -4601,31 +4673,34 @@
         <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E52" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F52" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J52" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="K52" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="P52" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R52" t="s">
+        <v>37</v>
       </c>
       <c r="S52" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T52" s="2">
         <v>370</v>
@@ -4645,28 +4720,31 @@
         <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D53" s="5">
         <v>1489</v>
       </c>
       <c r="E53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F53" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="J53" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="P53" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R53" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S53" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T53" s="2">
         <v>44</v>
@@ -4683,34 +4761,37 @@
     </row>
     <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B54" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="E54" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F54" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J54" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="K54" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="P54" t="s">
-        <v>334</v>
+        <v>338</v>
+      </c>
+      <c r="R54" t="s">
+        <v>36</v>
       </c>
       <c r="S54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T54" s="2">
         <v>348</v>
@@ -4727,34 +4808,37 @@
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B55" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E55" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F55" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J55" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="K55" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="P55" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R55" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S55" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T55" s="2">
         <v>200</v>
@@ -4771,34 +4855,37 @@
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B56" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D56" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="E56" t="s">
+        <v>81</v>
+      </c>
+      <c r="F56" t="s">
         <v>340</v>
       </c>
-      <c r="E56" t="s">
-        <v>82</v>
-      </c>
-      <c r="F56" t="s">
-        <v>336</v>
-      </c>
       <c r="J56" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="K56" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="P56" t="s">
-        <v>344</v>
+        <v>348</v>
+      </c>
+      <c r="R56" t="s">
+        <v>338</v>
       </c>
       <c r="S56" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T56" s="2">
         <v>420</v>
@@ -4815,34 +4902,37 @@
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B57" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E57" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F57" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="J57" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="K57" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="P57" t="s">
-        <v>350</v>
+        <v>354</v>
+      </c>
+      <c r="R57" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S57" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="U57" s="2">
         <v>120</v>
@@ -4856,37 +4946,40 @@
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B58" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E58" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F58" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="J58" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="K58" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="P58" t="s">
-        <v>37</v>
+        <v>36</v>
+      </c>
+      <c r="R58" t="s">
+        <v>36</v>
       </c>
       <c r="S58" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T58" s="2">
         <v>150</v>
@@ -4903,34 +4996,37 @@
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B59" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D59" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E59" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F59" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="J59" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="K59" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="P59" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R59" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S59" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T59" s="2">
         <v>118</v>
@@ -4947,34 +5043,37 @@
     </row>
     <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B60" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D60" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="E60" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F60" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J60" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K60" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="P60" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R60" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S60" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T60" s="2">
         <v>57</v>
@@ -4985,34 +5084,37 @@
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B61" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D61" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="E61" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F61" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="J61" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="K61" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L61" s="6" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="P61" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="R61" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="S61" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="T61" s="2">
         <v>70</v>
@@ -5026,19 +5128,19 @@
     </row>
     <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B62" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="E62" t="s">
+        <v>81</v>
+      </c>
+      <c r="F62" t="s">
         <v>82</v>
-      </c>
-      <c r="F62" t="s">
-        <v>83</v>
       </c>
       <c r="J62" t="s">
         <v>178</v>
@@ -5047,19 +5149,19 @@
         <v>179</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="P62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="U62" s="2">
         <v>51</v>
@@ -5073,40 +5175,40 @@
     </row>
     <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B63" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="E63" t="s">
+        <v>81</v>
+      </c>
+      <c r="F63" t="s">
         <v>82</v>
-      </c>
-      <c r="F63" t="s">
-        <v>83</v>
       </c>
       <c r="J63" t="s">
         <v>178</v>
       </c>
       <c r="K63" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="P63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R63" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S63" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="U63" s="2">
         <v>57</v>
@@ -5117,40 +5219,40 @@
     </row>
     <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E64" t="s">
+        <v>81</v>
+      </c>
+      <c r="F64" t="s">
         <v>82</v>
       </c>
-      <c r="F64" t="s">
-        <v>83</v>
-      </c>
       <c r="J64" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="K64" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="P64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R64" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T64" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="U64" s="2">
         <v>64</v>
@@ -5164,37 +5266,37 @@
     </row>
     <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="E65" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F65" t="s">
         <v>183</v>
       </c>
       <c r="J65" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="K65" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="P65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R65" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S65" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T65" s="2">
         <v>248</v>
@@ -5211,49 +5313,49 @@
     </row>
     <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B66" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E66" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F66" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="J66" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="K66" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="M66" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="P66" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R66" t="s">
+        <v>44</v>
+      </c>
+      <c r="S66" t="s">
         <v>45</v>
       </c>
-      <c r="S66" t="s">
-        <v>46</v>
-      </c>
       <c r="T66" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="U66" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="V66" s="2">
         <v>7</v>
@@ -5264,34 +5366,37 @@
     </row>
     <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B67" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E67" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F67" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J67" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="K67" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="P67" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R67" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="S67" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="T67" s="2">
         <v>420</v>
@@ -5308,43 +5413,43 @@
     </row>
     <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B68" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="E68" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F68" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="J68" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="K68" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="P68" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R68" t="s">
         <v>196</v>
       </c>
       <c r="S68" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="U68" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="W68" s="2">
         <v>1</v>
@@ -5352,37 +5457,40 @@
     </row>
     <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="B69" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E69" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F69" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J69" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="K69" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="P69" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R69" t="s">
+        <v>30</v>
       </c>
       <c r="S69" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="U69" s="2">
         <v>51</v>
@@ -5396,46 +5504,46 @@
     </row>
     <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B70" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E70" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F70" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J70" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="K70" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="P70" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R70" t="s">
+        <v>44</v>
+      </c>
+      <c r="S70" t="s">
         <v>45</v>
       </c>
-      <c r="S70" t="s">
-        <v>46</v>
-      </c>
       <c r="T70" s="2" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="U70" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="V70" s="2">
         <v>11</v>
@@ -5446,46 +5554,46 @@
     </row>
     <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B71" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E71" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F71" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J71" t="s">
+        <v>422</v>
+      </c>
+      <c r="K71" t="s">
+        <v>423</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="N71" s="1" t="s">
         <v>418</v>
       </c>
-      <c r="K71" t="s">
-        <v>419</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>420</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>414</v>
-      </c>
       <c r="P71" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S71" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="U71" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="W71" s="2">
         <v>1</v>
@@ -5493,16 +5601,16 @@
     </row>
     <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B72" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E72" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F72" t="s">
         <v>183</v>
@@ -5511,31 +5619,31 @@
         <v>184</v>
       </c>
       <c r="J72" t="s">
+        <v>114</v>
+      </c>
+      <c r="K72" t="s">
         <v>115</v>
       </c>
-      <c r="K72" t="s">
-        <v>116</v>
-      </c>
       <c r="L72" s="4" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="M72" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="P72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R72" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S72" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="W72" s="2">
         <v>1</v>
@@ -5543,16 +5651,16 @@
     </row>
     <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B73" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E73" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F73" t="s">
         <v>183</v>
@@ -5561,31 +5669,31 @@
         <v>184</v>
       </c>
       <c r="J73" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="K73" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="M73" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="P73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R73" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S73" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T73" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="U73" s="2">
         <v>100</v>
@@ -5599,16 +5707,16 @@
     </row>
     <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B74" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E74" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F74" t="s">
         <v>183</v>
@@ -5617,28 +5725,28 @@
         <v>184</v>
       </c>
       <c r="J74" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="K74" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="M74" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="P74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R74" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="S74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T74" s="2">
         <v>237</v>
@@ -5655,143 +5763,143 @@
     </row>
     <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B75" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E75" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F75" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="J75" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="K75" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="P75" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R75" t="s">
+        <v>44</v>
+      </c>
+      <c r="S75" t="s">
         <v>45</v>
       </c>
-      <c r="S75" t="s">
-        <v>46</v>
-      </c>
       <c r="T75" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="V75" s="2">
         <v>8</v>
       </c>
       <c r="W75" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B76" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E76" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="F76" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="J76" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="K76" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="P76" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R76" t="s">
+        <v>44</v>
+      </c>
+      <c r="S76" t="s">
         <v>45</v>
       </c>
-      <c r="S76" t="s">
-        <v>46</v>
-      </c>
       <c r="T76" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="U76" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="V76" s="2">
         <v>8</v>
       </c>
       <c r="W76" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="B77" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E77" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F77" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="H77" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="J77" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="K77" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="P77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="S77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T77" s="2">
         <v>85</v>
@@ -5800,45 +5908,45 @@
         <v>193</v>
       </c>
       <c r="W77" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B78" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E78" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="F78" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="H78" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="J78" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="K78" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="P78" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R78" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="S78" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T78" s="2">
         <v>50</v>
@@ -5855,40 +5963,40 @@
     </row>
     <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B79" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E79" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F79" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="H79" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="J79" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="K79" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="P79" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="R79" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="S79" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T79" s="2">
         <v>3500</v>
@@ -5897,45 +6005,45 @@
         <v>1000</v>
       </c>
       <c r="W79" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B80" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D80" s="5">
         <v>1475</v>
       </c>
       <c r="E80" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="F80" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="H80" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="J80" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="K80" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="P80" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R80" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="S80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T80" s="2">
         <v>44</v>
@@ -5947,45 +6055,45 @@
         <v>24</v>
       </c>
       <c r="W80" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B81" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E81" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F81" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="H81" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="J81" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="K81" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="P81" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R81" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="S81" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="T81" s="2">
         <v>44</v>
@@ -5994,39 +6102,39 @@
         <v>42</v>
       </c>
       <c r="W81" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B82" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E82" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F82" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J82" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="P82" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="R82" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S82" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T82" s="2">
         <v>1200</v>
@@ -6035,42 +6143,42 @@
         <v>700</v>
       </c>
       <c r="W82" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E83" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F83" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J83" t="s">
+        <v>49</v>
+      </c>
+      <c r="K83" t="s">
         <v>50</v>
       </c>
-      <c r="K83" t="s">
-        <v>51</v>
-      </c>
       <c r="L83" s="4" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="P83" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="R83" t="s">
-        <v>498</v>
+        <v>233</v>
       </c>
       <c r="S83" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T83" s="2">
         <v>180</v>
@@ -6079,42 +6187,42 @@
         <v>400</v>
       </c>
       <c r="W83" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B84" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="E84" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="F84" t="s">
+        <v>504</v>
+      </c>
+      <c r="J84" t="s">
+        <v>505</v>
+      </c>
+      <c r="K84" t="s">
+        <v>50</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="P84" t="s">
         <v>501</v>
       </c>
-      <c r="J84" t="s">
-        <v>502</v>
-      </c>
-      <c r="K84" t="s">
-        <v>51</v>
-      </c>
-      <c r="L84" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="P84" t="s">
-        <v>497</v>
-      </c>
       <c r="R84" t="s">
-        <v>498</v>
+        <v>233</v>
       </c>
       <c r="S84" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T84" s="2">
         <v>175</v>
@@ -6126,45 +6234,45 @@
         <v>200</v>
       </c>
       <c r="W84" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B85" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E85" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="F85" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="H85" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="J85" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="K85" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="P85" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="R85" t="s">
-        <v>498</v>
+        <v>233</v>
       </c>
       <c r="S85" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T85" s="2">
         <v>180</v>
@@ -6176,45 +6284,45 @@
         <v>110</v>
       </c>
       <c r="W85" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B86" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E86" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F86" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="H86" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="J86" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="K86" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="P86" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="R86" t="s">
-        <v>498</v>
+        <v>233</v>
       </c>
       <c r="S86" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T86" s="2">
         <v>180</v>
@@ -6226,45 +6334,48 @@
         <v>250</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B87" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E87" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F87" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J87" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="K87" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="N87" s="1" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="P87" t="s">
         <v>190</v>
       </c>
+      <c r="R87" s="7" t="s">
+        <v>30</v>
+      </c>
       <c r="S87" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="T87" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="U87" s="2">
         <v>55</v>
@@ -6278,34 +6389,37 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E88" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F88" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J88" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="K88" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="P88" t="s">
+        <v>36</v>
+      </c>
+      <c r="R88" t="s">
         <v>37</v>
       </c>
       <c r="S88" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="T88" s="2">
         <v>1200</v>
@@ -6319,34 +6433,37 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B89" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="E89" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="F89" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="J89" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="K89" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="P89" t="s">
+        <v>36</v>
+      </c>
+      <c r="R89" t="s">
         <v>37</v>
       </c>
       <c r="S89" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="T89" s="2">
         <v>150</v>
@@ -6360,37 +6477,37 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B90" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="E90" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="F90" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="J90" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="K90" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="P90" t="s">
+        <v>63</v>
+      </c>
+      <c r="R90" t="s">
         <v>64</v>
       </c>
-      <c r="R90" t="s">
-        <v>65</v>
-      </c>
       <c r="S90" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T90" s="2">
         <v>170</v>
@@ -6407,34 +6524,37 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="B91" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E91" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="F91" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="J91" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="K91" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="P91" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R91" t="s">
+        <v>30</v>
       </c>
       <c r="S91" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="T91" s="2">
         <v>38</v>
@@ -6451,37 +6571,37 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B92" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E92" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F92" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="J92" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="K92" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="P92" t="s">
+        <v>63</v>
+      </c>
+      <c r="R92" t="s">
         <v>64</v>
       </c>
-      <c r="R92" t="s">
-        <v>65</v>
-      </c>
       <c r="S92" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T92" s="2">
         <v>400</v>
@@ -6495,37 +6615,37 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B93" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D93" s="5">
         <v>1456</v>
       </c>
       <c r="E93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F93" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="J93" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="K93" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="P93" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R93" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S93" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T93" s="2">
         <v>58</v>
@@ -6537,42 +6657,42 @@
         <v>30</v>
       </c>
       <c r="W93" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B94" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E94" t="s">
+        <v>81</v>
+      </c>
+      <c r="F94" t="s">
         <v>82</v>
       </c>
-      <c r="F94" t="s">
-        <v>83</v>
-      </c>
       <c r="J94" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K94" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="P94" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R94" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="S94" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T94" s="2">
         <v>53</v>
@@ -6581,42 +6701,42 @@
         <v>57</v>
       </c>
       <c r="W94" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B95" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D95" s="5">
         <v>1470</v>
       </c>
       <c r="E95" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="F95" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="J95" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K95" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="P95" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R95" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S95" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T95" s="2">
         <v>73</v>
@@ -6625,42 +6745,42 @@
         <v>53</v>
       </c>
       <c r="W95" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B96" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E96" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F96" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="J96" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="K96" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="P96" t="s">
+        <v>63</v>
+      </c>
+      <c r="R96" t="s">
         <v>64</v>
       </c>
-      <c r="R96" t="s">
-        <v>65</v>
-      </c>
       <c r="S96" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="T96" s="2">
         <v>715</v>
@@ -6669,42 +6789,42 @@
         <v>316</v>
       </c>
       <c r="W96" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B97" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E97" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F97" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="J97" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="K97" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="P97" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R97" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="S97" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="T97" s="2">
         <v>250</v>
@@ -6713,48 +6833,48 @@
         <v>300</v>
       </c>
       <c r="W97" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="B98" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E98" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="F98" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="H98" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="J98" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="K98" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="N98" s="1" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="P98" t="s">
+        <v>63</v>
+      </c>
+      <c r="R98" t="s">
         <v>64</v>
       </c>
-      <c r="R98" t="s">
-        <v>65</v>
-      </c>
       <c r="S98" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T98" s="2">
         <v>466</v>
@@ -6766,36 +6886,39 @@
         <v>50</v>
       </c>
       <c r="W98" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B99" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E99" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F99" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J99" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="P99" t="s">
+        <v>36</v>
+      </c>
+      <c r="R99" t="s">
         <v>37</v>
       </c>
       <c r="S99" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="T99" s="2">
         <v>1300</v>
@@ -6809,37 +6932,37 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B100" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E100" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F100" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="J100" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="K100" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="P100" t="s">
+        <v>63</v>
+      </c>
+      <c r="R100" t="s">
         <v>64</v>
       </c>
-      <c r="R100" t="s">
-        <v>65</v>
-      </c>
       <c r="S100" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="T100" s="2">
         <v>386</v>
@@ -6856,34 +6979,37 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B101" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D101" s="5">
         <v>1495</v>
       </c>
       <c r="E101" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F101" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J101" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K101" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="P101" t="s">
-        <v>45</v>
+        <v>44</v>
+      </c>
+      <c r="R101" s="7" t="s">
+        <v>64</v>
       </c>
       <c r="S101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T101" s="2">
         <v>198</v>
@@ -6900,37 +7026,40 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B102" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="E102" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F102" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J102" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="K102" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M102" s="1" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="P102" t="s">
         <v>171</v>
       </c>
+      <c r="R102" t="s">
+        <v>30</v>
+      </c>
       <c r="S102" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="T102" s="2">
         <v>250</v>
@@ -6941,34 +7070,37 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B103" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="E103" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="F103" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="J103" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K103" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="P103" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="R103" t="s">
+        <v>30</v>
       </c>
       <c r="S103" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="T103" s="2">
         <v>140</v>
@@ -6985,37 +7117,37 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B104" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E104" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="F104" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="J104" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="K104" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="P104" t="s">
+        <v>63</v>
+      </c>
+      <c r="R104" t="s">
         <v>64</v>
       </c>
-      <c r="R104" t="s">
-        <v>65</v>
-      </c>
       <c r="S104" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="T104" s="2">
         <v>112</v>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76245ACB-C2B3-4E12-BF39-01823B480FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD86B021-6E1A-4EA7-8430-84248A2D1470}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="624">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1703,9 +1703,6 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG/1280px-Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
-  </si>
-  <si>
-    <t>Victoria and Albety Museum</t>
   </si>
   <si>
     <t>Buste de Giovanni Chellini</t>
@@ -2374,7 +2371,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
@@ -2421,7 +2418,7 @@
         <v>24</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="E3" t="s">
         <v>25</v>
@@ -6627,16 +6624,16 @@
         <v>47</v>
       </c>
       <c r="F93" t="s">
+        <v>48</v>
+      </c>
+      <c r="J93" t="s">
         <v>561</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>562</v>
       </c>
-      <c r="K93" t="s">
+      <c r="L93" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="L93" s="4" t="s">
-        <v>564</v>
       </c>
       <c r="P93" t="s">
         <v>30</v>
@@ -6677,13 +6674,13 @@
         <v>82</v>
       </c>
       <c r="J94" t="s">
+        <v>564</v>
+      </c>
+      <c r="K94" t="s">
         <v>565</v>
       </c>
-      <c r="K94" t="s">
+      <c r="L94" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="L94" s="4" t="s">
-        <v>567</v>
       </c>
       <c r="P94" t="s">
         <v>30</v>
@@ -6715,10 +6712,10 @@
         <v>1470</v>
       </c>
       <c r="E95" t="s">
+        <v>567</v>
+      </c>
+      <c r="F95" t="s">
         <v>568</v>
-      </c>
-      <c r="F95" t="s">
-        <v>569</v>
       </c>
       <c r="J95" t="s">
         <v>363</v>
@@ -6727,7 +6724,7 @@
         <v>364</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="P95" t="s">
         <v>52</v>
@@ -6750,7 +6747,7 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B96" t="s">
         <v>556</v>
@@ -6765,13 +6762,13 @@
         <v>103</v>
       </c>
       <c r="J96" t="s">
+        <v>571</v>
+      </c>
+      <c r="K96" t="s">
         <v>572</v>
       </c>
-      <c r="K96" t="s">
+      <c r="L96" s="4" t="s">
         <v>573</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>574</v>
       </c>
       <c r="P96" t="s">
         <v>63</v>
@@ -6780,7 +6777,7 @@
         <v>64</v>
       </c>
       <c r="S96" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="T96" s="2">
         <v>715</v>
@@ -6794,37 +6791,37 @@
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B97" t="s">
         <v>556</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E97" t="s">
         <v>324</v>
       </c>
       <c r="F97" t="s">
+        <v>576</v>
+      </c>
+      <c r="J97" t="s">
         <v>577</v>
       </c>
-      <c r="J97" t="s">
+      <c r="K97" t="s">
         <v>578</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" s="4" t="s">
         <v>579</v>
-      </c>
-      <c r="L97" s="4" t="s">
-        <v>580</v>
       </c>
       <c r="P97" t="s">
         <v>52</v>
       </c>
       <c r="R97" t="s">
+        <v>580</v>
+      </c>
+      <c r="S97" t="s">
         <v>581</v>
-      </c>
-      <c r="S97" t="s">
-        <v>582</v>
       </c>
       <c r="T97" s="2">
         <v>250</v>
@@ -6838,34 +6835,34 @@
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B98" t="s">
         <v>556</v>
       </c>
       <c r="D98" s="5" t="s">
+        <v>582</v>
+      </c>
+      <c r="E98" t="s">
         <v>583</v>
       </c>
-      <c r="E98" t="s">
+      <c r="F98" t="s">
         <v>584</v>
       </c>
-      <c r="F98" t="s">
+      <c r="H98" t="s">
         <v>585</v>
       </c>
-      <c r="H98" t="s">
+      <c r="J98" t="s">
         <v>586</v>
       </c>
-      <c r="J98" t="s">
+      <c r="K98" t="s">
         <v>587</v>
       </c>
-      <c r="K98" t="s">
+      <c r="L98" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="L98" s="4" t="s">
+      <c r="N98" s="1" t="s">
         <v>589</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>590</v>
       </c>
       <c r="P98" t="s">
         <v>63</v>
@@ -6891,25 +6888,25 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>590</v>
+      </c>
+      <c r="B99" t="s">
         <v>591</v>
       </c>
-      <c r="B99" t="s">
+      <c r="D99" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="D99" s="5" t="s">
+      <c r="E99" t="s">
         <v>593</v>
       </c>
-      <c r="E99" t="s">
+      <c r="F99" t="s">
         <v>594</v>
       </c>
-      <c r="F99" t="s">
+      <c r="J99" t="s">
         <v>595</v>
       </c>
-      <c r="J99" t="s">
+      <c r="L99" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>597</v>
       </c>
       <c r="P99" t="s">
         <v>36</v>
@@ -6918,7 +6915,7 @@
         <v>37</v>
       </c>
       <c r="S99" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="T99" s="2">
         <v>1300</v>
@@ -6932,28 +6929,28 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>590</v>
+      </c>
+      <c r="B100" t="s">
         <v>591</v>
-      </c>
-      <c r="B100" t="s">
-        <v>592</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>549</v>
       </c>
       <c r="E100" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F100" t="s">
+        <v>598</v>
+      </c>
+      <c r="J100" t="s">
         <v>599</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>600</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" s="4" t="s">
         <v>601</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>602</v>
       </c>
       <c r="P100" t="s">
         <v>63</v>
@@ -6962,7 +6959,7 @@
         <v>64</v>
       </c>
       <c r="S100" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="T100" s="2">
         <v>386</v>
@@ -6979,28 +6976,28 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
+        <v>590</v>
+      </c>
+      <c r="B101" t="s">
         <v>591</v>
-      </c>
-      <c r="B101" t="s">
-        <v>592</v>
       </c>
       <c r="D101" s="5">
         <v>1495</v>
       </c>
       <c r="E101" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F101" t="s">
+        <v>603</v>
+      </c>
+      <c r="J101" t="s">
         <v>604</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>605</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" s="4" t="s">
         <v>606</v>
-      </c>
-      <c r="L101" s="4" t="s">
-        <v>607</v>
       </c>
       <c r="P101" t="s">
         <v>44</v>
@@ -7026,31 +7023,31 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>590</v>
+      </c>
+      <c r="B102" t="s">
         <v>591</v>
       </c>
-      <c r="B102" t="s">
-        <v>592</v>
-      </c>
       <c r="D102" s="5" t="s">
+        <v>607</v>
+      </c>
+      <c r="E102" t="s">
+        <v>593</v>
+      </c>
+      <c r="F102" t="s">
+        <v>594</v>
+      </c>
+      <c r="J102" t="s">
         <v>608</v>
       </c>
-      <c r="E102" t="s">
-        <v>594</v>
-      </c>
-      <c r="F102" t="s">
-        <v>595</v>
-      </c>
-      <c r="J102" t="s">
+      <c r="K102" t="s">
         <v>609</v>
       </c>
-      <c r="K102" t="s">
+      <c r="L102" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="L102" s="4" t="s">
+      <c r="M102" s="1" t="s">
         <v>611</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>612</v>
       </c>
       <c r="P102" t="s">
         <v>171</v>
@@ -7059,7 +7056,7 @@
         <v>30</v>
       </c>
       <c r="S102" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="T102" s="2">
         <v>250</v>
@@ -7070,28 +7067,28 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>590</v>
+      </c>
+      <c r="B103" t="s">
         <v>591</v>
       </c>
-      <c r="B103" t="s">
-        <v>592</v>
-      </c>
       <c r="D103" s="5" t="s">
+        <v>613</v>
+      </c>
+      <c r="E103" t="s">
         <v>614</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>615</v>
-      </c>
-      <c r="F103" t="s">
-        <v>616</v>
       </c>
       <c r="J103" t="s">
         <v>363</v>
       </c>
       <c r="K103" t="s">
+        <v>616</v>
+      </c>
+      <c r="L103" s="4" t="s">
         <v>617</v>
-      </c>
-      <c r="L103" s="4" t="s">
-        <v>618</v>
       </c>
       <c r="P103" t="s">
         <v>30</v>
@@ -7117,28 +7114,28 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>590</v>
+      </c>
+      <c r="B104" t="s">
         <v>591</v>
-      </c>
-      <c r="B104" t="s">
-        <v>592</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>549</v>
       </c>
       <c r="E104" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F104" t="s">
+        <v>618</v>
+      </c>
+      <c r="J104" t="s">
         <v>619</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>620</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" s="4" t="s">
         <v>621</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>622</v>
       </c>
       <c r="P104" t="s">
         <v>63</v>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W109"/>
+  <dimension ref="A1:W105"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.28515625" customWidth="1" min="1" max="1"/>
@@ -613,7 +613,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Museo Correr</t>
+          <t>Musée Correr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Badia Fiorentina</t>
+          <t>Badia fiorentina</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bode-Museum</t>
+          <t>Musée Bode</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1457-1459</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2112,47 +2112,47 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Buste de jeune homme en armure</t>
+          <t>Croix de Saint Jean</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Busto de jeune homme en armure</t>
+          <t>Croce del Tesoro di San Giovanni</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg/960px-Antonio_del_Pollaiuolo_-_Bust_of_a_young_warrior_-_Bargello_National_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Betto_di_francesco_betti%2C_antonio_pollaiolo_e_domenico_dei%2C_croce_1457-59_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>Buste</t>
+          <t>Objet liturgique</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr">
+        <is>
+          <t>Objet liturgique</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Terre cuite</t>
+          <t>Argent, émaux et bois</t>
         </is>
       </c>
       <c r="T25" s="2" t="n">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="V25" s="2" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="W25" s="2" t="n">
         <v>3</v>
@@ -2161,17 +2161,17 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>POLLAIUOLO</t>
+          <t>del VERROCCHIO</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>1457-1459</t>
+          <t>1473-1475</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2181,84 +2181,106 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Musée de l'Œuvre du Duomo</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Croix de Saint Jean</t>
+          <t>David</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Croce del Tesoro di San Giovanni</t>
+          <t>David</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Betto_di_francesco_betti%2C_antonio_pollaiolo_e_domenico_dei%2C_croce_1457-59_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Objet liturgique</t>
-        </is>
-      </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>Objet liturgique</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>Argent, émaux et bois</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T26" s="2" t="n">
-        <v>193</v>
+        <v>126</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>POLLAIUOLO</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="n">
-        <v>1480</v>
+          <t>del VERROCCHIO</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>1467-1483</t>
+        </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bode-Museum</t>
+          <t>Église d'Orsanmichele</t>
+        </is>
+      </c>
+      <c r="G27" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Hercule au repos</t>
+          <t>L'Incrédulité de saint Thomas</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Incredulità di san Tommaso</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/f/f6/Berlin_-_Gem%C3%A4ldegalerie_9414.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Copie installée en 1992 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Donatello et Michelozzo en 1423</t>
+        </is>
+      </c>
+      <c r="N27" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg/960px-Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2268,7 +2290,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Groupe Ronde-bosse</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -2277,16 +2299,16 @@
         </is>
       </c>
       <c r="T27" s="2" t="n">
-        <v>40</v>
+        <v>241</v>
       </c>
       <c r="U27" s="2" t="n">
-        <v>16</v>
+        <v>120</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -2302,32 +2324,32 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>1473-1475</t>
+          <t>1480-1488</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Campo Santi Giovanni e Paolo</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Monument équestre à Bartolomeo Colleoni</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Monumento a Bartolomeo Colleoni</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2337,7 +2359,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2345,14 +2367,16 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T28" s="2" t="n">
-        <v>126</v>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>395 (statue) 400 (socle)</t>
+        </is>
       </c>
       <c r="U28" s="2" t="n">
-        <v>56</v>
+        <v>380</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="W28" s="2" t="n">
         <v>2</v>
@@ -2371,7 +2395,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>1467-1483</t>
+          <t>vers 1470</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2381,37 +2405,27 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
-        </is>
-      </c>
-      <c r="G29" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Palazzo Vecchio</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>L'Incrédulité de saint Thomas</t>
+          <t>Enfant au dauphin</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Incredulità di san Tommaso</t>
+          <t>Putto con delfino</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Putto_col_delfino_di_verrocchio_02.JPG/960px-Putto_col_delfino_di_verrocchio_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Copie installée en 1992 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Donatello et Michelozzo en 1423</t>
-        </is>
-      </c>
-      <c r="N29" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg/960px-Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Copie en bronze installée en 1959 dans le cortile de Palazzo Vacchio conçu par Michelozzo en 1453. La fontaine a été conçue par Vasari en 1555.</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2421,7 +2435,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Groupe Ronde-bosse</t>
+          <t>Statue de fontaine</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2430,13 +2444,13 @@
         </is>
       </c>
       <c r="T29" s="2" t="n">
-        <v>241</v>
+        <v>67</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="W29" s="2" t="n">
         <v>2</v>
@@ -2455,32 +2469,32 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>1480-1488</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Campo Santi Giovanni e Paolo</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Monument équestre à Bartolomeo Colleoni</t>
+          <t>Dame au bouquet</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Monumento a Bartolomeo Colleoni</t>
+          <t>Dama col mazzolino</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2490,24 +2504,22 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>395 (statue) 400 (socle)</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>59</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>380</v>
+        <v>46</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>145</v>
+        <v>24</v>
       </c>
       <c r="W30" s="2" t="n">
         <v>2</v>
@@ -2526,7 +2538,7 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>vers 1470</t>
+          <t>1469-1472</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2536,52 +2548,49 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Palazzo Vecchio</t>
+          <t>Basilique San Lorenzo</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Vieille Sacristie</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Enfant au dauphin</t>
+          <t>Tombeau de Pierre et Jean de Médicis</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Putto con delfino</t>
+          <t>Tomba di Piero e Giovanni de' Medici</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Putto_col_delfino_di_verrocchio_02.JPG/960px-Putto_col_delfino_di_verrocchio_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Copie en bronze installée en 1959 dans le cortile de Palazzo Vacchio conçu par Michelozzo en 1453. La fontaine a été conçue par Vasari en 1555.</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Statue de fontaine</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre, bronze et porphyre</t>
         </is>
       </c>
       <c r="T31" s="2" t="n">
-        <v>67</v>
+        <v>540</v>
       </c>
       <c r="U31" s="2" t="n">
-        <v>35</v>
-      </c>
-      <c r="V31" s="2" t="n">
-        <v>45</v>
+        <v>358</v>
       </c>
       <c r="W31" s="2" t="n">
         <v>2</v>
@@ -2590,182 +2599,200 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>del VERROCCHIO</t>
+          <t>d'ANTONIO</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Niccolo dell'ARCA</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Église Santa Maria della Vita</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Dame au bouquet</t>
+          <t>Lamentation sur le Christ mort</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Dama col mazzolino</t>
+          <t>Compianto sul Cristo morto</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>Buste</t>
+          <t>Groupe en ronde-bosse de sept statues</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>Groupe sculptural</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T32" s="2" t="n">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>46</v>
+        <v>350</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>del VERROCCHIO</t>
+          <t>d'ANTONIO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Niccolo dell'ARCA</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>1469-1472</t>
+          <t>1469-1473</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Basilique San Lorenzo</t>
+          <t>Basilique San Domenico</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Vieille Sacristie</t>
+          <t>Arca di San Domenico (Cimaise)</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Tombeau de Pierre et Jean de Médicis</t>
+          <t>Dieu le Père bénissant le monde</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Tomba di Piero e Giovanni de' Medici</t>
+          <t>Dio Padre benedicente il mondo</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R33" s="7" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Marbre, bronze et porphyre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T33" s="2" t="n">
-        <v>540</v>
+        <v>50</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>358</v>
+        <v>20</v>
+      </c>
+      <c r="V33" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>del VERROCCHIO</t>
+          <t>d'ANTONIO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Niccolo dell'ARCA</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>vers 1475</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Musée de la Basilique San Domenico</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Buste de Giuliano de Medici</t>
+          <t>Buste de saint Dominique</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Busto di Giuliano de' Medici</t>
+          <t>Busto di san Domenico</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Verrocchio%2C_giuliano_de%27_medici%2C_1475-78.JPG/1280px-Verrocchio%2C_giuliano_de%27_medici%2C_1475-78.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -2780,31 +2807,36 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Terre cuite peinte</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T34" s="2" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="V34" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="W34" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>del VERROCCHIO</t>
+          <t>d'ANTONIO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Niccolo dell'ARCA</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2814,195 +2846,180 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Modène</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Galerie Estense</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Décollation de saint Jean-Baptiste</t>
+          <t>Sainte Monique</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Decollazione del Battista</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Beheading_of_Saint_John.jpg/1280px-Beheading_of_Saint_John.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Autel d'argent de San Giovanni</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Haut-relief intégrant des éléments de ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>Argent</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T35" s="2" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="W35" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Niccolo</t>
+          <t>Jacopo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>d'ANTONIO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Niccolo dell'ARCA</t>
+          <t>della QUERCIA</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>1409-1419</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Eglise Santa Maria della Vita</t>
+          <t>Piazza del Campo</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Santa Maria della Scala (originaux)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Lamentation sur le Christ mort</t>
+          <t>Fontaine de la Joie</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Compianto sul Cristo morto</t>
+          <t>Fonte Gaia</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse de sept statues</t>
-        </is>
-      </c>
-      <c r="R36" s="7" t="inlineStr">
-        <is>
-          <t>Groupe sculptural</t>
+          <t>Monument sculpté en haut-relief</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T36" s="2" t="n">
-        <v>165</v>
+        <v>210</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>350</v>
+        <v>1020</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>250</v>
+        <v>610</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Niccolo</t>
+          <t>Jacopo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>d'ANTONIO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Niccolo dell'ARCA</t>
+          <t>della QUERCIA</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>1469-1473</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Basilique San Domenico</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Arca di San Domenico (Cimaise)</t>
+          <t>Cathédrale Saint-Martin</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Dieu le Père bénissant le monde</t>
+          <t>Tombeau d'Ilaria del Carretto</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Dio Padre benedicente il mondo</t>
+          <t>Monumento funebre a Ilaria del Carretto</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R37" s="7" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -3011,37 +3028,32 @@
         </is>
       </c>
       <c r="T37" s="2" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Niccolo</t>
+          <t>Jacopo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>d'ANTONIO</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Niccolo dell'ARCA</t>
+          <t>della QUERCIA</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1425-1438</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -3051,124 +3063,134 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Musée de la Basilique San Domenico</t>
+          <t>Basilique San Petronio</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Portail central</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Buste de saint Dominique</t>
+          <t>Portail de San Petronio dit Porta Magna</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Busto di san Domenico</t>
+          <t>Porta Magna</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument mixte en haut-relief et ronde-bosse</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Portail sculpté / Reliefs</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Pierre d'Istrie</t>
         </is>
       </c>
       <c r="T38" s="2" t="n">
-        <v>55</v>
+        <v>1800</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>40</v>
+        <v>900</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Niccolo</t>
+          <t>Jacopo</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>d'ANTONIO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Niccolo dell'ARCA</t>
+          <t>della QUERCIA</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>1478-1480</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Modène</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Galleria Estense</t>
+          <t>Basilique San Petronio</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Porta Magna</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sainte Monique</t>
+          <t>La Création d'Adam</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Creazione di Adamo</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Porta Magna</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Relief</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Pierre d'Istrie</t>
         </is>
       </c>
       <c r="T39" s="2" t="n">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="W39" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40" ht="15" customHeight="1">
@@ -3184,47 +3206,47 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>1409-1419</t>
+          <t>1411-1413</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Piazza del Campo</t>
+          <t>Basilique San Frediano</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Santa Maria della Scala (originaux)</t>
+          <t>Chapelle Trenta</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Fontaine de la Joie</t>
+          <t>Retable Trenta</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Fonte Gaia</t>
+          <t>Polittico Trenta</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Monument sculpté en haut-relief</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Retable / Autel sculpté</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3233,13 +3255,10 @@
         </is>
       </c>
       <c r="T40" s="2" t="n">
-        <v>210</v>
+        <v>439</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>1020</v>
-      </c>
-      <c r="V40" s="2" t="n">
-        <v>610</v>
+        <v>321</v>
       </c>
       <c r="W40" s="2" t="n">
         <v>2</v>
@@ -3258,7 +3277,7 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1411-1413</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3268,32 +3287,37 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Martin</t>
+          <t>Basilique San Frediano</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Chapelle Trenta</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Tombeau d'Ilaria del Carretto</t>
+          <t>Dalles funéraires de Lorenzo Trenta et sa femme</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Monumento funebre a Ilaria del Carretto</t>
+          <t>Tombe de Lorenzo Trenta e sua moglie</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Monument funéraire en bas-relief</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Dalles funéraires</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
@@ -3302,13 +3326,10 @@
         </is>
       </c>
       <c r="T41" s="2" t="n">
-        <v>76</v>
+        <v>244</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>214</v>
-      </c>
-      <c r="V41" s="2" t="n">
-        <v>83</v>
+        <v>246</v>
       </c>
       <c r="W41" s="2" t="n">
         <v>2</v>
@@ -3317,126 +3338,104 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Jacopo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>della QUERCIA</t>
+          <t>della ROBBIA</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>1425-1438</t>
+          <t>1487 environ</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Basilique San Petronio</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Portail central</t>
+          <t>Ospedale degli Innocenti</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Portail de San Petronio dit Porta Magna</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Porta Magna</t>
+          <t>"Tondi des Innocents"</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Monument mixte en haut-relief et ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R42" t="inlineStr">
-        <is>
-          <t>Portail sculpté / Reliefs</t>
+          <t>Haut-relief</t>
+        </is>
+      </c>
+      <c r="R42" s="7" t="inlineStr">
+        <is>
+          <t>Elément décoratif</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Pierre d'Istrie</t>
+          <t>Terre cuite vernissée</t>
         </is>
       </c>
       <c r="T42" s="2" t="n">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Jacopo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>della QUERCIA</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>1425</t>
-        </is>
+          <t>della ROBBIA</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>1475</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Séville</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Basilique San Petronio</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Porta Magna</t>
+          <t>Musée des Beaux-Arts</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>La Création d'Adam</t>
+          <t>Vierge au Coussin</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Creazione di Adamo</t>
-        </is>
-      </c>
-      <c r="L43" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Porta Magna</t>
+          <t>Madonna del Cuscino</t>
+        </is>
+      </c>
+      <c r="L43" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -3444,169 +3443,163 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
-        <is>
-          <t>Relief</t>
+      <c r="R43" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Pierre d'Istrie</t>
+          <t>Terre cuite émaillée</t>
         </is>
       </c>
       <c r="T43" s="2" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="V43" s="2" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Jacopo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>della QUERCIA</t>
+          <t>della ROBBIA</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>1411-1413</t>
+          <t>1475-1480</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Basilique San Frediano</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Chapelle Trenta</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Retable Trenta</t>
+          <t>Autel des Médicis</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Polittico Trenta</t>
-        </is>
-      </c>
-      <c r="L44" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Altare Medici</t>
+        </is>
+      </c>
+      <c r="L44" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
+          <t>Haut-relief</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
           <t>Mobilier liturgique</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>Retable / Autel sculpté</t>
-        </is>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite émaillée</t>
         </is>
       </c>
       <c r="T44" s="2" t="n">
-        <v>439</v>
+        <v>270</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>321</v>
+        <v>230</v>
+      </c>
+      <c r="V44" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="W44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Jacopo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>della QUERCIA</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>1411-1413</t>
-        </is>
+          <t>della ROBBIA</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>1489</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Prato</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Basilique San Frediano</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Chapelle Trenta</t>
+          <t>Cathédrale Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="G45" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/Duomo_Prato_01.jpg/1280px-Duomo_Prato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Dalles funéraires de Lorenzo Trenta et sa femme</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Tombe de Lorenzo Trenta e sua moglie</t>
-        </is>
-      </c>
-      <c r="L45" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Lunette de la Vierge Marie et l'Enfant Jésus entourés de saint Étienne et de saint Laurent.</t>
+        </is>
+      </c>
+      <c r="L45" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Monument funéraire en bas-relief</t>
-        </is>
-      </c>
-      <c r="R45" t="inlineStr">
-        <is>
-          <t>Dalles funéraires</t>
+          <t>Haut-relief</t>
+        </is>
+      </c>
+      <c r="R45" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite émaillée</t>
         </is>
       </c>
       <c r="T45" s="2" t="n">
-        <v>244</v>
+        <v>163</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>246</v>
+        <v>263</v>
+      </c>
+      <c r="V45" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="W45" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
@@ -3622,27 +3615,32 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>1487 environ</t>
+          <t>1490-1495</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>La Verna</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ospedale degli Innocenti</t>
+          <t>Sanctuaire de la Verna</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>"Tondi des Innocents"</t>
-        </is>
-      </c>
-      <c r="L46" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>L'Annonciation</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Annunciazione</t>
+        </is>
+      </c>
+      <c r="L46" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3652,22 +3650,24 @@
       </c>
       <c r="R46" s="7" t="inlineStr">
         <is>
-          <t>Elément décoratif</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Terre cuite vernissée</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="n">
-        <v>100</v>
+          <t>Terre cuite émaillée</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
       </c>
       <c r="U46" s="2" t="n">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W46" s="2" t="n">
         <v>1</v>
@@ -3684,32 +3684,34 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n">
-        <v>1475</v>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>1484</t>
+        </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Séville</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Musée des Beaux-Arts</t>
+          <t>Cathédrale Saints-Donat-et-Pierre</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Vierge au Coussin</t>
+          <t>Retable de la Trinité</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Madonna del Cuscino</t>
+          <t>Polittico de la Trinità</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3717,9 +3719,9 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R47" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -3728,13 +3730,13 @@
         </is>
       </c>
       <c r="T47" s="2" t="n">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>70</v>
+        <v>260</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="W47" s="2" t="n">
         <v>1</v>
@@ -3751,10 +3753,8 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>1475-1480</t>
-        </is>
+      <c r="D48" s="5" t="n">
+        <v>1489</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3763,22 +3763,17 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Autel des Médicis</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Altare Medici</t>
+          <t>Lunette avec la Vierge à l'Enfant et anges</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -3786,9 +3781,9 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>Mobilier liturgique</t>
+      <c r="R48" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3797,10 +3792,10 @@
         </is>
       </c>
       <c r="T48" s="2" t="n">
-        <v>270</v>
+        <v>44</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>230</v>
+        <v>92</v>
       </c>
       <c r="V48" s="2" t="n">
         <v>18</v>
@@ -3820,37 +3815,34 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D49" s="5" t="n">
-        <v>1489</v>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>après 1477</t>
+        </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Prato</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="G49" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/Duomo_Prato_01.jpg/1280px-Duomo_Prato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Lunette de la Vierge Marie et l'Enfant Jésus entourés de saint Étienne et de saint Laurent.</t>
-        </is>
-      </c>
-      <c r="L49" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>Haut-relief</t>
+          <t>L'Adoration de l'Enfant</t>
+        </is>
+      </c>
+      <c r="L49" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg/960px-Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="P49" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="R49" s="7" t="inlineStr">
@@ -3864,13 +3856,10 @@
         </is>
       </c>
       <c r="T49" s="2" t="n">
-        <v>163</v>
+        <v>128</v>
       </c>
       <c r="U49" s="2" t="n">
-        <v>263</v>
-      </c>
-      <c r="V49" s="2" t="n">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="W49" s="2" t="n">
         <v>1</v>
@@ -3879,7 +3868,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3889,59 +3878,57 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>1490-1495</t>
+          <t>1431-1438</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>La Verna</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sanctuaire de la Verna</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>L'Annonciation</t>
+          <t>La Cantoria</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Annunciazione</t>
-        </is>
-      </c>
-      <c r="L50" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Cantoria</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R50" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>Elément architectural</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
-        </is>
-      </c>
-      <c r="T50" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T50" s="2" t="n">
+        <v>348</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>210</v>
+        <v>560</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="W50" s="2" t="n">
         <v>1</v>
@@ -3950,7 +3937,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3960,32 +3947,32 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1442-1444</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cathédrale Saints-Donat-et-Pierre</t>
+          <t>Cathédrale Santa Maria del Fiore</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Retable de la Trinité</t>
+          <t>La Résurrection</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Polittico de la Trinità</t>
-        </is>
-      </c>
-      <c r="L51" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Resurrezione di Cristo</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -3993,9 +3980,9 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>Retable</t>
+      <c r="R51" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -4004,13 +3991,13 @@
         </is>
       </c>
       <c r="T51" s="2" t="n">
-        <v>370</v>
+        <v>200</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="V51" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W51" s="2" t="n">
         <v>1</v>
@@ -4019,7 +4006,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4027,8 +4014,10 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D52" s="5" t="n">
-        <v>1489</v>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>1446-1475</t>
+        </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -4037,42 +4026,47 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Museo dell’Opera del Duomo</t>
+          <t>Cathédrale Santa Maria del Fiore</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Lunette avec la Vierge à l'Enfant et anges</t>
-        </is>
-      </c>
-      <c r="L52" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Porte en bronze de la Sacristie</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Porta della Sacrestia delle Messe</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R52" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>10 panneaux en bas-relief</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T52" s="2" t="n">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="V52" s="2" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="W52" s="2" t="n">
         <v>1</v>
@@ -4081,7 +4075,7 @@
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4091,49 +4085,54 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>après 1477</t>
+          <t>1461-1466</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Église San Miniato al Monte</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>L'Adoration de l'Enfant</t>
-        </is>
-      </c>
-      <c r="L53" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg/960px-Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P53" s="7" t="inlineStr">
+          <t>Les Quatre Vertus Cardinales</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Le quattro virtù cardinali</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Médaillons en haut-relief</t>
+        </is>
+      </c>
+      <c r="R53" s="7" t="inlineStr">
         <is>
           <t>Bas-relief</t>
         </is>
       </c>
-      <c r="R53" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
-        </is>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>Terre cuite émaillée</t>
         </is>
       </c>
-      <c r="T53" s="2" t="n">
-        <v>128</v>
-      </c>
       <c r="U53" s="2" t="n">
-        <v>77</v>
+        <v>120</v>
+      </c>
+      <c r="V53" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="W53" s="2" t="n">
         <v>1</v>
@@ -4152,37 +4151,42 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>1431-1438</t>
+          <t>1445-1450</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Impruneta</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Collegiata di Santa Maria Impruneta</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>La Cantoria</t>
+          <t>Tabernacle de la Sainte Croix</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Cantoria</t>
+          <t>Tabernacolo della Santa Croce</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M54" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Elément architectural</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4192,17 +4196,17 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite émaillée</t>
         </is>
       </c>
       <c r="T54" s="2" t="n">
-        <v>348</v>
+        <v>150</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>560</v>
+        <v>65</v>
       </c>
       <c r="V54" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="W54" s="2" t="n">
         <v>1</v>
@@ -4219,34 +4223,34 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>1442-1444</t>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cathédrale Santa Maria del Fiore</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>La Résurrection</t>
+          <t>Vierge à l'Enfant avec trois chérubins</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Resurrezione di Cristo</t>
-        </is>
-      </c>
-      <c r="L55" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Madonna col Bambino (Madonna Genois)</t>
+        </is>
+      </c>
+      <c r="L55" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -4265,13 +4269,13 @@
         </is>
       </c>
       <c r="T55" s="2" t="n">
-        <v>200</v>
+        <v>118</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>265</v>
+        <v>73</v>
       </c>
       <c r="V55" s="2" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="W55" s="2" t="n">
         <v>1</v>
@@ -4288,9 +4292,9 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>1446-1475</t>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4300,47 +4304,41 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Cathédrale Santa Maria del Fiore</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Porte en bronze de la Sacristie</t>
+          <t>Vierge à l'Enfant</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Porta della Sacrestia delle Messe</t>
-        </is>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Madonna col Bambino</t>
+        </is>
+      </c>
+      <c r="L56" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>10 panneaux en bas-relief</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Elément architectural</t>
+          <t>Haut-relief</t>
+        </is>
+      </c>
+      <c r="R56" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Terre cuite émaillée</t>
         </is>
       </c>
       <c r="T56" s="2" t="n">
-        <v>420</v>
-      </c>
-      <c r="U56" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="V56" s="2" t="n">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="W56" s="2" t="n">
         <v>1</v>
@@ -4357,9 +4355,9 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>1461-1466</t>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1442-1444</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4369,27 +4367,27 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Basilique San Miniato al Monte</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Les Quatre Vertus Cardinales</t>
+          <t>Vierge à la pomme</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Le quattro virtù cardinali</t>
-        </is>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>Madonna col Bambino</t>
+        </is>
+      </c>
+      <c r="L57" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Médaillons en haut-relief</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R57" s="7" t="inlineStr">
@@ -4402,11 +4400,11 @@
           <t>Terre cuite émaillée</t>
         </is>
       </c>
+      <c r="T57" s="2" t="n">
+        <v>70</v>
+      </c>
       <c r="U57" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="V57" s="2" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="W57" s="2" t="n">
         <v>1</v>
@@ -4415,72 +4413,69 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Donato</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>della ROBBIA</t>
+          <t>di NICOLO</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>1445-1450</t>
+          <t>1440 environ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Impruneta</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Collegiata di Santa Maria Impruneta</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Tabernacle de la Sainte Croix</t>
+          <t>David (bronze)</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Tabernacolo della Santa Croce</t>
+          <t>David</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M58" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
-        </is>
-      </c>
-      <c r="T58" s="2" t="n">
-        <v>150</v>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="inlineStr">
+        <is>
+          <t>158 cm</t>
+        </is>
       </c>
       <c r="U58" s="2" t="n">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="V58" s="2" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="W58" s="2" t="n">
         <v>1</v>
@@ -4489,67 +4484,66 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Donato</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>della ROBBIA</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>1450 environ</t>
+          <t>di NICOLO</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>1408-1409</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Vierge à l'Enfant avec trois chérubins</t>
+          <t>David (marbre)</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Madonna col Bambino (Madonna Genois)</t>
-        </is>
-      </c>
-      <c r="L59" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>David in marmo</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R59" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="n">
-        <v>118</v>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="inlineStr">
+        <is>
+          <t>191 cm</t>
+        </is>
       </c>
       <c r="U59" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="V59" s="2" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="W59" s="2" t="n">
         <v>1</v>
@@ -4558,17 +4552,17 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Donato</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>della ROBBIA</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>1450 environ</t>
+          <t>di NICOLO</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>1415-1417</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4578,41 +4572,49 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Museo Nazionale del Bargello</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Vierge à l'Enfant</t>
+          <t>Saint Georges</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Madonna col Bambino</t>
-        </is>
-      </c>
-      <c r="L60" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>San Giorgio</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R60" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="n">
-        <v>57</v>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>209 cm</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="V60" s="2" t="n">
+        <v>53</v>
       </c>
       <c r="W60" s="2" t="n">
         <v>1</v>
@@ -4621,17 +4623,17 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Donato</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>della ROBBIA</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>1442-1444</t>
+          <t>di NICOLO</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>1411-1413</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4641,44 +4643,47 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Museo Nazionale del Bargello</t>
+          <t>Église d'Orsanmichele</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Vierge à la pomme</t>
+          <t>Saint Marc</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Madonna col Bambino</t>
-        </is>
-      </c>
-      <c r="L61" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>San Marco</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R61" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T61" s="2" t="n">
-        <v>70</v>
+        <v>248</v>
       </c>
       <c r="U61" s="2" t="n">
-        <v>52</v>
+        <v>74</v>
+      </c>
+      <c r="V61" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="W61" s="2" t="n">
         <v>1</v>
@@ -4697,59 +4702,71 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>1440 environ</t>
+          <t>1423-1425</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Baptistère San Giovanni</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>David (bronze)</t>
+          <t>Le Festin d'Hérode</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>David</t>
+          <t>Banchetto di Erode</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Fontaine baptismale du baptistère de Sienne</t>
+        </is>
+      </c>
+      <c r="N62" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Fonte_battesimale_di_Siena.jpg/960px-Fonte_battesimale_di_Siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>158 cm</t>
-        </is>
-      </c>
-      <c r="U62" s="2" t="n">
-        <v>51</v>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
       </c>
       <c r="V62" s="2" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
       <c r="W62" s="2" t="n">
         <v>1</v>
@@ -4768,7 +4785,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>1408-1409</t>
+          <t>1435 environ</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4778,22 +4795,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>David (marbre)</t>
+          <t>Annonciation Cavalcanti</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>David in marmo</t>
+          <t>Annunciazione Cavalcanti</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg/960px-Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -4801,23 +4818,24 @@
           <t>Ronde-bosse</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
+      <c r="R63" s="7" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="inlineStr">
-        <is>
-          <t>191 cm</t>
-        </is>
+          <t>Pierre sereine dorée, putti en terre cuite</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="n">
+        <v>420</v>
       </c>
       <c r="U63" s="2" t="n">
-        <v>57</v>
+        <v>274</v>
+      </c>
+      <c r="V63" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="W63" s="2" t="n">
         <v>1</v>
@@ -4836,32 +4854,32 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>1415-1417</t>
+          <t>1445-1453</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Padoue</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Piazza del Santo</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Saint Georges</t>
+          <t>Monument équestre à Gattamelata</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>San Giorgio</t>
+          <t>Monumento equestre al Gattamelata</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -4871,24 +4889,23 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>209 cm</t>
-        </is>
-      </c>
-      <c r="U64" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="V64" s="2" t="n">
-        <v>53</v>
+          <t>340 (statue) 800 (socle)</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>390 cm</t>
+        </is>
       </c>
       <c r="W64" s="2" t="n">
         <v>1</v>
@@ -4907,7 +4924,7 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>1411-1413</t>
+          <t>1453-1455</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4917,22 +4934,22 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Saint Marc</t>
+          <t>Madeleine pénitente</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>San Marco</t>
+          <t>Maddalena penitente</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Donatello%2C_maria_maddalena_02.JPG/960px-Donatello%2C_maria_maddalena_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -4947,17 +4964,19 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T65" s="2" t="n">
-        <v>248</v>
+          <t>Bois de peuplier polychrome</t>
+        </is>
+      </c>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>188 cm</t>
+        </is>
       </c>
       <c r="U65" s="2" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="V65" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="W65" s="2" t="n">
         <v>1</v>
@@ -4966,52 +4985,47 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Donato</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>di NICOLO</t>
+          <t>GHIBERTI</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>1423-1425</t>
+          <t>1425-1452</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Baptistère San Giovanni</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Le Festin d'Hérode</t>
+          <t>La Porte du Paradis</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Banchetto di Erode</t>
+          <t>Porta del Paradiso</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Fontaine baptismale du baptistère de Sienne</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Fonte_battesimale_di_Siena.jpg/960px-Fonte_battesimale_di_Siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5031,16 +5045,16 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>520 cm</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>60 cm</t>
+          <t>310 cm</t>
         </is>
       </c>
       <c r="V66" s="2" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="W66" s="2" t="n">
         <v>1</v>
@@ -5049,17 +5063,17 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Donato</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>di NICOLO</t>
+          <t>GHIBERTI</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>1435 environ</t>
+          <t>1403-1424</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -5069,47 +5083,53 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Annonciation Cavalcanti</t>
+          <t>Porte Nord du Baptistère</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Annunciazione Cavalcanti</t>
+          <t>Porta nord du battistero</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg/960px-Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="N67" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R67" s="7" t="inlineStr">
-        <is>
-          <t>Mobilier liturgique</t>
+          <t>Haut-relief</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>Pierre sereine dorée, putti en terre cuite</t>
-        </is>
-      </c>
-      <c r="T67" s="2" t="n">
-        <v>420</v>
-      </c>
-      <c r="U67" s="2" t="n">
-        <v>274</v>
-      </c>
-      <c r="V67" s="2" t="n">
-        <v>30</v>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T67" s="2" t="inlineStr">
+        <is>
+          <t>460 cm</t>
+        </is>
+      </c>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>270 cm</t>
+        </is>
       </c>
       <c r="W67" s="2" t="n">
         <v>1</v>
@@ -5118,42 +5138,57 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Donato</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>di NICOLO</t>
+          <t>GHIBERTI</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>1445-1453</t>
+          <t>1412-1416</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Padoue</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Piazza del Santo</t>
+          <t>Église d'Orsanmichele</t>
+        </is>
+      </c>
+      <c r="G68" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Monument équestre à Gattamelata</t>
+          <t>Saint Jean-Baptiste</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Monumento equestre al Gattamelata</t>
+          <t>San Giovanni Battista</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Albizzo di Piero en 1414</t>
+        </is>
+      </c>
+      <c r="N68" s="1" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -5163,7 +5198,7 @@
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S68" t="inlineStr">
@@ -5173,12 +5208,7 @@
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>340 (statue) 800 (socle)</t>
-        </is>
-      </c>
-      <c r="U68" s="2" t="inlineStr">
-        <is>
-          <t>390 cm</t>
+          <t>255 cm</t>
         </is>
       </c>
       <c r="W68" s="2" t="n">
@@ -5188,17 +5218,17 @@
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Donato</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>di NICOLO</t>
+          <t>GHIBERTI</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>1453-1455</t>
+          <t>1419-1423</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5208,22 +5238,37 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Église d'Orsanmichele</t>
+        </is>
+      </c>
+      <c r="G69" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Madeleine pénitente</t>
+          <t>Saint Matthieu</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Maddalena penitente</t>
+          <t>San Matteo</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Donatello%2C_maria_maddalena_02.JPG/960px-Donatello%2C_maria_maddalena_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Copie installée en 2005 sur la façade de l'Eglise Orsanmichele dans le tabernacle  sculpté par Lorenzo Ghiberti en 1414</t>
+        </is>
+      </c>
+      <c r="N69" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -5238,19 +5283,19 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Bois de peuplier polychrome</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>188 cm</t>
+          <t>270 cm</t>
         </is>
       </c>
       <c r="U69" s="2" t="n">
-        <v>51</v>
+        <v>100</v>
       </c>
       <c r="V69" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="W69" s="2" t="n">
         <v>1</v>
@@ -5269,7 +5314,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>1425-1452</t>
+          <t>1425-1429</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5279,56 +5324,62 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Église d'Orsanmichele</t>
+        </is>
+      </c>
+      <c r="G70" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>La Porte du Paradis</t>
+          <t>Saint Étienne</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Porta del Paradiso</t>
+          <t>Sant'Stefano</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Andrea Pisano en 1340</t>
         </is>
       </c>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5c/St_Stephen_Ghiberti_Orsanmichele.jpg/960px-St_Stephen_Ghiberti_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
-        </is>
-      </c>
-      <c r="T70" s="2" t="inlineStr">
-        <is>
-          <t>520 cm</t>
-        </is>
-      </c>
-      <c r="U70" s="2" t="inlineStr">
-        <is>
-          <t>310 cm</t>
-        </is>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T70" s="2" t="n">
+        <v>237</v>
+      </c>
+      <c r="U70" s="2" t="n">
+        <v>105</v>
       </c>
       <c r="V70" s="2" t="n">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="W70" s="2" t="n">
         <v>1</v>
@@ -5347,37 +5398,37 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>1403-1424</t>
+          <t>1417-1427</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Museo dell'Opera del Duomo</t>
+          <t>Baptistère San Giovanni</t>
+        </is>
+      </c>
+      <c r="G71" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Porte Nord du Baptistère</t>
+          <t>Le Baptême du Christ</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Porta nord du battistero</t>
+          <t>Battesimo di Cristo</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N71" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -5392,18 +5443,21 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>460 cm</t>
+          <t>60 cm</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>270 cm</t>
-        </is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="W71" s="2" t="n">
         <v>1</v>
@@ -5422,68 +5476,66 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>1412-1416</t>
+          <t>1417-1427</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
+          <t>Baptistère San Giovanni</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Saint Jean-Baptiste</t>
+          <t>L'Arrestation de Saint Jean-Baptiste</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>San Giovanni Battista</t>
+          <t>Cattura di San Giovanni Battista</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Albizzo di Piero en 1414</t>
-        </is>
-      </c>
-      <c r="N72" s="1" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>255 cm</t>
-        </is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="W72" s="2" t="n">
         <v>1</v>
@@ -5502,7 +5554,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>1419-1423</t>
+          <t>1432-1442</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5512,47 +5564,42 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
-        </is>
-      </c>
-      <c r="G73" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Cathédrale Santa Maria del Fiore</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Chapelle de Saint Zenobe</t>
+        </is>
+      </c>
+      <c r="I73" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Saint Matthieu</t>
+          <t>Châsse de Saint Zenobe</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>San Matteo</t>
+          <t>Arca di san Zanobi</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Copie installée en 2005 sur la façade de l'Eglise Orsanmichele dans le tabernacle  sculpté par Lorenzo Ghiberti en 1414</t>
-        </is>
-      </c>
-      <c r="N73" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -5560,16 +5607,11 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T73" s="2" t="inlineStr">
-        <is>
-          <t>270 cm</t>
-        </is>
+      <c r="T73" s="2" t="n">
+        <v>85</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="V73" s="2" t="n">
-        <v>60</v>
+        <v>193</v>
       </c>
       <c r="W73" s="2" t="n">
         <v>1</v>
@@ -5578,57 +5620,47 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GHIBERTI</t>
+          <t>LAURANA</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>1425-1429</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Palerme</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
-        </is>
-      </c>
-      <c r="G74" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Palazzo Abatellis</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Galerie régionale de Sicile</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Saint Étienne</t>
+          <t>Buste d'Éléonore d'Aragon</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Sant'Stefano</t>
+          <t>Busto di Eleonora d'Aragona</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Andrea Pisano en 1340</t>
-        </is>
-      </c>
-      <c r="N74" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5c/St_Stephen_Ghiberti_Orsanmichele.jpg/960px-St_Stephen_Ghiberti_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg/1280px-Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -5638,313 +5670,285 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Buste de portrait</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T74" s="2" t="n">
-        <v>237</v>
+        <v>50</v>
       </c>
       <c r="U74" s="2" t="n">
-        <v>105</v>
+        <v>48</v>
       </c>
       <c r="V74" s="2" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="W74" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GHIBERTI</t>
+          <t>LAURANA</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>1417-1427</t>
+          <t>1471-1474</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Baptistère San Giovanni</t>
-        </is>
-      </c>
-      <c r="G75" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>Castel Nuovo</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Arc de triomphe d'Alphonse d'Aragon</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Le Baptême du Christ</t>
+          <t>Le Triomphe d'Alphonse d'Aragon</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Battesimo di Cristo</t>
+          <t>Il Trionfo di Alfonso d'Aragona</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Triumphbogen_Castel_Nuovo_Neapel.jpg/500px-Triumphbogen_Castel_Nuovo_Neapel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ensemble architectural</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Relief monumental architectural</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
-        </is>
-      </c>
-      <c r="T75" s="2" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="U75" s="2" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="V75" s="2" t="n">
-        <v>8</v>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="n">
+        <v>3500</v>
+      </c>
+      <c r="U75" s="2" t="n">
+        <v>1000</v>
       </c>
       <c r="W75" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GHIBERTI</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="inlineStr">
-        <is>
-          <t>1417-1427</t>
-        </is>
+          <t>LAURANA</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>1475</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Baptistère San Giovanni</t>
-        </is>
-      </c>
-      <c r="G76" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>Musée du Louvre</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Département des Sculptures</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>L'Arrestation de Saint Jean-Baptiste</t>
+          <t>Buste de jeune femme</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Cattura di San Giovanni Battista</t>
+          <t>Busto di Maria di Sicilia</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Buste de portrait</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
-        </is>
-      </c>
-      <c r="T76" s="2" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="U76" s="2" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T76" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="U76" s="2" t="n">
+        <v>41</v>
       </c>
       <c r="V76" s="2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="W76" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GHIBERTI</t>
+          <t>LAURANA</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>1432-1442</t>
+          <t>1474-1475</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Cathédrale Santa Maria del Fiore</t>
+          <t>Kunsthistorisches Museum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Chapelle de Saint Zenobe</t>
-        </is>
-      </c>
-      <c r="I77" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Kunstkammer</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Châsse de Saint Zenobe</t>
+          <t>Buste de Laure de Noves</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Arca di san Zanobi</t>
+          <t>Busto di Laura de Noves</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Buste de portrait</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre polychrome</t>
         </is>
       </c>
       <c r="T77" s="2" t="n">
-        <v>85</v>
+        <v>44</v>
       </c>
       <c r="U77" s="2" t="n">
-        <v>193</v>
+        <v>42</v>
       </c>
       <c r="W77" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LAURANA</t>
+          <t>LOMBARDO</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1476-1481</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Palerme</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Palazzo Abatellis</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>Galleria Regionale della Sicilia</t>
+          <t>Basilique Santi Giovanni e Paolo</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Buste d'Éléonore d'Aragon</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Busto di Eleonora d'Aragona</t>
+          <t>"Tombeau du doge Pietro Mocenigo"</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg/1280px-Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG/1280px-Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire avec rondes-bosses</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Buste de portrait</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -5953,13 +5957,10 @@
         </is>
       </c>
       <c r="T78" s="2" t="n">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="U78" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="V78" s="2" t="n">
-        <v>24</v>
+        <v>700</v>
       </c>
       <c r="W78" s="2" t="n">
         <v>3</v>
@@ -5968,57 +5969,47 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LAURANA</t>
+          <t>LOMBARDO</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>1471-1474</t>
+          <t>1463 environ</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Castel Nuovo</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>Arc de triomphe d'Alphonse d'Aragon</t>
+          <t>Basilique Santi Giovanni e Paolo</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Le Triomphe d'Alphonse d'Aragon</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Il Trionfo di Alfonso d'Aragona</t>
-        </is>
-      </c>
-      <c r="L79" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Triumphbogen_Castel_Nuovo_Neapel.jpg/500px-Triumphbogen_Castel_Nuovo_Neapel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Tombeau du doge Pasquale Malipiero</t>
+        </is>
+      </c>
+      <c r="L79" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ensemble architectural</t>
+          <t>Monument funéraire avec rondes-bosses</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Relief monumental architectural</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -6027,10 +6018,13 @@
         </is>
       </c>
       <c r="T79" s="2" t="n">
-        <v>3500</v>
+        <v>500</v>
       </c>
       <c r="U79" s="2" t="n">
-        <v>1000</v>
+        <v>300</v>
+      </c>
+      <c r="V79" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="W79" s="2" t="n">
         <v>3</v>
@@ -6039,55 +6033,47 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LAURANA</t>
-        </is>
-      </c>
-      <c r="D80" s="5" t="n">
-        <v>1475</v>
+          <t>LOMBARDO</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="inlineStr">
+        <is>
+          <t>1483</t>
+        </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Ravenne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>Département des Sculptures</t>
+          <t>Tombeau de Dante</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Buste de jeune femme</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Busto di Maria di Sicilia</t>
-        </is>
-      </c>
-      <c r="L80" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Bas-relief de Dante lisant</t>
+        </is>
+      </c>
+      <c r="L80" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/SarcophageDeDante.jpg/960px-SarcophageDeDante.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire avec bas-relief</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Buste de portrait</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -6096,13 +6082,10 @@
         </is>
       </c>
       <c r="T80" s="2" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="U80" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="V80" s="2" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="W80" s="2" t="n">
         <v>3</v>
@@ -6111,69 +6094,62 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LAURANA</t>
+          <t>LOMBARDO</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>1474-1475</t>
+          <t>1481-1489</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kunsthistorisches Museum</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Kunstkammer</t>
+          <t>Église Santa Maria dei Miracoli</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Buste de Laure de Noves</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Busto di Laura de Noves</t>
-        </is>
-      </c>
-      <c r="L81" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Église Santa Maria dei Miracoli</t>
+        </is>
+      </c>
+      <c r="L81" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG/1280px-0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Ensemble architectural</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Buste de portrait</t>
+          <t>Monument</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>Marbre polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T81" s="2" t="n">
-        <v>44</v>
+        <v>1400</v>
       </c>
       <c r="U81" s="2" t="n">
-        <v>42</v>
+        <v>2600</v>
+      </c>
+      <c r="V81" s="2" t="n">
+        <v>700</v>
       </c>
       <c r="W81" s="2" t="n">
         <v>3</v>
@@ -6182,59 +6158,64 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Guido</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LOMBARDO</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>1476-1481</t>
+          <t>1477-1479 environ</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Modène</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Basilique Santi Giovanni e Paolo</t>
+          <t>Église San Giovanni Battista</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>"Tombeau du doge Pietro Mocenigo"</t>
+          <t>Lamentation sur le Christ mort</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Compianto sul Cristo morto</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG/1280px-Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG/1280px-Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Monument funéraire avec rondes-bosses</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Groupe sculptural</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T82" s="2" t="n">
-        <v>1200</v>
+        <v>180</v>
       </c>
       <c r="U82" s="2" t="n">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="W82" s="2" t="n">
         <v>3</v>
@@ -6243,62 +6224,67 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Guido</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LOMBARDO</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>1463 environ</t>
+          <t>1480-1485</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Ferrare</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Basilique Santi Giovanni e Paolo</t>
+          <t>Église du Gesù</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Tombeau du doge Pasquale Malipiero</t>
-        </is>
-      </c>
-      <c r="L83" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Déploration sur le Christ mort</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Compianto sul Cristo morto</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Monument funéraire avec rondes-bosses</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Groupe sculptural</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T83" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="U83" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="U83" s="2" t="n">
-        <v>300</v>
-      </c>
       <c r="V83" s="2" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="W83" s="2" t="n">
         <v>3</v>
@@ -6307,59 +6293,72 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Guido</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>LOMBARDO</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ravenne</t>
+          <t>Modène</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tombeau de Dante</t>
+          <t>Cathédrale de Modène</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Crypta</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Bas-relief de Dante lisant</t>
-        </is>
-      </c>
-      <c r="L84" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/SarcophageDeDante.jpg/960px-SarcophageDeDante.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>L'Adoration des bergers</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Presepio (Adorazione dei pastori)</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/20/Mazzoni_Adoration_Modena.jpg/1280px-Mazzoni_Adoration_Modena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Monument funéraire avec bas-relief</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Groupe sculptural</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T84" s="2" t="n">
-        <v>65</v>
+        <v>180</v>
       </c>
       <c r="U84" s="2" t="n">
-        <v>58</v>
+        <v>220</v>
+      </c>
+      <c r="V84" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="W84" s="2" t="n">
         <v>3</v>
@@ -6368,62 +6367,72 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Guido</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>LOMBARDO</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>1481-1489</t>
+          <t>1492-1494</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Église Santa Maria dei Miracoli</t>
+          <t>Église Sant'Anna dei Lombardi</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Cappella Compianto</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Église Santa Maria dei Miracoli</t>
-        </is>
-      </c>
-      <c r="L85" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG/1280px-0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Déploration sur le Christ mort</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Compianto sul Cristo morto</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg/1280px-GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ensemble architectural</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Monument</t>
+          <t>Groupe sculptural</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T85" s="2" t="n">
-        <v>1400</v>
+        <v>180</v>
       </c>
       <c r="U85" s="2" t="n">
-        <v>2600</v>
+        <v>450</v>
       </c>
       <c r="V85" s="2" t="n">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="W85" s="2" t="n">
         <v>3</v>
@@ -6432,42 +6441,47 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Guido</t>
+          <t>Tilman</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>RIEMENSCHNEIDER</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>1477-1479 environ</t>
+          <t>1490-1492</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Modène</t>
+          <t>Wurtzbourg</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Église San Giovanni Battista</t>
+          <t>Mainfränkisches Museum</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Lamentation sur le Christ mort</t>
+          <t>Adam et Ève</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Compianto sul Cristo morto</t>
+          <t>Adam und Eva</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG/1280px-Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg/1280px-Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="N86" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG/1280px-Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -6475,241 +6489,230 @@
           <t>Groupe en ronde-bosse</t>
         </is>
       </c>
-      <c r="R86" t="inlineStr">
-        <is>
-          <t>Groupe sculptural</t>
+      <c r="R86" s="7" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
-        </is>
-      </c>
-      <c r="T86" s="2" t="n">
-        <v>180</v>
+          <t>Pierre de grès</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="inlineStr">
+        <is>
+          <t>189 cm (Adam), 181 cm (Ève)</t>
+        </is>
       </c>
       <c r="U86" s="2" t="n">
-        <v>400</v>
+        <v>55</v>
+      </c>
+      <c r="V86" s="2" t="n">
+        <v>35</v>
       </c>
       <c r="W86" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Guido</t>
+          <t>Tilman</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>RIEMENSCHNEIDER</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>1480-1485</t>
+          <t>1490-1494</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ferrare</t>
+          <t>Münnerstadt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Église du Gesù</t>
+          <t>Église Sainte-Marie-Madeleine</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Déploration sur le Christ mort</t>
+          <t>Retable de Sainte Marie-Madeleine</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Compianto sul Cristo morto</t>
+          <t>Magdalenenaltar</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Groupe sculptural</t>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Bois de tilleul</t>
         </is>
       </c>
       <c r="T87" s="2" t="n">
-        <v>175</v>
+        <v>1200</v>
       </c>
       <c r="U87" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="V87" s="2" t="n">
-        <v>200</v>
+        <v>370</v>
       </c>
       <c r="W87" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Guido</t>
+          <t>Tilman</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>RIEMENSCHNEIDER</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Modène</t>
+          <t>Heidelberg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Cathédrale de Modène</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Crypta</t>
+          <t>Kurpfälzisches Museum</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>L'Adoration des bergers</t>
+          <t>Retable des Douze Apôtres de Windsheim</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Presepio (Adorazione dei pastori)</t>
+          <t>Windsheimer Zwölfbotenaltar</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/20/Mazzoni_Adoration_Modena.jpg/1280px-Mazzoni_Adoration_Modena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Bad_Windsheim-007.jpg/1280px-Bad_Windsheim-007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Groupe sculptural</t>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Bois de tilleul polychrome</t>
         </is>
       </c>
       <c r="T88" s="2" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="U88" s="2" t="n">
-        <v>220</v>
-      </c>
-      <c r="V88" s="2" t="n">
-        <v>110</v>
+        <v>250</v>
       </c>
       <c r="W88" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Guido</t>
+          <t>Tilman</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>RIEMENSCHNEIDER</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>1492-1494</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Bamberg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Église Sant'Anna dei Lombardi</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>Cappella Compianto</t>
+          <t>Cathédrale Saint-Pierre et Saint-Georges</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Déploration sur le Christ mort</t>
+          <t>Tombeau de l'empereur Henri II et de l'impératrice Cunégonde (commencé)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Compianto sul Cristo morto</t>
+          <t>Kaisergrab im Bamberger Dom</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg/1280px-GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/BambergDom-GrabHeinrichKunigunde.JPG/1280px-BambergDom-GrabHeinrichKunigunde.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Groupe sculptural</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T89" s="2" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="U89" s="2" t="n">
-        <v>450</v>
+        <v>340</v>
       </c>
       <c r="V89" s="2" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="W89" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1">
@@ -6725,64 +6728,57 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>1490-1492</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Wurtzbourg</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mainfränkisches Museum</t>
+          <t>Cleveland Museum of Art</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Adam et Ève</t>
+          <t>Saint Jérôme et le Lion</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Adam und Eva</t>
+          <t>Heiliger Hieronymus mit dem Löwen</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg/1280px-Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N90" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG/1280px-Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R90" s="7" t="inlineStr">
-        <is>
           <t>Ronde-bosse</t>
         </is>
       </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Pierre de grès</t>
-        </is>
-      </c>
-      <c r="T90" s="2" t="inlineStr">
-        <is>
-          <t>189 cm (Adam), 181 cm (Ève)</t>
-        </is>
+          <t>Albâtre</t>
+        </is>
+      </c>
+      <c r="T90" s="2" t="n">
+        <v>38</v>
       </c>
       <c r="U90" s="2" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="V90" s="2" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="W90" s="2" t="n">
         <v>2</v>
@@ -6801,54 +6797,52 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>1490-1494</t>
+          <t>1496-1499</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Münnerstadt</t>
+          <t>Wurtzbourg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Église Sainte-Marie-Madeleine</t>
+          <t>Cathédrale Saint-Kilian</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Retable de Sainte Marie-Madeleine</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Magdalenenaltar</t>
-        </is>
-      </c>
-      <c r="L91" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Tombeau du prince-évêque Rudolf von Scherenberg</t>
+        </is>
+      </c>
+      <c r="L91" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Scherenberggravewhole.jpg/500px-Scherenberggravewhole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Retable</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Bois de tilleul</t>
+          <t>Marbre rouge</t>
         </is>
       </c>
       <c r="T91" s="2" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="U91" s="2" t="n">
-        <v>370</v>
+        <v>158</v>
+      </c>
+      <c r="V91" s="2" t="n">
+        <v>45</v>
       </c>
       <c r="W91" s="2" t="n">
         <v>2</v>
@@ -6857,118 +6851,116 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Tilman</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RIEMENSCHNEIDER</t>
+          <t>ROSSELLINO</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1461-1466</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Heidelberg</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kurpfälzisches Museum</t>
+          <t>Église San Miniato al Monte</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Retable des Douze Apôtres de Windsheim</t>
+          <t>Tombeau du cardinal de Portugal (Jacques de Lusitanie)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Windsheimer Zwölfbotenaltar</t>
+          <t>Tomba del Cardinale del Portogallo</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Bad_Windsheim-007.jpg/1280px-Bad_Windsheim-007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG/1280px-Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>Retable</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>Bois de tilleul polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T92" s="2" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="U92" s="2" t="n">
-        <v>250</v>
+        <v>480</v>
       </c>
       <c r="W92" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Tilman</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RIEMENSCHNEIDER</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>1499</t>
-        </is>
+          <t>ROSSELLINO</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>1456</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bamberg</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Pierre et Saint-Georges</t>
+          <t>Victoria and Albert Museum</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Tombeau de l'empereur Henri II et de l'impératrice Cunégonde (commencé)</t>
+          <t>Buste de Giovanni Chellini</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Kaisergrab im Bamberger Dom</t>
+          <t>Busto di Giovanni di San Miniato</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/BambergDom-GrabHeinrichKunigunde.JPG/1280px-BambergDom-GrabHeinrichKunigunde.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -6977,57 +6969,57 @@
         </is>
       </c>
       <c r="T93" s="2" t="n">
-        <v>170</v>
+        <v>58</v>
       </c>
       <c r="U93" s="2" t="n">
-        <v>340</v>
+        <v>51</v>
       </c>
       <c r="V93" s="2" t="n">
-        <v>220</v>
+        <v>30</v>
       </c>
       <c r="W93" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Tilman</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RIEMENSCHNEIDER</t>
+          <t>ROSSELLINO</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Cleveland Museum of Art</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Saint Jérôme et le Lion</t>
+          <t>Buste de Matteo Palmieri</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Heiliger Hieronymus mit dem Löwen</t>
+          <t>Busto di Matteo Palmieri</t>
         </is>
       </c>
       <c r="L94" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -7037,95 +7029,92 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Albâtre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T94" s="2" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="U94" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="V94" s="2" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="W94" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Tilman</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RIEMENSCHNEIDER</t>
-        </is>
-      </c>
-      <c r="D95" s="5" t="inlineStr">
-        <is>
-          <t>1496-1499</t>
-        </is>
+          <t>ROSSELLINO</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>1470</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Wurtzbourg</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Kilian</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Tombeau du prince-évêque Rudolf von Scherenberg</t>
-        </is>
-      </c>
-      <c r="L95" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Scherenberggravewhole.jpg/500px-Scherenberggravewhole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Vierge à l'Enfant</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Madonna col Bambino</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Madonna_and_Child_with_Angels_MET_DP236934.jpg/960px-Madonna_and_Child_with_Angels_MET_DP236934.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Marbre rouge</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T95" s="2" t="n">
-        <v>400</v>
+        <v>73</v>
       </c>
       <c r="U95" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="V95" s="2" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="W95" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7135,7 +7124,7 @@
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>1461-1466</t>
+          <t>1445-1450</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -7145,22 +7134,22 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Chiesa di San Miniato al Monte</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Tombeau du cardinal de Portugal (Jacques de Lusitanie)</t>
+          <t>Tombeau de Leonardo Bruni</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Tomba del Cardinale del Portogallo</t>
+          <t>Tomba di Leonardo Bruni</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG/1280px-Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -7175,14 +7164,14 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Marbre scuplté et polychromie</t>
         </is>
       </c>
       <c r="T96" s="2" t="n">
-        <v>400</v>
+        <v>715</v>
       </c>
       <c r="U96" s="2" t="n">
-        <v>480</v>
+        <v>316</v>
       </c>
       <c r="W96" s="2" t="n">
         <v>3</v>
@@ -7191,7 +7180,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7199,57 +7188,56 @@
           <t>ROSSELLINO</t>
         </is>
       </c>
-      <c r="D97" s="5" t="n">
-        <v>1456</v>
+      <c r="D97" s="5" t="inlineStr">
+        <is>
+          <t>1443-1444</t>
+        </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Victoria and Albert Museum</t>
+          <t>Palazzo della Fraternita dei Laici</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Buste de Giovanni Chellini</t>
+          <t>Lunette de la Vierge de miséricorde</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Busto di Giovanni di San Miniato</t>
+          <t>Madonna della Misericordia</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Statue et relief de façade</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Marbre et pierre</t>
         </is>
       </c>
       <c r="T97" s="2" t="n">
-        <v>58</v>
+        <v>250</v>
       </c>
       <c r="U97" s="2" t="n">
-        <v>51</v>
-      </c>
-      <c r="V97" s="2" t="n">
-        <v>30</v>
+        <v>300</v>
       </c>
       <c r="W97" s="2" t="n">
         <v>3</v>
@@ -7258,7 +7246,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7268,42 +7256,52 @@
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1451-1452</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Cathédrale Saint-Zénon</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Chapelle du Sacrement</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Buste de Matteo Palmieri</t>
+          <t>Tombeau du juriste Filippo Lazzari</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Busto di Matteo Palmieri</t>
+          <t>Tomba di Filippo Lazzari</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="N98" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -7312,10 +7310,13 @@
         </is>
       </c>
       <c r="T98" s="2" t="n">
-        <v>53</v>
+        <v>466</v>
       </c>
       <c r="U98" s="2" t="n">
-        <v>57</v>
+        <v>233</v>
+      </c>
+      <c r="V98" s="2" t="n">
+        <v>50</v>
       </c>
       <c r="W98" s="2" t="n">
         <v>3</v>
@@ -7324,7 +7325,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -7332,54 +7333,55 @@
           <t>ROSSELLINO</t>
         </is>
       </c>
-      <c r="D99" s="5" t="n">
-        <v>1470</v>
+      <c r="D99" s="5" t="inlineStr">
+        <is>
+          <t>1449-1451</t>
+        </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Église Sant'Egidio</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Vierge à l'Enfant</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Madonna col Bambino</t>
-        </is>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Madonna_and_Child_with_Angels_MET_DP236934.jpg/960px-Madonna_and_Child_with_Angels_MET_DP236934.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+          <t>Tabernacle du Saint-Sacrement de Santa Maria Nuova</t>
+        </is>
+      </c>
+      <c r="L99" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG/960px-Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="N99" s="1" t="n"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T99" s="2" t="n">
-        <v>73</v>
+        <v>120</v>
       </c>
       <c r="U99" s="2" t="n">
-        <v>53</v>
+        <v>80</v>
+      </c>
+      <c r="V99" s="2" t="n">
+        <v>20</v>
       </c>
       <c r="W99" s="2" t="n">
         <v>3</v>
@@ -7388,277 +7390,266 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Veit</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>ROSSELLINO</t>
+          <t>STOSS</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>1445-1450</t>
+          <t>1477-1489</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Cracovie</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Basilique Notre-Dame</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Tombeau de Leonardo Bruni</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Tomba di Leonardo Bruni</t>
+          <t>"Retable de l'église Notre-Dame"</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Marbre scuplté et polychromie</t>
+          <t>Bois polychrome doré</t>
         </is>
       </c>
       <c r="T100" s="2" t="n">
-        <v>715</v>
+        <v>1300</v>
       </c>
       <c r="U100" s="2" t="n">
-        <v>316</v>
+        <v>1100</v>
       </c>
       <c r="W100" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Veit</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ROSSELLINO</t>
+          <t>STOSS</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>1443-1444</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Cracovie</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Palazzo della Fraternita dei Laici</t>
+          <t>Cathédrale du Wawel</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Lunette de la Vierge de miséricorde</t>
+          <t>Tombeau du roi Casimir IV Jagellon</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Madonna della Misericordia</t>
+          <t>Nagrobek Kazimierza IV Jagiellończyka</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>Statue et relief de façade</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Marbre et pierre</t>
+          <t>Marbre rouge de Salzbourg</t>
         </is>
       </c>
       <c r="T101" s="2" t="n">
-        <v>250</v>
+        <v>386</v>
       </c>
       <c r="U101" s="2" t="n">
-        <v>300</v>
+        <v>280</v>
+      </c>
+      <c r="V101" s="2" t="n">
+        <v>162</v>
       </c>
       <c r="W101" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Veit</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ROSSELLINO</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="inlineStr">
-        <is>
-          <t>1451-1452</t>
-        </is>
+          <t>STOSS</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>1495</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Pistoia</t>
+          <t>Cracovie</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Zénon</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Chapelle du Sacrement</t>
+          <t>Église des Dominicains</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Tombeau du juriste Filippo Lazzari</t>
+          <t>Épitaphe de Callimaque (Filippo Buonaccorsi)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Tomba di Filippo Lazzari</t>
+          <t>Tablica epitafijna Kallimacha</t>
         </is>
       </c>
       <c r="L102" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N102" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/.Epitafium_Kallimacha02.JPG/960px-.Epitafium_Kallimacha02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
-        </is>
-      </c>
-      <c r="R102" t="inlineStr">
+          <t>Bas-relief</t>
+        </is>
+      </c>
+      <c r="R102" s="7" t="inlineStr">
         <is>
           <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T102" s="2" t="n">
-        <v>466</v>
+        <v>198</v>
       </c>
       <c r="U102" s="2" t="n">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="V102" s="2" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="W102" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Veit</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ROSSELLINO</t>
+          <t>STOSS</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>1449-1451</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Cracovie</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Église Sant'Egidio</t>
+          <t>Basilique Notre-Dame</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Tabernacle du Saint-Sacrement de Santa Maria Nuova</t>
-        </is>
-      </c>
-      <c r="L103" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG/960px-Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N103" s="1" t="n"/>
+          <t>Crucifix de Slacker</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Krucyfiks kamienny Wita Stwosza</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Krucyfiks_Wita_Stwosza_03.jpg/1280px-Krucyfiks_Wita_Stwosza_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M103" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Objet liturgique</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Pierre calcaire</t>
         </is>
       </c>
       <c r="T103" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="U103" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="V103" s="2" t="n">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="W103" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104" ht="15" customHeight="1">
@@ -7674,49 +7665,57 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>1477-1489</t>
+          <t>1495-1500</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Cracovie</t>
+          <t>Nuremberg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Basilique Notre-Dame</t>
+          <t>Musée national germanique</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>"Retable de l'église Notre-Dame"</t>
+          <t>Vierge à l'Enfant</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Nürnberger Madonna</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Retable</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Bois polychrome doré</t>
+          <t>Bois de tilleul</t>
         </is>
       </c>
       <c r="T104" s="2" t="n">
-        <v>1300</v>
+        <v>140</v>
       </c>
       <c r="U104" s="2" t="n">
-        <v>1100</v>
+        <v>40</v>
+      </c>
+      <c r="V104" s="2" t="n">
+        <v>37</v>
       </c>
       <c r="W104" s="2" t="n">
         <v>2</v>
@@ -7745,22 +7744,22 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cathédrale du Wawel</t>
+          <t>Cathédrale de Wloclaweck</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Tombeau du roi Casimir IV Jagellon</t>
+          <t>Tombeau de l'évêque Piotr de Bnina</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Nagrobek Kazimierza IV Jagiellończyka</t>
+          <t>Nagrobek biskupa Piotra z Bnina</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -7775,295 +7774,26 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Marbre rouge de Salzbourg</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T105" s="2" t="n">
-        <v>386</v>
+        <v>112</v>
       </c>
       <c r="U105" s="2" t="n">
-        <v>280</v>
+        <v>217</v>
       </c>
       <c r="V105" s="2" t="n">
-        <v>162</v>
+        <v>70</v>
       </c>
       <c r="W105" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Veit</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>STOSS</t>
-        </is>
-      </c>
-      <c r="D106" s="5" t="n">
-        <v>1495</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>Cracovie</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>Église des Dominicains</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>Épitaphe de Callimaque (Filippo Buonaccorsi)</t>
-        </is>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Tablica epitafijna Kallimacha</t>
-        </is>
-      </c>
-      <c r="L106" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/.Epitafium_Kallimacha02.JPG/960px-.Epitafium_Kallimacha02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P106" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
-        </is>
-      </c>
-      <c r="R106" s="7" t="inlineStr">
-        <is>
-          <t>Monument funéraire avec ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T106" s="2" t="n">
-        <v>198</v>
-      </c>
-      <c r="U106" s="2" t="n">
-        <v>114</v>
-      </c>
-      <c r="V106" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="W106" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Veit</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>STOSS</t>
-        </is>
-      </c>
-      <c r="D107" s="5" t="inlineStr">
-        <is>
-          <t>1491</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Cracovie</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>Basilique Notre-Dame</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>Crucifix de Slacker</t>
-        </is>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Krucyfiks kamienny Wita Stwosza</t>
-        </is>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Krucyfiks_Wita_Stwosza_03.jpg/1280px-Krucyfiks_Wita_Stwosza_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M107" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P107" t="inlineStr">
-        <is>
-          <t>Objet liturgique</t>
-        </is>
-      </c>
-      <c r="R107" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>Pierre calcaire</t>
-        </is>
-      </c>
-      <c r="T107" s="2" t="n">
-        <v>250</v>
-      </c>
-      <c r="W107" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="108" ht="15" customHeight="1">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Veit</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>STOSS</t>
-        </is>
-      </c>
-      <c r="D108" s="5" t="inlineStr">
-        <is>
-          <t>1495-1500</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Nuremberg</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>Musée National Germanique</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>Vierge à l'Enfant</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Nürnberger Madonna</t>
-        </is>
-      </c>
-      <c r="L108" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P108" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R108" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>Bois de tilleul</t>
-        </is>
-      </c>
-      <c r="T108" s="2" t="n">
-        <v>140</v>
-      </c>
-      <c r="U108" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="V108" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="W108" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="109" ht="15" customHeight="1">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Veit</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>STOSS</t>
-        </is>
-      </c>
-      <c r="D109" s="5" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Cracovie</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Cathédrale de Wloclaweck</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>Tombeau de l'évêque Piotr de Bnina</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Nagrobek biskupa Piotra z Bnina</t>
-        </is>
-      </c>
-      <c r="L109" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P109" t="inlineStr">
-        <is>
-          <t>Monument funéraire</t>
-        </is>
-      </c>
-      <c r="R109" t="inlineStr">
-        <is>
-          <t>Monument funéraire avec ronde-bosse</t>
-        </is>
-      </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T109" s="2" t="n">
-        <v>112</v>
-      </c>
-      <c r="U109" s="2" t="n">
-        <v>217</v>
-      </c>
-      <c r="V109" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="W109" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
+    <row r="106" ht="15" customHeight="1"/>
+    <row r="107" ht="15" customHeight="1"/>
+    <row r="108" ht="15" customHeight="1"/>
+    <row r="109" ht="15" customHeight="1"/>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
@@ -8091,11 +7821,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId30"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId33"/>
@@ -8111,11 +7841,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G49" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId53"/>
@@ -8126,73 +7856,67 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId58"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId69"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId70"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N98" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId117"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N102" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId124"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M107" r:id="rId125"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId126"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L109" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-90" yWindow="0" windowWidth="17685" windowHeight="15060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="14490" yWindow="420" windowWidth="14010" windowHeight="15060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Feuil1" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,8 +31,14 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <sz val="8"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -42,6 +48,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -61,7 +73,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -81,6 +93,7 @@
       <protection locked="0" hidden="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,16 +462,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W105"/>
+  <dimension ref="A1:W108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="17.28515625" customWidth="1" min="1" max="1"/>
     <col width="26.85546875" customWidth="1" min="2" max="2"/>
-    <col width="41.140625" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10.42578125" customWidth="1" style="5" min="4" max="4"/>
     <col width="1.85546875" customWidth="1" min="7" max="7"/>
-    <col hidden="1" width="1.85546875" customWidth="1" min="8" max="8"/>
-    <col hidden="1" width="9.140625" customWidth="1" min="9" max="9"/>
+    <col width="4.7109375" customWidth="1" min="8" max="8"/>
+    <col width="16.140625" customWidth="1" min="9" max="9"/>
     <col width="5.5703125" customWidth="1" min="10" max="10"/>
     <col width="33.140625" customWidth="1" min="11" max="11"/>
     <col width="9.7109375" customWidth="1" style="3" min="12" max="12"/>
@@ -853,64 +866,67 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CIVITALI</t>
+          <t>BRUNELLESCHI</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>1472</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Martin</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Tombeau de Pietro da Noceto</t>
+          <t>Le Sacrifice d'Isaac (concours de 1401)</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Tomba di Pietro da Noceto</t>
-        </is>
-      </c>
-      <c r="L6" s="4" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fc/Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG/1280px-Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>Sacrificio di Isacco</t>
+        </is>
+      </c>
+      <c r="L6" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Filippo_Brunelleschi%2C_The_Sacrifice_of_Isaac%2C_1401-2%2C_Bargello%2C_Florence.jpg/960px-Filippo_Brunelleschi%2C_The_Sacrifice_of_Isaac%2C_1401-2%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T6" s="2" t="n">
-        <v>600</v>
+        <v>41.5</v>
       </c>
       <c r="U6" s="2" t="n">
-        <v>300</v>
+        <v>35</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>9</v>
       </c>
       <c r="W6" s="2" t="n">
         <v>3</v>
@@ -919,58 +935,64 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CIVITALI</t>
+          <t>BRUNELLESCHI</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>1479</t>
+          <t>vers 1410-1415</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Martin</t>
+          <t>Basilique Santa Maria Novella</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Tombeau de Domenico Bertini</t>
+          <t>Crucifix de Santa Maria Novella</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tomba di Domenico Bertini</t>
-        </is>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Crocifisso di Santa Maria Novella</t>
+        </is>
+      </c>
+      <c r="L7" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/35/Filippo_brunelleschi%2C_crocifisso_di_santa_maria_novella%2C_1410-15_ca..JPG/960px-Filippo_brunelleschi%2C_crocifisso_di_santa_maria_novella%2C_1410-15_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
+          <t>Bois polychromé</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>170</v>
+      </c>
+      <c r="U7" s="2" t="n">
+        <v>170</v>
       </c>
       <c r="W7" s="2" t="n">
         <v>3</v>
@@ -979,57 +1001,67 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CIVITALI</t>
+          <t>BRUNELLESCHI</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1399-1400</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Martin</t>
+          <t>Cathédrale Saint-Zénon</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Autel d'argent de saint Jacques</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Tempietto du Volto Santo</t>
+          <t>Prophètes de l'autel d'argent de saint Jacques</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Tempietto del Volto Santo</t>
-        </is>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Profeti dell'altare d'argento di San Jacopo</t>
+        </is>
+      </c>
+      <c r="L8" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg/1280px-Filippo_brunelleschi%2C_Geremia_e_Isaia%2C_1400-1401%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Edicule monumental</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Marbre de Carrare</t>
+          <t>Argent</t>
         </is>
       </c>
       <c r="W8" s="2" t="n">
@@ -1039,112 +1071,122 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Matteo</t>
+          <t>Filippo</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CIVITALI</t>
+          <t>BRUNELLESCHI</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1399-1401</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Martin</t>
+          <t>Cathédrale Saint-Zénon</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Autel d'argent de saint Jacques</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Autel de Saint Régule</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Altare di San Regolo</t>
-        </is>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Saint Jean l'Évangéliste (attribution)</t>
+        </is>
+      </c>
+      <c r="L9" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Filippo_Brunelleschi_%28attr.%29%2C_san_giovanni_evangelista%2C_1400-01_ca._03-156.jpg/960px-Filippo_Brunelleschi_%28attr.%29%2C_san_giovanni_evangelista%2C_1400-01_ca._03-156.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="n">
-        <v>3</v>
+          <t>Argent</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Mino</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>da FIESOLE</t>
+          <t>CIVITALI</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1472</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Cathédrale Saint-Martin</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Buste de Piero de Médicis</t>
+          <t>Tombeau de Pietro da Noceto</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Busto di Piero de' Medici</t>
+          <t>Tomba di Pietro da Noceto</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/f/fc/Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG/1280px-Tomba_di_Pietro_da_Noceto_segretario_di_Niccol%C3%B2_V%2C_opera_di_Matteo_Civitali_%281472%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Buste portrait</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1153,13 +1195,10 @@
         </is>
       </c>
       <c r="T10" s="2" t="n">
-        <v>55</v>
+        <v>600</v>
       </c>
       <c r="U10" s="2" t="n">
-        <v>48</v>
-      </c>
-      <c r="V10" s="2" t="n">
-        <v>23</v>
+        <v>300</v>
       </c>
       <c r="W10" s="2" t="n">
         <v>3</v>
@@ -1168,67 +1207,58 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Mino</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>da FIESOLE</t>
+          <t>CIVITALI</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>1454</t>
+          <t>1479</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Cathédrale Saint-Martin</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Buste de Giovanni de Médicis</t>
+          <t>Tombeau de Domenico Bertini</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Busto di Giovanni de' Medici</t>
+          <t>Tomba di Domenico Bertini</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG/960px-Matteo_civitali%2C_tomba_di_domenico_bertini%2C_1479%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Buste portrait</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>Marbre</t>
         </is>
-      </c>
-      <c r="T11" s="2" t="n">
-        <v>54</v>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>56</v>
-      </c>
-      <c r="V11" s="2" t="n">
-        <v>24</v>
       </c>
       <c r="W11" s="2" t="n">
         <v>3</v>
@@ -1237,64 +1267,58 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Mino</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>da FIESOLE</t>
+          <t>CIVITALI</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Cathédrale Saint-Martin</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Buste de Rinaldo della Luna</t>
+          <t>Tempietto du Volto Santo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Busto di Rinaldo della Luna</t>
+          <t>Tempietto del Volto Santo</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ef/A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg/1280px-A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0a/Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG/960px-Matteo_civitali%2C_tempietto_del_volto_santo%2C_1482-84%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Edicule monumental</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Buste portrait</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="n">
-        <v>37</v>
-      </c>
-      <c r="U12" s="2" t="n">
-        <v>40</v>
+          <t>Marbre de Carrare</t>
+        </is>
       </c>
       <c r="W12" s="2" t="n">
         <v>3</v>
@@ -1303,52 +1327,52 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mino</t>
+          <t>Matteo</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>da FIESOLE</t>
+          <t>CIVITALI</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Badia fiorentina</t>
+          <t>Cathédrale Saint-Martin</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Tombeau de Bernardo Giugni</t>
+          <t>Autel de Saint Régule</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Tomba di Bernardo Giugni</t>
+          <t>Altare di San Regolo</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Mino_da_fiesole%2C_tomba_di_bernardo_giugni%2C_02.JPG/1280px-Mino_da_fiesole%2C_tomba_di_bernardo_giugni%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7d/Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG/960px-Altare_di_San_Regolo%2C_Matteo_Civitali%2C_catedral_de_Lucca.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1363,17 +1387,17 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Benedetto</t>
+          <t>Mino</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>da MAIANO</t>
+          <t>da FIESOLE</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>1481-1487</t>
+          <t>1453</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1383,32 +1407,32 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Chaire de Santa Croce</t>
+          <t>Buste de Piero de Médicis</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Pulpito di Santa Croce</t>
+          <t>Busto di Piero de' Medici</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG/960px-Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/26/Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Piero_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Buste portrait</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1417,13 +1441,13 @@
         </is>
       </c>
       <c r="T14" s="2" t="n">
-        <v>254</v>
+        <v>55</v>
       </c>
       <c r="U14" s="2" t="n">
-        <v>179</v>
+        <v>48</v>
       </c>
       <c r="V14" s="2" t="n">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="W14" s="2" t="n">
         <v>3</v>
@@ -1432,17 +1456,17 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Benedetto</t>
+          <t>Mino</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>da MAIANO</t>
+          <t>da FIESOLE</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1457,17 +1481,17 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Buste de Pietro Mellini</t>
+          <t>Buste de Giovanni de Médicis</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Busto di Pietro Mellini</t>
+          <t>Busto di Giovanni de' Medici</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Benedetto_da_maiano%2C_busto_di_pietro_mellini.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/52/Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg/1280px-Bust_of_Giovanni_di_Cosimo_de%27_Medici_by_Mino_da_Fiesole-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1477,7 +1501,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Buste portrait</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1489,7 +1513,10 @@
         <v>54</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>60</v>
+        <v>56</v>
+      </c>
+      <c r="V15" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="W15" s="2" t="n">
         <v>3</v>
@@ -1498,17 +1525,17 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Benedetto</t>
+          <t>Mino</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>da MAIANO</t>
+          <t>da FIESOLE</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1456</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1518,22 +1545,22 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Palazzo Vecchio</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Saint Jean-Baptiste</t>
+          <t>Buste de Rinaldo della Luna</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>San Giovanni Battista</t>
+          <t>Busto di Rinaldo della Luna</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ef/A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg/1280px-A_bust_of_Rinaldo_della_Luna_by_Mino_da_Fiesole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1543,7 +1570,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>Statue</t>
+          <t>Buste portrait</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -1552,7 +1579,10 @@
         </is>
       </c>
       <c r="T16" s="2" t="n">
-        <v>144</v>
+        <v>37</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>40</v>
       </c>
       <c r="W16" s="2" t="n">
         <v>3</v>
@@ -1561,42 +1591,42 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Benedetto</t>
+          <t>Mino</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>da MAIANO</t>
+          <t>da FIESOLE</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>1470-1475</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Faenza</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Pierre Apôtre</t>
+          <t>Badia fiorentina</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Tombe de Saint Savin</t>
+          <t>Tombeau de Bernardo Giugni</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Arca di san Savino</t>
+          <t>Tomba di Bernardo Giugni</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Mino_da_fiesole%2C_tomba_di_bernardo_giugni%2C_02.JPG/1280px-Mino_da_fiesole%2C_tomba_di_bernardo_giugni%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1613,9 +1643,6 @@
         <is>
           <t>Marbre</t>
         </is>
-      </c>
-      <c r="T17" s="2" t="n">
-        <v>370</v>
       </c>
       <c r="W17" s="2" t="n">
         <v>3</v>
@@ -1624,52 +1651,52 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Desiderio</t>
+          <t>Benedetto</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>da SETTIGNANO</t>
+          <t>da MAIANO</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>1460-1464 environ</t>
+          <t>1481-1487</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Musée Bode</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Buste de Marietta Strozzi</t>
+          <t>Chaire de Santa Croce</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Ritratto di Marietta Strozzi</t>
+          <t>Pulpito di Santa Croce</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG/1280px-Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG/960px-Benedetto_da_Maiano%2C_pulpito_di_s._croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -1678,13 +1705,13 @@
         </is>
       </c>
       <c r="T18" s="2" t="n">
-        <v>53</v>
+        <v>254</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>48</v>
+        <v>179</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="W18" s="2" t="n">
         <v>3</v>
@@ -1693,17 +1720,17 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Desiderio</t>
+          <t>Benedetto</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>da SETTIGNANO</t>
+          <t>da MAIANO</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>1450-1455</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1713,32 +1740,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Tombeau de Carlo Marsuppini</t>
+          <t>Buste de Pietro Mellini</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Monumento funebre a Carlo Marsuppini</t>
+          <t>Busto di Pietro Mellini</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG/960px-Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/b/b0/Benedetto_da_maiano%2C_busto_di_pietro_mellini.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -1747,10 +1774,10 @@
         </is>
       </c>
       <c r="T19" s="2" t="n">
-        <v>601</v>
+        <v>54</v>
       </c>
       <c r="U19" s="2" t="n">
-        <v>358</v>
+        <v>60</v>
       </c>
       <c r="W19" s="2" t="n">
         <v>3</v>
@@ -1759,17 +1786,17 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Desiderio</t>
+          <t>Benedetto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>da SETTIGNANO</t>
+          <t>da MAIANO</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>1461</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1779,32 +1806,32 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Basilique San Lorenzo</t>
+          <t>Palazzo Vecchio</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Tabernacle du Sacrement</t>
+          <t>Saint Jean-Baptiste</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Tabernacolo del Sacramento</t>
+          <t>San Giovanni Battista</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/ae/Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg/1280px-Firenze_-_Florence_-_Palazzo_Vecchio_-_2nd_Floor_-_Sala_dei_Gigli_-_View_West_on_Statues_of_John_the_Baptist_%26_Putti_1481_by_Giuliano_da_Maiano.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Statue</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -1813,10 +1840,7 @@
         </is>
       </c>
       <c r="T20" s="2" t="n">
-        <v>447</v>
-      </c>
-      <c r="U20" s="2" t="n">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="W20" s="2" t="n">
         <v>3</v>
@@ -1825,47 +1849,52 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Desiderio</t>
+          <t>Benedetto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>da SETTIGNANO</t>
+          <t>da MAIANO</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>1460 environ</t>
+          <t>1470-1475</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Faenza</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Cathédrale Saint-Pierre Apôtre</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Saint Jean-Baptiste enfant</t>
+          <t>Tombe de Saint Savin</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Arca di san Savino</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg/1280px-Benedetto_da_Maiano%2C_arca_di_san_savino%2C_1468-74%2C_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -1874,10 +1903,7 @@
         </is>
       </c>
       <c r="T21" s="2" t="n">
-        <v>173</v>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>54</v>
+        <v>370</v>
       </c>
       <c r="W21" s="2" t="n">
         <v>3</v>
@@ -1886,62 +1912,67 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Desiderio</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>POLLAIUOLO</t>
+          <t>da SETTIGNANO</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>1484-1493</t>
+          <t>1460-1464 environ</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Vatican</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Musée du Trésor de Saint-Pierre</t>
+          <t>Musée Bode</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>"Tombeau du pape Sixte IV"</t>
+          <t>Buste de Marietta Strozzi</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ritratto di Marietta Strozzi</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ea/Tesoro_di_san_pietro%2C_tomba_di_sisto_IV_di_antonio_del_pollaiolo%2C_01.JPG/1280px-Tesoro_di_san_pietro%2C_tomba_di_sisto_IV_di_antonio_del_pollaiolo%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/eb/Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG/1280px-Desiderio_da_settignano%2C_marietta_strozzi%2C_1460_circa%2C_da_berlino_staatliche_museen-bode_museum.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T22" s="2" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="U22" s="2" t="n">
-        <v>445</v>
+        <v>48</v>
       </c>
       <c r="V22" s="2" t="n">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="W22" s="2" t="n">
         <v>3</v>
@@ -1950,42 +1981,42 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Desiderio</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>POLLAIUOLO</t>
+          <t>da SETTIGNANO</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>1492-1498</t>
+          <t>1450-1455</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Basilique Saint-Pierre</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Tombeau du pape Innocent VIII</t>
+          <t>Tombeau de Carlo Marsuppini</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sepolcro di Innocenzo VIII</t>
+          <t>Monumento funebre a Carlo Marsuppini</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG/960px-Desiderio_da_settignano%2C_tomba_di_Carlo_Marsuppini.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2000,19 +2031,14 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>601</v>
       </c>
       <c r="U23" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="V23" s="2" t="n">
-        <v>80</v>
+        <v>358</v>
       </c>
       <c r="W23" s="2" t="n">
         <v>3</v>
@@ -2021,17 +2047,17 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Desiderio</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>POLLAIUOLO</t>
+          <t>da SETTIGNANO</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>1475-1480</t>
+          <t>1461</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2041,49 +2067,44 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Basilique San Lorenzo</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hercule et Antée</t>
+          <t>Tabernacle du Sacrement</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Ercole e Anteo</t>
+          <t>Tabernacolo del Sacramento</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b9/Antonio_del_pollaiolo%2C_ercole_e_anteo%2C_01.JPG/960px-Antonio_del_pollaiolo%2C_ercole_e_anteo%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/49/Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG/960px-Desiderio_da_settignano%2C_tabernacolo_del_ss._sacramento%2C_1461%2C_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>447</v>
       </c>
       <c r="U24" s="2" t="n">
-        <v>34</v>
-      </c>
-      <c r="V24" s="2" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="W24" s="2" t="n">
         <v>3</v>
@@ -2092,17 +2113,17 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Desiderio</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>POLLAIUOLO</t>
+          <t>da SETTIGNANO</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>1457-1459</t>
+          <t>1460 environ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2112,47 +2133,39 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Musée de l'Œuvre du Duomo</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Croix de Saint Jean</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Croce del Tesoro di San Giovanni</t>
+          <t>Saint Jean-Baptiste enfant</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Betto_di_francesco_betti%2C_antonio_pollaiolo_e_domenico_dei%2C_croce_1457-59_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg/500px-Donatello%2C_St._John_the_Baptist_of_Casa_Martelli%2C_c1442%2C_Bargello%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Objet liturgique</t>
-        </is>
-      </c>
-      <c r="R25" s="7" t="inlineStr">
-        <is>
-          <t>Objet liturgique</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>Argent, émaux et bois</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T25" s="2" t="n">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="U25" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="V25" s="2" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="W25" s="2" t="n">
         <v>3</v>
@@ -2161,52 +2174,47 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>del VERROCCHIO</t>
+          <t>POLLAIUOLO</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>1473-1475</t>
+          <t>1484-1493</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Vatican</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Musée du Trésor de Saint-Pierre</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>David</t>
+          <t>"Tombeau du pape Sixte IV"</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/e/ea/Tesoro_di_san_pietro%2C_tomba_di_sisto_IV_di_antonio_del_pollaiolo%2C_01.JPG/1280px-Tesoro_di_san_pietro%2C_tomba_di_sisto_IV_di_antonio_del_pollaiolo%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -2215,82 +2223,67 @@
         </is>
       </c>
       <c r="T26" s="2" t="n">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="U26" s="2" t="n">
-        <v>56</v>
+        <v>445</v>
       </c>
       <c r="V26" s="2" t="n">
-        <v>41</v>
+        <v>210</v>
       </c>
       <c r="W26" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>del VERROCCHIO</t>
+          <t>POLLAIUOLO</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>1467-1483</t>
+          <t>1492-1498</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
-        </is>
-      </c>
-      <c r="G27" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Basilique Saint-Pierre</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>L'Incrédulité de saint Thomas</t>
+          <t>Tombeau du pape Innocent VIII</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Incredulità di san Tommaso</t>
+          <t>Sepolcro di Innocenzo VIII</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Copie installée en 1992 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Donatello et Michelozzo en 1423</t>
-        </is>
-      </c>
-      <c r="N27" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg/960px-Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/82/Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg/960px-Monument_to_Innocentius_VIII_in_Saint_Peter%27s_Basilica.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Groupe Ronde-bosse</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -2298,58 +2291,60 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T27" s="2" t="n">
-        <v>241</v>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
       </c>
       <c r="U27" s="2" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="V27" s="2" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="W27" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>del VERROCCHIO</t>
+          <t>POLLAIUOLO</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>1480-1488</t>
+          <t>1475-1480</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Campo Santi Giovanni e Paolo</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Monument équestre à Bartolomeo Colleoni</t>
+          <t>Hercule et Antée</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Monumento a Bartolomeo Colleoni</t>
+          <t>Ercole e Anteo</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b9/Antonio_del_pollaiolo%2C_ercole_e_anteo%2C_01.JPG/960px-Antonio_del_pollaiolo%2C_ercole_e_anteo%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2359,7 +2354,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -2369,17 +2364,17 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>395 (statue) 400 (socle)</t>
+          <t>45</t>
         </is>
       </c>
       <c r="U28" s="2" t="n">
-        <v>380</v>
+        <v>34</v>
       </c>
       <c r="V28" s="2" t="n">
-        <v>145</v>
+        <v>30</v>
       </c>
       <c r="W28" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" ht="15" customHeight="1">
@@ -2395,7 +2390,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>vers 1470</t>
+          <t>1473-1475</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2405,27 +2400,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Palazzo Vecchio</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Enfant au dauphin</t>
+          <t>David</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Putto con delfino</t>
+          <t>David</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Putto_col_delfino_di_verrocchio_02.JPG/960px-Putto_col_delfino_di_verrocchio_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Copie en bronze installée en 1959 dans le cortile de Palazzo Vacchio conçu par Michelozzo en 1453. La fontaine a été conçue par Vasari en 1555.</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/a/ae/David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg/1280px-David%2C_Andrea_del_Verrocchio%2C_ca._1466-69%2C_Bargello_Florenz-01.jpg</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2435,7 +2425,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Statue de fontaine</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -2444,13 +2434,13 @@
         </is>
       </c>
       <c r="T29" s="2" t="n">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="U29" s="2" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="V29" s="2" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="W29" s="2" t="n">
         <v>2</v>
@@ -2469,7 +2459,7 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>1475</t>
+          <t>1467-1483</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2479,22 +2469,37 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Église d'Orsanmichele</t>
+        </is>
+      </c>
+      <c r="G30" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Dame au bouquet</t>
+          <t>L'Incrédulité de saint Thomas</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Dama col mazzolino</t>
+          <t>Incredulità di san Tommaso</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG/960px-Incredulit%C3%A0_di_san_Tommaso_di_Andrea_di_Cione_detto_il_Verrocchio%2C1.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Copie installée en 1992 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Donatello et Michelozzo en 1423</t>
+        </is>
+      </c>
+      <c r="N30" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f3/Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg/960px-Firenze_aka_Florence%2C_Italy_%2827330071097%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -2504,22 +2509,22 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Groupe Ronde-bosse</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T30" s="2" t="n">
-        <v>59</v>
+        <v>241</v>
       </c>
       <c r="U30" s="2" t="n">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="V30" s="2" t="n">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="W30" s="2" t="n">
         <v>2</v>
@@ -2538,59 +2543,59 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>1469-1472</t>
+          <t>1480-1488</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Basilique San Lorenzo</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Vieille Sacristie</t>
+          <t>Campo Santi Giovanni e Paolo</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Tombeau de Pierre et Jean de Médicis</t>
+          <t>Monument équestre à Bartolomeo Colleoni</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Tomba di Piero e Giovanni de' Medici</t>
+          <t>Monumento a Bartolomeo Colleoni</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Marbre, bronze et porphyre</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="n">
-        <v>540</v>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>395 (statue) 400 (socle)</t>
+        </is>
       </c>
       <c r="U31" s="2" t="n">
-        <v>358</v>
+        <v>380</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>145</v>
       </c>
       <c r="W31" s="2" t="n">
         <v>2</v>
@@ -2599,126 +2604,116 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Niccolo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>d'ANTONIO</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Niccolo dell'ARCA</t>
+          <t>del VERROCCHIO</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>1463</t>
+          <t>vers 1470</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Église Santa Maria della Vita</t>
+          <t>Palazzo Vecchio</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Lamentation sur le Christ mort</t>
+          <t>Enfant au dauphin</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Compianto sul Cristo morto</t>
+          <t>Putto con delfino</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9b/Putto_col_delfino_di_verrocchio_02.JPG/960px-Putto_col_delfino_di_verrocchio_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Copie en bronze installée en 1959 dans le cortile de Palazzo Vacchio conçu par Michelozzo en 1453. La fontaine a été conçue par Vasari en 1555.</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse de sept statues</t>
-        </is>
-      </c>
-      <c r="R32" s="7" t="inlineStr">
-        <is>
-          <t>Groupe sculptural</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Statue de fontaine</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T32" s="2" t="n">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="U32" s="2" t="n">
-        <v>350</v>
+        <v>35</v>
       </c>
       <c r="V32" s="2" t="n">
-        <v>250</v>
+        <v>45</v>
       </c>
       <c r="W32" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Niccolo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>d'ANTONIO</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Niccolo dell'ARCA</t>
+          <t>del VERROCCHIO</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>1469-1473</t>
+          <t>1475</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Basilique San Domenico</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Arca di San Domenico (Cimaise)</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Dieu le Père bénissant le monde</t>
+          <t>Dame au bouquet</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Dio Padre benedicente il mondo</t>
+          <t>Dama col mazzolino</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg/960px-Andrea_del_verrocchio%2C_dama_col_mazzolino%2C_1475-80%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -2726,9 +2721,9 @@
           <t>Ronde-bosse</t>
         </is>
       </c>
-      <c r="R33" s="7" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -2737,90 +2732,87 @@
         </is>
       </c>
       <c r="T33" s="2" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="U33" s="2" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="V33" s="2" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="W33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Niccolo</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>d'ANTONIO</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Niccolo dell'ARCA</t>
+          <t>del VERROCCHIO</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1469-1472</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Musée de la Basilique San Domenico</t>
+          <t>Basilique San Lorenzo</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Vieille Sacristie</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Buste de saint Dominique</t>
+          <t>Tombeau de Pierre et Jean de Médicis</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Busto di san Domenico</t>
+          <t>Tomba di Piero e Giovanni de' Medici</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg/960px-Verrocchio%2C_tomba_di_piero_e_giovanni_de%27_medici%2C_lato_interno%2C_1469-1472%2C_00.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre, bronze et porphyre</t>
         </is>
       </c>
       <c r="T34" s="2" t="n">
-        <v>55</v>
+        <v>540</v>
       </c>
       <c r="U34" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="V34" s="2" t="n">
-        <v>30</v>
+        <v>358</v>
       </c>
       <c r="W34" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
@@ -2841,42 +2833,42 @@
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>1478-1480</t>
+          <t>1463</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Modène</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Galerie Estense</t>
+          <t>Église Santa Maria della Vita</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Sainte Monique</t>
+          <t>Lamentation sur le Christ mort</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Compianto sul Cristo morto</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/7/74/Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG/1280px-Niccol%C3%B2_dell%27arca%2C_Compianto_sul_Cristo_morto%2C_Chiesa_di_S._Maria_della_vita%2C_Bologna_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -2885,13 +2877,13 @@
         </is>
       </c>
       <c r="T35" s="2" t="n">
-        <v>50</v>
+        <v>165</v>
       </c>
       <c r="U35" s="2" t="n">
-        <v>40</v>
+        <v>350</v>
       </c>
       <c r="V35" s="2" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="W35" s="2" t="n">
         <v>3</v>
@@ -2900,57 +2892,62 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jacopo</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>della QUERCIA</t>
+          <t>d'ANTONIO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Niccolo dell'ARCA</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>1409-1419</t>
+          <t>1469-1473</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Piazza del Campo</t>
+          <t>Basilique San Domenico</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Santa Maria della Scala (originaux)</t>
+          <t>Arca di San Domenico (Cimaise)</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Fontaine de la Joie</t>
+          <t>Dieu le Père bénissant le monde</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Fonte Gaia</t>
+          <t>Dio Padre benedicente il mondo</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5d/Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg/960px-Basilique_San_Domenico_de_Bologne_-_S%C3%A9pulcre_de_Saint_Dominique.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Monument sculpté en haut-relief</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -2959,159 +2956,164 @@
         </is>
       </c>
       <c r="T36" s="2" t="n">
-        <v>210</v>
+        <v>50</v>
       </c>
       <c r="U36" s="2" t="n">
-        <v>1020</v>
+        <v>20</v>
       </c>
       <c r="V36" s="2" t="n">
-        <v>610</v>
+        <v>20</v>
       </c>
       <c r="W36" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Jacopo</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>della QUERCIA</t>
+          <t>d'ANTONIO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Niccolo dell'ARCA</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>1406</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Martin</t>
+          <t>Musée de la Basilique San Domenico</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Tombeau d'Ilaria del Carretto</t>
+          <t>Buste de saint Dominique</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Monumento funebre a Ilaria del Carretto</t>
+          <t>Busto di san Domenico</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7a/Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG/960px-Niccol%C3%B2_dell%27arca%2C_san_domenico%2C_1474%2C_da_fond._cavallini_sgarbi%2C_ro_ferrarese_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T37" s="2" t="n">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="U37" s="2" t="n">
-        <v>214</v>
+        <v>40</v>
       </c>
       <c r="V37" s="2" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="W37" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Jacopo</t>
+          <t>Niccolo</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>della QUERCIA</t>
+          <t>d'ANTONIO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Niccolo dell'ARCA</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>1425-1438</t>
+          <t>1478-1480</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Modène</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Basilique San Petronio</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Portail central</t>
+          <t>Galerie Estense</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Portail de San Petronio dit Porta Magna</t>
+          <t>Sainte Monique</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Porta Magna</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg/960px-Niccol%C3%B2_dell%27arca_%28attr.%29%2C_santa_monaca%2C_1480_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Monument mixte en haut-relief et ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>Portail sculpté / Reliefs</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>Pierre d'Istrie</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T38" s="2" t="n">
-        <v>1800</v>
+        <v>50</v>
       </c>
       <c r="U38" s="2" t="n">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="V38" s="2" t="n">
-        <v>300</v>
+        <v>25</v>
       </c>
       <c r="W38" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
@@ -3127,67 +3129,62 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>1425</t>
+          <t>1409-1419</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Bologne</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Basilique San Petronio</t>
+          <t>Piazza del Campo</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Porta Magna</t>
+          <t>Santa Maria della Scala (originaux)</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>La Création d'Adam</t>
+          <t>Fontaine de la Joie</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Creazione di Adamo</t>
+          <t>Fonte Gaia</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Porta Magna</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/b7/Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg/1280px-Jacopo_della_Quercia-Fonte_Gaia_in_Siena-Left_side_with_Creation_of_Adam-Piazza_del_Campo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Monument sculpté en haut-relief</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>Relief</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>Pierre d'Istrie</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T39" s="2" t="n">
-        <v>99</v>
+        <v>210</v>
       </c>
       <c r="U39" s="2" t="n">
-        <v>92</v>
+        <v>1020</v>
       </c>
       <c r="V39" s="2" t="n">
-        <v>10</v>
+        <v>610</v>
       </c>
       <c r="W39" s="2" t="n">
         <v>2</v>
@@ -3206,7 +3203,7 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>1411-1413</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3216,37 +3213,32 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Basilique San Frediano</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Chapelle Trenta</t>
+          <t>Cathédrale Saint-Martin</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Retable Trenta</t>
+          <t>Tombeau d'Ilaria del Carretto</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Polittico Trenta</t>
+          <t>Monumento funebre a Ilaria del Carretto</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg/1280px-Jacopo_della_quercia%2C_monumento_funebre_a_ilaria_del_carretto%2C_1406-1408_circa%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>Retable / Autel sculpté</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -3255,10 +3247,13 @@
         </is>
       </c>
       <c r="T40" s="2" t="n">
-        <v>439</v>
+        <v>76</v>
       </c>
       <c r="U40" s="2" t="n">
-        <v>321</v>
+        <v>214</v>
+      </c>
+      <c r="V40" s="2" t="n">
+        <v>83</v>
       </c>
       <c r="W40" s="2" t="n">
         <v>2</v>
@@ -3277,59 +3272,62 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>1411-1413</t>
+          <t>1425-1438</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Lucques</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Basilique San Frediano</t>
+          <t>Basilique San Petronio</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Chapelle Trenta</t>
+          <t>Portail central</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Dalles funéraires de Lorenzo Trenta et sa femme</t>
+          <t>Portail de San Petronio dit Porta Magna</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Tombe de Lorenzo Trenta e sua moglie</t>
+          <t>Porta Magna</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/97/Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg/1280px-Porta_Magna%2C_Basilica_di_San_Petronio%2C_Bologna_%2826682203535%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Monument funéraire en bas-relief</t>
+          <t>Monument mixte en haut-relief et ronde-bosse</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>Dalles funéraires</t>
+          <t>Portail sculpté / Reliefs</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Pierre d'Istrie</t>
         </is>
       </c>
       <c r="T41" s="2" t="n">
-        <v>244</v>
+        <v>1800</v>
       </c>
       <c r="U41" s="2" t="n">
-        <v>246</v>
+        <v>900</v>
+      </c>
+      <c r="V41" s="2" t="n">
+        <v>300</v>
       </c>
       <c r="W41" s="2" t="n">
         <v>2</v>
@@ -3338,37 +3336,52 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Jacopo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>della ROBBIA</t>
+          <t>della QUERCIA</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>1487 environ</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Bologne</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ospedale degli Innocenti</t>
+          <t>Basilique San Petronio</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Porta Magna</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>"Tondi des Innocents"</t>
+          <t>La Création d'Adam</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Creazione di Adamo</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg/1280px-Jacopo_della_Quercia%2C_Creazione_di_Adamo%2C_tra_il_1426_e_il_1434._San_Petronio%2C_Bologna%2C_porta_centrale_-FG.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Porta Magna</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -3376,163 +3389,169 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R42" s="7" t="inlineStr">
-        <is>
-          <t>Elément décoratif</t>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Relief</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>Terre cuite vernissée</t>
+          <t>Pierre d'Istrie</t>
         </is>
       </c>
       <c r="T42" s="2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="U42" s="2" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="V42" s="2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="W42" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Jacopo</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>della ROBBIA</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="n">
-        <v>1475</v>
+          <t>della QUERCIA</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>1411-1413</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Séville</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Musée des Beaux-Arts</t>
+          <t>Basilique San Frediano</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Chapelle Trenta</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Vierge au Coussin</t>
+          <t>Retable Trenta</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Madonna del Cuscino</t>
-        </is>
-      </c>
-      <c r="L43" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Polittico Trenta</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg/960px-Lucca%2C_Basilica_di_San_Frediano%2C_Jacopo_della_Quercia-Trenta_Altar.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R43" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Retable / Autel sculpté</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T43" s="2" t="n">
-        <v>80</v>
+        <v>439</v>
       </c>
       <c r="U43" s="2" t="n">
-        <v>70</v>
-      </c>
-      <c r="V43" s="2" t="n">
-        <v>12</v>
+        <v>321</v>
       </c>
       <c r="W43" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Andrea</t>
+          <t>Jacopo</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>della ROBBIA</t>
+          <t>della QUERCIA</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>1475-1480</t>
+          <t>1411-1413</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Lucques</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Basilique San Frediano</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Chapelle Trenta</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Autel des Médicis</t>
+          <t>Dalles funéraires de Lorenzo Trenta et sa femme</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Altare Medici</t>
-        </is>
-      </c>
-      <c r="L44" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Tombe de Lorenzo Trenta e sua moglie</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/7b/Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG/960px-Jacope_della_quercia%2C_tombe_e_pala_trenta%2C_1422%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Monument funéraire en bas-relief</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Dalles funéraires</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T44" s="2" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
       <c r="U44" s="2" t="n">
-        <v>230</v>
-      </c>
-      <c r="V44" s="2" t="n">
-        <v>18</v>
+        <v>246</v>
       </c>
       <c r="W44" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
@@ -3546,32 +3565,29 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n">
-        <v>1489</v>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>1487 environ</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prato</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Étienne</t>
-        </is>
-      </c>
-      <c r="G45" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/Duomo_Prato_01.jpg/1280px-Duomo_Prato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Ospedale degli Innocenti</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Lunette de la Vierge Marie et l'Enfant Jésus entourés de saint Étienne et de saint Laurent.</t>
-        </is>
-      </c>
-      <c r="L45" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>"Tondi des Innocents"</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -3579,21 +3595,21 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R45" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+      <c r="R45" s="8" t="inlineStr">
+        <is>
+          <t>Elément décoratif</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
+          <t>Terre cuite vernissée</t>
         </is>
       </c>
       <c r="T45" s="2" t="n">
-        <v>163</v>
+        <v>100</v>
       </c>
       <c r="U45" s="2" t="n">
-        <v>263</v>
+        <v>100</v>
       </c>
       <c r="V45" s="2" t="n">
         <v>20</v>
@@ -3613,34 +3629,32 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>1490-1495</t>
-        </is>
+      <c r="D46" s="5" t="n">
+        <v>1475</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>La Verna</t>
+          <t>Séville</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Sanctuaire de la Verna</t>
+          <t>Musée des Beaux-Arts</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>L'Annonciation</t>
+          <t>Vierge au Coussin</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Annunciazione</t>
+          <t>Madonna del Cuscino</t>
         </is>
       </c>
       <c r="L46" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -3648,9 +3662,9 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R46" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
@@ -3658,16 +3672,14 @@
           <t>Terre cuite émaillée</t>
         </is>
       </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
+      <c r="T46" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="U46" s="2" t="n">
-        <v>210</v>
+        <v>70</v>
       </c>
       <c r="V46" s="2" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="W46" s="2" t="n">
         <v>1</v>
@@ -3686,32 +3698,32 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>1484</t>
+          <t>1475-1480</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cathédrale Saints-Donat-et-Pierre</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Retable de la Trinité</t>
+          <t>Autel des Médicis</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Polittico de la Trinità</t>
+          <t>Altare Medici</t>
         </is>
       </c>
       <c r="L47" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -3721,7 +3733,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>Retable</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -3730,13 +3742,13 @@
         </is>
       </c>
       <c r="T47" s="2" t="n">
-        <v>370</v>
+        <v>270</v>
       </c>
       <c r="U47" s="2" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="V47" s="2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W47" s="2" t="n">
         <v>1</v>
@@ -3758,22 +3770,27 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Prato</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Musée de l'Œuvre du Duomo</t>
+          <t>Cathédrale Saint-Étienne</t>
+        </is>
+      </c>
+      <c r="G48" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f9/Duomo_Prato_01.jpg/1280px-Duomo_Prato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Lunette avec la Vierge à l'Enfant et anges</t>
+          <t>Lunette de la Vierge Marie et l'Enfant Jésus entourés de saint Étienne et de saint Laurent.</t>
         </is>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -3781,9 +3798,9 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R48" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -3792,13 +3809,13 @@
         </is>
       </c>
       <c r="T48" s="2" t="n">
-        <v>44</v>
+        <v>163</v>
       </c>
       <c r="U48" s="2" t="n">
-        <v>92</v>
+        <v>263</v>
       </c>
       <c r="V48" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W48" s="2" t="n">
         <v>1</v>
@@ -3817,37 +3834,42 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>après 1477</t>
+          <t>1490-1495</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>La Verna</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>National Gallery of Art</t>
+          <t>Sanctuaire de la Verna</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>L'Adoration de l'Enfant</t>
-        </is>
-      </c>
-      <c r="L49" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg/960px-Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P49" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
-        </is>
-      </c>
-      <c r="R49" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>L'Annonciation</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Annunciazione</t>
+        </is>
+      </c>
+      <c r="L49" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Haut-relief</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -3855,11 +3877,16 @@
           <t>Terre cuite émaillée</t>
         </is>
       </c>
-      <c r="T49" s="2" t="n">
-        <v>128</v>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
       </c>
       <c r="U49" s="2" t="n">
-        <v>77</v>
+        <v>210</v>
+      </c>
+      <c r="V49" s="2" t="n">
+        <v>18</v>
       </c>
       <c r="W49" s="2" t="n">
         <v>1</v>
@@ -3868,7 +3895,7 @@
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3878,57 +3905,57 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>1431-1438</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Musée de l'Œuvre du Duomo</t>
+          <t>Cathédrale Saints-Donat-et-Pierre</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>La Cantoria</t>
+          <t>Retable de la Trinité</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Cantoria</t>
-        </is>
-      </c>
-      <c r="L50" s="4" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>Polittico de la Trinità</t>
+        </is>
+      </c>
+      <c r="L50" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Elément architectural</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite émaillée</t>
         </is>
       </c>
       <c r="T50" s="2" t="n">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="U50" s="2" t="n">
-        <v>560</v>
+        <v>260</v>
       </c>
       <c r="V50" s="2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="W50" s="2" t="n">
         <v>1</v>
@@ -3937,7 +3964,7 @@
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3945,10 +3972,8 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>1442-1444</t>
-        </is>
+      <c r="D51" s="5" t="n">
+        <v>1489</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3957,22 +3982,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cathédrale Santa Maria del Fiore</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>La Résurrection</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Resurrezione di Cristo</t>
-        </is>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Lunette avec la Vierge à l'Enfant et anges</t>
+        </is>
+      </c>
+      <c r="L51" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -3980,9 +4000,9 @@
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R51" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -3991,10 +4011,10 @@
         </is>
       </c>
       <c r="T51" s="2" t="n">
-        <v>200</v>
+        <v>44</v>
       </c>
       <c r="U51" s="2" t="n">
-        <v>265</v>
+        <v>92</v>
       </c>
       <c r="V51" s="2" t="n">
         <v>18</v>
@@ -4006,7 +4026,7 @@
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Luca</t>
+          <t>Andrea</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4016,57 +4036,49 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>1446-1475</t>
+          <t>après 1477</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cathédrale Santa Maria del Fiore</t>
+          <t>National Gallery of Art</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Porte en bronze de la Sacristie</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Porta della Sacrestia delle Messe</t>
-        </is>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>10 panneaux en bas-relief</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Elément architectural</t>
+          <t>L'Adoration de l'Enfant</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg/960px-Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
+        </is>
+      </c>
+      <c r="R52" s="7" t="inlineStr">
+        <is>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Terre cuite émaillée</t>
         </is>
       </c>
       <c r="T52" s="2" t="n">
-        <v>420</v>
+        <v>128</v>
       </c>
       <c r="U52" s="2" t="n">
-        <v>200</v>
-      </c>
-      <c r="V52" s="2" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="W52" s="2" t="n">
         <v>1</v>
@@ -4085,7 +4097,7 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>1461-1466</t>
+          <t>1431-1438</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -4095,44 +4107,47 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Église San Miniato al Monte</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Les Quatre Vertus Cardinales</t>
+          <t>La Cantoria</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Le quattro virtù cardinali</t>
+          <t>Cantoria</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Médaillons en haut-relief</t>
-        </is>
-      </c>
-      <c r="R53" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>Elément architectural</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T53" s="2" t="n">
+        <v>348</v>
       </c>
       <c r="U53" s="2" t="n">
-        <v>120</v>
+        <v>560</v>
       </c>
       <c r="V53" s="2" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="W53" s="2" t="n">
         <v>1</v>
@@ -4151,47 +4166,42 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>1445-1450</t>
+          <t>1442-1444</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Impruneta</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Collegiata di Santa Maria Impruneta</t>
+          <t>Cathédrale Santa Maria del Fiore</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Tabernacle de la Sainte Croix</t>
+          <t>La Résurrection</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Tabernacolo della Santa Croce</t>
+          <t>Resurrezione di Cristo</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M54" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
@@ -4200,13 +4210,13 @@
         </is>
       </c>
       <c r="T54" s="2" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="U54" s="2" t="n">
-        <v>65</v>
+        <v>265</v>
       </c>
       <c r="V54" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W54" s="2" t="n">
         <v>1</v>
@@ -4223,59 +4233,59 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>1450 environ</t>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>1446-1475</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Cathédrale Santa Maria del Fiore</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Vierge à l'Enfant avec trois chérubins</t>
+          <t>Porte en bronze de la Sacristie</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Madonna col Bambino (Madonna Genois)</t>
-        </is>
-      </c>
-      <c r="L55" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Porta della Sacrestia delle Messe</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R55" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>10 panneaux en bas-relief</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Elément architectural</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Terre cuite émaillée</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T55" s="2" t="n">
-        <v>118</v>
+        <v>420</v>
       </c>
       <c r="U55" s="2" t="n">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="V55" s="2" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="W55" s="2" t="n">
         <v>1</v>
@@ -4292,9 +4302,9 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>1450 environ</t>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>1461-1466</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -4304,41 +4314,44 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Église San Miniato al Monte</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Vierge à l'Enfant</t>
+          <t>Les Quatre Vertus Cardinales</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Madonna col Bambino</t>
-        </is>
-      </c>
-      <c r="L56" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Le quattro virtù cardinali</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=imageinfo&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
+          <t>Médaillons en haut-relief</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
           <t>Haut-relief</t>
         </is>
       </c>
-      <c r="R56" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
-        </is>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>Terre cuite émaillée</t>
         </is>
       </c>
-      <c r="T56" s="2" t="n">
-        <v>57</v>
+      <c r="U56" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="V56" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="W56" s="2" t="n">
         <v>1</v>
@@ -4355,44 +4368,49 @@
           <t>della ROBBIA</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>1442-1444</t>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>1445-1450</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Impruneta</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Collegiata di Santa Maria Impruneta</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Vierge à la pomme</t>
+          <t>Tabernacle de la Sainte Croix</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Madonna col Bambino</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Tabernacolo della Santa Croce</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M57" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3e/Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg/1280px-Andrea_della_robbia%2C_putti_in_fasce_della_facciata_dello_spedale_degli_innocenti%2C_1487%2C_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
-        </is>
-      </c>
-      <c r="R57" s="7" t="inlineStr">
-        <is>
-          <t>Bas-relief</t>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -4401,10 +4419,13 @@
         </is>
       </c>
       <c r="T57" s="2" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="U57" s="2" t="n">
-        <v>52</v>
+        <v>65</v>
+      </c>
+      <c r="V57" s="2" t="n">
+        <v>15</v>
       </c>
       <c r="W57" s="2" t="n">
         <v>1</v>
@@ -4413,69 +4434,67 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Donato</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>di NICOLO</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>1440 environ</t>
+          <t>della ROBBIA</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Musée du Louvre</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>David (bronze)</t>
+          <t>Vierge à l'Enfant avec trois chérubins</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>David</t>
-        </is>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>Madonna col Bambino (Madonna Genois)</t>
+        </is>
+      </c>
+      <c r="L58" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T58" s="2" t="inlineStr">
-        <is>
-          <t>158 cm</t>
-        </is>
+          <t>Terre cuite émaillée</t>
+        </is>
+      </c>
+      <c r="T58" s="2" t="n">
+        <v>118</v>
       </c>
       <c r="U58" s="2" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="V58" s="2" t="n">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="W58" s="2" t="n">
         <v>1</v>
@@ -4484,17 +4503,17 @@
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Donato</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>di NICOLO</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>1408-1409</t>
+          <t>della ROBBIA</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1450 environ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4509,40 +4528,35 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>David (marbre)</t>
+          <t>Vierge à l'Enfant</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>David in marmo</t>
-        </is>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Madonna col Bambino</t>
+        </is>
+      </c>
+      <c r="L59" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>191 cm</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="n">
+          <t>Terre cuite émaillée</t>
+        </is>
+      </c>
+      <c r="T59" s="2" t="n">
         <v>57</v>
       </c>
       <c r="W59" s="2" t="n">
@@ -4552,17 +4566,17 @@
     <row r="60" ht="15" customHeight="1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Donato</t>
+          <t>Luca</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>di NICOLO</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>1415-1417</t>
+          <t>della ROBBIA</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1442-1444</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4577,44 +4591,39 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Saint Georges</t>
+          <t>Vierge à la pomme</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>San Giorgio</t>
-        </is>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>Madonna col Bambino</t>
+        </is>
+      </c>
+      <c r="L60" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>209 cm</t>
-        </is>
+          <t>Terre cuite émaillée</t>
+        </is>
+      </c>
+      <c r="T60" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="U60" s="2" t="n">
-        <v>64</v>
-      </c>
-      <c r="V60" s="2" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W60" s="2" t="n">
         <v>1</v>
@@ -4633,7 +4642,7 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>1411-1413</t>
+          <t>1440 environ</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4643,22 +4652,22 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Saint Marc</t>
+          <t>David (bronze)</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>San Marco</t>
+          <t>David</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -4673,17 +4682,19 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="n">
-        <v>248</v>
+          <t>Bronze</t>
+        </is>
+      </c>
+      <c r="T61" s="2" t="inlineStr">
+        <is>
+          <t>158 cm</t>
+        </is>
       </c>
       <c r="U61" s="2" t="n">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="V61" s="2" t="n">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="W61" s="2" t="n">
         <v>1</v>
@@ -4702,71 +4713,56 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>1423-1425</t>
+          <t>1408-1409</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Baptistère San Giovanni</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Le Festin d'Hérode</t>
+          <t>David (marbre)</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Banchetto di Erode</t>
+          <t>David in marmo</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Fontaine baptismale du baptistère de Sienne</t>
-        </is>
-      </c>
-      <c r="N62" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Fonte_battesimale_di_Siena.jpg/960px-Fonte_battesimale_di_Siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="U62" s="2" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="V62" s="2" t="n">
-        <v>7</v>
+          <t>191 cm</t>
+        </is>
+      </c>
+      <c r="U62" s="2" t="n">
+        <v>57</v>
       </c>
       <c r="W62" s="2" t="n">
         <v>1</v>
@@ -4785,7 +4781,7 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>1435 environ</t>
+          <t>1415-1417</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4795,22 +4791,22 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Annonciation Cavalcanti</t>
+          <t>Saint Georges</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Annunciazione Cavalcanti</t>
+          <t>San Giorgio</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg/960px-Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -4818,24 +4814,26 @@
           <t>Ronde-bosse</t>
         </is>
       </c>
-      <c r="R63" s="7" t="inlineStr">
-        <is>
-          <t>Mobilier liturgique</t>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>Pierre sereine dorée, putti en terre cuite</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="n">
-        <v>420</v>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>209 cm</t>
+        </is>
       </c>
       <c r="U63" s="2" t="n">
-        <v>274</v>
+        <v>64</v>
       </c>
       <c r="V63" s="2" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="W63" s="2" t="n">
         <v>1</v>
@@ -4854,32 +4852,32 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>1445-1453</t>
+          <t>1411-1413</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Padoue</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Piazza del Santo</t>
+          <t>Église d'Orsanmichele</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Monument équestre à Gattamelata</t>
+          <t>Saint Marc</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Monumento equestre al Gattamelata</t>
+          <t>San Marco</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -4889,23 +4887,22 @@
       </c>
       <c r="R64" t="inlineStr">
         <is>
-          <t>Monument avec ronde-bosse</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>Bronze</t>
-        </is>
-      </c>
-      <c r="T64" s="2" t="inlineStr">
-        <is>
-          <t>340 (statue) 800 (socle)</t>
-        </is>
-      </c>
-      <c r="U64" s="2" t="inlineStr">
-        <is>
-          <t>390 cm</t>
-        </is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T64" s="2" t="n">
+        <v>248</v>
+      </c>
+      <c r="U64" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="V64" s="2" t="n">
+        <v>60</v>
       </c>
       <c r="W64" s="2" t="n">
         <v>1</v>
@@ -4924,59 +4921,71 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>1453-1455</t>
+          <t>1423-1425</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Musée de l'Œuvre du Duomo</t>
+          <t>Baptistère San Giovanni</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Madeleine pénitente</t>
+          <t>Le Festin d'Hérode</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Maddalena penitente</t>
+          <t>Banchetto di Erode</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Donatello%2C_maria_maddalena_02.JPG/960px-Donatello%2C_maria_maddalena_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Fontaine baptismale du baptistère de Sienne</t>
+        </is>
+      </c>
+      <c r="N65" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/45/Fonte_battesimale_di_Siena.jpg/960px-Fonte_battesimale_di_Siena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>Bois de peuplier polychrome</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>188 cm</t>
-        </is>
-      </c>
-      <c r="U65" s="2" t="n">
-        <v>51</v>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
       </c>
       <c r="V65" s="2" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="W65" s="2" t="n">
         <v>1</v>
@@ -4985,17 +4994,17 @@
     <row r="66" ht="15" customHeight="1">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Donato</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GHIBERTI</t>
+          <t>di NICOLO</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>1425-1452</t>
+          <t>1435 environ</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -5005,27 +5014,22 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Musée de l'Œuvre du Duomo</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>La Porte du Paradis</t>
+          <t>Annonciation Cavalcanti</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Porta del Paradiso</t>
+          <t>Annunciazione Cavalcanti</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N66" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg/960px-Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -5035,26 +5039,22 @@
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
-        </is>
-      </c>
-      <c r="T66" s="2" t="inlineStr">
-        <is>
-          <t>520 cm</t>
-        </is>
-      </c>
-      <c r="U66" s="2" t="inlineStr">
-        <is>
-          <t>310 cm</t>
-        </is>
+          <t>Pierre sereine dorée, putti en terre cuite</t>
+        </is>
+      </c>
+      <c r="T66" s="2" t="n">
+        <v>420</v>
+      </c>
+      <c r="U66" s="2" t="n">
+        <v>274</v>
       </c>
       <c r="V66" s="2" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="W66" s="2" t="n">
         <v>1</v>
@@ -5063,57 +5063,52 @@
     <row r="67" ht="15" customHeight="1">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Donato</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GHIBERTI</t>
+          <t>di NICOLO</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>1403-1424</t>
+          <t>1445-1453</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Padoue</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Musée de l'Œuvre du Duomo</t>
+          <t>Piazza del Santo</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Porte Nord du Baptistère</t>
+          <t>Monument équestre à Gattamelata</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Porta nord du battistero</t>
+          <t>Monumento equestre al Gattamelata</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N67" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Monument avec ronde-bosse</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
@@ -5123,12 +5118,12 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>460 cm</t>
+          <t>340 (statue) 800 (socle)</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
         <is>
-          <t>270 cm</t>
+          <t>390 cm</t>
         </is>
       </c>
       <c r="W67" s="2" t="n">
@@ -5138,17 +5133,17 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Lorenzo</t>
+          <t>Donato</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GHIBERTI</t>
+          <t>di NICOLO</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>1412-1416</t>
+          <t>1453-1455</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -5158,37 +5153,22 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
-        </is>
-      </c>
-      <c r="G68" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Saint Jean-Baptiste</t>
+          <t>Madeleine pénitente</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>San Giovanni Battista</t>
+          <t>Maddalena penitente</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Albizzo di Piero en 1414</t>
-        </is>
-      </c>
-      <c r="N68" s="1" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Donatello%2C_maria_maddalena_02.JPG/960px-Donatello%2C_maria_maddalena_02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -5203,13 +5183,19 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bois de peuplier polychrome</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>255 cm</t>
-        </is>
+          <t>188 cm</t>
+        </is>
+      </c>
+      <c r="U68" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="V68" s="2" t="n">
+        <v>45</v>
       </c>
       <c r="W68" s="2" t="n">
         <v>1</v>
@@ -5228,7 +5214,7 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>1419-1423</t>
+          <t>1425-1452</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -5238,64 +5224,56 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
-        </is>
-      </c>
-      <c r="G69" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Saint Matthieu</t>
+          <t>La Porte du Paradis</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>San Matteo</t>
+          <t>Porta del Paradiso</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Copie installée en 2005 sur la façade de l'Eglise Orsanmichele dans le tabernacle  sculpté par Lorenzo Ghiberti en 1414</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Bronze doré</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>270 cm</t>
-        </is>
-      </c>
-      <c r="U69" s="2" t="n">
-        <v>100</v>
+          <t>520 cm</t>
+        </is>
+      </c>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>310 cm</t>
+        </is>
       </c>
       <c r="V69" s="2" t="n">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="W69" s="2" t="n">
         <v>1</v>
@@ -5314,7 +5292,7 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>1425-1429</t>
+          <t>1403-1424</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -5324,47 +5302,37 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Église d'Orsanmichele</t>
-        </is>
-      </c>
-      <c r="G70" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Musée de l'Œuvre du Duomo</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Saint Étienne</t>
+          <t>Porte Nord du Baptistère</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Sant'Stefano</t>
+          <t>Porta nord du battistero</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Andrea Pisano en 1340</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5c/St_Stephen_Ghiberti_Orsanmichele.jpg/960px-St_Stephen_Ghiberti_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/34/Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg/1280px-Firenze_Battistero_di_San_Giovanni_Esterno_04.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S70" t="inlineStr">
@@ -5372,14 +5340,15 @@
           <t>Bronze</t>
         </is>
       </c>
-      <c r="T70" s="2" t="n">
-        <v>237</v>
-      </c>
-      <c r="U70" s="2" t="n">
-        <v>105</v>
-      </c>
-      <c r="V70" s="2" t="n">
-        <v>70</v>
+      <c r="T70" s="2" t="inlineStr">
+        <is>
+          <t>460 cm</t>
+        </is>
+      </c>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>270 cm</t>
+        </is>
       </c>
       <c r="W70" s="2" t="n">
         <v>1</v>
@@ -5398,66 +5367,68 @@
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>1417-1427</t>
+          <t>1412-1416</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Baptistère San Giovanni</t>
+          <t>Église d'Orsanmichele</t>
         </is>
       </c>
       <c r="G71" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Le Baptême du Christ</t>
+          <t>Saint Jean-Baptiste</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Battesimo di Cristo</t>
+          <t>San Giovanni Battista</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Albizzo di Piero en 1414</t>
+        </is>
+      </c>
+      <c r="N71" s="1" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/6/68/StJohntheBaptistGhiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="U71" s="2" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="V71" s="2" t="n">
-        <v>8</v>
+          <t>255 cm</t>
+        </is>
       </c>
       <c r="W71" s="2" t="n">
         <v>1</v>
@@ -5476,66 +5447,74 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>1417-1427</t>
+          <t>1419-1423</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sienne</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Baptistère San Giovanni</t>
+          <t>Église d'Orsanmichele</t>
         </is>
       </c>
       <c r="G72" s="1" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>L'Arrestation de Saint Jean-Baptiste</t>
+          <t>Saint Matthieu</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Cattura di San Giovanni Battista</t>
+          <t>San Matteo</t>
         </is>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Copie installée en 2005 sur la façade de l'Eglise Orsanmichele dans le tabernacle  sculpté par Lorenzo Ghiberti en 1414</t>
+        </is>
+      </c>
+      <c r="N72" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg/960px-San_Matteo_%28Ghiberti%29_replica_and_original_niche-Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>Bronze doré</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>60 cm</t>
-        </is>
-      </c>
-      <c r="U72" s="2" t="inlineStr">
-        <is>
-          <t>60 cm</t>
-        </is>
+          <t>270 cm</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="n">
+        <v>100</v>
       </c>
       <c r="V72" s="2" t="n">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="W72" s="2" t="n">
         <v>1</v>
@@ -5554,7 +5533,7 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>1432-1442</t>
+          <t>1425-1429</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -5564,42 +5543,47 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Cathédrale Santa Maria del Fiore</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>Chapelle de Saint Zenobe</t>
-        </is>
-      </c>
-      <c r="I73" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Église d'Orsanmichele</t>
+        </is>
+      </c>
+      <c r="G73" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg/960px-La_chiesa_di_Orsanmichele%2C_detta_anticamente_anche_chiesa_di_San_Michele_in_Orto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Châsse de Saint Zenobe</t>
+          <t>Saint Étienne</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Arca di san Zanobi</t>
+          <t>Sant'Stefano</t>
         </is>
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Copie installée en 1966 sur la façade de l'Eglise Orsanmichele dans le tabernacle sculpté par Andrea Pisano en 1340</t>
+        </is>
+      </c>
+      <c r="N73" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5c/St_Stephen_Ghiberti_Orsanmichele.jpg/960px-St_Stephen_Ghiberti_Orsanmichele.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
@@ -5608,10 +5592,13 @@
         </is>
       </c>
       <c r="T73" s="2" t="n">
-        <v>85</v>
+        <v>237</v>
       </c>
       <c r="U73" s="2" t="n">
-        <v>193</v>
+        <v>105</v>
+      </c>
+      <c r="V73" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="W73" s="2" t="n">
         <v>1</v>
@@ -5620,218 +5607,233 @@
     <row r="74" ht="15" customHeight="1">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>LAURANA</t>
+          <t>GHIBERTI</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1417-1427</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Palerme</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Palazzo Abatellis</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>Galerie régionale de Sicile</t>
+          <t>Baptistère San Giovanni</t>
+        </is>
+      </c>
+      <c r="G74" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Buste d'Éléonore d'Aragon</t>
+          <t>Le Baptême du Christ</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Busto di Eleonora d'Aragona</t>
+          <t>Battesimo di Cristo</t>
         </is>
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg/1280px-Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>Buste de portrait</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T74" s="2" t="n">
-        <v>50</v>
-      </c>
-      <c r="U74" s="2" t="n">
-        <v>48</v>
+          <t>Bronze doré</t>
+        </is>
+      </c>
+      <c r="T74" s="2" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
       </c>
       <c r="V74" s="2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="W74" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>LAURANA</t>
+          <t>GHIBERTI</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>1471-1474</t>
+          <t>1417-1427</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Sienne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Castel Nuovo</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>Arc de triomphe d'Alphonse d'Aragon</t>
+          <t>Baptistère San Giovanni</t>
+        </is>
+      </c>
+      <c r="G75" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/SienaBattisteroSanGiovanni1.jpg/1280px-SienaBattisteroSanGiovanni1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Le Triomphe d'Alphonse d'Aragon</t>
+          <t>L'Arrestation de Saint Jean-Baptiste</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Il Trionfo di Alfonso d'Aragona</t>
+          <t>Cattura di San Giovanni Battista</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Triumphbogen_Castel_Nuovo_Neapel.jpg/500px-Triumphbogen_Castel_Nuovo_Neapel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ensemble architectural</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>Relief monumental architectural</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T75" s="2" t="n">
-        <v>3500</v>
-      </c>
-      <c r="U75" s="2" t="n">
-        <v>1000</v>
+          <t>Bronze doré</t>
+        </is>
+      </c>
+      <c r="T75" s="2" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>60 cm</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="n">
+        <v>8</v>
       </c>
       <c r="W75" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Francesco</t>
+          <t>Lorenzo</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>LAURANA</t>
-        </is>
-      </c>
-      <c r="D76" s="5" t="n">
-        <v>1475</v>
+          <t>GHIBERTI</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="inlineStr">
+        <is>
+          <t>1432-1442</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Musée du Louvre</t>
+          <t>Cathédrale Santa Maria del Fiore</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Département des Sculptures</t>
+          <t>Chapelle de Saint Zenobe</t>
+        </is>
+      </c>
+      <c r="I76" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG/1280px-Santa_maria_del_fiore%2C_tribuna_di_san_zanobi%2C_altare_di_san_zanobi_2.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Buste de jeune femme</t>
+          <t>Châsse de Saint Zenobe</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Busto di Maria di Sicilia</t>
+          <t>Arca di san Zanobi</t>
         </is>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>Buste de portrait</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T76" s="2" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="U76" s="2" t="n">
-        <v>41</v>
-      </c>
-      <c r="V76" s="2" t="n">
-        <v>24</v>
+        <v>193</v>
       </c>
       <c r="W76" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" ht="15" customHeight="1">
@@ -5847,37 +5849,37 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>1474-1475</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Vienne</t>
+          <t>Palerme</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kunsthistorisches Museum</t>
+          <t>Palazzo Abatellis</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Kunstkammer</t>
+          <t>Galerie régionale de Sicile</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Buste de Laure de Noves</t>
+          <t>Buste d'Éléonore d'Aragon</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Busto di Laura de Noves</t>
+          <t>Busto di Eleonora d'Aragona</t>
         </is>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg/1280px-Francesco_Laurana%2C_Busto_di_donna%2C_quasi_certamente_di_Eleonora_d%27Aragona%2C_1489-91_-FG1.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -5892,14 +5894,17 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>Marbre polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T77" s="2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="U77" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
+      </c>
+      <c r="V77" s="2" t="n">
+        <v>24</v>
       </c>
       <c r="W77" s="2" t="n">
         <v>3</v>
@@ -5908,47 +5913,57 @@
     <row r="78" ht="15" customHeight="1">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LOMBARDO</t>
+          <t>LAURANA</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>1476-1481</t>
+          <t>1471-1474</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Basilique Santi Giovanni e Paolo</t>
+          <t>Castel Nuovo</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Arc de triomphe d'Alphonse d'Aragon</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>"Tombeau du doge Pietro Mocenigo"</t>
+          <t>Le Triomphe d'Alphonse d'Aragon</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Il Trionfo di Alfonso d'Aragona</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG/1280px-Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Triumphbogen_Castel_Nuovo_Neapel.jpg/500px-Triumphbogen_Castel_Nuovo_Neapel.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Monument funéraire avec rondes-bosses</t>
+          <t>Ensemble architectural</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Relief monumental architectural</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
@@ -5957,10 +5972,10 @@
         </is>
       </c>
       <c r="T78" s="2" t="n">
-        <v>1200</v>
+        <v>3500</v>
       </c>
       <c r="U78" s="2" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="W78" s="2" t="n">
         <v>3</v>
@@ -5969,47 +5984,55 @@
     <row r="79" ht="15" customHeight="1">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LOMBARDO</t>
-        </is>
-      </c>
-      <c r="D79" s="5" t="inlineStr">
-        <is>
-          <t>1463 environ</t>
-        </is>
+          <t>LAURANA</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>1475</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Venise</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Basilique Santi Giovanni e Paolo</t>
+          <t>Musée du Louvre</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Département des Sculptures</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Tombeau du doge Pasquale Malipiero</t>
-        </is>
-      </c>
-      <c r="L79" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Buste de jeune femme</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Busto di Maria di Sicilia</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/db/Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg/1280px-Buste_de_jeune_femme_-_Francesco_Laurana_-_Mus%C3%A9e_du_Louvre_Peintures_MR_2597.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Monument funéraire avec rondes-bosses</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Buste de portrait</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
@@ -6018,13 +6041,13 @@
         </is>
       </c>
       <c r="T79" s="2" t="n">
-        <v>500</v>
+        <v>44</v>
       </c>
       <c r="U79" s="2" t="n">
-        <v>300</v>
+        <v>41</v>
       </c>
       <c r="V79" s="2" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="W79" s="2" t="n">
         <v>3</v>
@@ -6033,59 +6056,69 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Pietro</t>
+          <t>Francesco</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LOMBARDO</t>
+          <t>LAURANA</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1474-1475</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ravenne</t>
+          <t>Vienne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tombeau de Dante</t>
+          <t>Kunsthistorisches Museum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Kunstkammer</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Bas-relief de Dante lisant</t>
-        </is>
-      </c>
-      <c r="L80" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/SarcophageDeDante.jpg/960px-SarcophageDeDante.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Buste de Laure de Noves</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Busto di Laura de Noves</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG/960px-Female_bust_%28An_ideal_portrait_of_Laura%29_by_Francesco_Laurana.JPG?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Monument funéraire avec bas-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
+          <t>Buste de portrait</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Marbre polychrome</t>
         </is>
       </c>
       <c r="T80" s="2" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="U80" s="2" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="W80" s="2" t="n">
         <v>3</v>
@@ -6104,7 +6137,7 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>1481-1489</t>
+          <t>1476-1481</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -6114,27 +6147,27 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Église Santa Maria dei Miracoli</t>
+          <t>Basilique Santi Giovanni e Paolo</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Église Santa Maria dei Miracoli</t>
-        </is>
-      </c>
-      <c r="L81" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG/1280px-0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>"Tombeau du doge Pietro Mocenigo"</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/1/14/Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG/1280px-Pietro_Lombardo_-_Monumento_del_doge_Pietro_Mocenigo_-_Venezia-SS_Giovanni_e_Paolo.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ensemble architectural</t>
+          <t>Monument funéraire avec rondes-bosses</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>Monument</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
@@ -6143,12 +6176,9 @@
         </is>
       </c>
       <c r="T81" s="2" t="n">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="U81" s="2" t="n">
-        <v>2600</v>
-      </c>
-      <c r="V81" s="2" t="n">
         <v>700</v>
       </c>
       <c r="W81" s="2" t="n">
@@ -6158,64 +6188,62 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Guido</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>LOMBARDO</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>1477-1479 environ</t>
+          <t>1463 environ</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Modène</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Église San Giovanni Battista</t>
+          <t>Basilique Santi Giovanni e Paolo</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Lamentation sur le Christ mort</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Compianto sul Cristo morto</t>
-        </is>
-      </c>
-      <c r="L82" s="4" t="inlineStr">
-        <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG/1280px-Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>Tombeau du doge Pasquale Malipiero</t>
+        </is>
+      </c>
+      <c r="L82" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg/960px-Interior_of_Santi_Giovanni_e_Paolo_%28Venice%29_-_Monument_to_the_doge_Pasquale_Malipiero.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
+          <t>Monument funéraire avec rondes-bosses</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>Groupe sculptural</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T82" s="2" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="U82" s="2" t="n">
-        <v>400</v>
+        <v>300</v>
+      </c>
+      <c r="V82" s="2" t="n">
+        <v>70</v>
       </c>
       <c r="W82" s="2" t="n">
         <v>3</v>
@@ -6224,67 +6252,59 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Guido</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>LOMBARDO</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>1480-1485</t>
+          <t>1483</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ferrare</t>
+          <t>Ravenne</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Église du Gesù</t>
+          <t>Tombeau de Dante</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Déploration sur le Christ mort</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Compianto sul Cristo morto</t>
-        </is>
-      </c>
-      <c r="L83" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Bas-relief de Dante lisant</t>
+        </is>
+      </c>
+      <c r="L83" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/SarcophageDeDante.jpg/960px-SarcophageDeDante.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
+          <t>Monument funéraire avec bas-relief</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>Groupe sculptural</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T83" s="2" t="n">
-        <v>175</v>
+        <v>65</v>
       </c>
       <c r="U83" s="2" t="n">
-        <v>500</v>
-      </c>
-      <c r="V83" s="2" t="n">
-        <v>200</v>
+        <v>58</v>
       </c>
       <c r="W83" s="2" t="n">
         <v>3</v>
@@ -6293,72 +6313,62 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Guido</t>
+          <t>Pietro</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MAZZONI</t>
+          <t>LOMBARDO</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>1485</t>
+          <t>1481-1489</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Modène</t>
+          <t>Venise</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Cathédrale de Modène</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>Crypta</t>
+          <t>Église Santa Maria dei Miracoli</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>L'Adoration des bergers</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Presepio (Adorazione dei pastori)</t>
-        </is>
-      </c>
-      <c r="L84" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/20/Mazzoni_Adoration_Modena.jpg/1280px-Mazzoni_Adoration_Modena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Église Santa Maria dei Miracoli</t>
+        </is>
+      </c>
+      <c r="L84" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/22/0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG/1280px-0_Venise%2C_Santa_Maria_dei_Miracoli_%C3%A0_Venise_%281%29.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Groupe en ronde-bosse</t>
+          <t>Ensemble architectural</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>Groupe sculptural</t>
+          <t>Monument</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T84" s="2" t="n">
-        <v>180</v>
+        <v>1400</v>
       </c>
       <c r="U84" s="2" t="n">
-        <v>220</v>
+        <v>2600</v>
       </c>
       <c r="V84" s="2" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="W84" s="2" t="n">
         <v>3</v>
@@ -6377,27 +6387,22 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>1492-1494</t>
+          <t>1477-1479 environ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Modène</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Église Sant'Anna dei Lombardi</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>Cappella Compianto</t>
+          <t>Église San Giovanni Battista</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Déploration sur le Christ mort</t>
+          <t>Lamentation sur le Christ mort</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -6407,7 +6412,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg/1280px-GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/61/Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG/1280px-Modena%2C_San_Giovanni_Battista%2C_Compianto_sul_Cristo_Morto_by_Guido_Mazzoni_004.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -6417,7 +6422,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>Groupe sculptural</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -6429,10 +6434,7 @@
         <v>180</v>
       </c>
       <c r="U85" s="2" t="n">
-        <v>450</v>
-      </c>
-      <c r="V85" s="2" t="n">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="W85" s="2" t="n">
         <v>3</v>
@@ -6441,47 +6443,42 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tilman</t>
+          <t>Guido</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>RIEMENSCHNEIDER</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>1490-1492</t>
+          <t>1480-1485</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Wurtzbourg</t>
+          <t>Ferrare</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mainfränkisches Museum</t>
+          <t>Église du Gesù</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Adam et Ève</t>
+          <t>Déploration sur le Christ mort</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Adam und Eva</t>
+          <t>Compianto sul Cristo morto</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg/1280px-Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N86" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG/1280px-Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e0/Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG/1280px-Guido_Mazzoni_Compianto_sul_Cristo_morto_Chiesa_San_Michele_del_Ges%C3%B9_Ferrara.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -6489,161 +6486,175 @@
           <t>Groupe en ronde-bosse</t>
         </is>
       </c>
-      <c r="R86" s="7" t="inlineStr">
-        <is>
-          <t>Ronde-bosse</t>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>Pierre de grès</t>
-        </is>
-      </c>
-      <c r="T86" s="2" t="inlineStr">
-        <is>
-          <t>189 cm (Adam), 181 cm (Ève)</t>
-        </is>
+          <t>Terre cuite polychrome</t>
+        </is>
+      </c>
+      <c r="T86" s="2" t="n">
+        <v>175</v>
       </c>
       <c r="U86" s="2" t="n">
-        <v>55</v>
+        <v>500</v>
       </c>
       <c r="V86" s="2" t="n">
-        <v>35</v>
+        <v>200</v>
       </c>
       <c r="W86" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Tilman</t>
+          <t>Guido</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>RIEMENSCHNEIDER</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>1490-1494</t>
+          <t>1485</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Münnerstadt</t>
+          <t>Modène</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Église Sainte-Marie-Madeleine</t>
+          <t>Cathédrale de Modène</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Crypta</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Retable de Sainte Marie-Madeleine</t>
+          <t>L'Adoration des bergers</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Magdalenenaltar</t>
+          <t>Presepio (Adorazione dei pastori)</t>
         </is>
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/20/Mazzoni_Adoration_Modena.jpg/1280px-Mazzoni_Adoration_Modena.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>Retable</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>Bois de tilleul</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T87" s="2" t="n">
-        <v>1200</v>
+        <v>180</v>
       </c>
       <c r="U87" s="2" t="n">
-        <v>370</v>
+        <v>220</v>
+      </c>
+      <c r="V87" s="2" t="n">
+        <v>110</v>
       </c>
       <c r="W87" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Tilman</t>
+          <t>Guido</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RIEMENSCHNEIDER</t>
+          <t>MAZZONI</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1492-1494</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Heidelberg</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kurpfälzisches Museum</t>
+          <t>Église Sant'Anna dei Lombardi</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Cappella Compianto</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Retable des Douze Apôtres de Windsheim</t>
+          <t>Déploration sur le Christ mort</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Windsheimer Zwölfbotenaltar</t>
+          <t>Compianto sul Cristo morto</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Bad_Windsheim-007.jpg/1280px-Bad_Windsheim-007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg/1280px-GuidoMazzoniCompiantoNaplesAnnaLombardi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>Retable</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>Bois de tilleul polychrome</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T88" s="2" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="U88" s="2" t="n">
+        <v>450</v>
+      </c>
+      <c r="V88" s="2" t="n">
         <v>250</v>
       </c>
       <c r="W88" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89" ht="15" customHeight="1">
@@ -6659,57 +6670,64 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>1499</t>
+          <t>1490-1492</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bamberg</t>
+          <t>Wurtzbourg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Pierre et Saint-Georges</t>
+          <t>Mainfränkisches Museum</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Tombeau de l'empereur Henri II et de l'impératrice Cunégonde (commencé)</t>
+          <t>Adam et Ève</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Kaisergrab im Bamberger Dom</t>
+          <t>Adam und Eva</t>
         </is>
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/BambergDom-GrabHeinrichKunigunde.JPG/1280px-BambergDom-GrabHeinrichKunigunde.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e5/Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg/1280px-Stammtisch_S%C3%BCddeutschland-GLAM_2017-04-3788.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="N89" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG/1280px-Marienkapelle_W%C3%BCrzburg_-_IMG_6727.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Groupe en ronde-bosse</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>Marbre</t>
-        </is>
-      </c>
-      <c r="T89" s="2" t="n">
-        <v>170</v>
+          <t>Pierre de grès</t>
+        </is>
+      </c>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>189 cm (Adam), 181 cm (Ève)</t>
+        </is>
       </c>
       <c r="U89" s="2" t="n">
-        <v>340</v>
+        <v>55</v>
       </c>
       <c r="V89" s="2" t="n">
-        <v>220</v>
+        <v>35</v>
       </c>
       <c r="W89" s="2" t="n">
         <v>2</v>
@@ -6728,57 +6746,54 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1490-1494</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cleveland</t>
+          <t>Münnerstadt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Cleveland Museum of Art</t>
+          <t>Église Sainte-Marie-Madeleine</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Saint Jérôme et le Lion</t>
+          <t>Retable de Sainte Marie-Madeleine</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Heiliger Hieronymus mit dem Löwen</t>
+          <t>Magdalenenaltar</t>
         </is>
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8c/M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG/960px-M%C3%BCnnerstadt%2C_St_Maria_Magdalena_005.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>Albâtre</t>
+          <t>Bois de tilleul</t>
         </is>
       </c>
       <c r="T90" s="2" t="n">
-        <v>38</v>
+        <v>1200</v>
       </c>
       <c r="U90" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="V90" s="2" t="n">
-        <v>16</v>
+        <v>370</v>
       </c>
       <c r="W90" s="2" t="n">
         <v>2</v>
@@ -6797,52 +6812,54 @@
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>1496-1499</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wurtzbourg</t>
+          <t>Heidelberg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Kilian</t>
+          <t>Kurpfälzisches Museum</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Tombeau du prince-évêque Rudolf von Scherenberg</t>
-        </is>
-      </c>
-      <c r="L91" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Scherenberggravewhole.jpg/500px-Scherenberggravewhole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Retable des Douze Apôtres de Windsheim</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Windsheimer Zwölfbotenaltar</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Bad_Windsheim-007.jpg/1280px-Bad_Windsheim-007.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>Marbre rouge</t>
+          <t>Bois de tilleul polychrome</t>
         </is>
       </c>
       <c r="T91" s="2" t="n">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="U91" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="V91" s="2" t="n">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="W91" s="2" t="n">
         <v>2</v>
@@ -6851,42 +6868,42 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Tilman</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ROSSELLINO</t>
+          <t>RIEMENSCHNEIDER</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>1461-1466</t>
+          <t>1499</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Bamberg</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Église San Miniato al Monte</t>
+          <t>Cathédrale Saint-Pierre et Saint-Georges</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Tombeau du cardinal de Portugal (Jacques de Lusitanie)</t>
+          <t>Tombeau de l'empereur Henri II et de l'impératrice Cunégonde (commencé)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Tomba del Cardinale del Portogallo</t>
+          <t>Kaisergrab im Bamberger Dom</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG/1280px-Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/BambergDom-GrabHeinrichKunigunde.JPG/1280px-BambergDom-GrabHeinrichKunigunde.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
@@ -6905,52 +6922,57 @@
         </is>
       </c>
       <c r="T92" s="2" t="n">
-        <v>400</v>
+        <v>170</v>
       </c>
       <c r="U92" s="2" t="n">
-        <v>480</v>
+        <v>340</v>
+      </c>
+      <c r="V92" s="2" t="n">
+        <v>220</v>
       </c>
       <c r="W92" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Tilman</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>ROSSELLINO</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="n">
-        <v>1456</v>
+          <t>RIEMENSCHNEIDER</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Cleveland</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Victoria and Albert Museum</t>
+          <t>Cleveland Museum of Art</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Buste de Giovanni Chellini</t>
+          <t>Saint Jérôme et le Lion</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Busto di Giovanni di San Miniato</t>
+          <t>Heiliger Hieronymus mit dem Löwen</t>
         </is>
       </c>
       <c r="L93" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/74/Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg/960px-Tilman_riemenschneider%2C_san_girolamo_e_il_leone%2C_alabastro%2C_1495_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -6960,91 +6982,89 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Albâtre</t>
         </is>
       </c>
       <c r="T93" s="2" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="U93" s="2" t="n">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="V93" s="2" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="W93" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Antonio</t>
+          <t>Tilman</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ROSSELLINO</t>
+          <t>RIEMENSCHNEIDER</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1496-1499</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Wurtzbourg</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Musée national du Bargello</t>
+          <t>Cathédrale Saint-Kilian</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Buste de Matteo Palmieri</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Busto di Matteo Palmieri</t>
-        </is>
-      </c>
-      <c r="L94" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>Tombeau du prince-évêque Rudolf von Scherenberg</t>
+        </is>
+      </c>
+      <c r="L94" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Scherenberggravewhole.jpg/500px-Scherenberggravewhole.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>Buste</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Marbre rouge</t>
         </is>
       </c>
       <c r="T94" s="2" t="n">
-        <v>53</v>
+        <v>400</v>
       </c>
       <c r="U94" s="2" t="n">
-        <v>57</v>
+        <v>158</v>
+      </c>
+      <c r="V94" s="2" t="n">
+        <v>45</v>
       </c>
       <c r="W94" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1">
@@ -7058,54 +7078,56 @@
           <t>ROSSELLINO</t>
         </is>
       </c>
-      <c r="D95" s="5" t="n">
-        <v>1470</v>
+      <c r="D95" s="5" t="inlineStr">
+        <is>
+          <t>1461-1466</t>
+        </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Metropolitan Museum of Art</t>
+          <t>Église San Miniato al Monte</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Vierge à l'Enfant</t>
+          <t>Tombeau du cardinal de Portugal (Jacques de Lusitanie)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>Madonna col Bambino</t>
+          <t>Tomba del Cardinale del Portogallo</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Madonna_and_Child_with_Angels_MET_DP236934.jpg/960px-Madonna_and_Child_with_Angels_MET_DP236934.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG/1280px-Cappella_del_cardinale_di_portogallo_03_tomba_del_cardinale_di_antonio_e_bernardo_rossellino_05.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>Terre cuite polychrome</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T95" s="2" t="n">
-        <v>73</v>
+        <v>400</v>
       </c>
       <c r="U95" s="2" t="n">
-        <v>53</v>
+        <v>480</v>
       </c>
       <c r="W95" s="2" t="n">
         <v>3</v>
@@ -7114,7 +7136,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -7122,56 +7144,57 @@
           <t>ROSSELLINO</t>
         </is>
       </c>
-      <c r="D96" s="5" t="inlineStr">
-        <is>
-          <t>1445-1450</t>
-        </is>
+      <c r="D96" s="5" t="n">
+        <v>1456</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Florence</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Basilique Santa Croce</t>
+          <t>Victoria and Albert Museum</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Tombeau de Leonardo Bruni</t>
+          <t>Buste de Giovanni Chellini</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Tomba di Leonardo Bruni</t>
+          <t>Busto di Giovanni di San Miniato</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8d/Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg/960px-Antonio_Rossellino-Giovanni_di_Antonio_Chellini_da_San_Miniato-Victoria_and_Albert_Museum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Marbre scuplté et polychromie</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T96" s="2" t="n">
-        <v>715</v>
+        <v>58</v>
       </c>
       <c r="U96" s="2" t="n">
-        <v>316</v>
+        <v>51</v>
+      </c>
+      <c r="V96" s="2" t="n">
+        <v>30</v>
       </c>
       <c r="W96" s="2" t="n">
         <v>3</v>
@@ -7180,7 +7203,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -7190,54 +7213,54 @@
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>1443-1444</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Palazzo della Fraternita dei Laici</t>
+          <t>Musée national du Bargello</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Lunette de la Vierge de miséricorde</t>
+          <t>Buste de Matteo Palmieri</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>Madonna della Misericordia</t>
+          <t>Busto di Matteo Palmieri</t>
         </is>
       </c>
       <c r="L97" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg/1280px-Antonio_rossellino%2C_ritratto_di_matteo_plamieri%2C_da_canto_alle_rondini%2C_1468_ca._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Haut-relief</t>
+          <t>Ronde-bosse</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>Statue et relief de façade</t>
+          <t>Buste</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Marbre et pierre</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T97" s="2" t="n">
-        <v>250</v>
+        <v>53</v>
       </c>
       <c r="U97" s="2" t="n">
-        <v>300</v>
+        <v>57</v>
       </c>
       <c r="W97" s="2" t="n">
         <v>3</v>
@@ -7246,7 +7269,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Bernardo</t>
+          <t>Antonio</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -7254,69 +7277,54 @@
           <t>ROSSELLINO</t>
         </is>
       </c>
-      <c r="D98" s="5" t="inlineStr">
-        <is>
-          <t>1451-1452</t>
-        </is>
+      <c r="D98" s="5" t="n">
+        <v>1470</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Pistoia</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cathédrale Saint-Zénon</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>Chapelle du Sacrement</t>
+          <t>Metropolitan Museum of Art</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Tombeau du juriste Filippo Lazzari</t>
+          <t>Vierge à l'Enfant</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>Tomba di Filippo Lazzari</t>
+          <t>Madonna col Bambino</t>
         </is>
       </c>
       <c r="L98" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N98" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Madonna_and_Child_with_Angels_MET_DP236934.jpg/960px-Madonna_and_Child_with_Angels_MET_DP236934.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Terre cuite polychrome</t>
         </is>
       </c>
       <c r="T98" s="2" t="n">
-        <v>466</v>
+        <v>73</v>
       </c>
       <c r="U98" s="2" t="n">
-        <v>233</v>
-      </c>
-      <c r="V98" s="2" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="W98" s="2" t="n">
         <v>3</v>
@@ -7335,7 +7343,7 @@
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>1449-1451</t>
+          <t>1445-1450</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -7345,43 +7353,44 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Église Sant'Egidio</t>
+          <t>Basilique Santa Croce</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Tabernacle du Saint-Sacrement de Santa Maria Nuova</t>
-        </is>
-      </c>
-      <c r="L99" s="6" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG/960px-Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="N99" s="1" t="n"/>
+          <t>Tombeau de Leonardo Bruni</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Tomba di Leonardo Bruni</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>https://upload.wikimedia.org/wikipedia/commons/thumb/b/bd/Bruni_Santa_Croce_01.JPG/1280px-Bruni_Santa_Croce_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Marbre scuplté et polychromie</t>
         </is>
       </c>
       <c r="T99" s="2" t="n">
-        <v>120</v>
+        <v>715</v>
       </c>
       <c r="U99" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="V99" s="2" t="n">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="W99" s="2" t="n">
         <v>3</v>
@@ -7390,103 +7399,118 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Veit</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>STOSS</t>
+          <t>ROSSELLINO</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>1477-1489</t>
+          <t>1443-1444</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Cracovie</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Basilique Notre-Dame</t>
+          <t>Palazzo della Fraternita dei Laici</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>"Retable de l'église Notre-Dame"</t>
+          <t>Lunette de la Vierge de miséricorde</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Madonna della Misericordia</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg/1280px-Madonna_della_Misericordia%2C_opera_di_Bernardo_Rossellino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mobilier liturgique</t>
+          <t>Haut-relief</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>Retable</t>
+          <t>Statue et relief de façade</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Bois polychrome doré</t>
+          <t>Marbre et pierre</t>
         </is>
       </c>
       <c r="T100" s="2" t="n">
-        <v>1300</v>
+        <v>250</v>
       </c>
       <c r="U100" s="2" t="n">
-        <v>1100</v>
+        <v>300</v>
       </c>
       <c r="W100" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Veit</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>STOSS</t>
+          <t>ROSSELLINO</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>1492</t>
+          <t>1451-1452</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cracovie</t>
+          <t>Pistoia</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cathédrale du Wawel</t>
+          <t>Cathédrale Saint-Zénon</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Chapelle du Sacrement</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Tombeau du roi Casimir IV Jagellon</t>
+          <t>Tombeau du juriste Filippo Lazzari</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Nagrobek Kazimierza IV Jagiellończyka</t>
+          <t>Tomba di Filippo Lazzari</t>
         </is>
       </c>
       <c r="L101" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8e/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg/1280px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%282%29b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="N101" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg/960px-Monumento_sepolcrale_di_Filippo_Lazzari_di_Bernardo_e_Antonio_Rossellino%2C_1462_%281%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -7501,87 +7525,85 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>Marbre rouge de Salzbourg</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T101" s="2" t="n">
-        <v>386</v>
+        <v>466</v>
       </c>
       <c r="U101" s="2" t="n">
-        <v>280</v>
+        <v>233</v>
       </c>
       <c r="V101" s="2" t="n">
-        <v>162</v>
+        <v>50</v>
       </c>
       <c r="W101" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Veit</t>
+          <t>Bernardo</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>STOSS</t>
-        </is>
-      </c>
-      <c r="D102" s="5" t="n">
-        <v>1495</v>
+          <t>ROSSELLINO</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="inlineStr">
+        <is>
+          <t>1449-1451</t>
+        </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cracovie</t>
+          <t>Florence</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Église des Dominicains</t>
+          <t>Église Sant'Egidio</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Épitaphe de Callimaque (Filippo Buonaccorsi)</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Tablica epitafijna Kallimacha</t>
-        </is>
-      </c>
-      <c r="L102" s="4" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/.Epitafium_Kallimacha02.JPG/960px-.Epitafium_Kallimacha02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
+          <t>Tabernacle du Saint-Sacrement de Santa Maria Nuova</t>
+        </is>
+      </c>
+      <c r="L102" s="6" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/87/Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG/960px-Sant%27Egidio%2C_tabernacolo_di_Bernardo_Rossellino_e_Lorenzo_Ghiberti.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="N102" s="1" t="n"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Bas-relief</t>
-        </is>
-      </c>
-      <c r="R102" s="7" t="inlineStr">
-        <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Mobilier liturgique</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>Bronze</t>
+          <t>Marbre</t>
         </is>
       </c>
       <c r="T102" s="2" t="n">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="U102" s="2" t="n">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="V102" s="2" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="W102" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103" ht="15" customHeight="1">
@@ -7597,7 +7619,7 @@
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>1477-1489</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -7612,41 +7634,34 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Crucifix de Slacker</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Krucyfiks kamienny Wita Stwosza</t>
+          <t>"Retable de l'église Notre-Dame"</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Krucyfiks_Wita_Stwosza_03.jpg/1280px-Krucyfiks_Wita_Stwosza_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-        </is>
-      </c>
-      <c r="M103" s="1" t="inlineStr">
-        <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6a/Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg/1280px-Altar_of_Veit_Stoss%2C_St._Mary%27s_Church%2C_Krakow%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Objet liturgique</t>
+          <t>Mobilier liturgique</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Retable</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>Pierre calcaire</t>
+          <t>Bois polychrome doré</t>
         </is>
       </c>
       <c r="T103" s="2" t="n">
-        <v>250</v>
+        <v>1300</v>
+      </c>
+      <c r="U103" s="2" t="n">
+        <v>1100</v>
       </c>
       <c r="W103" s="2" t="n">
         <v>2</v>
@@ -7665,57 +7680,57 @@
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>1495-1500</t>
+          <t>1492</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Nuremberg</t>
+          <t>Cracovie</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Musée national germanique</t>
+          <t>Cathédrale du Wawel</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Vierge à l'Enfant</t>
+          <t>Tombeau du roi Casimir IV Jagellon</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Nürnberger Madonna</t>
+          <t>Nagrobek Kazimierza IV Jagiellończyka</t>
         </is>
       </c>
       <c r="L104" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg/960px-Tombstone_of_Kazimieras_Jogailaitis_with_Polish_Eagle%2C_Lithuanian_Vytis_%28Waykimas%29_and_Jagiellonian_Double_Cross_in_the_Wawel_Cathedral_in_Krakow%2C_1855-1858.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>Ronde-bosse</t>
+          <t>Monument funéraire avec ronde-bosse</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>Bois de tilleul</t>
+          <t>Marbre rouge de Salzbourg</t>
         </is>
       </c>
       <c r="T104" s="2" t="n">
-        <v>140</v>
+        <v>386</v>
       </c>
       <c r="U104" s="2" t="n">
-        <v>40</v>
+        <v>280</v>
       </c>
       <c r="V104" s="2" t="n">
-        <v>37</v>
+        <v>162</v>
       </c>
       <c r="W104" s="2" t="n">
         <v>2</v>
@@ -7732,10 +7747,8 @@
           <t>STOSS</t>
         </is>
       </c>
-      <c r="D105" s="5" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
+      <c r="D105" s="5" t="n">
+        <v>1495</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -7744,56 +7757,258 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Cathédrale de Wloclaweck</t>
+          <t>Église des Dominicains</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Tombeau de l'évêque Piotr de Bnina</t>
+          <t>Épitaphe de Callimaque (Filippo Buonaccorsi)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Nagrobek biskupa Piotra z Bnina</t>
+          <t>Tablica epitafijna Kallimacha</t>
         </is>
       </c>
       <c r="L105" s="4" t="inlineStr">
         <is>
-          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/10/.Epitafium_Kallimacha02.JPG/960px-.Epitafium_Kallimacha02.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Monument funéraire</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>Monument funéraire avec ronde-bosse</t>
+          <t>Bas-relief</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>Marbre</t>
+          <t>Bronze</t>
         </is>
       </c>
       <c r="T105" s="2" t="n">
-        <v>112</v>
+        <v>198</v>
       </c>
       <c r="U105" s="2" t="n">
-        <v>217</v>
+        <v>114</v>
       </c>
       <c r="V105" s="2" t="n">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="W105" s="2" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="106" ht="15" customHeight="1"/>
-    <row r="107" ht="15" customHeight="1"/>
-    <row r="108" ht="15" customHeight="1"/>
-    <row r="109" ht="15" customHeight="1"/>
+    <row r="106" ht="15" customHeight="1">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Veit</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>STOSS</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Cracovie</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Basilique Notre-Dame</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>Crucifix de Slacker</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Krucyfiks kamienny Wita Stwosza</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4e/Krucyfiks_Wita_Stwosza_03.jpg/1280px-Krucyfiks_Wita_Stwosza_03.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="M106" s="1" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fe/Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg/960px-Church_of_Our_Lady_Assumed_into_Heaven%2C_crucifix-ca._1496_by_Veit_Stoss_%2C_5_Mariacki_square%2C_Old_Town%2C_Krak%C3%B3w%2C_Poland.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Objet liturgique</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>Pierre calcaire</t>
+        </is>
+      </c>
+      <c r="T106" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="W106" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" ht="15" customHeight="1">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Veit</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>STOSS</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="inlineStr">
+        <is>
+          <t>1495-1500</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Nuremberg</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Musée national germanique</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>Vierge à l'Enfant</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Nürnberger Madonna</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg/960px-Madonna_with_Child%2C_Veit_Stoss%2C_Nuremberg%2C_c._1500%2C_limewood_-_Germanisches_Nationalmuseum_-_Nuremberg%2C_Germany_-DSC02845.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>Bois de tilleul</t>
+        </is>
+      </c>
+      <c r="T107" s="2" t="n">
+        <v>140</v>
+      </c>
+      <c r="U107" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="V107" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="W107" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" ht="15" customHeight="1">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Veit</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>STOSS</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="inlineStr">
+        <is>
+          <t>1492</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Cracovie</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Cathédrale de Wloclaweck</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>Tombeau de l'évêque Piotr de Bnina</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Nagrobek biskupa Piotra z Bnina</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/43/Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg/1280px-Nagrobek_bp._Piotra_z_Bnina._Katedra_W%C5%82oc%C5%82awek.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Monument funéraire</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Monument funéraire avec ronde-bosse</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Marbre</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="n">
+        <v>112</v>
+      </c>
+      <c r="U108" s="2" t="n">
+        <v>217</v>
+      </c>
+      <c r="V108" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="W108" s="2" t="n">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L2" r:id="rId1"/>
@@ -7802,121 +8017,126 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L7" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L8" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L9" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L10" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L11" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L12" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L13" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L14" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L15" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L16" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L17" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L18" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L19" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L20" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L21" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L22" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L23" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L24" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L25" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L26" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L27" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L28" r:id="rId29"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L29" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G45" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G68" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G69" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G70" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G30" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L30" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L31" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L32" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L33" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L34" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L35" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L36" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L37" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L38" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L39" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L40" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L41" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L42" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L43" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L44" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L45" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L46" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L47" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L48" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L49" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L50" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L51" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L52" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L53" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L54" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L55" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L56" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L57" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L58" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L59" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L60" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L61" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L62" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L63" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L64" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L65" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L66" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L67" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L68" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L69" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L70" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G71" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L71" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G72" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L72" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G73" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L73" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G74" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L74" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId106"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId107"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId108"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId109"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId110"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId111"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId112"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N98" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L75" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I76" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L76" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L77" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L78" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L79" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L80" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L81" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L82" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L83" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L84" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L85" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L86" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L87" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L88" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L89" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L90" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L91" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L92" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L93" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L94" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L95" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L96" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L97" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L98" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L99" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L100" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L101" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N101" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L102" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L103" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L104" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L105" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L106" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L107" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="L108" r:id="rId126"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{132E34F7-594D-4177-A41B-037A6ADC4D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63DDC69-8EF1-4FE6-9F54-8E3F1D922509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="636">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -604,12 +604,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b1/Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg/1280px-Bartolomeo_Colleoni_by_Andrea_del_Verrocchio.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Monument avec ronde-bosse</t>
-  </si>
-  <si>
-    <t>395 (statue) 400 (socle)</t>
-  </si>
-  <si>
     <t>1470 environ</t>
   </si>
   <si>
@@ -1159,9 +1153,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/29/Monumento_al_Gattamelata_Padova_jm56942.jpg/960px-Monumento_al_Gattamelata_Padova_jm56942.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>340 (statue) 800 (socle)</t>
-  </si>
-  <si>
     <t>390 cm</t>
   </si>
   <si>
@@ -1916,6 +1907,27 @@
   </si>
   <si>
     <t xml:space="preserve">Saint Jean l'Évangéliste </t>
+  </si>
+  <si>
+    <t>DONATELLO</t>
+  </si>
+  <si>
+    <t>340 pour la statue, 800 pour le socle</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse et bas-relief intégralement conçu par l'artiste.</t>
+  </si>
+  <si>
+    <t>Bronze (ronde-bosse) Pierre (socle)</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse conçue par l'artiste, le socle est dû à Alessando Leopardi.</t>
+  </si>
+  <si>
+    <t>395 pour la statue, 400 pour le socle</t>
+  </si>
+  <si>
+    <t>Bronze (statue) Pierre (socle)</t>
   </si>
 </sst>
 </file>
@@ -2299,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W108"/>
+  <dimension ref="A1:X108"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
@@ -2321,6 +2333,7 @@
     <col min="19" max="19" width="8.42578125" customWidth="1"/>
     <col min="20" max="20" width="6.85546875" style="2" customWidth="1"/>
     <col min="21" max="23" width="9.140625" style="2" customWidth="1"/>
+    <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2393,6 +2406,11 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artiste associé</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2402,7 +2420,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
@@ -2461,7 +2479,7 @@
         <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="S3" t="s">
         <v>37</v>
@@ -2575,7 +2593,7 @@
         <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="K6" t="s">
         <v>58</v>
@@ -2584,7 +2602,7 @@
         <v>59</v>
       </c>
       <c r="R6" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="S6" t="s">
         <v>44</v>
@@ -2710,7 +2728,7 @@
         <v>70</v>
       </c>
       <c r="J9" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>76</v>
@@ -2865,7 +2883,7 @@
         <v>99</v>
       </c>
       <c r="R13" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="S13" t="s">
         <v>52</v>
@@ -3029,7 +3047,7 @@
         <v>116</v>
       </c>
       <c r="R17" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="S17" t="s">
         <v>52</v>
@@ -3064,7 +3082,7 @@
         <v>123</v>
       </c>
       <c r="R18" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="S18" t="s">
         <v>52</v>
@@ -3187,7 +3205,7 @@
         <v>137</v>
       </c>
       <c r="R21" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="S21" t="s">
         <v>52</v>
@@ -3269,7 +3287,7 @@
         <v>149</v>
       </c>
       <c r="R23" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="S23" t="s">
         <v>52</v>
@@ -3310,7 +3328,7 @@
         <v>154</v>
       </c>
       <c r="R24" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="S24" t="s">
         <v>52</v>
@@ -3386,7 +3404,7 @@
         <v>163</v>
       </c>
       <c r="R26" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="S26" t="s">
         <v>31</v>
@@ -3430,7 +3448,7 @@
         <v>169</v>
       </c>
       <c r="R27" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="S27" t="s">
         <v>31</v>
@@ -3474,7 +3492,7 @@
         <v>174</v>
       </c>
       <c r="R28" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S28" t="s">
         <v>31</v>
@@ -3500,7 +3518,7 @@
         <v>177</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="E29" t="s">
         <v>56</v>
@@ -3614,14 +3632,16 @@
       <c r="L31" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="R31" t="s">
-        <v>194</v>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument avec ronde-bosse conçue par l'artiste, le socle est dû à Alessandro Leopardi.</t>
+        </is>
       </c>
       <c r="S31" t="s">
-        <v>31</v>
+        <v>635</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>195</v>
+        <v>634</v>
       </c>
       <c r="U31" s="2">
         <v>380</v>
@@ -3641,7 +3661,7 @@
         <v>177</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E32" t="s">
         <v>56</v>
@@ -3650,16 +3670,16 @@
         <v>129</v>
       </c>
       <c r="J32" t="s">
+        <v>195</v>
+      </c>
+      <c r="K32" t="s">
+        <v>196</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="K32" t="s">
+      <c r="M32" t="s">
         <v>198</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="M32" t="s">
-        <v>200</v>
       </c>
       <c r="R32" t="s">
         <v>30</v>
@@ -3697,13 +3717,13 @@
         <v>57</v>
       </c>
       <c r="J33" t="s">
+        <v>199</v>
+      </c>
+      <c r="K33" t="s">
+        <v>200</v>
+      </c>
+      <c r="L33" s="4" t="s">
         <v>201</v>
-      </c>
-      <c r="K33" t="s">
-        <v>202</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>203</v>
       </c>
       <c r="R33" t="s">
         <v>30</v>
@@ -3732,7 +3752,7 @@
         <v>177</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E34" t="s">
         <v>56</v>
@@ -3741,22 +3761,22 @@
         <v>151</v>
       </c>
       <c r="H34" t="s">
+        <v>203</v>
+      </c>
+      <c r="J34" t="s">
+        <v>204</v>
+      </c>
+      <c r="K34" t="s">
         <v>205</v>
       </c>
-      <c r="J34" t="s">
+      <c r="L34" s="6" t="s">
         <v>206</v>
-      </c>
-      <c r="K34" t="s">
-        <v>207</v>
-      </c>
-      <c r="L34" s="6" t="s">
-        <v>208</v>
       </c>
       <c r="R34" t="s">
         <v>86</v>
       </c>
       <c r="S34" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="T34" s="2">
         <v>540</v>
@@ -3770,22 +3790,22 @@
     </row>
     <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" t="s">
+        <v>209</v>
+      </c>
+      <c r="C35" t="s">
         <v>210</v>
       </c>
-      <c r="B35" t="s">
+      <c r="D35" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C35" t="s">
+      <c r="E35" t="s">
         <v>212</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="F35" t="s">
         <v>213</v>
-      </c>
-      <c r="E35" t="s">
-        <v>214</v>
-      </c>
-      <c r="F35" t="s">
-        <v>215</v>
       </c>
       <c r="J35" t="s">
         <v>48</v>
@@ -3794,13 +3814,13 @@
         <v>49</v>
       </c>
       <c r="L35" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="R35" t="s">
+        <v>215</v>
+      </c>
+      <c r="S35" t="s">
         <v>216</v>
-      </c>
-      <c r="R35" t="s">
-        <v>217</v>
-      </c>
-      <c r="S35" t="s">
-        <v>218</v>
       </c>
       <c r="T35" s="2">
         <v>165</v>
@@ -3817,37 +3837,37 @@
     </row>
     <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>208</v>
+      </c>
+      <c r="B36" t="s">
+        <v>209</v>
+      </c>
+      <c r="C36" t="s">
         <v>210</v>
       </c>
-      <c r="B36" t="s">
-        <v>211</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="D36" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E36" t="s">
         <v>212</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="F36" t="s">
+        <v>218</v>
+      </c>
+      <c r="H36" t="s">
         <v>219</v>
       </c>
-      <c r="E36" t="s">
-        <v>214</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="J36" t="s">
         <v>220</v>
       </c>
-      <c r="H36" t="s">
+      <c r="K36" t="s">
         <v>221</v>
       </c>
-      <c r="J36" t="s">
+      <c r="L36" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="K36" t="s">
-        <v>223</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>224</v>
-      </c>
       <c r="R36" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="S36" t="s">
         <v>52</v>
@@ -3867,37 +3887,37 @@
     </row>
     <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>208</v>
+      </c>
+      <c r="B37" t="s">
+        <v>209</v>
+      </c>
+      <c r="C37" t="s">
         <v>210</v>
-      </c>
-      <c r="B37" t="s">
-        <v>211</v>
-      </c>
-      <c r="C37" t="s">
-        <v>212</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>124</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="F37" t="s">
+        <v>223</v>
+      </c>
+      <c r="J37" t="s">
+        <v>224</v>
+      </c>
+      <c r="K37" t="s">
         <v>225</v>
       </c>
-      <c r="J37" t="s">
+      <c r="L37" s="6" t="s">
         <v>226</v>
-      </c>
-      <c r="K37" t="s">
-        <v>227</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>228</v>
       </c>
       <c r="R37" t="s">
         <v>30</v>
       </c>
       <c r="S37" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T37" s="2">
         <v>55</v>
@@ -3914,37 +3934,37 @@
     </row>
     <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>208</v>
+      </c>
+      <c r="B38" t="s">
+        <v>209</v>
+      </c>
+      <c r="C38" t="s">
         <v>210</v>
       </c>
-      <c r="B38" t="s">
-        <v>211</v>
-      </c>
-      <c r="C38" t="s">
-        <v>212</v>
-      </c>
       <c r="D38" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="E38" t="s">
+        <v>228</v>
+      </c>
+      <c r="F38" t="s">
         <v>229</v>
       </c>
-      <c r="E38" t="s">
+      <c r="J38" t="s">
         <v>230</v>
       </c>
-      <c r="F38" t="s">
+      <c r="K38" t="s">
         <v>231</v>
       </c>
-      <c r="J38" t="s">
+      <c r="L38" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="K38" t="s">
-        <v>233</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="R38" t="s">
         <v>30</v>
       </c>
       <c r="S38" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T38" s="2">
         <v>50</v>
@@ -3961,34 +3981,34 @@
     </row>
     <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>233</v>
+      </c>
+      <c r="B39" t="s">
+        <v>234</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="B39" t="s">
+      <c r="E39" t="s">
         <v>236</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="F39" t="s">
         <v>237</v>
       </c>
-      <c r="E39" t="s">
+      <c r="H39" t="s">
         <v>238</v>
       </c>
-      <c r="F39" t="s">
+      <c r="J39" t="s">
         <v>239</v>
       </c>
-      <c r="H39" t="s">
+      <c r="K39" t="s">
         <v>240</v>
       </c>
-      <c r="J39" t="s">
+      <c r="L39" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="K39" t="s">
-        <v>242</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>243</v>
-      </c>
       <c r="R39" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="S39" t="s">
         <v>52</v>
@@ -4008,13 +4028,13 @@
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E40" t="s">
         <v>81</v>
@@ -4023,16 +4043,16 @@
         <v>82</v>
       </c>
       <c r="J40" t="s">
+        <v>243</v>
+      </c>
+      <c r="K40" t="s">
+        <v>244</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="K40" t="s">
-        <v>246</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>247</v>
-      </c>
       <c r="R40" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="S40" t="s">
         <v>52</v>
@@ -4052,37 +4072,37 @@
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="E41" t="s">
+        <v>212</v>
+      </c>
+      <c r="F41" t="s">
+        <v>247</v>
+      </c>
+      <c r="H41" t="s">
         <v>248</v>
       </c>
-      <c r="E41" t="s">
-        <v>214</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
         <v>249</v>
       </c>
-      <c r="H41" t="s">
+      <c r="K41" t="s">
         <v>250</v>
       </c>
-      <c r="J41" t="s">
+      <c r="L41" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="K41" t="s">
+      <c r="R41" t="s">
+        <v>616</v>
+      </c>
+      <c r="S41" t="s">
         <v>252</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="R41" t="s">
-        <v>619</v>
-      </c>
-      <c r="S41" t="s">
-        <v>254</v>
       </c>
       <c r="T41" s="2">
         <v>1800</v>
@@ -4099,40 +4119,40 @@
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B42" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E42" t="s">
+        <v>212</v>
+      </c>
+      <c r="F42" t="s">
+        <v>247</v>
+      </c>
+      <c r="H42" t="s">
+        <v>250</v>
+      </c>
+      <c r="J42" t="s">
+        <v>254</v>
+      </c>
+      <c r="K42" t="s">
         <v>255</v>
       </c>
-      <c r="E42" t="s">
-        <v>214</v>
-      </c>
-      <c r="F42" t="s">
-        <v>249</v>
-      </c>
-      <c r="H42" t="s">
-        <v>252</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="L42" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="K42" t="s">
-        <v>257</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>258</v>
-      </c>
       <c r="M42" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="R42" t="s">
         <v>51</v>
       </c>
       <c r="S42" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="T42" s="2">
         <v>99</v>
@@ -4149,34 +4169,34 @@
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E43" t="s">
         <v>81</v>
       </c>
       <c r="F43" t="s">
+        <v>258</v>
+      </c>
+      <c r="H43" t="s">
+        <v>259</v>
+      </c>
+      <c r="J43" t="s">
         <v>260</v>
       </c>
-      <c r="H43" t="s">
+      <c r="K43" t="s">
         <v>261</v>
       </c>
-      <c r="J43" t="s">
+      <c r="L43" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="K43" t="s">
-        <v>263</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>264</v>
-      </c>
       <c r="R43" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="S43" t="s">
         <v>52</v>
@@ -4193,34 +4213,34 @@
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B44" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E44" t="s">
         <v>81</v>
       </c>
       <c r="F44" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H44" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="J44" t="s">
+        <v>263</v>
+      </c>
+      <c r="K44" t="s">
+        <v>264</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="K44" t="s">
+      <c r="R44" t="s">
         <v>266</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="R44" t="s">
-        <v>268</v>
       </c>
       <c r="S44" t="s">
         <v>52</v>
@@ -4240,28 +4260,28 @@
         <v>176</v>
       </c>
       <c r="B45" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E45" t="s">
         <v>56</v>
       </c>
       <c r="F45" t="s">
+        <v>269</v>
+      </c>
+      <c r="J45" t="s">
+        <v>270</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>271</v>
-      </c>
-      <c r="J45" t="s">
-        <v>272</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>273</v>
       </c>
       <c r="R45" t="s">
         <v>51</v>
       </c>
       <c r="S45" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="T45" s="2">
         <v>100</v>
@@ -4281,31 +4301,31 @@
         <v>176</v>
       </c>
       <c r="B46" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D46" s="5">
         <v>1520</v>
       </c>
       <c r="E46" t="s">
+        <v>273</v>
+      </c>
+      <c r="F46" t="s">
+        <v>607</v>
+      </c>
+      <c r="J46" t="s">
+        <v>274</v>
+      </c>
+      <c r="K46" t="s">
         <v>275</v>
       </c>
-      <c r="F46" t="s">
-        <v>610</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="L46" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="K46" t="s">
-        <v>277</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>278</v>
       </c>
       <c r="R46" t="s">
         <v>51</v>
       </c>
       <c r="S46" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T46" s="2">
         <v>80</v>
@@ -4325,7 +4345,7 @@
         <v>176</v>
       </c>
       <c r="B47" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>171</v>
@@ -4337,19 +4357,19 @@
         <v>120</v>
       </c>
       <c r="J47" t="s">
+        <v>278</v>
+      </c>
+      <c r="K47" t="s">
+        <v>279</v>
+      </c>
+      <c r="L47" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="K47" t="s">
-        <v>281</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>282</v>
-      </c>
       <c r="R47" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="S47" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T47" s="2">
         <v>270</v>
@@ -4369,31 +4389,31 @@
         <v>176</v>
       </c>
       <c r="B48" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D48" s="5">
         <v>1489</v>
       </c>
       <c r="E48" t="s">
+        <v>281</v>
+      </c>
+      <c r="F48" t="s">
+        <v>282</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="F48" t="s">
+      <c r="J48" t="s">
         <v>284</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>285</v>
-      </c>
-      <c r="J48" t="s">
-        <v>286</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>287</v>
       </c>
       <c r="R48" t="s">
         <v>51</v>
       </c>
       <c r="S48" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T48" s="2">
         <v>163</v>
@@ -4413,34 +4433,34 @@
         <v>176</v>
       </c>
       <c r="B49" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D49" s="5">
         <v>1475</v>
       </c>
       <c r="E49" t="s">
+        <v>286</v>
+      </c>
+      <c r="F49" t="s">
+        <v>287</v>
+      </c>
+      <c r="J49" t="s">
         <v>288</v>
       </c>
-      <c r="F49" t="s">
+      <c r="K49" t="s">
         <v>289</v>
       </c>
-      <c r="J49" t="s">
+      <c r="L49" s="6" t="s">
         <v>290</v>
-      </c>
-      <c r="K49" t="s">
-        <v>291</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>292</v>
       </c>
       <c r="R49" t="s">
         <v>51</v>
       </c>
       <c r="S49" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="U49" s="2">
         <v>210</v>
@@ -4457,31 +4477,31 @@
         <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>91</v>
       </c>
       <c r="E50" t="s">
+        <v>292</v>
+      </c>
+      <c r="F50" t="s">
+        <v>293</v>
+      </c>
+      <c r="J50" t="s">
         <v>294</v>
       </c>
-      <c r="F50" t="s">
+      <c r="K50" t="s">
         <v>295</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="K50" t="s">
-        <v>297</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="R50" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="S50" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T50" s="2">
         <v>370</v>
@@ -4501,7 +4521,7 @@
         <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D51" s="5">
         <v>1489</v>
@@ -4510,19 +4530,19 @@
         <v>56</v>
       </c>
       <c r="F51" t="s">
+        <v>297</v>
+      </c>
+      <c r="J51" t="s">
+        <v>298</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>299</v>
-      </c>
-      <c r="J51" t="s">
-        <v>300</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>301</v>
       </c>
       <c r="R51" t="s">
         <v>51</v>
       </c>
       <c r="S51" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T51" s="2">
         <v>44</v>
@@ -4542,10 +4562,10 @@
         <v>176</v>
       </c>
       <c r="B52" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E52" t="s">
         <v>38</v>
@@ -4554,17 +4574,17 @@
         <v>39</v>
       </c>
       <c r="J52" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="P52" s="7"/>
       <c r="R52" s="7" t="s">
         <v>43</v>
       </c>
       <c r="S52" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T52" s="2">
         <v>128</v>
@@ -4578,28 +4598,28 @@
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B53" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E53" t="s">
         <v>56</v>
       </c>
       <c r="F53" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J53" t="s">
+        <v>305</v>
+      </c>
+      <c r="K53" t="s">
+        <v>306</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>307</v>
-      </c>
-      <c r="K53" t="s">
-        <v>308</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>309</v>
       </c>
       <c r="R53" t="s">
         <v>36</v>
@@ -4622,34 +4642,34 @@
     </row>
     <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B54" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E54" t="s">
         <v>56</v>
       </c>
       <c r="F54" t="s">
+        <v>310</v>
+      </c>
+      <c r="J54" t="s">
+        <v>311</v>
+      </c>
+      <c r="K54" t="s">
         <v>312</v>
       </c>
-      <c r="J54" t="s">
+      <c r="L54" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="K54" t="s">
-        <v>314</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>315</v>
       </c>
       <c r="R54" t="s">
         <v>51</v>
       </c>
       <c r="S54" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T54" s="2">
         <v>200</v>
@@ -4666,28 +4686,28 @@
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B55" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E55" t="s">
         <v>56</v>
       </c>
       <c r="F55" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="J55" t="s">
+        <v>315</v>
+      </c>
+      <c r="K55" t="s">
+        <v>316</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>317</v>
-      </c>
-      <c r="K55" t="s">
-        <v>318</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="R55" t="s">
         <v>51</v>
@@ -4710,34 +4730,34 @@
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B56" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E56" t="s">
         <v>56</v>
       </c>
       <c r="F56" t="s">
+        <v>319</v>
+      </c>
+      <c r="J56" t="s">
+        <v>320</v>
+      </c>
+      <c r="K56" t="s">
         <v>321</v>
       </c>
-      <c r="J56" t="s">
+      <c r="L56" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="K56" t="s">
-        <v>323</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="R56" t="s">
         <v>51</v>
       </c>
       <c r="S56" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="U56" s="2">
         <v>120</v>
@@ -4751,37 +4771,37 @@
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B57" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="E57" t="s">
+        <v>324</v>
+      </c>
+      <c r="F57" t="s">
         <v>325</v>
       </c>
-      <c r="E57" t="s">
+      <c r="J57" t="s">
         <v>326</v>
       </c>
-      <c r="F57" t="s">
+      <c r="K57" t="s">
         <v>327</v>
       </c>
-      <c r="J57" t="s">
+      <c r="L57" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="K57" t="s">
+      <c r="M57" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="L57" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>331</v>
-      </c>
       <c r="R57" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="S57" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T57" s="2">
         <v>150</v>
@@ -4798,34 +4818,34 @@
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B58" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D58" t="s">
+        <v>330</v>
+      </c>
+      <c r="E58" t="s">
+        <v>331</v>
+      </c>
+      <c r="F58" t="s">
         <v>332</v>
       </c>
-      <c r="E58" t="s">
+      <c r="J58" t="s">
         <v>333</v>
       </c>
-      <c r="F58" t="s">
+      <c r="K58" t="s">
         <v>334</v>
       </c>
-      <c r="J58" t="s">
+      <c r="L58" s="1" t="s">
         <v>335</v>
-      </c>
-      <c r="K58" t="s">
-        <v>336</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>337</v>
       </c>
       <c r="R58" t="s">
         <v>51</v>
       </c>
       <c r="S58" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T58" s="2">
         <v>118</v>
@@ -4842,13 +4862,13 @@
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B59" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D59" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E59" t="s">
         <v>56</v>
@@ -4857,19 +4877,19 @@
         <v>57</v>
       </c>
       <c r="J59" t="s">
+        <v>336</v>
+      </c>
+      <c r="K59" t="s">
+        <v>337</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="K59" t="s">
-        <v>339</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>340</v>
       </c>
       <c r="R59" t="s">
         <v>51</v>
       </c>
       <c r="S59" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T59" s="2">
         <v>57</v>
@@ -4880,13 +4900,13 @@
     </row>
     <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B60" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D60" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E60" t="s">
         <v>56</v>
@@ -4895,19 +4915,19 @@
         <v>57</v>
       </c>
       <c r="J60" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="K60" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="R60" t="s">
         <v>51</v>
       </c>
       <c r="S60" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T60" s="2">
         <v>70</v>
@@ -4921,13 +4941,13 @@
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>341</v>
+      </c>
+      <c r="B61" t="s">
+        <v>342</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>343</v>
-      </c>
-      <c r="B61" t="s">
-        <v>344</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>345</v>
       </c>
       <c r="E61" t="s">
         <v>56</v>
@@ -4936,13 +4956,13 @@
         <v>57</v>
       </c>
       <c r="J61" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="K61" t="s">
         <v>178</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="R61" t="s">
         <v>30</v>
@@ -4951,7 +4971,7 @@
         <v>31</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="U61" s="2">
         <v>51</v>
@@ -4965,13 +4985,16 @@
     </row>
     <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B62" t="s">
-        <v>344</v>
+        <v>342</v>
+      </c>
+      <c r="C62" t="s">
+        <v>629</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E62" t="s">
         <v>56</v>
@@ -4980,13 +5003,13 @@
         <v>57</v>
       </c>
       <c r="J62" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="K62" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="R62" t="s">
         <v>30</v>
@@ -4995,7 +5018,7 @@
         <v>52</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="U62" s="2">
         <v>57</v>
@@ -5006,13 +5029,16 @@
     </row>
     <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B63" t="s">
-        <v>344</v>
+        <v>342</v>
+      </c>
+      <c r="C63" t="s">
+        <v>629</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E63" t="s">
         <v>56</v>
@@ -5021,13 +5047,13 @@
         <v>57</v>
       </c>
       <c r="J63" t="s">
+        <v>351</v>
+      </c>
+      <c r="K63" t="s">
+        <v>352</v>
+      </c>
+      <c r="L63" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="K63" t="s">
-        <v>354</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="R63" t="s">
         <v>30</v>
@@ -5036,7 +5062,7 @@
         <v>52</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="U63" s="2">
         <v>64</v>
@@ -5050,13 +5076,16 @@
     </row>
     <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
-        <v>344</v>
+        <v>342</v>
+      </c>
+      <c r="C64" t="s">
+        <v>629</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="E64" t="s">
         <v>56</v>
@@ -5065,13 +5094,13 @@
         <v>181</v>
       </c>
       <c r="J64" t="s">
+        <v>355</v>
+      </c>
+      <c r="K64" t="s">
+        <v>356</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>357</v>
-      </c>
-      <c r="K64" t="s">
-        <v>358</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>359</v>
       </c>
       <c r="R64" t="s">
         <v>30</v>
@@ -5094,34 +5123,37 @@
     </row>
     <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B65" t="s">
-        <v>344</v>
+        <v>342</v>
+      </c>
+      <c r="C65" t="s">
+        <v>629</v>
       </c>
       <c r="D65" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="E65" t="s">
+        <v>236</v>
+      </c>
+      <c r="F65" t="s">
+        <v>359</v>
+      </c>
+      <c r="J65" t="s">
         <v>360</v>
       </c>
-      <c r="E65" t="s">
-        <v>238</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="K65" t="s">
         <v>361</v>
       </c>
-      <c r="J65" t="s">
+      <c r="L65" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="K65" t="s">
+      <c r="M65" t="s">
         <v>363</v>
       </c>
-      <c r="L65" s="4" t="s">
+      <c r="N65" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="M65" t="s">
-        <v>365</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>366</v>
       </c>
       <c r="R65" t="s">
         <v>43</v>
@@ -5130,10 +5162,10 @@
         <v>44</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="V65" s="2">
         <v>7</v>
@@ -5144,13 +5176,16 @@
     </row>
     <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B66" t="s">
-        <v>344</v>
+        <v>342</v>
+      </c>
+      <c r="C66" t="s">
+        <v>629</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E66" t="s">
         <v>56</v>
@@ -5159,19 +5194,19 @@
         <v>120</v>
       </c>
       <c r="J66" t="s">
+        <v>367</v>
+      </c>
+      <c r="K66" t="s">
+        <v>368</v>
+      </c>
+      <c r="L66" s="4" t="s">
         <v>369</v>
-      </c>
-      <c r="K66" t="s">
-        <v>370</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>371</v>
       </c>
       <c r="R66" t="s">
         <v>51</v>
       </c>
       <c r="S66" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="T66" s="2">
         <v>218</v>
@@ -5185,40 +5220,43 @@
     </row>
     <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B67" t="s">
-        <v>344</v>
+        <v>342</v>
+      </c>
+      <c r="C67" t="s">
+        <v>629</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="E67" t="s">
+        <v>372</v>
+      </c>
+      <c r="F67" t="s">
         <v>373</v>
       </c>
-      <c r="E67" t="s">
+      <c r="J67" t="s">
         <v>374</v>
       </c>
-      <c r="F67" t="s">
+      <c r="K67" t="s">
         <v>375</v>
       </c>
-      <c r="J67" t="s">
+      <c r="L67" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="K67" t="s">
+      <c r="R67" t="s">
+        <v>631</v>
+      </c>
+      <c r="S67" t="s">
+        <v>632</v>
+      </c>
+      <c r="T67" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="U67" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="R67" t="s">
-        <v>194</v>
-      </c>
-      <c r="S67" t="s">
-        <v>31</v>
-      </c>
-      <c r="T67" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="U67" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="W67" s="2">
         <v>1</v>
@@ -5226,37 +5264,40 @@
     </row>
     <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B68" t="s">
-        <v>344</v>
+        <v>342</v>
+      </c>
+      <c r="C68" t="s">
+        <v>629</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E68" t="s">
         <v>56</v>
       </c>
       <c r="F68" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J68" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="K68" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="R68" t="s">
         <v>30</v>
       </c>
       <c r="S68" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="U68" s="2">
         <v>51</v>
@@ -5270,31 +5311,31 @@
     </row>
     <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B69" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E69" t="s">
         <v>56</v>
       </c>
       <c r="F69" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J69" t="s">
+        <v>387</v>
+      </c>
+      <c r="K69" t="s">
+        <v>388</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="N69" s="1" t="s">
         <v>390</v>
-      </c>
-      <c r="K69" t="s">
-        <v>391</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>393</v>
       </c>
       <c r="R69" t="s">
         <v>43</v>
@@ -5303,10 +5344,10 @@
         <v>44</v>
       </c>
       <c r="T69" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="U69" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="V69" s="2">
         <v>11</v>
@@ -5317,31 +5358,31 @@
     </row>
     <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B70" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D70" s="5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="E70" t="s">
         <v>56</v>
       </c>
       <c r="F70" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J70" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="K70" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="R70" t="s">
         <v>43</v>
@@ -5361,13 +5402,13 @@
     </row>
     <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B71" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D71" s="5" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E71" t="s">
         <v>56</v>
@@ -5385,13 +5426,13 @@
         <v>131</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="M71" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="R71" t="s">
         <v>30</v>
@@ -5400,7 +5441,7 @@
         <v>31</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="W71" s="2">
         <v>1</v>
@@ -5408,13 +5449,13 @@
     </row>
     <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B72" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D72" s="5" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="E72" t="s">
         <v>56</v>
@@ -5426,19 +5467,19 @@
         <v>182</v>
       </c>
       <c r="J72" t="s">
+        <v>404</v>
+      </c>
+      <c r="K72" t="s">
+        <v>405</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="M72" t="s">
         <v>407</v>
       </c>
-      <c r="K72" t="s">
+      <c r="N72" s="1" t="s">
         <v>408</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="M72" t="s">
-        <v>410</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>411</v>
       </c>
       <c r="R72" t="s">
         <v>30</v>
@@ -5447,7 +5488,7 @@
         <v>31</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="U72" s="2">
         <v>100</v>
@@ -5461,13 +5502,13 @@
     </row>
     <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B73" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D73" s="5" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E73" t="s">
         <v>56</v>
@@ -5479,19 +5520,19 @@
         <v>182</v>
       </c>
       <c r="J73" t="s">
+        <v>410</v>
+      </c>
+      <c r="K73" t="s">
+        <v>411</v>
+      </c>
+      <c r="L73" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="M73" t="s">
         <v>413</v>
       </c>
-      <c r="K73" t="s">
+      <c r="N73" s="1" t="s">
         <v>414</v>
-      </c>
-      <c r="L73" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="M73" t="s">
-        <v>416</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>417</v>
       </c>
       <c r="R73" t="s">
         <v>30</v>
@@ -5514,43 +5555,43 @@
     </row>
     <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B74" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D74" s="5" t="s">
+        <v>415</v>
+      </c>
+      <c r="E74" t="s">
+        <v>236</v>
+      </c>
+      <c r="F74" t="s">
+        <v>359</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="J74" t="s">
+        <v>417</v>
+      </c>
+      <c r="K74" t="s">
         <v>418</v>
       </c>
-      <c r="E74" t="s">
-        <v>238</v>
-      </c>
-      <c r="F74" t="s">
-        <v>361</v>
-      </c>
-      <c r="G74" s="1" t="s">
+      <c r="L74" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="J74" t="s">
-        <v>420</v>
-      </c>
-      <c r="K74" t="s">
-        <v>421</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>422</v>
-      </c>
       <c r="R74" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="S74" t="s">
         <v>44</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="U74" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="V74" s="2">
         <v>8</v>
@@ -5561,43 +5602,43 @@
     </row>
     <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B75" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="E75" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="F75" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="J75" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="K75" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="R75" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="S75" t="s">
         <v>44</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="V75" s="2">
         <v>8</v>
@@ -5608,37 +5649,37 @@
     </row>
     <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B76" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="E76" t="s">
         <v>56</v>
       </c>
       <c r="F76" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="H76" t="s">
+        <v>424</v>
+      </c>
+      <c r="I76" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="J76" t="s">
+        <v>426</v>
+      </c>
+      <c r="K76" t="s">
         <v>427</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="L76" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="J76" t="s">
-        <v>429</v>
-      </c>
-      <c r="K76" t="s">
-        <v>430</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>431</v>
-      </c>
       <c r="R76" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="S76" t="s">
         <v>31</v>
@@ -5655,31 +5696,31 @@
     </row>
     <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>429</v>
+      </c>
+      <c r="B77" t="s">
+        <v>430</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>431</v>
+      </c>
+      <c r="E77" t="s">
         <v>432</v>
       </c>
-      <c r="B77" t="s">
+      <c r="F77" t="s">
         <v>433</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="H77" t="s">
         <v>434</v>
       </c>
-      <c r="E77" t="s">
+      <c r="J77" t="s">
         <v>435</v>
       </c>
-      <c r="F77" t="s">
+      <c r="K77" t="s">
         <v>436</v>
       </c>
-      <c r="H77" t="s">
+      <c r="L77" s="4" t="s">
         <v>437</v>
-      </c>
-      <c r="J77" t="s">
-        <v>438</v>
-      </c>
-      <c r="K77" t="s">
-        <v>439</v>
-      </c>
-      <c r="L77" s="4" t="s">
-        <v>440</v>
       </c>
       <c r="R77" t="s">
         <v>30</v>
@@ -5702,34 +5743,34 @@
     </row>
     <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B78" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D78" s="5" t="s">
+        <v>438</v>
+      </c>
+      <c r="E78" t="s">
+        <v>439</v>
+      </c>
+      <c r="F78" t="s">
+        <v>440</v>
+      </c>
+      <c r="H78" t="s">
         <v>441</v>
       </c>
-      <c r="E78" t="s">
+      <c r="J78" t="s">
         <v>442</v>
       </c>
-      <c r="F78" t="s">
+      <c r="K78" t="s">
         <v>443</v>
       </c>
-      <c r="H78" t="s">
+      <c r="L78" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="J78" t="s">
-        <v>445</v>
-      </c>
-      <c r="K78" t="s">
-        <v>446</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>447</v>
-      </c>
       <c r="R78" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="S78" t="s">
         <v>52</v>
@@ -5746,31 +5787,31 @@
     </row>
     <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B79" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D79" s="5">
         <v>1475</v>
       </c>
       <c r="E79" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F79" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H79" t="s">
+        <v>445</v>
+      </c>
+      <c r="J79" t="s">
+        <v>446</v>
+      </c>
+      <c r="K79" t="s">
+        <v>447</v>
+      </c>
+      <c r="L79" s="4" t="s">
         <v>448</v>
-      </c>
-      <c r="J79" t="s">
-        <v>449</v>
-      </c>
-      <c r="K79" t="s">
-        <v>450</v>
-      </c>
-      <c r="L79" s="4" t="s">
-        <v>451</v>
       </c>
       <c r="R79" t="s">
         <v>30</v>
@@ -5793,37 +5834,37 @@
     </row>
     <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B80" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="E80" t="s">
+        <v>450</v>
+      </c>
+      <c r="F80" t="s">
+        <v>451</v>
+      </c>
+      <c r="H80" t="s">
         <v>452</v>
       </c>
-      <c r="E80" t="s">
+      <c r="J80" t="s">
         <v>453</v>
       </c>
-      <c r="F80" t="s">
+      <c r="K80" t="s">
         <v>454</v>
       </c>
-      <c r="H80" t="s">
+      <c r="L80" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="J80" t="s">
-        <v>456</v>
-      </c>
-      <c r="K80" t="s">
-        <v>457</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>458</v>
       </c>
       <c r="R80" t="s">
         <v>30</v>
       </c>
       <c r="S80" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="T80" s="2">
         <v>44</v>
@@ -5837,28 +5878,28 @@
     </row>
     <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B81" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
       </c>
       <c r="F81" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="J81" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="R81" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="S81" t="s">
         <v>52</v>
@@ -5875,28 +5916,28 @@
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B82" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
       </c>
       <c r="F82" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="J82" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="R82" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="S82" t="s">
         <v>52</v>
@@ -5916,28 +5957,28 @@
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B83" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D83" s="5" t="s">
+        <v>466</v>
+      </c>
+      <c r="E83" t="s">
+        <v>467</v>
+      </c>
+      <c r="F83" t="s">
+        <v>468</v>
+      </c>
+      <c r="J83" t="s">
         <v>469</v>
       </c>
-      <c r="E83" t="s">
+      <c r="L83" s="6" t="s">
         <v>470</v>
       </c>
-      <c r="F83" t="s">
+      <c r="R83" t="s">
         <v>471</v>
-      </c>
-      <c r="J83" t="s">
-        <v>472</v>
-      </c>
-      <c r="L83" s="6" t="s">
-        <v>473</v>
-      </c>
-      <c r="R83" t="s">
-        <v>474</v>
       </c>
       <c r="S83" t="s">
         <v>52</v>
@@ -5954,28 +5995,28 @@
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="B84" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="J84" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="R84" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="S84" t="s">
         <v>52</v>
@@ -5995,19 +6036,19 @@
     </row>
     <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>475</v>
+      </c>
+      <c r="B85" t="s">
+        <v>476</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E85" t="s">
+        <v>228</v>
+      </c>
+      <c r="F85" t="s">
         <v>478</v>
-      </c>
-      <c r="B85" t="s">
-        <v>479</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>480</v>
-      </c>
-      <c r="E85" t="s">
-        <v>230</v>
-      </c>
-      <c r="F85" t="s">
-        <v>481</v>
       </c>
       <c r="J85" t="s">
         <v>48</v>
@@ -6016,13 +6057,13 @@
         <v>49</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="R85" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S85" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T85" s="2">
         <v>180</v>
@@ -6036,34 +6077,34 @@
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B86" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D86" s="5" t="s">
+        <v>480</v>
+      </c>
+      <c r="E86" t="s">
+        <v>481</v>
+      </c>
+      <c r="F86" t="s">
+        <v>482</v>
+      </c>
+      <c r="J86" t="s">
         <v>483</v>
-      </c>
-      <c r="E86" t="s">
-        <v>484</v>
-      </c>
-      <c r="F86" t="s">
-        <v>485</v>
-      </c>
-      <c r="J86" t="s">
-        <v>486</v>
       </c>
       <c r="K86" t="s">
         <v>49</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="R86" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S86" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T86" s="2">
         <v>175</v>
@@ -6080,37 +6121,37 @@
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B87" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D87" s="5" t="s">
+        <v>485</v>
+      </c>
+      <c r="E87" t="s">
+        <v>228</v>
+      </c>
+      <c r="F87" t="s">
+        <v>617</v>
+      </c>
+      <c r="H87" t="s">
+        <v>486</v>
+      </c>
+      <c r="J87" t="s">
+        <v>487</v>
+      </c>
+      <c r="K87" t="s">
         <v>488</v>
       </c>
-      <c r="E87" t="s">
-        <v>230</v>
-      </c>
-      <c r="F87" t="s">
-        <v>620</v>
-      </c>
-      <c r="H87" t="s">
+      <c r="L87" s="4" t="s">
         <v>489</v>
       </c>
-      <c r="J87" t="s">
-        <v>490</v>
-      </c>
-      <c r="K87" t="s">
-        <v>491</v>
-      </c>
-      <c r="L87" s="4" t="s">
-        <v>492</v>
-      </c>
       <c r="R87" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S87" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T87" s="2">
         <v>180</v>
@@ -6127,37 +6168,37 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="B88" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="E88" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F88" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="H88" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="J88" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="K88" t="s">
         <v>49</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="R88" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="S88" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T88" s="2">
         <v>180</v>
@@ -6174,40 +6215,40 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>494</v>
+      </c>
+      <c r="B89" t="s">
+        <v>495</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>496</v>
+      </c>
+      <c r="E89" t="s">
         <v>497</v>
       </c>
-      <c r="B89" t="s">
+      <c r="F89" t="s">
         <v>498</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="J89" t="s">
         <v>499</v>
       </c>
-      <c r="E89" t="s">
+      <c r="K89" t="s">
         <v>500</v>
       </c>
-      <c r="F89" t="s">
+      <c r="L89" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="J89" t="s">
+      <c r="N89" s="1" t="s">
         <v>502</v>
       </c>
-      <c r="K89" t="s">
+      <c r="R89" t="s">
+        <v>215</v>
+      </c>
+      <c r="S89" t="s">
         <v>503</v>
       </c>
-      <c r="L89" s="4" t="s">
+      <c r="T89" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="R89" t="s">
-        <v>217</v>
-      </c>
-      <c r="S89" t="s">
-        <v>506</v>
-      </c>
-      <c r="T89" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="U89" s="2">
         <v>55</v>
@@ -6221,34 +6262,34 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B90" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D90" s="5" t="s">
+        <v>505</v>
+      </c>
+      <c r="E90" t="s">
+        <v>506</v>
+      </c>
+      <c r="F90" t="s">
+        <v>507</v>
+      </c>
+      <c r="J90" t="s">
         <v>508</v>
       </c>
-      <c r="E90" t="s">
+      <c r="K90" t="s">
         <v>509</v>
       </c>
-      <c r="F90" t="s">
+      <c r="L90" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="J90" t="s">
+      <c r="R90" t="s">
+        <v>603</v>
+      </c>
+      <c r="S90" t="s">
         <v>511</v>
-      </c>
-      <c r="K90" t="s">
-        <v>512</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="R90" t="s">
-        <v>606</v>
-      </c>
-      <c r="S90" t="s">
-        <v>514</v>
       </c>
       <c r="T90" s="2">
         <v>1200</v>
@@ -6262,34 +6303,34 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B91" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D91" s="5" t="s">
+        <v>512</v>
+      </c>
+      <c r="E91" t="s">
+        <v>513</v>
+      </c>
+      <c r="F91" t="s">
+        <v>514</v>
+      </c>
+      <c r="J91" t="s">
         <v>515</v>
       </c>
-      <c r="E91" t="s">
+      <c r="K91" t="s">
         <v>516</v>
       </c>
-      <c r="F91" t="s">
+      <c r="L91" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="J91" t="s">
+      <c r="R91" t="s">
+        <v>618</v>
+      </c>
+      <c r="S91" t="s">
         <v>518</v>
-      </c>
-      <c r="K91" t="s">
-        <v>519</v>
-      </c>
-      <c r="L91" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="R91" t="s">
-        <v>621</v>
-      </c>
-      <c r="S91" t="s">
-        <v>521</v>
       </c>
       <c r="T91" s="2">
         <v>150</v>
@@ -6303,31 +6344,31 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B92" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D92" s="5" t="s">
+        <v>519</v>
+      </c>
+      <c r="E92" t="s">
+        <v>520</v>
+      </c>
+      <c r="F92" t="s">
+        <v>521</v>
+      </c>
+      <c r="J92" t="s">
         <v>522</v>
       </c>
-      <c r="E92" t="s">
+      <c r="K92" t="s">
         <v>523</v>
       </c>
-      <c r="F92" t="s">
+      <c r="L92" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="J92" t="s">
-        <v>525</v>
-      </c>
-      <c r="K92" t="s">
-        <v>526</v>
-      </c>
-      <c r="L92" s="4" t="s">
-        <v>527</v>
-      </c>
       <c r="R92" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="S92" t="s">
         <v>52</v>
@@ -6347,34 +6388,34 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="B93" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="D93" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="E93" t="s">
+        <v>526</v>
+      </c>
+      <c r="F93" t="s">
+        <v>527</v>
+      </c>
+      <c r="J93" t="s">
         <v>528</v>
       </c>
-      <c r="E93" t="s">
+      <c r="K93" t="s">
         <v>529</v>
       </c>
-      <c r="F93" t="s">
+      <c r="L93" s="4" t="s">
         <v>530</v>
-      </c>
-      <c r="J93" t="s">
-        <v>531</v>
-      </c>
-      <c r="K93" t="s">
-        <v>532</v>
-      </c>
-      <c r="L93" s="4" t="s">
-        <v>533</v>
       </c>
       <c r="R93" t="s">
         <v>30</v>
       </c>
       <c r="S93" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="T93" s="2">
         <v>38</v>
@@ -6391,31 +6432,31 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>494</v>
+      </c>
+      <c r="B94" t="s">
+        <v>495</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>532</v>
+      </c>
+      <c r="E94" t="s">
         <v>497</v>
       </c>
-      <c r="B94" t="s">
-        <v>498</v>
-      </c>
-      <c r="D94" s="5" t="s">
+      <c r="F94" t="s">
+        <v>533</v>
+      </c>
+      <c r="J94" t="s">
+        <v>534</v>
+      </c>
+      <c r="L94" s="6" t="s">
         <v>535</v>
       </c>
-      <c r="E94" t="s">
-        <v>500</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="R94" t="s">
+        <v>609</v>
+      </c>
+      <c r="S94" t="s">
         <v>536</v>
-      </c>
-      <c r="J94" t="s">
-        <v>537</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>538</v>
-      </c>
-      <c r="R94" t="s">
-        <v>612</v>
-      </c>
-      <c r="S94" t="s">
-        <v>539</v>
       </c>
       <c r="T94" s="2">
         <v>400</v>
@@ -6435,25 +6476,25 @@
         <v>157</v>
       </c>
       <c r="B95" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E95" t="s">
         <v>56</v>
       </c>
       <c r="F95" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="J95" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="K95" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="R95" t="s">
         <v>86</v>
@@ -6476,7 +6517,7 @@
         <v>157</v>
       </c>
       <c r="B96" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D96" s="5">
         <v>1456</v>
@@ -6488,13 +6529,13 @@
         <v>47</v>
       </c>
       <c r="J96" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="K96" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="R96" t="s">
         <v>30</v>
@@ -6520,10 +6561,10 @@
         <v>157</v>
       </c>
       <c r="B97" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E97" t="s">
         <v>56</v>
@@ -6532,13 +6573,13 @@
         <v>57</v>
       </c>
       <c r="J97" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="K97" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="R97" t="s">
         <v>30</v>
@@ -6561,31 +6602,31 @@
         <v>157</v>
       </c>
       <c r="B98" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D98" s="5">
         <v>1470</v>
       </c>
       <c r="E98" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="F98" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J98" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K98" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="R98" t="s">
         <v>51</v>
       </c>
       <c r="S98" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="T98" s="2">
         <v>73</v>
@@ -6599,13 +6640,13 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E99" t="s">
         <v>56</v>
@@ -6614,19 +6655,19 @@
         <v>120</v>
       </c>
       <c r="J99" t="s">
+        <v>550</v>
+      </c>
+      <c r="K99" t="s">
+        <v>551</v>
+      </c>
+      <c r="L99" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="R99" t="s">
+        <v>623</v>
+      </c>
+      <c r="S99" t="s">
         <v>553</v>
-      </c>
-      <c r="K99" t="s">
-        <v>554</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="R99" t="s">
-        <v>626</v>
-      </c>
-      <c r="S99" t="s">
-        <v>556</v>
       </c>
       <c r="T99" s="2">
         <v>715</v>
@@ -6640,34 +6681,34 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B100" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D100" s="5" t="s">
+        <v>554</v>
+      </c>
+      <c r="E100" t="s">
+        <v>292</v>
+      </c>
+      <c r="F100" t="s">
+        <v>555</v>
+      </c>
+      <c r="J100" t="s">
+        <v>556</v>
+      </c>
+      <c r="K100" t="s">
         <v>557</v>
       </c>
-      <c r="E100" t="s">
-        <v>294</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="L100" s="4" t="s">
         <v>558</v>
-      </c>
-      <c r="J100" t="s">
-        <v>559</v>
-      </c>
-      <c r="K100" t="s">
-        <v>560</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>561</v>
       </c>
       <c r="R100" t="s">
         <v>51</v>
       </c>
       <c r="S100" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="T100" s="2">
         <v>250</v>
@@ -6681,13 +6722,13 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B101" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="E101" t="s">
         <v>67</v>
@@ -6696,22 +6737,22 @@
         <v>68</v>
       </c>
       <c r="H101" t="s">
+        <v>561</v>
+      </c>
+      <c r="J101" t="s">
+        <v>562</v>
+      </c>
+      <c r="K101" t="s">
+        <v>563</v>
+      </c>
+      <c r="L101" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="J101" t="s">
+      <c r="N101" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="K101" t="s">
-        <v>566</v>
-      </c>
-      <c r="L101" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>568</v>
-      </c>
       <c r="R101" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="S101" t="s">
         <v>52</v>
@@ -6731,29 +6772,29 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="B102" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="E102" t="s">
         <v>56</v>
       </c>
       <c r="F102" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J102" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="L102" s="6" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="N102" s="1"/>
       <c r="R102" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="S102" t="s">
         <v>52</v>
@@ -6773,31 +6814,31 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>570</v>
+      </c>
+      <c r="B103" t="s">
+        <v>571</v>
+      </c>
+      <c r="D103" s="5" t="s">
+        <v>572</v>
+      </c>
+      <c r="E103" t="s">
         <v>573</v>
       </c>
-      <c r="B103" t="s">
+      <c r="F103" t="s">
         <v>574</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="J103" t="s">
         <v>575</v>
       </c>
-      <c r="E103" t="s">
+      <c r="L103" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="F103" t="s">
+      <c r="R103" t="s">
+        <v>603</v>
+      </c>
+      <c r="S103" t="s">
         <v>577</v>
-      </c>
-      <c r="J103" t="s">
-        <v>578</v>
-      </c>
-      <c r="L103" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="R103" t="s">
-        <v>606</v>
-      </c>
-      <c r="S103" t="s">
-        <v>580</v>
       </c>
       <c r="T103" s="2">
         <v>1300</v>
@@ -6811,34 +6852,34 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>570</v>
+      </c>
+      <c r="B104" t="s">
+        <v>571</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="E104" t="s">
         <v>573</v>
       </c>
-      <c r="B104" t="s">
-        <v>574</v>
-      </c>
-      <c r="D104" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="E104" t="s">
-        <v>576</v>
-      </c>
       <c r="F104" t="s">
+        <v>578</v>
+      </c>
+      <c r="J104" t="s">
+        <v>579</v>
+      </c>
+      <c r="K104" t="s">
+        <v>580</v>
+      </c>
+      <c r="L104" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="J104" t="s">
+      <c r="R104" t="s">
+        <v>622</v>
+      </c>
+      <c r="S104" t="s">
         <v>582</v>
-      </c>
-      <c r="K104" t="s">
-        <v>583</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="R104" t="s">
-        <v>625</v>
-      </c>
-      <c r="S104" t="s">
-        <v>585</v>
       </c>
       <c r="T104" s="2">
         <v>386</v>
@@ -6855,28 +6896,28 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B105" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D105" s="5">
         <v>1495</v>
       </c>
       <c r="E105" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="F105" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J105" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="K105" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="R105" t="s">
         <v>43</v>
@@ -6899,40 +6940,40 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>570</v>
+      </c>
+      <c r="B106" t="s">
+        <v>571</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>586</v>
+      </c>
+      <c r="E106" t="s">
         <v>573</v>
       </c>
-      <c r="B106" t="s">
+      <c r="F106" t="s">
         <v>574</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="J106" t="s">
+        <v>587</v>
+      </c>
+      <c r="K106" t="s">
+        <v>588</v>
+      </c>
+      <c r="L106" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="E106" t="s">
-        <v>576</v>
-      </c>
-      <c r="F106" t="s">
-        <v>577</v>
-      </c>
-      <c r="J106" t="s">
+      <c r="M106" s="1" t="s">
         <v>590</v>
       </c>
-      <c r="K106" t="s">
+      <c r="P106" t="s">
         <v>591</v>
-      </c>
-      <c r="L106" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>593</v>
-      </c>
-      <c r="P106" t="s">
-        <v>594</v>
       </c>
       <c r="R106" t="s">
         <v>30</v>
       </c>
       <c r="S106" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="T106" s="2">
         <v>250</v>
@@ -6943,34 +6984,34 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B107" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D107" s="5" t="s">
+        <v>593</v>
+      </c>
+      <c r="E107" t="s">
+        <v>594</v>
+      </c>
+      <c r="F107" t="s">
+        <v>595</v>
+      </c>
+      <c r="J107" t="s">
+        <v>336</v>
+      </c>
+      <c r="K107" t="s">
         <v>596</v>
       </c>
-      <c r="E107" t="s">
+      <c r="L107" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="F107" t="s">
-        <v>598</v>
-      </c>
-      <c r="J107" t="s">
-        <v>338</v>
-      </c>
-      <c r="K107" t="s">
-        <v>599</v>
-      </c>
-      <c r="L107" s="4" t="s">
-        <v>600</v>
       </c>
       <c r="R107" t="s">
         <v>30</v>
       </c>
       <c r="S107" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="T107" s="2">
         <v>140</v>
@@ -6987,31 +7028,31 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>570</v>
+      </c>
+      <c r="B108" t="s">
+        <v>571</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>525</v>
+      </c>
+      <c r="E108" t="s">
         <v>573</v>
       </c>
-      <c r="B108" t="s">
-        <v>574</v>
-      </c>
-      <c r="D108" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="E108" t="s">
-        <v>576</v>
-      </c>
       <c r="F108" t="s">
+        <v>598</v>
+      </c>
+      <c r="J108" t="s">
+        <v>599</v>
+      </c>
+      <c r="K108" t="s">
+        <v>600</v>
+      </c>
+      <c r="L108" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="J108" t="s">
-        <v>602</v>
-      </c>
-      <c r="K108" t="s">
-        <v>603</v>
-      </c>
-      <c r="L108" s="4" t="s">
-        <v>604</v>
-      </c>
       <c r="R108" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="S108" t="s">
         <v>52</v>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -3637,8 +3637,10 @@
           <t xml:space="preserve">Monument avec ronde-bosse conçue par l'artiste, le socle est dû à Alessandro Leopardi.</t>
         </is>
       </c>
-      <c r="S31" t="s">
-        <v>635</v>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la statue, pierre pour le socle</t>
+        </is>
       </c>
       <c r="T31" s="2" t="s">
         <v>634</v>
@@ -5249,8 +5251,10 @@
       <c r="R67" t="s">
         <v>631</v>
       </c>
-      <c r="S67" t="s">
-        <v>632</v>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bronze pour la ronde-bosse, pierre pour le socle</t>
+        </is>
       </c>
       <c r="T67" s="2" t="s">
         <v>630</v>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -3634,7 +3634,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Monument avec ronde-bosse conçue par l'artiste, le socle est dû à Alessandro Leopardi.</t>
+          <t xml:space="preserve">Monument avec ronde-bosse en bronze conçue par l'artiste, le socle en pierre est dû à Alessandro Leopardi.</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -5248,8 +5248,10 @@
       <c r="L67" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="R67" t="s">
-        <v>631</v>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Monument avec ronde-bosse en bronze et bas-relief, intégralement conçu par l'artiste, sur un socle en pierre.</t>
+        </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63DDC69-8EF1-4FE6-9F54-8E3F1D922509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2095F301-9934-4D5F-826E-920B74936843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="640">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -736,9 +736,6 @@
     <t>Piazza del Campo</t>
   </si>
   <si>
-    <t>Santa Maria della Scala (originaux)</t>
-  </si>
-  <si>
     <t>Fontaine de la Joie</t>
   </si>
   <si>
@@ -1915,19 +1912,34 @@
     <t>340 pour la statue, 800 pour le socle</t>
   </si>
   <si>
-    <t>Monument avec ronde-bosse et bas-relief intégralement conçu par l'artiste.</t>
-  </si>
-  <si>
-    <t>Bronze (ronde-bosse) Pierre (socle)</t>
-  </si>
-  <si>
-    <t>Monument avec ronde-bosse conçue par l'artiste, le socle est dû à Alessando Leopardi.</t>
-  </si>
-  <si>
     <t>395 pour la statue, 400 pour le socle</t>
   </si>
   <si>
-    <t>Bronze (statue) Pierre (socle)</t>
+    <t>Artiste associé</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse en bronze conçue par l'artiste, le socle en pierre est dû à Alessandro Leopardi.</t>
+  </si>
+  <si>
+    <t>Bronze pour la statue, pierre pour le socle</t>
+  </si>
+  <si>
+    <t>Monument avec ronde-bosse en bronze et bas-relief, intégralement conçu par l'artiste, sur un socle en pierre.</t>
+  </si>
+  <si>
+    <t>Bronze pour la ronde-bosse, pierre pour le socle</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG/1280px-Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/3/37/Gattamelata.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/5/50/ItaliaSienaFontanaPiazzaCampo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg/1280px-The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -2315,17 +2327,17 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="23" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="10.42578125" style="5" customWidth="1"/>
-    <col min="7" max="7" width="1.85546875" customWidth="1"/>
-    <col min="8" max="8" width="4.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="17.140625" customWidth="1"/>
     <col min="9" max="9" width="16.140625" customWidth="1"/>
     <col min="10" max="10" width="45.7109375" customWidth="1"/>
     <col min="11" max="11" width="15.140625" customWidth="1"/>
     <col min="12" max="12" width="9.7109375" style="3" customWidth="1"/>
     <col min="13" max="13" width="5.5703125" customWidth="1"/>
-    <col min="14" max="14" width="2.42578125" customWidth="1"/>
+    <col min="14" max="14" width="10.5703125" customWidth="1"/>
     <col min="15" max="15" width="19.7109375" customWidth="1"/>
     <col min="16" max="16" width="20.28515625" customWidth="1"/>
     <col min="17" max="17" width="21.5703125" customWidth="1"/>
@@ -2336,7 +2348,7 @@
     <col min="24" max="24" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2406,13 +2418,11 @@
       <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artiste associé</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="X1" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>23</v>
       </c>
@@ -2420,7 +2430,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
@@ -2456,7 +2466,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -2479,7 +2489,7 @@
         <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="S3" t="s">
         <v>37</v>
@@ -2491,7 +2501,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2532,7 +2542,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -2576,7 +2586,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>53</v>
       </c>
@@ -2593,7 +2603,7 @@
         <v>57</v>
       </c>
       <c r="J6" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="K6" t="s">
         <v>58</v>
@@ -2602,7 +2612,7 @@
         <v>59</v>
       </c>
       <c r="R6" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="S6" t="s">
         <v>44</v>
@@ -2620,7 +2630,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>53</v>
       </c>
@@ -2664,7 +2674,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>53</v>
       </c>
@@ -2705,7 +2715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
@@ -2728,7 +2738,7 @@
         <v>70</v>
       </c>
       <c r="J9" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="L9" s="6" t="s">
         <v>76</v>
@@ -2746,7 +2756,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>78</v>
       </c>
@@ -2787,7 +2797,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>78</v>
       </c>
@@ -2822,7 +2832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>78</v>
       </c>
@@ -2857,7 +2867,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>78</v>
       </c>
@@ -2883,7 +2893,7 @@
         <v>99</v>
       </c>
       <c r="R13" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="S13" t="s">
         <v>52</v>
@@ -2892,7 +2902,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>100</v>
       </c>
@@ -2936,7 +2946,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>100</v>
       </c>
@@ -2980,7 +2990,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>100</v>
       </c>
@@ -3047,7 +3057,7 @@
         <v>116</v>
       </c>
       <c r="R17" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="S17" t="s">
         <v>52</v>
@@ -3082,7 +3092,7 @@
         <v>123</v>
       </c>
       <c r="R18" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="S18" t="s">
         <v>52</v>
@@ -3205,7 +3215,7 @@
         <v>137</v>
       </c>
       <c r="R21" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="S21" t="s">
         <v>52</v>
@@ -3287,7 +3297,7 @@
         <v>149</v>
       </c>
       <c r="R23" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="S23" t="s">
         <v>52</v>
@@ -3328,7 +3338,7 @@
         <v>154</v>
       </c>
       <c r="R24" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="S24" t="s">
         <v>52</v>
@@ -3404,7 +3414,7 @@
         <v>163</v>
       </c>
       <c r="R26" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="S26" t="s">
         <v>31</v>
@@ -3448,7 +3458,7 @@
         <v>169</v>
       </c>
       <c r="R27" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="S27" t="s">
         <v>31</v>
@@ -3518,7 +3528,7 @@
         <v>177</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E29" t="s">
         <v>56</v>
@@ -3632,18 +3642,14 @@
       <c r="L31" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="R31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument avec ronde-bosse en bronze conçue par l'artiste, le socle en pierre est dû à Alessandro Leopardi.</t>
-        </is>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la statue, pierre pour le socle</t>
-        </is>
+      <c r="R31" t="s">
+        <v>632</v>
+      </c>
+      <c r="S31" t="s">
+        <v>633</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="U31" s="2">
         <v>380</v>
@@ -3869,7 +3875,7 @@
         <v>222</v>
       </c>
       <c r="R36" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="S36" t="s">
         <v>52</v>
@@ -3997,20 +4003,23 @@
       <c r="F39" t="s">
         <v>237</v>
       </c>
-      <c r="H39" t="s">
+      <c r="G39" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="J39" t="s">
         <v>238</v>
       </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>239</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="L39" s="4" t="s">
-        <v>241</v>
-      </c>
       <c r="R39" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="S39" t="s">
         <v>52</v>
@@ -4036,7 +4045,7 @@
         <v>234</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E40" t="s">
         <v>81</v>
@@ -4045,16 +4054,16 @@
         <v>82</v>
       </c>
       <c r="J40" t="s">
+        <v>242</v>
+      </c>
+      <c r="K40" t="s">
         <v>243</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="L40" s="4" t="s">
-        <v>245</v>
-      </c>
       <c r="R40" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="S40" t="s">
         <v>52</v>
@@ -4080,31 +4089,31 @@
         <v>234</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E41" t="s">
         <v>212</v>
       </c>
       <c r="F41" t="s">
+        <v>246</v>
+      </c>
+      <c r="H41" t="s">
         <v>247</v>
       </c>
-      <c r="H41" t="s">
+      <c r="J41" t="s">
         <v>248</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>249</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="L41" s="4" t="s">
+      <c r="R41" t="s">
+        <v>615</v>
+      </c>
+      <c r="S41" t="s">
         <v>251</v>
-      </c>
-      <c r="R41" t="s">
-        <v>616</v>
-      </c>
-      <c r="S41" t="s">
-        <v>252</v>
       </c>
       <c r="T41" s="2">
         <v>1800</v>
@@ -4127,34 +4136,34 @@
         <v>234</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E42" t="s">
         <v>212</v>
       </c>
       <c r="F42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H42" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J42" t="s">
+        <v>253</v>
+      </c>
+      <c r="K42" t="s">
         <v>254</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="L42" s="6" t="s">
-        <v>256</v>
-      </c>
       <c r="M42" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R42" t="s">
         <v>51</v>
       </c>
       <c r="S42" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="T42" s="2">
         <v>99</v>
@@ -4177,28 +4186,28 @@
         <v>234</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E43" t="s">
         <v>81</v>
       </c>
       <c r="F43" t="s">
+        <v>257</v>
+      </c>
+      <c r="H43" t="s">
         <v>258</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>259</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>260</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>262</v>
-      </c>
       <c r="R43" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="S43" t="s">
         <v>52</v>
@@ -4221,28 +4230,28 @@
         <v>234</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E44" t="s">
         <v>81</v>
       </c>
       <c r="F44" t="s">
+        <v>257</v>
+      </c>
+      <c r="H44" t="s">
         <v>258</v>
       </c>
-      <c r="H44" t="s">
-        <v>259</v>
-      </c>
       <c r="J44" t="s">
+        <v>262</v>
+      </c>
+      <c r="K44" t="s">
         <v>263</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="R44" t="s">
         <v>265</v>
-      </c>
-      <c r="R44" t="s">
-        <v>266</v>
       </c>
       <c r="S44" t="s">
         <v>52</v>
@@ -4262,28 +4271,28 @@
         <v>176</v>
       </c>
       <c r="B45" t="s">
+        <v>266</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>267</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>268</v>
       </c>
       <c r="E45" t="s">
         <v>56</v>
       </c>
       <c r="F45" t="s">
+        <v>268</v>
+      </c>
+      <c r="J45" t="s">
         <v>269</v>
       </c>
-      <c r="J45" t="s">
+      <c r="L45" s="4" t="s">
         <v>270</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>271</v>
       </c>
       <c r="R45" t="s">
         <v>51</v>
       </c>
       <c r="S45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="T45" s="2">
         <v>100</v>
@@ -4303,31 +4312,31 @@
         <v>176</v>
       </c>
       <c r="B46" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D46" s="5">
         <v>1520</v>
       </c>
       <c r="E46" t="s">
+        <v>272</v>
+      </c>
+      <c r="F46" t="s">
+        <v>606</v>
+      </c>
+      <c r="J46" t="s">
         <v>273</v>
       </c>
-      <c r="F46" t="s">
-        <v>607</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>274</v>
       </c>
-      <c r="K46" t="s">
+      <c r="L46" s="1" t="s">
         <v>275</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>276</v>
       </c>
       <c r="R46" t="s">
         <v>51</v>
       </c>
       <c r="S46" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T46" s="2">
         <v>80</v>
@@ -4347,7 +4356,7 @@
         <v>176</v>
       </c>
       <c r="B47" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>171</v>
@@ -4359,19 +4368,19 @@
         <v>120</v>
       </c>
       <c r="J47" t="s">
+        <v>277</v>
+      </c>
+      <c r="K47" t="s">
         <v>278</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="L47" s="6" t="s">
-        <v>280</v>
-      </c>
       <c r="R47" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="S47" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T47" s="2">
         <v>270</v>
@@ -4391,31 +4400,31 @@
         <v>176</v>
       </c>
       <c r="B48" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D48" s="5">
         <v>1489</v>
       </c>
       <c r="E48" t="s">
+        <v>280</v>
+      </c>
+      <c r="F48" t="s">
         <v>281</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="J48" t="s">
         <v>283</v>
       </c>
-      <c r="J48" t="s">
+      <c r="L48" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>285</v>
       </c>
       <c r="R48" t="s">
         <v>51</v>
       </c>
       <c r="S48" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T48" s="2">
         <v>163</v>
@@ -4435,34 +4444,34 @@
         <v>176</v>
       </c>
       <c r="B49" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D49" s="5">
         <v>1475</v>
       </c>
       <c r="E49" t="s">
+        <v>285</v>
+      </c>
+      <c r="F49" t="s">
         <v>286</v>
       </c>
-      <c r="F49" t="s">
+      <c r="J49" t="s">
         <v>287</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>288</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" s="6" t="s">
         <v>289</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="R49" t="s">
         <v>51</v>
       </c>
       <c r="S49" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U49" s="2">
         <v>210</v>
@@ -4479,31 +4488,31 @@
         <v>176</v>
       </c>
       <c r="B50" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>91</v>
       </c>
       <c r="E50" t="s">
+        <v>291</v>
+      </c>
+      <c r="F50" t="s">
         <v>292</v>
       </c>
-      <c r="F50" t="s">
+      <c r="J50" t="s">
         <v>293</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>294</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>296</v>
-      </c>
       <c r="R50" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="S50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T50" s="2">
         <v>370</v>
@@ -4523,7 +4532,7 @@
         <v>176</v>
       </c>
       <c r="B51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D51" s="5">
         <v>1489</v>
@@ -4532,19 +4541,19 @@
         <v>56</v>
       </c>
       <c r="F51" t="s">
+        <v>296</v>
+      </c>
+      <c r="J51" t="s">
         <v>297</v>
       </c>
-      <c r="J51" t="s">
+      <c r="L51" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>299</v>
       </c>
       <c r="R51" t="s">
         <v>51</v>
       </c>
       <c r="S51" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T51" s="2">
         <v>44</v>
@@ -4564,10 +4573,10 @@
         <v>176</v>
       </c>
       <c r="B52" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E52" t="s">
         <v>38</v>
@@ -4576,17 +4585,17 @@
         <v>39</v>
       </c>
       <c r="J52" t="s">
+        <v>300</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>301</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>302</v>
       </c>
       <c r="P52" s="7"/>
       <c r="R52" s="7" t="s">
         <v>43</v>
       </c>
       <c r="S52" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T52" s="2">
         <v>128</v>
@@ -4600,28 +4609,28 @@
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>302</v>
+      </c>
+      <c r="B53" t="s">
+        <v>266</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>303</v>
-      </c>
-      <c r="B53" t="s">
-        <v>267</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>304</v>
       </c>
       <c r="E53" t="s">
         <v>56</v>
       </c>
       <c r="F53" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J53" t="s">
+        <v>304</v>
+      </c>
+      <c r="K53" t="s">
         <v>305</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" s="4" t="s">
         <v>306</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>307</v>
       </c>
       <c r="R53" t="s">
         <v>36</v>
@@ -4644,34 +4653,34 @@
     </row>
     <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B54" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E54" t="s">
         <v>56</v>
       </c>
       <c r="F54" t="s">
+        <v>309</v>
+      </c>
+      <c r="J54" t="s">
         <v>310</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>311</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="R54" t="s">
         <v>51</v>
       </c>
       <c r="S54" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T54" s="2">
         <v>200</v>
@@ -4688,28 +4697,28 @@
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B55" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E55" t="s">
         <v>56</v>
       </c>
       <c r="F55" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="J55" t="s">
+        <v>314</v>
+      </c>
+      <c r="K55" t="s">
         <v>315</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" s="4" t="s">
         <v>316</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>317</v>
       </c>
       <c r="R55" t="s">
         <v>51</v>
@@ -4732,34 +4741,34 @@
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B56" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E56" t="s">
         <v>56</v>
       </c>
       <c r="F56" t="s">
+        <v>318</v>
+      </c>
+      <c r="J56" t="s">
         <v>319</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>320</v>
       </c>
-      <c r="K56" t="s">
+      <c r="L56" s="4" t="s">
         <v>321</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>322</v>
       </c>
       <c r="R56" t="s">
         <v>51</v>
       </c>
       <c r="S56" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="U56" s="2">
         <v>120</v>
@@ -4773,37 +4782,37 @@
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B57" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="E57" t="s">
         <v>323</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>324</v>
       </c>
-      <c r="F57" t="s">
+      <c r="J57" t="s">
         <v>325</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>326</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="L57" s="4" t="s">
+      <c r="M57" s="1" t="s">
         <v>328</v>
       </c>
-      <c r="M57" s="1" t="s">
-        <v>329</v>
-      </c>
       <c r="R57" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="S57" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T57" s="2">
         <v>150</v>
@@ -4820,34 +4829,34 @@
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B58" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D58" t="s">
+        <v>329</v>
+      </c>
+      <c r="E58" t="s">
         <v>330</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>331</v>
       </c>
-      <c r="F58" t="s">
+      <c r="J58" t="s">
         <v>332</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>333</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="R58" t="s">
         <v>51</v>
       </c>
       <c r="S58" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T58" s="2">
         <v>118</v>
@@ -4864,13 +4873,13 @@
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B59" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D59" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="E59" t="s">
         <v>56</v>
@@ -4879,19 +4888,19 @@
         <v>57</v>
       </c>
       <c r="J59" t="s">
+        <v>335</v>
+      </c>
+      <c r="K59" t="s">
         <v>336</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" s="1" t="s">
         <v>337</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>338</v>
       </c>
       <c r="R59" t="s">
         <v>51</v>
       </c>
       <c r="S59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T59" s="2">
         <v>57</v>
@@ -4902,13 +4911,13 @@
     </row>
     <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B60" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D60" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E60" t="s">
         <v>56</v>
@@ -4917,19 +4926,19 @@
         <v>57</v>
       </c>
       <c r="J60" t="s">
+        <v>338</v>
+      </c>
+      <c r="K60" t="s">
+        <v>336</v>
+      </c>
+      <c r="L60" s="6" t="s">
         <v>339</v>
-      </c>
-      <c r="K60" t="s">
-        <v>337</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>340</v>
       </c>
       <c r="R60" t="s">
         <v>51</v>
       </c>
       <c r="S60" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="T60" s="2">
         <v>70</v>
@@ -4943,13 +4952,13 @@
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>340</v>
+      </c>
+      <c r="B61" t="s">
         <v>341</v>
       </c>
-      <c r="B61" t="s">
+      <c r="D61" s="5" t="s">
         <v>342</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>343</v>
       </c>
       <c r="E61" t="s">
         <v>56</v>
@@ -4958,13 +4967,13 @@
         <v>57</v>
       </c>
       <c r="J61" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K61" t="s">
         <v>178</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="R61" t="s">
         <v>30</v>
@@ -4973,7 +4982,7 @@
         <v>31</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="U61" s="2">
         <v>51</v>
@@ -4987,16 +4996,16 @@
     </row>
     <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>340</v>
+      </c>
+      <c r="B62" t="s">
         <v>341</v>
       </c>
-      <c r="B62" t="s">
-        <v>342</v>
-      </c>
       <c r="C62" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E62" t="s">
         <v>56</v>
@@ -5005,13 +5014,13 @@
         <v>57</v>
       </c>
       <c r="J62" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="K62" t="s">
+        <v>346</v>
+      </c>
+      <c r="L62" s="4" t="s">
         <v>347</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>348</v>
       </c>
       <c r="R62" t="s">
         <v>30</v>
@@ -5020,7 +5029,7 @@
         <v>52</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="U62" s="2">
         <v>57</v>
@@ -5031,16 +5040,16 @@
     </row>
     <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>340</v>
+      </c>
+      <c r="B63" t="s">
         <v>341</v>
       </c>
-      <c r="B63" t="s">
-        <v>342</v>
-      </c>
       <c r="C63" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E63" t="s">
         <v>56</v>
@@ -5049,13 +5058,13 @@
         <v>57</v>
       </c>
       <c r="J63" t="s">
+        <v>350</v>
+      </c>
+      <c r="K63" t="s">
         <v>351</v>
       </c>
-      <c r="K63" t="s">
+      <c r="L63" s="4" t="s">
         <v>352</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>353</v>
       </c>
       <c r="R63" t="s">
         <v>30</v>
@@ -5064,7 +5073,7 @@
         <v>52</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="U63" s="2">
         <v>64</v>
@@ -5078,16 +5087,16 @@
     </row>
     <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>340</v>
+      </c>
+      <c r="B64" t="s">
         <v>341</v>
       </c>
-      <c r="B64" t="s">
-        <v>342</v>
-      </c>
       <c r="C64" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E64" t="s">
         <v>56</v>
@@ -5096,13 +5105,13 @@
         <v>181</v>
       </c>
       <c r="J64" t="s">
+        <v>354</v>
+      </c>
+      <c r="K64" t="s">
         <v>355</v>
       </c>
-      <c r="K64" t="s">
+      <c r="L64" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>357</v>
       </c>
       <c r="R64" t="s">
         <v>30</v>
@@ -5125,37 +5134,38 @@
     </row>
     <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>340</v>
+      </c>
+      <c r="B65" t="s">
         <v>341</v>
       </c>
-      <c r="B65" t="s">
-        <v>342</v>
-      </c>
       <c r="C65" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E65" t="s">
         <v>236</v>
       </c>
       <c r="F65" t="s">
+        <v>358</v>
+      </c>
+      <c r="I65" s="6"/>
+      <c r="J65" t="s">
         <v>359</v>
       </c>
-      <c r="J65" t="s">
+      <c r="K65" t="s">
         <v>360</v>
       </c>
-      <c r="K65" t="s">
+      <c r="L65" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="L65" s="4" t="s">
+      <c r="M65" t="s">
         <v>362</v>
       </c>
-      <c r="M65" t="s">
+      <c r="N65" s="1" t="s">
         <v>363</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>364</v>
       </c>
       <c r="R65" t="s">
         <v>43</v>
@@ -5164,10 +5174,10 @@
         <v>44</v>
       </c>
       <c r="T65" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U65" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="V65" s="2">
         <v>7</v>
@@ -5178,16 +5188,16 @@
     </row>
     <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>340</v>
+      </c>
+      <c r="B66" t="s">
         <v>341</v>
       </c>
-      <c r="B66" t="s">
-        <v>342</v>
-      </c>
       <c r="C66" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E66" t="s">
         <v>56</v>
@@ -5196,19 +5206,19 @@
         <v>120</v>
       </c>
       <c r="J66" t="s">
+        <v>366</v>
+      </c>
+      <c r="K66" t="s">
         <v>367</v>
       </c>
-      <c r="K66" t="s">
+      <c r="L66" s="4" t="s">
         <v>368</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>369</v>
       </c>
       <c r="R66" t="s">
         <v>51</v>
       </c>
       <c r="S66" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="T66" s="2">
         <v>218</v>
@@ -5222,47 +5232,50 @@
     </row>
     <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>340</v>
+      </c>
+      <c r="B67" t="s">
         <v>341</v>
       </c>
-      <c r="B67" t="s">
-        <v>342</v>
-      </c>
       <c r="C67" t="s">
+        <v>628</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E67" t="s">
+        <v>371</v>
+      </c>
+      <c r="F67" t="s">
+        <v>372</v>
+      </c>
+      <c r="G67" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="J67" t="s">
+        <v>373</v>
+      </c>
+      <c r="K67" t="s">
+        <v>374</v>
+      </c>
+      <c r="L67" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="O67" s="6"/>
+      <c r="R67" t="s">
+        <v>634</v>
+      </c>
+      <c r="S67" t="s">
+        <v>635</v>
+      </c>
+      <c r="T67" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="D67" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="E67" t="s">
-        <v>372</v>
-      </c>
-      <c r="F67" t="s">
-        <v>373</v>
-      </c>
-      <c r="J67" t="s">
-        <v>374</v>
-      </c>
-      <c r="K67" t="s">
-        <v>375</v>
-      </c>
-      <c r="L67" s="4" t="s">
+      <c r="U67" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Monument avec ronde-bosse en bronze et bas-relief, intégralement conçu par l'artiste, sur un socle en pierre.</t>
-        </is>
-      </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bronze pour la ronde-bosse, pierre pour le socle</t>
-        </is>
-      </c>
-      <c r="T67" s="2" t="s">
-        <v>630</v>
-      </c>
-      <c r="U67" s="2" t="s">
-        <v>377</v>
       </c>
       <c r="W67" s="2">
         <v>1</v>
@@ -5270,40 +5283,40 @@
     </row>
     <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>340</v>
+      </c>
+      <c r="B68" t="s">
         <v>341</v>
       </c>
-      <c r="B68" t="s">
-        <v>342</v>
-      </c>
       <c r="C68" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E68" t="s">
         <v>56</v>
       </c>
       <c r="F68" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J68" t="s">
+        <v>378</v>
+      </c>
+      <c r="K68" t="s">
         <v>379</v>
       </c>
-      <c r="K68" t="s">
+      <c r="L68" s="4" t="s">
         <v>380</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>381</v>
       </c>
       <c r="R68" t="s">
         <v>30</v>
       </c>
       <c r="S68" t="s">
+        <v>381</v>
+      </c>
+      <c r="T68" s="2" t="s">
         <v>382</v>
-      </c>
-      <c r="T68" s="2" t="s">
-        <v>383</v>
       </c>
       <c r="U68" s="2">
         <v>51</v>
@@ -5317,31 +5330,31 @@
     </row>
     <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>383</v>
+      </c>
+      <c r="B69" t="s">
         <v>384</v>
       </c>
-      <c r="B69" t="s">
+      <c r="D69" s="5" t="s">
         <v>385</v>
-      </c>
-      <c r="D69" s="5" t="s">
-        <v>386</v>
       </c>
       <c r="E69" t="s">
         <v>56</v>
       </c>
       <c r="F69" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J69" t="s">
+        <v>386</v>
+      </c>
+      <c r="K69" t="s">
         <v>387</v>
       </c>
-      <c r="K69" t="s">
+      <c r="L69" s="4" t="s">
         <v>388</v>
       </c>
-      <c r="L69" s="4" t="s">
+      <c r="N69" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>390</v>
       </c>
       <c r="R69" t="s">
         <v>43</v>
@@ -5350,10 +5363,10 @@
         <v>44</v>
       </c>
       <c r="T69" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="U69" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="U69" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="V69" s="2">
         <v>11</v>
@@ -5364,31 +5377,31 @@
     </row>
     <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>383</v>
+      </c>
+      <c r="B70" t="s">
         <v>384</v>
       </c>
-      <c r="B70" t="s">
-        <v>385</v>
-      </c>
       <c r="D70" s="5" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E70" t="s">
         <v>56</v>
       </c>
       <c r="F70" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="J70" t="s">
+        <v>393</v>
+      </c>
+      <c r="K70" t="s">
         <v>394</v>
       </c>
-      <c r="K70" t="s">
+      <c r="L70" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="L70" s="4" t="s">
-        <v>396</v>
-      </c>
       <c r="N70" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="R70" t="s">
         <v>43</v>
@@ -5408,13 +5421,13 @@
     </row>
     <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>383</v>
+      </c>
+      <c r="B71" t="s">
         <v>384</v>
       </c>
-      <c r="B71" t="s">
-        <v>385</v>
-      </c>
       <c r="D71" s="5" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E71" t="s">
         <v>56</v>
@@ -5432,13 +5445,13 @@
         <v>131</v>
       </c>
       <c r="L71" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="M71" t="s">
         <v>399</v>
       </c>
-      <c r="M71" t="s">
+      <c r="N71" s="1" t="s">
         <v>400</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>401</v>
       </c>
       <c r="R71" t="s">
         <v>30</v>
@@ -5447,7 +5460,7 @@
         <v>31</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="W71" s="2">
         <v>1</v>
@@ -5455,13 +5468,13 @@
     </row>
     <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>383</v>
+      </c>
+      <c r="B72" t="s">
         <v>384</v>
       </c>
-      <c r="B72" t="s">
-        <v>385</v>
-      </c>
       <c r="D72" s="5" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="E72" t="s">
         <v>56</v>
@@ -5473,19 +5486,19 @@
         <v>182</v>
       </c>
       <c r="J72" t="s">
+        <v>403</v>
+      </c>
+      <c r="K72" t="s">
         <v>404</v>
       </c>
-      <c r="K72" t="s">
+      <c r="L72" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="L72" s="4" t="s">
+      <c r="M72" t="s">
         <v>406</v>
       </c>
-      <c r="M72" t="s">
+      <c r="N72" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>408</v>
       </c>
       <c r="R72" t="s">
         <v>30</v>
@@ -5494,7 +5507,7 @@
         <v>31</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="U72" s="2">
         <v>100</v>
@@ -5508,13 +5521,13 @@
     </row>
     <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>383</v>
+      </c>
+      <c r="B73" t="s">
         <v>384</v>
       </c>
-      <c r="B73" t="s">
-        <v>385</v>
-      </c>
       <c r="D73" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E73" t="s">
         <v>56</v>
@@ -5526,19 +5539,19 @@
         <v>182</v>
       </c>
       <c r="J73" t="s">
+        <v>409</v>
+      </c>
+      <c r="K73" t="s">
         <v>410</v>
       </c>
-      <c r="K73" t="s">
+      <c r="L73" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="L73" s="4" t="s">
+      <c r="M73" t="s">
         <v>412</v>
       </c>
-      <c r="M73" t="s">
+      <c r="N73" s="1" t="s">
         <v>413</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>414</v>
       </c>
       <c r="R73" t="s">
         <v>30</v>
@@ -5561,43 +5574,43 @@
     </row>
     <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>383</v>
+      </c>
+      <c r="B74" t="s">
         <v>384</v>
       </c>
-      <c r="B74" t="s">
-        <v>385</v>
-      </c>
       <c r="D74" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E74" t="s">
         <v>236</v>
       </c>
       <c r="F74" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G74" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="J74" t="s">
         <v>416</v>
       </c>
-      <c r="J74" t="s">
+      <c r="K74" t="s">
         <v>417</v>
       </c>
-      <c r="K74" t="s">
+      <c r="L74" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="L74" s="4" t="s">
-        <v>419</v>
-      </c>
       <c r="R74" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="S74" t="s">
         <v>44</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U74" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="V74" s="2">
         <v>8</v>
@@ -5608,43 +5621,43 @@
     </row>
     <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
+        <v>383</v>
+      </c>
+      <c r="B75" t="s">
         <v>384</v>
       </c>
-      <c r="B75" t="s">
-        <v>385</v>
-      </c>
       <c r="D75" s="5" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="E75" t="s">
         <v>236</v>
       </c>
       <c r="F75" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J75" t="s">
+        <v>419</v>
+      </c>
+      <c r="K75" t="s">
         <v>420</v>
       </c>
-      <c r="K75" t="s">
+      <c r="L75" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="L75" s="4" t="s">
-        <v>422</v>
-      </c>
       <c r="R75" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="S75" t="s">
         <v>44</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="V75" s="2">
         <v>8</v>
@@ -5655,37 +5668,37 @@
     </row>
     <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
+        <v>383</v>
+      </c>
+      <c r="B76" t="s">
         <v>384</v>
       </c>
-      <c r="B76" t="s">
-        <v>385</v>
-      </c>
       <c r="D76" s="5" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E76" t="s">
         <v>56</v>
       </c>
       <c r="F76" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H76" t="s">
+        <v>423</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>424</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="J76" t="s">
         <v>425</v>
       </c>
-      <c r="J76" t="s">
+      <c r="K76" t="s">
         <v>426</v>
       </c>
-      <c r="K76" t="s">
+      <c r="L76" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="L76" s="4" t="s">
-        <v>428</v>
-      </c>
       <c r="R76" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="S76" t="s">
         <v>31</v>
@@ -5702,31 +5715,31 @@
     </row>
     <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>428</v>
+      </c>
+      <c r="B77" t="s">
         <v>429</v>
       </c>
-      <c r="B77" t="s">
+      <c r="D77" s="5" t="s">
         <v>430</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="E77" t="s">
         <v>431</v>
       </c>
-      <c r="E77" t="s">
+      <c r="F77" t="s">
         <v>432</v>
       </c>
-      <c r="F77" t="s">
+      <c r="H77" t="s">
         <v>433</v>
       </c>
-      <c r="H77" t="s">
+      <c r="J77" t="s">
         <v>434</v>
       </c>
-      <c r="J77" t="s">
+      <c r="K77" t="s">
         <v>435</v>
       </c>
-      <c r="K77" t="s">
+      <c r="L77" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="L77" s="4" t="s">
-        <v>437</v>
       </c>
       <c r="R77" t="s">
         <v>30</v>
@@ -5749,34 +5762,34 @@
     </row>
     <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>428</v>
+      </c>
+      <c r="B78" t="s">
         <v>429</v>
       </c>
-      <c r="B78" t="s">
-        <v>430</v>
-      </c>
       <c r="D78" s="5" t="s">
+        <v>437</v>
+      </c>
+      <c r="E78" t="s">
         <v>438</v>
       </c>
-      <c r="E78" t="s">
+      <c r="F78" t="s">
         <v>439</v>
       </c>
-      <c r="F78" t="s">
+      <c r="H78" t="s">
         <v>440</v>
       </c>
-      <c r="H78" t="s">
+      <c r="J78" t="s">
         <v>441</v>
       </c>
-      <c r="J78" t="s">
+      <c r="K78" t="s">
         <v>442</v>
       </c>
-      <c r="K78" t="s">
+      <c r="L78" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="L78" s="4" t="s">
-        <v>444</v>
-      </c>
       <c r="R78" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="S78" t="s">
         <v>52</v>
@@ -5793,31 +5806,31 @@
     </row>
     <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>428</v>
+      </c>
+      <c r="B79" t="s">
         <v>429</v>
-      </c>
-      <c r="B79" t="s">
-        <v>430</v>
       </c>
       <c r="D79" s="5">
         <v>1475</v>
       </c>
       <c r="E79" t="s">
+        <v>330</v>
+      </c>
+      <c r="F79" t="s">
         <v>331</v>
       </c>
-      <c r="F79" t="s">
-        <v>332</v>
-      </c>
       <c r="H79" t="s">
+        <v>444</v>
+      </c>
+      <c r="J79" t="s">
         <v>445</v>
       </c>
-      <c r="J79" t="s">
+      <c r="K79" t="s">
         <v>446</v>
       </c>
-      <c r="K79" t="s">
+      <c r="L79" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="L79" s="4" t="s">
-        <v>448</v>
       </c>
       <c r="R79" t="s">
         <v>30</v>
@@ -5840,37 +5853,37 @@
     </row>
     <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>428</v>
+      </c>
+      <c r="B80" t="s">
         <v>429</v>
       </c>
-      <c r="B80" t="s">
-        <v>430</v>
-      </c>
       <c r="D80" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="E80" t="s">
         <v>449</v>
       </c>
-      <c r="E80" t="s">
+      <c r="F80" t="s">
         <v>450</v>
       </c>
-      <c r="F80" t="s">
+      <c r="H80" t="s">
         <v>451</v>
       </c>
-      <c r="H80" t="s">
+      <c r="J80" t="s">
         <v>452</v>
       </c>
-      <c r="J80" t="s">
+      <c r="K80" t="s">
         <v>453</v>
       </c>
-      <c r="K80" t="s">
+      <c r="L80" s="4" t="s">
         <v>454</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>455</v>
       </c>
       <c r="R80" t="s">
         <v>30</v>
       </c>
       <c r="S80" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="T80" s="2">
         <v>44</v>
@@ -5884,28 +5897,28 @@
     </row>
     <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>456</v>
+      </c>
+      <c r="B81" t="s">
         <v>457</v>
       </c>
-      <c r="B81" t="s">
+      <c r="D81" s="5" t="s">
         <v>458</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>459</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
       </c>
       <c r="F81" t="s">
+        <v>459</v>
+      </c>
+      <c r="J81" t="s">
         <v>460</v>
       </c>
-      <c r="J81" t="s">
+      <c r="L81" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="L81" s="4" t="s">
-        <v>462</v>
-      </c>
       <c r="R81" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="S81" t="s">
         <v>52</v>
@@ -5922,28 +5935,28 @@
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
+        <v>456</v>
+      </c>
+      <c r="B82" t="s">
         <v>457</v>
       </c>
-      <c r="B82" t="s">
-        <v>458</v>
-      </c>
       <c r="D82" s="5" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
       </c>
       <c r="F82" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="J82" t="s">
+        <v>463</v>
+      </c>
+      <c r="L82" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="L82" s="6" t="s">
-        <v>465</v>
-      </c>
       <c r="R82" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="S82" t="s">
         <v>52</v>
@@ -5963,28 +5976,28 @@
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
+        <v>456</v>
+      </c>
+      <c r="B83" t="s">
         <v>457</v>
       </c>
-      <c r="B83" t="s">
-        <v>458</v>
-      </c>
       <c r="D83" s="5" t="s">
+        <v>465</v>
+      </c>
+      <c r="E83" t="s">
         <v>466</v>
       </c>
-      <c r="E83" t="s">
+      <c r="F83" t="s">
         <v>467</v>
       </c>
-      <c r="F83" t="s">
+      <c r="J83" t="s">
         <v>468</v>
       </c>
-      <c r="J83" t="s">
+      <c r="L83" s="6" t="s">
         <v>469</v>
       </c>
-      <c r="L83" s="6" t="s">
+      <c r="R83" t="s">
         <v>470</v>
-      </c>
-      <c r="R83" t="s">
-        <v>471</v>
       </c>
       <c r="S83" t="s">
         <v>52</v>
@@ -6001,28 +6014,28 @@
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>456</v>
+      </c>
+      <c r="B84" t="s">
         <v>457</v>
       </c>
-      <c r="B84" t="s">
-        <v>458</v>
-      </c>
       <c r="D84" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
       </c>
       <c r="F84" t="s">
+        <v>472</v>
+      </c>
+      <c r="J84" t="s">
+        <v>472</v>
+      </c>
+      <c r="L84" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="J84" t="s">
-        <v>473</v>
-      </c>
-      <c r="L84" s="6" t="s">
-        <v>474</v>
-      </c>
       <c r="R84" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="S84" t="s">
         <v>52</v>
@@ -6042,19 +6055,19 @@
     </row>
     <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>474</v>
+      </c>
+      <c r="B85" t="s">
         <v>475</v>
       </c>
-      <c r="B85" t="s">
+      <c r="D85" s="5" t="s">
         <v>476</v>
-      </c>
-      <c r="D85" s="5" t="s">
-        <v>477</v>
       </c>
       <c r="E85" t="s">
         <v>228</v>
       </c>
       <c r="F85" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="J85" t="s">
         <v>48</v>
@@ -6063,7 +6076,7 @@
         <v>49</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="R85" t="s">
         <v>215</v>
@@ -6083,28 +6096,28 @@
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>474</v>
+      </c>
+      <c r="B86" t="s">
         <v>475</v>
       </c>
-      <c r="B86" t="s">
-        <v>476</v>
-      </c>
       <c r="D86" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="E86" t="s">
         <v>480</v>
       </c>
-      <c r="E86" t="s">
+      <c r="F86" t="s">
         <v>481</v>
       </c>
-      <c r="F86" t="s">
+      <c r="J86" t="s">
         <v>482</v>
-      </c>
-      <c r="J86" t="s">
-        <v>483</v>
       </c>
       <c r="K86" t="s">
         <v>49</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="R86" t="s">
         <v>215</v>
@@ -6127,31 +6140,31 @@
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>474</v>
+      </c>
+      <c r="B87" t="s">
         <v>475</v>
       </c>
-      <c r="B87" t="s">
-        <v>476</v>
-      </c>
       <c r="D87" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E87" t="s">
         <v>228</v>
       </c>
       <c r="F87" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H87" t="s">
+        <v>485</v>
+      </c>
+      <c r="J87" t="s">
         <v>486</v>
       </c>
-      <c r="J87" t="s">
+      <c r="K87" t="s">
         <v>487</v>
       </c>
-      <c r="K87" t="s">
+      <c r="L87" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="L87" s="4" t="s">
-        <v>489</v>
       </c>
       <c r="R87" t="s">
         <v>215</v>
@@ -6174,31 +6187,31 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
+        <v>474</v>
+      </c>
+      <c r="B88" t="s">
         <v>475</v>
       </c>
-      <c r="B88" t="s">
-        <v>476</v>
-      </c>
       <c r="D88" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="E88" t="s">
+        <v>438</v>
+      </c>
+      <c r="F88" t="s">
         <v>490</v>
       </c>
-      <c r="E88" t="s">
-        <v>439</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="H88" t="s">
         <v>491</v>
       </c>
-      <c r="H88" t="s">
-        <v>492</v>
-      </c>
       <c r="J88" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="K88" t="s">
         <v>49</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="R88" t="s">
         <v>215</v>
@@ -6221,40 +6234,40 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>493</v>
+      </c>
+      <c r="B89" t="s">
         <v>494</v>
       </c>
-      <c r="B89" t="s">
+      <c r="D89" s="5" t="s">
         <v>495</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="E89" t="s">
         <v>496</v>
       </c>
-      <c r="E89" t="s">
+      <c r="F89" t="s">
         <v>497</v>
       </c>
-      <c r="F89" t="s">
+      <c r="J89" t="s">
         <v>498</v>
       </c>
-      <c r="J89" t="s">
+      <c r="K89" t="s">
         <v>499</v>
       </c>
-      <c r="K89" t="s">
+      <c r="L89" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="L89" s="4" t="s">
+      <c r="N89" s="1" t="s">
         <v>501</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>502</v>
       </c>
       <c r="R89" t="s">
         <v>215</v>
       </c>
       <c r="S89" t="s">
+        <v>502</v>
+      </c>
+      <c r="T89" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="T89" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="U89" s="2">
         <v>55</v>
@@ -6268,34 +6281,34 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>493</v>
+      </c>
+      <c r="B90" t="s">
         <v>494</v>
       </c>
-      <c r="B90" t="s">
-        <v>495</v>
-      </c>
       <c r="D90" s="5" t="s">
+        <v>504</v>
+      </c>
+      <c r="E90" t="s">
         <v>505</v>
       </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
         <v>506</v>
       </c>
-      <c r="F90" t="s">
+      <c r="J90" t="s">
         <v>507</v>
       </c>
-      <c r="J90" t="s">
+      <c r="K90" t="s">
         <v>508</v>
       </c>
-      <c r="K90" t="s">
+      <c r="L90" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="L90" s="4" t="s">
+      <c r="R90" t="s">
+        <v>602</v>
+      </c>
+      <c r="S90" t="s">
         <v>510</v>
-      </c>
-      <c r="R90" t="s">
-        <v>603</v>
-      </c>
-      <c r="S90" t="s">
-        <v>511</v>
       </c>
       <c r="T90" s="2">
         <v>1200</v>
@@ -6309,34 +6322,34 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
+        <v>493</v>
+      </c>
+      <c r="B91" t="s">
         <v>494</v>
       </c>
-      <c r="B91" t="s">
-        <v>495</v>
-      </c>
       <c r="D91" s="5" t="s">
+        <v>511</v>
+      </c>
+      <c r="E91" t="s">
         <v>512</v>
       </c>
-      <c r="E91" t="s">
+      <c r="F91" t="s">
         <v>513</v>
       </c>
-      <c r="F91" t="s">
+      <c r="J91" t="s">
         <v>514</v>
       </c>
-      <c r="J91" t="s">
+      <c r="K91" t="s">
         <v>515</v>
       </c>
-      <c r="K91" t="s">
+      <c r="L91" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="L91" s="4" t="s">
+      <c r="R91" t="s">
+        <v>617</v>
+      </c>
+      <c r="S91" t="s">
         <v>517</v>
-      </c>
-      <c r="R91" t="s">
-        <v>618</v>
-      </c>
-      <c r="S91" t="s">
-        <v>518</v>
       </c>
       <c r="T91" s="2">
         <v>150</v>
@@ -6350,31 +6363,31 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
+        <v>493</v>
+      </c>
+      <c r="B92" t="s">
         <v>494</v>
       </c>
-      <c r="B92" t="s">
-        <v>495</v>
-      </c>
       <c r="D92" s="5" t="s">
+        <v>518</v>
+      </c>
+      <c r="E92" t="s">
         <v>519</v>
       </c>
-      <c r="E92" t="s">
+      <c r="F92" t="s">
         <v>520</v>
       </c>
-      <c r="F92" t="s">
+      <c r="J92" t="s">
         <v>521</v>
       </c>
-      <c r="J92" t="s">
+      <c r="K92" t="s">
         <v>522</v>
       </c>
-      <c r="K92" t="s">
+      <c r="L92" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="L92" s="4" t="s">
-        <v>524</v>
-      </c>
       <c r="R92" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="S92" t="s">
         <v>52</v>
@@ -6394,34 +6407,34 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>493</v>
+      </c>
+      <c r="B93" t="s">
         <v>494</v>
       </c>
-      <c r="B93" t="s">
-        <v>495</v>
-      </c>
       <c r="D93" s="5" t="s">
+        <v>524</v>
+      </c>
+      <c r="E93" t="s">
         <v>525</v>
       </c>
-      <c r="E93" t="s">
+      <c r="F93" t="s">
         <v>526</v>
       </c>
-      <c r="F93" t="s">
+      <c r="J93" t="s">
         <v>527</v>
       </c>
-      <c r="J93" t="s">
+      <c r="K93" t="s">
         <v>528</v>
       </c>
-      <c r="K93" t="s">
+      <c r="L93" s="4" t="s">
         <v>529</v>
-      </c>
-      <c r="L93" s="4" t="s">
-        <v>530</v>
       </c>
       <c r="R93" t="s">
         <v>30</v>
       </c>
       <c r="S93" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="T93" s="2">
         <v>38</v>
@@ -6438,31 +6451,31 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>493</v>
+      </c>
+      <c r="B94" t="s">
         <v>494</v>
       </c>
-      <c r="B94" t="s">
-        <v>495</v>
-      </c>
       <c r="D94" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="E94" t="s">
+        <v>496</v>
+      </c>
+      <c r="F94" t="s">
         <v>532</v>
       </c>
-      <c r="E94" t="s">
-        <v>497</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="J94" t="s">
         <v>533</v>
       </c>
-      <c r="J94" t="s">
+      <c r="L94" s="6" t="s">
         <v>534</v>
       </c>
-      <c r="L94" s="6" t="s">
+      <c r="R94" t="s">
+        <v>608</v>
+      </c>
+      <c r="S94" t="s">
         <v>535</v>
-      </c>
-      <c r="R94" t="s">
-        <v>609</v>
-      </c>
-      <c r="S94" t="s">
-        <v>536</v>
       </c>
       <c r="T94" s="2">
         <v>400</v>
@@ -6482,25 +6495,25 @@
         <v>157</v>
       </c>
       <c r="B95" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E95" t="s">
         <v>56</v>
       </c>
       <c r="F95" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J95" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="K95" t="s">
+        <v>537</v>
+      </c>
+      <c r="L95" s="4" t="s">
         <v>538</v>
-      </c>
-      <c r="L95" s="4" t="s">
-        <v>539</v>
       </c>
       <c r="R95" t="s">
         <v>86</v>
@@ -6523,7 +6536,7 @@
         <v>157</v>
       </c>
       <c r="B96" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D96" s="5">
         <v>1456</v>
@@ -6535,13 +6548,13 @@
         <v>47</v>
       </c>
       <c r="J96" t="s">
+        <v>539</v>
+      </c>
+      <c r="K96" t="s">
         <v>540</v>
       </c>
-      <c r="K96" t="s">
+      <c r="L96" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>542</v>
       </c>
       <c r="R96" t="s">
         <v>30</v>
@@ -6567,10 +6580,10 @@
         <v>157</v>
       </c>
       <c r="B97" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E97" t="s">
         <v>56</v>
@@ -6579,13 +6592,13 @@
         <v>57</v>
       </c>
       <c r="J97" t="s">
+        <v>542</v>
+      </c>
+      <c r="K97" t="s">
         <v>543</v>
       </c>
-      <c r="K97" t="s">
+      <c r="L97" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="L97" s="4" t="s">
-        <v>545</v>
       </c>
       <c r="R97" t="s">
         <v>30</v>
@@ -6608,25 +6621,25 @@
         <v>157</v>
       </c>
       <c r="B98" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D98" s="5">
         <v>1470</v>
       </c>
       <c r="E98" t="s">
+        <v>545</v>
+      </c>
+      <c r="F98" t="s">
         <v>546</v>
       </c>
-      <c r="F98" t="s">
+      <c r="J98" t="s">
+        <v>335</v>
+      </c>
+      <c r="K98" t="s">
+        <v>336</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="J98" t="s">
-        <v>336</v>
-      </c>
-      <c r="K98" t="s">
-        <v>337</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>548</v>
       </c>
       <c r="R98" t="s">
         <v>51</v>
@@ -6646,13 +6659,13 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B99" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E99" t="s">
         <v>56</v>
@@ -6661,19 +6674,19 @@
         <v>120</v>
       </c>
       <c r="J99" t="s">
+        <v>549</v>
+      </c>
+      <c r="K99" t="s">
         <v>550</v>
       </c>
-      <c r="K99" t="s">
+      <c r="L99" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="L99" s="4" t="s">
+      <c r="R99" t="s">
+        <v>622</v>
+      </c>
+      <c r="S99" t="s">
         <v>552</v>
-      </c>
-      <c r="R99" t="s">
-        <v>623</v>
-      </c>
-      <c r="S99" t="s">
-        <v>553</v>
       </c>
       <c r="T99" s="2">
         <v>715</v>
@@ -6687,34 +6700,34 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B100" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D100" s="5" t="s">
+        <v>553</v>
+      </c>
+      <c r="E100" t="s">
+        <v>291</v>
+      </c>
+      <c r="F100" t="s">
         <v>554</v>
       </c>
-      <c r="E100" t="s">
-        <v>292</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="J100" t="s">
         <v>555</v>
       </c>
-      <c r="J100" t="s">
+      <c r="K100" t="s">
         <v>556</v>
       </c>
-      <c r="K100" t="s">
+      <c r="L100" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>558</v>
       </c>
       <c r="R100" t="s">
         <v>51</v>
       </c>
       <c r="S100" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="T100" s="2">
         <v>250</v>
@@ -6728,13 +6741,13 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B101" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="E101" t="s">
         <v>67</v>
@@ -6743,22 +6756,22 @@
         <v>68</v>
       </c>
       <c r="H101" t="s">
+        <v>560</v>
+      </c>
+      <c r="J101" t="s">
         <v>561</v>
       </c>
-      <c r="J101" t="s">
+      <c r="K101" t="s">
         <v>562</v>
       </c>
-      <c r="K101" t="s">
+      <c r="L101" s="4" t="s">
         <v>563</v>
       </c>
-      <c r="L101" s="4" t="s">
+      <c r="N101" s="1" t="s">
         <v>564</v>
       </c>
-      <c r="N101" s="1" t="s">
-        <v>565</v>
-      </c>
       <c r="R101" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="S101" t="s">
         <v>52</v>
@@ -6778,29 +6791,29 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B102" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E102" t="s">
         <v>56</v>
       </c>
       <c r="F102" t="s">
+        <v>566</v>
+      </c>
+      <c r="J102" t="s">
         <v>567</v>
       </c>
-      <c r="J102" t="s">
+      <c r="L102" s="6" t="s">
         <v>568</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>569</v>
       </c>
       <c r="N102" s="1"/>
       <c r="R102" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="S102" t="s">
         <v>52</v>
@@ -6820,31 +6833,31 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>569</v>
+      </c>
+      <c r="B103" t="s">
         <v>570</v>
       </c>
-      <c r="B103" t="s">
+      <c r="D103" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="E103" t="s">
         <v>572</v>
       </c>
-      <c r="E103" t="s">
+      <c r="F103" t="s">
         <v>573</v>
       </c>
-      <c r="F103" t="s">
+      <c r="J103" t="s">
         <v>574</v>
       </c>
-      <c r="J103" t="s">
+      <c r="L103" s="4" t="s">
         <v>575</v>
       </c>
-      <c r="L103" s="4" t="s">
+      <c r="R103" t="s">
+        <v>602</v>
+      </c>
+      <c r="S103" t="s">
         <v>576</v>
-      </c>
-      <c r="R103" t="s">
-        <v>603</v>
-      </c>
-      <c r="S103" t="s">
-        <v>577</v>
       </c>
       <c r="T103" s="2">
         <v>1300</v>
@@ -6858,34 +6871,34 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>569</v>
+      </c>
+      <c r="B104" t="s">
         <v>570</v>
       </c>
-      <c r="B104" t="s">
-        <v>571</v>
-      </c>
       <c r="D104" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E104" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F104" t="s">
+        <v>577</v>
+      </c>
+      <c r="J104" t="s">
         <v>578</v>
       </c>
-      <c r="J104" t="s">
+      <c r="K104" t="s">
         <v>579</v>
       </c>
-      <c r="K104" t="s">
+      <c r="L104" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="L104" s="4" t="s">
+      <c r="R104" t="s">
+        <v>621</v>
+      </c>
+      <c r="S104" t="s">
         <v>581</v>
-      </c>
-      <c r="R104" t="s">
-        <v>622</v>
-      </c>
-      <c r="S104" t="s">
-        <v>582</v>
       </c>
       <c r="T104" s="2">
         <v>386</v>
@@ -6902,28 +6915,28 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>569</v>
+      </c>
+      <c r="B105" t="s">
         <v>570</v>
-      </c>
-      <c r="B105" t="s">
-        <v>571</v>
       </c>
       <c r="D105" s="5">
         <v>1495</v>
       </c>
       <c r="E105" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F105" t="s">
+        <v>582</v>
+      </c>
+      <c r="J105" t="s">
+        <v>626</v>
+      </c>
+      <c r="K105" t="s">
         <v>583</v>
       </c>
-      <c r="J105" t="s">
-        <v>627</v>
-      </c>
-      <c r="K105" t="s">
+      <c r="L105" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="L105" s="4" t="s">
-        <v>585</v>
       </c>
       <c r="R105" t="s">
         <v>43</v>
@@ -6946,40 +6959,40 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
+        <v>569</v>
+      </c>
+      <c r="B106" t="s">
         <v>570</v>
       </c>
-      <c r="B106" t="s">
-        <v>571</v>
-      </c>
       <c r="D106" s="5" t="s">
+        <v>585</v>
+      </c>
+      <c r="E106" t="s">
+        <v>572</v>
+      </c>
+      <c r="F106" t="s">
+        <v>573</v>
+      </c>
+      <c r="J106" t="s">
         <v>586</v>
       </c>
-      <c r="E106" t="s">
-        <v>573</v>
-      </c>
-      <c r="F106" t="s">
-        <v>574</v>
-      </c>
-      <c r="J106" t="s">
+      <c r="K106" t="s">
         <v>587</v>
       </c>
-      <c r="K106" t="s">
+      <c r="L106" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="L106" s="4" t="s">
+      <c r="M106" s="1" t="s">
         <v>589</v>
       </c>
-      <c r="M106" s="1" t="s">
+      <c r="P106" t="s">
         <v>590</v>
-      </c>
-      <c r="P106" t="s">
-        <v>591</v>
       </c>
       <c r="R106" t="s">
         <v>30</v>
       </c>
       <c r="S106" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="T106" s="2">
         <v>250</v>
@@ -6990,34 +7003,34 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
+        <v>569</v>
+      </c>
+      <c r="B107" t="s">
         <v>570</v>
       </c>
-      <c r="B107" t="s">
-        <v>571</v>
-      </c>
       <c r="D107" s="5" t="s">
+        <v>592</v>
+      </c>
+      <c r="E107" t="s">
         <v>593</v>
       </c>
-      <c r="E107" t="s">
+      <c r="F107" t="s">
         <v>594</v>
       </c>
-      <c r="F107" t="s">
+      <c r="J107" t="s">
+        <v>335</v>
+      </c>
+      <c r="K107" t="s">
         <v>595</v>
       </c>
-      <c r="J107" t="s">
-        <v>336</v>
-      </c>
-      <c r="K107" t="s">
+      <c r="L107" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="L107" s="4" t="s">
-        <v>597</v>
       </c>
       <c r="R107" t="s">
         <v>30</v>
       </c>
       <c r="S107" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="T107" s="2">
         <v>140</v>
@@ -7034,31 +7047,31 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>569</v>
+      </c>
+      <c r="B108" t="s">
         <v>570</v>
       </c>
-      <c r="B108" t="s">
-        <v>571</v>
-      </c>
       <c r="D108" s="5" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="E108" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="F108" t="s">
+        <v>597</v>
+      </c>
+      <c r="J108" t="s">
         <v>598</v>
       </c>
-      <c r="J108" t="s">
+      <c r="K108" t="s">
         <v>599</v>
       </c>
-      <c r="K108" t="s">
+      <c r="L108" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="L108" s="4" t="s">
-        <v>601</v>
-      </c>
       <c r="R108" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="S108" t="s">
         <v>52</v>
@@ -7149,7 +7162,7 @@
     <hyperlink ref="L65" r:id="rId69" xr:uid="{00000000-0004-0000-0000-000044000000}"/>
     <hyperlink ref="N65" r:id="rId70" xr:uid="{00000000-0004-0000-0000-000045000000}"/>
     <hyperlink ref="L66" r:id="rId71" xr:uid="{00000000-0004-0000-0000-000046000000}"/>
-    <hyperlink ref="L67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
+    <hyperlink ref="G67" r:id="rId72" xr:uid="{00000000-0004-0000-0000-000047000000}"/>
     <hyperlink ref="L68" r:id="rId73" xr:uid="{00000000-0004-0000-0000-000048000000}"/>
     <hyperlink ref="L69" r:id="rId74" xr:uid="{00000000-0004-0000-0000-000049000000}"/>
     <hyperlink ref="N69" r:id="rId75" xr:uid="{00000000-0004-0000-0000-00004A000000}"/>
@@ -7204,6 +7217,10 @@
     <hyperlink ref="L106" r:id="rId124" xr:uid="{00000000-0004-0000-0000-00007B000000}"/>
     <hyperlink ref="L107" r:id="rId125" xr:uid="{00000000-0004-0000-0000-00007C000000}"/>
     <hyperlink ref="L108" r:id="rId126" xr:uid="{00000000-0004-0000-0000-00007D000000}"/>
+    <hyperlink ref="L67" r:id="rId127" xr:uid="{C6477186-110A-45E6-9BEB-36C410AD4F0B}"/>
+    <hyperlink ref="I67" r:id="rId128" xr:uid="{FD634D05-0696-42B0-809E-92A37EC03100}"/>
+    <hyperlink ref="I39" r:id="rId129" xr:uid="{0DDD83AD-5616-4DF4-A79E-5D1AA62710E3}"/>
+    <hyperlink ref="G39" r:id="rId130" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg/1280px-The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC88C9D7-D842-4DF2-8D24-D182CC0AB952}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2095F301-9934-4D5F-826E-920B74936843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6F85DF-59EA-4EDC-97DB-CC193A244BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="641">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1940,6 +1940,9 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg/1280px-The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Pistoîa</t>
   </si>
 </sst>
 </file>
@@ -2685,7 +2688,7 @@
         <v>66</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>640</v>
       </c>
       <c r="F8" t="s">
         <v>68</v>
@@ -2726,7 +2729,7 @@
         <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>67</v>
+        <v>640</v>
       </c>
       <c r="F9" t="s">
         <v>68</v>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A6F85DF-59EA-4EDC-97DB-CC193A244BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32D5B14-255E-4720-8379-CEEB8D2F590C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="640">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -130,9 +130,6 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/73/Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg/960px-Chapel_of_Mary_Magdalene_-_Altarpiece_said_the_Virgin_Length.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Mobilier liturgique</t>
-  </si>
-  <si>
     <t>Marbre et stuc</t>
   </si>
   <si>
@@ -679,9 +676,6 @@
     <t>Basilique San Domenico</t>
   </si>
   <si>
-    <t>Arca di San Domenico (Cimaise)</t>
-  </si>
-  <si>
     <t>Dieu le Père bénissant le monde</t>
   </si>
   <si>
@@ -1943,6 +1937,9 @@
   </si>
   <si>
     <t>Pistoîa</t>
+  </si>
+  <si>
+    <t>Mobilier funéraire avec groupe en ronde-bosse et bas-relief. L'artiste a conçu la cimaise de la châsse de Saint Dominique.</t>
   </si>
 </sst>
 </file>
@@ -2422,7 +2419,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2433,7 +2430,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
@@ -2492,10 +2489,10 @@
         <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="S3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="T3" s="2">
         <v>400</v>
@@ -2515,25 +2512,25 @@
         <v>1490</v>
       </c>
       <c r="E4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" t="s">
         <v>38</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>39</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>40</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="R4" t="s">
         <v>42</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>43</v>
-      </c>
-      <c r="S4" t="s">
-        <v>44</v>
       </c>
       <c r="T4" s="2">
         <v>24</v>
@@ -2553,28 +2550,28 @@
         <v>24</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
         <v>45</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>46</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>47</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>48</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="R5" t="s">
         <v>50</v>
       </c>
-      <c r="R5" t="s">
+      <c r="S5" t="s">
         <v>51</v>
-      </c>
-      <c r="S5" t="s">
-        <v>52</v>
       </c>
       <c r="T5" s="2">
         <v>102</v>
@@ -2591,34 +2588,34 @@
     </row>
     <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" t="s">
         <v>53</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" t="s">
         <v>55</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>56</v>
       </c>
-      <c r="F6" t="s">
+      <c r="J6" t="s">
+        <v>601</v>
+      </c>
+      <c r="K6" t="s">
         <v>57</v>
       </c>
-      <c r="J6" t="s">
-        <v>603</v>
-      </c>
-      <c r="K6" t="s">
+      <c r="L6" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="L6" s="6" t="s">
-        <v>59</v>
-      </c>
       <c r="R6" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="S6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T6" s="2">
         <v>41.5</v>
@@ -2635,28 +2632,28 @@
     </row>
     <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" t="s">
         <v>53</v>
       </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
       <c r="D7" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F7" t="s">
         <v>60</v>
       </c>
-      <c r="E7" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="J7" t="s">
         <v>61</v>
       </c>
-      <c r="J7" t="s">
+      <c r="K7" t="s">
         <v>62</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="P7" t="s">
         <v>30</v>
@@ -2665,7 +2662,7 @@
         <v>30</v>
       </c>
       <c r="S7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T7" s="2">
         <v>170</v>
@@ -2679,40 +2676,40 @@
     </row>
     <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" t="s">
         <v>53</v>
       </c>
-      <c r="B8" t="s">
-        <v>54</v>
-      </c>
       <c r="D8" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F8" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" t="s">
         <v>68</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" t="s">
         <v>70</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>71</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="R8" t="s">
+        <v>50</v>
+      </c>
+      <c r="S8" t="s">
         <v>73</v>
-      </c>
-      <c r="R8" t="s">
-        <v>51</v>
-      </c>
-      <c r="S8" t="s">
-        <v>74</v>
       </c>
       <c r="W8" s="2">
         <v>3</v>
@@ -2720,75 +2717,75 @@
     </row>
     <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>52</v>
+      </c>
+      <c r="B9" t="s">
         <v>53</v>
       </c>
-      <c r="B9" t="s">
-        <v>54</v>
-      </c>
       <c r="D9" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" t="s">
+        <v>638</v>
+      </c>
+      <c r="F9" t="s">
+        <v>67</v>
+      </c>
+      <c r="H9" t="s">
+        <v>68</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" t="s">
+        <v>625</v>
+      </c>
+      <c r="L9" s="6" t="s">
         <v>75</v>
-      </c>
-      <c r="E9" t="s">
-        <v>640</v>
-      </c>
-      <c r="F9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="J9" t="s">
-        <v>627</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>76</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
       </c>
       <c r="S9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="T9" s="2">
         <v>40</v>
       </c>
       <c r="W9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" t="s">
         <v>78</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" t="s">
         <v>80</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>81</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
         <v>82</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>83</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="R10" t="s">
         <v>85</v>
       </c>
-      <c r="R10" t="s">
-        <v>86</v>
-      </c>
       <c r="S10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T10" s="2">
         <v>600</v>
@@ -2802,34 +2799,34 @@
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" t="s">
         <v>78</v>
       </c>
-      <c r="B11" t="s">
-        <v>79</v>
-      </c>
       <c r="D11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" t="s">
+        <v>81</v>
+      </c>
+      <c r="J11" t="s">
         <v>87</v>
       </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F11" t="s">
-        <v>82</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>88</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="R11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W11" s="2">
         <v>3</v>
@@ -2837,34 +2834,34 @@
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" t="s">
         <v>78</v>
       </c>
-      <c r="B12" t="s">
-        <v>79</v>
-      </c>
       <c r="D12" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E12" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J12" t="s">
         <v>91</v>
       </c>
-      <c r="E12" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>92</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="R12" t="s">
         <v>94</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>95</v>
-      </c>
-      <c r="S12" t="s">
-        <v>96</v>
       </c>
       <c r="W12" s="2">
         <v>3</v>
@@ -2872,34 +2869,34 @@
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B13" t="s">
         <v>78</v>
       </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="F13" t="s">
         <v>81</v>
       </c>
-      <c r="F13" t="s">
-        <v>82</v>
-      </c>
       <c r="J13" t="s">
+        <v>96</v>
+      </c>
+      <c r="K13" t="s">
         <v>97</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="R13" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="S13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W13" s="2">
         <v>3</v>
@@ -2907,34 +2904,34 @@
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>99</v>
+      </c>
+      <c r="B14" t="s">
         <v>100</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" t="s">
+        <v>56</v>
+      </c>
+      <c r="J14" t="s">
         <v>102</v>
       </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
         <v>103</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>105</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
       </c>
       <c r="S14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T14" s="2">
         <v>55</v>
@@ -2951,34 +2948,34 @@
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" t="s">
         <v>100</v>
-      </c>
-      <c r="B15" t="s">
-        <v>101</v>
       </c>
       <c r="D15" s="5">
         <v>1455</v>
       </c>
       <c r="E15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" t="s">
         <v>56</v>
       </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
       <c r="J15" t="s">
+        <v>105</v>
+      </c>
+      <c r="K15" t="s">
         <v>106</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" s="4" t="s">
         <v>107</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>108</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
       </c>
       <c r="S15" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T15" s="2">
         <v>54</v>
@@ -2995,34 +2992,34 @@
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>99</v>
+      </c>
+      <c r="B16" t="s">
         <v>100</v>
-      </c>
-      <c r="B16" t="s">
-        <v>101</v>
       </c>
       <c r="D16" s="5">
         <v>1461</v>
       </c>
       <c r="E16" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" t="s">
         <v>56</v>
       </c>
-      <c r="F16" t="s">
-        <v>57</v>
-      </c>
       <c r="J16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K16" t="s">
         <v>109</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="4" t="s">
         <v>110</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>111</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
       </c>
       <c r="S16" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T16" s="2">
         <v>37</v>
@@ -3036,34 +3033,34 @@
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>99</v>
+      </c>
+      <c r="B17" t="s">
         <v>100</v>
       </c>
-      <c r="B17" t="s">
-        <v>101</v>
-      </c>
       <c r="D17" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" t="s">
         <v>112</v>
       </c>
-      <c r="E17" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>113</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>114</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="L17" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="R17" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="S17" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="W17" s="2">
         <v>3</v>
@@ -3071,34 +3068,34 @@
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>116</v>
+      </c>
+      <c r="B18" t="s">
         <v>117</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="E18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F18" t="s">
         <v>119</v>
       </c>
-      <c r="E18" t="s">
-        <v>56</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="J18" t="s">
         <v>120</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>121</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="R18" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="S18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T18" s="2">
         <v>254</v>
@@ -3115,34 +3112,34 @@
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>116</v>
+      </c>
+      <c r="B19" t="s">
         <v>117</v>
       </c>
-      <c r="B19" t="s">
-        <v>118</v>
-      </c>
       <c r="D19" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" t="s">
+        <v>56</v>
+      </c>
+      <c r="J19" t="s">
         <v>124</v>
       </c>
-      <c r="E19" t="s">
-        <v>56</v>
-      </c>
-      <c r="F19" t="s">
-        <v>57</v>
-      </c>
-      <c r="J19" t="s">
+      <c r="K19" t="s">
         <v>125</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>127</v>
       </c>
       <c r="R19" t="s">
         <v>30</v>
       </c>
       <c r="S19" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T19" s="2">
         <v>54</v>
@@ -3156,34 +3153,34 @@
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>116</v>
+      </c>
+      <c r="B20" t="s">
         <v>117</v>
       </c>
-      <c r="B20" t="s">
-        <v>118</v>
-      </c>
       <c r="D20" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="E20" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" t="s">
         <v>128</v>
       </c>
-      <c r="E20" t="s">
-        <v>56</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="J20" t="s">
         <v>129</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>130</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>132</v>
       </c>
       <c r="R20" t="s">
         <v>30</v>
       </c>
       <c r="S20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T20" s="2">
         <v>144</v>
@@ -3194,34 +3191,34 @@
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B21" t="s">
         <v>117</v>
       </c>
-      <c r="B21" t="s">
-        <v>118</v>
-      </c>
       <c r="D21" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E21" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" t="s">
         <v>133</v>
       </c>
-      <c r="F21" t="s">
+      <c r="J21" t="s">
         <v>134</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>135</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="R21" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="S21" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T21" s="2">
         <v>370</v>
@@ -3232,34 +3229,34 @@
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" t="s">
         <v>138</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" t="s">
         <v>140</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>141</v>
       </c>
-      <c r="F22" t="s">
+      <c r="J22" t="s">
         <v>142</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>143</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="R22" t="s">
         <v>30</v>
       </c>
       <c r="S22" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T22" s="2">
         <v>53</v>
@@ -3276,34 +3273,34 @@
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
         <v>138</v>
       </c>
-      <c r="B23" t="s">
-        <v>139</v>
-      </c>
       <c r="D23" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="E23" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" t="s">
+        <v>119</v>
+      </c>
+      <c r="J23" t="s">
         <v>146</v>
       </c>
-      <c r="E23" t="s">
-        <v>56</v>
-      </c>
-      <c r="F23" t="s">
-        <v>120</v>
-      </c>
-      <c r="J23" t="s">
+      <c r="K23" t="s">
         <v>147</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>149</v>
-      </c>
       <c r="R23" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="S23" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T23" s="2">
         <v>601</v>
@@ -3317,34 +3314,34 @@
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
         <v>138</v>
       </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
       <c r="D24" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" t="s">
+        <v>55</v>
+      </c>
+      <c r="F24" t="s">
         <v>150</v>
       </c>
-      <c r="E24" t="s">
-        <v>56</v>
-      </c>
-      <c r="F24" t="s">
+      <c r="J24" t="s">
         <v>151</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>152</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>154</v>
-      </c>
       <c r="R24" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="S24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T24" s="2">
         <v>447</v>
@@ -3358,31 +3355,31 @@
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>137</v>
+      </c>
+      <c r="B25" t="s">
         <v>138</v>
-      </c>
-      <c r="B25" t="s">
-        <v>139</v>
       </c>
       <c r="D25" s="5">
         <v>1464</v>
       </c>
       <c r="E25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F25" t="s">
         <v>56</v>
       </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
       <c r="J25" t="s">
+        <v>154</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>156</v>
       </c>
       <c r="R25" s="8" t="s">
         <v>30</v>
       </c>
       <c r="S25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T25" s="2">
         <v>173</v>
@@ -3396,28 +3393,28 @@
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>156</v>
+      </c>
+      <c r="B26" t="s">
         <v>157</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" t="s">
         <v>159</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>160</v>
       </c>
-      <c r="F26" t="s">
+      <c r="J26" t="s">
         <v>161</v>
       </c>
-      <c r="J26" t="s">
+      <c r="L26" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="L26" s="6" t="s">
-        <v>163</v>
-      </c>
       <c r="R26" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="S26" t="s">
         <v>31</v>
@@ -3437,37 +3434,37 @@
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" t="s">
         <v>157</v>
       </c>
-      <c r="B27" t="s">
-        <v>158</v>
-      </c>
       <c r="D27" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="E27" t="s">
         <v>164</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>165</v>
       </c>
-      <c r="F27" t="s">
+      <c r="J27" t="s">
         <v>166</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>167</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>169</v>
-      </c>
       <c r="R27" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="S27" t="s">
         <v>31</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="U27" s="2">
         <v>230</v>
@@ -3481,37 +3478,37 @@
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
         <v>157</v>
       </c>
-      <c r="B28" t="s">
-        <v>158</v>
-      </c>
       <c r="D28" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="J28" t="s">
         <v>171</v>
       </c>
-      <c r="E28" t="s">
-        <v>56</v>
-      </c>
-      <c r="F28" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" t="s">
+      <c r="K28" t="s">
         <v>172</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="L28" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="R28" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="S28" t="s">
         <v>31</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="U28" s="2">
         <v>34</v>
@@ -3525,28 +3522,28 @@
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>175</v>
+      </c>
+      <c r="B29" t="s">
         <v>176</v>
       </c>
-      <c r="B29" t="s">
+      <c r="D29" s="5" t="s">
+        <v>603</v>
+      </c>
+      <c r="E29" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="J29" t="s">
         <v>177</v>
       </c>
-      <c r="D29" s="5" t="s">
-        <v>605</v>
-      </c>
-      <c r="E29" t="s">
-        <v>56</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="J29" t="s">
+      <c r="K29" t="s">
+        <v>177</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>178</v>
-      </c>
-      <c r="K29" t="s">
-        <v>178</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>179</v>
       </c>
       <c r="R29" t="s">
         <v>30</v>
@@ -3569,40 +3566,40 @@
     </row>
     <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>175</v>
+      </c>
+      <c r="B30" t="s">
         <v>176</v>
       </c>
-      <c r="B30" t="s">
-        <v>177</v>
-      </c>
       <c r="D30" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="E30" t="s">
+        <v>55</v>
+      </c>
+      <c r="F30" t="s">
         <v>180</v>
       </c>
-      <c r="E30" t="s">
-        <v>56</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="J30" t="s">
         <v>182</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>183</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="M30" t="s">
         <v>185</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="R30" t="s">
         <v>187</v>
-      </c>
-      <c r="R30" t="s">
-        <v>188</v>
       </c>
       <c r="S30" t="s">
         <v>31</v>
@@ -3622,37 +3619,37 @@
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>175</v>
+      </c>
+      <c r="B31" t="s">
         <v>176</v>
       </c>
-      <c r="B31" t="s">
-        <v>177</v>
-      </c>
       <c r="D31" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
       </c>
       <c r="F31" t="s">
+        <v>189</v>
+      </c>
+      <c r="J31" t="s">
         <v>190</v>
       </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>191</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>193</v>
-      </c>
       <c r="R31" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="S31" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="U31" s="2">
         <v>380</v>
@@ -3666,31 +3663,31 @@
     </row>
     <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" t="s">
         <v>176</v>
       </c>
-      <c r="B32" t="s">
-        <v>177</v>
-      </c>
       <c r="D32" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="E32" t="s">
+        <v>55</v>
+      </c>
+      <c r="F32" t="s">
+        <v>128</v>
+      </c>
+      <c r="J32" t="s">
         <v>194</v>
       </c>
-      <c r="E32" t="s">
-        <v>56</v>
-      </c>
-      <c r="F32" t="s">
-        <v>129</v>
-      </c>
-      <c r="J32" t="s">
+      <c r="K32" t="s">
         <v>195</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="M32" t="s">
         <v>197</v>
-      </c>
-      <c r="M32" t="s">
-        <v>198</v>
       </c>
       <c r="R32" t="s">
         <v>30</v>
@@ -3713,34 +3710,34 @@
     </row>
     <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>175</v>
+      </c>
+      <c r="B33" t="s">
         <v>176</v>
       </c>
-      <c r="B33" t="s">
-        <v>177</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
+        <v>55</v>
+      </c>
+      <c r="F33" t="s">
         <v>56</v>
       </c>
-      <c r="F33" t="s">
-        <v>57</v>
-      </c>
       <c r="J33" t="s">
+        <v>198</v>
+      </c>
+      <c r="K33" t="s">
         <v>199</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="R33" t="s">
         <v>30</v>
       </c>
       <c r="S33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T33" s="2">
         <v>59</v>
@@ -3757,37 +3754,37 @@
     </row>
     <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>175</v>
+      </c>
+      <c r="B34" t="s">
         <v>176</v>
       </c>
-      <c r="B34" t="s">
-        <v>177</v>
-      </c>
       <c r="D34" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F34" t="s">
+        <v>150</v>
+      </c>
+      <c r="H34" t="s">
         <v>202</v>
       </c>
-      <c r="E34" t="s">
-        <v>56</v>
-      </c>
-      <c r="F34" t="s">
-        <v>151</v>
-      </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
         <v>203</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>204</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="R34" t="s">
+        <v>85</v>
+      </c>
+      <c r="S34" t="s">
         <v>206</v>
-      </c>
-      <c r="R34" t="s">
-        <v>86</v>
-      </c>
-      <c r="S34" t="s">
-        <v>207</v>
       </c>
       <c r="T34" s="2">
         <v>540</v>
@@ -3801,37 +3798,37 @@
     </row>
     <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>207</v>
+      </c>
+      <c r="B35" t="s">
         <v>208</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>209</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" t="s">
         <v>211</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>212</v>
       </c>
-      <c r="F35" t="s">
+      <c r="J35" t="s">
+        <v>47</v>
+      </c>
+      <c r="K35" t="s">
+        <v>48</v>
+      </c>
+      <c r="L35" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="J35" t="s">
-        <v>48</v>
-      </c>
-      <c r="K35" t="s">
-        <v>49</v>
-      </c>
-      <c r="L35" s="6" t="s">
+      <c r="R35" t="s">
         <v>214</v>
       </c>
-      <c r="R35" t="s">
+      <c r="S35" t="s">
         <v>215</v>
-      </c>
-      <c r="S35" t="s">
-        <v>216</v>
       </c>
       <c r="T35" s="2">
         <v>165</v>
@@ -3848,40 +3845,37 @@
     </row>
     <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" t="s">
         <v>208</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>209</v>
       </c>
-      <c r="C36" t="s">
-        <v>210</v>
-      </c>
       <c r="D36" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="E36" t="s">
+        <v>211</v>
+      </c>
+      <c r="F36" t="s">
         <v>217</v>
       </c>
-      <c r="E36" t="s">
-        <v>212</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="J36" t="s">
         <v>218</v>
       </c>
-      <c r="H36" t="s">
+      <c r="K36" t="s">
         <v>219</v>
       </c>
-      <c r="J36" t="s">
+      <c r="L36" s="6" t="s">
         <v>220</v>
       </c>
-      <c r="K36" t="s">
-        <v>221</v>
-      </c>
-      <c r="L36" s="6" t="s">
-        <v>222</v>
-      </c>
       <c r="R36" t="s">
-        <v>609</v>
+        <v>639</v>
       </c>
       <c r="S36" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T36" s="2">
         <v>50</v>
@@ -3898,37 +3892,37 @@
     </row>
     <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>207</v>
+      </c>
+      <c r="B37" t="s">
         <v>208</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>209</v>
       </c>
-      <c r="C37" t="s">
-        <v>210</v>
-      </c>
       <c r="D37" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F37" t="s">
+        <v>221</v>
+      </c>
+      <c r="J37" t="s">
+        <v>222</v>
+      </c>
+      <c r="K37" t="s">
         <v>223</v>
       </c>
-      <c r="J37" t="s">
+      <c r="L37" s="6" t="s">
         <v>224</v>
-      </c>
-      <c r="K37" t="s">
-        <v>225</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>226</v>
       </c>
       <c r="R37" t="s">
         <v>30</v>
       </c>
       <c r="S37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T37" s="2">
         <v>55</v>
@@ -3945,37 +3939,37 @@
     </row>
     <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>207</v>
+      </c>
+      <c r="B38" t="s">
         <v>208</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>209</v>
       </c>
-      <c r="C38" t="s">
-        <v>210</v>
-      </c>
       <c r="D38" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="E38" t="s">
+        <v>226</v>
+      </c>
+      <c r="F38" t="s">
         <v>227</v>
       </c>
-      <c r="E38" t="s">
+      <c r="J38" t="s">
         <v>228</v>
       </c>
-      <c r="F38" t="s">
+      <c r="K38" t="s">
         <v>229</v>
       </c>
-      <c r="J38" t="s">
+      <c r="L38" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="K38" t="s">
-        <v>231</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>232</v>
       </c>
       <c r="R38" t="s">
         <v>30</v>
       </c>
       <c r="S38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T38" s="2">
         <v>50</v>
@@ -3992,40 +3986,40 @@
     </row>
     <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>231</v>
+      </c>
+      <c r="B39" t="s">
+        <v>232</v>
+      </c>
+      <c r="D39" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B39" t="s">
+      <c r="E39" t="s">
         <v>234</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="F39" t="s">
         <v>235</v>
       </c>
-      <c r="E39" t="s">
+      <c r="G39" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="J39" t="s">
         <v>236</v>
       </c>
-      <c r="F39" t="s">
+      <c r="K39" t="s">
         <v>237</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>638</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="L39" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="K39" t="s">
-        <v>239</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="R39" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="S39" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T39" s="2">
         <v>210</v>
@@ -4042,34 +4036,34 @@
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B40" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D40" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="E40" t="s">
+        <v>80</v>
+      </c>
+      <c r="F40" t="s">
+        <v>81</v>
+      </c>
+      <c r="J40" t="s">
+        <v>240</v>
+      </c>
+      <c r="K40" t="s">
         <v>241</v>
       </c>
-      <c r="E40" t="s">
-        <v>81</v>
-      </c>
-      <c r="F40" t="s">
-        <v>82</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="L40" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="K40" t="s">
-        <v>243</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>244</v>
-      </c>
       <c r="R40" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="S40" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T40" s="2">
         <v>76</v>
@@ -4086,37 +4080,37 @@
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B41" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D41" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="E41" t="s">
+        <v>211</v>
+      </c>
+      <c r="F41" t="s">
+        <v>244</v>
+      </c>
+      <c r="H41" t="s">
         <v>245</v>
       </c>
-      <c r="E41" t="s">
-        <v>212</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="J41" t="s">
         <v>246</v>
       </c>
-      <c r="H41" t="s">
+      <c r="K41" t="s">
         <v>247</v>
       </c>
-      <c r="J41" t="s">
+      <c r="L41" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="K41" t="s">
+      <c r="R41" t="s">
+        <v>613</v>
+      </c>
+      <c r="S41" t="s">
         <v>249</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="R41" t="s">
-        <v>615</v>
-      </c>
-      <c r="S41" t="s">
-        <v>251</v>
       </c>
       <c r="T41" s="2">
         <v>1800</v>
@@ -4133,40 +4127,40 @@
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B42" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="E42" t="s">
+        <v>211</v>
+      </c>
+      <c r="F42" t="s">
+        <v>244</v>
+      </c>
+      <c r="H42" t="s">
+        <v>247</v>
+      </c>
+      <c r="J42" t="s">
+        <v>251</v>
+      </c>
+      <c r="K42" t="s">
         <v>252</v>
       </c>
-      <c r="E42" t="s">
-        <v>212</v>
-      </c>
-      <c r="F42" t="s">
-        <v>246</v>
-      </c>
-      <c r="H42" t="s">
+      <c r="L42" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="M42" t="s">
+        <v>247</v>
+      </c>
+      <c r="R42" t="s">
+        <v>50</v>
+      </c>
+      <c r="S42" t="s">
         <v>249</v>
-      </c>
-      <c r="J42" t="s">
-        <v>253</v>
-      </c>
-      <c r="K42" t="s">
-        <v>254</v>
-      </c>
-      <c r="L42" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="M42" t="s">
-        <v>249</v>
-      </c>
-      <c r="R42" t="s">
-        <v>51</v>
-      </c>
-      <c r="S42" t="s">
-        <v>251</v>
       </c>
       <c r="T42" s="2">
         <v>99</v>
@@ -4183,37 +4177,37 @@
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B43" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E43" t="s">
+        <v>80</v>
+      </c>
+      <c r="F43" t="s">
+        <v>255</v>
+      </c>
+      <c r="H43" t="s">
         <v>256</v>
       </c>
-      <c r="E43" t="s">
-        <v>81</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="J43" t="s">
         <v>257</v>
       </c>
-      <c r="H43" t="s">
+      <c r="K43" t="s">
         <v>258</v>
       </c>
-      <c r="J43" t="s">
+      <c r="L43" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="K43" t="s">
-        <v>260</v>
-      </c>
-      <c r="L43" s="6" t="s">
-        <v>261</v>
-      </c>
       <c r="R43" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="S43" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T43" s="2">
         <v>439</v>
@@ -4227,37 +4221,37 @@
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B44" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D44" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="E44" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" t="s">
+        <v>255</v>
+      </c>
+      <c r="H44" t="s">
         <v>256</v>
       </c>
-      <c r="E44" t="s">
-        <v>81</v>
-      </c>
-      <c r="F44" t="s">
-        <v>257</v>
-      </c>
-      <c r="H44" t="s">
-        <v>258</v>
-      </c>
       <c r="J44" t="s">
+        <v>260</v>
+      </c>
+      <c r="K44" t="s">
+        <v>261</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="K44" t="s">
+      <c r="R44" t="s">
         <v>263</v>
       </c>
-      <c r="L44" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="R44" t="s">
-        <v>265</v>
-      </c>
       <c r="S44" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T44" s="2">
         <v>244</v>
@@ -4271,31 +4265,31 @@
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B45" t="s">
+        <v>264</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="E45" t="s">
+        <v>55</v>
+      </c>
+      <c r="F45" t="s">
         <v>266</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="J45" t="s">
         <v>267</v>
       </c>
-      <c r="E45" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="L45" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="J45" t="s">
+      <c r="R45" t="s">
+        <v>50</v>
+      </c>
+      <c r="S45" t="s">
         <v>269</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="R45" t="s">
-        <v>51</v>
-      </c>
-      <c r="S45" t="s">
-        <v>271</v>
       </c>
       <c r="T45" s="2">
         <v>100</v>
@@ -4312,34 +4306,34 @@
     </row>
     <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B46" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D46" s="5">
         <v>1520</v>
       </c>
       <c r="E46" t="s">
+        <v>270</v>
+      </c>
+      <c r="F46" t="s">
+        <v>604</v>
+      </c>
+      <c r="J46" t="s">
+        <v>271</v>
+      </c>
+      <c r="K46" t="s">
         <v>272</v>
       </c>
-      <c r="F46" t="s">
-        <v>606</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="L46" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K46" t="s">
+      <c r="R46" t="s">
+        <v>50</v>
+      </c>
+      <c r="S46" t="s">
         <v>274</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>275</v>
-      </c>
-      <c r="R46" t="s">
-        <v>51</v>
-      </c>
-      <c r="S46" t="s">
-        <v>276</v>
       </c>
       <c r="T46" s="2">
         <v>80</v>
@@ -4356,34 +4350,34 @@
     </row>
     <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="E47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
+        <v>275</v>
+      </c>
+      <c r="K47" t="s">
+        <v>276</v>
+      </c>
+      <c r="L47" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="K47" t="s">
-        <v>278</v>
-      </c>
-      <c r="L47" s="6" t="s">
-        <v>279</v>
-      </c>
       <c r="R47" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="S47" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T47" s="2">
         <v>270</v>
@@ -4400,34 +4394,34 @@
     </row>
     <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B48" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D48" s="5">
         <v>1489</v>
       </c>
       <c r="E48" t="s">
+        <v>278</v>
+      </c>
+      <c r="F48" t="s">
+        <v>279</v>
+      </c>
+      <c r="G48" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="F48" t="s">
+      <c r="J48" t="s">
         <v>281</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="J48" t="s">
-        <v>283</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>284</v>
-      </c>
       <c r="R48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S48" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T48" s="2">
         <v>163</v>
@@ -4444,37 +4438,37 @@
     </row>
     <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B49" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D49" s="5">
         <v>1475</v>
       </c>
       <c r="E49" t="s">
+        <v>283</v>
+      </c>
+      <c r="F49" t="s">
+        <v>284</v>
+      </c>
+      <c r="J49" t="s">
         <v>285</v>
       </c>
-      <c r="F49" t="s">
+      <c r="K49" t="s">
         <v>286</v>
       </c>
-      <c r="J49" t="s">
+      <c r="L49" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="K49" t="s">
+      <c r="R49" t="s">
+        <v>50</v>
+      </c>
+      <c r="S49" t="s">
+        <v>274</v>
+      </c>
+      <c r="T49" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>289</v>
-      </c>
-      <c r="R49" t="s">
-        <v>51</v>
-      </c>
-      <c r="S49" t="s">
-        <v>276</v>
-      </c>
-      <c r="T49" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="U49" s="2">
         <v>210</v>
@@ -4488,34 +4482,34 @@
     </row>
     <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E50" t="s">
+        <v>289</v>
+      </c>
+      <c r="F50" t="s">
+        <v>290</v>
+      </c>
+      <c r="J50" t="s">
         <v>291</v>
       </c>
-      <c r="F50" t="s">
+      <c r="K50" t="s">
         <v>292</v>
       </c>
-      <c r="J50" t="s">
+      <c r="L50" s="1" t="s">
         <v>293</v>
       </c>
-      <c r="K50" t="s">
-        <v>294</v>
-      </c>
-      <c r="L50" s="1" t="s">
-        <v>295</v>
-      </c>
       <c r="R50" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="S50" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T50" s="2">
         <v>370</v>
@@ -4532,31 +4526,31 @@
     </row>
     <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B51" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D51" s="5">
         <v>1489</v>
       </c>
       <c r="E51" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F51" t="s">
+        <v>294</v>
+      </c>
+      <c r="J51" t="s">
+        <v>295</v>
+      </c>
+      <c r="L51" s="1" t="s">
         <v>296</v>
       </c>
-      <c r="J51" t="s">
-        <v>297</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>298</v>
-      </c>
       <c r="R51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S51" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T51" s="2">
         <v>44</v>
@@ -4573,32 +4567,32 @@
     </row>
     <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B52" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D52" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="E52" t="s">
+        <v>37</v>
+      </c>
+      <c r="F52" t="s">
+        <v>38</v>
+      </c>
+      <c r="J52" t="s">
+        <v>298</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="E52" t="s">
-        <v>38</v>
-      </c>
-      <c r="F52" t="s">
-        <v>39</v>
-      </c>
-      <c r="J52" t="s">
-        <v>300</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="P52" s="7"/>
       <c r="R52" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S52" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T52" s="2">
         <v>128</v>
@@ -4612,34 +4606,34 @@
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>300</v>
+      </c>
+      <c r="B53" t="s">
+        <v>264</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="E53" t="s">
+        <v>55</v>
+      </c>
+      <c r="F53" t="s">
+        <v>294</v>
+      </c>
+      <c r="J53" t="s">
         <v>302</v>
       </c>
-      <c r="B53" t="s">
-        <v>266</v>
-      </c>
-      <c r="D53" s="5" t="s">
+      <c r="K53" t="s">
         <v>303</v>
       </c>
-      <c r="E53" t="s">
-        <v>56</v>
-      </c>
-      <c r="F53" t="s">
-        <v>296</v>
-      </c>
-      <c r="J53" t="s">
+      <c r="L53" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="K53" t="s">
+      <c r="R53" t="s">
         <v>305</v>
       </c>
-      <c r="L53" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="R53" t="s">
-        <v>36</v>
-      </c>
       <c r="S53" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T53" s="2">
         <v>348</v>
@@ -4656,34 +4650,34 @@
     </row>
     <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B54" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D54" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="E54" t="s">
+        <v>55</v>
+      </c>
+      <c r="F54" t="s">
+        <v>307</v>
+      </c>
+      <c r="J54" t="s">
         <v>308</v>
       </c>
-      <c r="E54" t="s">
-        <v>56</v>
-      </c>
-      <c r="F54" t="s">
+      <c r="K54" t="s">
         <v>309</v>
       </c>
-      <c r="J54" t="s">
+      <c r="L54" s="4" t="s">
         <v>310</v>
       </c>
-      <c r="K54" t="s">
-        <v>311</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>312</v>
-      </c>
       <c r="R54" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S54" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T54" s="2">
         <v>200</v>
@@ -4700,31 +4694,31 @@
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B55" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D55" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="E55" t="s">
+        <v>55</v>
+      </c>
+      <c r="F55" t="s">
+        <v>307</v>
+      </c>
+      <c r="J55" t="s">
+        <v>312</v>
+      </c>
+      <c r="K55" t="s">
         <v>313</v>
       </c>
-      <c r="E55" t="s">
-        <v>56</v>
-      </c>
-      <c r="F55" t="s">
-        <v>309</v>
-      </c>
-      <c r="J55" t="s">
+      <c r="L55" s="4" t="s">
         <v>314</v>
       </c>
-      <c r="K55" t="s">
-        <v>315</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>316</v>
-      </c>
       <c r="R55" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S55" t="s">
         <v>31</v>
@@ -4744,34 +4738,34 @@
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B56" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D56" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E56" t="s">
+        <v>55</v>
+      </c>
+      <c r="F56" t="s">
+        <v>316</v>
+      </c>
+      <c r="J56" t="s">
         <v>317</v>
       </c>
-      <c r="E56" t="s">
-        <v>56</v>
-      </c>
-      <c r="F56" t="s">
+      <c r="K56" t="s">
         <v>318</v>
       </c>
-      <c r="J56" t="s">
+      <c r="L56" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="K56" t="s">
-        <v>320</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>321</v>
-      </c>
       <c r="R56" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S56" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="U56" s="2">
         <v>120</v>
@@ -4785,37 +4779,37 @@
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B57" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E57" t="s">
+        <v>321</v>
+      </c>
+      <c r="F57" t="s">
         <v>322</v>
       </c>
-      <c r="E57" t="s">
+      <c r="J57" t="s">
         <v>323</v>
       </c>
-      <c r="F57" t="s">
+      <c r="K57" t="s">
         <v>324</v>
       </c>
-      <c r="J57" t="s">
+      <c r="L57" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="K57" t="s">
+      <c r="M57" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="L57" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="M57" s="1" t="s">
-        <v>328</v>
-      </c>
       <c r="R57" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="S57" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T57" s="2">
         <v>150</v>
@@ -4832,34 +4826,34 @@
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B58" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D58" t="s">
+        <v>327</v>
+      </c>
+      <c r="E58" t="s">
+        <v>328</v>
+      </c>
+      <c r="F58" t="s">
         <v>329</v>
       </c>
-      <c r="E58" t="s">
+      <c r="J58" t="s">
         <v>330</v>
       </c>
-      <c r="F58" t="s">
+      <c r="K58" t="s">
         <v>331</v>
       </c>
-      <c r="J58" t="s">
+      <c r="L58" s="1" t="s">
         <v>332</v>
       </c>
-      <c r="K58" t="s">
-        <v>333</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>334</v>
-      </c>
       <c r="R58" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S58" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T58" s="2">
         <v>118</v>
@@ -4876,34 +4870,34 @@
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B59" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D59" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E59" t="s">
+        <v>55</v>
+      </c>
+      <c r="F59" t="s">
         <v>56</v>
       </c>
-      <c r="F59" t="s">
-        <v>57</v>
-      </c>
       <c r="J59" t="s">
+        <v>333</v>
+      </c>
+      <c r="K59" t="s">
+        <v>334</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>335</v>
       </c>
-      <c r="K59" t="s">
-        <v>336</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>337</v>
-      </c>
       <c r="R59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S59" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T59" s="2">
         <v>57</v>
@@ -4914,34 +4908,34 @@
     </row>
     <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B60" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D60" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E60" t="s">
+        <v>55</v>
+      </c>
+      <c r="F60" t="s">
         <v>56</v>
       </c>
-      <c r="F60" t="s">
-        <v>57</v>
-      </c>
       <c r="J60" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="K60" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="L60" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="R60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S60" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="T60" s="2">
         <v>70</v>
@@ -4955,28 +4949,31 @@
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>338</v>
+      </c>
+      <c r="B61" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" t="s">
+        <v>626</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B61" t="s">
+      <c r="E61" t="s">
+        <v>55</v>
+      </c>
+      <c r="F61" t="s">
+        <v>56</v>
+      </c>
+      <c r="J61" t="s">
+        <v>622</v>
+      </c>
+      <c r="K61" t="s">
+        <v>177</v>
+      </c>
+      <c r="L61" s="4" t="s">
         <v>341</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="E61" t="s">
-        <v>56</v>
-      </c>
-      <c r="F61" t="s">
-        <v>57</v>
-      </c>
-      <c r="J61" t="s">
-        <v>624</v>
-      </c>
-      <c r="K61" t="s">
-        <v>178</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>343</v>
       </c>
       <c r="R61" t="s">
         <v>30</v>
@@ -4985,7 +4982,7 @@
         <v>31</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="U61" s="2">
         <v>51</v>
@@ -4999,40 +4996,40 @@
     </row>
     <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B62" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C62" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D62" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="E62" t="s">
+        <v>55</v>
+      </c>
+      <c r="F62" t="s">
+        <v>56</v>
+      </c>
+      <c r="J62" t="s">
+        <v>622</v>
+      </c>
+      <c r="K62" t="s">
+        <v>344</v>
+      </c>
+      <c r="L62" s="4" t="s">
         <v>345</v>
-      </c>
-      <c r="E62" t="s">
-        <v>56</v>
-      </c>
-      <c r="F62" t="s">
-        <v>57</v>
-      </c>
-      <c r="J62" t="s">
-        <v>624</v>
-      </c>
-      <c r="K62" t="s">
-        <v>346</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>347</v>
       </c>
       <c r="R62" t="s">
         <v>30</v>
       </c>
       <c r="S62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T62" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="U62" s="2">
         <v>57</v>
@@ -5043,40 +5040,40 @@
     </row>
     <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B63" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C63" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D63" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="E63" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" t="s">
+        <v>56</v>
+      </c>
+      <c r="J63" t="s">
+        <v>348</v>
+      </c>
+      <c r="K63" t="s">
         <v>349</v>
       </c>
-      <c r="E63" t="s">
-        <v>56</v>
-      </c>
-      <c r="F63" t="s">
-        <v>57</v>
-      </c>
-      <c r="J63" t="s">
+      <c r="L63" s="4" t="s">
         <v>350</v>
-      </c>
-      <c r="K63" t="s">
-        <v>351</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>352</v>
       </c>
       <c r="R63" t="s">
         <v>30</v>
       </c>
       <c r="S63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T63" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="U63" s="2">
         <v>64</v>
@@ -5090,37 +5087,37 @@
     </row>
     <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B64" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C64" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E64" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F64" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J64" t="s">
+        <v>352</v>
+      </c>
+      <c r="K64" t="s">
+        <v>353</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>354</v>
-      </c>
-      <c r="K64" t="s">
-        <v>355</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>356</v>
       </c>
       <c r="R64" t="s">
         <v>30</v>
       </c>
       <c r="S64" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T64" s="2">
         <v>248</v>
@@ -5137,50 +5134,50 @@
     </row>
     <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B65" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C65" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="E65" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F65" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="I65" s="6"/>
       <c r="J65" t="s">
+        <v>357</v>
+      </c>
+      <c r="K65" t="s">
+        <v>358</v>
+      </c>
+      <c r="L65" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="K65" t="s">
+      <c r="M65" t="s">
         <v>360</v>
       </c>
-      <c r="L65" s="4" t="s">
+      <c r="N65" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="M65" t="s">
+      <c r="R65" t="s">
+        <v>42</v>
+      </c>
+      <c r="S65" t="s">
+        <v>43</v>
+      </c>
+      <c r="T65" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="N65" s="1" t="s">
-        <v>363</v>
-      </c>
-      <c r="R65" t="s">
-        <v>43</v>
-      </c>
-      <c r="S65" t="s">
-        <v>44</v>
-      </c>
-      <c r="T65" s="2" t="s">
-        <v>364</v>
-      </c>
       <c r="U65" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="V65" s="2">
         <v>7</v>
@@ -5191,37 +5188,37 @@
     </row>
     <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B66" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C66" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D66" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="E66" t="s">
+        <v>55</v>
+      </c>
+      <c r="F66" t="s">
+        <v>119</v>
+      </c>
+      <c r="J66" t="s">
+        <v>364</v>
+      </c>
+      <c r="K66" t="s">
         <v>365</v>
       </c>
-      <c r="E66" t="s">
-        <v>56</v>
-      </c>
-      <c r="F66" t="s">
-        <v>120</v>
-      </c>
-      <c r="J66" t="s">
+      <c r="L66" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="K66" t="s">
+      <c r="R66" t="s">
+        <v>50</v>
+      </c>
+      <c r="S66" t="s">
         <v>367</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>368</v>
-      </c>
-      <c r="R66" t="s">
-        <v>51</v>
-      </c>
-      <c r="S66" t="s">
-        <v>369</v>
       </c>
       <c r="T66" s="2">
         <v>218</v>
@@ -5235,50 +5232,50 @@
     </row>
     <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B67" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C67" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D67" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="E67" t="s">
+        <v>369</v>
+      </c>
+      <c r="F67" t="s">
         <v>370</v>
       </c>
-      <c r="E67" t="s">
+      <c r="G67" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="I67" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="J67" t="s">
         <v>371</v>
       </c>
-      <c r="F67" t="s">
+      <c r="K67" t="s">
         <v>372</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>375</v>
-      </c>
-      <c r="I67" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="J67" t="s">
-        <v>373</v>
-      </c>
-      <c r="K67" t="s">
-        <v>374</v>
-      </c>
       <c r="L67" s="6" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="O67" s="6"/>
       <c r="R67" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="S67" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="T67" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="U67" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="W67" s="2">
         <v>1</v>
@@ -5286,40 +5283,40 @@
     </row>
     <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B68" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C68" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D68" s="5" t="s">
+        <v>375</v>
+      </c>
+      <c r="E68" t="s">
+        <v>55</v>
+      </c>
+      <c r="F68" t="s">
+        <v>294</v>
+      </c>
+      <c r="J68" t="s">
+        <v>376</v>
+      </c>
+      <c r="K68" t="s">
         <v>377</v>
       </c>
-      <c r="E68" t="s">
-        <v>56</v>
-      </c>
-      <c r="F68" t="s">
-        <v>296</v>
-      </c>
-      <c r="J68" t="s">
+      <c r="L68" s="4" t="s">
         <v>378</v>
-      </c>
-      <c r="K68" t="s">
-        <v>379</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>380</v>
       </c>
       <c r="R68" t="s">
         <v>30</v>
       </c>
       <c r="S68" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="T68" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="U68" s="2">
         <v>51</v>
@@ -5333,43 +5330,43 @@
     </row>
     <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>381</v>
+      </c>
+      <c r="B69" t="s">
+        <v>382</v>
+      </c>
+      <c r="D69" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B69" t="s">
+      <c r="E69" t="s">
+        <v>55</v>
+      </c>
+      <c r="F69" t="s">
+        <v>294</v>
+      </c>
+      <c r="J69" t="s">
         <v>384</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="K69" t="s">
         <v>385</v>
       </c>
-      <c r="E69" t="s">
-        <v>56</v>
-      </c>
-      <c r="F69" t="s">
-        <v>296</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="L69" s="4" t="s">
         <v>386</v>
       </c>
-      <c r="K69" t="s">
+      <c r="N69" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="L69" s="4" t="s">
+      <c r="R69" t="s">
+        <v>42</v>
+      </c>
+      <c r="S69" t="s">
+        <v>43</v>
+      </c>
+      <c r="T69" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="N69" s="1" t="s">
+      <c r="U69" s="2" t="s">
         <v>389</v>
-      </c>
-      <c r="R69" t="s">
-        <v>43</v>
-      </c>
-      <c r="S69" t="s">
-        <v>44</v>
-      </c>
-      <c r="T69" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="U69" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="V69" s="2">
         <v>11</v>
@@ -5380,34 +5377,34 @@
     </row>
     <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B70" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D70" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E70" t="s">
+        <v>55</v>
+      </c>
+      <c r="F70" t="s">
+        <v>294</v>
+      </c>
+      <c r="J70" t="s">
+        <v>391</v>
+      </c>
+      <c r="K70" t="s">
         <v>392</v>
       </c>
-      <c r="E70" t="s">
-        <v>56</v>
-      </c>
-      <c r="F70" t="s">
-        <v>296</v>
-      </c>
-      <c r="J70" t="s">
+      <c r="L70" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="K70" t="s">
-        <v>394</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>395</v>
-      </c>
       <c r="N70" s="1" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="R70" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S70" t="s">
         <v>31</v>
@@ -5424,37 +5421,37 @@
     </row>
     <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B71" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D71" s="5" t="s">
+        <v>395</v>
+      </c>
+      <c r="E71" t="s">
+        <v>55</v>
+      </c>
+      <c r="F71" t="s">
+        <v>180</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J71" t="s">
+        <v>129</v>
+      </c>
+      <c r="K71" t="s">
+        <v>130</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="M71" t="s">
         <v>397</v>
       </c>
-      <c r="E71" t="s">
-        <v>56</v>
-      </c>
-      <c r="F71" t="s">
-        <v>181</v>
-      </c>
-      <c r="G71" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J71" t="s">
-        <v>130</v>
-      </c>
-      <c r="K71" t="s">
-        <v>131</v>
-      </c>
-      <c r="L71" s="4" t="s">
+      <c r="N71" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="M71" t="s">
-        <v>399</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="R71" t="s">
         <v>30</v>
@@ -5463,7 +5460,7 @@
         <v>31</v>
       </c>
       <c r="T71" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="W71" s="2">
         <v>1</v>
@@ -5471,37 +5468,37 @@
     </row>
     <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B72" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D72" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E72" t="s">
+        <v>55</v>
+      </c>
+      <c r="F72" t="s">
+        <v>180</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J72" t="s">
+        <v>401</v>
+      </c>
+      <c r="K72" t="s">
         <v>402</v>
       </c>
-      <c r="E72" t="s">
-        <v>56</v>
-      </c>
-      <c r="F72" t="s">
-        <v>181</v>
-      </c>
-      <c r="G72" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J72" t="s">
+      <c r="L72" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="K72" t="s">
+      <c r="M72" t="s">
         <v>404</v>
       </c>
-      <c r="L72" s="4" t="s">
+      <c r="N72" s="1" t="s">
         <v>405</v>
-      </c>
-      <c r="M72" t="s">
-        <v>406</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>407</v>
       </c>
       <c r="R72" t="s">
         <v>30</v>
@@ -5510,7 +5507,7 @@
         <v>31</v>
       </c>
       <c r="T72" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="U72" s="2">
         <v>100</v>
@@ -5524,37 +5521,37 @@
     </row>
     <row r="73" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B73" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D73" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E73" t="s">
+        <v>55</v>
+      </c>
+      <c r="F73" t="s">
+        <v>180</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="J73" t="s">
+        <v>407</v>
+      </c>
+      <c r="K73" t="s">
         <v>408</v>
       </c>
-      <c r="E73" t="s">
-        <v>56</v>
-      </c>
-      <c r="F73" t="s">
-        <v>181</v>
-      </c>
-      <c r="G73" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="J73" t="s">
+      <c r="L73" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="K73" t="s">
+      <c r="M73" t="s">
         <v>410</v>
       </c>
-      <c r="L73" s="4" t="s">
+      <c r="N73" s="1" t="s">
         <v>411</v>
-      </c>
-      <c r="M73" t="s">
-        <v>412</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>413</v>
       </c>
       <c r="R73" t="s">
         <v>30</v>
@@ -5577,43 +5574,43 @@
     </row>
     <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B74" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D74" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E74" t="s">
+        <v>234</v>
+      </c>
+      <c r="F74" t="s">
+        <v>356</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="J74" t="s">
         <v>414</v>
       </c>
-      <c r="E74" t="s">
-        <v>236</v>
-      </c>
-      <c r="F74" t="s">
-        <v>358</v>
-      </c>
-      <c r="G74" s="1" t="s">
+      <c r="K74" t="s">
         <v>415</v>
       </c>
-      <c r="J74" t="s">
+      <c r="L74" s="4" t="s">
         <v>416</v>
       </c>
-      <c r="K74" t="s">
-        <v>417</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>418</v>
-      </c>
       <c r="R74" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="S74" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T74" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U74" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="V74" s="2">
         <v>8</v>
@@ -5624,43 +5621,43 @@
     </row>
     <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B75" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E75" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="F75" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="J75" t="s">
+        <v>417</v>
+      </c>
+      <c r="K75" t="s">
+        <v>418</v>
+      </c>
+      <c r="L75" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="K75" t="s">
-        <v>420</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="R75" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="S75" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="T75" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="U75" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="V75" s="2">
         <v>8</v>
@@ -5671,37 +5668,37 @@
     </row>
     <row r="76" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B76" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D76" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E76" t="s">
+        <v>55</v>
+      </c>
+      <c r="F76" t="s">
+        <v>307</v>
+      </c>
+      <c r="H76" t="s">
+        <v>421</v>
+      </c>
+      <c r="I76" s="1" t="s">
         <v>422</v>
       </c>
-      <c r="E76" t="s">
-        <v>56</v>
-      </c>
-      <c r="F76" t="s">
-        <v>309</v>
-      </c>
-      <c r="H76" t="s">
+      <c r="J76" t="s">
         <v>423</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="K76" t="s">
         <v>424</v>
       </c>
-      <c r="J76" t="s">
+      <c r="L76" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="K76" t="s">
-        <v>426</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>427</v>
-      </c>
       <c r="R76" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="S76" t="s">
         <v>31</v>
@@ -5718,37 +5715,37 @@
     </row>
     <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>426</v>
+      </c>
+      <c r="B77" t="s">
+        <v>427</v>
+      </c>
+      <c r="D77" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="B77" t="s">
+      <c r="E77" t="s">
         <v>429</v>
       </c>
-      <c r="D77" s="5" t="s">
+      <c r="F77" t="s">
         <v>430</v>
       </c>
-      <c r="E77" t="s">
+      <c r="H77" t="s">
         <v>431</v>
       </c>
-      <c r="F77" t="s">
+      <c r="J77" t="s">
         <v>432</v>
       </c>
-      <c r="H77" t="s">
+      <c r="K77" t="s">
         <v>433</v>
       </c>
-      <c r="J77" t="s">
+      <c r="L77" s="4" t="s">
         <v>434</v>
-      </c>
-      <c r="K77" t="s">
-        <v>435</v>
-      </c>
-      <c r="L77" s="4" t="s">
-        <v>436</v>
       </c>
       <c r="R77" t="s">
         <v>30</v>
       </c>
       <c r="S77" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T77" s="2">
         <v>50</v>
@@ -5765,37 +5762,37 @@
     </row>
     <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B78" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D78" s="5" t="s">
+        <v>435</v>
+      </c>
+      <c r="E78" t="s">
+        <v>436</v>
+      </c>
+      <c r="F78" t="s">
         <v>437</v>
       </c>
-      <c r="E78" t="s">
+      <c r="H78" t="s">
         <v>438</v>
       </c>
-      <c r="F78" t="s">
+      <c r="J78" t="s">
         <v>439</v>
       </c>
-      <c r="H78" t="s">
+      <c r="K78" t="s">
         <v>440</v>
       </c>
-      <c r="J78" t="s">
+      <c r="L78" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="K78" t="s">
-        <v>442</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>443</v>
-      </c>
       <c r="R78" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="S78" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T78" s="2">
         <v>3500</v>
@@ -5809,37 +5806,37 @@
     </row>
     <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B79" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D79" s="5">
         <v>1475</v>
       </c>
       <c r="E79" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="F79" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="H79" t="s">
+        <v>442</v>
+      </c>
+      <c r="J79" t="s">
+        <v>443</v>
+      </c>
+      <c r="K79" t="s">
         <v>444</v>
       </c>
-      <c r="J79" t="s">
+      <c r="L79" s="4" t="s">
         <v>445</v>
-      </c>
-      <c r="K79" t="s">
-        <v>446</v>
-      </c>
-      <c r="L79" s="4" t="s">
-        <v>447</v>
       </c>
       <c r="R79" t="s">
         <v>30</v>
       </c>
       <c r="S79" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T79" s="2">
         <v>44</v>
@@ -5856,37 +5853,37 @@
     </row>
     <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B80" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D80" s="5" t="s">
+        <v>446</v>
+      </c>
+      <c r="E80" t="s">
+        <v>447</v>
+      </c>
+      <c r="F80" t="s">
         <v>448</v>
       </c>
-      <c r="E80" t="s">
+      <c r="H80" t="s">
         <v>449</v>
       </c>
-      <c r="F80" t="s">
+      <c r="J80" t="s">
         <v>450</v>
       </c>
-      <c r="H80" t="s">
+      <c r="K80" t="s">
         <v>451</v>
       </c>
-      <c r="J80" t="s">
+      <c r="L80" s="4" t="s">
         <v>452</v>
-      </c>
-      <c r="K80" t="s">
-        <v>453</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>454</v>
       </c>
       <c r="R80" t="s">
         <v>30</v>
       </c>
       <c r="S80" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="T80" s="2">
         <v>44</v>
@@ -5900,31 +5897,31 @@
     </row>
     <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>454</v>
+      </c>
+      <c r="B81" t="s">
+        <v>455</v>
+      </c>
+      <c r="D81" s="5" t="s">
         <v>456</v>
-      </c>
-      <c r="B81" t="s">
-        <v>457</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>458</v>
       </c>
       <c r="E81" t="s">
         <v>25</v>
       </c>
       <c r="F81" t="s">
+        <v>457</v>
+      </c>
+      <c r="J81" t="s">
+        <v>458</v>
+      </c>
+      <c r="L81" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="J81" t="s">
-        <v>460</v>
-      </c>
-      <c r="L81" s="4" t="s">
-        <v>461</v>
-      </c>
       <c r="R81" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="S81" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T81" s="2">
         <v>1200</v>
@@ -5938,31 +5935,31 @@
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B82" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="E82" t="s">
         <v>25</v>
       </c>
       <c r="F82" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J82" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="L82" s="6" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="R82" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="S82" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T82" s="2">
         <v>500</v>
@@ -5979,31 +5976,31 @@
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B83" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D83" s="5" t="s">
+        <v>463</v>
+      </c>
+      <c r="E83" t="s">
+        <v>464</v>
+      </c>
+      <c r="F83" t="s">
         <v>465</v>
       </c>
-      <c r="E83" t="s">
+      <c r="J83" t="s">
         <v>466</v>
       </c>
-      <c r="F83" t="s">
+      <c r="L83" s="6" t="s">
         <v>467</v>
       </c>
-      <c r="J83" t="s">
+      <c r="R83" t="s">
         <v>468</v>
       </c>
-      <c r="L83" s="6" t="s">
-        <v>469</v>
-      </c>
-      <c r="R83" t="s">
-        <v>470</v>
-      </c>
       <c r="S83" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T83" s="2">
         <v>65</v>
@@ -6017,31 +6014,31 @@
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B84" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E84" t="s">
         <v>25</v>
       </c>
       <c r="F84" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="J84" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="L84" s="6" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="R84" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="S84" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T84" s="2">
         <v>1400</v>
@@ -6058,34 +6055,34 @@
     </row>
     <row r="85" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>472</v>
+      </c>
+      <c r="B85" t="s">
+        <v>473</v>
+      </c>
+      <c r="D85" s="5" t="s">
         <v>474</v>
       </c>
-      <c r="B85" t="s">
+      <c r="E85" t="s">
+        <v>226</v>
+      </c>
+      <c r="F85" t="s">
         <v>475</v>
       </c>
-      <c r="D85" s="5" t="s">
+      <c r="J85" t="s">
+        <v>47</v>
+      </c>
+      <c r="K85" t="s">
+        <v>48</v>
+      </c>
+      <c r="L85" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="E85" t="s">
-        <v>228</v>
-      </c>
-      <c r="F85" t="s">
-        <v>477</v>
-      </c>
-      <c r="J85" t="s">
-        <v>48</v>
-      </c>
-      <c r="K85" t="s">
-        <v>49</v>
-      </c>
-      <c r="L85" s="4" t="s">
-        <v>478</v>
-      </c>
       <c r="R85" t="s">
+        <v>214</v>
+      </c>
+      <c r="S85" t="s">
         <v>215</v>
-      </c>
-      <c r="S85" t="s">
-        <v>216</v>
       </c>
       <c r="T85" s="2">
         <v>180</v>
@@ -6099,34 +6096,34 @@
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B86" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D86" s="5" t="s">
+        <v>477</v>
+      </c>
+      <c r="E86" t="s">
+        <v>478</v>
+      </c>
+      <c r="F86" t="s">
         <v>479</v>
       </c>
-      <c r="E86" t="s">
+      <c r="J86" t="s">
         <v>480</v>
       </c>
-      <c r="F86" t="s">
+      <c r="K86" t="s">
+        <v>48</v>
+      </c>
+      <c r="L86" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="J86" t="s">
-        <v>482</v>
-      </c>
-      <c r="K86" t="s">
-        <v>49</v>
-      </c>
-      <c r="L86" s="4" t="s">
-        <v>483</v>
-      </c>
       <c r="R86" t="s">
+        <v>214</v>
+      </c>
+      <c r="S86" t="s">
         <v>215</v>
-      </c>
-      <c r="S86" t="s">
-        <v>216</v>
       </c>
       <c r="T86" s="2">
         <v>175</v>
@@ -6143,37 +6140,37 @@
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B87" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D87" s="5" t="s">
+        <v>482</v>
+      </c>
+      <c r="E87" t="s">
+        <v>226</v>
+      </c>
+      <c r="F87" t="s">
+        <v>614</v>
+      </c>
+      <c r="H87" t="s">
+        <v>483</v>
+      </c>
+      <c r="J87" t="s">
         <v>484</v>
       </c>
-      <c r="E87" t="s">
-        <v>228</v>
-      </c>
-      <c r="F87" t="s">
-        <v>616</v>
-      </c>
-      <c r="H87" t="s">
+      <c r="K87" t="s">
         <v>485</v>
       </c>
-      <c r="J87" t="s">
+      <c r="L87" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="K87" t="s">
-        <v>487</v>
-      </c>
-      <c r="L87" s="4" t="s">
-        <v>488</v>
-      </c>
       <c r="R87" t="s">
+        <v>214</v>
+      </c>
+      <c r="S87" t="s">
         <v>215</v>
-      </c>
-      <c r="S87" t="s">
-        <v>216</v>
       </c>
       <c r="T87" s="2">
         <v>180</v>
@@ -6190,37 +6187,37 @@
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B88" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D88" s="5" t="s">
+        <v>487</v>
+      </c>
+      <c r="E88" t="s">
+        <v>436</v>
+      </c>
+      <c r="F88" t="s">
+        <v>488</v>
+      </c>
+      <c r="H88" t="s">
         <v>489</v>
       </c>
-      <c r="E88" t="s">
-        <v>438</v>
-      </c>
-      <c r="F88" t="s">
+      <c r="J88" t="s">
+        <v>480</v>
+      </c>
+      <c r="K88" t="s">
+        <v>48</v>
+      </c>
+      <c r="L88" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="H88" t="s">
-        <v>491</v>
-      </c>
-      <c r="J88" t="s">
-        <v>482</v>
-      </c>
-      <c r="K88" t="s">
-        <v>49</v>
-      </c>
-      <c r="L88" s="4" t="s">
-        <v>492</v>
-      </c>
       <c r="R88" t="s">
+        <v>214</v>
+      </c>
+      <c r="S88" t="s">
         <v>215</v>
-      </c>
-      <c r="S88" t="s">
-        <v>216</v>
       </c>
       <c r="T88" s="2">
         <v>180</v>
@@ -6237,40 +6234,40 @@
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>491</v>
+      </c>
+      <c r="B89" t="s">
+        <v>492</v>
+      </c>
+      <c r="D89" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="B89" t="s">
+      <c r="E89" t="s">
         <v>494</v>
       </c>
-      <c r="D89" s="5" t="s">
+      <c r="F89" t="s">
         <v>495</v>
       </c>
-      <c r="E89" t="s">
+      <c r="J89" t="s">
         <v>496</v>
       </c>
-      <c r="F89" t="s">
+      <c r="K89" t="s">
         <v>497</v>
       </c>
-      <c r="J89" t="s">
+      <c r="L89" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="K89" t="s">
+      <c r="N89" s="1" t="s">
         <v>499</v>
       </c>
-      <c r="L89" s="4" t="s">
+      <c r="R89" t="s">
+        <v>214</v>
+      </c>
+      <c r="S89" t="s">
         <v>500</v>
       </c>
-      <c r="N89" s="1" t="s">
+      <c r="T89" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="R89" t="s">
-        <v>215</v>
-      </c>
-      <c r="S89" t="s">
-        <v>502</v>
-      </c>
-      <c r="T89" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="U89" s="2">
         <v>55</v>
@@ -6284,34 +6281,34 @@
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B90" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D90" s="5" t="s">
+        <v>502</v>
+      </c>
+      <c r="E90" t="s">
+        <v>503</v>
+      </c>
+      <c r="F90" t="s">
         <v>504</v>
       </c>
-      <c r="E90" t="s">
+      <c r="J90" t="s">
         <v>505</v>
       </c>
-      <c r="F90" t="s">
+      <c r="K90" t="s">
         <v>506</v>
       </c>
-      <c r="J90" t="s">
+      <c r="L90" s="4" t="s">
         <v>507</v>
       </c>
-      <c r="K90" t="s">
+      <c r="R90" t="s">
+        <v>600</v>
+      </c>
+      <c r="S90" t="s">
         <v>508</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>509</v>
-      </c>
-      <c r="R90" t="s">
-        <v>602</v>
-      </c>
-      <c r="S90" t="s">
-        <v>510</v>
       </c>
       <c r="T90" s="2">
         <v>1200</v>
@@ -6325,34 +6322,34 @@
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D91" s="5" t="s">
+        <v>509</v>
+      </c>
+      <c r="E91" t="s">
+        <v>510</v>
+      </c>
+      <c r="F91" t="s">
         <v>511</v>
       </c>
-      <c r="E91" t="s">
+      <c r="J91" t="s">
         <v>512</v>
       </c>
-      <c r="F91" t="s">
+      <c r="K91" t="s">
         <v>513</v>
       </c>
-      <c r="J91" t="s">
+      <c r="L91" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="K91" t="s">
+      <c r="R91" t="s">
+        <v>615</v>
+      </c>
+      <c r="S91" t="s">
         <v>515</v>
-      </c>
-      <c r="L91" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="R91" t="s">
-        <v>617</v>
-      </c>
-      <c r="S91" t="s">
-        <v>517</v>
       </c>
       <c r="T91" s="2">
         <v>150</v>
@@ -6366,34 +6363,34 @@
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B92" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D92" s="5" t="s">
+        <v>516</v>
+      </c>
+      <c r="E92" t="s">
+        <v>517</v>
+      </c>
+      <c r="F92" t="s">
         <v>518</v>
       </c>
-      <c r="E92" t="s">
+      <c r="J92" t="s">
         <v>519</v>
       </c>
-      <c r="F92" t="s">
+      <c r="K92" t="s">
         <v>520</v>
       </c>
-      <c r="J92" t="s">
+      <c r="L92" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="K92" t="s">
-        <v>522</v>
-      </c>
-      <c r="L92" s="4" t="s">
-        <v>523</v>
-      </c>
       <c r="R92" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="S92" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T92" s="2">
         <v>170</v>
@@ -6410,34 +6407,34 @@
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B93" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D93" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="E93" t="s">
+        <v>523</v>
+      </c>
+      <c r="F93" t="s">
         <v>524</v>
       </c>
-      <c r="E93" t="s">
+      <c r="J93" t="s">
         <v>525</v>
       </c>
-      <c r="F93" t="s">
+      <c r="K93" t="s">
         <v>526</v>
       </c>
-      <c r="J93" t="s">
+      <c r="L93" s="4" t="s">
         <v>527</v>
-      </c>
-      <c r="K93" t="s">
-        <v>528</v>
-      </c>
-      <c r="L93" s="4" t="s">
-        <v>529</v>
       </c>
       <c r="R93" t="s">
         <v>30</v>
       </c>
       <c r="S93" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="T93" s="2">
         <v>38</v>
@@ -6454,31 +6451,31 @@
     </row>
     <row r="94" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B94" t="s">
+        <v>492</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>529</v>
+      </c>
+      <c r="E94" t="s">
         <v>494</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="F94" t="s">
+        <v>530</v>
+      </c>
+      <c r="J94" t="s">
         <v>531</v>
       </c>
-      <c r="E94" t="s">
-        <v>496</v>
-      </c>
-      <c r="F94" t="s">
+      <c r="L94" s="6" t="s">
         <v>532</v>
       </c>
-      <c r="J94" t="s">
+      <c r="R94" t="s">
+        <v>606</v>
+      </c>
+      <c r="S94" t="s">
         <v>533</v>
-      </c>
-      <c r="L94" s="6" t="s">
-        <v>534</v>
-      </c>
-      <c r="R94" t="s">
-        <v>608</v>
-      </c>
-      <c r="S94" t="s">
-        <v>535</v>
       </c>
       <c r="T94" s="2">
         <v>400</v>
@@ -6495,34 +6492,34 @@
     </row>
     <row r="95" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B95" t="s">
+        <v>534</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="E95" t="s">
+        <v>55</v>
+      </c>
+      <c r="F95" t="s">
+        <v>316</v>
+      </c>
+      <c r="J95" t="s">
+        <v>623</v>
+      </c>
+      <c r="K95" t="s">
+        <v>535</v>
+      </c>
+      <c r="L95" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="D95" s="5" t="s">
-        <v>317</v>
-      </c>
-      <c r="E95" t="s">
-        <v>56</v>
-      </c>
-      <c r="F95" t="s">
-        <v>318</v>
-      </c>
-      <c r="J95" t="s">
-        <v>625</v>
-      </c>
-      <c r="K95" t="s">
-        <v>537</v>
-      </c>
-      <c r="L95" s="4" t="s">
-        <v>538</v>
-      </c>
       <c r="R95" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S95" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T95" s="2">
         <v>400</v>
@@ -6536,34 +6533,34 @@
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B96" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D96" s="5">
         <v>1456</v>
       </c>
       <c r="E96" t="s">
+        <v>45</v>
+      </c>
+      <c r="F96" t="s">
         <v>46</v>
       </c>
-      <c r="F96" t="s">
-        <v>47</v>
-      </c>
       <c r="J96" t="s">
+        <v>537</v>
+      </c>
+      <c r="K96" t="s">
+        <v>538</v>
+      </c>
+      <c r="L96" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="K96" t="s">
-        <v>540</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>541</v>
       </c>
       <c r="R96" t="s">
         <v>30</v>
       </c>
       <c r="S96" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T96" s="2">
         <v>58</v>
@@ -6580,34 +6577,34 @@
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B97" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E97" t="s">
+        <v>55</v>
+      </c>
+      <c r="F97" t="s">
         <v>56</v>
       </c>
-      <c r="F97" t="s">
-        <v>57</v>
-      </c>
       <c r="J97" t="s">
+        <v>540</v>
+      </c>
+      <c r="K97" t="s">
+        <v>541</v>
+      </c>
+      <c r="L97" s="4" t="s">
         <v>542</v>
-      </c>
-      <c r="K97" t="s">
-        <v>543</v>
-      </c>
-      <c r="L97" s="4" t="s">
-        <v>544</v>
       </c>
       <c r="R97" t="s">
         <v>30</v>
       </c>
       <c r="S97" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T97" s="2">
         <v>53</v>
@@ -6621,34 +6618,34 @@
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B98" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D98" s="5">
         <v>1470</v>
       </c>
       <c r="E98" t="s">
+        <v>543</v>
+      </c>
+      <c r="F98" t="s">
+        <v>544</v>
+      </c>
+      <c r="J98" t="s">
+        <v>333</v>
+      </c>
+      <c r="K98" t="s">
+        <v>334</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="F98" t="s">
-        <v>546</v>
-      </c>
-      <c r="J98" t="s">
-        <v>335</v>
-      </c>
-      <c r="K98" t="s">
-        <v>336</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>547</v>
-      </c>
       <c r="R98" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S98" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="T98" s="2">
         <v>73</v>
@@ -6662,34 +6659,34 @@
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>546</v>
+      </c>
+      <c r="B99" t="s">
+        <v>534</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>320</v>
+      </c>
+      <c r="E99" t="s">
+        <v>55</v>
+      </c>
+      <c r="F99" t="s">
+        <v>119</v>
+      </c>
+      <c r="J99" t="s">
+        <v>547</v>
+      </c>
+      <c r="K99" t="s">
         <v>548</v>
       </c>
-      <c r="B99" t="s">
-        <v>536</v>
-      </c>
-      <c r="D99" s="5" t="s">
-        <v>322</v>
-      </c>
-      <c r="E99" t="s">
-        <v>56</v>
-      </c>
-      <c r="F99" t="s">
-        <v>120</v>
-      </c>
-      <c r="J99" t="s">
+      <c r="L99" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="K99" t="s">
+      <c r="R99" t="s">
+        <v>620</v>
+      </c>
+      <c r="S99" t="s">
         <v>550</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>551</v>
-      </c>
-      <c r="R99" t="s">
-        <v>622</v>
-      </c>
-      <c r="S99" t="s">
-        <v>552</v>
       </c>
       <c r="T99" s="2">
         <v>715</v>
@@ -6703,34 +6700,34 @@
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B100" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D100" s="5" t="s">
+        <v>551</v>
+      </c>
+      <c r="E100" t="s">
+        <v>289</v>
+      </c>
+      <c r="F100" t="s">
+        <v>552</v>
+      </c>
+      <c r="J100" t="s">
         <v>553</v>
       </c>
-      <c r="E100" t="s">
-        <v>291</v>
-      </c>
-      <c r="F100" t="s">
+      <c r="K100" t="s">
         <v>554</v>
       </c>
-      <c r="J100" t="s">
+      <c r="L100" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="K100" t="s">
+      <c r="R100" t="s">
+        <v>50</v>
+      </c>
+      <c r="S100" t="s">
         <v>556</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>557</v>
-      </c>
-      <c r="R100" t="s">
-        <v>51</v>
-      </c>
-      <c r="S100" t="s">
-        <v>558</v>
       </c>
       <c r="T100" s="2">
         <v>250</v>
@@ -6744,40 +6741,40 @@
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B101" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D101" s="5" t="s">
+        <v>557</v>
+      </c>
+      <c r="E101" t="s">
+        <v>66</v>
+      </c>
+      <c r="F101" t="s">
+        <v>67</v>
+      </c>
+      <c r="H101" t="s">
+        <v>558</v>
+      </c>
+      <c r="J101" t="s">
         <v>559</v>
       </c>
-      <c r="E101" t="s">
-        <v>67</v>
-      </c>
-      <c r="F101" t="s">
-        <v>68</v>
-      </c>
-      <c r="H101" t="s">
+      <c r="K101" t="s">
         <v>560</v>
       </c>
-      <c r="J101" t="s">
+      <c r="L101" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="K101" t="s">
+      <c r="N101" s="1" t="s">
         <v>562</v>
       </c>
-      <c r="L101" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="R101" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="S101" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T101" s="2">
         <v>466</v>
@@ -6794,32 +6791,32 @@
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="B102" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D102" s="5" t="s">
+        <v>563</v>
+      </c>
+      <c r="E102" t="s">
+        <v>55</v>
+      </c>
+      <c r="F102" t="s">
+        <v>564</v>
+      </c>
+      <c r="J102" t="s">
         <v>565</v>
       </c>
-      <c r="E102" t="s">
-        <v>56</v>
-      </c>
-      <c r="F102" t="s">
+      <c r="L102" s="6" t="s">
         <v>566</v>
-      </c>
-      <c r="J102" t="s">
-        <v>567</v>
-      </c>
-      <c r="L102" s="6" t="s">
-        <v>568</v>
       </c>
       <c r="N102" s="1"/>
       <c r="R102" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="S102" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T102" s="2">
         <v>120</v>
@@ -6836,31 +6833,31 @@
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>567</v>
+      </c>
+      <c r="B103" t="s">
+        <v>568</v>
+      </c>
+      <c r="D103" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="B103" t="s">
+      <c r="E103" t="s">
         <v>570</v>
       </c>
-      <c r="D103" s="5" t="s">
+      <c r="F103" t="s">
         <v>571</v>
       </c>
-      <c r="E103" t="s">
+      <c r="J103" t="s">
         <v>572</v>
       </c>
-      <c r="F103" t="s">
+      <c r="L103" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="J103" t="s">
+      <c r="R103" t="s">
+        <v>600</v>
+      </c>
+      <c r="S103" t="s">
         <v>574</v>
-      </c>
-      <c r="L103" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="R103" t="s">
-        <v>602</v>
-      </c>
-      <c r="S103" t="s">
-        <v>576</v>
       </c>
       <c r="T103" s="2">
         <v>1300</v>
@@ -6874,34 +6871,34 @@
     </row>
     <row r="104" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B104" t="s">
+        <v>568</v>
+      </c>
+      <c r="D104" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="E104" t="s">
         <v>570</v>
       </c>
-      <c r="D104" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="E104" t="s">
-        <v>572</v>
-      </c>
       <c r="F104" t="s">
+        <v>575</v>
+      </c>
+      <c r="J104" t="s">
+        <v>576</v>
+      </c>
+      <c r="K104" t="s">
         <v>577</v>
       </c>
-      <c r="J104" t="s">
+      <c r="L104" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="K104" t="s">
+      <c r="R104" t="s">
+        <v>619</v>
+      </c>
+      <c r="S104" t="s">
         <v>579</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="R104" t="s">
-        <v>621</v>
-      </c>
-      <c r="S104" t="s">
-        <v>581</v>
       </c>
       <c r="T104" s="2">
         <v>386</v>
@@ -6918,31 +6915,31 @@
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B105" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D105" s="5">
         <v>1495</v>
       </c>
       <c r="E105" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F105" t="s">
+        <v>580</v>
+      </c>
+      <c r="J105" t="s">
+        <v>624</v>
+      </c>
+      <c r="K105" t="s">
+        <v>581</v>
+      </c>
+      <c r="L105" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="J105" t="s">
-        <v>626</v>
-      </c>
-      <c r="K105" t="s">
-        <v>583</v>
-      </c>
-      <c r="L105" s="4" t="s">
-        <v>584</v>
-      </c>
       <c r="R105" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="S105" t="s">
         <v>31</v>
@@ -6962,40 +6959,40 @@
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B106" t="s">
+        <v>568</v>
+      </c>
+      <c r="D106" s="5" t="s">
+        <v>583</v>
+      </c>
+      <c r="E106" t="s">
         <v>570</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="F106" t="s">
+        <v>571</v>
+      </c>
+      <c r="J106" t="s">
+        <v>584</v>
+      </c>
+      <c r="K106" t="s">
         <v>585</v>
       </c>
-      <c r="E106" t="s">
-        <v>572</v>
-      </c>
-      <c r="F106" t="s">
-        <v>573</v>
-      </c>
-      <c r="J106" t="s">
+      <c r="L106" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="K106" t="s">
+      <c r="M106" s="1" t="s">
         <v>587</v>
       </c>
-      <c r="L106" s="4" t="s">
+      <c r="P106" t="s">
         <v>588</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>589</v>
-      </c>
-      <c r="P106" t="s">
-        <v>590</v>
       </c>
       <c r="R106" t="s">
         <v>30</v>
       </c>
       <c r="S106" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="T106" s="2">
         <v>250</v>
@@ -7006,34 +7003,34 @@
     </row>
     <row r="107" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B107" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D107" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="E107" t="s">
+        <v>591</v>
+      </c>
+      <c r="F107" t="s">
         <v>592</v>
       </c>
-      <c r="E107" t="s">
+      <c r="J107" t="s">
+        <v>333</v>
+      </c>
+      <c r="K107" t="s">
         <v>593</v>
       </c>
-      <c r="F107" t="s">
+      <c r="L107" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="J107" t="s">
-        <v>335</v>
-      </c>
-      <c r="K107" t="s">
-        <v>595</v>
-      </c>
-      <c r="L107" s="4" t="s">
-        <v>596</v>
       </c>
       <c r="R107" t="s">
         <v>30</v>
       </c>
       <c r="S107" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="T107" s="2">
         <v>140</v>
@@ -7050,34 +7047,34 @@
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B108" t="s">
+        <v>568</v>
+      </c>
+      <c r="D108" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="E108" t="s">
         <v>570</v>
       </c>
-      <c r="D108" s="5" t="s">
-        <v>524</v>
-      </c>
-      <c r="E108" t="s">
-        <v>572</v>
-      </c>
       <c r="F108" t="s">
+        <v>595</v>
+      </c>
+      <c r="J108" t="s">
+        <v>596</v>
+      </c>
+      <c r="K108" t="s">
         <v>597</v>
       </c>
-      <c r="J108" t="s">
+      <c r="L108" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="K108" t="s">
-        <v>599</v>
-      </c>
-      <c r="L108" s="4" t="s">
-        <v>600</v>
-      </c>
       <c r="R108" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="S108" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="T108" s="2">
         <v>112</v>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32D5B14-255E-4720-8379-CEEB8D2F590C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6316400E-BE00-4371-8CE7-033A2B3A1889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="642">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -1936,10 +1936,16 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg/1280px-The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
-    <t>Pistoîa</t>
-  </si>
-  <si>
     <t>Mobilier funéraire avec groupe en ronde-bosse et bas-relief. L'artiste a conçu la cimaise de la châsse de Saint Dominique.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Venice_%2850444397307%29.jpg/1280px-Venice_%2850444397307%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg/1280px-Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>Pistoïa</t>
   </si>
 </sst>
 </file>
@@ -2685,7 +2691,7 @@
         <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
@@ -2726,7 +2732,7 @@
         <v>74</v>
       </c>
       <c r="E9" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
@@ -3633,6 +3639,12 @@
       <c r="F31" t="s">
         <v>189</v>
       </c>
+      <c r="G31" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>639</v>
+      </c>
       <c r="J31" t="s">
         <v>190</v>
       </c>
@@ -3872,7 +3884,7 @@
         <v>220</v>
       </c>
       <c r="R36" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="S36" t="s">
         <v>51</v>
@@ -7221,6 +7233,8 @@
     <hyperlink ref="I67" r:id="rId128" xr:uid="{FD634D05-0696-42B0-809E-92A37EC03100}"/>
     <hyperlink ref="I39" r:id="rId129" xr:uid="{0DDD83AD-5616-4DF4-A79E-5D1AA62710E3}"/>
     <hyperlink ref="G39" r:id="rId130" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/39/The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg/1280px-The_Piazza_Del_Campo_from_Torre_del_Mangia%2C_Siena%2C_Italy.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{AC88C9D7-D842-4DF2-8D24-D182CC0AB952}"/>
+    <hyperlink ref="I31" r:id="rId131" xr:uid="{D1DE0D48-3CB7-4D39-A144-1AF06E9BD6D1}"/>
+    <hyperlink ref="G31" r:id="rId132" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg/1280px-Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{A5AA9B15-4880-44D7-ABB9-1C0AD939DE1D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/quizzes/sculpture-15e.xlsx
+++ b/quizzes/sculpture-15e.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\éléments à uploader\vers quizzes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6316400E-BE00-4371-8CE7-033A2B3A1889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB2A594-E1CC-4715-A84F-0046D2CA3F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="640">
   <si>
     <t>Prénom artiste</t>
   </si>
@@ -226,9 +226,6 @@
     <t>Cathédrale Saint-Zénon</t>
   </si>
   <si>
-    <t>Autel d'argent de saint Jacques</t>
-  </si>
-  <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ec/%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg/960px-%22Ein_herausragendes_Meisterwerk_der_mittelalterlichen_Gold-_und_Silberschmiedekunst%22._01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
   <si>
@@ -1943,9 +1940,6 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg/1280px-Castello%2C_30100_Venezia%2C_Italy_-_panoramio_%28404%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
-  </si>
-  <si>
-    <t>Pistoïa</t>
   </si>
 </sst>
 </file>
@@ -2425,7 +2419,7 @@
         <v>22</v>
       </c>
       <c r="X1" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2436,7 +2430,7 @@
         <v>24</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E2" t="s">
         <v>25</v>
@@ -2495,7 +2489,7 @@
         <v>35</v>
       </c>
       <c r="R3" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="S3" t="s">
         <v>36</v>
@@ -2609,7 +2603,7 @@
         <v>56</v>
       </c>
       <c r="J6" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="K6" t="s">
         <v>57</v>
@@ -2618,7 +2612,7 @@
         <v>58</v>
       </c>
       <c r="R6" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
@@ -2691,31 +2685,28 @@
         <v>65</v>
       </c>
       <c r="E8" t="s">
-        <v>641</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
         <v>67</v>
       </c>
-      <c r="H8" t="s">
+      <c r="G8" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="J8" t="s">
         <v>69</v>
       </c>
-      <c r="J8" t="s">
+      <c r="K8" t="s">
         <v>70</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>72</v>
       </c>
       <c r="R8" t="s">
         <v>50</v>
       </c>
       <c r="S8" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="W8" s="2">
         <v>3</v>
@@ -2729,66 +2720,63 @@
         <v>53</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" t="s">
-        <v>641</v>
+        <v>66</v>
       </c>
       <c r="F9" t="s">
         <v>67</v>
       </c>
-      <c r="H9" t="s">
+      <c r="G9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="I9" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="J9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="R9" t="s">
         <v>30</v>
       </c>
       <c r="S9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="T9" s="2">
         <v>40</v>
       </c>
       <c r="W9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="E10" t="s">
         <v>79</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>80</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
         <v>81</v>
       </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
         <v>82</v>
       </c>
-      <c r="K10" t="s">
+      <c r="L10" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="R10" t="s">
         <v>84</v>
-      </c>
-      <c r="R10" t="s">
-        <v>85</v>
       </c>
       <c r="S10" t="s">
         <v>51</v>
@@ -2805,31 +2793,31 @@
     </row>
     <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" t="s">
         <v>77</v>
       </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
       <c r="D11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" t="s">
+        <v>80</v>
+      </c>
+      <c r="J11" t="s">
         <v>86</v>
       </c>
-      <c r="E11" t="s">
-        <v>80</v>
-      </c>
-      <c r="F11" t="s">
-        <v>81</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="K11" t="s">
         <v>87</v>
       </c>
-      <c r="K11" t="s">
+      <c r="L11" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="R11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S11" t="s">
         <v>51</v>
@@ -2840,34 +2828,34 @@
     </row>
     <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
         <v>77</v>
       </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
       <c r="D12" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12" t="s">
         <v>90</v>
       </c>
-      <c r="E12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>91</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="R12" t="s">
         <v>93</v>
       </c>
-      <c r="R12" t="s">
+      <c r="S12" t="s">
         <v>94</v>
-      </c>
-      <c r="S12" t="s">
-        <v>95</v>
       </c>
       <c r="W12" s="2">
         <v>3</v>
@@ -2875,31 +2863,31 @@
     </row>
     <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" t="s">
         <v>77</v>
       </c>
-      <c r="B13" t="s">
-        <v>78</v>
-      </c>
       <c r="D13" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" t="s">
         <v>80</v>
       </c>
-      <c r="F13" t="s">
-        <v>81</v>
-      </c>
       <c r="J13" t="s">
+        <v>95</v>
+      </c>
+      <c r="K13" t="s">
         <v>96</v>
       </c>
-      <c r="K13" t="s">
+      <c r="L13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>98</v>
-      </c>
       <c r="R13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="S13" t="s">
         <v>51</v>
@@ -2910,13 +2898,13 @@
     </row>
     <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" t="s">
         <v>99</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D14" s="5" t="s">
         <v>100</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="E14" t="s">
         <v>55</v>
@@ -2925,13 +2913,13 @@
         <v>56</v>
       </c>
       <c r="J14" t="s">
+        <v>101</v>
+      </c>
+      <c r="K14" t="s">
         <v>102</v>
       </c>
-      <c r="K14" t="s">
+      <c r="L14" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>104</v>
       </c>
       <c r="R14" t="s">
         <v>30</v>
@@ -2954,10 +2942,10 @@
     </row>
     <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" t="s">
         <v>99</v>
-      </c>
-      <c r="B15" t="s">
-        <v>100</v>
       </c>
       <c r="D15" s="5">
         <v>1455</v>
@@ -2969,13 +2957,13 @@
         <v>56</v>
       </c>
       <c r="J15" t="s">
+        <v>104</v>
+      </c>
+      <c r="K15" t="s">
         <v>105</v>
       </c>
-      <c r="K15" t="s">
+      <c r="L15" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="R15" t="s">
         <v>30</v>
@@ -2998,10 +2986,10 @@
     </row>
     <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" t="s">
         <v>99</v>
-      </c>
-      <c r="B16" t="s">
-        <v>100</v>
       </c>
       <c r="D16" s="5">
         <v>1461</v>
@@ -3013,13 +3001,13 @@
         <v>56</v>
       </c>
       <c r="J16" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" t="s">
         <v>108</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="R16" t="s">
         <v>30</v>
@@ -3039,31 +3027,31 @@
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>98</v>
+      </c>
+      <c r="B17" t="s">
         <v>99</v>
       </c>
-      <c r="B17" t="s">
-        <v>100</v>
-      </c>
       <c r="D17" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E17" t="s">
         <v>55</v>
       </c>
       <c r="F17" t="s">
+        <v>111</v>
+      </c>
+      <c r="J17" t="s">
         <v>112</v>
       </c>
-      <c r="J17" t="s">
+      <c r="K17" t="s">
         <v>113</v>
       </c>
-      <c r="K17" t="s">
+      <c r="L17" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="L17" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="R17" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="S17" t="s">
         <v>51</v>
@@ -3074,31 +3062,31 @@
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" t="s">
         <v>116</v>
       </c>
-      <c r="B18" t="s">
+      <c r="D18" s="5" t="s">
         <v>117</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>118</v>
       </c>
       <c r="E18" t="s">
         <v>55</v>
       </c>
       <c r="F18" t="s">
+        <v>118</v>
+      </c>
+      <c r="J18" t="s">
         <v>119</v>
       </c>
-      <c r="J18" t="s">
+      <c r="K18" t="s">
         <v>120</v>
       </c>
-      <c r="K18" t="s">
+      <c r="L18" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>122</v>
-      </c>
       <c r="R18" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="S18" t="s">
         <v>51</v>
@@ -3118,13 +3106,13 @@
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B19" t="s">
         <v>116</v>
       </c>
-      <c r="B19" t="s">
-        <v>117</v>
-      </c>
       <c r="D19" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
         <v>55</v>
@@ -3133,13 +3121,13 @@
         <v>56</v>
       </c>
       <c r="J19" t="s">
+        <v>123</v>
+      </c>
+      <c r="K19" t="s">
         <v>124</v>
       </c>
-      <c r="K19" t="s">
+      <c r="L19" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>126</v>
       </c>
       <c r="R19" t="s">
         <v>30</v>
@@ -3159,28 +3147,28 @@
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
         <v>116</v>
       </c>
-      <c r="B20" t="s">
-        <v>117</v>
-      </c>
       <c r="D20" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E20" t="s">
         <v>55</v>
       </c>
       <c r="F20" t="s">
+        <v>127</v>
+      </c>
+      <c r="J20" t="s">
         <v>128</v>
       </c>
-      <c r="J20" t="s">
+      <c r="K20" t="s">
         <v>129</v>
       </c>
-      <c r="K20" t="s">
+      <c r="L20" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="R20" t="s">
         <v>30</v>
@@ -3197,31 +3185,31 @@
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>115</v>
+      </c>
+      <c r="B21" t="s">
         <v>116</v>
-      </c>
-      <c r="B21" t="s">
-        <v>117</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>44</v>
       </c>
       <c r="E21" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" t="s">
         <v>132</v>
       </c>
-      <c r="F21" t="s">
+      <c r="J21" t="s">
         <v>133</v>
       </c>
-      <c r="J21" t="s">
+      <c r="K21" t="s">
         <v>134</v>
       </c>
-      <c r="K21" t="s">
+      <c r="L21" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>136</v>
-      </c>
       <c r="R21" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="S21" t="s">
         <v>51</v>
@@ -3235,28 +3223,28 @@
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B22" t="s">
         <v>137</v>
       </c>
-      <c r="B22" t="s">
+      <c r="D22" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" t="s">
         <v>139</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>140</v>
       </c>
-      <c r="F22" t="s">
+      <c r="J22" t="s">
         <v>141</v>
       </c>
-      <c r="J22" t="s">
+      <c r="K22" t="s">
         <v>142</v>
       </c>
-      <c r="K22" t="s">
+      <c r="L22" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="L22" s="4" t="s">
-        <v>144</v>
       </c>
       <c r="R22" t="s">
         <v>30</v>
@@ -3279,31 +3267,31 @@
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>136</v>
+      </c>
+      <c r="B23" t="s">
         <v>137</v>
       </c>
-      <c r="B23" t="s">
-        <v>138</v>
-      </c>
       <c r="D23" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E23" t="s">
         <v>55</v>
       </c>
       <c r="F23" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J23" t="s">
+        <v>145</v>
+      </c>
+      <c r="K23" t="s">
         <v>146</v>
       </c>
-      <c r="K23" t="s">
+      <c r="L23" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="R23" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="S23" t="s">
         <v>51</v>
@@ -3320,31 +3308,31 @@
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" t="s">
         <v>137</v>
       </c>
-      <c r="B24" t="s">
-        <v>138</v>
-      </c>
       <c r="D24" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E24" t="s">
         <v>55</v>
       </c>
       <c r="F24" t="s">
+        <v>149</v>
+      </c>
+      <c r="J24" t="s">
         <v>150</v>
       </c>
-      <c r="J24" t="s">
+      <c r="K24" t="s">
         <v>151</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="L24" s="6" t="s">
-        <v>153</v>
-      </c>
       <c r="R24" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="S24" t="s">
         <v>51</v>
@@ -3361,10 +3349,10 @@
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>136</v>
+      </c>
+      <c r="B25" t="s">
         <v>137</v>
-      </c>
-      <c r="B25" t="s">
-        <v>138</v>
       </c>
       <c r="D25" s="5">
         <v>1464</v>
@@ -3376,10 +3364,10 @@
         <v>56</v>
       </c>
       <c r="J25" t="s">
+        <v>153</v>
+      </c>
+      <c r="L25" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="L25" s="4" t="s">
-        <v>155</v>
       </c>
       <c r="R25" s="8" t="s">
         <v>30</v>
@@ -3399,28 +3387,28 @@
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s">
         <v>156</v>
       </c>
-      <c r="B26" t="s">
+      <c r="D26" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="E26" t="s">
         <v>158</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>159</v>
       </c>
-      <c r="F26" t="s">
+      <c r="J26" t="s">
         <v>160</v>
       </c>
-      <c r="J26" t="s">
+      <c r="L26" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="L26" s="6" t="s">
-        <v>162</v>
-      </c>
       <c r="R26" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="S26" t="s">
         <v>31</v>
@@ -3440,37 +3428,37 @@
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" t="s">
         <v>156</v>
       </c>
-      <c r="B27" t="s">
-        <v>157</v>
-      </c>
       <c r="D27" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="E27" t="s">
         <v>163</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>164</v>
       </c>
-      <c r="F27" t="s">
+      <c r="J27" t="s">
         <v>165</v>
       </c>
-      <c r="J27" t="s">
+      <c r="K27" t="s">
         <v>166</v>
       </c>
-      <c r="K27" t="s">
+      <c r="L27" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="R27" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="S27" t="s">
         <v>31</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="U27" s="2">
         <v>230</v>
@@ -3484,13 +3472,13 @@
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>155</v>
+      </c>
+      <c r="B28" t="s">
         <v>156</v>
       </c>
-      <c r="B28" t="s">
-        <v>157</v>
-      </c>
       <c r="D28" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E28" t="s">
         <v>55</v>
@@ -3499,22 +3487,22 @@
         <v>56</v>
       </c>
       <c r="J28" t="s">
+        <v>170</v>
+      </c>
+      <c r="K28" t="s">
         <v>171</v>
       </c>
-      <c r="K28" t="s">
+      <c r="L28" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="L28" s="4" t="s">
-        <v>173</v>
-      </c>
       <c r="R28" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="S28" t="s">
         <v>31</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="U28" s="2">
         <v>34</v>
@@ -3528,13 +3516,13 @@
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>174</v>
+      </c>
+      <c r="B29" t="s">
         <v>175</v>
       </c>
-      <c r="B29" t="s">
-        <v>176</v>
-      </c>
       <c r="D29" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E29" t="s">
         <v>55</v>
@@ -3543,13 +3531,13 @@
         <v>56</v>
       </c>
       <c r="J29" t="s">
+        <v>176</v>
+      </c>
+      <c r="K29" t="s">
+        <v>176</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="K29" t="s">
-        <v>177</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>178</v>
       </c>
       <c r="R29" t="s">
         <v>30</v>
@@ -3572,40 +3560,40 @@
     </row>
     <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B30" t="s">
         <v>175</v>
       </c>
-      <c r="B30" t="s">
-        <v>176</v>
-      </c>
       <c r="D30" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E30" t="s">
         <v>55</v>
       </c>
       <c r="F30" t="s">
+        <v>179</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="J30" t="s">
         <v>181</v>
       </c>
-      <c r="J30" t="s">
+      <c r="K30" t="s">
         <v>182</v>
       </c>
-      <c r="K30" t="s">
+      <c r="L30" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="L30" s="4" t="s">
+      <c r="M30" t="s">
         <v>184</v>
       </c>
-      <c r="M30" t="s">
+      <c r="N30" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="N30" s="1" t="s">
+      <c r="R30" t="s">
         <v>186</v>
-      </c>
-      <c r="R30" t="s">
-        <v>187</v>
       </c>
       <c r="S30" t="s">
         <v>31</v>
@@ -3625,43 +3613,43 @@
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B31" t="s">
         <v>175</v>
       </c>
-      <c r="B31" t="s">
-        <v>176</v>
-      </c>
       <c r="D31" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E31" t="s">
         <v>25</v>
       </c>
       <c r="F31" t="s">
+        <v>188</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="J31" t="s">
         <v>189</v>
       </c>
-      <c r="G31" s="6" t="s">
-        <v>640</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>639</v>
-      </c>
-      <c r="J31" t="s">
+      <c r="K31" t="s">
         <v>190</v>
       </c>
-      <c r="K31" t="s">
+      <c r="L31" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="L31" s="4" t="s">
-        <v>192</v>
-      </c>
       <c r="R31" t="s">
+        <v>629</v>
+      </c>
+      <c r="S31" t="s">
         <v>630</v>
       </c>
-      <c r="S31" t="s">
-        <v>631</v>
-      </c>
       <c r="T31" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="U31" s="2">
         <v>380</v>
@@ -3675,31 +3663,31 @@
     </row>
     <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>174</v>
+      </c>
+      <c r="B32" t="s">
         <v>175</v>
       </c>
-      <c r="B32" t="s">
-        <v>176</v>
-      </c>
       <c r="D32" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E32" t="s">
         <v>55</v>
       </c>
       <c r="F32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J32" t="s">
+        <v>193</v>
+      </c>
+      <c r="K32" t="s">
         <v>194</v>
       </c>
-      <c r="K32" t="s">
+      <c r="L32" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="L32" s="4" t="s">
+      <c r="M32" t="s">
         <v>196</v>
-      </c>
-      <c r="M32" t="s">
-        <v>197</v>
       </c>
       <c r="R32" t="s">
         <v>30</v>
@@ -3722,13 +3710,13 @@
     </row>
     <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" t="s">
         <v>175</v>
       </c>
-      <c r="B33" t="s">
-        <v>176</v>
-      </c>
       <c r="D33" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E33" t="s">
         <v>55</v>
@@ -3737,13 +3725,13 @@
         <v>56</v>
       </c>
       <c r="J33" t="s">
+        <v>197</v>
+      </c>
+      <c r="K33" t="s">
         <v>198</v>
       </c>
-      <c r="K33" t="s">
+      <c r="L33" s="4" t="s">
         <v>199</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>200</v>
       </c>
       <c r="R33" t="s">
         <v>30</v>
@@ -3766,37 +3754,37 @@
     </row>
     <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B34" t="s">
         <v>175</v>
       </c>
-      <c r="B34" t="s">
-        <v>176</v>
-      </c>
       <c r="D34" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E34" t="s">
         <v>55</v>
       </c>
       <c r="F34" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H34" t="s">
+        <v>201</v>
+      </c>
+      <c r="J34" t="s">
         <v>202</v>
       </c>
-      <c r="J34" t="s">
+      <c r="K34" t="s">
         <v>203</v>
       </c>
-      <c r="K34" t="s">
+      <c r="L34" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="L34" s="6" t="s">
+      <c r="R34" t="s">
+        <v>84</v>
+      </c>
+      <c r="S34" t="s">
         <v>205</v>
-      </c>
-      <c r="R34" t="s">
-        <v>85</v>
-      </c>
-      <c r="S34" t="s">
-        <v>206</v>
       </c>
       <c r="T34" s="2">
         <v>540</v>
@@ -3810,22 +3798,22 @@
     </row>
     <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>206</v>
+      </c>
+      <c r="B35" t="s">
         <v>207</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>208</v>
       </c>
-      <c r="C35" t="s">
+      <c r="D35" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="E35" t="s">
         <v>210</v>
       </c>
-      <c r="E35" t="s">
+      <c r="F35" t="s">
         <v>211</v>
-      </c>
-      <c r="F35" t="s">
-        <v>212</v>
       </c>
       <c r="J35" t="s">
         <v>47</v>
@@ -3834,13 +3822,13 @@
         <v>48</v>
       </c>
       <c r="L35" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="R35" t="s">
         <v>213</v>
       </c>
-      <c r="R35" t="s">
+      <c r="S35" t="s">
         <v>214</v>
-      </c>
-      <c r="S35" t="s">
-        <v>215</v>
       </c>
       <c r="T35" s="2">
         <v>165</v>
@@ -3857,34 +3845,34 @@
     </row>
     <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B36" t="s">
         <v>207</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>208</v>
       </c>
-      <c r="C36" t="s">
-        <v>209</v>
-      </c>
       <c r="D36" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" t="s">
+        <v>210</v>
+      </c>
+      <c r="F36" t="s">
         <v>216</v>
       </c>
-      <c r="E36" t="s">
-        <v>211</v>
-      </c>
-      <c r="F36" t="s">
+      <c r="J36" t="s">
         <v>217</v>
       </c>
-      <c r="J36" t="s">
+      <c r="K36" t="s">
         <v>218</v>
       </c>
-      <c r="K36" t="s">
+      <c r="L36" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="L36" s="6" t="s">
-        <v>220</v>
-      </c>
       <c r="R36" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="S36" t="s">
         <v>51</v>
@@ -3904,37 +3892,37 @@
     </row>
     <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>206</v>
+      </c>
+      <c r="B37" t="s">
         <v>207</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>208</v>
       </c>
-      <c r="C37" t="s">
-        <v>209</v>
-      </c>
       <c r="D37" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E37" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F37" t="s">
+        <v>220</v>
+      </c>
+      <c r="J37" t="s">
         <v>221</v>
       </c>
-      <c r="J37" t="s">
+      <c r="K37" t="s">
         <v>222</v>
       </c>
-      <c r="K37" t="s">
+      <c r="L37" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="L37" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="R37" t="s">
         <v>30</v>
       </c>
       <c r="S37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T37" s="2">
         <v>55</v>
@@ -3951,37 +3939,37 @@
     </row>
     <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>206</v>
+      </c>
+      <c r="B38" t="s">
         <v>207</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>208</v>
       </c>
-      <c r="C38" t="s">
-        <v>209</v>
-      </c>
       <c r="D38" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="E38" t="s">
         <v>225</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>226</v>
       </c>
-      <c r="F38" t="s">
+      <c r="J38" t="s">
         <v>227</v>
       </c>
-      <c r="J38" t="s">
+      <c r="K38" t="s">
         <v>228</v>
       </c>
-      <c r="K38" t="s">
+      <c r="L38" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="R38" t="s">
         <v>30</v>
       </c>
       <c r="S38" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="T38" s="2">
         <v>50</v>
@@ -3998,37 +3986,37 @@
     </row>
     <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>230</v>
+      </c>
+      <c r="B39" t="s">
         <v>231</v>
       </c>
-      <c r="B39" t="s">
+      <c r="D39" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="E39" t="s">
         <v>233</v>
       </c>
-      <c r="E39" t="s">
+      <c r="F39" t="s">
         <v>234</v>
       </c>
-      <c r="F39" t="s">
+      <c r="G39" s="6" t="s">
+        <v>636</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>635</v>
+      </c>
+      <c r="J39" t="s">
         <v>235</v>
       </c>
-      <c r="G39" s="6" t="s">
-        <v>637</v>
-      </c>
-      <c r="I39" s="6" t="s">
-        <v>636</v>
-      </c>
-      <c r="J39" t="s">
+      <c r="K39" t="s">
         <v>236</v>
       </c>
-      <c r="K39" t="s">
+      <c r="L39" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="L39" s="4" t="s">
-        <v>238</v>
-      </c>
       <c r="R39" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="S39" t="s">
         <v>51</v>
@@ -4048,31 +4036,31 @@
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>230</v>
+      </c>
+      <c r="B40" t="s">
         <v>231</v>
       </c>
-      <c r="B40" t="s">
-        <v>232</v>
-      </c>
       <c r="D40" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" t="s">
+        <v>79</v>
+      </c>
+      <c r="F40" t="s">
+        <v>80</v>
+      </c>
+      <c r="J40" t="s">
         <v>239</v>
       </c>
-      <c r="E40" t="s">
-        <v>80</v>
-      </c>
-      <c r="F40" t="s">
-        <v>81</v>
-      </c>
-      <c r="J40" t="s">
+      <c r="K40" t="s">
         <v>240</v>
       </c>
-      <c r="K40" t="s">
+      <c r="L40" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="L40" s="4" t="s">
-        <v>242</v>
-      </c>
       <c r="R40" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="S40" t="s">
         <v>51</v>
@@ -4092,37 +4080,37 @@
     </row>
     <row r="41" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>230</v>
+      </c>
+      <c r="B41" t="s">
         <v>231</v>
       </c>
-      <c r="B41" t="s">
-        <v>232</v>
-      </c>
       <c r="D41" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="E41" t="s">
+        <v>210</v>
+      </c>
+      <c r="F41" t="s">
         <v>243</v>
       </c>
-      <c r="E41" t="s">
-        <v>211</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="H41" t="s">
         <v>244</v>
       </c>
-      <c r="H41" t="s">
+      <c r="J41" t="s">
         <v>245</v>
       </c>
-      <c r="J41" t="s">
+      <c r="K41" t="s">
         <v>246</v>
       </c>
-      <c r="K41" t="s">
+      <c r="L41" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="L41" s="4" t="s">
+      <c r="R41" t="s">
+        <v>612</v>
+      </c>
+      <c r="S41" t="s">
         <v>248</v>
-      </c>
-      <c r="R41" t="s">
-        <v>613</v>
-      </c>
-      <c r="S41" t="s">
-        <v>249</v>
       </c>
       <c r="T41" s="2">
         <v>1800</v>
@@ -4139,40 +4127,40 @@
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>230</v>
+      </c>
+      <c r="B42" t="s">
         <v>231</v>
       </c>
-      <c r="B42" t="s">
-        <v>232</v>
-      </c>
       <c r="D42" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="E42" t="s">
+        <v>210</v>
+      </c>
+      <c r="F42" t="s">
+        <v>243</v>
+      </c>
+      <c r="H42" t="s">
+        <v>246</v>
+      </c>
+      <c r="J42" t="s">
         <v>250</v>
       </c>
-      <c r="E42" t="s">
-        <v>211</v>
-      </c>
-      <c r="F42" t="s">
-        <v>244</v>
-      </c>
-      <c r="H42" t="s">
-        <v>247</v>
-      </c>
-      <c r="J42" t="s">
+      <c r="K42" t="s">
         <v>251</v>
       </c>
-      <c r="K42" t="s">
+      <c r="L42" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="L42" s="6" t="s">
-        <v>253</v>
-      </c>
       <c r="M42" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="R42" t="s">
         <v>50</v>
       </c>
       <c r="S42" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="T42" s="2">
         <v>99</v>
@@ -4189,34 +4177,34 @@
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>230</v>
+      </c>
+      <c r="B43" t="s">
         <v>231</v>
       </c>
-      <c r="B43" t="s">
-        <v>232</v>
-      </c>
       <c r="D43" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E43" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" t="s">
         <v>254</v>
       </c>
-      <c r="E43" t="s">
-        <v>80</v>
-      </c>
-      <c r="F43" t="s">
+      <c r="H43" t="s">
         <v>255</v>
       </c>
-      <c r="H43" t="s">
+      <c r="J43" t="s">
         <v>256</v>
       </c>
-      <c r="J43" t="s">
+      <c r="K43" t="s">
         <v>257</v>
       </c>
-      <c r="K43" t="s">
+      <c r="L43" s="6" t="s">
         <v>258</v>
       </c>
-      <c r="L43" s="6" t="s">
-        <v>259</v>
-      </c>
       <c r="R43" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="S43" t="s">
         <v>51</v>
@@ -4233,34 +4221,34 @@
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>230</v>
+      </c>
+      <c r="B44" t="s">
         <v>231</v>
       </c>
-      <c r="B44" t="s">
-        <v>232</v>
-      </c>
       <c r="D44" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="E44" t="s">
+        <v>79</v>
+      </c>
+      <c r="F44" t="s">
         <v>254</v>
       </c>
-      <c r="E44" t="s">
-        <v>80</v>
-      </c>
-      <c r="F44" t="s">
+      <c r="H44" t="s">
         <v>255</v>
       </c>
-      <c r="H44" t="s">
-        <v>256</v>
-      </c>
       <c r="J44" t="s">
+        <v>259</v>
+      </c>
+      <c r="K44" t="s">
         <v>260</v>
       </c>
-      <c r="K44" t="s">
+      <c r="L44" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="R44" t="s">
         <v>262</v>
-      </c>
-      <c r="R44" t="s">
-        <v>263</v>
       </c>
       <c r="S44" t="s">
         <v>51</v>
@@ -4277,31 +4265,31 @@
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B45" t="s">
+        <v>263</v>
+      </c>
+      <c r="D45" s="5" t="s">
         <v>264</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>265</v>
       </c>
       <c r="E45" t="s">
         <v>55</v>
       </c>
       <c r="F45" t="s">
+        <v>265</v>
+      </c>
+      <c r="J45" t="s">
         <v>266</v>
       </c>
-      <c r="J45" t="s">
+      <c r="L45" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="R45" t="s">
         <v>50</v>
       </c>
       <c r="S45" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="T45" s="2">
         <v>100</v>
@@ -4318,34 +4306,34 @@
     </row>
     <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B46" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D46" s="5">
         <v>1520</v>
       </c>
       <c r="E46" t="s">
+        <v>269</v>
+      </c>
+      <c r="F46" t="s">
+        <v>603</v>
+      </c>
+      <c r="J46" t="s">
         <v>270</v>
       </c>
-      <c r="F46" t="s">
-        <v>604</v>
-      </c>
-      <c r="J46" t="s">
+      <c r="K46" t="s">
         <v>271</v>
       </c>
-      <c r="K46" t="s">
+      <c r="L46" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="R46" t="s">
         <v>50</v>
       </c>
       <c r="S46" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T46" s="2">
         <v>80</v>
@@ -4362,34 +4350,34 @@
     </row>
     <row r="47" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E47" t="s">
         <v>55</v>
       </c>
       <c r="F47" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J47" t="s">
+        <v>274</v>
+      </c>
+      <c r="K47" t="s">
         <v>275</v>
       </c>
-      <c r="K47" t="s">
+      <c r="L47" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="L47" s="6" t="s">
-        <v>277</v>
-      </c>
       <c r="R47" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="S47" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T47" s="2">
         <v>270</v>
@@ -4406,34 +4394,34 @@
     </row>
     <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B48" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D48" s="5">
         <v>1489</v>
       </c>
       <c r="E48" t="s">
+        <v>277</v>
+      </c>
+      <c r="F48" t="s">
         <v>278</v>
       </c>
-      <c r="F48" t="s">
+      <c r="G48" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="J48" t="s">
         <v>280</v>
       </c>
-      <c r="J48" t="s">
+      <c r="L48" s="1" t="s">
         <v>281</v>
-      </c>
-      <c r="L48" s="1" t="s">
-        <v>282</v>
       </c>
       <c r="R48" t="s">
         <v>50</v>
       </c>
       <c r="S48" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T48" s="2">
         <v>163</v>
@@ -4450,37 +4438,37 @@
     </row>
     <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B49" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D49" s="5">
         <v>1475</v>
       </c>
       <c r="E49" t="s">
+        <v>282</v>
+      </c>
+      <c r="F49" t="s">
         <v>283</v>
       </c>
-      <c r="F49" t="s">
+      <c r="J49" t="s">
         <v>284</v>
       </c>
-      <c r="J49" t="s">
+      <c r="K49" t="s">
         <v>285</v>
       </c>
-      <c r="K49" t="s">
+      <c r="L49" s="6" t="s">
         <v>286</v>
-      </c>
-      <c r="L49" s="6" t="s">
-        <v>287</v>
       </c>
       <c r="R49" t="s">
         <v>50</v>
       </c>
       <c r="S49" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T49" s="2" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="U49" s="2">
         <v>210</v>
@@ -4494,34 +4482,34 @@
     </row>
     <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E50" t="s">
+        <v>288</v>
+      </c>
+      <c r="F50" t="s">
         <v>289</v>
       </c>
-      <c r="F50" t="s">
+      <c r="J50" t="s">
         <v>290</v>
       </c>
-      <c r="J50" t="s">
+      <c r="K50" t="s">
         <v>291</v>
       </c>
-      <c r="K50" t="s">
+      <c r="L50" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="R50" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="S50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T50" s="2">
         <v>370</v>
@@ -4538,10 +4526,10 @@
     </row>
     <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B51" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D51" s="5">
         <v>1489</v>
@@ -4550,19 +4538,19 @@
         <v>55</v>
       </c>
       <c r="F51" t="s">
+        <v>293</v>
+      </c>
+      <c r="J51" t="s">
         <v>294</v>
       </c>
-      <c r="J51" t="s">
+      <c r="L51" s="1" t="s">
         <v>295</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>296</v>
       </c>
       <c r="R51" t="s">
         <v>50</v>
       </c>
       <c r="S51" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T51" s="2">
         <v>44</v>
@@ -4579,13 +4567,13 @@
     </row>
     <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B52" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E52" t="s">
         <v>37</v>
@@ -4594,17 +4582,17 @@
         <v>38</v>
       </c>
       <c r="J52" t="s">
+        <v>297</v>
+      </c>
+      <c r="L52" s="6" t="s">
         <v>298</v>
-      </c>
-      <c r="L52" s="6" t="s">
-        <v>299</v>
       </c>
       <c r="P52" s="7"/>
       <c r="R52" s="7" t="s">
         <v>42</v>
       </c>
       <c r="S52" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T52" s="2">
         <v>128</v>
@@ -4618,31 +4606,31 @@
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>299</v>
+      </c>
+      <c r="B53" t="s">
+        <v>263</v>
+      </c>
+      <c r="D53" s="5" t="s">
         <v>300</v>
-      </c>
-      <c r="B53" t="s">
-        <v>264</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>301</v>
       </c>
       <c r="E53" t="s">
         <v>55</v>
       </c>
       <c r="F53" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="J53" t="s">
+        <v>301</v>
+      </c>
+      <c r="K53" t="s">
         <v>302</v>
       </c>
-      <c r="K53" t="s">
+      <c r="L53" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="L53" s="4" t="s">
+      <c r="R53" t="s">
         <v>304</v>
-      </c>
-      <c r="R53" t="s">
-        <v>305</v>
       </c>
       <c r="S53" t="s">
         <v>51</v>
@@ -4662,34 +4650,34 @@
     </row>
     <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B54" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E54" t="s">
         <v>55</v>
       </c>
       <c r="F54" t="s">
+        <v>306</v>
+      </c>
+      <c r="J54" t="s">
         <v>307</v>
       </c>
-      <c r="J54" t="s">
+      <c r="K54" t="s">
         <v>308</v>
       </c>
-      <c r="K54" t="s">
+      <c r="L54" s="4" t="s">
         <v>309</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>310</v>
       </c>
       <c r="R54" t="s">
         <v>50</v>
       </c>
       <c r="S54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T54" s="2">
         <v>200</v>
@@ -4706,28 +4694,28 @@
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B55" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E55" t="s">
         <v>55</v>
       </c>
       <c r="F55" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J55" t="s">
+        <v>311</v>
+      </c>
+      <c r="K55" t="s">
         <v>312</v>
       </c>
-      <c r="K55" t="s">
+      <c r="L55" s="4" t="s">
         <v>313</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>314</v>
       </c>
       <c r="R55" t="s">
         <v>50</v>
@@ -4750,34 +4738,34 @@
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B56" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E56" t="s">
         <v>55</v>
       </c>
       <c r="F56" t="s">
+        <v>315</v>
+      </c>
+      <c r="J56" t="s">
         <v>316</v>
       </c>
-      <c r="J56" t="s">
+      <c r="K56" t="s">
         <v>317</v>
       </c>
-      <c r="K56" t="s">
+      <c r="L56" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="R56" t="s">
         <v>50</v>
       </c>
       <c r="S56" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="U56" s="2">
         <v>120</v>
@@ -4791,37 +4779,37 @@
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B57" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D57" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E57" t="s">
         <v>320</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>321</v>
       </c>
-      <c r="F57" t="s">
+      <c r="J57" t="s">
         <v>322</v>
       </c>
-      <c r="J57" t="s">
+      <c r="K57" t="s">
         <v>323</v>
       </c>
-      <c r="K57" t="s">
+      <c r="L57" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="L57" s="4" t="s">
+      <c r="M57" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="M57" s="1" t="s">
-        <v>326</v>
-      </c>
       <c r="R57" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="S57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T57" s="2">
         <v>150</v>
@@ -4838,34 +4826,34 @@
     </row>
     <row r="58" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B58" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D58" t="s">
+        <v>326</v>
+      </c>
+      <c r="E58" t="s">
         <v>327</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>328</v>
       </c>
-      <c r="F58" t="s">
+      <c r="J58" t="s">
         <v>329</v>
       </c>
-      <c r="J58" t="s">
+      <c r="K58" t="s">
         <v>330</v>
       </c>
-      <c r="K58" t="s">
+      <c r="L58" s="1" t="s">
         <v>331</v>
-      </c>
-      <c r="L58" s="1" t="s">
-        <v>332</v>
       </c>
       <c r="R58" t="s">
         <v>50</v>
       </c>
       <c r="S58" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T58" s="2">
         <v>118</v>
@@ -4882,13 +4870,13 @@
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B59" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D59" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E59" t="s">
         <v>55</v>
@@ -4897,19 +4885,19 @@
         <v>56</v>
       </c>
       <c r="J59" t="s">
+        <v>332</v>
+      </c>
+      <c r="K59" t="s">
         <v>333</v>
       </c>
-      <c r="K59" t="s">
+      <c r="L59" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>335</v>
       </c>
       <c r="R59" t="s">
         <v>50</v>
       </c>
       <c r="S59" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T59" s="2">
         <v>57</v>
@@ -4920,13 +4908,13 @@
     </row>
     <row r="60" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B60" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D60" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E60" t="s">
         <v>55</v>
@@ -4935,19 +4923,19 @@
         <v>56</v>
       </c>
       <c r="J60" t="s">
+        <v>335</v>
+      </c>
+      <c r="K60" t="s">
+        <v>333</v>
+      </c>
+      <c r="L60" s="6" t="s">
         <v>336</v>
-      </c>
-      <c r="K60" t="s">
-        <v>334</v>
-      </c>
-      <c r="L60" s="6" t="s">
-        <v>337</v>
       </c>
       <c r="R60" t="s">
         <v>50</v>
       </c>
       <c r="S60" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="T60" s="2">
         <v>70</v>
@@ -4961,16 +4949,16 @@
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>337</v>
+      </c>
+      <c r="B61" t="s">
         <v>338</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
+        <v>625</v>
+      </c>
+      <c r="D61" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="C61" t="s">
-        <v>626</v>
-      </c>
-      <c r="D61" s="5" t="s">
-        <v>340</v>
       </c>
       <c r="E61" t="s">
         <v>55</v>
@@ -4979,13 +4967,13 @@
         <v>56</v>
       </c>
       <c r="J61" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K61" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="R61" t="s">
         <v>30</v>
@@ -4994,7 +4982,7 @@
         <v>31</v>
       </c>
       <c r="T61" s="2" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="U61" s="2">
         <v>51</v>
@@ -5008,16 +4996,16 @@
     </row>
     <row r="62" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>337</v>
+      </c>
+      <c r="B62" t="s">
         <v>338</v>
       </c>
-      <c r="B62" t="s">
-        <v>339</v>
-      </c>
       <c r="C62" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E62" t="s">
         <v>55</v>
@@ -5026,13 +5014,13 @@
         <v>56</v>
       </c>
       <c r="J62" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="K62" t="s">
+        <v>343</v>
+      </c>
+      <c r="L62" s="4" t="s">
         <v>344</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>345</v>
       </c>
